--- a/TelemDefinition/DownlinkSpecPacsat.xlsx
+++ b/TelemDefinition/DownlinkSpecPacsat.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="322">
   <si>
     <t xml:space="preserve">//</t>
   </si>
@@ -170,249 +170,300 @@
     <t xml:space="preserve">FSAvailable</t>
   </si>
   <si>
+    <t xml:space="preserve">KB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Space left in the file system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File Storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Files</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FSTotalFiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total files in the file system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bytes Queued</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UploadQueueBytes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bytes reserved by the upload queue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Files Queued</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UploadQueueFiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Files in the tmp folder queued to upload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RF Power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TXPower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uint8_t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TX RF Power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tx Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TXPwrMode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TX Power Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rx0 Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX0PwrMode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX0 Power Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rx1 Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX1PwrMode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX1Power Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rx2 Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX2PwrMode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX2 Power Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rx3 Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX3PwrMode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX3 Power Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rx0 RSSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX0RSSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dBm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSSI for Receiver 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rx1 RSSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX1RSSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSSI for Receiver 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rx2 RSSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX2RSSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSSI for receiver 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rx3 RSSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX3RSSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSSI for receiver 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IHUTemp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA Temp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATemp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power Amplifier Temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power Temp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PowerTemp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power Supply Temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Totals:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commonPayload2 is common to realtime,  hi/low, and WOD,  but it is not compared for hi/low.  It is fetched fresh.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structure: commonRtWodPayload_t,file:common2Downlink.h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ifdef LEGACY_IHU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto Safe Allowed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AutoSafeAllowed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autosafe Allowed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto Safe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AutoSafeModeActive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autosafe Mode Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PB Enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pbEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pacsat Broadcast is available for use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uplink Enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uplinkEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pacsat file upload is available for use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digi Enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DigiEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Packet Digipeater is enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pad155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pad202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">endif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ifdef RTIHU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LogLevel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The current logging level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telem &amp; Control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time Period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TimePeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The period between time packets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telem Period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TelemPeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The period between telemetry packets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WOD Period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WodPeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The time between WOD saves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max WOD Size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxWodFileSize</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bytes</t>
   </si>
   <si>
-    <t xml:space="preserve">Space left in the file system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File Storage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Files</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FSTotalFiles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total files in the file system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bytes Queued</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UploadQueueBytes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bytes reserved by the upload queue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Files Queued</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UploadQueueFiles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Files in the tmp folder queued to upload</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RF Power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXPower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uint8_t</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TX RF Power</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TXPwrMode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TX Power Mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RX0PwrMode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RX0 Power Mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RX1PwrMode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RX1Power Mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RX2PwrMode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RX2 Power Mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RX3PwrMode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RX3 Power Mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RSSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RX0RSSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dBm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RSSI for Receiver 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RX1RSSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RSSI for Receiver 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RX2RSSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RSSI for receiver 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RX3RSSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RSSI for receiver 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temperature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHUTemp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer temperature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Totals:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commonPayload2 is common to realtime,  hi/low, and WOD,  but it is not compared for hi/low.  It is fetched fresh.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Structure: commonRtWodPayload_t,file:common2Downlink.h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ifdef LEGACY_IHU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto Safe Allowed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AutoSafeAllowed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autosafe Allowed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto Safe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AutoSafeModeActive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autosafe Mode Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PB Enabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pbEnabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pacsat Broadcast is available for use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uplink Enabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uplinkEnabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pacsat file upload is available for use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pad155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pad202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">endif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ifdef RTIHU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LogLevel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The current logging level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Telem &amp; Control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time Period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TimePeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The period between time packets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Telem Period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TelemPeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The period between telemetry packets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WOD Period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WodPeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The time between WOD saves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max WOD Size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxWodFileSize</t>
-  </si>
-  <si>
     <t xml:space="preserve">The maximum size of a WOD file before it is added to the directory</t>
   </si>
   <si>
@@ -452,6 +503,15 @@
     <t xml:space="preserve">The period between uplink status packets</t>
   </si>
   <si>
+    <t xml:space="preserve">SW Cmd Cnt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">swCmdCnt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of software commands since last reset</t>
+  </si>
+  <si>
     <t xml:space="preserve">Min/Max Resets</t>
   </si>
   <si>
@@ -461,22 +521,13 @@
     <t xml:space="preserve">Number of times command stations reset stored telemetry</t>
   </si>
   <si>
-    <t xml:space="preserve">Commands</t>
+    <t xml:space="preserve">Cmd Ring</t>
   </si>
   <si>
     <t xml:space="preserve">swCmds</t>
   </si>
   <si>
-    <t xml:space="preserve">Command Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SW Cmd Cnt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">swCmdCnt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of software commands since last reset</t>
+    <t xml:space="preserve">Command Ring showing last 4 commands</t>
   </si>
   <si>
     <t xml:space="preserve">MRAM Status</t>
@@ -485,7 +536,7 @@
     <t xml:space="preserve">MRAMstatus</t>
   </si>
   <si>
-    <t xml:space="preserve">TBD</t>
+    <t xml:space="preserve">Status of the MRAM</t>
   </si>
   <si>
     <t xml:space="preserve">Total Length</t>
@@ -2180,10 +2231,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="30" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D27" s="30" t="n">
         <v>8</v>
@@ -2199,7 +2250,7 @@
         <v>34</v>
       </c>
       <c r="I27" s="23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J27" s="4" t="n">
         <f aca="false">J26+D26</f>
@@ -2232,10 +2283,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="30" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D28" s="30" t="n">
         <v>8</v>
@@ -2251,7 +2302,7 @@
         <v>34</v>
       </c>
       <c r="I28" s="23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J28" s="4" t="n">
         <f aca="false">J27+D27</f>
@@ -2284,10 +2335,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="30" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D29" s="30" t="n">
         <v>8</v>
@@ -2303,7 +2354,7 @@
         <v>34</v>
       </c>
       <c r="I29" s="23" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J29" s="4" t="n">
         <f aca="false">J28+D28</f>
@@ -2336,10 +2387,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="30" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C30" s="30" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D30" s="30" t="n">
         <v>8</v>
@@ -2355,7 +2406,7 @@
         <v>34</v>
       </c>
       <c r="I30" s="23" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J30" s="4" t="n">
         <f aca="false">J29+D29</f>
@@ -2388,10 +2439,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="30" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D31" s="30" t="n">
         <v>8</v>
@@ -2404,10 +2455,10 @@
         <v>6</v>
       </c>
       <c r="H31" s="22" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I31" s="23" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J31" s="4" t="n">
         <f aca="false">J30+D30</f>
@@ -2440,10 +2491,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="30" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D32" s="30" t="n">
         <v>8</v>
@@ -2456,10 +2507,10 @@
         <v>6</v>
       </c>
       <c r="H32" s="22" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I32" s="23" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J32" s="4" t="n">
         <f aca="false">J31+D31</f>
@@ -2492,10 +2543,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="30" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D33" s="30" t="n">
         <v>8</v>
@@ -2508,10 +2559,10 @@
         <v>6</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I33" s="23" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="J33" s="4" t="n">
         <f aca="false">J32+D32</f>
@@ -2544,10 +2595,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="30" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D34" s="30" t="n">
         <v>8</v>
@@ -2560,10 +2611,10 @@
         <v>6</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I34" s="23" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="J34" s="4" t="n">
         <f aca="false">J33+D33</f>
@@ -2596,10 +2647,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="30" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C35" s="30" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D35" s="30" t="n">
         <v>8</v>
@@ -2612,10 +2663,10 @@
         <v>9</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="I35" s="23" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="J35" s="4" t="n">
         <f aca="false">J34+D34</f>
@@ -2634,7 +2685,7 @@
         <v>4.75</v>
       </c>
       <c r="N35" s="5" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="O35" s="24" t="n">
         <v>3</v>
@@ -2647,18 +2698,27 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" s="30"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="23"/>
+      <c r="B36" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="C36" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="D36" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="E36" s="23" t="s">
+        <v>25</v>
+      </c>
       <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="23"/>
+      <c r="G36" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="I36" s="23" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="J36" s="4" t="n">
         <f aca="false">J35+D35</f>
@@ -2676,40 +2736,103 @@
         <f aca="false">J36/32</f>
         <v>5</v>
       </c>
+      <c r="N36" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="O36" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="P36" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q36" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="23"/>
+      <c r="B37" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="C37" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="D37" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="E37" s="23" t="s">
+        <v>25</v>
+      </c>
       <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="23"/>
-      <c r="I37" s="23"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="27"/>
-      <c r="M37" s="27"/>
-    </row>
-    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G37" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I37" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <f aca="false">J36+D36</f>
+        <v>168</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <f aca="false">J37/8</f>
+        <v>21</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <f aca="false">J37/16</f>
+        <v>10.5</v>
+      </c>
+      <c r="M37" s="5" t="n">
+        <f aca="false">J37/32</f>
+        <v>5.25</v>
+      </c>
+      <c r="N37" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="O37" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="P37" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q37" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="8"/>
+        <v>44</v>
+      </c>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <f aca="false">J37+D37</f>
+        <v>176</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <f aca="false">J38/8</f>
+        <v>22</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <f aca="false">J38/16</f>
+        <v>11</v>
+      </c>
+      <c r="M38" s="5" t="n">
+        <f aca="false">J38/32</f>
+        <v>5.5</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="B39" s="30"/>
       <c r="C39" s="30"/>
       <c r="D39" s="30"/>
@@ -2723,132 +2846,61 @@
       <c r="L39" s="27"/>
       <c r="M39" s="27"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="23"/>
-      <c r="J40" s="28"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="27"/>
-      <c r="M40" s="27"/>
+        <v>0</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="C41" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="D41" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="23" t="s">
-        <v>25</v>
-      </c>
+      <c r="A41" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="23"/>
       <c r="F41" s="23"/>
-      <c r="G41" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I41" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="J41" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="27" t="n">
-        <f aca="false">J41/8</f>
-        <v>0</v>
-      </c>
-      <c r="L41" s="27" t="n">
-        <f aca="false">J41/16</f>
-        <v>0</v>
-      </c>
-      <c r="M41" s="27" t="n">
-        <f aca="false">J41/32</f>
-        <v>0</v>
-      </c>
-      <c r="N41" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="O41" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="P41" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q41" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="G41" s="23"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="23"/>
+      <c r="J41" s="28"/>
+      <c r="K41" s="27"/>
+      <c r="L41" s="27"/>
+      <c r="M41" s="27"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="C42" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="D42" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="23" t="s">
-        <v>25</v>
-      </c>
+      <c r="A42" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="23"/>
       <c r="F42" s="23"/>
-      <c r="G42" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I42" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="J42" s="4" t="n">
-        <f aca="false">J41+D41</f>
-        <v>1</v>
-      </c>
-      <c r="K42" s="5" t="n">
-        <f aca="false">J42/8</f>
-        <v>0.125</v>
-      </c>
-      <c r="L42" s="5" t="n">
-        <f aca="false">J42/16</f>
-        <v>0.0625</v>
-      </c>
-      <c r="M42" s="5" t="n">
-        <f aca="false">J42/32</f>
-        <v>0.03125</v>
-      </c>
-      <c r="N42" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="O42" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="P42" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q42" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="G42" s="23"/>
+      <c r="H42" s="23"/>
+      <c r="I42" s="23"/>
+      <c r="J42" s="28"/>
+      <c r="K42" s="27"/>
+      <c r="L42" s="27"/>
+      <c r="M42" s="27"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="30" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C43" s="30" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D43" s="30" t="n">
         <v>1</v>
@@ -2864,32 +2916,31 @@
         <v>34</v>
       </c>
       <c r="I43" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="J43" s="4" t="n">
-        <f aca="false">J42+D42</f>
+        <v>112</v>
+      </c>
+      <c r="J43" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="27" t="n">
+        <f aca="false">J43/8</f>
+        <v>0</v>
+      </c>
+      <c r="L43" s="27" t="n">
+        <f aca="false">J43/16</f>
+        <v>0</v>
+      </c>
+      <c r="M43" s="27" t="n">
+        <f aca="false">J43/32</f>
+        <v>0</v>
+      </c>
+      <c r="N43" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="O43" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="P43" s="1" t="n">
         <v>2</v>
-      </c>
-      <c r="K43" s="5" t="n">
-        <f aca="false">J43/8</f>
-        <v>0.25</v>
-      </c>
-      <c r="L43" s="5" t="n">
-        <f aca="false">J43/16</f>
-        <v>0.125</v>
-      </c>
-      <c r="M43" s="5" t="n">
-        <f aca="false">J43/32</f>
-        <v>0.0625</v>
-      </c>
-      <c r="N43" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O43" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="P43" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="Q43" s="1" t="n">
         <v>0</v>
@@ -2897,10 +2948,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="30" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C44" s="30" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D44" s="30" t="n">
         <v>1</v>
@@ -2916,128 +2967,202 @@
         <v>34</v>
       </c>
       <c r="I44" s="23" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="J44" s="4" t="n">
         <f aca="false">J43+D43</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K44" s="5" t="n">
         <f aca="false">J44/8</f>
-        <v>0.375</v>
+        <v>0.125</v>
       </c>
       <c r="L44" s="5" t="n">
         <f aca="false">J44/16</f>
-        <v>0.1875</v>
+        <v>0.0625</v>
       </c>
       <c r="M44" s="5" t="n">
         <f aca="false">J44/32</f>
-        <v>0.09375</v>
+        <v>0.03125</v>
       </c>
       <c r="N44" s="5" t="s">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="O44" s="24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q44" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="C45" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="D45" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="E45" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F45" s="22"/>
+      <c r="B45" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="C45" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="D45" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" s="23"/>
       <c r="G45" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" s="22" t="s">
         <v>34</v>
       </c>
       <c r="I45" s="23" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="J45" s="4" t="n">
         <f aca="false">J44+D44</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K45" s="5" t="n">
         <f aca="false">J45/8</f>
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L45" s="5" t="n">
         <f aca="false">J45/16</f>
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="M45" s="5" t="n">
         <f aca="false">J45/32</f>
+        <v>0.0625</v>
+      </c>
+      <c r="N45" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="O45" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="P45" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q45" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="C46" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="D46" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="23"/>
+      <c r="G46" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="I46" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <f aca="false">J45+D45</f>
+        <v>3</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <f aca="false">J46/8</f>
+        <v>0.375</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <f aca="false">J46/16</f>
+        <v>0.1875</v>
+      </c>
+      <c r="M46" s="5" t="n">
+        <f aca="false">J46/32</f>
+        <v>0.09375</v>
+      </c>
+      <c r="N46" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="O46" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="P46" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q46" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="C47" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="D47" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" s="23"/>
+      <c r="G47" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="I47" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="J47" s="4" t="n">
+        <f aca="false">J46+D46</f>
+        <v>4</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <f aca="false">J47/8</f>
+        <v>0.5</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <f aca="false">J47/16</f>
+        <v>0.25</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <f aca="false">J47/32</f>
         <v>0.125</v>
       </c>
-      <c r="N45" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O45" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B46" s="22"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="22"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="22"/>
-      <c r="H46" s="22"/>
-      <c r="I46" s="23"/>
-      <c r="N46" s="5"/>
-      <c r="O46" s="24"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B47" s="22"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="22"/>
-      <c r="H47" s="22"/>
-      <c r="I47" s="23"/>
-      <c r="N47" s="5"/>
-      <c r="O47" s="24"/>
+      <c r="N47" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="O47" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="P47" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q47" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="22" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D48" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E48" s="22" t="s">
         <v>25</v>
@@ -3050,23 +3175,23 @@
         <v>34</v>
       </c>
       <c r="I48" s="23" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="J48" s="4" t="n">
         <f aca="false">J47+D47</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K48" s="5" t="n">
         <f aca="false">J48/8</f>
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="L48" s="5" t="n">
         <f aca="false">J48/16</f>
-        <v>0</v>
+        <v>0.3125</v>
       </c>
       <c r="M48" s="5" t="n">
         <f aca="false">J48/32</f>
-        <v>0</v>
+        <v>0.15625</v>
       </c>
       <c r="N48" s="5" t="s">
         <v>28</v>
@@ -3082,156 +3207,82 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="C49" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="D49" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F49" s="23"/>
-      <c r="G49" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I49" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="J49" s="4" t="n">
-        <f aca="false">J48+D48</f>
-        <v>4</v>
-      </c>
-      <c r="K49" s="5" t="n">
-        <f aca="false">J49/8</f>
-        <v>0.5</v>
-      </c>
-      <c r="L49" s="5" t="n">
-        <f aca="false">J49/16</f>
-        <v>0.25</v>
-      </c>
-      <c r="M49" s="5" t="n">
-        <f aca="false">J49/32</f>
-        <v>0.125</v>
-      </c>
-      <c r="N49" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O49" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="P49" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q49" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="A49" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B49" s="22"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="22"/>
+      <c r="H49" s="22"/>
+      <c r="I49" s="23"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="24"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="C50" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="D50" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F50" s="23"/>
-      <c r="G50" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I50" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="J50" s="4" t="n">
-        <f aca="false">J49+D49</f>
-        <v>5</v>
-      </c>
-      <c r="K50" s="5" t="n">
-        <f aca="false">J50/8</f>
-        <v>0.625</v>
-      </c>
-      <c r="L50" s="5" t="n">
-        <f aca="false">J50/16</f>
-        <v>0.3125</v>
-      </c>
-      <c r="M50" s="5" t="n">
-        <f aca="false">J50/32</f>
-        <v>0.15625</v>
-      </c>
-      <c r="N50" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O50" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="P50" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q50" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="A50" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B50" s="22"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="22"/>
+      <c r="H50" s="22"/>
+      <c r="I50" s="23"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="24"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="C51" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="D51" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F51" s="23"/>
+      <c r="B51" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="D51" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51" s="22"/>
       <c r="G51" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" s="22" t="s">
         <v>34</v>
       </c>
       <c r="I51" s="23" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="J51" s="4" t="n">
         <f aca="false">J50+D50</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K51" s="5" t="n">
         <f aca="false">J51/8</f>
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L51" s="5" t="n">
         <f aca="false">J51/16</f>
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="M51" s="5" t="n">
         <f aca="false">J51/32</f>
-        <v>0.1875</v>
+        <v>0</v>
       </c>
       <c r="N51" s="5" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="O51" s="24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="1" t="n">
         <v>0</v>
@@ -3239,10 +3290,10 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="30" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="C52" s="30" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="D52" s="30" t="n">
         <v>1</v>
@@ -3258,200 +3309,237 @@
         <v>34</v>
       </c>
       <c r="I52" s="23" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="J52" s="4" t="n">
         <f aca="false">J51+D51</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K52" s="5" t="n">
         <f aca="false">J52/8</f>
-        <v>0.875</v>
+        <v>0.375</v>
       </c>
       <c r="L52" s="5" t="n">
         <f aca="false">J52/16</f>
-        <v>0.4375</v>
+        <v>0.1875</v>
       </c>
       <c r="M52" s="5" t="n">
         <f aca="false">J52/32</f>
-        <v>0.21875</v>
+        <v>0.09375</v>
       </c>
       <c r="N52" s="5" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="O52" s="24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q52" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B53" s="22"/>
-      <c r="C53" s="22"/>
-      <c r="D53" s="22"/>
-      <c r="E53" s="22"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="22"/>
-      <c r="H53" s="22"/>
-      <c r="I53" s="23"/>
-      <c r="N53" s="5"/>
-      <c r="O53" s="24"/>
+      <c r="B53" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="C53" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="D53" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" s="23"/>
+      <c r="G53" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="I53" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="J53" s="4" t="n">
+        <f aca="false">J52+D52</f>
+        <v>4</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <f aca="false">J53/8</f>
+        <v>0.5</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <f aca="false">J53/16</f>
+        <v>0.25</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <f aca="false">J53/32</f>
+        <v>0.125</v>
+      </c>
+      <c r="N53" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="O53" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="P53" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q53" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="C54" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="D54" s="22" t="n">
-        <v>8</v>
+      <c r="B54" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="C54" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="D54" s="30" t="n">
+        <v>1</v>
       </c>
       <c r="E54" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="F54" s="22"/>
+      <c r="F54" s="23"/>
       <c r="G54" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54" s="22" t="s">
         <v>34</v>
       </c>
       <c r="I54" s="23" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J54" s="4" t="n">
-        <f aca="false">J52+D52</f>
-        <v>8</v>
+        <f aca="false">J53+D53</f>
+        <v>5</v>
       </c>
       <c r="K54" s="5" t="n">
         <f aca="false">J54/8</f>
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="L54" s="5" t="n">
         <f aca="false">J54/16</f>
-        <v>0.5</v>
+        <v>0.3125</v>
       </c>
       <c r="M54" s="5" t="n">
         <f aca="false">J54/32</f>
-        <v>0.25</v>
+        <v>0.15625</v>
       </c>
       <c r="N54" s="5" t="s">
-        <v>117</v>
+        <v>51</v>
       </c>
       <c r="O54" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="P54" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q54" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="C55" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="D55" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="P54" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q54" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="C55" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="D55" s="22" t="n">
-        <v>16</v>
-      </c>
       <c r="E55" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="F55" s="22"/>
+      <c r="F55" s="23"/>
       <c r="G55" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H55" s="22" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="I55" s="23" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="J55" s="4" t="n">
         <f aca="false">J54+D54</f>
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K55" s="5" t="n">
         <f aca="false">J55/8</f>
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="L55" s="5" t="n">
         <f aca="false">J55/16</f>
-        <v>1</v>
+        <v>0.375</v>
       </c>
       <c r="M55" s="5" t="n">
         <f aca="false">J55/32</f>
-        <v>0.5</v>
+        <v>0.1875</v>
       </c>
       <c r="N55" s="5" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="O55" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="P55" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q55" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="C56" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="D56" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="P55" s="1" t="n">
+      <c r="E56" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" s="23"/>
+      <c r="G56" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="Q55" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="C56" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="D56" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="E56" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F56" s="22"/>
-      <c r="G56" s="22" t="n">
-        <v>2</v>
-      </c>
       <c r="H56" s="22" t="s">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="I56" s="23" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="J56" s="4" t="n">
         <f aca="false">J55+D55</f>
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="K56" s="5" t="n">
         <f aca="false">J56/8</f>
-        <v>4</v>
+        <v>0.875</v>
       </c>
       <c r="L56" s="5" t="n">
         <f aca="false">J56/16</f>
-        <v>2</v>
+        <v>0.4375</v>
       </c>
       <c r="M56" s="5" t="n">
         <f aca="false">J56/32</f>
-        <v>1</v>
+        <v>0.21875</v>
       </c>
       <c r="N56" s="5" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="O56" s="24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P56" s="1" t="n">
         <v>2</v>
@@ -3461,66 +3549,29 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="C57" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="D57" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="E57" s="23" t="s">
-        <v>25</v>
-      </c>
+      <c r="A57" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B57" s="22"/>
+      <c r="C57" s="22"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
       <c r="F57" s="22"/>
-      <c r="G57" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="H57" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="I57" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="J57" s="4" t="n">
-        <f aca="false">J56+D56</f>
-        <v>48</v>
-      </c>
-      <c r="K57" s="5" t="n">
-        <f aca="false">J57/8</f>
-        <v>6</v>
-      </c>
-      <c r="L57" s="5" t="n">
-        <f aca="false">J57/16</f>
-        <v>3</v>
-      </c>
-      <c r="M57" s="5" t="n">
-        <f aca="false">J57/32</f>
-        <v>1.5</v>
-      </c>
-      <c r="N57" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="O57" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="P57" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="25.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G57" s="22"/>
+      <c r="H57" s="22"/>
+      <c r="I57" s="23"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="24"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D58" s="22" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E58" s="23" t="s">
         <v>25</v>
@@ -3530,46 +3581,46 @@
         <v>2</v>
       </c>
       <c r="H58" s="22" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="I58" s="23" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J58" s="4" t="n">
-        <f aca="false">J57+D57</f>
-        <v>64</v>
+        <f aca="false">J56+D56</f>
+        <v>8</v>
       </c>
       <c r="K58" s="5" t="n">
         <f aca="false">J58/8</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L58" s="5" t="n">
         <f aca="false">J58/16</f>
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="M58" s="5" t="n">
         <f aca="false">J58/32</f>
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="N58" s="5" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="O58" s="24" t="n">
         <v>1</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q58" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="25.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="22" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D59" s="22" t="n">
         <v>16</v>
@@ -3582,46 +3633,46 @@
         <v>2</v>
       </c>
       <c r="H59" s="22" t="s">
-        <v>49</v>
+        <v>136</v>
       </c>
       <c r="I59" s="23" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="J59" s="4" t="n">
         <f aca="false">J58+D58</f>
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="K59" s="5" t="n">
         <f aca="false">J59/8</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L59" s="5" t="n">
         <f aca="false">J59/16</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M59" s="5" t="n">
         <f aca="false">J59/32</f>
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="N59" s="5" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="O59" s="24" t="n">
         <v>1</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q59" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="25.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="22" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D60" s="22" t="n">
         <v>16</v>
@@ -3634,35 +3685,35 @@
         <v>2</v>
       </c>
       <c r="H60" s="22" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="I60" s="23" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="J60" s="4" t="n">
         <f aca="false">J59+D59</f>
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="K60" s="5" t="n">
         <f aca="false">J60/8</f>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L60" s="5" t="n">
         <f aca="false">J60/16</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M60" s="5" t="n">
         <f aca="false">J60/32</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N60" s="5" t="s">
-        <v>51</v>
+        <v>133</v>
       </c>
       <c r="O60" s="24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Q60" s="1" t="n">
         <v>0</v>
@@ -3670,10 +3721,10 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="22" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C61" s="22" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D61" s="22" t="n">
         <v>16</v>
@@ -3686,46 +3737,46 @@
         <v>2</v>
       </c>
       <c r="H61" s="22" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="I61" s="23" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="J61" s="4" t="n">
         <f aca="false">J60+D60</f>
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="K61" s="5" t="n">
         <f aca="false">J61/8</f>
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L61" s="5" t="n">
         <f aca="false">J61/16</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M61" s="5" t="n">
         <f aca="false">J61/32</f>
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="N61" s="5" t="s">
-        <v>51</v>
+        <v>133</v>
       </c>
       <c r="O61" s="24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q61" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="25.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="22" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D62" s="22" t="n">
         <v>16</v>
@@ -3738,431 +3789,535 @@
         <v>2</v>
       </c>
       <c r="H62" s="22" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="I62" s="23" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="J62" s="4" t="n">
         <f aca="false">J61+D61</f>
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="K62" s="5" t="n">
         <f aca="false">J62/8</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L62" s="5" t="n">
         <f aca="false">J62/16</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M62" s="5" t="n">
         <f aca="false">J62/32</f>
+        <v>2</v>
+      </c>
+      <c r="N62" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="O62" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P62" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="N62" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O62" s="24" t="n">
-        <v>4</v>
-      </c>
-      <c r="P62" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="Q62" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="25.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="C63" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="D63" s="30" t="n">
-        <v>8</v>
+      <c r="B63" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="C63" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="D63" s="22" t="n">
+        <v>16</v>
       </c>
       <c r="E63" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="F63" s="23"/>
+      <c r="F63" s="22"/>
       <c r="G63" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H63" s="22" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="I63" s="23" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="J63" s="4" t="n">
         <f aca="false">J62+D62</f>
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="K63" s="5" t="n">
         <f aca="false">J63/8</f>
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="L63" s="5" t="n">
         <f aca="false">J63/16</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M63" s="5" t="n">
         <f aca="false">J63/32</f>
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="N63" s="5" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="O63" s="24" t="n">
         <v>1</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q63" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="C64" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="D64" s="30" t="n">
-        <v>8</v>
+    <row r="64" customFormat="false" ht="25.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="C64" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="D64" s="22" t="n">
+        <v>16</v>
       </c>
       <c r="E64" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="F64" s="23"/>
+      <c r="F64" s="22"/>
       <c r="G64" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H64" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I64" s="30" t="s">
-        <v>148</v>
+        <v>136</v>
+      </c>
+      <c r="I64" s="23" t="s">
+        <v>153</v>
       </c>
       <c r="J64" s="4" t="n">
         <f aca="false">J63+D63</f>
-        <v>152</v>
+        <v>96</v>
       </c>
       <c r="K64" s="5" t="n">
         <f aca="false">J64/8</f>
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="L64" s="5" t="n">
         <f aca="false">J64/16</f>
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="M64" s="5" t="n">
         <f aca="false">J64/32</f>
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="N64" s="5" t="s">
-        <v>117</v>
+        <v>51</v>
       </c>
       <c r="O64" s="24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q64" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="C65" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="D65" s="30" t="n">
-        <v>8</v>
+      <c r="B65" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="C65" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="D65" s="22" t="n">
+        <v>16</v>
       </c>
       <c r="E65" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="F65" s="23"/>
+        <v>25</v>
+      </c>
+      <c r="F65" s="22"/>
       <c r="G65" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H65" s="22" t="s">
-        <v>34</v>
+        <v>136</v>
       </c>
       <c r="I65" s="23" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="J65" s="4" t="n">
         <f aca="false">J64+D64</f>
-        <v>160</v>
+        <v>112</v>
       </c>
       <c r="K65" s="5" t="n">
         <f aca="false">J65/8</f>
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L65" s="5" t="n">
         <f aca="false">J65/16</f>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M65" s="5" t="n">
         <f aca="false">J65/32</f>
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="N65" s="5" t="s">
-        <v>117</v>
+        <v>51</v>
       </c>
       <c r="O65" s="24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q65" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="C66" s="30" t="s">
-        <v>153</v>
-      </c>
-      <c r="D66" s="30" t="n">
-        <v>8</v>
+      <c r="B66" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="C66" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="D66" s="22" t="n">
+        <v>16</v>
       </c>
       <c r="E66" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="F66" s="23"/>
+        <v>25</v>
+      </c>
+      <c r="F66" s="22"/>
       <c r="G66" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H66" s="22" t="s">
-        <v>34</v>
+        <v>136</v>
       </c>
       <c r="I66" s="23" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="J66" s="4" t="n">
         <f aca="false">J65+D65</f>
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="K66" s="5" t="n">
         <f aca="false">J66/8</f>
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="L66" s="5" t="n">
         <f aca="false">J66/16</f>
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="M66" s="5" t="n">
         <f aca="false">J66/32</f>
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="N66" s="5" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="O66" s="24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q66" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="67" s="15" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="B67" s="31"/>
-      <c r="C67" s="32"/>
-      <c r="D67" s="33"/>
-      <c r="E67" s="33"/>
-      <c r="F67" s="33"/>
-      <c r="G67" s="33"/>
-      <c r="H67" s="32"/>
-      <c r="I67" s="33" t="s">
-        <v>155</v>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="C67" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="D67" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="E67" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="F67" s="23"/>
+      <c r="G67" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="I67" s="23" t="s">
+        <v>162</v>
       </c>
       <c r="J67" s="4" t="n">
         <f aca="false">J66+D66</f>
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="K67" s="5" t="n">
         <f aca="false">J67/8</f>
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L67" s="5" t="n">
         <f aca="false">J67/16</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M67" s="5" t="n">
         <f aca="false">J67/32</f>
-        <v>5.5</v>
-      </c>
-      <c r="O67" s="34"/>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="25"/>
+        <v>4.5</v>
+      </c>
+      <c r="N67" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="O67" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q67" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="25.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="C68" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="D68" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="E68" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F68" s="23"/>
+      <c r="G68" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="I68" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="J68" s="4" t="n">
+        <f aca="false">J67+D67</f>
+        <v>152</v>
+      </c>
+      <c r="K68" s="5" t="n">
+        <f aca="false">J68/8</f>
+        <v>19</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <f aca="false">J68/16</f>
+        <v>9.5</v>
+      </c>
+      <c r="M68" s="5" t="n">
+        <f aca="false">J68/32</f>
+        <v>4.75</v>
+      </c>
+      <c r="N68" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="O68" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P68" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q68" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="s">
+      <c r="B69" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="C69" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="D69" s="30" t="n">
+        <v>32</v>
+      </c>
+      <c r="E69" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F69" s="23"/>
+      <c r="G69" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="I69" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="J69" s="4" t="n">
+        <f aca="false">J68+D68</f>
+        <v>160</v>
+      </c>
+      <c r="K69" s="5" t="n">
+        <f aca="false">J69/8</f>
+        <v>20</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <f aca="false">J69/16</f>
+        <v>10</v>
+      </c>
+      <c r="M69" s="5" t="n">
+        <f aca="false">J69/32</f>
+        <v>5</v>
+      </c>
+      <c r="N69" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="O69" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q69" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="23"/>
+      <c r="B70" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="C70" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="D70" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="E70" s="23" t="s">
+        <v>63</v>
+      </c>
       <c r="F70" s="23"/>
-      <c r="G70" s="23"/>
-      <c r="H70" s="23"/>
-      <c r="I70" s="23"/>
-      <c r="J70" s="28"/>
-      <c r="K70" s="27"/>
-      <c r="L70" s="27"/>
-      <c r="M70" s="27"/>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="C71" s="30" t="s">
-        <v>157</v>
-      </c>
-      <c r="D71" s="30" t="n">
-        <v>32</v>
-      </c>
-      <c r="E71" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="F71" s="23"/>
-      <c r="G71" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="22" t="s">
+      <c r="G70" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="I71" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="J71" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="27" t="n">
+      <c r="I70" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="J70" s="4" t="n">
+        <f aca="false">J69+D69</f>
+        <v>192</v>
+      </c>
+      <c r="K70" s="5" t="n">
+        <f aca="false">J70/8</f>
+        <v>24</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <f aca="false">J70/16</f>
+        <v>12</v>
+      </c>
+      <c r="M70" s="5" t="n">
+        <f aca="false">J70/32</f>
+        <v>6</v>
+      </c>
+      <c r="N70" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="O70" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="P70" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q70" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" s="15" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B71" s="31"/>
+      <c r="C71" s="32"/>
+      <c r="D71" s="33"/>
+      <c r="E71" s="33"/>
+      <c r="F71" s="33"/>
+      <c r="G71" s="33"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="J71" s="4" t="n">
+        <f aca="false">J70+D70</f>
+        <v>200</v>
+      </c>
+      <c r="K71" s="5" t="n">
         <f aca="false">J71/8</f>
-        <v>0</v>
-      </c>
-      <c r="L71" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="L71" s="5" t="n">
         <f aca="false">J71/16</f>
-        <v>0</v>
-      </c>
-      <c r="M71" s="27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="M71" s="5" t="n">
         <f aca="false">J71/32</f>
-        <v>0</v>
-      </c>
-      <c r="N71" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O71" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="B72" s="31"/>
-      <c r="C72" s="32"/>
-      <c r="D72" s="33"/>
-      <c r="E72" s="33"/>
-      <c r="F72" s="33"/>
-      <c r="G72" s="33"/>
-      <c r="H72" s="32"/>
-      <c r="I72" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="J72" s="4" t="n">
-        <f aca="false">J71+D71</f>
-        <v>32</v>
-      </c>
-      <c r="K72" s="5" t="n">
-        <f aca="false">J72/8</f>
-        <v>4</v>
-      </c>
-      <c r="L72" s="5" t="n">
-        <f aca="false">J72/16</f>
-        <v>2</v>
-      </c>
-      <c r="M72" s="5" t="n">
-        <f aca="false">J72/32</f>
-        <v>1</v>
-      </c>
-      <c r="O72" s="34"/>
-    </row>
-    <row r="73" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="31"/>
-      <c r="C73" s="32"/>
-      <c r="D73" s="33"/>
-      <c r="E73" s="33"/>
-      <c r="F73" s="33"/>
-      <c r="G73" s="33"/>
-      <c r="H73" s="32"/>
-      <c r="I73" s="33"/>
-      <c r="J73" s="28"/>
-      <c r="K73" s="27"/>
-      <c r="L73" s="27"/>
-      <c r="M73" s="27"/>
-      <c r="O73" s="34"/>
+        <v>6.25</v>
+      </c>
+      <c r="O71" s="34"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B72" s="25"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B74" s="25"/>
+        <v>173</v>
+      </c>
+      <c r="B74" s="30"/>
+      <c r="C74" s="30"/>
+      <c r="D74" s="30"/>
+      <c r="E74" s="23"/>
+      <c r="F74" s="23"/>
+      <c r="G74" s="23"/>
+      <c r="H74" s="23"/>
+      <c r="I74" s="23"/>
+      <c r="J74" s="28"/>
+      <c r="K74" s="27"/>
+      <c r="L74" s="27"/>
+      <c r="M74" s="27"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="30" t="s">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c r="C75" s="30" t="s">
-        <v>160</v>
-      </c>
-      <c r="D75" s="26" t="n">
+        <v>174</v>
+      </c>
+      <c r="D75" s="30" t="n">
         <v>32</v>
       </c>
-      <c r="E75" s="35" t="s">
-        <v>161</v>
+      <c r="E75" s="23" t="s">
+        <v>63</v>
       </c>
       <c r="F75" s="23"/>
-      <c r="G75" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I75" s="27" t="s">
-        <v>162</v>
+      <c r="G75" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="I75" s="23" t="s">
+        <v>127</v>
       </c>
       <c r="J75" s="28" t="n">
         <v>0</v>
@@ -4192,25 +4347,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="C76" s="30" t="s">
-        <v>164</v>
-      </c>
-      <c r="D76" s="26" t="n">
-        <v>16</v>
-      </c>
-      <c r="E76" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F76" s="23"/>
-      <c r="G76" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="27" t="s">
-        <v>165</v>
+    <row r="76" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B76" s="31"/>
+      <c r="C76" s="32"/>
+      <c r="D76" s="33"/>
+      <c r="E76" s="33"/>
+      <c r="F76" s="33"/>
+      <c r="G76" s="33"/>
+      <c r="H76" s="32"/>
+      <c r="I76" s="33" t="s">
+        <v>172</v>
       </c>
       <c r="J76" s="4" t="n">
         <f aca="false">J75+D75</f>
@@ -4228,394 +4377,309 @@
         <f aca="false">J76/32</f>
         <v>1</v>
       </c>
-      <c r="N76" s="5" t="s">
+      <c r="O76" s="34"/>
+    </row>
+    <row r="77" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="31"/>
+      <c r="C77" s="32"/>
+      <c r="D77" s="33"/>
+      <c r="E77" s="33"/>
+      <c r="F77" s="33"/>
+      <c r="G77" s="33"/>
+      <c r="H77" s="32"/>
+      <c r="I77" s="33"/>
+      <c r="J77" s="28"/>
+      <c r="K77" s="27"/>
+      <c r="L77" s="27"/>
+      <c r="M77" s="27"/>
+      <c r="O77" s="34"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B78" s="25"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="C79" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="D79" s="26" t="n">
+        <v>32</v>
+      </c>
+      <c r="E79" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="F79" s="23"/>
+      <c r="G79" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="I79" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="J79" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="27" t="n">
+        <f aca="false">J79/8</f>
+        <v>0</v>
+      </c>
+      <c r="L79" s="27" t="n">
+        <f aca="false">J79/16</f>
+        <v>0</v>
+      </c>
+      <c r="M79" s="27" t="n">
+        <f aca="false">J79/32</f>
+        <v>0</v>
+      </c>
+      <c r="N79" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="O76" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="C77" s="30" t="s">
-        <v>167</v>
-      </c>
-      <c r="D77" s="26" t="n">
+      <c r="O79" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="C80" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="D80" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="E80" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="F80" s="23"/>
+      <c r="G80" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="J80" s="4" t="n">
+        <f aca="false">J79+D79</f>
+        <v>32</v>
+      </c>
+      <c r="K80" s="5" t="n">
+        <f aca="false">J80/8</f>
+        <v>4</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <f aca="false">J80/16</f>
+        <v>2</v>
+      </c>
+      <c r="M80" s="5" t="n">
+        <f aca="false">J80/32</f>
+        <v>1</v>
+      </c>
+      <c r="N80" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O80" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="C81" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="D81" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="E77" s="35" t="s">
-        <v>161</v>
-      </c>
-      <c r="F77" s="23"/>
-      <c r="G77" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="22" t="s">
+      <c r="E81" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="F81" s="23"/>
+      <c r="G81" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="I77" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="J77" s="4" t="n">
-        <f aca="false">J76+D76</f>
+      <c r="I81" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="J81" s="4" t="n">
+        <f aca="false">J80+D80</f>
         <v>48</v>
       </c>
-      <c r="K77" s="5" t="n">
-        <f aca="false">J77/8</f>
+      <c r="K81" s="5" t="n">
+        <f aca="false">J81/8</f>
         <v>6</v>
       </c>
-      <c r="L77" s="5" t="n">
-        <f aca="false">J77/16</f>
+      <c r="L81" s="5" t="n">
+        <f aca="false">J81/16</f>
         <v>3</v>
       </c>
-      <c r="M77" s="5" t="n">
-        <f aca="false">J77/32</f>
+      <c r="M81" s="5" t="n">
+        <f aca="false">J81/32</f>
         <v>1.5</v>
       </c>
-      <c r="N77" s="5" t="s">
+      <c r="N81" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="O77" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="30" t="s">
-        <v>169</v>
-      </c>
-      <c r="C78" s="30" t="s">
-        <v>170</v>
-      </c>
-      <c r="D78" s="26" t="n">
+      <c r="O81" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B82" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="C82" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="D82" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="E78" s="35"/>
-      <c r="F78" s="23"/>
-      <c r="G78" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="22" t="s">
+      <c r="E82" s="35"/>
+      <c r="F82" s="23"/>
+      <c r="G82" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="I78" s="27" t="s">
-        <v>171</v>
-      </c>
-      <c r="J78" s="4" t="n">
-        <f aca="false">J77+D77</f>
+      <c r="I82" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="J82" s="4" t="n">
+        <f aca="false">J81+D81</f>
         <v>56</v>
       </c>
-      <c r="K78" s="5" t="n">
-        <f aca="false">J78/8</f>
+      <c r="K82" s="5" t="n">
+        <f aca="false">J82/8</f>
         <v>7</v>
       </c>
-      <c r="L78" s="5" t="n">
-        <f aca="false">J78/16</f>
+      <c r="L82" s="5" t="n">
+        <f aca="false">J82/16</f>
         <v>3.5</v>
       </c>
-      <c r="M78" s="5" t="n">
-        <f aca="false">J78/32</f>
+      <c r="M82" s="5" t="n">
+        <f aca="false">J82/32</f>
         <v>1.75</v>
       </c>
-      <c r="N78" s="5" t="s">
+      <c r="N82" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="O78" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="s">
+      <c r="O82" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B79" s="25"/>
-      <c r="C79" s="32"/>
-      <c r="D79" s="33"/>
-      <c r="E79" s="33"/>
-      <c r="F79" s="33"/>
-      <c r="G79" s="33"/>
-      <c r="H79" s="32"/>
-      <c r="I79" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="J79" s="4" t="n">
-        <f aca="false">J78+D78</f>
+      <c r="B83" s="25"/>
+      <c r="C83" s="32"/>
+      <c r="D83" s="33"/>
+      <c r="E83" s="33"/>
+      <c r="F83" s="33"/>
+      <c r="G83" s="33"/>
+      <c r="H83" s="32"/>
+      <c r="I83" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="J83" s="4" t="n">
+        <f aca="false">J82+D82</f>
         <v>64</v>
       </c>
-      <c r="K79" s="5" t="n">
-        <f aca="false">J79/8</f>
+      <c r="K83" s="5" t="n">
+        <f aca="false">J83/8</f>
         <v>8</v>
       </c>
-      <c r="L79" s="5" t="n">
-        <f aca="false">J79/16</f>
+      <c r="L83" s="5" t="n">
+        <f aca="false">J83/16</f>
         <v>4</v>
       </c>
-      <c r="M79" s="5" t="n">
-        <f aca="false">J79/32</f>
+      <c r="M83" s="5" t="n">
+        <f aca="false">J83/32</f>
         <v>2</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="25"/>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="25"/>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B82" s="25"/>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="30" t="s">
-        <v>173</v>
-      </c>
-      <c r="C83" s="30" t="s">
-        <v>174</v>
-      </c>
-      <c r="D83" s="26" t="n">
-        <v>32</v>
-      </c>
-      <c r="E83" s="35"/>
-      <c r="F83" s="23"/>
-      <c r="G83" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I83" s="27" t="s">
-        <v>162</v>
-      </c>
-      <c r="J83" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="27" t="n">
-        <f aca="false">J83/8</f>
-        <v>0</v>
-      </c>
-      <c r="L83" s="27" t="n">
-        <f aca="false">J83/16</f>
-        <v>0</v>
-      </c>
-      <c r="M83" s="27" t="n">
-        <f aca="false">J83/32</f>
-        <v>0</v>
-      </c>
-      <c r="N83" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O83" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="30" t="s">
-        <v>175</v>
-      </c>
-      <c r="C84" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="D84" s="26" t="n">
-        <v>16</v>
-      </c>
-      <c r="E84" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F84" s="23"/>
-      <c r="G84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" s="27" t="s">
-        <v>165</v>
-      </c>
-      <c r="J84" s="4" t="n">
-        <f aca="false">J83+D83</f>
-        <v>32</v>
-      </c>
-      <c r="K84" s="5" t="n">
-        <f aca="false">J84/8</f>
-        <v>4</v>
-      </c>
-      <c r="L84" s="5" t="n">
-        <f aca="false">J84/16</f>
-        <v>2</v>
-      </c>
-      <c r="M84" s="5" t="n">
-        <f aca="false">J84/32</f>
-        <v>1</v>
-      </c>
-      <c r="N84" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O84" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="B84" s="25"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="C85" s="30" t="s">
-        <v>178</v>
-      </c>
-      <c r="D85" s="26" t="n">
-        <v>16</v>
-      </c>
-      <c r="E85" s="35"/>
-      <c r="F85" s="23"/>
-      <c r="G85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="J85" s="4" t="n">
-        <f aca="false">J84+D84</f>
-        <v>48</v>
-      </c>
-      <c r="K85" s="5" t="n">
-        <f aca="false">J85/8</f>
-        <v>6</v>
-      </c>
-      <c r="L85" s="5" t="n">
-        <f aca="false">J85/16</f>
-        <v>3</v>
-      </c>
-      <c r="M85" s="5" t="n">
-        <f aca="false">J85/32</f>
-        <v>1.5</v>
-      </c>
-      <c r="N85" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O85" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="B85" s="25"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="30" t="s">
-        <v>180</v>
-      </c>
-      <c r="C86" s="30" t="s">
-        <v>181</v>
-      </c>
-      <c r="D86" s="26" t="n">
-        <v>32</v>
-      </c>
-      <c r="E86" s="35"/>
-      <c r="F86" s="23"/>
-      <c r="G86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="27" t="s">
-        <v>182</v>
-      </c>
-      <c r="J86" s="4" t="n">
-        <f aca="false">J85+D85</f>
-        <v>64</v>
-      </c>
-      <c r="K86" s="5" t="n">
-        <f aca="false">J86/8</f>
-        <v>8</v>
-      </c>
-      <c r="L86" s="5" t="n">
-        <f aca="false">J86/16</f>
-        <v>4</v>
-      </c>
-      <c r="M86" s="5" t="n">
-        <f aca="false">J86/32</f>
-        <v>2</v>
-      </c>
-      <c r="N86" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O86" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q86" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="A86" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B86" s="25"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="30" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C87" s="30" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="D87" s="26" t="n">
-        <v>8</v>
-      </c>
-      <c r="E87" s="35" t="s">
-        <v>161</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="E87" s="35"/>
       <c r="F87" s="23"/>
       <c r="G87" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H87" s="22" t="s">
-        <v>34</v>
+      <c r="H87" s="3" t="s">
+        <v>136</v>
       </c>
       <c r="I87" s="27" t="s">
-        <v>185</v>
-      </c>
-      <c r="J87" s="4" t="n">
-        <f aca="false">J86+D86</f>
-        <v>96</v>
-      </c>
-      <c r="K87" s="5" t="n">
+        <v>179</v>
+      </c>
+      <c r="J87" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="27" t="n">
         <f aca="false">J87/8</f>
-        <v>12</v>
-      </c>
-      <c r="L87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="27" t="n">
         <f aca="false">J87/16</f>
-        <v>6</v>
-      </c>
-      <c r="M87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="27" t="n">
         <f aca="false">J87/32</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N87" s="5" t="s">
         <v>28</v>
@@ -4632,40 +4696,39 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="30" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="C88" s="30" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D88" s="26" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E88" s="35" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="F88" s="23"/>
       <c r="G88" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H88" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I88" s="27"/>
+      <c r="I88" s="27" t="s">
+        <v>182</v>
+      </c>
       <c r="J88" s="4" t="n">
         <f aca="false">J87+D87</f>
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="K88" s="5" t="n">
         <f aca="false">J88/8</f>
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L88" s="5" t="n">
         <f aca="false">J88/16</f>
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="M88" s="5" t="n">
         <f aca="false">J88/32</f>
-        <v>3.25</v>
+        <v>1</v>
       </c>
       <c r="N88" s="5" t="s">
         <v>28</v>
@@ -4681,558 +4744,546 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B89" s="31"/>
-      <c r="C89" s="32"/>
-      <c r="D89" s="33"/>
-      <c r="E89" s="33"/>
-      <c r="F89" s="33"/>
-      <c r="G89" s="33"/>
-      <c r="H89" s="32"/>
-      <c r="I89" s="33" t="s">
-        <v>155</v>
+      <c r="B89" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="C89" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="D89" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="E89" s="35"/>
+      <c r="F89" s="23"/>
+      <c r="G89" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="27" t="s">
+        <v>196</v>
       </c>
       <c r="J89" s="4" t="n">
         <f aca="false">J88+D88</f>
-        <v>128</v>
+        <v>48</v>
       </c>
       <c r="K89" s="5" t="n">
         <f aca="false">J89/8</f>
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="L89" s="5" t="n">
         <f aca="false">J89/16</f>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M89" s="5" t="n">
         <f aca="false">J89/32</f>
+        <v>1.5</v>
+      </c>
+      <c r="N89" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O89" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B90" s="30" t="s">
+        <v>197</v>
+      </c>
+      <c r="C90" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="D90" s="26" t="n">
+        <v>32</v>
+      </c>
+      <c r="E90" s="35"/>
+      <c r="F90" s="23"/>
+      <c r="G90" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="J90" s="4" t="n">
+        <f aca="false">J89+D89</f>
+        <v>64</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <f aca="false">J90/8</f>
+        <v>8</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <f aca="false">J90/16</f>
         <v>4</v>
       </c>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="25"/>
+      <c r="M90" s="5" t="n">
+        <f aca="false">J90/32</f>
+        <v>2</v>
+      </c>
+      <c r="N90" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O90" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B91" s="25"/>
+      <c r="B91" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="C91" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="D91" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E91" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="F91" s="23"/>
+      <c r="G91" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="I91" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="J91" s="4" t="n">
+        <f aca="false">J90+D90</f>
+        <v>96</v>
+      </c>
+      <c r="K91" s="5" t="n">
+        <f aca="false">J91/8</f>
+        <v>12</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <f aca="false">J91/16</f>
+        <v>6</v>
+      </c>
+      <c r="M91" s="5" t="n">
+        <f aca="false">J91/32</f>
+        <v>3</v>
+      </c>
+      <c r="N91" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O91" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B92" s="25"/>
+      <c r="B92" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="C92" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="D92" s="26" t="n">
+        <v>24</v>
+      </c>
+      <c r="E92" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="F92" s="23"/>
+      <c r="G92" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="I92" s="27"/>
+      <c r="J92" s="4" t="n">
+        <f aca="false">J91+D91</f>
+        <v>104</v>
+      </c>
+      <c r="K92" s="5" t="n">
+        <f aca="false">J92/8</f>
+        <v>13</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <f aca="false">J92/16</f>
+        <v>6.5</v>
+      </c>
+      <c r="M92" s="5" t="n">
+        <f aca="false">J92/32</f>
+        <v>3.25</v>
+      </c>
+      <c r="N92" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O92" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B93" s="25"/>
+        <v>44</v>
+      </c>
+      <c r="B93" s="31"/>
+      <c r="C93" s="32"/>
+      <c r="D93" s="33"/>
+      <c r="E93" s="33"/>
+      <c r="F93" s="33"/>
+      <c r="G93" s="33"/>
+      <c r="H93" s="32"/>
+      <c r="I93" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="J93" s="4" t="n">
+        <f aca="false">J92+D92</f>
+        <v>128</v>
+      </c>
+      <c r="K93" s="5" t="n">
+        <f aca="false">J93/8</f>
+        <v>16</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <f aca="false">J93/16</f>
+        <v>8</v>
+      </c>
+      <c r="M93" s="5" t="n">
+        <f aca="false">J93/32</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="30" t="s">
-        <v>188</v>
-      </c>
-      <c r="C94" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="D94" s="26" t="n">
-        <v>32</v>
-      </c>
-      <c r="E94" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F94" s="23"/>
-      <c r="G94" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="I94" s="27" t="s">
-        <v>190</v>
-      </c>
-      <c r="J94" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" s="27" t="n">
-        <f aca="false">J94/8</f>
-        <v>0</v>
-      </c>
-      <c r="L94" s="27" t="n">
-        <f aca="false">J94/16</f>
-        <v>0</v>
-      </c>
-      <c r="M94" s="27" t="n">
-        <f aca="false">J94/32</f>
-        <v>0</v>
-      </c>
-      <c r="N94" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O94" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="B94" s="25"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B95" s="30" t="s">
-        <v>191</v>
-      </c>
-      <c r="C95" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="D95" s="26" t="n">
-        <v>16</v>
-      </c>
-      <c r="E95" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F95" s="23"/>
-      <c r="G95" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="I95" s="27" t="s">
-        <v>190</v>
-      </c>
-      <c r="J95" s="4" t="n">
-        <f aca="false">J94+D94</f>
-        <v>32</v>
-      </c>
-      <c r="K95" s="5" t="n">
-        <f aca="false">J95/8</f>
-        <v>4</v>
-      </c>
-      <c r="L95" s="5" t="n">
-        <f aca="false">J95/16</f>
-        <v>2</v>
-      </c>
-      <c r="M95" s="5" t="n">
-        <f aca="false">J95/32</f>
-        <v>1</v>
-      </c>
-      <c r="N95" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O95" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q95" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="B95" s="25"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B96" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="C96" s="30" t="s">
-        <v>194</v>
-      </c>
-      <c r="D96" s="26" t="n">
-        <v>8</v>
-      </c>
-      <c r="E96" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F96" s="23"/>
-      <c r="G96" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I96" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="J96" s="4" t="n">
-        <f aca="false">J95+D95</f>
-        <v>48</v>
-      </c>
-      <c r="K96" s="5" t="n">
-        <f aca="false">J96/8</f>
-        <v>6</v>
-      </c>
-      <c r="L96" s="5" t="n">
-        <f aca="false">J96/16</f>
-        <v>3</v>
-      </c>
-      <c r="M96" s="5" t="n">
-        <f aca="false">J96/32</f>
-        <v>1.5</v>
-      </c>
-      <c r="N96" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O96" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="A96" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B96" s="25"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B97" s="25"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B98" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C98" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="D98" s="26" t="n">
+        <v>32</v>
+      </c>
+      <c r="E98" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="F98" s="23"/>
+      <c r="G98" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="I98" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="J98" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="27" t="n">
+        <f aca="false">J98/8</f>
+        <v>0</v>
+      </c>
+      <c r="L98" s="27" t="n">
+        <f aca="false">J98/16</f>
+        <v>0</v>
+      </c>
+      <c r="M98" s="27" t="n">
+        <f aca="false">J98/32</f>
+        <v>0</v>
+      </c>
+      <c r="N98" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O98" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B99" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="C99" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="D99" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="E99" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="F99" s="23"/>
+      <c r="G99" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="I99" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="J99" s="4" t="n">
+        <f aca="false">J98+D98</f>
+        <v>32</v>
+      </c>
+      <c r="K99" s="5" t="n">
+        <f aca="false">J99/8</f>
+        <v>4</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <f aca="false">J99/16</f>
+        <v>2</v>
+      </c>
+      <c r="M99" s="5" t="n">
+        <f aca="false">J99/32</f>
+        <v>1</v>
+      </c>
+      <c r="N99" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O99" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B100" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="C100" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="D100" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E100" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="F100" s="23"/>
+      <c r="G100" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="I100" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="J100" s="4" t="n">
+        <f aca="false">J99+D99</f>
+        <v>48</v>
+      </c>
+      <c r="K100" s="5" t="n">
+        <f aca="false">J100/8</f>
+        <v>6</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <f aca="false">J100/16</f>
+        <v>3</v>
+      </c>
+      <c r="M100" s="5" t="n">
+        <f aca="false">J100/32</f>
+        <v>1.5</v>
+      </c>
+      <c r="N100" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O100" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B97" s="30"/>
-      <c r="I97" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J97" s="4" t="n">
-        <f aca="false">J96+D96</f>
+      <c r="B101" s="30"/>
+      <c r="I101" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="J101" s="4" t="n">
+        <f aca="false">J100+D100</f>
         <v>56</v>
       </c>
-      <c r="K97" s="5" t="n">
-        <f aca="false">J97/8</f>
+      <c r="K101" s="5" t="n">
+        <f aca="false">J101/8</f>
         <v>7</v>
       </c>
-      <c r="L97" s="5" t="n">
-        <f aca="false">J97/16</f>
+      <c r="L101" s="5" t="n">
+        <f aca="false">J101/16</f>
         <v>3.5</v>
       </c>
-      <c r="M97" s="5" t="n">
-        <f aca="false">J97/32</f>
+      <c r="M101" s="5" t="n">
+        <f aca="false">J101/32</f>
         <v>1.75</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B98" s="30"/>
-      <c r="J98" s="28"/>
-      <c r="K98" s="27"/>
-      <c r="L98" s="27"/>
-      <c r="M98" s="27"/>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="J100" s="38"/>
-      <c r="K100" s="27"/>
-      <c r="L100" s="27"/>
-      <c r="M100" s="27"/>
-      <c r="N100" s="20" t="s">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B102" s="30"/>
+      <c r="J102" s="28"/>
+      <c r="K102" s="27"/>
+      <c r="L102" s="27"/>
+      <c r="M102" s="27"/>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="37" t="s">
+        <v>213</v>
+      </c>
+      <c r="J104" s="38"/>
+      <c r="K104" s="27"/>
+      <c r="L104" s="27"/>
+      <c r="M104" s="27"/>
+      <c r="N104" s="20" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="101" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B101" s="16" t="s">
+    <row r="105" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B105" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C101" s="13" t="s">
+      <c r="C105" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D101" s="13" t="s">
+      <c r="D105" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E101" s="13" t="s">
+      <c r="E105" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F101" s="13" t="s">
+      <c r="F105" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G101" s="13" t="s">
+      <c r="G105" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="H101" s="13" t="s">
+      <c r="H105" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I101" s="14" t="s">
+      <c r="I105" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="J101" s="29" t="s">
+      <c r="J105" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="K101" s="15" t="s">
+      <c r="K105" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="L101" s="15" t="s">
+      <c r="L105" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="M101" s="15" t="s">
+      <c r="M105" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="N101" s="5"/>
-      <c r="O101" s="21" t="s">
+      <c r="N105" s="5"/>
+      <c r="O105" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="P101" s="15" t="s">
+      <c r="P105" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="Q101" s="15" t="s">
+      <c r="Q105" s="15" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="102" s="39" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B102" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="C102" s="40" t="s">
-        <v>198</v>
-      </c>
-      <c r="D102" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="E102" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F102" s="41"/>
-      <c r="G102" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="H102" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="I102" s="35" t="s">
-        <v>199</v>
-      </c>
-      <c r="J102" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" s="27" t="n">
-        <f aca="false">J102/8</f>
-        <v>0</v>
-      </c>
-      <c r="L102" s="27" t="n">
-        <f aca="false">J102/16</f>
-        <v>0</v>
-      </c>
-      <c r="M102" s="27" t="n">
-        <f aca="false">J102/32</f>
-        <v>0</v>
-      </c>
-      <c r="N102" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="O102" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="P102" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q102" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" s="39" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B103" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="C103" s="40" t="s">
-        <v>201</v>
-      </c>
-      <c r="D103" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E103" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F103" s="41"/>
-      <c r="G103" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="H103" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="I103" s="35" t="s">
-        <v>199</v>
-      </c>
-      <c r="J103" s="4" t="n">
-        <f aca="false">J102+D102</f>
-        <v>9</v>
-      </c>
-      <c r="K103" s="5" t="n">
-        <f aca="false">J103/8</f>
-        <v>1.125</v>
-      </c>
-      <c r="L103" s="5" t="n">
-        <f aca="false">J103/16</f>
-        <v>0.5625</v>
-      </c>
-      <c r="M103" s="5" t="n">
-        <f aca="false">J103/32</f>
-        <v>0.28125</v>
-      </c>
-      <c r="N103" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="O103" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="P103" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q103" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" s="39" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B104" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="C104" s="40" t="s">
-        <v>203</v>
-      </c>
-      <c r="D104" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E104" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F104" s="41"/>
-      <c r="G104" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="H104" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="I104" s="35" t="s">
-        <v>204</v>
-      </c>
-      <c r="J104" s="4" t="n">
-        <f aca="false">J103+D103</f>
-        <v>14</v>
-      </c>
-      <c r="K104" s="5" t="n">
-        <f aca="false">J104/8</f>
-        <v>1.75</v>
-      </c>
-      <c r="L104" s="5" t="n">
-        <f aca="false">J104/16</f>
-        <v>0.875</v>
-      </c>
-      <c r="M104" s="5" t="n">
-        <f aca="false">J104/32</f>
-        <v>0.4375</v>
-      </c>
-      <c r="N104" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="O104" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="P104" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q104" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" s="39" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B105" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="C105" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="D105" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E105" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F105" s="41"/>
-      <c r="G105" s="35" t="n">
-        <v>2</v>
-      </c>
-      <c r="H105" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="I105" s="35" t="s">
-        <v>207</v>
-      </c>
-      <c r="J105" s="4" t="n">
-        <f aca="false">J104+D104</f>
-        <v>18</v>
-      </c>
-      <c r="K105" s="5" t="n">
-        <f aca="false">J105/8</f>
-        <v>2.25</v>
-      </c>
-      <c r="L105" s="5" t="n">
-        <f aca="false">J105/16</f>
-        <v>1.125</v>
-      </c>
-      <c r="M105" s="5" t="n">
-        <f aca="false">J105/32</f>
-        <v>0.5625</v>
-      </c>
-      <c r="N105" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="O105" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="P105" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q105" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="106" s="39" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B106" s="22" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C106" s="40" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="D106" s="1" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E106" s="35" t="s">
         <v>25</v>
       </c>
       <c r="F106" s="41"/>
-      <c r="G106" s="22" t="n">
+      <c r="G106" s="35" t="n">
         <v>2</v>
       </c>
       <c r="H106" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="I106" s="22" t="s">
-        <v>210</v>
-      </c>
-      <c r="J106" s="4" t="n">
-        <f aca="false">J105+D105</f>
-        <v>22</v>
-      </c>
-      <c r="K106" s="5" t="n">
+      <c r="I106" s="35" t="s">
+        <v>216</v>
+      </c>
+      <c r="J106" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="27" t="n">
         <f aca="false">J106/8</f>
-        <v>2.75</v>
-      </c>
-      <c r="L106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="27" t="n">
         <f aca="false">J106/16</f>
-        <v>1.375</v>
-      </c>
-      <c r="M106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="27" t="n">
         <f aca="false">J106/32</f>
-        <v>0.6875</v>
+        <v>0</v>
       </c>
       <c r="N106" s="5" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="O106" s="24" t="n">
         <v>1</v>
       </c>
       <c r="P106" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q106" s="1" t="n">
         <v>0</v>
@@ -5240,51 +5291,51 @@
     </row>
     <row r="107" s="39" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B107" s="22" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C107" s="40" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D107" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E107" s="35" t="s">
         <v>25</v>
       </c>
       <c r="F107" s="41"/>
-      <c r="G107" s="22" t="n">
+      <c r="G107" s="35" t="n">
         <v>2</v>
       </c>
       <c r="H107" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="I107" s="22" t="s">
-        <v>213</v>
+      <c r="I107" s="35" t="s">
+        <v>216</v>
       </c>
       <c r="J107" s="4" t="n">
         <f aca="false">J106+D106</f>
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="K107" s="5" t="n">
         <f aca="false">J107/8</f>
-        <v>3.125</v>
+        <v>1.125</v>
       </c>
       <c r="L107" s="5" t="n">
         <f aca="false">J107/16</f>
-        <v>1.5625</v>
+        <v>0.5625</v>
       </c>
       <c r="M107" s="5" t="n">
         <f aca="false">J107/32</f>
-        <v>0.78125</v>
+        <v>0.28125</v>
       </c>
       <c r="N107" s="5" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="O107" s="24" t="n">
         <v>1</v>
       </c>
       <c r="P107" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q107" s="1" t="n">
         <v>0</v>
@@ -5292,51 +5343,51 @@
     </row>
     <row r="108" s="39" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B108" s="22" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C108" s="40" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D108" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E108" s="35" t="s">
         <v>25</v>
       </c>
       <c r="F108" s="41"/>
-      <c r="G108" s="22" t="n">
-        <v>1</v>
+      <c r="G108" s="35" t="n">
+        <v>2</v>
       </c>
       <c r="H108" s="35" t="s">
         <v>34</v>
       </c>
       <c r="I108" s="35" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="J108" s="4" t="n">
         <f aca="false">J107+D107</f>
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="K108" s="5" t="n">
         <f aca="false">J108/8</f>
-        <v>3.25</v>
+        <v>1.75</v>
       </c>
       <c r="L108" s="5" t="n">
         <f aca="false">J108/16</f>
-        <v>1.625</v>
+        <v>0.875</v>
       </c>
       <c r="M108" s="5" t="n">
         <f aca="false">J108/32</f>
-        <v>0.8125</v>
+        <v>0.4375</v>
       </c>
       <c r="N108" s="5" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="O108" s="24" t="n">
         <v>1</v>
       </c>
       <c r="P108" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q108" s="1" t="n">
         <v>0</v>
@@ -5344,51 +5395,51 @@
     </row>
     <row r="109" s="39" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B109" s="22" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C109" s="40" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="D109" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E109" s="35" t="s">
         <v>25</v>
       </c>
       <c r="F109" s="41"/>
-      <c r="G109" s="22" t="n">
-        <v>0</v>
+      <c r="G109" s="35" t="n">
+        <v>2</v>
       </c>
       <c r="H109" s="35" t="s">
         <v>34</v>
       </c>
       <c r="I109" s="35" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="J109" s="4" t="n">
         <f aca="false">J108+D108</f>
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K109" s="5" t="n">
         <f aca="false">J109/8</f>
-        <v>3.375</v>
+        <v>2.25</v>
       </c>
       <c r="L109" s="5" t="n">
         <f aca="false">J109/16</f>
-        <v>1.6875</v>
+        <v>1.125</v>
       </c>
       <c r="M109" s="5" t="n">
         <f aca="false">J109/32</f>
-        <v>0.84375</v>
+        <v>0.5625</v>
       </c>
       <c r="N109" s="5" t="s">
-        <v>28</v>
+        <v>99</v>
       </c>
       <c r="O109" s="24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P109" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q109" s="1" t="n">
         <v>0</v>
@@ -5396,13 +5447,13 @@
     </row>
     <row r="110" s="39" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B110" s="22" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="C110" s="40" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="D110" s="1" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="E110" s="35" t="s">
         <v>25</v>
@@ -5414,156 +5465,156 @@
       <c r="H110" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="I110" s="35" t="s">
-        <v>199</v>
+      <c r="I110" s="22" t="s">
+        <v>227</v>
       </c>
       <c r="J110" s="4" t="n">
         <f aca="false">J109+D109</f>
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="K110" s="5" t="n">
         <f aca="false">J110/8</f>
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="L110" s="5" t="n">
         <f aca="false">J110/16</f>
-        <v>2</v>
+        <v>1.375</v>
       </c>
       <c r="M110" s="5" t="n">
         <f aca="false">J110/32</f>
-        <v>1</v>
+        <v>0.6875</v>
       </c>
       <c r="N110" s="5" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="O110" s="24" t="n">
         <v>1</v>
       </c>
       <c r="P110" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q110" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" s="39" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B111" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="C111" s="22" t="s">
-        <v>221</v>
+        <v>228</v>
+      </c>
+      <c r="C111" s="40" t="s">
+        <v>229</v>
       </c>
       <c r="D111" s="1" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="E111" s="35" t="s">
-        <v>161</v>
-      </c>
-      <c r="F111" s="35"/>
+        <v>25</v>
+      </c>
+      <c r="F111" s="41"/>
       <c r="G111" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H111" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="I111" s="35" t="s">
-        <v>199</v>
+      <c r="I111" s="22" t="s">
+        <v>230</v>
       </c>
       <c r="J111" s="4" t="n">
         <f aca="false">J110+D110</f>
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="K111" s="5" t="n">
         <f aca="false">J111/8</f>
-        <v>8</v>
+        <v>3.125</v>
       </c>
       <c r="L111" s="5" t="n">
         <f aca="false">J111/16</f>
-        <v>4</v>
+        <v>1.5625</v>
       </c>
       <c r="M111" s="5" t="n">
         <f aca="false">J111/32</f>
-        <v>2</v>
+        <v>0.78125</v>
       </c>
       <c r="N111" s="5" t="s">
-        <v>222</v>
+        <v>99</v>
       </c>
       <c r="O111" s="24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P111" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q111" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" s="39" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B112" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="C112" s="40" t="s">
+        <v>232</v>
+      </c>
+      <c r="D112" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="Q111" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B112" s="22" t="s">
-        <v>223</v>
-      </c>
-      <c r="C112" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="D112" s="1" t="n">
-        <v>32</v>
-      </c>
       <c r="E112" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="F112" s="35"/>
+      <c r="F112" s="41"/>
       <c r="G112" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112" s="35" t="s">
         <v>34</v>
       </c>
       <c r="I112" s="35" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="J112" s="4" t="n">
         <f aca="false">J111+D111</f>
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="K112" s="5" t="n">
         <f aca="false">J112/8</f>
-        <v>12</v>
+        <v>3.25</v>
       </c>
       <c r="L112" s="5" t="n">
         <f aca="false">J112/16</f>
-        <v>6</v>
+        <v>1.625</v>
       </c>
       <c r="M112" s="5" t="n">
         <f aca="false">J112/32</f>
-        <v>3</v>
+        <v>0.8125</v>
       </c>
       <c r="N112" s="5" t="s">
-        <v>222</v>
+        <v>99</v>
       </c>
       <c r="O112" s="24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P112" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q112" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" s="39" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B113" s="22" t="s">
-        <v>225</v>
-      </c>
-      <c r="C113" s="22" t="s">
-        <v>226</v>
+        <v>233</v>
+      </c>
+      <c r="C113" s="40" t="s">
+        <v>234</v>
       </c>
       <c r="D113" s="1" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="E113" s="35" t="s">
-        <v>161</v>
-      </c>
-      <c r="F113" s="35"/>
+        <v>25</v>
+      </c>
+      <c r="F113" s="41"/>
       <c r="G113" s="22" t="n">
         <v>0</v>
       </c>
@@ -5571,43 +5622,43 @@
         <v>34</v>
       </c>
       <c r="I113" s="35" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="J113" s="4" t="n">
         <f aca="false">J112+D112</f>
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="K113" s="5" t="n">
         <f aca="false">J113/8</f>
-        <v>16</v>
+        <v>3.375</v>
       </c>
       <c r="L113" s="5" t="n">
         <f aca="false">J113/16</f>
-        <v>8</v>
+        <v>1.6875</v>
       </c>
       <c r="M113" s="5" t="n">
         <f aca="false">J113/32</f>
-        <v>4</v>
+        <v>0.84375</v>
       </c>
       <c r="N113" s="5" t="s">
-        <v>222</v>
+        <v>28</v>
       </c>
       <c r="O113" s="24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P113" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q113" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" s="39" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B114" s="22" t="s">
-        <v>227</v>
-      </c>
-      <c r="C114" s="22" t="s">
-        <v>228</v>
+        <v>235</v>
+      </c>
+      <c r="C114" s="40" t="s">
+        <v>236</v>
       </c>
       <c r="D114" s="1" t="n">
         <v>32</v>
@@ -5615,40 +5666,40 @@
       <c r="E114" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="F114" s="35"/>
+      <c r="F114" s="41"/>
       <c r="G114" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H114" s="35" t="s">
         <v>34</v>
       </c>
       <c r="I114" s="35" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="J114" s="4" t="n">
         <f aca="false">J113+D113</f>
-        <v>160</v>
+        <v>32</v>
       </c>
       <c r="K114" s="5" t="n">
         <f aca="false">J114/8</f>
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="L114" s="5" t="n">
         <f aca="false">J114/16</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M114" s="5" t="n">
         <f aca="false">J114/32</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N114" s="5" t="s">
-        <v>222</v>
+        <v>99</v>
       </c>
       <c r="O114" s="24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P114" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q114" s="1" t="n">
         <v>0</v>
@@ -5656,16 +5707,16 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B115" s="22" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C115" s="22" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="D115" s="1" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E115" s="35" t="s">
-        <v>25</v>
+        <v>178</v>
       </c>
       <c r="F115" s="35"/>
       <c r="G115" s="22" t="n">
@@ -5675,29 +5726,29 @@
         <v>34</v>
       </c>
       <c r="I115" s="35" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="J115" s="4" t="n">
         <f aca="false">J114+D114</f>
-        <v>192</v>
+        <v>64</v>
       </c>
       <c r="K115" s="5" t="n">
         <f aca="false">J115/8</f>
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="L115" s="5" t="n">
         <f aca="false">J115/16</f>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M115" s="5" t="n">
         <f aca="false">J115/32</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N115" s="5" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="O115" s="24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P115" s="1" t="n">
         <v>1</v>
@@ -5708,13 +5759,13 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B116" s="22" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C116" s="22" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D116" s="1" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E116" s="35" t="s">
         <v>25</v>
@@ -5727,29 +5778,29 @@
         <v>34</v>
       </c>
       <c r="I116" s="35" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="J116" s="4" t="n">
         <f aca="false">J115+D115</f>
-        <v>200</v>
+        <v>96</v>
       </c>
       <c r="K116" s="5" t="n">
         <f aca="false">J116/8</f>
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="L116" s="5" t="n">
         <f aca="false">J116/16</f>
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="M116" s="5" t="n">
         <f aca="false">J116/32</f>
-        <v>6.25</v>
+        <v>3</v>
       </c>
       <c r="N116" s="5" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="O116" s="24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P116" s="1" t="n">
         <v>2</v>
@@ -5760,16 +5811,16 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B117" s="22" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C117" s="22" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D117" s="1" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E117" s="35" t="s">
-        <v>25</v>
+        <v>178</v>
       </c>
       <c r="F117" s="35"/>
       <c r="G117" s="22" t="n">
@@ -5779,29 +5830,29 @@
         <v>34</v>
       </c>
       <c r="I117" s="35" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="J117" s="4" t="n">
         <f aca="false">J116+D116</f>
-        <v>208</v>
+        <v>128</v>
       </c>
       <c r="K117" s="5" t="n">
         <f aca="false">J117/8</f>
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="L117" s="5" t="n">
         <f aca="false">J117/16</f>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M117" s="5" t="n">
         <f aca="false">J117/32</f>
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="N117" s="5" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="O117" s="24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P117" s="1" t="n">
         <v>3</v>
@@ -5812,13 +5863,13 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B118" s="22" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C118" s="22" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D118" s="1" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E118" s="35" t="s">
         <v>25</v>
@@ -5831,29 +5882,29 @@
         <v>34</v>
       </c>
       <c r="I118" s="35" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="J118" s="4" t="n">
         <f aca="false">J117+D117</f>
-        <v>216</v>
+        <v>160</v>
       </c>
       <c r="K118" s="5" t="n">
         <f aca="false">J118/8</f>
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="L118" s="5" t="n">
         <f aca="false">J118/16</f>
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="M118" s="5" t="n">
         <f aca="false">J118/32</f>
-        <v>6.75</v>
+        <v>5</v>
       </c>
       <c r="N118" s="5" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="O118" s="24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P118" s="1" t="n">
         <v>4</v>
@@ -5864,10 +5915,10 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B119" s="22" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C119" s="22" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D119" s="1" t="n">
         <v>8</v>
@@ -5883,32 +5934,32 @@
         <v>34</v>
       </c>
       <c r="I119" s="35" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="J119" s="4" t="n">
         <f aca="false">J118+D118</f>
-        <v>224</v>
+        <v>192</v>
       </c>
       <c r="K119" s="5" t="n">
         <f aca="false">J119/8</f>
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L119" s="5" t="n">
         <f aca="false">J119/16</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M119" s="5" t="n">
         <f aca="false">J119/32</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N119" s="5" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="O119" s="24" t="n">
         <v>4</v>
       </c>
       <c r="P119" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q119" s="1" t="n">
         <v>0</v>
@@ -5916,10 +5967,10 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B120" s="22" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C120" s="22" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="D120" s="1" t="n">
         <v>8</v>
@@ -5934,33 +5985,33 @@
       <c r="H120" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="I120" s="22" t="s">
-        <v>245</v>
+      <c r="I120" s="35" t="s">
+        <v>252</v>
       </c>
       <c r="J120" s="4" t="n">
         <f aca="false">J119+D119</f>
-        <v>232</v>
+        <v>200</v>
       </c>
       <c r="K120" s="5" t="n">
         <f aca="false">J120/8</f>
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L120" s="5" t="n">
         <f aca="false">J120/16</f>
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="M120" s="5" t="n">
         <f aca="false">J120/32</f>
-        <v>7.25</v>
+        <v>6.25</v>
       </c>
       <c r="N120" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O120" s="24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P120" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q120" s="1" t="n">
         <v>0</v>
@@ -5968,10 +6019,10 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B121" s="22" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C121" s="22" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="D121" s="1" t="n">
         <v>8</v>
@@ -5986,33 +6037,33 @@
       <c r="H121" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="I121" s="22" t="s">
-        <v>248</v>
+      <c r="I121" s="35" t="s">
+        <v>255</v>
       </c>
       <c r="J121" s="4" t="n">
         <f aca="false">J120+D120</f>
-        <v>240</v>
+        <v>208</v>
       </c>
       <c r="K121" s="5" t="n">
         <f aca="false">J121/8</f>
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L121" s="5" t="n">
         <f aca="false">J121/16</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M121" s="5" t="n">
         <f aca="false">J121/32</f>
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="N121" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O121" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="P121" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="P121" s="1" t="n">
-        <v>2</v>
       </c>
       <c r="Q121" s="1" t="n">
         <v>0</v>
@@ -6020,10 +6071,10 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B122" s="22" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C122" s="22" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="D122" s="1" t="n">
         <v>8</v>
@@ -6038,33 +6089,33 @@
       <c r="H122" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="I122" s="22" t="s">
-        <v>250</v>
+      <c r="I122" s="35" t="s">
+        <v>258</v>
       </c>
       <c r="J122" s="4" t="n">
         <f aca="false">J121+D121</f>
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="K122" s="5" t="n">
         <f aca="false">J122/8</f>
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L122" s="5" t="n">
         <f aca="false">J122/16</f>
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="M122" s="5" t="n">
         <f aca="false">J122/32</f>
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
       <c r="N122" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O122" s="24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P122" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q122" s="1" t="n">
         <v>0</v>
@@ -6072,10 +6123,10 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B123" s="22" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C123" s="22" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="D123" s="1" t="n">
         <v>8</v>
@@ -6090,33 +6141,33 @@
       <c r="H123" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="I123" s="22" t="s">
-        <v>252</v>
+      <c r="I123" s="35" t="s">
+        <v>261</v>
       </c>
       <c r="J123" s="4" t="n">
         <f aca="false">J122+D122</f>
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="K123" s="5" t="n">
         <f aca="false">J123/8</f>
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L123" s="5" t="n">
         <f aca="false">J123/16</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M123" s="5" t="n">
         <f aca="false">J123/32</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N123" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O123" s="24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P123" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q123" s="1" t="n">
         <v>0</v>
@@ -6124,10 +6175,10 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B124" s="22" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="C124" s="22" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="D124" s="1" t="n">
         <v>8</v>
@@ -6143,32 +6194,32 @@
         <v>34</v>
       </c>
       <c r="I124" s="22" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="J124" s="4" t="n">
         <f aca="false">J123+D123</f>
-        <v>264</v>
+        <v>232</v>
       </c>
       <c r="K124" s="5" t="n">
         <f aca="false">J124/8</f>
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L124" s="5" t="n">
         <f aca="false">J124/16</f>
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="M124" s="5" t="n">
         <f aca="false">J124/32</f>
-        <v>8.25</v>
+        <v>7.25</v>
       </c>
       <c r="N124" s="5" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="O124" s="24" t="n">
         <v>3</v>
       </c>
       <c r="P124" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q124" s="1" t="n">
         <v>0</v>
@@ -6176,10 +6227,10 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B125" s="22" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="C125" s="22" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="D125" s="1" t="n">
         <v>8</v>
@@ -6195,32 +6246,32 @@
         <v>34</v>
       </c>
       <c r="I125" s="22" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="J125" s="4" t="n">
         <f aca="false">J124+D124</f>
-        <v>272</v>
+        <v>240</v>
       </c>
       <c r="K125" s="5" t="n">
         <f aca="false">J125/8</f>
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L125" s="5" t="n">
         <f aca="false">J125/16</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M125" s="5" t="n">
         <f aca="false">J125/32</f>
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="N125" s="5" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="O125" s="24" t="n">
         <v>3</v>
       </c>
       <c r="P125" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q125" s="1" t="n">
         <v>0</v>
@@ -6228,10 +6279,10 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B126" s="22" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="C126" s="22" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D126" s="1" t="n">
         <v>8</v>
@@ -6247,32 +6298,32 @@
         <v>34</v>
       </c>
       <c r="I126" s="22" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="J126" s="4" t="n">
         <f aca="false">J125+D125</f>
-        <v>280</v>
+        <v>248</v>
       </c>
       <c r="K126" s="5" t="n">
         <f aca="false">J126/8</f>
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="L126" s="5" t="n">
         <f aca="false">J126/16</f>
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="M126" s="5" t="n">
         <f aca="false">J126/32</f>
-        <v>8.75</v>
+        <v>7.75</v>
       </c>
       <c r="N126" s="5" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="O126" s="24" t="n">
         <v>3</v>
       </c>
       <c r="P126" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q126" s="1" t="n">
         <v>0</v>
@@ -6280,10 +6331,10 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B127" s="22" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="C127" s="22" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="D127" s="1" t="n">
         <v>8</v>
@@ -6299,32 +6350,32 @@
         <v>34</v>
       </c>
       <c r="I127" s="22" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="J127" s="4" t="n">
         <f aca="false">J126+D126</f>
-        <v>288</v>
+        <v>256</v>
       </c>
       <c r="K127" s="5" t="n">
         <f aca="false">J127/8</f>
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L127" s="5" t="n">
         <f aca="false">J127/16</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M127" s="5" t="n">
         <f aca="false">J127/32</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N127" s="5" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="O127" s="24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P127" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q127" s="1" t="n">
         <v>0</v>
@@ -6332,10 +6383,10 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B128" s="22" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="C128" s="22" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="D128" s="1" t="n">
         <v>8</v>
@@ -6351,32 +6402,32 @@
         <v>34</v>
       </c>
       <c r="I128" s="22" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="J128" s="4" t="n">
         <f aca="false">J127+D127</f>
-        <v>296</v>
+        <v>264</v>
       </c>
       <c r="K128" s="5" t="n">
         <f aca="false">J128/8</f>
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="L128" s="5" t="n">
         <f aca="false">J128/16</f>
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="M128" s="5" t="n">
         <f aca="false">J128/32</f>
-        <v>9.25</v>
+        <v>8.25</v>
       </c>
       <c r="N128" s="5" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="O128" s="24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P128" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q128" s="1" t="n">
         <v>0</v>
@@ -6384,10 +6435,10 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B129" s="22" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="C129" s="22" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="D129" s="1" t="n">
         <v>8</v>
@@ -6403,32 +6454,32 @@
         <v>34</v>
       </c>
       <c r="I129" s="22" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="J129" s="4" t="n">
         <f aca="false">J128+D128</f>
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="K129" s="5" t="n">
         <f aca="false">J129/8</f>
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L129" s="5" t="n">
         <f aca="false">J129/16</f>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M129" s="5" t="n">
         <f aca="false">J129/32</f>
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="N129" s="5" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="O129" s="24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P129" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q129" s="1" t="n">
         <v>0</v>
@@ -6436,10 +6487,10 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B130" s="22" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="C130" s="22" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="D130" s="1" t="n">
         <v>8</v>
@@ -6455,32 +6506,32 @@
         <v>34</v>
       </c>
       <c r="I130" s="22" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="J130" s="4" t="n">
         <f aca="false">J129+D129</f>
-        <v>312</v>
+        <v>280</v>
       </c>
       <c r="K130" s="5" t="n">
         <f aca="false">J130/8</f>
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="L130" s="5" t="n">
         <f aca="false">J130/16</f>
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="M130" s="5" t="n">
         <f aca="false">J130/32</f>
-        <v>9.75</v>
+        <v>8.75</v>
       </c>
       <c r="N130" s="5" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="O130" s="24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P130" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q130" s="1" t="n">
         <v>0</v>
@@ -6488,10 +6539,10 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B131" s="22" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="C131" s="22" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="D131" s="1" t="n">
         <v>8</v>
@@ -6507,32 +6558,32 @@
         <v>34</v>
       </c>
       <c r="I131" s="22" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="J131" s="4" t="n">
         <f aca="false">J130+D130</f>
-        <v>320</v>
+        <v>288</v>
       </c>
       <c r="K131" s="5" t="n">
         <f aca="false">J131/8</f>
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="L131" s="5" t="n">
         <f aca="false">J131/16</f>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M131" s="5" t="n">
         <f aca="false">J131/32</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N131" s="5" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="O131" s="24" t="n">
         <v>2</v>
       </c>
       <c r="P131" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q131" s="1" t="n">
         <v>0</v>
@@ -6540,10 +6591,10 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B132" s="22" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="C132" s="22" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="D132" s="1" t="n">
         <v>8</v>
@@ -6559,32 +6610,32 @@
         <v>34</v>
       </c>
       <c r="I132" s="22" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="J132" s="4" t="n">
         <f aca="false">J131+D131</f>
-        <v>328</v>
+        <v>296</v>
       </c>
       <c r="K132" s="5" t="n">
         <f aca="false">J132/8</f>
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="L132" s="5" t="n">
         <f aca="false">J132/16</f>
-        <v>20.5</v>
+        <v>18.5</v>
       </c>
       <c r="M132" s="5" t="n">
         <f aca="false">J132/32</f>
-        <v>10.25</v>
+        <v>9.25</v>
       </c>
       <c r="N132" s="5" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="O132" s="24" t="n">
         <v>2</v>
       </c>
       <c r="P132" s="1" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q132" s="1" t="n">
         <v>0</v>
@@ -6592,10 +6643,10 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B133" s="22" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C133" s="22" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="D133" s="1" t="n">
         <v>8</v>
@@ -6611,32 +6662,32 @@
         <v>34</v>
       </c>
       <c r="I133" s="22" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="J133" s="4" t="n">
         <f aca="false">J132+D132</f>
-        <v>336</v>
+        <v>304</v>
       </c>
       <c r="K133" s="5" t="n">
         <f aca="false">J133/8</f>
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L133" s="5" t="n">
         <f aca="false">J133/16</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M133" s="5" t="n">
         <f aca="false">J133/32</f>
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="N133" s="5" t="s">
-        <v>92</v>
+        <v>239</v>
       </c>
       <c r="O133" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P133" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q133" s="1" t="n">
         <v>0</v>
@@ -6644,10 +6695,10 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B134" s="22" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="C134" s="22" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="D134" s="1" t="n">
         <v>8</v>
@@ -6663,32 +6714,32 @@
         <v>34</v>
       </c>
       <c r="I134" s="22" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="J134" s="4" t="n">
         <f aca="false">J133+D133</f>
-        <v>344</v>
+        <v>312</v>
       </c>
       <c r="K134" s="5" t="n">
         <f aca="false">J134/8</f>
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L134" s="5" t="n">
         <f aca="false">J134/16</f>
-        <v>21.5</v>
+        <v>19.5</v>
       </c>
       <c r="M134" s="5" t="n">
         <f aca="false">J134/32</f>
-        <v>10.75</v>
+        <v>9.75</v>
       </c>
       <c r="N134" s="5" t="s">
-        <v>92</v>
+        <v>239</v>
       </c>
       <c r="O134" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P134" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q134" s="1" t="n">
         <v>0</v>
@@ -6696,10 +6747,10 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B135" s="22" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="C135" s="22" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="D135" s="1" t="n">
         <v>8</v>
@@ -6715,32 +6766,32 @@
         <v>34</v>
       </c>
       <c r="I135" s="22" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="J135" s="4" t="n">
         <f aca="false">J134+D134</f>
-        <v>352</v>
+        <v>320</v>
       </c>
       <c r="K135" s="5" t="n">
         <f aca="false">J135/8</f>
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L135" s="5" t="n">
         <f aca="false">J135/16</f>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M135" s="5" t="n">
         <f aca="false">J135/32</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N135" s="5" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="O135" s="24" t="n">
         <v>2</v>
       </c>
       <c r="P135" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q135" s="1" t="n">
         <v>0</v>
@@ -6748,10 +6799,10 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B136" s="22" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="C136" s="22" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D136" s="1" t="n">
         <v>8</v>
@@ -6767,32 +6818,32 @@
         <v>34</v>
       </c>
       <c r="I136" s="22" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="J136" s="4" t="n">
         <f aca="false">J135+D135</f>
-        <v>360</v>
+        <v>328</v>
       </c>
       <c r="K136" s="5" t="n">
         <f aca="false">J136/8</f>
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="L136" s="5" t="n">
         <f aca="false">J136/16</f>
-        <v>22.5</v>
+        <v>20.5</v>
       </c>
       <c r="M136" s="5" t="n">
         <f aca="false">J136/32</f>
-        <v>11.25</v>
+        <v>10.25</v>
       </c>
       <c r="N136" s="5" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="O136" s="24" t="n">
         <v>2</v>
       </c>
       <c r="P136" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q136" s="1" t="n">
         <v>0</v>
@@ -6800,10 +6851,10 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B137" s="22" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C137" s="22" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="D137" s="1" t="n">
         <v>8</v>
@@ -6819,32 +6870,32 @@
         <v>34</v>
       </c>
       <c r="I137" s="22" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="J137" s="4" t="n">
         <f aca="false">J136+D136</f>
-        <v>368</v>
+        <v>336</v>
       </c>
       <c r="K137" s="5" t="n">
         <f aca="false">J137/8</f>
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L137" s="5" t="n">
         <f aca="false">J137/16</f>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M137" s="5" t="n">
         <f aca="false">J137/32</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="N137" s="5" t="s">
-        <v>222</v>
+        <v>99</v>
       </c>
       <c r="O137" s="24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P137" s="1" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Q137" s="1" t="n">
         <v>0</v>
@@ -6852,10 +6903,10 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B138" s="22" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="C138" s="22" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="D138" s="1" t="n">
         <v>8</v>
@@ -6871,32 +6922,32 @@
         <v>34</v>
       </c>
       <c r="I138" s="22" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="J138" s="4" t="n">
         <f aca="false">J137+D137</f>
-        <v>376</v>
+        <v>344</v>
       </c>
       <c r="K138" s="5" t="n">
         <f aca="false">J138/8</f>
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="L138" s="5" t="n">
         <f aca="false">J138/16</f>
-        <v>23.5</v>
+        <v>21.5</v>
       </c>
       <c r="M138" s="5" t="n">
         <f aca="false">J138/32</f>
-        <v>11.75</v>
+        <v>10.75</v>
       </c>
       <c r="N138" s="5" t="s">
-        <v>222</v>
+        <v>99</v>
       </c>
       <c r="O138" s="24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P138" s="1" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q138" s="1" t="n">
         <v>0</v>
@@ -6904,10 +6955,10 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B139" s="22" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C139" s="22" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="D139" s="1" t="n">
         <v>8</v>
@@ -6923,32 +6974,32 @@
         <v>34</v>
       </c>
       <c r="I139" s="22" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="J139" s="4" t="n">
         <f aca="false">J138+D138</f>
-        <v>384</v>
+        <v>352</v>
       </c>
       <c r="K139" s="5" t="n">
         <f aca="false">J139/8</f>
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L139" s="5" t="n">
         <f aca="false">J139/16</f>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M139" s="5" t="n">
         <f aca="false">J139/32</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N139" s="5" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="O139" s="24" t="n">
         <v>2</v>
       </c>
       <c r="P139" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q139" s="1" t="n">
         <v>0</v>
@@ -6956,10 +7007,10 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B140" s="22" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="C140" s="22" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="D140" s="1" t="n">
         <v>8</v>
@@ -6975,32 +7026,32 @@
         <v>34</v>
       </c>
       <c r="I140" s="22" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="J140" s="4" t="n">
         <f aca="false">J139+D139</f>
-        <v>392</v>
+        <v>360</v>
       </c>
       <c r="K140" s="5" t="n">
         <f aca="false">J140/8</f>
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L140" s="5" t="n">
         <f aca="false">J140/16</f>
-        <v>24.5</v>
+        <v>22.5</v>
       </c>
       <c r="M140" s="5" t="n">
         <f aca="false">J140/32</f>
-        <v>12.25</v>
+        <v>11.25</v>
       </c>
       <c r="N140" s="5" t="s">
-        <v>92</v>
+        <v>239</v>
       </c>
       <c r="O140" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P140" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q140" s="1" t="n">
         <v>0</v>
@@ -7008,10 +7059,10 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B141" s="22" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="C141" s="22" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D141" s="1" t="n">
         <v>8</v>
@@ -7027,32 +7078,32 @@
         <v>34</v>
       </c>
       <c r="I141" s="22" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="J141" s="4" t="n">
         <f aca="false">J140+D140</f>
-        <v>400</v>
+        <v>368</v>
       </c>
       <c r="K141" s="5" t="n">
         <f aca="false">J141/8</f>
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L141" s="5" t="n">
         <f aca="false">J141/16</f>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M141" s="5" t="n">
         <f aca="false">J141/32</f>
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="N141" s="5" t="s">
-        <v>92</v>
+        <v>239</v>
       </c>
       <c r="O141" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P141" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q141" s="1" t="n">
         <v>0</v>
@@ -7060,10 +7111,10 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B142" s="22" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="C142" s="22" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D142" s="1" t="n">
         <v>8</v>
@@ -7079,86 +7130,84 @@
         <v>34</v>
       </c>
       <c r="I142" s="22" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="J142" s="4" t="n">
         <f aca="false">J141+D141</f>
-        <v>408</v>
+        <v>376</v>
       </c>
       <c r="K142" s="5" t="n">
         <f aca="false">J142/8</f>
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="L142" s="5" t="n">
         <f aca="false">J142/16</f>
-        <v>25.5</v>
+        <v>23.5</v>
       </c>
       <c r="M142" s="5" t="n">
         <f aca="false">J142/32</f>
-        <v>12.75</v>
+        <v>11.75</v>
       </c>
       <c r="N142" s="5" t="s">
-        <v>92</v>
+        <v>239</v>
       </c>
       <c r="O142" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P142" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q142" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B143" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="C143" s="3" t="s">
-        <v>293</v>
+      <c r="B143" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="C143" s="22" t="s">
+        <v>302</v>
       </c>
       <c r="D143" s="1" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E143" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="F143" s="35" t="s">
-        <v>63</v>
-      </c>
+      <c r="F143" s="35"/>
       <c r="G143" s="22" t="n">
         <v>0</v>
       </c>
       <c r="H143" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="I143" s="3" t="s">
-        <v>292</v>
+      <c r="I143" s="22" t="s">
+        <v>301</v>
       </c>
       <c r="J143" s="4" t="n">
         <f aca="false">J142+D142</f>
-        <v>416</v>
+        <v>384</v>
       </c>
       <c r="K143" s="5" t="n">
         <f aca="false">J143/8</f>
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L143" s="5" t="n">
         <f aca="false">J143/16</f>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M143" s="5" t="n">
         <f aca="false">J143/32</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N143" s="5" t="s">
-        <v>92</v>
+        <v>239</v>
       </c>
       <c r="O143" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P143" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q143" s="1" t="n">
         <v>0</v>
@@ -7166,10 +7215,10 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B144" s="22" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="C144" s="22" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D144" s="1" t="n">
         <v>8</v>
@@ -7179,55 +7228,55 @@
       </c>
       <c r="F144" s="35"/>
       <c r="G144" s="22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H144" s="35" t="s">
         <v>34</v>
       </c>
       <c r="I144" s="22" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="J144" s="4" t="n">
         <f aca="false">J143+D143</f>
-        <v>432</v>
+        <v>392</v>
       </c>
       <c r="K144" s="5" t="n">
         <f aca="false">J144/8</f>
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="L144" s="5" t="n">
         <f aca="false">J144/16</f>
-        <v>27</v>
+        <v>24.5</v>
       </c>
       <c r="M144" s="5" t="n">
         <f aca="false">J144/32</f>
-        <v>13.5</v>
+        <v>12.25</v>
       </c>
       <c r="N144" s="5" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="O144" s="24" t="n">
         <v>1</v>
       </c>
       <c r="P144" s="1" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q144" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B145" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C145" s="3" t="s">
-        <v>297</v>
+      <c r="B145" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="C145" s="22" t="s">
+        <v>306</v>
       </c>
       <c r="D145" s="1" t="n">
         <v>8</v>
       </c>
       <c r="E145" s="35" t="s">
-        <v>298</v>
+        <v>25</v>
       </c>
       <c r="F145" s="35"/>
       <c r="G145" s="22" t="n">
@@ -7236,73 +7285,279 @@
       <c r="H145" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="I145" s="35" t="s">
-        <v>199</v>
+      <c r="I145" s="22" t="s">
+        <v>305</v>
       </c>
       <c r="J145" s="4" t="n">
         <f aca="false">J144+D144</f>
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="K145" s="5" t="n">
         <f aca="false">J145/8</f>
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="L145" s="5" t="n">
         <f aca="false">J145/16</f>
-        <v>27.5</v>
+        <v>25</v>
       </c>
       <c r="M145" s="5" t="n">
         <f aca="false">J145/32</f>
-        <v>13.75</v>
+        <v>12.5</v>
       </c>
       <c r="N145" s="5" t="s">
-        <v>28</v>
+        <v>99</v>
       </c>
       <c r="O145" s="24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P145" s="1" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q145" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="1" t="s">
-        <v>44</v>
+      <c r="B146" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="C146" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="D146" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E146" s="35" t="s">
+        <v>25</v>
       </c>
       <c r="F146" s="35"/>
-      <c r="G146" s="35"/>
-      <c r="H146" s="35"/>
-      <c r="I146" s="35"/>
+      <c r="G146" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="I146" s="22" t="s">
+        <v>307</v>
+      </c>
       <c r="J146" s="4" t="n">
         <f aca="false">J145+D145</f>
-        <v>448</v>
+        <v>408</v>
       </c>
       <c r="K146" s="5" t="n">
         <f aca="false">J146/8</f>
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L146" s="5" t="n">
         <f aca="false">J146/16</f>
-        <v>28</v>
+        <v>25.5</v>
       </c>
       <c r="M146" s="5" t="n">
         <f aca="false">J146/32</f>
+        <v>12.75</v>
+      </c>
+      <c r="N146" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="O146" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P146" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q146" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B147" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D147" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="E147" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="F147" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="G147" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="I147" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="J147" s="4" t="n">
+        <f aca="false">J146+D146</f>
+        <v>416</v>
+      </c>
+      <c r="K147" s="5" t="n">
+        <f aca="false">J147/8</f>
+        <v>52</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <f aca="false">J147/16</f>
+        <v>26</v>
+      </c>
+      <c r="M147" s="5" t="n">
+        <f aca="false">J147/32</f>
+        <v>13</v>
+      </c>
+      <c r="N147" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="O147" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P147" s="1" t="n">
         <v>14</v>
       </c>
-    </row>
-    <row r="147" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C147" s="3"/>
-      <c r="H147" s="3"/>
-      <c r="J147" s="42"/>
-      <c r="O147" s="3"/>
-    </row>
-    <row r="1048299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="Q147" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B148" s="22" t="s">
+        <v>311</v>
+      </c>
+      <c r="C148" s="22" t="s">
+        <v>312</v>
+      </c>
+      <c r="D148" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E148" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="F148" s="35"/>
+      <c r="G148" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H148" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="I148" s="22" t="s">
+        <v>311</v>
+      </c>
+      <c r="J148" s="4" t="n">
+        <f aca="false">J147+D147</f>
+        <v>432</v>
+      </c>
+      <c r="K148" s="5" t="n">
+        <f aca="false">J148/8</f>
+        <v>54</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <f aca="false">J148/16</f>
+        <v>27</v>
+      </c>
+      <c r="M148" s="5" t="n">
+        <f aca="false">J148/32</f>
+        <v>13.5</v>
+      </c>
+      <c r="N148" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="O148" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P148" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q148" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B149" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D149" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E149" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="F149" s="35"/>
+      <c r="G149" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="I149" s="35" t="s">
+        <v>216</v>
+      </c>
+      <c r="J149" s="4" t="n">
+        <f aca="false">J148+D148</f>
+        <v>440</v>
+      </c>
+      <c r="K149" s="5" t="n">
+        <f aca="false">J149/8</f>
+        <v>55</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <f aca="false">J149/16</f>
+        <v>27.5</v>
+      </c>
+      <c r="M149" s="5" t="n">
+        <f aca="false">J149/32</f>
+        <v>13.75</v>
+      </c>
+      <c r="N149" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O149" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q149" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F150" s="35"/>
+      <c r="G150" s="35"/>
+      <c r="H150" s="35"/>
+      <c r="I150" s="35"/>
+      <c r="J150" s="4" t="n">
+        <f aca="false">J149+D149</f>
+        <v>448</v>
+      </c>
+      <c r="K150" s="5" t="n">
+        <f aca="false">J150/8</f>
+        <v>56</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <f aca="false">J150/16</f>
+        <v>28</v>
+      </c>
+      <c r="M150" s="5" t="n">
+        <f aca="false">J150/32</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="151" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C151" s="3"/>
+      <c r="H151" s="3"/>
+      <c r="J151" s="42"/>
+      <c r="O151" s="3"/>
+    </row>
     <row r="1048303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -7584,10 +7839,10 @@
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="B4:I4"/>
     <mergeCell ref="B5:I5"/>
-    <mergeCell ref="B38:I38"/>
+    <mergeCell ref="B40:I40"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A100" r:id="rId1" display="Structure:rt1Errors_t,file:rt1ErrorsDownlink.h"/>
+    <hyperlink ref="A104" r:id="rId1" display="Structure:rt1Errors_t,file:rt1ErrorsDownlink.h"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -7615,22 +7870,22 @@
     <row r="6" s="43" customFormat="true" ht="34.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="44"/>
       <c r="C6" s="44" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="D6" s="44" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="F6" s="44" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="G6" s="44" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="H6" s="44" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="I6" s="44"/>
     </row>

--- a/TelemDefinition/DownlinkSpecPacsat.xlsx
+++ b/TelemDefinition/DownlinkSpecPacsat.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="DownlinkSpecPacsat" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="DownlinkSpecPacsat" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -155,6 +155,9 @@
     <t xml:space="preserve">The spacecraft mode e.g. SAFE MODE</t>
   </si>
   <si>
+    <t xml:space="preserve">Telem &amp; Control</t>
+  </si>
+  <si>
     <t xml:space="preserve">END</t>
   </si>
   <si>
@@ -420,9 +423,6 @@
   </si>
   <si>
     <t xml:space="preserve">The current logging level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Telem &amp; Control</t>
   </si>
   <si>
     <t xml:space="preserve">Time Period</t>
@@ -1125,188 +1125,172 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1322,13 +1306,119 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q1048576"/>
-  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="53.01"/>
@@ -1339,8 +1429,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="23.94"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="8.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="50.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="4" width="8.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="11" style="5" width="8.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="10" style="4" width="8.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="18.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="3" width="8.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="13.22"/>
@@ -1351,194 +1440,194 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
     </row>
     <row r="2" customFormat="false" ht="14.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="10" t="n">
+      <c r="B6" s="8"/>
+      <c r="C6" s="9" t="n">
         <v>44173</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="14"/>
-    </row>
-    <row r="8" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="16" t="s">
+      <c r="B7" s="11"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="13"/>
+    </row>
+    <row r="8" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="H8" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="18" t="s">
+      <c r="J8" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K8" s="19" t="s">
+      <c r="K8" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="L8" s="19" t="s">
+      <c r="L8" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="M8" s="19" t="s">
+      <c r="M8" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="N8" s="20" t="s">
+      <c r="N8" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="O8" s="21" t="s">
+      <c r="O8" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="P8" s="15" t="s">
+      <c r="P8" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="Q8" s="15" t="s">
+      <c r="Q8" s="14" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="63.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="22" t="s">
+    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="20" t="n">
         <v>32</v>
       </c>
-      <c r="E9" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="22" t="s">
+      <c r="E9" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="I9" s="23" t="s">
+      <c r="I9" s="21" t="s">
         <v>27</v>
       </c>
       <c r="J9" s="4" t="n">
         <f aca="false">J7+D7</f>
         <v>0</v>
       </c>
-      <c r="K9" s="5" t="n">
+      <c r="K9" s="4" t="n">
         <f aca="false">J9/8</f>
         <v>0</v>
       </c>
-      <c r="L9" s="5" t="n">
+      <c r="L9" s="4" t="n">
         <f aca="false">J9/16</f>
         <v>0</v>
       </c>
-      <c r="M9" s="5" t="n">
+      <c r="M9" s="4" t="n">
         <f aca="false">J9/32</f>
         <v>0</v>
       </c>
-      <c r="N9" s="5" t="s">
+      <c r="N9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O9" s="24" t="n">
+      <c r="O9" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P9" s="1" t="n">
@@ -1548,49 +1637,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="88.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="22" t="s">
+    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="E10" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="22" t="s">
+      <c r="E10" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="I10" s="23" t="s">
+      <c r="I10" s="21" t="s">
         <v>31</v>
       </c>
       <c r="J10" s="4" t="n">
         <f aca="false">J9+D9</f>
         <v>32</v>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="K10" s="4" t="n">
         <f aca="false">J10/8</f>
         <v>4</v>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="L10" s="4" t="n">
         <f aca="false">J10/16</f>
         <v>2</v>
       </c>
-      <c r="M10" s="5" t="n">
+      <c r="M10" s="4" t="n">
         <f aca="false">J10/32</f>
         <v>1</v>
       </c>
-      <c r="N10" s="5" t="s">
+      <c r="N10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="24" t="n">
+      <c r="O10" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P10" s="1" t="n">
@@ -1601,48 +1690,48 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="37.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="E11" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="22" t="s">
+      <c r="E11" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I11" s="23" t="s">
+      <c r="I11" s="21" t="s">
         <v>35</v>
       </c>
       <c r="J11" s="4" t="n">
         <f aca="false">J10+D10</f>
         <v>48</v>
       </c>
-      <c r="K11" s="5" t="n">
+      <c r="K11" s="4" t="n">
         <f aca="false">J11/8</f>
         <v>6</v>
       </c>
-      <c r="L11" s="5" t="n">
+      <c r="L11" s="4" t="n">
         <f aca="false">J11/16</f>
         <v>3</v>
       </c>
-      <c r="M11" s="5" t="n">
+      <c r="M11" s="4" t="n">
         <f aca="false">J11/32</f>
         <v>1.5</v>
       </c>
-      <c r="N11" s="5" t="s">
+      <c r="N11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O11" s="24" t="n">
+      <c r="O11" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P11" s="1" t="n">
@@ -1653,48 +1742,48 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="37.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="E12" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="22" t="s">
+      <c r="E12" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="23" t="s">
+      <c r="I12" s="21" t="s">
         <v>38</v>
       </c>
       <c r="J12" s="4" t="n">
         <f aca="false">J11+D11</f>
         <v>56</v>
       </c>
-      <c r="K12" s="5" t="n">
+      <c r="K12" s="4" t="n">
         <f aca="false">J12/8</f>
         <v>7</v>
       </c>
-      <c r="L12" s="5" t="n">
+      <c r="L12" s="4" t="n">
         <f aca="false">J12/16</f>
         <v>3.5</v>
       </c>
-      <c r="M12" s="5" t="n">
+      <c r="M12" s="4" t="n">
         <f aca="false">J12/32</f>
         <v>1.75</v>
       </c>
-      <c r="N12" s="5" t="s">
+      <c r="N12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O12" s="24" t="n">
+      <c r="O12" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P12" s="1" t="n">
@@ -1705,48 +1794,48 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="37.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="E13" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="22" t="s">
+      <c r="E13" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I13" s="23" t="s">
+      <c r="I13" s="21" t="s">
         <v>38</v>
       </c>
       <c r="J13" s="4" t="n">
         <f aca="false">J12+D12</f>
         <v>64</v>
       </c>
-      <c r="K13" s="5" t="n">
+      <c r="K13" s="4" t="n">
         <f aca="false">J13/8</f>
         <v>8</v>
       </c>
-      <c r="L13" s="5" t="n">
+      <c r="L13" s="4" t="n">
         <f aca="false">J13/16</f>
         <v>4</v>
       </c>
-      <c r="M13" s="5" t="n">
+      <c r="M13" s="4" t="n">
         <f aca="false">J13/32</f>
         <v>2</v>
       </c>
-      <c r="N13" s="5" t="s">
+      <c r="N13" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O13" s="24" t="n">
+      <c r="O13" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P13" s="1" t="n">
@@ -1757,209 +1846,209 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="37.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="E14" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="22"/>
-      <c r="I14" s="23" t="s">
+      <c r="E14" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" s="20"/>
+      <c r="I14" s="21" t="s">
         <v>43</v>
       </c>
       <c r="J14" s="4" t="n">
         <f aca="false">J13+D13</f>
         <v>72</v>
       </c>
-      <c r="K14" s="5" t="n">
+      <c r="K14" s="4" t="n">
         <f aca="false">J14/8</f>
         <v>9</v>
       </c>
-      <c r="L14" s="5" t="n">
+      <c r="L14" s="4" t="n">
         <f aca="false">J14/16</f>
         <v>4.5</v>
       </c>
-      <c r="M14" s="5" t="n">
+      <c r="M14" s="4" t="n">
         <f aca="false">J14/32</f>
         <v>2.25</v>
       </c>
-      <c r="N14" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="O14" s="24" t="n">
-        <v>0</v>
+      <c r="N14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="O14" s="22" t="n">
+        <v>1</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="25" t="s">
-        <v>44</v>
+      <c r="A15" s="23" t="s">
+        <v>45</v>
       </c>
       <c r="C15" s="2"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
       <c r="H15" s="2"/>
-      <c r="I15" s="25" t="s">
-        <v>45</v>
+      <c r="I15" s="23" t="s">
+        <v>46</v>
       </c>
       <c r="J15" s="4" t="n">
         <f aca="false">J14+D14</f>
         <v>80</v>
       </c>
-      <c r="K15" s="5" t="n">
+      <c r="K15" s="4" t="n">
         <f aca="false">J15/8</f>
         <v>10</v>
       </c>
-      <c r="L15" s="5" t="n">
+      <c r="L15" s="4" t="n">
         <f aca="false">J15/16</f>
         <v>5</v>
       </c>
-      <c r="M15" s="5" t="n">
+      <c r="M15" s="4" t="n">
         <f aca="false">J15/32</f>
         <v>2.5</v>
       </c>
-      <c r="N15" s="5"/>
-      <c r="O15" s="24"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="22"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="25"/>
+      <c r="B16" s="23"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="25"/>
+      <c r="B17" s="23"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B18" s="25"/>
+      <c r="B18" s="23"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="25"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="27"/>
-      <c r="L19" s="27"/>
-      <c r="M19" s="27"/>
-    </row>
-    <row r="20" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="25"/>
+    </row>
+    <row r="20" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="13" t="s">
+      <c r="F20" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G20" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="H20" s="13" t="s">
+      <c r="H20" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="I20" s="14" t="s">
+      <c r="I20" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J20" s="29" t="s">
+      <c r="J20" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="K20" s="15" t="s">
+      <c r="K20" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="L20" s="15" t="s">
+      <c r="L20" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="M20" s="15" t="s">
+      <c r="M20" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="N20" s="20" t="s">
+      <c r="N20" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="O20" s="21" t="s">
+      <c r="O20" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="P20" s="15" t="s">
+      <c r="P20" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="Q20" s="15" t="s">
+      <c r="Q20" s="14" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="30" t="s">
+      <c r="B21" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="30" t="n">
+      <c r="C21" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="26" t="n">
         <v>32</v>
       </c>
-      <c r="E21" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="23"/>
-      <c r="G21" s="22" t="n">
+      <c r="E21" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="21"/>
+      <c r="G21" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="H21" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="I21" s="23" t="s">
+      <c r="H21" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="J21" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="27" t="n">
+      <c r="I21" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J21" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="25" t="n">
         <f aca="false">J21/8</f>
         <v>0</v>
       </c>
-      <c r="L21" s="27" t="n">
+      <c r="L21" s="25" t="n">
         <f aca="false">J21/16</f>
         <v>0</v>
       </c>
-      <c r="M21" s="27" t="n">
+      <c r="M21" s="25" t="n">
         <f aca="false">J21/32</f>
         <v>0</v>
       </c>
-      <c r="N21" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O21" s="24" t="n">
+      <c r="N21" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O21" s="22" t="n">
         <v>4</v>
       </c>
       <c r="P21" s="1" t="n">
@@ -1970,48 +2059,48 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="30" t="s">
+      <c r="B22" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="30" t="n">
+      <c r="C22" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="26" t="n">
         <v>16</v>
       </c>
-      <c r="E22" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="23"/>
-      <c r="G22" s="22" t="n">
+      <c r="E22" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="21"/>
+      <c r="G22" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="H22" s="22" t="s">
+      <c r="H22" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I22" s="23" t="s">
-        <v>54</v>
+      <c r="I22" s="21" t="s">
+        <v>55</v>
       </c>
       <c r="J22" s="4" t="n">
         <f aca="false">J21+D21</f>
         <v>32</v>
       </c>
-      <c r="K22" s="5" t="n">
+      <c r="K22" s="4" t="n">
         <f aca="false">J22/8</f>
         <v>4</v>
       </c>
-      <c r="L22" s="5" t="n">
+      <c r="L22" s="4" t="n">
         <f aca="false">J22/16</f>
         <v>2</v>
       </c>
-      <c r="M22" s="5" t="n">
+      <c r="M22" s="4" t="n">
         <f aca="false">J22/32</f>
         <v>1</v>
       </c>
-      <c r="N22" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O22" s="24" t="n">
+      <c r="N22" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O22" s="22" t="n">
         <v>4</v>
       </c>
       <c r="P22" s="1" t="n">
@@ -2022,48 +2111,48 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="30" t="s">
+      <c r="B23" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="D23" s="30" t="n">
+      <c r="C23" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" s="26" t="n">
         <v>16</v>
       </c>
-      <c r="E23" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="23"/>
-      <c r="G23" s="22" t="n">
+      <c r="E23" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="21"/>
+      <c r="G23" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="22" t="s">
+      <c r="H23" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I23" s="23" t="s">
-        <v>57</v>
+      <c r="I23" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="J23" s="4" t="n">
         <f aca="false">J22+D22</f>
         <v>48</v>
       </c>
-      <c r="K23" s="5" t="n">
+      <c r="K23" s="4" t="n">
         <f aca="false">J23/8</f>
         <v>6</v>
       </c>
-      <c r="L23" s="5" t="n">
+      <c r="L23" s="4" t="n">
         <f aca="false">J23/16</f>
         <v>3</v>
       </c>
-      <c r="M23" s="5" t="n">
+      <c r="M23" s="4" t="n">
         <f aca="false">J23/32</f>
         <v>1.5</v>
       </c>
-      <c r="N23" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O23" s="24" t="n">
+      <c r="N23" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O23" s="22" t="n">
         <v>4</v>
       </c>
       <c r="P23" s="1" t="n">
@@ -2074,48 +2163,48 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" s="30" t="s">
+      <c r="B24" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="D24" s="30" t="n">
+      <c r="C24" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="E24" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="23"/>
-      <c r="G24" s="22" t="n">
+      <c r="E24" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="21"/>
+      <c r="G24" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="22" t="s">
+      <c r="H24" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I24" s="23" t="s">
-        <v>60</v>
+      <c r="I24" s="21" t="s">
+        <v>61</v>
       </c>
       <c r="J24" s="4" t="n">
         <f aca="false">J23+D23</f>
         <v>64</v>
       </c>
-      <c r="K24" s="5" t="n">
+      <c r="K24" s="4" t="n">
         <f aca="false">J24/8</f>
         <v>8</v>
       </c>
-      <c r="L24" s="5" t="n">
+      <c r="L24" s="4" t="n">
         <f aca="false">J24/16</f>
         <v>4</v>
       </c>
-      <c r="M24" s="5" t="n">
+      <c r="M24" s="4" t="n">
         <f aca="false">J24/32</f>
         <v>2</v>
       </c>
-      <c r="N24" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O24" s="24" t="n">
+      <c r="N24" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O24" s="22" t="n">
         <v>4</v>
       </c>
       <c r="P24" s="1" t="n">
@@ -2126,48 +2215,48 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="30" t="s">
+      <c r="B25" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="D25" s="30" t="n">
+      <c r="C25" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="E25" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="F25" s="23"/>
-      <c r="G25" s="22" t="n">
+      <c r="E25" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F25" s="21"/>
+      <c r="G25" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="H25" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="I25" s="23" t="s">
+      <c r="H25" s="20" t="s">
         <v>65</v>
+      </c>
+      <c r="I25" s="21" t="s">
+        <v>66</v>
       </c>
       <c r="J25" s="4" t="n">
         <f aca="false">J24+D24</f>
         <v>72</v>
       </c>
-      <c r="K25" s="5" t="n">
+      <c r="K25" s="4" t="n">
         <f aca="false">J25/8</f>
         <v>9</v>
       </c>
-      <c r="L25" s="5" t="n">
+      <c r="L25" s="4" t="n">
         <f aca="false">J25/16</f>
         <v>4.5</v>
       </c>
-      <c r="M25" s="5" t="n">
+      <c r="M25" s="4" t="n">
         <f aca="false">J25/32</f>
         <v>2.25</v>
       </c>
-      <c r="N25" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O25" s="24" t="n">
+      <c r="N25" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="O25" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P25" s="1" t="n">
@@ -2178,48 +2267,48 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="30" t="s">
+      <c r="B26" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="D26" s="30" t="n">
+      <c r="C26" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="E26" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="F26" s="23"/>
-      <c r="G26" s="22" t="n">
+      <c r="E26" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" s="21"/>
+      <c r="G26" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="H26" s="22" t="s">
+      <c r="H26" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I26" s="23" t="s">
-        <v>69</v>
+      <c r="I26" s="21" t="s">
+        <v>70</v>
       </c>
       <c r="J26" s="4" t="n">
         <f aca="false">J25+D25</f>
         <v>80</v>
       </c>
-      <c r="K26" s="5" t="n">
+      <c r="K26" s="4" t="n">
         <f aca="false">J26/8</f>
         <v>10</v>
       </c>
-      <c r="L26" s="5" t="n">
+      <c r="L26" s="4" t="n">
         <f aca="false">J26/16</f>
         <v>5</v>
       </c>
-      <c r="M26" s="5" t="n">
+      <c r="M26" s="4" t="n">
         <f aca="false">J26/32</f>
         <v>2.5</v>
       </c>
-      <c r="N26" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O26" s="24" t="n">
+      <c r="N26" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="O26" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P26" s="1" t="n">
@@ -2230,48 +2319,48 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" s="30" t="s">
+      <c r="B27" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="D27" s="30" t="n">
+      <c r="C27" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="E27" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="23"/>
-      <c r="G27" s="22" t="n">
+      <c r="E27" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="21"/>
+      <c r="G27" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="H27" s="22" t="s">
+      <c r="H27" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I27" s="23" t="s">
-        <v>72</v>
+      <c r="I27" s="21" t="s">
+        <v>73</v>
       </c>
       <c r="J27" s="4" t="n">
         <f aca="false">J26+D26</f>
         <v>88</v>
       </c>
-      <c r="K27" s="5" t="n">
+      <c r="K27" s="4" t="n">
         <f aca="false">J27/8</f>
         <v>11</v>
       </c>
-      <c r="L27" s="5" t="n">
+      <c r="L27" s="4" t="n">
         <f aca="false">J27/16</f>
         <v>5.5</v>
       </c>
-      <c r="M27" s="5" t="n">
+      <c r="M27" s="4" t="n">
         <f aca="false">J27/32</f>
         <v>2.75</v>
       </c>
-      <c r="N27" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O27" s="24" t="n">
+      <c r="N27" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="O27" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P27" s="1" t="n">
@@ -2282,48 +2371,48 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="C28" s="30" t="s">
+      <c r="B28" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="D28" s="30" t="n">
+      <c r="C28" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="E28" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="23"/>
-      <c r="G28" s="22" t="n">
+      <c r="E28" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="21"/>
+      <c r="G28" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="H28" s="22" t="s">
+      <c r="H28" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I28" s="23" t="s">
-        <v>75</v>
+      <c r="I28" s="21" t="s">
+        <v>76</v>
       </c>
       <c r="J28" s="4" t="n">
         <f aca="false">J27+D27</f>
         <v>96</v>
       </c>
-      <c r="K28" s="5" t="n">
+      <c r="K28" s="4" t="n">
         <f aca="false">J28/8</f>
         <v>12</v>
       </c>
-      <c r="L28" s="5" t="n">
+      <c r="L28" s="4" t="n">
         <f aca="false">J28/16</f>
         <v>6</v>
       </c>
-      <c r="M28" s="5" t="n">
+      <c r="M28" s="4" t="n">
         <f aca="false">J28/32</f>
         <v>3</v>
       </c>
-      <c r="N28" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O28" s="24" t="n">
+      <c r="N28" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="O28" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P28" s="1" t="n">
@@ -2334,48 +2423,48 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="C29" s="30" t="s">
+      <c r="B29" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="D29" s="30" t="n">
+      <c r="C29" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="E29" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="23"/>
-      <c r="G29" s="22" t="n">
+      <c r="E29" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" s="21"/>
+      <c r="G29" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="H29" s="22" t="s">
+      <c r="H29" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I29" s="23" t="s">
-        <v>78</v>
+      <c r="I29" s="21" t="s">
+        <v>79</v>
       </c>
       <c r="J29" s="4" t="n">
         <f aca="false">J28+D28</f>
         <v>104</v>
       </c>
-      <c r="K29" s="5" t="n">
+      <c r="K29" s="4" t="n">
         <f aca="false">J29/8</f>
         <v>13</v>
       </c>
-      <c r="L29" s="5" t="n">
+      <c r="L29" s="4" t="n">
         <f aca="false">J29/16</f>
         <v>6.5</v>
       </c>
-      <c r="M29" s="5" t="n">
+      <c r="M29" s="4" t="n">
         <f aca="false">J29/32</f>
         <v>3.25</v>
       </c>
-      <c r="N29" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O29" s="24" t="n">
+      <c r="N29" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="O29" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P29" s="1" t="n">
@@ -2386,48 +2475,48 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" s="30" t="s">
+      <c r="B30" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="D30" s="30" t="n">
+      <c r="C30" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="E30" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="23"/>
-      <c r="G30" s="22" t="n">
+      <c r="E30" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" s="21"/>
+      <c r="G30" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="H30" s="22" t="s">
+      <c r="H30" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I30" s="23" t="s">
-        <v>81</v>
+      <c r="I30" s="21" t="s">
+        <v>82</v>
       </c>
       <c r="J30" s="4" t="n">
         <f aca="false">J29+D29</f>
         <v>112</v>
       </c>
-      <c r="K30" s="5" t="n">
+      <c r="K30" s="4" t="n">
         <f aca="false">J30/8</f>
         <v>14</v>
       </c>
-      <c r="L30" s="5" t="n">
+      <c r="L30" s="4" t="n">
         <f aca="false">J30/16</f>
         <v>7</v>
       </c>
-      <c r="M30" s="5" t="n">
+      <c r="M30" s="4" t="n">
         <f aca="false">J30/32</f>
         <v>3.5</v>
       </c>
-      <c r="N30" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O30" s="24" t="n">
+      <c r="N30" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="O30" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P30" s="1" t="n">
@@ -2438,48 +2527,48 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="C31" s="30" t="s">
+      <c r="B31" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="D31" s="30" t="n">
+      <c r="C31" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="D31" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="E31" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="23"/>
-      <c r="G31" s="22" t="n">
+      <c r="E31" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="21"/>
+      <c r="G31" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="H31" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="I31" s="23" t="s">
+      <c r="H31" s="20" t="s">
         <v>85</v>
+      </c>
+      <c r="I31" s="21" t="s">
+        <v>86</v>
       </c>
       <c r="J31" s="4" t="n">
         <f aca="false">J30+D30</f>
         <v>120</v>
       </c>
-      <c r="K31" s="5" t="n">
+      <c r="K31" s="4" t="n">
         <f aca="false">J31/8</f>
         <v>15</v>
       </c>
-      <c r="L31" s="5" t="n">
+      <c r="L31" s="4" t="n">
         <f aca="false">J31/16</f>
         <v>7.5</v>
       </c>
-      <c r="M31" s="5" t="n">
+      <c r="M31" s="4" t="n">
         <f aca="false">J31/32</f>
         <v>3.75</v>
       </c>
-      <c r="N31" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O31" s="24" t="n">
+      <c r="N31" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="O31" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P31" s="1" t="n">
@@ -2490,48 +2579,48 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" s="30" t="s">
+      <c r="B32" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="D32" s="30" t="n">
+      <c r="C32" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="E32" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="23"/>
-      <c r="G32" s="22" t="n">
+      <c r="E32" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="21"/>
+      <c r="G32" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="H32" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="I32" s="23" t="s">
-        <v>88</v>
+      <c r="H32" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="I32" s="21" t="s">
+        <v>89</v>
       </c>
       <c r="J32" s="4" t="n">
         <f aca="false">J31+D31</f>
         <v>128</v>
       </c>
-      <c r="K32" s="5" t="n">
+      <c r="K32" s="4" t="n">
         <f aca="false">J32/8</f>
         <v>16</v>
       </c>
-      <c r="L32" s="5" t="n">
+      <c r="L32" s="4" t="n">
         <f aca="false">J32/16</f>
         <v>8</v>
       </c>
-      <c r="M32" s="5" t="n">
+      <c r="M32" s="4" t="n">
         <f aca="false">J32/32</f>
         <v>4</v>
       </c>
-      <c r="N32" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O32" s="24" t="n">
+      <c r="N32" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="O32" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P32" s="1" t="n">
@@ -2542,48 +2631,48 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="C33" s="30" t="s">
+      <c r="B33" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="D33" s="30" t="n">
+      <c r="C33" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="E33" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" s="23"/>
-      <c r="G33" s="22" t="n">
+      <c r="E33" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="21"/>
+      <c r="G33" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="H33" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="I33" s="23" t="s">
-        <v>91</v>
+      <c r="H33" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="I33" s="21" t="s">
+        <v>92</v>
       </c>
       <c r="J33" s="4" t="n">
         <f aca="false">J32+D32</f>
         <v>136</v>
       </c>
-      <c r="K33" s="5" t="n">
+      <c r="K33" s="4" t="n">
         <f aca="false">J33/8</f>
         <v>17</v>
       </c>
-      <c r="L33" s="5" t="n">
+      <c r="L33" s="4" t="n">
         <f aca="false">J33/16</f>
         <v>8.5</v>
       </c>
-      <c r="M33" s="5" t="n">
+      <c r="M33" s="4" t="n">
         <f aca="false">J33/32</f>
         <v>4.25</v>
       </c>
-      <c r="N33" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O33" s="24" t="n">
+      <c r="N33" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="O33" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P33" s="1" t="n">
@@ -2594,48 +2683,48 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="C34" s="30" t="s">
+      <c r="B34" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="D34" s="30" t="n">
+      <c r="C34" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="E34" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F34" s="23"/>
-      <c r="G34" s="22" t="n">
+      <c r="E34" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" s="21"/>
+      <c r="G34" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="H34" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="I34" s="23" t="s">
-        <v>94</v>
+      <c r="H34" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="I34" s="21" t="s">
+        <v>95</v>
       </c>
       <c r="J34" s="4" t="n">
         <f aca="false">J33+D33</f>
         <v>144</v>
       </c>
-      <c r="K34" s="5" t="n">
+      <c r="K34" s="4" t="n">
         <f aca="false">J34/8</f>
         <v>18</v>
       </c>
-      <c r="L34" s="5" t="n">
+      <c r="L34" s="4" t="n">
         <f aca="false">J34/16</f>
         <v>9</v>
       </c>
-      <c r="M34" s="5" t="n">
+      <c r="M34" s="4" t="n">
         <f aca="false">J34/32</f>
         <v>4.5</v>
       </c>
-      <c r="N34" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O34" s="24" t="n">
+      <c r="N34" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="O34" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P34" s="1" t="n">
@@ -2646,48 +2735,48 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" s="30" t="s">
+      <c r="B35" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="D35" s="30" t="n">
+      <c r="C35" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="D35" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="E35" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F35" s="23"/>
-      <c r="G35" s="22" t="n">
+      <c r="E35" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="21"/>
+      <c r="G35" s="20" t="n">
         <v>9</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I35" s="23" t="s">
         <v>98</v>
+      </c>
+      <c r="I35" s="21" t="s">
+        <v>99</v>
       </c>
       <c r="J35" s="4" t="n">
         <f aca="false">J34+D34</f>
         <v>152</v>
       </c>
-      <c r="K35" s="5" t="n">
+      <c r="K35" s="4" t="n">
         <f aca="false">J35/8</f>
         <v>19</v>
       </c>
-      <c r="L35" s="5" t="n">
+      <c r="L35" s="4" t="n">
         <f aca="false">J35/16</f>
         <v>9.5</v>
       </c>
-      <c r="M35" s="5" t="n">
+      <c r="M35" s="4" t="n">
         <f aca="false">J35/32</f>
         <v>4.75</v>
       </c>
-      <c r="N35" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O35" s="24" t="n">
+      <c r="N35" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O35" s="22" t="n">
         <v>3</v>
       </c>
       <c r="P35" s="1" t="n">
@@ -2698,48 +2787,48 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="C36" s="30" t="s">
+      <c r="B36" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="D36" s="30" t="n">
+      <c r="C36" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="D36" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="E36" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F36" s="23"/>
-      <c r="G36" s="22" t="n">
+      <c r="E36" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="21"/>
+      <c r="G36" s="20" t="n">
         <v>9</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I36" s="23" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="I36" s="21" t="s">
+        <v>103</v>
       </c>
       <c r="J36" s="4" t="n">
         <f aca="false">J35+D35</f>
         <v>160</v>
       </c>
-      <c r="K36" s="5" t="n">
+      <c r="K36" s="4" t="n">
         <f aca="false">J36/8</f>
         <v>20</v>
       </c>
-      <c r="L36" s="5" t="n">
+      <c r="L36" s="4" t="n">
         <f aca="false">J36/16</f>
         <v>10</v>
       </c>
-      <c r="M36" s="5" t="n">
+      <c r="M36" s="4" t="n">
         <f aca="false">J36/32</f>
         <v>5</v>
       </c>
-      <c r="N36" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="O36" s="24" t="n">
+      <c r="N36" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="O36" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P36" s="1" t="n">
@@ -2750,48 +2839,48 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="C37" s="30" t="s">
+      <c r="B37" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="D37" s="30" t="n">
+      <c r="C37" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="D37" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="E37" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F37" s="23"/>
-      <c r="G37" s="22" t="n">
+      <c r="E37" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" s="21"/>
+      <c r="G37" s="20" t="n">
         <v>9</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I37" s="23" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="I37" s="21" t="s">
+        <v>106</v>
       </c>
       <c r="J37" s="4" t="n">
         <f aca="false">J36+D36</f>
         <v>168</v>
       </c>
-      <c r="K37" s="5" t="n">
+      <c r="K37" s="4" t="n">
         <f aca="false">J37/8</f>
         <v>21</v>
       </c>
-      <c r="L37" s="5" t="n">
+      <c r="L37" s="4" t="n">
         <f aca="false">J37/16</f>
         <v>10.5</v>
       </c>
-      <c r="M37" s="5" t="n">
+      <c r="M37" s="4" t="n">
         <f aca="false">J37/32</f>
         <v>5.25</v>
       </c>
-      <c r="N37" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O37" s="24" t="n">
+      <c r="N37" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O37" s="22" t="n">
         <v>3</v>
       </c>
       <c r="P37" s="1" t="n">
@@ -2803,140 +2892,140 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="30"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="23" t="s">
-        <v>106</v>
+        <v>45</v>
+      </c>
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21" t="s">
+        <v>107</v>
       </c>
       <c r="J38" s="4" t="n">
         <f aca="false">J37+D37</f>
         <v>176</v>
       </c>
-      <c r="K38" s="5" t="n">
+      <c r="K38" s="4" t="n">
         <f aca="false">J38/8</f>
         <v>22</v>
       </c>
-      <c r="L38" s="5" t="n">
+      <c r="L38" s="4" t="n">
         <f aca="false">J38/16</f>
         <v>11</v>
       </c>
-      <c r="M38" s="5" t="n">
+      <c r="M38" s="4" t="n">
         <f aca="false">J38/32</f>
         <v>5.5</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="30"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="23"/>
-      <c r="H39" s="23"/>
-      <c r="I39" s="23"/>
-      <c r="J39" s="28"/>
-      <c r="K39" s="27"/>
-      <c r="L39" s="27"/>
-      <c r="M39" s="27"/>
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="25"/>
+      <c r="K39" s="25"/>
+      <c r="L39" s="25"/>
+      <c r="M39" s="25"/>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B40" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
-      <c r="I40" s="8"/>
+      <c r="B40" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B41" s="30"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="23"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="23"/>
-      <c r="J41" s="28"/>
-      <c r="K41" s="27"/>
-      <c r="L41" s="27"/>
-      <c r="M41" s="27"/>
+        <v>109</v>
+      </c>
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="25"/>
+      <c r="K41" s="25"/>
+      <c r="L41" s="25"/>
+      <c r="M41" s="25"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="23"/>
-      <c r="J42" s="28"/>
-      <c r="K42" s="27"/>
-      <c r="L42" s="27"/>
-      <c r="M42" s="27"/>
+        <v>110</v>
+      </c>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="25"/>
+      <c r="K42" s="25"/>
+      <c r="L42" s="25"/>
+      <c r="M42" s="25"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="C43" s="30" t="s">
+      <c r="B43" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="D43" s="30" t="n">
+      <c r="C43" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D43" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="E43" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" s="23"/>
-      <c r="G43" s="22" t="n">
+      <c r="E43" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="21"/>
+      <c r="G43" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="22" t="s">
+      <c r="H43" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I43" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="J43" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="27" t="n">
+      <c r="I43" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="J43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="25" t="n">
         <f aca="false">J43/8</f>
         <v>0</v>
       </c>
-      <c r="L43" s="27" t="n">
+      <c r="L43" s="25" t="n">
         <f aca="false">J43/16</f>
         <v>0</v>
       </c>
-      <c r="M43" s="27" t="n">
+      <c r="M43" s="25" t="n">
         <f aca="false">J43/32</f>
         <v>0</v>
       </c>
-      <c r="N43" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O43" s="24" t="n">
+      <c r="N43" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O43" s="22" t="n">
         <v>3</v>
       </c>
       <c r="P43" s="1" t="n">
@@ -2947,48 +3036,48 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="C44" s="30" t="s">
+      <c r="B44" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="D44" s="30" t="n">
+      <c r="C44" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="D44" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="E44" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F44" s="23"/>
-      <c r="G44" s="22" t="n">
+      <c r="E44" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" s="21"/>
+      <c r="G44" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="22" t="s">
+      <c r="H44" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I44" s="23" t="s">
-        <v>115</v>
+      <c r="I44" s="21" t="s">
+        <v>116</v>
       </c>
       <c r="J44" s="4" t="n">
         <f aca="false">J43+D43</f>
         <v>1</v>
       </c>
-      <c r="K44" s="5" t="n">
+      <c r="K44" s="4" t="n">
         <f aca="false">J44/8</f>
         <v>0.125</v>
       </c>
-      <c r="L44" s="5" t="n">
+      <c r="L44" s="4" t="n">
         <f aca="false">J44/16</f>
         <v>0.0625</v>
       </c>
-      <c r="M44" s="5" t="n">
+      <c r="M44" s="4" t="n">
         <f aca="false">J44/32</f>
         <v>0.03125</v>
       </c>
-      <c r="N44" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O44" s="24" t="n">
+      <c r="N44" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O44" s="22" t="n">
         <v>3</v>
       </c>
       <c r="P44" s="1" t="n">
@@ -2999,48 +3088,48 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="C45" s="30" t="s">
+      <c r="B45" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="D45" s="30" t="n">
+      <c r="C45" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="D45" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="E45" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F45" s="23"/>
-      <c r="G45" s="22" t="n">
+      <c r="E45" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" s="21"/>
+      <c r="G45" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="22" t="s">
+      <c r="H45" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I45" s="23" t="s">
-        <v>118</v>
+      <c r="I45" s="21" t="s">
+        <v>119</v>
       </c>
       <c r="J45" s="4" t="n">
         <f aca="false">J44+D44</f>
         <v>2</v>
       </c>
-      <c r="K45" s="5" t="n">
+      <c r="K45" s="4" t="n">
         <f aca="false">J45/8</f>
         <v>0.25</v>
       </c>
-      <c r="L45" s="5" t="n">
+      <c r="L45" s="4" t="n">
         <f aca="false">J45/16</f>
         <v>0.125</v>
       </c>
-      <c r="M45" s="5" t="n">
+      <c r="M45" s="4" t="n">
         <f aca="false">J45/32</f>
         <v>0.0625</v>
       </c>
-      <c r="N45" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O45" s="24" t="n">
+      <c r="N45" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O45" s="22" t="n">
         <v>4</v>
       </c>
       <c r="P45" s="1" t="n">
@@ -3051,48 +3140,48 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="C46" s="30" t="s">
+      <c r="B46" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="D46" s="30" t="n">
+      <c r="C46" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="D46" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="E46" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F46" s="23"/>
-      <c r="G46" s="22" t="n">
+      <c r="E46" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="21"/>
+      <c r="G46" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="22" t="s">
+      <c r="H46" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I46" s="23" t="s">
-        <v>121</v>
+      <c r="I46" s="21" t="s">
+        <v>122</v>
       </c>
       <c r="J46" s="4" t="n">
         <f aca="false">J45+D45</f>
         <v>3</v>
       </c>
-      <c r="K46" s="5" t="n">
+      <c r="K46" s="4" t="n">
         <f aca="false">J46/8</f>
         <v>0.375</v>
       </c>
-      <c r="L46" s="5" t="n">
+      <c r="L46" s="4" t="n">
         <f aca="false">J46/16</f>
         <v>0.1875</v>
       </c>
-      <c r="M46" s="5" t="n">
+      <c r="M46" s="4" t="n">
         <f aca="false">J46/32</f>
         <v>0.09375</v>
       </c>
-      <c r="N46" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O46" s="24" t="n">
+      <c r="N46" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O46" s="22" t="n">
         <v>4</v>
       </c>
       <c r="P46" s="1" t="n">
@@ -3103,48 +3192,48 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="C47" s="30" t="s">
+      <c r="B47" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="D47" s="30" t="n">
+      <c r="C47" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="D47" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="E47" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F47" s="23"/>
-      <c r="G47" s="22" t="n">
+      <c r="E47" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" s="21"/>
+      <c r="G47" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="22" t="s">
+      <c r="H47" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I47" s="23" t="s">
-        <v>124</v>
+      <c r="I47" s="21" t="s">
+        <v>125</v>
       </c>
       <c r="J47" s="4" t="n">
         <f aca="false">J46+D46</f>
         <v>4</v>
       </c>
-      <c r="K47" s="5" t="n">
+      <c r="K47" s="4" t="n">
         <f aca="false">J47/8</f>
         <v>0.5</v>
       </c>
-      <c r="L47" s="5" t="n">
+      <c r="L47" s="4" t="n">
         <f aca="false">J47/16</f>
         <v>0.25</v>
       </c>
-      <c r="M47" s="5" t="n">
+      <c r="M47" s="4" t="n">
         <f aca="false">J47/32</f>
         <v>0.125</v>
       </c>
-      <c r="N47" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O47" s="24" t="n">
+      <c r="N47" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O47" s="22" t="n">
         <v>4</v>
       </c>
       <c r="P47" s="1" t="n">
@@ -3155,48 +3244,48 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="C48" s="22" t="s">
+      <c r="B48" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="D48" s="22" t="n">
+      <c r="C48" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D48" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="E48" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F48" s="22"/>
-      <c r="G48" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="22" t="s">
+      <c r="E48" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I48" s="23" t="s">
-        <v>127</v>
+      <c r="I48" s="21" t="s">
+        <v>128</v>
       </c>
       <c r="J48" s="4" t="n">
         <f aca="false">J47+D47</f>
         <v>5</v>
       </c>
-      <c r="K48" s="5" t="n">
+      <c r="K48" s="4" t="n">
         <f aca="false">J48/8</f>
         <v>0.625</v>
       </c>
-      <c r="L48" s="5" t="n">
+      <c r="L48" s="4" t="n">
         <f aca="false">J48/16</f>
         <v>0.3125</v>
       </c>
-      <c r="M48" s="5" t="n">
+      <c r="M48" s="4" t="n">
         <f aca="false">J48/32</f>
         <v>0.15625</v>
       </c>
-      <c r="N48" s="5" t="s">
+      <c r="N48" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O48" s="24" t="n">
+      <c r="O48" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P48" s="1" t="n">
@@ -3208,77 +3297,77 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B49" s="22"/>
-      <c r="C49" s="22"/>
-      <c r="D49" s="22"/>
-      <c r="E49" s="22"/>
-      <c r="F49" s="22"/>
-      <c r="G49" s="22"/>
-      <c r="H49" s="22"/>
-      <c r="I49" s="23"/>
-      <c r="N49" s="5"/>
-      <c r="O49" s="24"/>
+        <v>129</v>
+      </c>
+      <c r="B49" s="20"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="20"/>
+      <c r="H49" s="20"/>
+      <c r="I49" s="21"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="22"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B50" s="22"/>
-      <c r="C50" s="22"/>
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22"/>
-      <c r="G50" s="22"/>
-      <c r="H50" s="22"/>
-      <c r="I50" s="23"/>
-      <c r="N50" s="5"/>
-      <c r="O50" s="24"/>
+        <v>130</v>
+      </c>
+      <c r="B50" s="20"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="21"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="22"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="C51" s="22" t="s">
+      <c r="B51" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="D51" s="22" t="n">
+      <c r="C51" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D51" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="E51" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F51" s="22"/>
-      <c r="G51" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="22" t="s">
+      <c r="E51" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I51" s="23" t="s">
-        <v>127</v>
+      <c r="I51" s="21" t="s">
+        <v>128</v>
       </c>
       <c r="J51" s="4" t="n">
         <f aca="false">J50+D50</f>
         <v>0</v>
       </c>
-      <c r="K51" s="5" t="n">
+      <c r="K51" s="4" t="n">
         <f aca="false">J51/8</f>
         <v>0</v>
       </c>
-      <c r="L51" s="5" t="n">
+      <c r="L51" s="4" t="n">
         <f aca="false">J51/16</f>
         <v>0</v>
       </c>
-      <c r="M51" s="5" t="n">
+      <c r="M51" s="4" t="n">
         <f aca="false">J51/32</f>
         <v>0</v>
       </c>
-      <c r="N51" s="5" t="s">
+      <c r="N51" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O51" s="24" t="n">
+      <c r="O51" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P51" s="1" t="n">
@@ -3289,48 +3378,48 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="C52" s="30" t="s">
+      <c r="B52" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="D52" s="30" t="n">
+      <c r="C52" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="D52" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="E52" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F52" s="23"/>
-      <c r="G52" s="22" t="n">
+      <c r="E52" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F52" s="21"/>
+      <c r="G52" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H52" s="22" t="s">
+      <c r="H52" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I52" s="23" t="s">
-        <v>124</v>
+      <c r="I52" s="21" t="s">
+        <v>125</v>
       </c>
       <c r="J52" s="4" t="n">
         <f aca="false">J51+D51</f>
         <v>3</v>
       </c>
-      <c r="K52" s="5" t="n">
+      <c r="K52" s="4" t="n">
         <f aca="false">J52/8</f>
         <v>0.375</v>
       </c>
-      <c r="L52" s="5" t="n">
+      <c r="L52" s="4" t="n">
         <f aca="false">J52/16</f>
         <v>0.1875</v>
       </c>
-      <c r="M52" s="5" t="n">
+      <c r="M52" s="4" t="n">
         <f aca="false">J52/32</f>
         <v>0.09375</v>
       </c>
-      <c r="N52" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O52" s="24" t="n">
+      <c r="N52" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O52" s="22" t="n">
         <v>4</v>
       </c>
       <c r="P52" s="1" t="n">
@@ -3341,48 +3430,48 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="C53" s="30" t="s">
+      <c r="B53" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="D53" s="30" t="n">
+      <c r="C53" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="D53" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="E53" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F53" s="23"/>
-      <c r="G53" s="22" t="n">
+      <c r="E53" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" s="21"/>
+      <c r="G53" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H53" s="22" t="s">
+      <c r="H53" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I53" s="23" t="s">
-        <v>121</v>
+      <c r="I53" s="21" t="s">
+        <v>122</v>
       </c>
       <c r="J53" s="4" t="n">
         <f aca="false">J52+D52</f>
         <v>4</v>
       </c>
-      <c r="K53" s="5" t="n">
+      <c r="K53" s="4" t="n">
         <f aca="false">J53/8</f>
         <v>0.5</v>
       </c>
-      <c r="L53" s="5" t="n">
+      <c r="L53" s="4" t="n">
         <f aca="false">J53/16</f>
         <v>0.25</v>
       </c>
-      <c r="M53" s="5" t="n">
+      <c r="M53" s="4" t="n">
         <f aca="false">J53/32</f>
         <v>0.125</v>
       </c>
-      <c r="N53" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O53" s="24" t="n">
+      <c r="N53" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O53" s="22" t="n">
         <v>4</v>
       </c>
       <c r="P53" s="1" t="n">
@@ -3393,48 +3482,48 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="C54" s="30" t="s">
+      <c r="B54" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="D54" s="30" t="n">
+      <c r="C54" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="D54" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="E54" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F54" s="23"/>
-      <c r="G54" s="22" t="n">
+      <c r="E54" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" s="21"/>
+      <c r="G54" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H54" s="22" t="s">
+      <c r="H54" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I54" s="23" t="s">
-        <v>118</v>
+      <c r="I54" s="21" t="s">
+        <v>119</v>
       </c>
       <c r="J54" s="4" t="n">
         <f aca="false">J53+D53</f>
         <v>5</v>
       </c>
-      <c r="K54" s="5" t="n">
+      <c r="K54" s="4" t="n">
         <f aca="false">J54/8</f>
         <v>0.625</v>
       </c>
-      <c r="L54" s="5" t="n">
+      <c r="L54" s="4" t="n">
         <f aca="false">J54/16</f>
         <v>0.3125</v>
       </c>
-      <c r="M54" s="5" t="n">
+      <c r="M54" s="4" t="n">
         <f aca="false">J54/32</f>
         <v>0.15625</v>
       </c>
-      <c r="N54" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O54" s="24" t="n">
+      <c r="N54" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O54" s="22" t="n">
         <v>4</v>
       </c>
       <c r="P54" s="1" t="n">
@@ -3445,48 +3534,48 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="C55" s="30" t="s">
+      <c r="B55" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="D55" s="30" t="n">
+      <c r="C55" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="D55" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="E55" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F55" s="23"/>
-      <c r="G55" s="22" t="n">
+      <c r="E55" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55" s="21"/>
+      <c r="G55" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H55" s="22" t="s">
+      <c r="H55" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I55" s="23" t="s">
-        <v>115</v>
+      <c r="I55" s="21" t="s">
+        <v>116</v>
       </c>
       <c r="J55" s="4" t="n">
         <f aca="false">J54+D54</f>
         <v>6</v>
       </c>
-      <c r="K55" s="5" t="n">
+      <c r="K55" s="4" t="n">
         <f aca="false">J55/8</f>
         <v>0.75</v>
       </c>
-      <c r="L55" s="5" t="n">
+      <c r="L55" s="4" t="n">
         <f aca="false">J55/16</f>
         <v>0.375</v>
       </c>
-      <c r="M55" s="5" t="n">
+      <c r="M55" s="4" t="n">
         <f aca="false">J55/32</f>
         <v>0.1875</v>
       </c>
-      <c r="N55" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O55" s="24" t="n">
+      <c r="N55" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O55" s="22" t="n">
         <v>3</v>
       </c>
       <c r="P55" s="1" t="n">
@@ -3497,48 +3586,48 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="C56" s="30" t="s">
+      <c r="B56" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="D56" s="30" t="n">
+      <c r="C56" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D56" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="E56" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F56" s="23"/>
-      <c r="G56" s="22" t="n">
+      <c r="E56" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" s="21"/>
+      <c r="G56" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H56" s="22" t="s">
+      <c r="H56" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I56" s="23" t="s">
-        <v>112</v>
+      <c r="I56" s="21" t="s">
+        <v>113</v>
       </c>
       <c r="J56" s="4" t="n">
         <f aca="false">J55+D55</f>
         <v>7</v>
       </c>
-      <c r="K56" s="5" t="n">
+      <c r="K56" s="4" t="n">
         <f aca="false">J56/8</f>
         <v>0.875</v>
       </c>
-      <c r="L56" s="5" t="n">
+      <c r="L56" s="4" t="n">
         <f aca="false">J56/16</f>
         <v>0.4375</v>
       </c>
-      <c r="M56" s="5" t="n">
+      <c r="M56" s="4" t="n">
         <f aca="false">J56/32</f>
         <v>0.21875</v>
       </c>
-      <c r="N56" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O56" s="24" t="n">
+      <c r="N56" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O56" s="22" t="n">
         <v>3</v>
       </c>
       <c r="P56" s="1" t="n">
@@ -3550,686 +3639,686 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B57" s="22"/>
-      <c r="C57" s="22"/>
-      <c r="D57" s="22"/>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="22"/>
-      <c r="H57" s="22"/>
-      <c r="I57" s="23"/>
-      <c r="N57" s="5"/>
-      <c r="O57" s="24"/>
+        <v>129</v>
+      </c>
+      <c r="B57" s="20"/>
+      <c r="C57" s="20"/>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
+      <c r="H57" s="20"/>
+      <c r="I57" s="21"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="22"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="C58" s="22" t="s">
+      <c r="B58" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="D58" s="22" t="n">
+      <c r="C58" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="D58" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="E58" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F58" s="22"/>
-      <c r="G58" s="22" t="n">
+      <c r="E58" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" s="20"/>
+      <c r="G58" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="H58" s="22" t="s">
+      <c r="H58" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I58" s="23" t="s">
-        <v>132</v>
+      <c r="I58" s="21" t="s">
+        <v>133</v>
       </c>
       <c r="J58" s="4" t="n">
         <f aca="false">J56+D56</f>
         <v>8</v>
       </c>
-      <c r="K58" s="5" t="n">
+      <c r="K58" s="4" t="n">
         <f aca="false">J58/8</f>
         <v>1</v>
       </c>
-      <c r="L58" s="5" t="n">
+      <c r="L58" s="4" t="n">
         <f aca="false">J58/16</f>
         <v>0.5</v>
       </c>
-      <c r="M58" s="5" t="n">
+      <c r="M58" s="4" t="n">
         <f aca="false">J58/32</f>
         <v>0.25</v>
       </c>
-      <c r="N58" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="O58" s="24" t="n">
+      <c r="N58" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="O58" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q58" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="22" t="s">
+      <c r="B59" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="C59" s="22" t="s">
+      <c r="C59" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="D59" s="22" t="n">
+      <c r="D59" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="E59" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F59" s="22"/>
-      <c r="G59" s="22" t="n">
+      <c r="E59" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="H59" s="22" t="s">
+      <c r="H59" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="I59" s="23" t="s">
+      <c r="I59" s="21" t="s">
         <v>137</v>
       </c>
       <c r="J59" s="4" t="n">
         <f aca="false">J58+D58</f>
         <v>16</v>
       </c>
-      <c r="K59" s="5" t="n">
+      <c r="K59" s="4" t="n">
         <f aca="false">J59/8</f>
         <v>2</v>
       </c>
-      <c r="L59" s="5" t="n">
+      <c r="L59" s="4" t="n">
         <f aca="false">J59/16</f>
         <v>1</v>
       </c>
-      <c r="M59" s="5" t="n">
+      <c r="M59" s="4" t="n">
         <f aca="false">J59/32</f>
         <v>0.5</v>
       </c>
-      <c r="N59" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="O59" s="24" t="n">
+      <c r="N59" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="O59" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q59" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="22" t="s">
+      <c r="B60" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="C60" s="22" t="s">
+      <c r="C60" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="D60" s="22" t="n">
+      <c r="D60" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="E60" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F60" s="22"/>
-      <c r="G60" s="22" t="n">
+      <c r="E60" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60" s="20"/>
+      <c r="G60" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="H60" s="22" t="s">
+      <c r="H60" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="I60" s="23" t="s">
+      <c r="I60" s="21" t="s">
         <v>140</v>
       </c>
       <c r="J60" s="4" t="n">
         <f aca="false">J59+D59</f>
         <v>32</v>
       </c>
-      <c r="K60" s="5" t="n">
+      <c r="K60" s="4" t="n">
         <f aca="false">J60/8</f>
         <v>4</v>
       </c>
-      <c r="L60" s="5" t="n">
+      <c r="L60" s="4" t="n">
         <f aca="false">J60/16</f>
         <v>2</v>
       </c>
-      <c r="M60" s="5" t="n">
+      <c r="M60" s="4" t="n">
         <f aca="false">J60/32</f>
         <v>1</v>
       </c>
-      <c r="N60" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="O60" s="24" t="n">
+      <c r="N60" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="O60" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P60" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="C61" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="D61" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="E61" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F61" s="20"/>
+      <c r="G61" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="Q60" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="C61" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="D61" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="E61" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F61" s="22"/>
-      <c r="G61" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="H61" s="22" t="s">
+      <c r="H61" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="I61" s="23" t="s">
+      <c r="I61" s="21" t="s">
         <v>143</v>
       </c>
       <c r="J61" s="4" t="n">
         <f aca="false">J60+D60</f>
         <v>48</v>
       </c>
-      <c r="K61" s="5" t="n">
+      <c r="K61" s="4" t="n">
         <f aca="false">J61/8</f>
         <v>6</v>
       </c>
-      <c r="L61" s="5" t="n">
+      <c r="L61" s="4" t="n">
         <f aca="false">J61/16</f>
         <v>3</v>
       </c>
-      <c r="M61" s="5" t="n">
+      <c r="M61" s="4" t="n">
         <f aca="false">J61/32</f>
         <v>1.5</v>
       </c>
-      <c r="N61" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="O61" s="24" t="n">
+      <c r="N61" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="O61" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q61" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="25.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="22" t="s">
+    <row r="62" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="C62" s="22" t="s">
+      <c r="C62" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="D62" s="22" t="n">
+      <c r="D62" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="E62" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F62" s="22"/>
-      <c r="G62" s="22" t="n">
+      <c r="E62" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="H62" s="22" t="s">
+      <c r="H62" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="I62" s="23" t="s">
+      <c r="I62" s="21" t="s">
         <v>147</v>
       </c>
       <c r="J62" s="4" t="n">
         <f aca="false">J61+D61</f>
         <v>64</v>
       </c>
-      <c r="K62" s="5" t="n">
+      <c r="K62" s="4" t="n">
         <f aca="false">J62/8</f>
         <v>8</v>
       </c>
-      <c r="L62" s="5" t="n">
+      <c r="L62" s="4" t="n">
         <f aca="false">J62/16</f>
         <v>4</v>
       </c>
-      <c r="M62" s="5" t="n">
+      <c r="M62" s="4" t="n">
         <f aca="false">J62/32</f>
         <v>2</v>
       </c>
-      <c r="N62" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="O62" s="24" t="n">
+      <c r="N62" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="O62" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q62" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="25.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="22" t="s">
+    <row r="63" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="C63" s="22" t="s">
+      <c r="C63" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="D63" s="22" t="n">
+      <c r="D63" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="E63" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F63" s="22"/>
-      <c r="G63" s="22" t="n">
+      <c r="E63" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="H63" s="22" t="s">
+      <c r="H63" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="I63" s="23" t="s">
+      <c r="I63" s="21" t="s">
         <v>150</v>
       </c>
       <c r="J63" s="4" t="n">
         <f aca="false">J62+D62</f>
         <v>80</v>
       </c>
-      <c r="K63" s="5" t="n">
+      <c r="K63" s="4" t="n">
         <f aca="false">J63/8</f>
         <v>10</v>
       </c>
-      <c r="L63" s="5" t="n">
+      <c r="L63" s="4" t="n">
         <f aca="false">J63/16</f>
         <v>5</v>
       </c>
-      <c r="M63" s="5" t="n">
+      <c r="M63" s="4" t="n">
         <f aca="false">J63/32</f>
         <v>2.5</v>
       </c>
-      <c r="N63" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="O63" s="24" t="n">
+      <c r="N63" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="O63" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q63" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="25.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="22" t="s">
+    <row r="64" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="C64" s="22" t="s">
+      <c r="C64" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="D64" s="22" t="n">
+      <c r="D64" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="E64" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F64" s="22"/>
-      <c r="G64" s="22" t="n">
+      <c r="E64" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F64" s="20"/>
+      <c r="G64" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="H64" s="22" t="s">
+      <c r="H64" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="I64" s="23" t="s">
+      <c r="I64" s="21" t="s">
         <v>153</v>
       </c>
       <c r="J64" s="4" t="n">
         <f aca="false">J63+D63</f>
         <v>96</v>
       </c>
-      <c r="K64" s="5" t="n">
+      <c r="K64" s="4" t="n">
         <f aca="false">J64/8</f>
         <v>12</v>
       </c>
-      <c r="L64" s="5" t="n">
+      <c r="L64" s="4" t="n">
         <f aca="false">J64/16</f>
         <v>6</v>
       </c>
-      <c r="M64" s="5" t="n">
+      <c r="M64" s="4" t="n">
         <f aca="false">J64/32</f>
         <v>3</v>
       </c>
-      <c r="N64" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O64" s="24" t="n">
+      <c r="N64" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O64" s="22" t="n">
         <v>4</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q64" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="22" t="s">
+      <c r="B65" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="C65" s="22" t="s">
+      <c r="C65" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="D65" s="22" t="n">
+      <c r="D65" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="E65" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22" t="n">
+      <c r="E65" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F65" s="20"/>
+      <c r="G65" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="H65" s="22" t="s">
+      <c r="H65" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="I65" s="23" t="s">
+      <c r="I65" s="21" t="s">
         <v>156</v>
       </c>
       <c r="J65" s="4" t="n">
         <f aca="false">J64+D64</f>
         <v>112</v>
       </c>
-      <c r="K65" s="5" t="n">
+      <c r="K65" s="4" t="n">
         <f aca="false">J65/8</f>
         <v>14</v>
       </c>
-      <c r="L65" s="5" t="n">
+      <c r="L65" s="4" t="n">
         <f aca="false">J65/16</f>
         <v>7</v>
       </c>
-      <c r="M65" s="5" t="n">
+      <c r="M65" s="4" t="n">
         <f aca="false">J65/32</f>
         <v>3.5</v>
       </c>
-      <c r="N65" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O65" s="24" t="n">
+      <c r="N65" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O65" s="22" t="n">
         <v>4</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q65" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="22" t="s">
+      <c r="B66" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="C66" s="22" t="s">
+      <c r="C66" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="D66" s="22" t="n">
+      <c r="D66" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="E66" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F66" s="22"/>
-      <c r="G66" s="22" t="n">
+      <c r="E66" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F66" s="20"/>
+      <c r="G66" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="H66" s="22" t="s">
+      <c r="H66" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="I66" s="23" t="s">
+      <c r="I66" s="21" t="s">
         <v>159</v>
       </c>
       <c r="J66" s="4" t="n">
         <f aca="false">J65+D65</f>
         <v>128</v>
       </c>
-      <c r="K66" s="5" t="n">
+      <c r="K66" s="4" t="n">
         <f aca="false">J66/8</f>
         <v>16</v>
       </c>
-      <c r="L66" s="5" t="n">
+      <c r="L66" s="4" t="n">
         <f aca="false">J66/16</f>
         <v>8</v>
       </c>
-      <c r="M66" s="5" t="n">
+      <c r="M66" s="4" t="n">
         <f aca="false">J66/32</f>
         <v>4</v>
       </c>
-      <c r="N66" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="O66" s="24" t="n">
+      <c r="N66" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O66" s="22" t="n">
         <v>4</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q66" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="30" t="s">
+      <c r="B67" s="26" t="s">
         <v>160</v>
       </c>
-      <c r="C67" s="30" t="s">
+      <c r="C67" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="D67" s="30" t="n">
+      <c r="D67" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="E67" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="F67" s="23"/>
-      <c r="G67" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="22" t="s">
+      <c r="E67" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F67" s="21"/>
+      <c r="G67" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H67" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I67" s="23" t="s">
+      <c r="I67" s="21" t="s">
         <v>162</v>
       </c>
       <c r="J67" s="4" t="n">
         <f aca="false">J66+D66</f>
         <v>144</v>
       </c>
-      <c r="K67" s="5" t="n">
+      <c r="K67" s="4" t="n">
         <f aca="false">J67/8</f>
         <v>18</v>
       </c>
-      <c r="L67" s="5" t="n">
+      <c r="L67" s="4" t="n">
         <f aca="false">J67/16</f>
         <v>9</v>
       </c>
-      <c r="M67" s="5" t="n">
+      <c r="M67" s="4" t="n">
         <f aca="false">J67/32</f>
         <v>4.5</v>
       </c>
-      <c r="N67" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="O67" s="24" t="n">
+      <c r="N67" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="O67" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q67" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="25.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="30" t="s">
+    <row r="68" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="C68" s="30" t="s">
+      <c r="C68" s="26" t="s">
         <v>164</v>
       </c>
-      <c r="D68" s="30" t="n">
+      <c r="D68" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="E68" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F68" s="23"/>
-      <c r="G68" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="22" t="s">
+      <c r="E68" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F68" s="21"/>
+      <c r="G68" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H68" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I68" s="23" t="s">
+      <c r="I68" s="21" t="s">
         <v>165</v>
       </c>
       <c r="J68" s="4" t="n">
         <f aca="false">J67+D67</f>
         <v>152</v>
       </c>
-      <c r="K68" s="5" t="n">
+      <c r="K68" s="4" t="n">
         <f aca="false">J68/8</f>
         <v>19</v>
       </c>
-      <c r="L68" s="5" t="n">
+      <c r="L68" s="4" t="n">
         <f aca="false">J68/16</f>
         <v>9.5</v>
       </c>
-      <c r="M68" s="5" t="n">
+      <c r="M68" s="4" t="n">
         <f aca="false">J68/32</f>
         <v>4.75</v>
       </c>
-      <c r="N68" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="O68" s="24" t="n">
+      <c r="N68" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="O68" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P68" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q68" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="30" t="s">
+      <c r="B69" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="C69" s="30" t="s">
+      <c r="C69" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="D69" s="30" t="n">
+      <c r="D69" s="26" t="n">
         <v>32</v>
       </c>
-      <c r="E69" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F69" s="23"/>
-      <c r="G69" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="22" t="s">
+      <c r="E69" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F69" s="21"/>
+      <c r="G69" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I69" s="30" t="s">
+      <c r="I69" s="26" t="s">
         <v>168</v>
       </c>
       <c r="J69" s="4" t="n">
         <f aca="false">J68+D68</f>
         <v>160</v>
       </c>
-      <c r="K69" s="5" t="n">
+      <c r="K69" s="4" t="n">
         <f aca="false">J69/8</f>
         <v>20</v>
       </c>
-      <c r="L69" s="5" t="n">
+      <c r="L69" s="4" t="n">
         <f aca="false">J69/16</f>
         <v>10</v>
       </c>
-      <c r="M69" s="5" t="n">
+      <c r="M69" s="4" t="n">
         <f aca="false">J69/32</f>
         <v>5</v>
       </c>
-      <c r="N69" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="O69" s="24" t="n">
+      <c r="N69" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="O69" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P69" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q69" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="C70" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="D70" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Q69" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="30" t="s">
-        <v>169</v>
-      </c>
-      <c r="C70" s="30" t="s">
-        <v>170</v>
-      </c>
-      <c r="D70" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="E70" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="F70" s="23"/>
-      <c r="G70" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="22" t="s">
+      <c r="E70" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F70" s="21"/>
+      <c r="G70" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I70" s="23" t="s">
+      <c r="I70" s="21" t="s">
         <v>171</v>
       </c>
       <c r="J70" s="4" t="n">
         <f aca="false">J69+D69</f>
         <v>192</v>
       </c>
-      <c r="K70" s="5" t="n">
+      <c r="K70" s="4" t="n">
         <f aca="false">J70/8</f>
         <v>24</v>
       </c>
-      <c r="L70" s="5" t="n">
+      <c r="L70" s="4" t="n">
         <f aca="false">J70/16</f>
         <v>12</v>
       </c>
-      <c r="M70" s="5" t="n">
+      <c r="M70" s="4" t="n">
         <f aca="false">J70/32</f>
         <v>6</v>
       </c>
-      <c r="N70" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O70" s="24" t="n">
+      <c r="N70" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O70" s="22" t="n">
         <v>3</v>
       </c>
       <c r="P70" s="1" t="n">
@@ -4239,40 +4328,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" s="15" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="B71" s="31"/>
-      <c r="C71" s="32"/>
-      <c r="D71" s="33"/>
-      <c r="E71" s="33"/>
-      <c r="F71" s="33"/>
-      <c r="G71" s="33"/>
-      <c r="H71" s="32"/>
-      <c r="I71" s="33" t="s">
+    <row r="71" s="14" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B71" s="27"/>
+      <c r="C71" s="28"/>
+      <c r="D71" s="29"/>
+      <c r="E71" s="29"/>
+      <c r="F71" s="29"/>
+      <c r="G71" s="29"/>
+      <c r="H71" s="28"/>
+      <c r="I71" s="29" t="s">
         <v>172</v>
       </c>
       <c r="J71" s="4" t="n">
         <f aca="false">J70+D70</f>
         <v>200</v>
       </c>
-      <c r="K71" s="5" t="n">
+      <c r="K71" s="4" t="n">
         <f aca="false">J71/8</f>
         <v>25</v>
       </c>
-      <c r="L71" s="5" t="n">
+      <c r="L71" s="4" t="n">
         <f aca="false">J71/16</f>
         <v>12.5</v>
       </c>
-      <c r="M71" s="5" t="n">
+      <c r="M71" s="4" t="n">
         <f aca="false">J71/32</f>
         <v>6.25</v>
       </c>
-      <c r="O71" s="34"/>
+      <c r="O71" s="30"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="25"/>
+      <c r="B72" s="23"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
@@ -4283,61 +4372,61 @@
       <c r="A74" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B74" s="30"/>
-      <c r="C74" s="30"/>
-      <c r="D74" s="30"/>
-      <c r="E74" s="23"/>
-      <c r="F74" s="23"/>
-      <c r="G74" s="23"/>
-      <c r="H74" s="23"/>
-      <c r="I74" s="23"/>
-      <c r="J74" s="28"/>
-      <c r="K74" s="27"/>
-      <c r="L74" s="27"/>
-      <c r="M74" s="27"/>
+      <c r="B74" s="26"/>
+      <c r="C74" s="26"/>
+      <c r="D74" s="26"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="21"/>
+      <c r="G74" s="21"/>
+      <c r="H74" s="21"/>
+      <c r="I74" s="21"/>
+      <c r="J74" s="25"/>
+      <c r="K74" s="25"/>
+      <c r="L74" s="25"/>
+      <c r="M74" s="25"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="30" t="s">
-        <v>127</v>
-      </c>
-      <c r="C75" s="30" t="s">
+      <c r="B75" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="C75" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="D75" s="30" t="n">
+      <c r="D75" s="26" t="n">
         <v>32</v>
       </c>
-      <c r="E75" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="F75" s="23"/>
-      <c r="G75" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="22" t="s">
+      <c r="E75" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F75" s="21"/>
+      <c r="G75" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I75" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="J75" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="27" t="n">
+      <c r="I75" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="J75" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="25" t="n">
         <f aca="false">J75/8</f>
         <v>0</v>
       </c>
-      <c r="L75" s="27" t="n">
+      <c r="L75" s="25" t="n">
         <f aca="false">J75/16</f>
         <v>0</v>
       </c>
-      <c r="M75" s="27" t="n">
+      <c r="M75" s="25" t="n">
         <f aca="false">J75/32</f>
         <v>0</v>
       </c>
-      <c r="N75" s="5" t="s">
+      <c r="N75" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O75" s="24" t="n">
+      <c r="O75" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="1" t="n">
@@ -4347,101 +4436,101 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="B76" s="31"/>
-      <c r="C76" s="32"/>
-      <c r="D76" s="33"/>
-      <c r="E76" s="33"/>
-      <c r="F76" s="33"/>
-      <c r="G76" s="33"/>
-      <c r="H76" s="32"/>
-      <c r="I76" s="33" t="s">
+    <row r="76" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B76" s="27"/>
+      <c r="C76" s="28"/>
+      <c r="D76" s="29"/>
+      <c r="E76" s="29"/>
+      <c r="F76" s="29"/>
+      <c r="G76" s="29"/>
+      <c r="H76" s="28"/>
+      <c r="I76" s="29" t="s">
         <v>172</v>
       </c>
       <c r="J76" s="4" t="n">
         <f aca="false">J75+D75</f>
         <v>32</v>
       </c>
-      <c r="K76" s="5" t="n">
+      <c r="K76" s="4" t="n">
         <f aca="false">J76/8</f>
         <v>4</v>
       </c>
-      <c r="L76" s="5" t="n">
+      <c r="L76" s="4" t="n">
         <f aca="false">J76/16</f>
         <v>2</v>
       </c>
-      <c r="M76" s="5" t="n">
+      <c r="M76" s="4" t="n">
         <f aca="false">J76/32</f>
         <v>1</v>
       </c>
-      <c r="O76" s="34"/>
-    </row>
-    <row r="77" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="31"/>
-      <c r="C77" s="32"/>
-      <c r="D77" s="33"/>
-      <c r="E77" s="33"/>
-      <c r="F77" s="33"/>
-      <c r="G77" s="33"/>
-      <c r="H77" s="32"/>
-      <c r="I77" s="33"/>
-      <c r="J77" s="28"/>
-      <c r="K77" s="27"/>
-      <c r="L77" s="27"/>
-      <c r="M77" s="27"/>
-      <c r="O77" s="34"/>
+      <c r="O76" s="30"/>
+    </row>
+    <row r="77" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="27"/>
+      <c r="C77" s="28"/>
+      <c r="D77" s="29"/>
+      <c r="E77" s="29"/>
+      <c r="F77" s="29"/>
+      <c r="G77" s="29"/>
+      <c r="H77" s="28"/>
+      <c r="I77" s="29"/>
+      <c r="J77" s="25"/>
+      <c r="K77" s="25"/>
+      <c r="L77" s="25"/>
+      <c r="M77" s="25"/>
+      <c r="O77" s="30"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B78" s="25"/>
+      <c r="B78" s="23"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="30" t="s">
+      <c r="B79" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="C79" s="30" t="s">
+      <c r="C79" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="D79" s="26" t="n">
+      <c r="D79" s="24" t="n">
         <v>32</v>
       </c>
-      <c r="E79" s="35" t="s">
+      <c r="E79" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="F79" s="23"/>
-      <c r="G79" s="22" t="n">
+      <c r="F79" s="21"/>
+      <c r="G79" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="I79" s="27" t="s">
+      <c r="I79" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="J79" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="27" t="n">
+      <c r="J79" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="25" t="n">
         <f aca="false">J79/8</f>
         <v>0</v>
       </c>
-      <c r="L79" s="27" t="n">
+      <c r="L79" s="25" t="n">
         <f aca="false">J79/16</f>
         <v>0</v>
       </c>
-      <c r="M79" s="27" t="n">
+      <c r="M79" s="25" t="n">
         <f aca="false">J79/32</f>
         <v>0</v>
       </c>
-      <c r="N79" s="5" t="s">
+      <c r="N79" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O79" s="24" t="n">
+      <c r="O79" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P79" s="1" t="n">
@@ -4452,45 +4541,45 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="30" t="s">
+      <c r="B80" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="C80" s="30" t="s">
+      <c r="C80" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="D80" s="26" t="n">
+      <c r="D80" s="24" t="n">
         <v>16</v>
       </c>
-      <c r="E80" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F80" s="23"/>
-      <c r="G80" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="27" t="s">
+      <c r="E80" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F80" s="21"/>
+      <c r="G80" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="25" t="s">
         <v>182</v>
       </c>
       <c r="J80" s="4" t="n">
         <f aca="false">J79+D79</f>
         <v>32</v>
       </c>
-      <c r="K80" s="5" t="n">
+      <c r="K80" s="4" t="n">
         <f aca="false">J80/8</f>
         <v>4</v>
       </c>
-      <c r="L80" s="5" t="n">
+      <c r="L80" s="4" t="n">
         <f aca="false">J80/16</f>
         <v>2</v>
       </c>
-      <c r="M80" s="5" t="n">
+      <c r="M80" s="4" t="n">
         <f aca="false">J80/32</f>
         <v>1</v>
       </c>
-      <c r="N80" s="5" t="s">
+      <c r="N80" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O80" s="24" t="n">
+      <c r="O80" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="1" t="n">
@@ -4501,48 +4590,48 @@
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="30" t="s">
+      <c r="B81" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="C81" s="30" t="s">
+      <c r="C81" s="26" t="s">
         <v>184</v>
       </c>
-      <c r="D81" s="26" t="n">
+      <c r="D81" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="E81" s="35" t="s">
+      <c r="E81" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="F81" s="23"/>
-      <c r="G81" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="22" t="s">
+      <c r="F81" s="21"/>
+      <c r="G81" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I81" s="27" t="s">
+      <c r="I81" s="25" t="s">
         <v>185</v>
       </c>
       <c r="J81" s="4" t="n">
         <f aca="false">J80+D80</f>
         <v>48</v>
       </c>
-      <c r="K81" s="5" t="n">
+      <c r="K81" s="4" t="n">
         <f aca="false">J81/8</f>
         <v>6</v>
       </c>
-      <c r="L81" s="5" t="n">
+      <c r="L81" s="4" t="n">
         <f aca="false">J81/16</f>
         <v>3</v>
       </c>
-      <c r="M81" s="5" t="n">
+      <c r="M81" s="4" t="n">
         <f aca="false">J81/32</f>
         <v>1.5</v>
       </c>
-      <c r="N81" s="5" t="s">
+      <c r="N81" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O81" s="24" t="n">
+      <c r="O81" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P81" s="1" t="n">
@@ -4553,46 +4642,46 @@
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="30" t="s">
+      <c r="B82" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="C82" s="30" t="s">
+      <c r="C82" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="D82" s="26" t="n">
+      <c r="D82" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="E82" s="35"/>
-      <c r="F82" s="23"/>
-      <c r="G82" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" s="22" t="s">
+      <c r="E82" s="31"/>
+      <c r="F82" s="21"/>
+      <c r="G82" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I82" s="27" t="s">
+      <c r="I82" s="25" t="s">
         <v>188</v>
       </c>
       <c r="J82" s="4" t="n">
         <f aca="false">J81+D81</f>
         <v>56</v>
       </c>
-      <c r="K82" s="5" t="n">
+      <c r="K82" s="4" t="n">
         <f aca="false">J82/8</f>
         <v>7</v>
       </c>
-      <c r="L82" s="5" t="n">
+      <c r="L82" s="4" t="n">
         <f aca="false">J82/16</f>
         <v>3.5</v>
       </c>
-      <c r="M82" s="5" t="n">
+      <c r="M82" s="4" t="n">
         <f aca="false">J82/32</f>
         <v>1.75</v>
       </c>
-      <c r="N82" s="5" t="s">
+      <c r="N82" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O82" s="24" t="n">
+      <c r="O82" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P82" s="1" t="n">
@@ -4604,87 +4693,87 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B83" s="25"/>
-      <c r="C83" s="32"/>
-      <c r="D83" s="33"/>
-      <c r="E83" s="33"/>
-      <c r="F83" s="33"/>
-      <c r="G83" s="33"/>
-      <c r="H83" s="32"/>
-      <c r="I83" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="B83" s="23"/>
+      <c r="C83" s="28"/>
+      <c r="D83" s="29"/>
+      <c r="E83" s="29"/>
+      <c r="F83" s="29"/>
+      <c r="G83" s="29"/>
+      <c r="H83" s="28"/>
+      <c r="I83" s="29" t="s">
         <v>172</v>
       </c>
       <c r="J83" s="4" t="n">
         <f aca="false">J82+D82</f>
         <v>64</v>
       </c>
-      <c r="K83" s="5" t="n">
+      <c r="K83" s="4" t="n">
         <f aca="false">J83/8</f>
         <v>8</v>
       </c>
-      <c r="L83" s="5" t="n">
+      <c r="L83" s="4" t="n">
         <f aca="false">J83/16</f>
         <v>4</v>
       </c>
-      <c r="M83" s="5" t="n">
+      <c r="M83" s="4" t="n">
         <f aca="false">J83/32</f>
         <v>2</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="25"/>
+      <c r="B84" s="23"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="25"/>
+      <c r="B85" s="23"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B86" s="25"/>
+      <c r="B86" s="23"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="30" t="s">
+      <c r="B87" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="C87" s="30" t="s">
+      <c r="C87" s="26" t="s">
         <v>191</v>
       </c>
-      <c r="D87" s="26" t="n">
+      <c r="D87" s="24" t="n">
         <v>32</v>
       </c>
-      <c r="E87" s="35"/>
-      <c r="F87" s="23"/>
-      <c r="G87" s="22" t="n">
+      <c r="E87" s="31"/>
+      <c r="F87" s="21"/>
+      <c r="G87" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="I87" s="27" t="s">
+      <c r="I87" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="J87" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="27" t="n">
+      <c r="J87" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="25" t="n">
         <f aca="false">J87/8</f>
         <v>0</v>
       </c>
-      <c r="L87" s="27" t="n">
+      <c r="L87" s="25" t="n">
         <f aca="false">J87/16</f>
         <v>0</v>
       </c>
-      <c r="M87" s="27" t="n">
+      <c r="M87" s="25" t="n">
         <f aca="false">J87/32</f>
         <v>0</v>
       </c>
-      <c r="N87" s="5" t="s">
+      <c r="N87" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O87" s="24" t="n">
+      <c r="O87" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P87" s="1" t="n">
@@ -4695,45 +4784,45 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B88" s="30" t="s">
+      <c r="B88" s="26" t="s">
         <v>192</v>
       </c>
-      <c r="C88" s="30" t="s">
+      <c r="C88" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="D88" s="26" t="n">
+      <c r="D88" s="24" t="n">
         <v>16</v>
       </c>
-      <c r="E88" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F88" s="23"/>
-      <c r="G88" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="27" t="s">
+      <c r="E88" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F88" s="21"/>
+      <c r="G88" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="25" t="s">
         <v>182</v>
       </c>
       <c r="J88" s="4" t="n">
         <f aca="false">J87+D87</f>
         <v>32</v>
       </c>
-      <c r="K88" s="5" t="n">
+      <c r="K88" s="4" t="n">
         <f aca="false">J88/8</f>
         <v>4</v>
       </c>
-      <c r="L88" s="5" t="n">
+      <c r="L88" s="4" t="n">
         <f aca="false">J88/16</f>
         <v>2</v>
       </c>
-      <c r="M88" s="5" t="n">
+      <c r="M88" s="4" t="n">
         <f aca="false">J88/32</f>
         <v>1</v>
       </c>
-      <c r="N88" s="5" t="s">
+      <c r="N88" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O88" s="24" t="n">
+      <c r="O88" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="1" t="n">
@@ -4744,43 +4833,43 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="30" t="s">
+      <c r="B89" s="26" t="s">
         <v>194</v>
       </c>
-      <c r="C89" s="30" t="s">
+      <c r="C89" s="26" t="s">
         <v>195</v>
       </c>
-      <c r="D89" s="26" t="n">
+      <c r="D89" s="24" t="n">
         <v>16</v>
       </c>
-      <c r="E89" s="35"/>
-      <c r="F89" s="23"/>
-      <c r="G89" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="27" t="s">
+      <c r="E89" s="31"/>
+      <c r="F89" s="21"/>
+      <c r="G89" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="25" t="s">
         <v>196</v>
       </c>
       <c r="J89" s="4" t="n">
         <f aca="false">J88+D88</f>
         <v>48</v>
       </c>
-      <c r="K89" s="5" t="n">
+      <c r="K89" s="4" t="n">
         <f aca="false">J89/8</f>
         <v>6</v>
       </c>
-      <c r="L89" s="5" t="n">
+      <c r="L89" s="4" t="n">
         <f aca="false">J89/16</f>
         <v>3</v>
       </c>
-      <c r="M89" s="5" t="n">
+      <c r="M89" s="4" t="n">
         <f aca="false">J89/32</f>
         <v>1.5</v>
       </c>
-      <c r="N89" s="5" t="s">
+      <c r="N89" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O89" s="24" t="n">
+      <c r="O89" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="1" t="n">
@@ -4791,43 +4880,43 @@
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="30" t="s">
+      <c r="B90" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="C90" s="30" t="s">
+      <c r="C90" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="D90" s="26" t="n">
+      <c r="D90" s="24" t="n">
         <v>32</v>
       </c>
-      <c r="E90" s="35"/>
-      <c r="F90" s="23"/>
-      <c r="G90" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="27" t="s">
+      <c r="E90" s="31"/>
+      <c r="F90" s="21"/>
+      <c r="G90" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="25" t="s">
         <v>199</v>
       </c>
       <c r="J90" s="4" t="n">
         <f aca="false">J89+D89</f>
         <v>64</v>
       </c>
-      <c r="K90" s="5" t="n">
+      <c r="K90" s="4" t="n">
         <f aca="false">J90/8</f>
         <v>8</v>
       </c>
-      <c r="L90" s="5" t="n">
+      <c r="L90" s="4" t="n">
         <f aca="false">J90/16</f>
         <v>4</v>
       </c>
-      <c r="M90" s="5" t="n">
+      <c r="M90" s="4" t="n">
         <f aca="false">J90/32</f>
         <v>2</v>
       </c>
-      <c r="N90" s="5" t="s">
+      <c r="N90" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O90" s="24" t="n">
+      <c r="O90" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="1" t="n">
@@ -4838,48 +4927,48 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B91" s="30" t="s">
+      <c r="B91" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="C91" s="30" t="s">
+      <c r="C91" s="26" t="s">
         <v>201</v>
       </c>
-      <c r="D91" s="26" t="n">
+      <c r="D91" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="E91" s="35" t="s">
+      <c r="E91" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="F91" s="23"/>
-      <c r="G91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" s="22" t="s">
+      <c r="F91" s="21"/>
+      <c r="G91" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I91" s="27" t="s">
+      <c r="I91" s="25" t="s">
         <v>202</v>
       </c>
       <c r="J91" s="4" t="n">
         <f aca="false">J90+D90</f>
         <v>96</v>
       </c>
-      <c r="K91" s="5" t="n">
+      <c r="K91" s="4" t="n">
         <f aca="false">J91/8</f>
         <v>12</v>
       </c>
-      <c r="L91" s="5" t="n">
+      <c r="L91" s="4" t="n">
         <f aca="false">J91/16</f>
         <v>6</v>
       </c>
-      <c r="M91" s="5" t="n">
+      <c r="M91" s="4" t="n">
         <f aca="false">J91/32</f>
         <v>3</v>
       </c>
-      <c r="N91" s="5" t="s">
+      <c r="N91" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O91" s="24" t="n">
+      <c r="O91" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P91" s="1" t="n">
@@ -4890,46 +4979,46 @@
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B92" s="30" t="s">
+      <c r="B92" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="C92" s="30" t="s">
+      <c r="C92" s="26" t="s">
         <v>203</v>
       </c>
-      <c r="D92" s="26" t="n">
+      <c r="D92" s="24" t="n">
         <v>24</v>
       </c>
-      <c r="E92" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="F92" s="23"/>
-      <c r="G92" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="22" t="s">
+      <c r="E92" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="F92" s="21"/>
+      <c r="G92" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I92" s="27"/>
+      <c r="I92" s="25"/>
       <c r="J92" s="4" t="n">
         <f aca="false">J91+D91</f>
         <v>104</v>
       </c>
-      <c r="K92" s="5" t="n">
+      <c r="K92" s="4" t="n">
         <f aca="false">J92/8</f>
         <v>13</v>
       </c>
-      <c r="L92" s="5" t="n">
+      <c r="L92" s="4" t="n">
         <f aca="false">J92/16</f>
         <v>6.5</v>
       </c>
-      <c r="M92" s="5" t="n">
+      <c r="M92" s="4" t="n">
         <f aca="false">J92/32</f>
         <v>3.25</v>
       </c>
-      <c r="N92" s="5" t="s">
+      <c r="N92" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O92" s="24" t="n">
+      <c r="O92" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="1" t="n">
@@ -4941,95 +5030,95 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B93" s="31"/>
-      <c r="C93" s="32"/>
-      <c r="D93" s="33"/>
-      <c r="E93" s="33"/>
-      <c r="F93" s="33"/>
-      <c r="G93" s="33"/>
-      <c r="H93" s="32"/>
-      <c r="I93" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="B93" s="27"/>
+      <c r="C93" s="28"/>
+      <c r="D93" s="29"/>
+      <c r="E93" s="29"/>
+      <c r="F93" s="29"/>
+      <c r="G93" s="29"/>
+      <c r="H93" s="28"/>
+      <c r="I93" s="29" t="s">
         <v>172</v>
       </c>
       <c r="J93" s="4" t="n">
         <f aca="false">J92+D92</f>
         <v>128</v>
       </c>
-      <c r="K93" s="5" t="n">
+      <c r="K93" s="4" t="n">
         <f aca="false">J93/8</f>
         <v>16</v>
       </c>
-      <c r="L93" s="5" t="n">
+      <c r="L93" s="4" t="n">
         <f aca="false">J93/16</f>
         <v>8</v>
       </c>
-      <c r="M93" s="5" t="n">
+      <c r="M93" s="4" t="n">
         <f aca="false">J93/32</f>
         <v>4</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="25"/>
+      <c r="B94" s="23"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B95" s="25"/>
+      <c r="B95" s="23"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B96" s="25"/>
+      <c r="B96" s="23"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B97" s="25"/>
+      <c r="B97" s="23"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B98" s="30" t="s">
+      <c r="B98" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="C98" s="30" t="s">
+      <c r="C98" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="D98" s="26" t="n">
+      <c r="D98" s="24" t="n">
         <v>32</v>
       </c>
-      <c r="E98" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F98" s="23"/>
-      <c r="G98" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="36" t="s">
+      <c r="E98" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F98" s="21"/>
+      <c r="G98" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="I98" s="27" t="s">
+      <c r="I98" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="J98" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" s="27" t="n">
+      <c r="J98" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="25" t="n">
         <f aca="false">J98/8</f>
         <v>0</v>
       </c>
-      <c r="L98" s="27" t="n">
+      <c r="L98" s="25" t="n">
         <f aca="false">J98/16</f>
         <v>0</v>
       </c>
-      <c r="M98" s="27" t="n">
+      <c r="M98" s="25" t="n">
         <f aca="false">J98/32</f>
         <v>0</v>
       </c>
-      <c r="N98" s="5" t="s">
+      <c r="N98" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O98" s="24" t="n">
+      <c r="O98" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P98" s="1" t="n">
@@ -5040,48 +5129,48 @@
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B99" s="30" t="s">
+      <c r="B99" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="C99" s="30" t="s">
+      <c r="C99" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="D99" s="26" t="n">
+      <c r="D99" s="24" t="n">
         <v>16</v>
       </c>
-      <c r="E99" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F99" s="23"/>
-      <c r="G99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" s="36" t="s">
+      <c r="E99" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F99" s="21"/>
+      <c r="G99" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="I99" s="27" t="s">
+      <c r="I99" s="25" t="s">
         <v>207</v>
       </c>
       <c r="J99" s="4" t="n">
         <f aca="false">J98+D98</f>
         <v>32</v>
       </c>
-      <c r="K99" s="5" t="n">
+      <c r="K99" s="4" t="n">
         <f aca="false">J99/8</f>
         <v>4</v>
       </c>
-      <c r="L99" s="5" t="n">
+      <c r="L99" s="4" t="n">
         <f aca="false">J99/16</f>
         <v>2</v>
       </c>
-      <c r="M99" s="5" t="n">
+      <c r="M99" s="4" t="n">
         <f aca="false">J99/32</f>
         <v>1</v>
       </c>
-      <c r="N99" s="5" t="s">
+      <c r="N99" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O99" s="24" t="n">
+      <c r="O99" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P99" s="1" t="n">
@@ -5092,48 +5181,48 @@
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B100" s="30" t="s">
+      <c r="B100" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="C100" s="30" t="s">
+      <c r="C100" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="D100" s="26" t="n">
+      <c r="D100" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="E100" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F100" s="23"/>
-      <c r="G100" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" s="22" t="s">
+      <c r="E100" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F100" s="21"/>
+      <c r="G100" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I100" s="27" t="s">
+      <c r="I100" s="25" t="s">
         <v>212</v>
       </c>
       <c r="J100" s="4" t="n">
         <f aca="false">J99+D99</f>
         <v>48</v>
       </c>
-      <c r="K100" s="5" t="n">
+      <c r="K100" s="4" t="n">
         <f aca="false">J100/8</f>
         <v>6</v>
       </c>
-      <c r="L100" s="5" t="n">
+      <c r="L100" s="4" t="n">
         <f aca="false">J100/16</f>
         <v>3</v>
       </c>
-      <c r="M100" s="5" t="n">
+      <c r="M100" s="4" t="n">
         <f aca="false">J100/32</f>
         <v>1.5</v>
       </c>
-      <c r="N100" s="5" t="s">
+      <c r="N100" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O100" s="24" t="n">
+      <c r="O100" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P100" s="1" t="n">
@@ -5145,141 +5234,141 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B101" s="30"/>
+        <v>45</v>
+      </c>
+      <c r="B101" s="26"/>
       <c r="I101" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J101" s="4" t="n">
         <f aca="false">J100+D100</f>
         <v>56</v>
       </c>
-      <c r="K101" s="5" t="n">
+      <c r="K101" s="4" t="n">
         <f aca="false">J101/8</f>
         <v>7</v>
       </c>
-      <c r="L101" s="5" t="n">
+      <c r="L101" s="4" t="n">
         <f aca="false">J101/16</f>
         <v>3.5</v>
       </c>
-      <c r="M101" s="5" t="n">
+      <c r="M101" s="4" t="n">
         <f aca="false">J101/32</f>
         <v>1.75</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B102" s="30"/>
-      <c r="J102" s="28"/>
-      <c r="K102" s="27"/>
-      <c r="L102" s="27"/>
-      <c r="M102" s="27"/>
+      <c r="B102" s="26"/>
+      <c r="J102" s="25"/>
+      <c r="K102" s="25"/>
+      <c r="L102" s="25"/>
+      <c r="M102" s="25"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="37" t="s">
+      <c r="A104" s="33" t="s">
         <v>213</v>
       </c>
-      <c r="J104" s="38"/>
-      <c r="K104" s="27"/>
-      <c r="L104" s="27"/>
-      <c r="M104" s="27"/>
-      <c r="N104" s="20" t="s">
+      <c r="J104" s="34"/>
+      <c r="K104" s="25"/>
+      <c r="L104" s="25"/>
+      <c r="M104" s="25"/>
+      <c r="N104" s="18" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="105" s="15" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B105" s="16" t="s">
+    <row r="105" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C105" s="13" t="s">
+      <c r="C105" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D105" s="13" t="s">
+      <c r="D105" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E105" s="13" t="s">
+      <c r="E105" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F105" s="13" t="s">
+      <c r="F105" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="G105" s="13" t="s">
+      <c r="G105" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="H105" s="13" t="s">
+      <c r="H105" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="I105" s="14" t="s">
+      <c r="I105" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J105" s="29" t="s">
+      <c r="J105" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="K105" s="15" t="s">
+      <c r="K105" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="L105" s="15" t="s">
+      <c r="L105" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="M105" s="15" t="s">
+      <c r="M105" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="N105" s="5"/>
-      <c r="O105" s="21" t="s">
+      <c r="N105" s="4"/>
+      <c r="O105" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="P105" s="15" t="s">
+      <c r="P105" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="Q105" s="15" t="s">
+      <c r="Q105" s="14" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="106" s="39" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B106" s="22" t="s">
+    <row r="106" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B106" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="C106" s="40" t="s">
+      <c r="C106" s="36" t="s">
         <v>215</v>
       </c>
       <c r="D106" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="E106" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F106" s="41"/>
-      <c r="G106" s="35" t="n">
+      <c r="E106" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F106" s="37"/>
+      <c r="G106" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H106" s="35" t="s">
+      <c r="H106" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I106" s="35" t="s">
+      <c r="I106" s="31" t="s">
         <v>216</v>
       </c>
-      <c r="J106" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" s="27" t="n">
+      <c r="J106" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="25" t="n">
         <f aca="false">J106/8</f>
         <v>0</v>
       </c>
-      <c r="L106" s="27" t="n">
+      <c r="L106" s="25" t="n">
         <f aca="false">J106/16</f>
         <v>0</v>
       </c>
-      <c r="M106" s="27" t="n">
+      <c r="M106" s="25" t="n">
         <f aca="false">J106/32</f>
         <v>0</v>
       </c>
-      <c r="N106" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O106" s="24" t="n">
+      <c r="N106" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O106" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P106" s="1" t="n">
@@ -5289,49 +5378,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" s="39" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B107" s="22" t="s">
+    <row r="107" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B107" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="C107" s="40" t="s">
+      <c r="C107" s="36" t="s">
         <v>218</v>
       </c>
       <c r="D107" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E107" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F107" s="41"/>
-      <c r="G107" s="35" t="n">
+      <c r="E107" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F107" s="37"/>
+      <c r="G107" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H107" s="35" t="s">
+      <c r="H107" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I107" s="35" t="s">
+      <c r="I107" s="31" t="s">
         <v>216</v>
       </c>
       <c r="J107" s="4" t="n">
         <f aca="false">J106+D106</f>
         <v>9</v>
       </c>
-      <c r="K107" s="5" t="n">
+      <c r="K107" s="4" t="n">
         <f aca="false">J107/8</f>
         <v>1.125</v>
       </c>
-      <c r="L107" s="5" t="n">
+      <c r="L107" s="4" t="n">
         <f aca="false">J107/16</f>
         <v>0.5625</v>
       </c>
-      <c r="M107" s="5" t="n">
+      <c r="M107" s="4" t="n">
         <f aca="false">J107/32</f>
         <v>0.28125</v>
       </c>
-      <c r="N107" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O107" s="24" t="n">
+      <c r="N107" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O107" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P107" s="1" t="n">
@@ -5341,49 +5430,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" s="39" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B108" s="22" t="s">
+    <row r="108" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B108" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="C108" s="40" t="s">
+      <c r="C108" s="36" t="s">
         <v>220</v>
       </c>
       <c r="D108" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E108" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F108" s="41"/>
-      <c r="G108" s="35" t="n">
+      <c r="E108" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F108" s="37"/>
+      <c r="G108" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H108" s="35" t="s">
+      <c r="H108" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I108" s="35" t="s">
+      <c r="I108" s="31" t="s">
         <v>221</v>
       </c>
       <c r="J108" s="4" t="n">
         <f aca="false">J107+D107</f>
         <v>14</v>
       </c>
-      <c r="K108" s="5" t="n">
+      <c r="K108" s="4" t="n">
         <f aca="false">J108/8</f>
         <v>1.75</v>
       </c>
-      <c r="L108" s="5" t="n">
+      <c r="L108" s="4" t="n">
         <f aca="false">J108/16</f>
         <v>0.875</v>
       </c>
-      <c r="M108" s="5" t="n">
+      <c r="M108" s="4" t="n">
         <f aca="false">J108/32</f>
         <v>0.4375</v>
       </c>
-      <c r="N108" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O108" s="24" t="n">
+      <c r="N108" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O108" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P108" s="1" t="n">
@@ -5393,49 +5482,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" s="39" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B109" s="22" t="s">
+    <row r="109" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B109" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="C109" s="40" t="s">
+      <c r="C109" s="36" t="s">
         <v>223</v>
       </c>
       <c r="D109" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E109" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F109" s="41"/>
-      <c r="G109" s="35" t="n">
+      <c r="E109" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F109" s="37"/>
+      <c r="G109" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H109" s="35" t="s">
+      <c r="H109" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I109" s="35" t="s">
+      <c r="I109" s="31" t="s">
         <v>224</v>
       </c>
       <c r="J109" s="4" t="n">
         <f aca="false">J108+D108</f>
         <v>18</v>
       </c>
-      <c r="K109" s="5" t="n">
+      <c r="K109" s="4" t="n">
         <f aca="false">J109/8</f>
         <v>2.25</v>
       </c>
-      <c r="L109" s="5" t="n">
+      <c r="L109" s="4" t="n">
         <f aca="false">J109/16</f>
         <v>1.125</v>
       </c>
-      <c r="M109" s="5" t="n">
+      <c r="M109" s="4" t="n">
         <f aca="false">J109/32</f>
         <v>0.5625</v>
       </c>
-      <c r="N109" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O109" s="24" t="n">
+      <c r="N109" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O109" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P109" s="1" t="n">
@@ -5445,49 +5534,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" s="39" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B110" s="22" t="s">
+    <row r="110" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B110" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="C110" s="40" t="s">
+      <c r="C110" s="36" t="s">
         <v>226</v>
       </c>
       <c r="D110" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E110" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F110" s="41"/>
-      <c r="G110" s="22" t="n">
+      <c r="E110" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F110" s="37"/>
+      <c r="G110" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="H110" s="35" t="s">
+      <c r="H110" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I110" s="22" t="s">
+      <c r="I110" s="20" t="s">
         <v>227</v>
       </c>
       <c r="J110" s="4" t="n">
         <f aca="false">J109+D109</f>
         <v>22</v>
       </c>
-      <c r="K110" s="5" t="n">
+      <c r="K110" s="4" t="n">
         <f aca="false">J110/8</f>
         <v>2.75</v>
       </c>
-      <c r="L110" s="5" t="n">
+      <c r="L110" s="4" t="n">
         <f aca="false">J110/16</f>
         <v>1.375</v>
       </c>
-      <c r="M110" s="5" t="n">
+      <c r="M110" s="4" t="n">
         <f aca="false">J110/32</f>
         <v>0.6875</v>
       </c>
-      <c r="N110" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O110" s="24" t="n">
+      <c r="N110" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O110" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P110" s="1" t="n">
@@ -5497,49 +5586,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" s="39" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B111" s="22" t="s">
+    <row r="111" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B111" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="C111" s="40" t="s">
+      <c r="C111" s="36" t="s">
         <v>229</v>
       </c>
       <c r="D111" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E111" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F111" s="41"/>
-      <c r="G111" s="22" t="n">
+      <c r="E111" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F111" s="37"/>
+      <c r="G111" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="H111" s="35" t="s">
+      <c r="H111" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I111" s="22" t="s">
+      <c r="I111" s="20" t="s">
         <v>230</v>
       </c>
       <c r="J111" s="4" t="n">
         <f aca="false">J110+D110</f>
         <v>25</v>
       </c>
-      <c r="K111" s="5" t="n">
+      <c r="K111" s="4" t="n">
         <f aca="false">J111/8</f>
         <v>3.125</v>
       </c>
-      <c r="L111" s="5" t="n">
+      <c r="L111" s="4" t="n">
         <f aca="false">J111/16</f>
         <v>1.5625</v>
       </c>
-      <c r="M111" s="5" t="n">
+      <c r="M111" s="4" t="n">
         <f aca="false">J111/32</f>
         <v>0.78125</v>
       </c>
-      <c r="N111" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O111" s="24" t="n">
+      <c r="N111" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O111" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P111" s="1" t="n">
@@ -5549,49 +5638,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" s="39" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B112" s="22" t="s">
+    <row r="112" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B112" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="C112" s="40" t="s">
+      <c r="C112" s="36" t="s">
         <v>232</v>
       </c>
       <c r="D112" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E112" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F112" s="41"/>
-      <c r="G112" s="22" t="n">
+      <c r="E112" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F112" s="37"/>
+      <c r="G112" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H112" s="35" t="s">
+      <c r="H112" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I112" s="35" t="s">
+      <c r="I112" s="31" t="s">
         <v>216</v>
       </c>
       <c r="J112" s="4" t="n">
         <f aca="false">J111+D111</f>
         <v>26</v>
       </c>
-      <c r="K112" s="5" t="n">
+      <c r="K112" s="4" t="n">
         <f aca="false">J112/8</f>
         <v>3.25</v>
       </c>
-      <c r="L112" s="5" t="n">
+      <c r="L112" s="4" t="n">
         <f aca="false">J112/16</f>
         <v>1.625</v>
       </c>
-      <c r="M112" s="5" t="n">
+      <c r="M112" s="4" t="n">
         <f aca="false">J112/32</f>
         <v>0.8125</v>
       </c>
-      <c r="N112" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O112" s="24" t="n">
+      <c r="N112" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O112" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P112" s="1" t="n">
@@ -5601,49 +5690,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" s="39" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B113" s="22" t="s">
+    <row r="113" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B113" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="C113" s="40" t="s">
+      <c r="C113" s="36" t="s">
         <v>234</v>
       </c>
       <c r="D113" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E113" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F113" s="41"/>
-      <c r="G113" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" s="35" t="s">
+      <c r="E113" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F113" s="37"/>
+      <c r="G113" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I113" s="35" t="s">
+      <c r="I113" s="31" t="s">
         <v>216</v>
       </c>
       <c r="J113" s="4" t="n">
         <f aca="false">J112+D112</f>
         <v>27</v>
       </c>
-      <c r="K113" s="5" t="n">
+      <c r="K113" s="4" t="n">
         <f aca="false">J113/8</f>
         <v>3.375</v>
       </c>
-      <c r="L113" s="5" t="n">
+      <c r="L113" s="4" t="n">
         <f aca="false">J113/16</f>
         <v>1.6875</v>
       </c>
-      <c r="M113" s="5" t="n">
+      <c r="M113" s="4" t="n">
         <f aca="false">J113/32</f>
         <v>0.84375</v>
       </c>
-      <c r="N113" s="5" t="s">
+      <c r="N113" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O113" s="24" t="n">
+      <c r="O113" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P113" s="1" t="n">
@@ -5653,49 +5742,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" s="39" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B114" s="22" t="s">
+    <row r="114" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B114" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="C114" s="40" t="s">
+      <c r="C114" s="36" t="s">
         <v>236</v>
       </c>
       <c r="D114" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="E114" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F114" s="41"/>
-      <c r="G114" s="22" t="n">
+      <c r="E114" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F114" s="37"/>
+      <c r="G114" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="H114" s="35" t="s">
+      <c r="H114" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I114" s="35" t="s">
+      <c r="I114" s="31" t="s">
         <v>216</v>
       </c>
       <c r="J114" s="4" t="n">
         <f aca="false">J113+D113</f>
         <v>32</v>
       </c>
-      <c r="K114" s="5" t="n">
+      <c r="K114" s="4" t="n">
         <f aca="false">J114/8</f>
         <v>4</v>
       </c>
-      <c r="L114" s="5" t="n">
+      <c r="L114" s="4" t="n">
         <f aca="false">J114/16</f>
         <v>2</v>
       </c>
-      <c r="M114" s="5" t="n">
+      <c r="M114" s="4" t="n">
         <f aca="false">J114/32</f>
         <v>1</v>
       </c>
-      <c r="N114" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O114" s="24" t="n">
+      <c r="N114" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O114" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P114" s="1" t="n">
@@ -5706,48 +5795,48 @@
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B115" s="22" t="s">
+      <c r="B115" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="C115" s="22" t="s">
+      <c r="C115" s="20" t="s">
         <v>238</v>
       </c>
       <c r="D115" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="E115" s="35" t="s">
+      <c r="E115" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="F115" s="35"/>
-      <c r="G115" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" s="35" t="s">
+      <c r="F115" s="31"/>
+      <c r="G115" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I115" s="35" t="s">
+      <c r="I115" s="31" t="s">
         <v>216</v>
       </c>
       <c r="J115" s="4" t="n">
         <f aca="false">J114+D114</f>
         <v>64</v>
       </c>
-      <c r="K115" s="5" t="n">
+      <c r="K115" s="4" t="n">
         <f aca="false">J115/8</f>
         <v>8</v>
       </c>
-      <c r="L115" s="5" t="n">
+      <c r="L115" s="4" t="n">
         <f aca="false">J115/16</f>
         <v>4</v>
       </c>
-      <c r="M115" s="5" t="n">
+      <c r="M115" s="4" t="n">
         <f aca="false">J115/32</f>
         <v>2</v>
       </c>
-      <c r="N115" s="5" t="s">
+      <c r="N115" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="O115" s="24" t="n">
+      <c r="O115" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P115" s="1" t="n">
@@ -5758,48 +5847,48 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B116" s="22" t="s">
+      <c r="B116" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="C116" s="22" t="s">
+      <c r="C116" s="20" t="s">
         <v>241</v>
       </c>
       <c r="D116" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="E116" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F116" s="35"/>
-      <c r="G116" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" s="35" t="s">
+      <c r="E116" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F116" s="31"/>
+      <c r="G116" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I116" s="35" t="s">
+      <c r="I116" s="31" t="s">
         <v>216</v>
       </c>
       <c r="J116" s="4" t="n">
         <f aca="false">J115+D115</f>
         <v>96</v>
       </c>
-      <c r="K116" s="5" t="n">
+      <c r="K116" s="4" t="n">
         <f aca="false">J116/8</f>
         <v>12</v>
       </c>
-      <c r="L116" s="5" t="n">
+      <c r="L116" s="4" t="n">
         <f aca="false">J116/16</f>
         <v>6</v>
       </c>
-      <c r="M116" s="5" t="n">
+      <c r="M116" s="4" t="n">
         <f aca="false">J116/32</f>
         <v>3</v>
       </c>
-      <c r="N116" s="5" t="s">
+      <c r="N116" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="O116" s="24" t="n">
+      <c r="O116" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P116" s="1" t="n">
@@ -5810,48 +5899,48 @@
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B117" s="22" t="s">
+      <c r="B117" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="C117" s="22" t="s">
+      <c r="C117" s="20" t="s">
         <v>243</v>
       </c>
       <c r="D117" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="E117" s="35" t="s">
+      <c r="E117" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="F117" s="35"/>
-      <c r="G117" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H117" s="35" t="s">
+      <c r="F117" s="31"/>
+      <c r="G117" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I117" s="35" t="s">
+      <c r="I117" s="31" t="s">
         <v>216</v>
       </c>
       <c r="J117" s="4" t="n">
         <f aca="false">J116+D116</f>
         <v>128</v>
       </c>
-      <c r="K117" s="5" t="n">
+      <c r="K117" s="4" t="n">
         <f aca="false">J117/8</f>
         <v>16</v>
       </c>
-      <c r="L117" s="5" t="n">
+      <c r="L117" s="4" t="n">
         <f aca="false">J117/16</f>
         <v>8</v>
       </c>
-      <c r="M117" s="5" t="n">
+      <c r="M117" s="4" t="n">
         <f aca="false">J117/32</f>
         <v>4</v>
       </c>
-      <c r="N117" s="5" t="s">
+      <c r="N117" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="O117" s="24" t="n">
+      <c r="O117" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P117" s="1" t="n">
@@ -5862,48 +5951,48 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B118" s="22" t="s">
+      <c r="B118" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="C118" s="22" t="s">
+      <c r="C118" s="20" t="s">
         <v>245</v>
       </c>
       <c r="D118" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="E118" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F118" s="35"/>
-      <c r="G118" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" s="35" t="s">
+      <c r="E118" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F118" s="31"/>
+      <c r="G118" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I118" s="35" t="s">
+      <c r="I118" s="31" t="s">
         <v>216</v>
       </c>
       <c r="J118" s="4" t="n">
         <f aca="false">J117+D117</f>
         <v>160</v>
       </c>
-      <c r="K118" s="5" t="n">
+      <c r="K118" s="4" t="n">
         <f aca="false">J118/8</f>
         <v>20</v>
       </c>
-      <c r="L118" s="5" t="n">
+      <c r="L118" s="4" t="n">
         <f aca="false">J118/16</f>
         <v>10</v>
       </c>
-      <c r="M118" s="5" t="n">
+      <c r="M118" s="4" t="n">
         <f aca="false">J118/32</f>
         <v>5</v>
       </c>
-      <c r="N118" s="5" t="s">
+      <c r="N118" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="O118" s="24" t="n">
+      <c r="O118" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P118" s="1" t="n">
@@ -5914,48 +6003,48 @@
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B119" s="22" t="s">
+      <c r="B119" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="C119" s="22" t="s">
+      <c r="C119" s="20" t="s">
         <v>247</v>
       </c>
       <c r="D119" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E119" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F119" s="35"/>
-      <c r="G119" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" s="35" t="s">
+      <c r="E119" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F119" s="31"/>
+      <c r="G119" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I119" s="35" t="s">
+      <c r="I119" s="31" t="s">
         <v>248</v>
       </c>
       <c r="J119" s="4" t="n">
         <f aca="false">J118+D118</f>
         <v>192</v>
       </c>
-      <c r="K119" s="5" t="n">
+      <c r="K119" s="4" t="n">
         <f aca="false">J119/8</f>
         <v>24</v>
       </c>
-      <c r="L119" s="5" t="n">
+      <c r="L119" s="4" t="n">
         <f aca="false">J119/16</f>
         <v>12</v>
       </c>
-      <c r="M119" s="5" t="n">
+      <c r="M119" s="4" t="n">
         <f aca="false">J119/32</f>
         <v>6</v>
       </c>
-      <c r="N119" s="5" t="s">
+      <c r="N119" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="O119" s="24" t="n">
+      <c r="O119" s="22" t="n">
         <v>4</v>
       </c>
       <c r="P119" s="1" t="n">
@@ -5966,48 +6055,48 @@
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B120" s="22" t="s">
+      <c r="B120" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="C120" s="22" t="s">
+      <c r="C120" s="20" t="s">
         <v>251</v>
       </c>
       <c r="D120" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E120" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F120" s="35"/>
-      <c r="G120" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" s="35" t="s">
+      <c r="E120" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F120" s="31"/>
+      <c r="G120" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I120" s="35" t="s">
+      <c r="I120" s="31" t="s">
         <v>252</v>
       </c>
       <c r="J120" s="4" t="n">
         <f aca="false">J119+D119</f>
         <v>200</v>
       </c>
-      <c r="K120" s="5" t="n">
+      <c r="K120" s="4" t="n">
         <f aca="false">J120/8</f>
         <v>25</v>
       </c>
-      <c r="L120" s="5" t="n">
+      <c r="L120" s="4" t="n">
         <f aca="false">J120/16</f>
         <v>12.5</v>
       </c>
-      <c r="M120" s="5" t="n">
+      <c r="M120" s="4" t="n">
         <f aca="false">J120/32</f>
         <v>6.25</v>
       </c>
-      <c r="N120" s="5" t="s">
+      <c r="N120" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="O120" s="24" t="n">
+      <c r="O120" s="22" t="n">
         <v>4</v>
       </c>
       <c r="P120" s="1" t="n">
@@ -6018,48 +6107,48 @@
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B121" s="22" t="s">
+      <c r="B121" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="C121" s="22" t="s">
+      <c r="C121" s="20" t="s">
         <v>254</v>
       </c>
       <c r="D121" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E121" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F121" s="35"/>
-      <c r="G121" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H121" s="35" t="s">
+      <c r="E121" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F121" s="31"/>
+      <c r="G121" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I121" s="35" t="s">
+      <c r="I121" s="31" t="s">
         <v>255</v>
       </c>
       <c r="J121" s="4" t="n">
         <f aca="false">J120+D120</f>
         <v>208</v>
       </c>
-      <c r="K121" s="5" t="n">
+      <c r="K121" s="4" t="n">
         <f aca="false">J121/8</f>
         <v>26</v>
       </c>
-      <c r="L121" s="5" t="n">
+      <c r="L121" s="4" t="n">
         <f aca="false">J121/16</f>
         <v>13</v>
       </c>
-      <c r="M121" s="5" t="n">
+      <c r="M121" s="4" t="n">
         <f aca="false">J121/32</f>
         <v>6.5</v>
       </c>
-      <c r="N121" s="5" t="s">
+      <c r="N121" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="O121" s="24" t="n">
+      <c r="O121" s="22" t="n">
         <v>4</v>
       </c>
       <c r="P121" s="1" t="n">
@@ -6070,48 +6159,48 @@
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B122" s="22" t="s">
+      <c r="B122" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="C122" s="22" t="s">
+      <c r="C122" s="20" t="s">
         <v>257</v>
       </c>
       <c r="D122" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E122" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F122" s="35"/>
-      <c r="G122" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" s="35" t="s">
+      <c r="E122" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F122" s="31"/>
+      <c r="G122" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I122" s="35" t="s">
+      <c r="I122" s="31" t="s">
         <v>258</v>
       </c>
       <c r="J122" s="4" t="n">
         <f aca="false">J121+D121</f>
         <v>216</v>
       </c>
-      <c r="K122" s="5" t="n">
+      <c r="K122" s="4" t="n">
         <f aca="false">J122/8</f>
         <v>27</v>
       </c>
-      <c r="L122" s="5" t="n">
+      <c r="L122" s="4" t="n">
         <f aca="false">J122/16</f>
         <v>13.5</v>
       </c>
-      <c r="M122" s="5" t="n">
+      <c r="M122" s="4" t="n">
         <f aca="false">J122/32</f>
         <v>6.75</v>
       </c>
-      <c r="N122" s="5" t="s">
+      <c r="N122" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="O122" s="24" t="n">
+      <c r="O122" s="22" t="n">
         <v>4</v>
       </c>
       <c r="P122" s="1" t="n">
@@ -6122,48 +6211,48 @@
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B123" s="22" t="s">
+      <c r="B123" s="20" t="s">
         <v>259</v>
       </c>
-      <c r="C123" s="22" t="s">
+      <c r="C123" s="20" t="s">
         <v>260</v>
       </c>
       <c r="D123" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E123" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F123" s="35"/>
-      <c r="G123" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H123" s="35" t="s">
+      <c r="E123" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F123" s="31"/>
+      <c r="G123" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I123" s="35" t="s">
+      <c r="I123" s="31" t="s">
         <v>261</v>
       </c>
       <c r="J123" s="4" t="n">
         <f aca="false">J122+D122</f>
         <v>224</v>
       </c>
-      <c r="K123" s="5" t="n">
+      <c r="K123" s="4" t="n">
         <f aca="false">J123/8</f>
         <v>28</v>
       </c>
-      <c r="L123" s="5" t="n">
+      <c r="L123" s="4" t="n">
         <f aca="false">J123/16</f>
         <v>14</v>
       </c>
-      <c r="M123" s="5" t="n">
+      <c r="M123" s="4" t="n">
         <f aca="false">J123/32</f>
         <v>7</v>
       </c>
-      <c r="N123" s="5" t="s">
+      <c r="N123" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="O123" s="24" t="n">
+      <c r="O123" s="22" t="n">
         <v>4</v>
       </c>
       <c r="P123" s="1" t="n">
@@ -6174,48 +6263,48 @@
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B124" s="22" t="s">
+      <c r="B124" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="C124" s="22" t="s">
+      <c r="C124" s="20" t="s">
         <v>263</v>
       </c>
       <c r="D124" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E124" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F124" s="35"/>
-      <c r="G124" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H124" s="35" t="s">
+      <c r="E124" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F124" s="31"/>
+      <c r="G124" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I124" s="22" t="s">
+      <c r="I124" s="20" t="s">
         <v>262</v>
       </c>
       <c r="J124" s="4" t="n">
         <f aca="false">J123+D123</f>
         <v>232</v>
       </c>
-      <c r="K124" s="5" t="n">
+      <c r="K124" s="4" t="n">
         <f aca="false">J124/8</f>
         <v>29</v>
       </c>
-      <c r="L124" s="5" t="n">
+      <c r="L124" s="4" t="n">
         <f aca="false">J124/16</f>
         <v>14.5</v>
       </c>
-      <c r="M124" s="5" t="n">
+      <c r="M124" s="4" t="n">
         <f aca="false">J124/32</f>
         <v>7.25</v>
       </c>
-      <c r="N124" s="5" t="s">
+      <c r="N124" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="O124" s="24" t="n">
+      <c r="O124" s="22" t="n">
         <v>3</v>
       </c>
       <c r="P124" s="1" t="n">
@@ -6226,48 +6315,48 @@
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B125" s="22" t="s">
+      <c r="B125" s="20" t="s">
         <v>265</v>
       </c>
-      <c r="C125" s="22" t="s">
+      <c r="C125" s="20" t="s">
         <v>266</v>
       </c>
       <c r="D125" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E125" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F125" s="35"/>
-      <c r="G125" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H125" s="35" t="s">
+      <c r="E125" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F125" s="31"/>
+      <c r="G125" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I125" s="22" t="s">
+      <c r="I125" s="20" t="s">
         <v>265</v>
       </c>
       <c r="J125" s="4" t="n">
         <f aca="false">J124+D124</f>
         <v>240</v>
       </c>
-      <c r="K125" s="5" t="n">
+      <c r="K125" s="4" t="n">
         <f aca="false">J125/8</f>
         <v>30</v>
       </c>
-      <c r="L125" s="5" t="n">
+      <c r="L125" s="4" t="n">
         <f aca="false">J125/16</f>
         <v>15</v>
       </c>
-      <c r="M125" s="5" t="n">
+      <c r="M125" s="4" t="n">
         <f aca="false">J125/32</f>
         <v>7.5</v>
       </c>
-      <c r="N125" s="5" t="s">
+      <c r="N125" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="O125" s="24" t="n">
+      <c r="O125" s="22" t="n">
         <v>3</v>
       </c>
       <c r="P125" s="1" t="n">
@@ -6278,48 +6367,48 @@
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B126" s="22" t="s">
+      <c r="B126" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="C126" s="22" t="s">
+      <c r="C126" s="20" t="s">
         <v>268</v>
       </c>
       <c r="D126" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E126" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F126" s="35"/>
-      <c r="G126" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" s="35" t="s">
+      <c r="E126" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F126" s="31"/>
+      <c r="G126" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I126" s="22" t="s">
+      <c r="I126" s="20" t="s">
         <v>267</v>
       </c>
       <c r="J126" s="4" t="n">
         <f aca="false">J125+D125</f>
         <v>248</v>
       </c>
-      <c r="K126" s="5" t="n">
+      <c r="K126" s="4" t="n">
         <f aca="false">J126/8</f>
         <v>31</v>
       </c>
-      <c r="L126" s="5" t="n">
+      <c r="L126" s="4" t="n">
         <f aca="false">J126/16</f>
         <v>15.5</v>
       </c>
-      <c r="M126" s="5" t="n">
+      <c r="M126" s="4" t="n">
         <f aca="false">J126/32</f>
         <v>7.75</v>
       </c>
-      <c r="N126" s="5" t="s">
+      <c r="N126" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="O126" s="24" t="n">
+      <c r="O126" s="22" t="n">
         <v>3</v>
       </c>
       <c r="P126" s="1" t="n">
@@ -6330,48 +6419,48 @@
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B127" s="22" t="s">
+      <c r="B127" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="C127" s="22" t="s">
+      <c r="C127" s="20" t="s">
         <v>270</v>
       </c>
       <c r="D127" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E127" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F127" s="35"/>
-      <c r="G127" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H127" s="35" t="s">
+      <c r="E127" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F127" s="31"/>
+      <c r="G127" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I127" s="22" t="s">
+      <c r="I127" s="20" t="s">
         <v>269</v>
       </c>
       <c r="J127" s="4" t="n">
         <f aca="false">J126+D126</f>
         <v>256</v>
       </c>
-      <c r="K127" s="5" t="n">
+      <c r="K127" s="4" t="n">
         <f aca="false">J127/8</f>
         <v>32</v>
       </c>
-      <c r="L127" s="5" t="n">
+      <c r="L127" s="4" t="n">
         <f aca="false">J127/16</f>
         <v>16</v>
       </c>
-      <c r="M127" s="5" t="n">
+      <c r="M127" s="4" t="n">
         <f aca="false">J127/32</f>
         <v>8</v>
       </c>
-      <c r="N127" s="5" t="s">
+      <c r="N127" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="O127" s="24" t="n">
+      <c r="O127" s="22" t="n">
         <v>3</v>
       </c>
       <c r="P127" s="1" t="n">
@@ -6382,48 +6471,48 @@
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B128" s="22" t="s">
+      <c r="B128" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="C128" s="22" t="s">
+      <c r="C128" s="20" t="s">
         <v>272</v>
       </c>
       <c r="D128" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E128" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F128" s="35"/>
-      <c r="G128" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H128" s="35" t="s">
+      <c r="E128" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F128" s="31"/>
+      <c r="G128" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I128" s="22" t="s">
+      <c r="I128" s="20" t="s">
         <v>271</v>
       </c>
       <c r="J128" s="4" t="n">
         <f aca="false">J127+D127</f>
         <v>264</v>
       </c>
-      <c r="K128" s="5" t="n">
+      <c r="K128" s="4" t="n">
         <f aca="false">J128/8</f>
         <v>33</v>
       </c>
-      <c r="L128" s="5" t="n">
+      <c r="L128" s="4" t="n">
         <f aca="false">J128/16</f>
         <v>16.5</v>
       </c>
-      <c r="M128" s="5" t="n">
+      <c r="M128" s="4" t="n">
         <f aca="false">J128/32</f>
         <v>8.25</v>
       </c>
-      <c r="N128" s="5" t="s">
+      <c r="N128" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="O128" s="24" t="n">
+      <c r="O128" s="22" t="n">
         <v>3</v>
       </c>
       <c r="P128" s="1" t="n">
@@ -6434,48 +6523,48 @@
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B129" s="22" t="s">
+      <c r="B129" s="20" t="s">
         <v>273</v>
       </c>
-      <c r="C129" s="22" t="s">
+      <c r="C129" s="20" t="s">
         <v>274</v>
       </c>
       <c r="D129" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E129" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F129" s="35"/>
-      <c r="G129" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" s="35" t="s">
+      <c r="E129" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F129" s="31"/>
+      <c r="G129" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I129" s="22" t="s">
+      <c r="I129" s="20" t="s">
         <v>273</v>
       </c>
       <c r="J129" s="4" t="n">
         <f aca="false">J128+D128</f>
         <v>272</v>
       </c>
-      <c r="K129" s="5" t="n">
+      <c r="K129" s="4" t="n">
         <f aca="false">J129/8</f>
         <v>34</v>
       </c>
-      <c r="L129" s="5" t="n">
+      <c r="L129" s="4" t="n">
         <f aca="false">J129/16</f>
         <v>17</v>
       </c>
-      <c r="M129" s="5" t="n">
+      <c r="M129" s="4" t="n">
         <f aca="false">J129/32</f>
         <v>8.5</v>
       </c>
-      <c r="N129" s="5" t="s">
+      <c r="N129" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="O129" s="24" t="n">
+      <c r="O129" s="22" t="n">
         <v>3</v>
       </c>
       <c r="P129" s="1" t="n">
@@ -6486,48 +6575,48 @@
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B130" s="22" t="s">
+      <c r="B130" s="20" t="s">
         <v>275</v>
       </c>
-      <c r="C130" s="22" t="s">
+      <c r="C130" s="20" t="s">
         <v>276</v>
       </c>
       <c r="D130" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E130" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F130" s="35"/>
-      <c r="G130" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" s="35" t="s">
+      <c r="E130" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F130" s="31"/>
+      <c r="G130" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I130" s="22" t="s">
+      <c r="I130" s="20" t="s">
         <v>275</v>
       </c>
       <c r="J130" s="4" t="n">
         <f aca="false">J129+D129</f>
         <v>280</v>
       </c>
-      <c r="K130" s="5" t="n">
+      <c r="K130" s="4" t="n">
         <f aca="false">J130/8</f>
         <v>35</v>
       </c>
-      <c r="L130" s="5" t="n">
+      <c r="L130" s="4" t="n">
         <f aca="false">J130/16</f>
         <v>17.5</v>
       </c>
-      <c r="M130" s="5" t="n">
+      <c r="M130" s="4" t="n">
         <f aca="false">J130/32</f>
         <v>8.75</v>
       </c>
-      <c r="N130" s="5" t="s">
+      <c r="N130" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="O130" s="24" t="n">
+      <c r="O130" s="22" t="n">
         <v>3</v>
       </c>
       <c r="P130" s="1" t="n">
@@ -6538,48 +6627,48 @@
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B131" s="22" t="s">
+      <c r="B131" s="20" t="s">
         <v>277</v>
       </c>
-      <c r="C131" s="22" t="s">
+      <c r="C131" s="20" t="s">
         <v>278</v>
       </c>
       <c r="D131" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E131" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F131" s="35"/>
-      <c r="G131" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H131" s="35" t="s">
+      <c r="E131" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F131" s="31"/>
+      <c r="G131" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I131" s="22" t="s">
+      <c r="I131" s="20" t="s">
         <v>277</v>
       </c>
       <c r="J131" s="4" t="n">
         <f aca="false">J130+D130</f>
         <v>288</v>
       </c>
-      <c r="K131" s="5" t="n">
+      <c r="K131" s="4" t="n">
         <f aca="false">J131/8</f>
         <v>36</v>
       </c>
-      <c r="L131" s="5" t="n">
+      <c r="L131" s="4" t="n">
         <f aca="false">J131/16</f>
         <v>18</v>
       </c>
-      <c r="M131" s="5" t="n">
+      <c r="M131" s="4" t="n">
         <f aca="false">J131/32</f>
         <v>9</v>
       </c>
-      <c r="N131" s="5" t="s">
+      <c r="N131" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="O131" s="24" t="n">
+      <c r="O131" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P131" s="1" t="n">
@@ -6590,48 +6679,48 @@
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B132" s="22" t="s">
+      <c r="B132" s="20" t="s">
         <v>279</v>
       </c>
-      <c r="C132" s="22" t="s">
+      <c r="C132" s="20" t="s">
         <v>280</v>
       </c>
       <c r="D132" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E132" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F132" s="35"/>
-      <c r="G132" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H132" s="35" t="s">
+      <c r="E132" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F132" s="31"/>
+      <c r="G132" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I132" s="22" t="s">
+      <c r="I132" s="20" t="s">
         <v>279</v>
       </c>
       <c r="J132" s="4" t="n">
         <f aca="false">J131+D131</f>
         <v>296</v>
       </c>
-      <c r="K132" s="5" t="n">
+      <c r="K132" s="4" t="n">
         <f aca="false">J132/8</f>
         <v>37</v>
       </c>
-      <c r="L132" s="5" t="n">
+      <c r="L132" s="4" t="n">
         <f aca="false">J132/16</f>
         <v>18.5</v>
       </c>
-      <c r="M132" s="5" t="n">
+      <c r="M132" s="4" t="n">
         <f aca="false">J132/32</f>
         <v>9.25</v>
       </c>
-      <c r="N132" s="5" t="s">
+      <c r="N132" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="O132" s="24" t="n">
+      <c r="O132" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P132" s="1" t="n">
@@ -6642,48 +6731,48 @@
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B133" s="22" t="s">
+      <c r="B133" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="C133" s="22" t="s">
+      <c r="C133" s="20" t="s">
         <v>282</v>
       </c>
       <c r="D133" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E133" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F133" s="35"/>
-      <c r="G133" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" s="35" t="s">
+      <c r="E133" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F133" s="31"/>
+      <c r="G133" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I133" s="22" t="s">
+      <c r="I133" s="20" t="s">
         <v>281</v>
       </c>
       <c r="J133" s="4" t="n">
         <f aca="false">J132+D132</f>
         <v>304</v>
       </c>
-      <c r="K133" s="5" t="n">
+      <c r="K133" s="4" t="n">
         <f aca="false">J133/8</f>
         <v>38</v>
       </c>
-      <c r="L133" s="5" t="n">
+      <c r="L133" s="4" t="n">
         <f aca="false">J133/16</f>
         <v>19</v>
       </c>
-      <c r="M133" s="5" t="n">
+      <c r="M133" s="4" t="n">
         <f aca="false">J133/32</f>
         <v>9.5</v>
       </c>
-      <c r="N133" s="5" t="s">
+      <c r="N133" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="O133" s="24" t="n">
+      <c r="O133" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P133" s="1" t="n">
@@ -6694,48 +6783,48 @@
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B134" s="22" t="s">
+      <c r="B134" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="C134" s="22" t="s">
+      <c r="C134" s="20" t="s">
         <v>284</v>
       </c>
       <c r="D134" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E134" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F134" s="35"/>
-      <c r="G134" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H134" s="35" t="s">
+      <c r="E134" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F134" s="31"/>
+      <c r="G134" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I134" s="22" t="s">
+      <c r="I134" s="20" t="s">
         <v>283</v>
       </c>
       <c r="J134" s="4" t="n">
         <f aca="false">J133+D133</f>
         <v>312</v>
       </c>
-      <c r="K134" s="5" t="n">
+      <c r="K134" s="4" t="n">
         <f aca="false">J134/8</f>
         <v>39</v>
       </c>
-      <c r="L134" s="5" t="n">
+      <c r="L134" s="4" t="n">
         <f aca="false">J134/16</f>
         <v>19.5</v>
       </c>
-      <c r="M134" s="5" t="n">
+      <c r="M134" s="4" t="n">
         <f aca="false">J134/32</f>
         <v>9.75</v>
       </c>
-      <c r="N134" s="5" t="s">
+      <c r="N134" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="O134" s="24" t="n">
+      <c r="O134" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P134" s="1" t="n">
@@ -6746,48 +6835,48 @@
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B135" s="22" t="s">
+      <c r="B135" s="20" t="s">
         <v>285</v>
       </c>
-      <c r="C135" s="22" t="s">
+      <c r="C135" s="20" t="s">
         <v>286</v>
       </c>
       <c r="D135" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E135" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F135" s="35"/>
-      <c r="G135" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" s="35" t="s">
+      <c r="E135" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F135" s="31"/>
+      <c r="G135" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I135" s="22" t="s">
+      <c r="I135" s="20" t="s">
         <v>285</v>
       </c>
       <c r="J135" s="4" t="n">
         <f aca="false">J134+D134</f>
         <v>320</v>
       </c>
-      <c r="K135" s="5" t="n">
+      <c r="K135" s="4" t="n">
         <f aca="false">J135/8</f>
         <v>40</v>
       </c>
-      <c r="L135" s="5" t="n">
+      <c r="L135" s="4" t="n">
         <f aca="false">J135/16</f>
         <v>20</v>
       </c>
-      <c r="M135" s="5" t="n">
+      <c r="M135" s="4" t="n">
         <f aca="false">J135/32</f>
         <v>10</v>
       </c>
-      <c r="N135" s="5" t="s">
+      <c r="N135" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="O135" s="24" t="n">
+      <c r="O135" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P135" s="1" t="n">
@@ -6798,48 +6887,48 @@
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B136" s="22" t="s">
+      <c r="B136" s="20" t="s">
         <v>287</v>
       </c>
-      <c r="C136" s="22" t="s">
+      <c r="C136" s="20" t="s">
         <v>288</v>
       </c>
       <c r="D136" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E136" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F136" s="35"/>
-      <c r="G136" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H136" s="35" t="s">
+      <c r="E136" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F136" s="31"/>
+      <c r="G136" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I136" s="22" t="s">
+      <c r="I136" s="20" t="s">
         <v>287</v>
       </c>
       <c r="J136" s="4" t="n">
         <f aca="false">J135+D135</f>
         <v>328</v>
       </c>
-      <c r="K136" s="5" t="n">
+      <c r="K136" s="4" t="n">
         <f aca="false">J136/8</f>
         <v>41</v>
       </c>
-      <c r="L136" s="5" t="n">
+      <c r="L136" s="4" t="n">
         <f aca="false">J136/16</f>
         <v>20.5</v>
       </c>
-      <c r="M136" s="5" t="n">
+      <c r="M136" s="4" t="n">
         <f aca="false">J136/32</f>
         <v>10.25</v>
       </c>
-      <c r="N136" s="5" t="s">
+      <c r="N136" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="O136" s="24" t="n">
+      <c r="O136" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P136" s="1" t="n">
@@ -6850,48 +6939,48 @@
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B137" s="22" t="s">
+      <c r="B137" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="C137" s="22" t="s">
+      <c r="C137" s="20" t="s">
         <v>290</v>
       </c>
       <c r="D137" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E137" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F137" s="35"/>
-      <c r="G137" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H137" s="35" t="s">
+      <c r="E137" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F137" s="31"/>
+      <c r="G137" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I137" s="22" t="s">
+      <c r="I137" s="20" t="s">
         <v>289</v>
       </c>
       <c r="J137" s="4" t="n">
         <f aca="false">J136+D136</f>
         <v>336</v>
       </c>
-      <c r="K137" s="5" t="n">
+      <c r="K137" s="4" t="n">
         <f aca="false">J137/8</f>
         <v>42</v>
       </c>
-      <c r="L137" s="5" t="n">
+      <c r="L137" s="4" t="n">
         <f aca="false">J137/16</f>
         <v>21</v>
       </c>
-      <c r="M137" s="5" t="n">
+      <c r="M137" s="4" t="n">
         <f aca="false">J137/32</f>
         <v>10.5</v>
       </c>
-      <c r="N137" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O137" s="24" t="n">
+      <c r="N137" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O137" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P137" s="1" t="n">
@@ -6902,48 +6991,48 @@
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B138" s="22" t="s">
+      <c r="B138" s="20" t="s">
         <v>291</v>
       </c>
-      <c r="C138" s="22" t="s">
+      <c r="C138" s="20" t="s">
         <v>292</v>
       </c>
       <c r="D138" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E138" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F138" s="35"/>
-      <c r="G138" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" s="35" t="s">
+      <c r="E138" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F138" s="31"/>
+      <c r="G138" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I138" s="22" t="s">
+      <c r="I138" s="20" t="s">
         <v>291</v>
       </c>
       <c r="J138" s="4" t="n">
         <f aca="false">J137+D137</f>
         <v>344</v>
       </c>
-      <c r="K138" s="5" t="n">
+      <c r="K138" s="4" t="n">
         <f aca="false">J138/8</f>
         <v>43</v>
       </c>
-      <c r="L138" s="5" t="n">
+      <c r="L138" s="4" t="n">
         <f aca="false">J138/16</f>
         <v>21.5</v>
       </c>
-      <c r="M138" s="5" t="n">
+      <c r="M138" s="4" t="n">
         <f aca="false">J138/32</f>
         <v>10.75</v>
       </c>
-      <c r="N138" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O138" s="24" t="n">
+      <c r="N138" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O138" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P138" s="1" t="n">
@@ -6954,48 +7043,48 @@
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B139" s="22" t="s">
+      <c r="B139" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="C139" s="22" t="s">
+      <c r="C139" s="20" t="s">
         <v>294</v>
       </c>
       <c r="D139" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E139" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F139" s="35"/>
-      <c r="G139" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H139" s="35" t="s">
+      <c r="E139" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F139" s="31"/>
+      <c r="G139" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I139" s="22" t="s">
+      <c r="I139" s="20" t="s">
         <v>293</v>
       </c>
       <c r="J139" s="4" t="n">
         <f aca="false">J138+D138</f>
         <v>352</v>
       </c>
-      <c r="K139" s="5" t="n">
+      <c r="K139" s="4" t="n">
         <f aca="false">J139/8</f>
         <v>44</v>
       </c>
-      <c r="L139" s="5" t="n">
+      <c r="L139" s="4" t="n">
         <f aca="false">J139/16</f>
         <v>22</v>
       </c>
-      <c r="M139" s="5" t="n">
+      <c r="M139" s="4" t="n">
         <f aca="false">J139/32</f>
         <v>11</v>
       </c>
-      <c r="N139" s="5" t="s">
+      <c r="N139" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="O139" s="24" t="n">
+      <c r="O139" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P139" s="1" t="n">
@@ -7006,48 +7095,48 @@
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B140" s="22" t="s">
+      <c r="B140" s="20" t="s">
         <v>295</v>
       </c>
-      <c r="C140" s="22" t="s">
+      <c r="C140" s="20" t="s">
         <v>296</v>
       </c>
       <c r="D140" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E140" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F140" s="35"/>
-      <c r="G140" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H140" s="35" t="s">
+      <c r="E140" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F140" s="31"/>
+      <c r="G140" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I140" s="22" t="s">
+      <c r="I140" s="20" t="s">
         <v>295</v>
       </c>
       <c r="J140" s="4" t="n">
         <f aca="false">J139+D139</f>
         <v>360</v>
       </c>
-      <c r="K140" s="5" t="n">
+      <c r="K140" s="4" t="n">
         <f aca="false">J140/8</f>
         <v>45</v>
       </c>
-      <c r="L140" s="5" t="n">
+      <c r="L140" s="4" t="n">
         <f aca="false">J140/16</f>
         <v>22.5</v>
       </c>
-      <c r="M140" s="5" t="n">
+      <c r="M140" s="4" t="n">
         <f aca="false">J140/32</f>
         <v>11.25</v>
       </c>
-      <c r="N140" s="5" t="s">
+      <c r="N140" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="O140" s="24" t="n">
+      <c r="O140" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P140" s="1" t="n">
@@ -7058,48 +7147,48 @@
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B141" s="22" t="s">
+      <c r="B141" s="20" t="s">
         <v>297</v>
       </c>
-      <c r="C141" s="22" t="s">
+      <c r="C141" s="20" t="s">
         <v>298</v>
       </c>
       <c r="D141" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E141" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F141" s="35"/>
-      <c r="G141" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H141" s="35" t="s">
+      <c r="E141" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F141" s="31"/>
+      <c r="G141" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I141" s="22" t="s">
+      <c r="I141" s="20" t="s">
         <v>297</v>
       </c>
       <c r="J141" s="4" t="n">
         <f aca="false">J140+D140</f>
         <v>368</v>
       </c>
-      <c r="K141" s="5" t="n">
+      <c r="K141" s="4" t="n">
         <f aca="false">J141/8</f>
         <v>46</v>
       </c>
-      <c r="L141" s="5" t="n">
+      <c r="L141" s="4" t="n">
         <f aca="false">J141/16</f>
         <v>23</v>
       </c>
-      <c r="M141" s="5" t="n">
+      <c r="M141" s="4" t="n">
         <f aca="false">J141/32</f>
         <v>11.5</v>
       </c>
-      <c r="N141" s="5" t="s">
+      <c r="N141" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="O141" s="24" t="n">
+      <c r="O141" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P141" s="1" t="n">
@@ -7110,48 +7199,48 @@
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B142" s="22" t="s">
+      <c r="B142" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="C142" s="22" t="s">
+      <c r="C142" s="20" t="s">
         <v>300</v>
       </c>
       <c r="D142" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E142" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F142" s="35"/>
-      <c r="G142" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H142" s="35" t="s">
+      <c r="E142" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F142" s="31"/>
+      <c r="G142" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I142" s="22" t="s">
+      <c r="I142" s="20" t="s">
         <v>299</v>
       </c>
       <c r="J142" s="4" t="n">
         <f aca="false">J141+D141</f>
         <v>376</v>
       </c>
-      <c r="K142" s="5" t="n">
+      <c r="K142" s="4" t="n">
         <f aca="false">J142/8</f>
         <v>47</v>
       </c>
-      <c r="L142" s="5" t="n">
+      <c r="L142" s="4" t="n">
         <f aca="false">J142/16</f>
         <v>23.5</v>
       </c>
-      <c r="M142" s="5" t="n">
+      <c r="M142" s="4" t="n">
         <f aca="false">J142/32</f>
         <v>11.75</v>
       </c>
-      <c r="N142" s="5" t="s">
+      <c r="N142" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="O142" s="24" t="n">
+      <c r="O142" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P142" s="1" t="n">
@@ -7162,48 +7251,48 @@
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B143" s="22" t="s">
+      <c r="B143" s="20" t="s">
         <v>301</v>
       </c>
-      <c r="C143" s="22" t="s">
+      <c r="C143" s="20" t="s">
         <v>302</v>
       </c>
       <c r="D143" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E143" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F143" s="35"/>
-      <c r="G143" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H143" s="35" t="s">
+      <c r="E143" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F143" s="31"/>
+      <c r="G143" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I143" s="22" t="s">
+      <c r="I143" s="20" t="s">
         <v>301</v>
       </c>
       <c r="J143" s="4" t="n">
         <f aca="false">J142+D142</f>
         <v>384</v>
       </c>
-      <c r="K143" s="5" t="n">
+      <c r="K143" s="4" t="n">
         <f aca="false">J143/8</f>
         <v>48</v>
       </c>
-      <c r="L143" s="5" t="n">
+      <c r="L143" s="4" t="n">
         <f aca="false">J143/16</f>
         <v>24</v>
       </c>
-      <c r="M143" s="5" t="n">
+      <c r="M143" s="4" t="n">
         <f aca="false">J143/32</f>
         <v>12</v>
       </c>
-      <c r="N143" s="5" t="s">
+      <c r="N143" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="O143" s="24" t="n">
+      <c r="O143" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P143" s="1" t="n">
@@ -7214,48 +7303,48 @@
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B144" s="22" t="s">
+      <c r="B144" s="20" t="s">
         <v>303</v>
       </c>
-      <c r="C144" s="22" t="s">
+      <c r="C144" s="20" t="s">
         <v>304</v>
       </c>
       <c r="D144" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E144" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F144" s="35"/>
-      <c r="G144" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H144" s="35" t="s">
+      <c r="E144" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F144" s="31"/>
+      <c r="G144" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I144" s="22" t="s">
+      <c r="I144" s="20" t="s">
         <v>303</v>
       </c>
       <c r="J144" s="4" t="n">
         <f aca="false">J143+D143</f>
         <v>392</v>
       </c>
-      <c r="K144" s="5" t="n">
+      <c r="K144" s="4" t="n">
         <f aca="false">J144/8</f>
         <v>49</v>
       </c>
-      <c r="L144" s="5" t="n">
+      <c r="L144" s="4" t="n">
         <f aca="false">J144/16</f>
         <v>24.5</v>
       </c>
-      <c r="M144" s="5" t="n">
+      <c r="M144" s="4" t="n">
         <f aca="false">J144/32</f>
         <v>12.25</v>
       </c>
-      <c r="N144" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O144" s="24" t="n">
+      <c r="N144" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O144" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P144" s="1" t="n">
@@ -7266,48 +7355,48 @@
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B145" s="22" t="s">
+      <c r="B145" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="C145" s="22" t="s">
+      <c r="C145" s="20" t="s">
         <v>306</v>
       </c>
       <c r="D145" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E145" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F145" s="35"/>
-      <c r="G145" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H145" s="35" t="s">
+      <c r="E145" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F145" s="31"/>
+      <c r="G145" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I145" s="22" t="s">
+      <c r="I145" s="20" t="s">
         <v>305</v>
       </c>
       <c r="J145" s="4" t="n">
         <f aca="false">J144+D144</f>
         <v>400</v>
       </c>
-      <c r="K145" s="5" t="n">
+      <c r="K145" s="4" t="n">
         <f aca="false">J145/8</f>
         <v>50</v>
       </c>
-      <c r="L145" s="5" t="n">
+      <c r="L145" s="4" t="n">
         <f aca="false">J145/16</f>
         <v>25</v>
       </c>
-      <c r="M145" s="5" t="n">
+      <c r="M145" s="4" t="n">
         <f aca="false">J145/32</f>
         <v>12.5</v>
       </c>
-      <c r="N145" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O145" s="24" t="n">
+      <c r="N145" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O145" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P145" s="1" t="n">
@@ -7318,48 +7407,48 @@
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B146" s="22" t="s">
+      <c r="B146" s="20" t="s">
         <v>307</v>
       </c>
-      <c r="C146" s="22" t="s">
+      <c r="C146" s="20" t="s">
         <v>308</v>
       </c>
       <c r="D146" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E146" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F146" s="35"/>
-      <c r="G146" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H146" s="35" t="s">
+      <c r="E146" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F146" s="31"/>
+      <c r="G146" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I146" s="22" t="s">
+      <c r="I146" s="20" t="s">
         <v>307</v>
       </c>
       <c r="J146" s="4" t="n">
         <f aca="false">J145+D145</f>
         <v>408</v>
       </c>
-      <c r="K146" s="5" t="n">
+      <c r="K146" s="4" t="n">
         <f aca="false">J146/8</f>
         <v>51</v>
       </c>
-      <c r="L146" s="5" t="n">
+      <c r="L146" s="4" t="n">
         <f aca="false">J146/16</f>
         <v>25.5</v>
       </c>
-      <c r="M146" s="5" t="n">
+      <c r="M146" s="4" t="n">
         <f aca="false">J146/32</f>
         <v>12.75</v>
       </c>
-      <c r="N146" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O146" s="24" t="n">
+      <c r="N146" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O146" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P146" s="1" t="n">
@@ -7379,16 +7468,16 @@
       <c r="D147" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="E147" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F147" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="G147" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H147" s="35" t="s">
+      <c r="E147" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F147" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="G147" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" s="31" t="s">
         <v>34</v>
       </c>
       <c r="I147" s="3" t="s">
@@ -7398,22 +7487,22 @@
         <f aca="false">J146+D146</f>
         <v>416</v>
       </c>
-      <c r="K147" s="5" t="n">
+      <c r="K147" s="4" t="n">
         <f aca="false">J147/8</f>
         <v>52</v>
       </c>
-      <c r="L147" s="5" t="n">
+      <c r="L147" s="4" t="n">
         <f aca="false">J147/16</f>
         <v>26</v>
       </c>
-      <c r="M147" s="5" t="n">
+      <c r="M147" s="4" t="n">
         <f aca="false">J147/32</f>
         <v>13</v>
       </c>
-      <c r="N147" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O147" s="24" t="n">
+      <c r="N147" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O147" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P147" s="1" t="n">
@@ -7424,48 +7513,48 @@
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B148" s="22" t="s">
+      <c r="B148" s="20" t="s">
         <v>311</v>
       </c>
-      <c r="C148" s="22" t="s">
+      <c r="C148" s="20" t="s">
         <v>312</v>
       </c>
       <c r="D148" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E148" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="F148" s="35"/>
-      <c r="G148" s="22" t="n">
+      <c r="E148" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F148" s="31"/>
+      <c r="G148" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="H148" s="35" t="s">
+      <c r="H148" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I148" s="22" t="s">
+      <c r="I148" s="20" t="s">
         <v>311</v>
       </c>
       <c r="J148" s="4" t="n">
         <f aca="false">J147+D147</f>
         <v>432</v>
       </c>
-      <c r="K148" s="5" t="n">
+      <c r="K148" s="4" t="n">
         <f aca="false">J148/8</f>
         <v>54</v>
       </c>
-      <c r="L148" s="5" t="n">
+      <c r="L148" s="4" t="n">
         <f aca="false">J148/16</f>
         <v>27</v>
       </c>
-      <c r="M148" s="5" t="n">
+      <c r="M148" s="4" t="n">
         <f aca="false">J148/32</f>
         <v>13.5</v>
       </c>
-      <c r="N148" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="O148" s="24" t="n">
+      <c r="N148" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="O148" s="22" t="n">
         <v>1</v>
       </c>
       <c r="P148" s="1" t="n">
@@ -7485,39 +7574,39 @@
       <c r="D149" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E149" s="35" t="s">
+      <c r="E149" s="31" t="s">
         <v>315</v>
       </c>
-      <c r="F149" s="35"/>
-      <c r="G149" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H149" s="35" t="s">
+      <c r="F149" s="31"/>
+      <c r="G149" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I149" s="35" t="s">
+      <c r="I149" s="31" t="s">
         <v>216</v>
       </c>
       <c r="J149" s="4" t="n">
         <f aca="false">J148+D148</f>
         <v>440</v>
       </c>
-      <c r="K149" s="5" t="n">
+      <c r="K149" s="4" t="n">
         <f aca="false">J149/8</f>
         <v>55</v>
       </c>
-      <c r="L149" s="5" t="n">
+      <c r="L149" s="4" t="n">
         <f aca="false">J149/16</f>
         <v>27.5</v>
       </c>
-      <c r="M149" s="5" t="n">
+      <c r="M149" s="4" t="n">
         <f aca="false">J149/32</f>
         <v>13.75</v>
       </c>
-      <c r="N149" s="5" t="s">
+      <c r="N149" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O149" s="24" t="n">
+      <c r="O149" s="22" t="n">
         <v>0</v>
       </c>
       <c r="P149" s="1" t="n">
@@ -7529,25 +7618,25 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F150" s="35"/>
-      <c r="G150" s="35"/>
-      <c r="H150" s="35"/>
-      <c r="I150" s="35"/>
+        <v>45</v>
+      </c>
+      <c r="F150" s="31"/>
+      <c r="G150" s="31"/>
+      <c r="H150" s="31"/>
+      <c r="I150" s="31"/>
       <c r="J150" s="4" t="n">
         <f aca="false">J149+D149</f>
         <v>448</v>
       </c>
-      <c r="K150" s="5" t="n">
+      <c r="K150" s="4" t="n">
         <f aca="false">J150/8</f>
         <v>56</v>
       </c>
-      <c r="L150" s="5" t="n">
+      <c r="L150" s="4" t="n">
         <f aca="false">J150/16</f>
         <v>28</v>
       </c>
-      <c r="M150" s="5" t="n">
+      <c r="M150" s="4" t="n">
         <f aca="false">J150/32</f>
         <v>14</v>
       </c>
@@ -7555,7 +7644,6 @@
     <row r="151" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C151" s="3"/>
       <c r="H151" s="3"/>
-      <c r="J151" s="42"/>
       <c r="O151" s="3"/>
     </row>
     <row r="1048303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -7855,403 +7943,403 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B6:I20"/>
-  <sheetFormatPr defaultColWidth="9.2890625" defaultRowHeight="13.2" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.2890625" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="38" width="20.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="38" width="16.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="38" width="13.66"/>
   </cols>
   <sheetData>
-    <row r="6" s="43" customFormat="true" ht="34.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="44"/>
-      <c r="C6" s="44" t="s">
+    <row r="6" s="39" customFormat="true" ht="34.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="40"/>
+      <c r="C6" s="40" t="s">
         <v>316</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="40" t="s">
         <v>317</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="40" t="s">
         <v>318</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="40" t="s">
         <v>319</v>
       </c>
-      <c r="G6" s="44" t="s">
+      <c r="G6" s="40" t="s">
         <v>320</v>
       </c>
-      <c r="H6" s="44" t="s">
+      <c r="H6" s="40" t="s">
         <v>321</v>
       </c>
-      <c r="I6" s="44"/>
+      <c r="I6" s="40"/>
     </row>
     <row r="7" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="45"/>
-      <c r="C7" s="45" t="n">
+      <c r="B7" s="41"/>
+      <c r="C7" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="45" t="n">
+      <c r="D7" s="41" t="n">
         <f aca="false">C7*64+8</f>
         <v>72</v>
       </c>
-      <c r="E7" s="45" t="n">
+      <c r="E7" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="45" t="n">
+      <c r="F7" s="41" t="n">
         <f aca="false">(D7+(E7*32))</f>
         <v>104</v>
       </c>
-      <c r="G7" s="45" t="n">
+      <c r="G7" s="41" t="n">
         <f aca="false">(D7+(E7*32))*10</f>
         <v>1040</v>
       </c>
-      <c r="H7" s="45" t="n">
+      <c r="H7" s="41" t="n">
         <f aca="false">G7/1200</f>
         <v>0.866666666666667</v>
       </c>
-      <c r="I7" s="45"/>
+      <c r="I7" s="41"/>
     </row>
     <row r="8" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="45"/>
-      <c r="C8" s="45" t="n">
+      <c r="B8" s="41"/>
+      <c r="C8" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="D8" s="45" t="n">
+      <c r="D8" s="41" t="n">
         <f aca="false">C8*64+8</f>
         <v>392</v>
       </c>
-      <c r="E8" s="45" t="n">
+      <c r="E8" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="45" t="n">
+      <c r="F8" s="41" t="n">
         <f aca="false">(D8+(E8*32))</f>
         <v>456</v>
       </c>
-      <c r="G8" s="45" t="n">
+      <c r="G8" s="41" t="n">
         <f aca="false">(D8+(E8*32))*10</f>
         <v>4560</v>
       </c>
-      <c r="H8" s="45" t="n">
+      <c r="H8" s="41" t="n">
         <f aca="false">G8/1200</f>
         <v>3.8</v>
       </c>
-      <c r="I8" s="45"/>
+      <c r="I8" s="41"/>
     </row>
     <row r="9" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="45"/>
-      <c r="C9" s="45" t="n">
+      <c r="B9" s="41"/>
+      <c r="C9" s="41" t="n">
         <v>7</v>
       </c>
-      <c r="D9" s="45" t="n">
+      <c r="D9" s="41" t="n">
         <f aca="false">C9*64+8</f>
         <v>456</v>
       </c>
-      <c r="E9" s="45" t="n">
+      <c r="E9" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="45" t="n">
+      <c r="F9" s="41" t="n">
         <f aca="false">(D9+(E9*32))</f>
         <v>552</v>
       </c>
-      <c r="G9" s="45" t="n">
+      <c r="G9" s="41" t="n">
         <f aca="false">(D9+(E9*32))*10</f>
         <v>5520</v>
       </c>
-      <c r="H9" s="45" t="n">
+      <c r="H9" s="41" t="n">
         <f aca="false">G9/1200</f>
         <v>4.6</v>
       </c>
-      <c r="I9" s="45"/>
+      <c r="I9" s="41"/>
     </row>
     <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="45"/>
-      <c r="C10" s="45" t="n">
+      <c r="B10" s="41"/>
+      <c r="C10" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="D10" s="45" t="n">
+      <c r="D10" s="41" t="n">
         <f aca="false">C10*64+8</f>
         <v>520</v>
       </c>
-      <c r="E10" s="45" t="n">
+      <c r="E10" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="45" t="n">
+      <c r="F10" s="41" t="n">
         <f aca="false">(D10+(E10*32))</f>
         <v>616</v>
       </c>
-      <c r="G10" s="45" t="n">
+      <c r="G10" s="41" t="n">
         <f aca="false">(D10+(E10*32))*10</f>
         <v>6160</v>
       </c>
-      <c r="H10" s="45" t="n">
+      <c r="H10" s="41" t="n">
         <f aca="false">G10/1200</f>
         <v>5.13333333333333</v>
       </c>
-      <c r="I10" s="45"/>
+      <c r="I10" s="41"/>
     </row>
     <row r="11" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="45"/>
-      <c r="C11" s="45" t="n">
+      <c r="B11" s="41"/>
+      <c r="C11" s="41" t="n">
         <v>9</v>
       </c>
-      <c r="D11" s="45" t="n">
+      <c r="D11" s="41" t="n">
         <f aca="false">C11*64+8</f>
         <v>584</v>
       </c>
-      <c r="E11" s="45" t="n">
+      <c r="E11" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="45" t="n">
+      <c r="F11" s="41" t="n">
         <f aca="false">(D11+(E11*32))</f>
         <v>680</v>
       </c>
-      <c r="G11" s="45" t="n">
+      <c r="G11" s="41" t="n">
         <f aca="false">(D11+(E11*32))*10</f>
         <v>6800</v>
       </c>
-      <c r="H11" s="45" t="n">
+      <c r="H11" s="41" t="n">
         <f aca="false">G11/1200</f>
         <v>5.66666666666667</v>
       </c>
-      <c r="I11" s="45"/>
+      <c r="I11" s="41"/>
     </row>
     <row r="12" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="45"/>
-      <c r="C12" s="45" t="n">
+      <c r="B12" s="41"/>
+      <c r="C12" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="D12" s="45" t="n">
+      <c r="D12" s="41" t="n">
         <f aca="false">C12*64+8</f>
         <v>648</v>
       </c>
-      <c r="E12" s="45" t="n">
+      <c r="E12" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="45" t="n">
+      <c r="F12" s="41" t="n">
         <f aca="false">(D12+(E12*32))</f>
         <v>744</v>
       </c>
-      <c r="G12" s="45" t="n">
+      <c r="G12" s="41" t="n">
         <f aca="false">(D12+(E12*32))*10</f>
         <v>7440</v>
       </c>
-      <c r="H12" s="45" t="n">
+      <c r="H12" s="41" t="n">
         <f aca="false">G12/1200</f>
         <v>6.2</v>
       </c>
-      <c r="I12" s="45"/>
+      <c r="I12" s="41"/>
     </row>
     <row r="13" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="45"/>
-      <c r="C13" s="45" t="n">
+      <c r="B13" s="41"/>
+      <c r="C13" s="41" t="n">
         <v>11</v>
       </c>
-      <c r="D13" s="45" t="n">
+      <c r="D13" s="41" t="n">
         <f aca="false">C13*64+8</f>
         <v>712</v>
       </c>
-      <c r="E13" s="45" t="n">
+      <c r="E13" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="F13" s="45" t="n">
+      <c r="F13" s="41" t="n">
         <f aca="false">(D13+(E13*32))</f>
         <v>840</v>
       </c>
-      <c r="G13" s="45" t="n">
+      <c r="G13" s="41" t="n">
         <f aca="false">(D13+(E13*32))*10</f>
         <v>8400</v>
       </c>
-      <c r="H13" s="45" t="n">
+      <c r="H13" s="41" t="n">
         <f aca="false">G13/1200</f>
         <v>7</v>
       </c>
-      <c r="I13" s="45"/>
+      <c r="I13" s="41"/>
     </row>
     <row r="14" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="45"/>
-      <c r="C14" s="45" t="n">
+      <c r="B14" s="41"/>
+      <c r="C14" s="41" t="n">
         <v>12</v>
       </c>
-      <c r="D14" s="45" t="n">
+      <c r="D14" s="41" t="n">
         <f aca="false">C14*64+8</f>
         <v>776</v>
       </c>
-      <c r="E14" s="45" t="n">
+      <c r="E14" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="F14" s="45" t="n">
+      <c r="F14" s="41" t="n">
         <f aca="false">(D14+(E14*32))</f>
         <v>904</v>
       </c>
-      <c r="G14" s="45" t="n">
+      <c r="G14" s="41" t="n">
         <f aca="false">(D14+(E14*32))*10</f>
         <v>9040</v>
       </c>
-      <c r="H14" s="45" t="n">
+      <c r="H14" s="41" t="n">
         <f aca="false">G14/1200</f>
         <v>7.53333333333333</v>
       </c>
-      <c r="I14" s="45"/>
+      <c r="I14" s="41"/>
     </row>
     <row r="15" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="45"/>
-      <c r="C15" s="45" t="n">
+      <c r="B15" s="41"/>
+      <c r="C15" s="41" t="n">
         <v>13</v>
       </c>
-      <c r="D15" s="45" t="n">
+      <c r="D15" s="41" t="n">
         <f aca="false">C15*64+8</f>
         <v>840</v>
       </c>
-      <c r="E15" s="45" t="n">
+      <c r="E15" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="F15" s="45" t="n">
+      <c r="F15" s="41" t="n">
         <f aca="false">(D15+(E15*32))</f>
         <v>968</v>
       </c>
-      <c r="G15" s="45" t="n">
+      <c r="G15" s="41" t="n">
         <f aca="false">(D15+(E15*32))*10</f>
         <v>9680</v>
       </c>
-      <c r="H15" s="45" t="n">
+      <c r="H15" s="41" t="n">
         <f aca="false">G15/1200</f>
         <v>8.06666666666667</v>
       </c>
-      <c r="I15" s="45"/>
+      <c r="I15" s="41"/>
     </row>
     <row r="16" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="45"/>
-      <c r="C16" s="45" t="n">
+      <c r="B16" s="41"/>
+      <c r="C16" s="41" t="n">
         <v>14</v>
       </c>
-      <c r="D16" s="45" t="n">
+      <c r="D16" s="41" t="n">
         <f aca="false">C16*64+8</f>
         <v>904</v>
       </c>
-      <c r="E16" s="45" t="n">
+      <c r="E16" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="F16" s="45" t="n">
+      <c r="F16" s="41" t="n">
         <f aca="false">(D16+(E16*32))</f>
         <v>1064</v>
       </c>
-      <c r="G16" s="45" t="n">
+      <c r="G16" s="41" t="n">
         <f aca="false">(D16+(E16*32))*10</f>
         <v>10640</v>
       </c>
-      <c r="H16" s="45" t="n">
+      <c r="H16" s="41" t="n">
         <f aca="false">G16/1200</f>
         <v>8.86666666666667</v>
       </c>
-      <c r="I16" s="45"/>
+      <c r="I16" s="41"/>
     </row>
     <row r="17" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="45"/>
-      <c r="C17" s="45" t="n">
+      <c r="B17" s="41"/>
+      <c r="C17" s="41" t="n">
         <v>15</v>
       </c>
-      <c r="D17" s="45" t="n">
+      <c r="D17" s="41" t="n">
         <f aca="false">C17*64+8</f>
         <v>968</v>
       </c>
-      <c r="E17" s="45" t="n">
+      <c r="E17" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="F17" s="45" t="n">
+      <c r="F17" s="41" t="n">
         <f aca="false">(D17+(E17*32))</f>
         <v>1128</v>
       </c>
-      <c r="G17" s="45" t="n">
+      <c r="G17" s="41" t="n">
         <f aca="false">(D17+(E17*32))*10</f>
         <v>11280</v>
       </c>
-      <c r="H17" s="45" t="n">
+      <c r="H17" s="41" t="n">
         <f aca="false">G17/1200</f>
         <v>9.4</v>
       </c>
-      <c r="I17" s="45"/>
+      <c r="I17" s="41"/>
     </row>
     <row r="18" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="45"/>
-      <c r="C18" s="45" t="n">
+      <c r="B18" s="41"/>
+      <c r="C18" s="41" t="n">
         <v>16</v>
       </c>
-      <c r="D18" s="45" t="n">
+      <c r="D18" s="41" t="n">
         <f aca="false">C18*64+8</f>
         <v>1032</v>
       </c>
-      <c r="E18" s="45" t="n">
+      <c r="E18" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="F18" s="45" t="n">
+      <c r="F18" s="41" t="n">
         <f aca="false">(D18+(E18*32))</f>
         <v>1192</v>
       </c>
-      <c r="G18" s="45" t="n">
+      <c r="G18" s="41" t="n">
         <f aca="false">(D18+(E18*32))*10</f>
         <v>11920</v>
       </c>
-      <c r="H18" s="45" t="n">
+      <c r="H18" s="41" t="n">
         <f aca="false">G18/1200</f>
         <v>9.93333333333333</v>
       </c>
-      <c r="I18" s="45"/>
+      <c r="I18" s="41"/>
     </row>
     <row r="19" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="45"/>
-      <c r="C19" s="45" t="n">
+      <c r="B19" s="41"/>
+      <c r="C19" s="41" t="n">
         <v>17</v>
       </c>
-      <c r="D19" s="45" t="n">
+      <c r="D19" s="41" t="n">
         <f aca="false">C19*64+8</f>
         <v>1096</v>
       </c>
-      <c r="E19" s="45" t="n">
+      <c r="E19" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="F19" s="45" t="n">
+      <c r="F19" s="41" t="n">
         <f aca="false">(D19+(E19*32))</f>
         <v>1256</v>
       </c>
-      <c r="G19" s="45" t="n">
+      <c r="G19" s="41" t="n">
         <f aca="false">(D19+(E19*32))*10</f>
         <v>12560</v>
       </c>
-      <c r="H19" s="45" t="n">
+      <c r="H19" s="41" t="n">
         <f aca="false">G19/1200</f>
         <v>10.4666666666667</v>
       </c>
-      <c r="I19" s="45"/>
+      <c r="I19" s="41"/>
     </row>
     <row r="20" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="45"/>
-      <c r="C20" s="45" t="n">
+      <c r="B20" s="41"/>
+      <c r="C20" s="41" t="n">
         <v>18</v>
       </c>
-      <c r="D20" s="45" t="n">
+      <c r="D20" s="41" t="n">
         <f aca="false">C20*64+8</f>
         <v>1160</v>
       </c>
-      <c r="E20" s="45" t="n">
+      <c r="E20" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="F20" s="45" t="n">
+      <c r="F20" s="41" t="n">
         <f aca="false">(D20+(E20*32))</f>
         <v>1352</v>
       </c>
-      <c r="G20" s="45" t="n">
+      <c r="G20" s="41" t="n">
         <f aca="false">(D20+(E20*32))*10</f>
         <v>13520</v>
       </c>
-      <c r="H20" s="45" t="n">
+      <c r="H20" s="41" t="n">
         <f aca="false">G20/1200</f>
         <v>11.2666666666667</v>
       </c>
-      <c r="I20" s="45"/>
+      <c r="I20" s="41"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/TelemDefinition/DownlinkSpecPacsat.xlsx
+++ b/TelemDefinition/DownlinkSpecPacsat.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -8,8 +8,8 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="DownlinkSpecPacsat" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="DownlinkSpecPacsat" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="320">
   <si>
     <t xml:space="preserve">//</t>
   </si>
@@ -224,10 +224,7 @@
     <t xml:space="preserve">TX RF Power</t>
   </si>
   <si>
-    <t xml:space="preserve">Radio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tx Mode</t>
+    <t xml:space="preserve">Transmitter</t>
   </si>
   <si>
     <t xml:space="preserve">TXPwrMode</t>
@@ -236,7 +233,13 @@
     <t xml:space="preserve">TX Power Mode</t>
   </si>
   <si>
-    <t xml:space="preserve">Rx0 Mode</t>
+    <t xml:space="preserve">Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TxMode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The modulation mode of the TX</t>
   </si>
   <si>
     <t xml:space="preserve">RX0PwrMode</t>
@@ -245,7 +248,7 @@
     <t xml:space="preserve">RX0 Power Mode</t>
   </si>
   <si>
-    <t xml:space="preserve">Rx1 Mode</t>
+    <t xml:space="preserve">Receiver 1</t>
   </si>
   <si>
     <t xml:space="preserve">RX1PwrMode</t>
@@ -254,7 +257,7 @@
     <t xml:space="preserve">RX1Power Mode</t>
   </si>
   <si>
-    <t xml:space="preserve">Rx2 Mode</t>
+    <t xml:space="preserve">Receiver 2</t>
   </si>
   <si>
     <t xml:space="preserve">RX2PwrMode</t>
@@ -263,7 +266,7 @@
     <t xml:space="preserve">RX2 Power Mode</t>
   </si>
   <si>
-    <t xml:space="preserve">Rx3 Mode</t>
+    <t xml:space="preserve">Receiver 3</t>
   </si>
   <si>
     <t xml:space="preserve">RX3PwrMode</t>
@@ -272,7 +275,7 @@
     <t xml:space="preserve">RX3 Power Mode</t>
   </si>
   <si>
-    <t xml:space="preserve">Rx0 RSSI</t>
+    <t xml:space="preserve">Receiver 4</t>
   </si>
   <si>
     <t xml:space="preserve">RX0RSSI</t>
@@ -284,27 +287,18 @@
     <t xml:space="preserve">RSSI for Receiver 0</t>
   </si>
   <si>
-    <t xml:space="preserve">Rx1 RSSI</t>
-  </si>
-  <si>
     <t xml:space="preserve">RX1RSSI</t>
   </si>
   <si>
     <t xml:space="preserve">RSSI for Receiver 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Rx2 RSSI</t>
-  </si>
-  <si>
     <t xml:space="preserve">RX2RSSI</t>
   </si>
   <si>
     <t xml:space="preserve">RSSI for receiver 2</t>
   </si>
   <si>
-    <t xml:space="preserve">Rx3 RSSI</t>
-  </si>
-  <si>
     <t xml:space="preserve">RX3RSSI</t>
   </si>
   <si>
@@ -431,133 +425,133 @@
     <t xml:space="preserve">TimePeriod</t>
   </si>
   <si>
+    <t xml:space="preserve">min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The period between time packets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telem Period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TelemPeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The period between telemetry packets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WOD Period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WodPeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The time between WOD saves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max WOD Size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxWodFileSize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The maximum size of a WOD file before it is added to the directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max EXP Size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxExpFileSize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The maximum size of a experiment file before it is added to the directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PB Status Period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PbStatusPeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The period between Pacsat Broadcast Status packets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PB Timeout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PbTimeout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The maximum time a client can be on the PB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uplink Status Period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UplinkStatusPeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The period between uplink status packets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SW Cmd Cnt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">swCmdCnt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of software commands since last reset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min/Max Resets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLMresets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of times command stations reset stored telemetry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cmd Ring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">swCmds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Command Ring showing last 4 commands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRAM Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRAMstatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status of the MRAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Length</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structure: realtimeSpecific_t, file:realtimeDownlink.h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pad5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structure: maxSpecific_t, file: maxDownlink.h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Last Chg Secs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maxTimestampUptime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unsigned</t>
+  </si>
+  <si>
     <t xml:space="preserve">s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The period between time packets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Telem Period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TelemPeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The period between telemetry packets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WOD Period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WodPeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The time between WOD saves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max WOD Size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxWodFileSize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bytes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The maximum size of a WOD file before it is added to the directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max EXP Size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxExpFileSize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The maximum size of a experiment file before it is added to the directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PB Status Period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PbStatusPeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The period between Pacsat Broadcast Status packets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PB Timeout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PbTimeout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The maximum time a client can be on the PB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uplink Status Period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UplinkStatusPeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The period between uplink status packets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SW Cmd Cnt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">swCmdCnt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of software commands since last reset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Min/Max Resets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLMresets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of times command stations reset stored telemetry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cmd Ring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">swCmds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Command Ring showing last 4 commands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRAM Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRAMstatus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status of the MRAM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Length</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Structure: realtimeSpecific_t, file:realtimeDownlink.h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pad5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Structure: maxSpecific_t, file: maxDownlink.h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Last Chg Secs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">maxTimestampUptime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unsigned</t>
   </si>
   <si>
     <t xml:space="preserve">Timestamp Resets</t>
@@ -1306,119 +1300,13 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
-  <a:themeElements>
-    <a:clrScheme name="LibreOffice">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="ffffff"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="18a303"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="0369a3"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="a33e03"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8e03a3"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="c99c00"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="c9211e"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000ee"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="551a8b"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q1048576"/>
-  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="53.01"/>
@@ -2049,7 +1937,7 @@
         <v>52</v>
       </c>
       <c r="O21" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P21" s="1" t="n">
         <v>1</v>
@@ -2101,7 +1989,7 @@
         <v>52</v>
       </c>
       <c r="O22" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P22" s="1" t="n">
         <v>2</v>
@@ -2118,7 +2006,7 @@
         <v>57</v>
       </c>
       <c r="D23" s="26" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E23" s="21" t="s">
         <v>25</v>
@@ -2153,7 +2041,7 @@
         <v>52</v>
       </c>
       <c r="O23" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P23" s="1" t="n">
         <v>3</v>
@@ -2187,25 +2075,25 @@
       </c>
       <c r="J24" s="4" t="n">
         <f aca="false">J23+D23</f>
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="K24" s="4" t="n">
         <f aca="false">J24/8</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L24" s="4" t="n">
         <f aca="false">J24/16</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="M24" s="4" t="n">
         <f aca="false">J24/32</f>
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="N24" s="4" t="s">
         <v>52</v>
       </c>
       <c r="O24" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P24" s="1" t="n">
         <v>4</v>
@@ -2239,28 +2127,28 @@
       </c>
       <c r="J25" s="4" t="n">
         <f aca="false">J24+D24</f>
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="K25" s="4" t="n">
         <f aca="false">J25/8</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L25" s="4" t="n">
         <f aca="false">J25/16</f>
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="M25" s="4" t="n">
         <f aca="false">J25/32</f>
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="N25" s="4" t="s">
         <v>67</v>
       </c>
       <c r="O25" s="22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q25" s="1" t="n">
         <v>0</v>
@@ -2271,7 +2159,7 @@
         <v>68</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D26" s="26" t="n">
         <v>8</v>
@@ -2287,29 +2175,29 @@
         <v>34</v>
       </c>
       <c r="I26" s="21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J26" s="4" t="n">
         <f aca="false">J25+D25</f>
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="K26" s="4" t="n">
         <f aca="false">J26/8</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L26" s="4" t="n">
         <f aca="false">J26/16</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="M26" s="4" t="n">
         <f aca="false">J26/32</f>
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="N26" s="4" t="s">
         <v>67</v>
       </c>
       <c r="O26" s="22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P26" s="1" t="n">
         <v>1</v>
@@ -2320,48 +2208,48 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="C27" s="26" t="s">
-        <v>72</v>
-      </c>
       <c r="D27" s="26" t="n">
         <v>8</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="F27" s="21"/>
       <c r="G27" s="20" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H27" s="20" t="s">
         <v>34</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J27" s="4" t="n">
         <f aca="false">J26+D26</f>
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K27" s="4" t="n">
         <f aca="false">J27/8</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L27" s="4" t="n">
         <f aca="false">J27/16</f>
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="M27" s="4" t="n">
         <f aca="false">J27/32</f>
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="N27" s="4" t="s">
         <v>67</v>
       </c>
       <c r="O27" s="22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P27" s="1" t="n">
         <v>3</v>
@@ -2372,10 +2260,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D28" s="26" t="n">
         <v>8</v>
@@ -2391,32 +2279,32 @@
         <v>34</v>
       </c>
       <c r="I28" s="21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J28" s="4" t="n">
         <f aca="false">J27+D27</f>
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="K28" s="4" t="n">
         <f aca="false">J28/8</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L28" s="4" t="n">
         <f aca="false">J28/16</f>
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="M28" s="4" t="n">
         <f aca="false">J28/32</f>
+        <v>2.75</v>
+      </c>
+      <c r="N28" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="O28" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="P28" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="N28" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="O28" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="P28" s="1" t="n">
-        <v>4</v>
       </c>
       <c r="Q28" s="1" t="n">
         <v>0</v>
@@ -2424,10 +2312,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D29" s="26" t="n">
         <v>8</v>
@@ -2443,32 +2331,32 @@
         <v>34</v>
       </c>
       <c r="I29" s="21" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J29" s="4" t="n">
         <f aca="false">J28+D28</f>
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="K29" s="4" t="n">
         <f aca="false">J29/8</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L29" s="4" t="n">
         <f aca="false">J29/16</f>
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="M29" s="4" t="n">
         <f aca="false">J29/32</f>
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="O29" s="22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q29" s="1" t="n">
         <v>0</v>
@@ -2476,10 +2364,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D30" s="26" t="n">
         <v>8</v>
@@ -2495,32 +2383,32 @@
         <v>34</v>
       </c>
       <c r="I30" s="21" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J30" s="4" t="n">
         <f aca="false">J29+D29</f>
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="K30" s="4" t="n">
         <f aca="false">J30/8</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L30" s="4" t="n">
         <f aca="false">J30/16</f>
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="M30" s="4" t="n">
         <f aca="false">J30/32</f>
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N30" s="4" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="O30" s="22" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q30" s="1" t="n">
         <v>0</v>
@@ -2528,10 +2416,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D31" s="26" t="n">
         <v>8</v>
@@ -2541,38 +2429,38 @@
       </c>
       <c r="F31" s="21"/>
       <c r="G31" s="20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="I31" s="21" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J31" s="4" t="n">
         <f aca="false">J30+D30</f>
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="K31" s="4" t="n">
         <f aca="false">J31/8</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L31" s="4" t="n">
         <f aca="false">J31/16</f>
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="M31" s="4" t="n">
         <f aca="false">J31/32</f>
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N31" s="4" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="O31" s="22" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q31" s="1" t="n">
         <v>0</v>
@@ -2580,10 +2468,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C32" s="26" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D32" s="26" t="n">
         <v>8</v>
@@ -2596,35 +2484,35 @@
         <v>6</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I32" s="21" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J32" s="4" t="n">
         <f aca="false">J31+D31</f>
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="K32" s="4" t="n">
         <f aca="false">J32/8</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L32" s="4" t="n">
         <f aca="false">J32/16</f>
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="M32" s="4" t="n">
         <f aca="false">J32/32</f>
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="O32" s="22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q32" s="1" t="n">
         <v>0</v>
@@ -2632,10 +2520,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D33" s="26" t="n">
         <v>8</v>
@@ -2648,35 +2536,35 @@
         <v>6</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I33" s="21" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="J33" s="4" t="n">
         <f aca="false">J32+D32</f>
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="K33" s="4" t="n">
         <f aca="false">J33/8</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L33" s="4" t="n">
         <f aca="false">J33/16</f>
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="M33" s="4" t="n">
         <f aca="false">J33/32</f>
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="N33" s="4" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="O33" s="22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q33" s="1" t="n">
         <v>0</v>
@@ -2684,10 +2572,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="26" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D34" s="26" t="n">
         <v>8</v>
@@ -2700,35 +2588,35 @@
         <v>6</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I34" s="21" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J34" s="4" t="n">
         <f aca="false">J33+D33</f>
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="K34" s="4" t="n">
         <f aca="false">J34/8</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L34" s="4" t="n">
         <f aca="false">J34/16</f>
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="M34" s="4" t="n">
         <f aca="false">J34/32</f>
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="N34" s="4" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="O34" s="22" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q34" s="1" t="n">
         <v>0</v>
@@ -2736,10 +2624,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D35" s="26" t="n">
         <v>8</v>
@@ -2749,38 +2637,38 @@
       </c>
       <c r="F35" s="21"/>
       <c r="G35" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>98</v>
+        <v>6</v>
+      </c>
+      <c r="H35" s="20" t="s">
+        <v>86</v>
       </c>
       <c r="I35" s="21" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="J35" s="4" t="n">
         <f aca="false">J34+D34</f>
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="K35" s="4" t="n">
         <f aca="false">J35/8</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L35" s="4" t="n">
         <f aca="false">J35/16</f>
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="M35" s="4" t="n">
         <f aca="false">J35/32</f>
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="N35" s="4" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="O35" s="22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q35" s="1" t="n">
         <v>0</v>
@@ -2788,10 +2676,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="26" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D36" s="26" t="n">
         <v>8</v>
@@ -2804,35 +2692,35 @@
         <v>9</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I36" s="21" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="J36" s="4" t="n">
         <f aca="false">J35+D35</f>
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="K36" s="4" t="n">
         <f aca="false">J36/8</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L36" s="4" t="n">
         <f aca="false">J36/16</f>
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="M36" s="4" t="n">
         <f aca="false">J36/32</f>
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="N36" s="4" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="O36" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q36" s="1" t="n">
         <v>0</v>
@@ -2840,10 +2728,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="26" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D37" s="26" t="n">
         <v>8</v>
@@ -2856,72 +2744,96 @@
         <v>9</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I37" s="21" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="J37" s="4" t="n">
         <f aca="false">J36+D36</f>
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="K37" s="4" t="n">
         <f aca="false">J37/8</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L37" s="4" t="n">
         <f aca="false">J37/16</f>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="M37" s="4" t="n">
         <f aca="false">J37/32</f>
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="N37" s="4" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="O37" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q37" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="26"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="26"/>
-      <c r="E38" s="21"/>
+      <c r="B38" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="C38" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="D38" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>25</v>
+      </c>
       <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
-      <c r="H38" s="21"/>
+      <c r="G38" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="I38" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="J38" s="4" t="n">
         <f aca="false">J37+D37</f>
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="K38" s="4" t="n">
         <f aca="false">J38/8</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L38" s="4" t="n">
         <f aca="false">J38/16</f>
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="M38" s="4" t="n">
         <f aca="false">J38/32</f>
-        <v>5.5</v>
+        <v>5.25</v>
+      </c>
+      <c r="N38" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="O38" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P38" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q38" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="B39" s="26"/>
       <c r="C39" s="26"/>
       <c r="D39" s="26"/>
@@ -2929,47 +2841,58 @@
       <c r="F39" s="21"/>
       <c r="G39" s="21"/>
       <c r="H39" s="21"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="25"/>
-      <c r="K39" s="25"/>
-      <c r="L39" s="25"/>
-      <c r="M39" s="25"/>
-    </row>
-    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I39" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="J39" s="4" t="n">
+        <f aca="false">J38+D38</f>
+        <v>176</v>
+      </c>
+      <c r="K39" s="4" t="n">
+        <f aca="false">J39/8</f>
+        <v>22</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <f aca="false">J39/16</f>
+        <v>11</v>
+      </c>
+      <c r="M39" s="4" t="n">
+        <f aca="false">J39/32</f>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="26"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="25"/>
+      <c r="K40" s="25"/>
+      <c r="L40" s="25"/>
+      <c r="M40" s="25"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B41" s="26"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="25"/>
-      <c r="K41" s="25"/>
-      <c r="L41" s="25"/>
-      <c r="M41" s="25"/>
+        <v>0</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B42" s="26"/>
       <c r="C42" s="26"/>
@@ -2985,62 +2908,28 @@
       <c r="M42" s="25"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="C43" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="D43" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="21" t="s">
-        <v>25</v>
-      </c>
+      <c r="A43" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="21"/>
       <c r="F43" s="21"/>
-      <c r="G43" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="I43" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="J43" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="25" t="n">
-        <f aca="false">J43/8</f>
-        <v>0</v>
-      </c>
-      <c r="L43" s="25" t="n">
-        <f aca="false">J43/16</f>
-        <v>0</v>
-      </c>
-      <c r="M43" s="25" t="n">
-        <f aca="false">J43/32</f>
-        <v>0</v>
-      </c>
-      <c r="N43" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="O43" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="P43" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q43" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="25"/>
+      <c r="K43" s="25"/>
+      <c r="L43" s="25"/>
+      <c r="M43" s="25"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="26" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D44" s="26" t="n">
         <v>1</v>
@@ -3056,32 +2945,31 @@
         <v>34</v>
       </c>
       <c r="I44" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="J44" s="4" t="n">
-        <f aca="false">J43+D43</f>
-        <v>1</v>
-      </c>
-      <c r="K44" s="4" t="n">
+        <v>111</v>
+      </c>
+      <c r="J44" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="25" t="n">
         <f aca="false">J44/8</f>
-        <v>0.125</v>
-      </c>
-      <c r="L44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="25" t="n">
         <f aca="false">J44/16</f>
-        <v>0.0625</v>
-      </c>
-      <c r="M44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="25" t="n">
         <f aca="false">J44/32</f>
-        <v>0.03125</v>
+        <v>0</v>
       </c>
       <c r="N44" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O44" s="22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q44" s="1" t="n">
         <v>0</v>
@@ -3089,10 +2977,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="26" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D45" s="26" t="n">
         <v>1</v>
@@ -3108,32 +2996,32 @@
         <v>34</v>
       </c>
       <c r="I45" s="21" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J45" s="4" t="n">
         <f aca="false">J44+D44</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K45" s="4" t="n">
         <f aca="false">J45/8</f>
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="L45" s="4" t="n">
         <f aca="false">J45/16</f>
-        <v>0.125</v>
+        <v>0.0625</v>
       </c>
       <c r="M45" s="4" t="n">
         <f aca="false">J45/32</f>
-        <v>0.0625</v>
+        <v>0.03125</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="O45" s="22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q45" s="1" t="n">
         <v>0</v>
@@ -3141,10 +3029,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="26" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D46" s="26" t="n">
         <v>1</v>
@@ -3160,32 +3048,32 @@
         <v>34</v>
       </c>
       <c r="I46" s="21" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="J46" s="4" t="n">
         <f aca="false">J45+D45</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K46" s="4" t="n">
         <f aca="false">J46/8</f>
-        <v>0.375</v>
+        <v>0.25</v>
       </c>
       <c r="L46" s="4" t="n">
         <f aca="false">J46/16</f>
-        <v>0.1875</v>
+        <v>0.125</v>
       </c>
       <c r="M46" s="4" t="n">
         <f aca="false">J46/32</f>
-        <v>0.09375</v>
+        <v>0.0625</v>
       </c>
       <c r="N46" s="4" t="s">
         <v>52</v>
       </c>
       <c r="O46" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q46" s="1" t="n">
         <v>0</v>
@@ -3193,10 +3081,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="26" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D47" s="26" t="n">
         <v>1</v>
@@ -3212,107 +3100,144 @@
         <v>34</v>
       </c>
       <c r="I47" s="21" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="J47" s="4" t="n">
         <f aca="false">J46+D46</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K47" s="4" t="n">
         <f aca="false">J47/8</f>
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="L47" s="4" t="n">
         <f aca="false">J47/16</f>
-        <v>0.25</v>
+        <v>0.1875</v>
       </c>
       <c r="M47" s="4" t="n">
         <f aca="false">J47/32</f>
-        <v>0.125</v>
+        <v>0.09375</v>
       </c>
       <c r="N47" s="4" t="s">
         <v>52</v>
       </c>
       <c r="O47" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q47" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="C48" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="D48" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F48" s="20"/>
+      <c r="B48" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="C48" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="D48" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="21"/>
       <c r="G48" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="20" t="s">
         <v>34</v>
       </c>
       <c r="I48" s="21" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="J48" s="4" t="n">
         <f aca="false">J47+D47</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K48" s="4" t="n">
         <f aca="false">J48/8</f>
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="L48" s="4" t="n">
         <f aca="false">J48/16</f>
-        <v>0.3125</v>
+        <v>0.25</v>
       </c>
       <c r="M48" s="4" t="n">
         <f aca="false">J48/32</f>
+        <v>0.125</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O48" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P48" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q48" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="D49" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F49" s="20"/>
+      <c r="G49" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I49" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="J49" s="4" t="n">
+        <f aca="false">J48+D48</f>
+        <v>5</v>
+      </c>
+      <c r="K49" s="4" t="n">
+        <f aca="false">J49/8</f>
+        <v>0.625</v>
+      </c>
+      <c r="L49" s="4" t="n">
+        <f aca="false">J49/16</f>
+        <v>0.3125</v>
+      </c>
+      <c r="M49" s="4" t="n">
+        <f aca="false">J49/32</f>
         <v>0.15625</v>
       </c>
-      <c r="N48" s="4" t="s">
+      <c r="N49" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O48" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B49" s="20"/>
-      <c r="C49" s="20"/>
-      <c r="D49" s="20"/>
-      <c r="E49" s="20"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="20"/>
-      <c r="H49" s="20"/>
-      <c r="I49" s="21"/>
-      <c r="N49" s="4"/>
-      <c r="O49" s="22"/>
+      <c r="O49" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B50" s="20"/>
       <c r="C50" s="20"/>
@@ -3326,104 +3251,67 @@
       <c r="O50" s="22"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="C51" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="D51" s="20" t="n">
+      <c r="A51" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B51" s="20"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="21"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="22"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="C52" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="D52" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="E51" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F51" s="20"/>
-      <c r="G51" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="I51" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="J51" s="4" t="n">
-        <f aca="false">J50+D50</f>
-        <v>0</v>
-      </c>
-      <c r="K51" s="4" t="n">
-        <f aca="false">J51/8</f>
-        <v>0</v>
-      </c>
-      <c r="L51" s="4" t="n">
-        <f aca="false">J51/16</f>
-        <v>0</v>
-      </c>
-      <c r="M51" s="4" t="n">
-        <f aca="false">J51/32</f>
-        <v>0</v>
-      </c>
-      <c r="N51" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O51" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="C52" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="D52" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F52" s="21"/>
+      <c r="E52" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F52" s="20"/>
       <c r="G52" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52" s="20" t="s">
         <v>34</v>
       </c>
       <c r="I52" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J52" s="4" t="n">
         <f aca="false">J51+D51</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K52" s="4" t="n">
         <f aca="false">J52/8</f>
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="L52" s="4" t="n">
         <f aca="false">J52/16</f>
-        <v>0.1875</v>
+        <v>0</v>
       </c>
       <c r="M52" s="4" t="n">
         <f aca="false">J52/32</f>
-        <v>0.09375</v>
+        <v>0</v>
       </c>
       <c r="N52" s="4" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="O52" s="22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="1" t="n">
         <v>0</v>
@@ -3431,10 +3319,10 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C53" s="26" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D53" s="26" t="n">
         <v>1</v>
@@ -3450,32 +3338,32 @@
         <v>34</v>
       </c>
       <c r="I53" s="21" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J53" s="4" t="n">
         <f aca="false">J52+D52</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K53" s="4" t="n">
         <f aca="false">J53/8</f>
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="L53" s="4" t="n">
         <f aca="false">J53/16</f>
-        <v>0.25</v>
+        <v>0.1875</v>
       </c>
       <c r="M53" s="4" t="n">
         <f aca="false">J53/32</f>
-        <v>0.125</v>
+        <v>0.09375</v>
       </c>
       <c r="N53" s="4" t="s">
         <v>52</v>
       </c>
       <c r="O53" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q53" s="1" t="n">
         <v>0</v>
@@ -3483,10 +3371,10 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="26" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C54" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D54" s="26" t="n">
         <v>1</v>
@@ -3502,32 +3390,32 @@
         <v>34</v>
       </c>
       <c r="I54" s="21" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J54" s="4" t="n">
         <f aca="false">J53+D53</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K54" s="4" t="n">
         <f aca="false">J54/8</f>
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="L54" s="4" t="n">
         <f aca="false">J54/16</f>
-        <v>0.3125</v>
+        <v>0.25</v>
       </c>
       <c r="M54" s="4" t="n">
         <f aca="false">J54/32</f>
-        <v>0.15625</v>
+        <v>0.125</v>
       </c>
       <c r="N54" s="4" t="s">
         <v>52</v>
       </c>
       <c r="O54" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q54" s="1" t="n">
         <v>0</v>
@@ -3535,10 +3423,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C55" s="26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D55" s="26" t="n">
         <v>1</v>
@@ -3554,32 +3442,32 @@
         <v>34</v>
       </c>
       <c r="I55" s="21" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J55" s="4" t="n">
         <f aca="false">J54+D54</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K55" s="4" t="n">
         <f aca="false">J55/8</f>
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="L55" s="4" t="n">
         <f aca="false">J55/16</f>
-        <v>0.375</v>
+        <v>0.3125</v>
       </c>
       <c r="M55" s="4" t="n">
         <f aca="false">J55/32</f>
-        <v>0.1875</v>
+        <v>0.15625</v>
       </c>
       <c r="N55" s="4" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="O55" s="22" t="n">
         <v>3</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q55" s="1" t="n">
         <v>0</v>
@@ -3587,10 +3475,10 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C56" s="26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D56" s="26" t="n">
         <v>1</v>
@@ -3606,113 +3494,113 @@
         <v>34</v>
       </c>
       <c r="I56" s="21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J56" s="4" t="n">
         <f aca="false">J55+D55</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K56" s="4" t="n">
         <f aca="false">J56/8</f>
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="L56" s="4" t="n">
         <f aca="false">J56/16</f>
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="M56" s="4" t="n">
         <f aca="false">J56/32</f>
+        <v>0.1875</v>
+      </c>
+      <c r="N56" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="O56" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P56" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q56" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="C57" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="D57" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F57" s="21"/>
+      <c r="G57" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I57" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="J57" s="4" t="n">
+        <f aca="false">J56+D56</f>
+        <v>7</v>
+      </c>
+      <c r="K57" s="4" t="n">
+        <f aca="false">J57/8</f>
+        <v>0.875</v>
+      </c>
+      <c r="L57" s="4" t="n">
+        <f aca="false">J57/16</f>
+        <v>0.4375</v>
+      </c>
+      <c r="M57" s="4" t="n">
+        <f aca="false">J57/32</f>
         <v>0.21875</v>
       </c>
-      <c r="N56" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="O56" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="P56" s="1" t="n">
+      <c r="N57" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="O57" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="Q56" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B57" s="20"/>
-      <c r="C57" s="20"/>
-      <c r="D57" s="20"/>
-      <c r="E57" s="20"/>
-      <c r="F57" s="20"/>
-      <c r="G57" s="20"/>
-      <c r="H57" s="20"/>
-      <c r="I57" s="21"/>
-      <c r="N57" s="4"/>
-      <c r="O57" s="22"/>
+      <c r="P57" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q57" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="C58" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="D58" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="E58" s="21" t="s">
-        <v>25</v>
-      </c>
+      <c r="A58" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B58" s="20"/>
+      <c r="C58" s="20"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20"/>
       <c r="F58" s="20"/>
-      <c r="G58" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H58" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="I58" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="J58" s="4" t="n">
-        <f aca="false">J56+D56</f>
-        <v>8</v>
-      </c>
-      <c r="K58" s="4" t="n">
-        <f aca="false">J58/8</f>
-        <v>1</v>
-      </c>
-      <c r="L58" s="4" t="n">
-        <f aca="false">J58/16</f>
-        <v>0.5</v>
-      </c>
-      <c r="M58" s="4" t="n">
-        <f aca="false">J58/32</f>
-        <v>0.25</v>
-      </c>
-      <c r="N58" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="O58" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P58" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q58" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="G58" s="20"/>
+      <c r="H58" s="20"/>
+      <c r="I58" s="21"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="22"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="20" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D59" s="20" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E59" s="21" t="s">
         <v>25</v>
@@ -3722,26 +3610,26 @@
         <v>2</v>
       </c>
       <c r="H59" s="20" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="I59" s="21" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J59" s="4" t="n">
-        <f aca="false">J58+D58</f>
-        <v>16</v>
+        <f aca="false">J57+D57</f>
+        <v>8</v>
       </c>
       <c r="K59" s="4" t="n">
         <f aca="false">J59/8</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L59" s="4" t="n">
         <f aca="false">J59/16</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M59" s="4" t="n">
         <f aca="false">J59/32</f>
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="N59" s="4" t="s">
         <v>44</v>
@@ -3750,7 +3638,7 @@
         <v>1</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q59" s="1" t="n">
         <v>0</v>
@@ -3758,42 +3646,42 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="20" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D60" s="20" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E60" s="21" t="s">
         <v>25</v>
       </c>
       <c r="F60" s="20"/>
       <c r="G60" s="20" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H60" s="20" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I60" s="21" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="J60" s="4" t="n">
         <f aca="false">J59+D59</f>
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K60" s="4" t="n">
         <f aca="false">J60/8</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L60" s="4" t="n">
         <f aca="false">J60/16</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M60" s="4" t="n">
         <f aca="false">J60/32</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N60" s="4" t="s">
         <v>44</v>
@@ -3802,7 +3690,7 @@
         <v>1</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q60" s="1" t="n">
         <v>0</v>
@@ -3810,42 +3698,42 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="20" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D61" s="20" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E61" s="21" t="s">
         <v>25</v>
       </c>
       <c r="F61" s="20"/>
       <c r="G61" s="20" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I61" s="21" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="J61" s="4" t="n">
         <f aca="false">J60+D60</f>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="K61" s="4" t="n">
         <f aca="false">J61/8</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L61" s="4" t="n">
         <f aca="false">J61/16</f>
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="M61" s="4" t="n">
         <f aca="false">J61/32</f>
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="N61" s="4" t="s">
         <v>44</v>
@@ -3854,50 +3742,50 @@
         <v>1</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q61" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="20" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D62" s="20" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E62" s="21" t="s">
         <v>25</v>
       </c>
       <c r="F62" s="20"/>
       <c r="G62" s="20" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H62" s="20" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="I62" s="21" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="J62" s="4" t="n">
         <f aca="false">J61+D61</f>
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="K62" s="4" t="n">
         <f aca="false">J62/8</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L62" s="4" t="n">
         <f aca="false">J62/16</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M62" s="4" t="n">
         <f aca="false">J62/32</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N62" s="4" t="s">
         <v>44</v>
@@ -3906,7 +3794,7 @@
         <v>1</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q62" s="1" t="n">
         <v>0</v>
@@ -3914,42 +3802,42 @@
     </row>
     <row r="63" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="20" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D63" s="20" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E63" s="21" t="s">
         <v>25</v>
       </c>
       <c r="F63" s="20"/>
       <c r="G63" s="20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H63" s="20" t="s">
-        <v>146</v>
+        <v>50</v>
       </c>
       <c r="I63" s="21" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="J63" s="4" t="n">
         <f aca="false">J62+D62</f>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K63" s="4" t="n">
         <f aca="false">J63/8</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L63" s="4" t="n">
         <f aca="false">J63/16</f>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M63" s="4" t="n">
         <f aca="false">J63/32</f>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="N63" s="4" t="s">
         <v>44</v>
@@ -3958,7 +3846,7 @@
         <v>1</v>
       </c>
       <c r="P63" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q63" s="1" t="n">
         <v>0</v>
@@ -3966,103 +3854,103 @@
     </row>
     <row r="64" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="20" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D64" s="20" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E64" s="21" t="s">
         <v>25</v>
       </c>
       <c r="F64" s="20"/>
       <c r="G64" s="20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H64" s="20" t="s">
-        <v>136</v>
+        <v>50</v>
       </c>
       <c r="I64" s="21" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="J64" s="4" t="n">
         <f aca="false">J63+D63</f>
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="K64" s="4" t="n">
         <f aca="false">J64/8</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L64" s="4" t="n">
         <f aca="false">J64/16</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M64" s="4" t="n">
         <f aca="false">J64/32</f>
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="N64" s="4" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="O64" s="22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q64" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="20" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D65" s="20" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E65" s="21" t="s">
         <v>25</v>
       </c>
       <c r="F65" s="20"/>
       <c r="G65" s="20" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H65" s="20" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I65" s="21" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="J65" s="4" t="n">
         <f aca="false">J64+D64</f>
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="K65" s="4" t="n">
         <f aca="false">J65/8</f>
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="L65" s="4" t="n">
         <f aca="false">J65/16</f>
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="M65" s="4" t="n">
         <f aca="false">J65/32</f>
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="N65" s="4" t="s">
         <v>52</v>
       </c>
       <c r="O65" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q65" s="1" t="n">
         <v>0</v>
@@ -4070,100 +3958,100 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="20" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D66" s="20" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E66" s="21" t="s">
         <v>25</v>
       </c>
       <c r="F66" s="20"/>
       <c r="G66" s="20" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H66" s="20" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I66" s="21" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J66" s="4" t="n">
         <f aca="false">J65+D65</f>
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="K66" s="4" t="n">
         <f aca="false">J66/8</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L66" s="4" t="n">
         <f aca="false">J66/16</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M66" s="4" t="n">
         <f aca="false">J66/32</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N66" s="4" t="s">
         <v>52</v>
       </c>
       <c r="O66" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P66" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q66" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="C67" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="D67" s="26" t="n">
+      <c r="B67" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="C67" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="D67" s="20" t="n">
         <v>8</v>
       </c>
       <c r="E67" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="F67" s="21"/>
+        <v>25</v>
+      </c>
+      <c r="F67" s="20"/>
       <c r="G67" s="20" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H67" s="20" t="s">
-        <v>34</v>
+        <v>134</v>
       </c>
       <c r="I67" s="21" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="J67" s="4" t="n">
         <f aca="false">J66+D66</f>
-        <v>144</v>
+        <v>72</v>
       </c>
       <c r="K67" s="4" t="n">
         <f aca="false">J67/8</f>
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="L67" s="4" t="n">
         <f aca="false">J67/16</f>
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="M67" s="4" t="n">
         <f aca="false">J67/32</f>
-        <v>4.5</v>
+        <v>2.25</v>
       </c>
       <c r="N67" s="4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="O67" s="22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P67" s="1" t="n">
         <v>10</v>
@@ -4172,18 +4060,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="26" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C68" s="26" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D68" s="26" t="n">
         <v>8</v>
       </c>
       <c r="E68" s="21" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="F68" s="21"/>
       <c r="G68" s="20" t="n">
@@ -4193,23 +4081,23 @@
         <v>34</v>
       </c>
       <c r="I68" s="21" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="J68" s="4" t="n">
         <f aca="false">J67+D67</f>
-        <v>152</v>
+        <v>80</v>
       </c>
       <c r="K68" s="4" t="n">
         <f aca="false">J68/8</f>
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="L68" s="4" t="n">
         <f aca="false">J68/16</f>
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="M68" s="4" t="n">
         <f aca="false">J68/32</f>
-        <v>4.75</v>
+        <v>2.5</v>
       </c>
       <c r="N68" s="4" t="s">
         <v>44</v>
@@ -4218,50 +4106,50 @@
         <v>1</v>
       </c>
       <c r="P68" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q68" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="26" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C69" s="26" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D69" s="26" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E69" s="21" t="s">
         <v>25</v>
       </c>
       <c r="F69" s="21"/>
       <c r="G69" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H69" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I69" s="26" t="s">
-        <v>168</v>
+      <c r="I69" s="21" t="s">
+        <v>162</v>
       </c>
       <c r="J69" s="4" t="n">
         <f aca="false">J68+D68</f>
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="K69" s="4" t="n">
         <f aca="false">J69/8</f>
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="L69" s="4" t="n">
         <f aca="false">J69/16</f>
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="M69" s="4" t="n">
         <f aca="false">J69/32</f>
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="N69" s="4" t="s">
         <v>44</v>
@@ -4270,7 +4158,7 @@
         <v>1</v>
       </c>
       <c r="P69" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q69" s="1" t="n">
         <v>0</v>
@@ -4278,16 +4166,16 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="26" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C70" s="26" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D70" s="26" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E70" s="21" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="F70" s="21"/>
       <c r="G70" s="20" t="n">
@@ -4296,179 +4184,202 @@
       <c r="H70" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I70" s="21" t="s">
-        <v>171</v>
+      <c r="I70" s="26" t="s">
+        <v>165</v>
       </c>
       <c r="J70" s="4" t="n">
         <f aca="false">J69+D69</f>
-        <v>192</v>
+        <v>96</v>
       </c>
       <c r="K70" s="4" t="n">
         <f aca="false">J70/8</f>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L70" s="4" t="n">
         <f aca="false">J70/16</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M70" s="4" t="n">
         <f aca="false">J70/32</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N70" s="4" t="s">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="O70" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P70" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q70" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="71" s="14" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B71" s="27"/>
-      <c r="C71" s="28"/>
-      <c r="D71" s="29"/>
-      <c r="E71" s="29"/>
-      <c r="F71" s="29"/>
-      <c r="G71" s="29"/>
-      <c r="H71" s="28"/>
-      <c r="I71" s="29" t="s">
-        <v>172</v>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="C71" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="D71" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E71" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F71" s="21"/>
+      <c r="G71" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I71" s="21" t="s">
+        <v>168</v>
       </c>
       <c r="J71" s="4" t="n">
         <f aca="false">J70+D70</f>
-        <v>200</v>
+        <v>128</v>
       </c>
       <c r="K71" s="4" t="n">
         <f aca="false">J71/8</f>
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="L71" s="4" t="n">
         <f aca="false">J71/16</f>
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="M71" s="4" t="n">
         <f aca="false">J71/32</f>
-        <v>6.25</v>
-      </c>
-      <c r="O71" s="30"/>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="23"/>
+        <v>4</v>
+      </c>
+      <c r="N71" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="O71" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P71" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q71" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" s="14" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B72" s="27"/>
+      <c r="C72" s="28"/>
+      <c r="D72" s="29"/>
+      <c r="E72" s="29"/>
+      <c r="F72" s="29"/>
+      <c r="G72" s="29"/>
+      <c r="H72" s="28"/>
+      <c r="I72" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="J72" s="4" t="n">
+        <f aca="false">J71+D71</f>
+        <v>136</v>
+      </c>
+      <c r="K72" s="4" t="n">
+        <f aca="false">J72/8</f>
+        <v>17</v>
+      </c>
+      <c r="L72" s="4" t="n">
+        <f aca="false">J72/16</f>
+        <v>8.5</v>
+      </c>
+      <c r="M72" s="4" t="n">
+        <f aca="false">J72/32</f>
+        <v>4.25</v>
+      </c>
+      <c r="O72" s="30"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="B73" s="23"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B74" s="26"/>
-      <c r="C74" s="26"/>
-      <c r="D74" s="26"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
-      <c r="H74" s="21"/>
-      <c r="I74" s="21"/>
-      <c r="J74" s="25"/>
-      <c r="K74" s="25"/>
-      <c r="L74" s="25"/>
-      <c r="M74" s="25"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="C75" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="D75" s="26" t="n">
-        <v>32</v>
-      </c>
-      <c r="E75" s="21" t="s">
+      <c r="A75" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B75" s="26"/>
+      <c r="C75" s="26"/>
+      <c r="D75" s="26"/>
+      <c r="E75" s="21"/>
+      <c r="F75" s="21"/>
+      <c r="G75" s="21"/>
+      <c r="H75" s="21"/>
+      <c r="I75" s="21"/>
+      <c r="J75" s="25"/>
+      <c r="K75" s="25"/>
+      <c r="L75" s="25"/>
+      <c r="M75" s="25"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="C76" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="D76" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E76" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="F75" s="21"/>
-      <c r="G75" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="20" t="s">
+      <c r="F76" s="21"/>
+      <c r="G76" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I75" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="J75" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="25" t="n">
-        <f aca="false">J75/8</f>
-        <v>0</v>
-      </c>
-      <c r="L75" s="25" t="n">
-        <f aca="false">J75/16</f>
-        <v>0</v>
-      </c>
-      <c r="M75" s="25" t="n">
-        <f aca="false">J75/32</f>
-        <v>0</v>
-      </c>
-      <c r="N75" s="4" t="s">
+      <c r="I76" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="J76" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="25" t="n">
+        <f aca="false">J76/8</f>
+        <v>0</v>
+      </c>
+      <c r="L76" s="25" t="n">
+        <f aca="false">J76/16</f>
+        <v>0</v>
+      </c>
+      <c r="M76" s="25" t="n">
+        <f aca="false">J76/32</f>
+        <v>0</v>
+      </c>
+      <c r="N76" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O75" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="14" t="s">
+      <c r="O76" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B76" s="27"/>
-      <c r="C76" s="28"/>
-      <c r="D76" s="29"/>
-      <c r="E76" s="29"/>
-      <c r="F76" s="29"/>
-      <c r="G76" s="29"/>
-      <c r="H76" s="28"/>
-      <c r="I76" s="29" t="s">
-        <v>172</v>
-      </c>
-      <c r="J76" s="4" t="n">
-        <f aca="false">J75+D75</f>
-        <v>32</v>
-      </c>
-      <c r="K76" s="4" t="n">
-        <f aca="false">J76/8</f>
-        <v>4</v>
-      </c>
-      <c r="L76" s="4" t="n">
-        <f aca="false">J76/16</f>
-        <v>2</v>
-      </c>
-      <c r="M76" s="4" t="n">
-        <f aca="false">J76/32</f>
-        <v>1</v>
-      </c>
-      <c r="O76" s="30"/>
-    </row>
-    <row r="77" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="27"/>
       <c r="C77" s="28"/>
       <c r="D77" s="29"/>
@@ -4476,105 +4387,85 @@
       <c r="F77" s="29"/>
       <c r="G77" s="29"/>
       <c r="H77" s="28"/>
-      <c r="I77" s="29"/>
-      <c r="J77" s="25"/>
-      <c r="K77" s="25"/>
-      <c r="L77" s="25"/>
-      <c r="M77" s="25"/>
+      <c r="I77" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="J77" s="4" t="n">
+        <f aca="false">J76+D76</f>
+        <v>8</v>
+      </c>
+      <c r="K77" s="4" t="n">
+        <f aca="false">J77/8</f>
+        <v>1</v>
+      </c>
+      <c r="L77" s="4" t="n">
+        <f aca="false">J77/16</f>
+        <v>0.5</v>
+      </c>
+      <c r="M77" s="4" t="n">
+        <f aca="false">J77/32</f>
+        <v>0.25</v>
+      </c>
       <c r="O77" s="30"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B78" s="23"/>
+    <row r="78" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="27"/>
+      <c r="C78" s="28"/>
+      <c r="D78" s="29"/>
+      <c r="E78" s="29"/>
+      <c r="F78" s="29"/>
+      <c r="G78" s="29"/>
+      <c r="H78" s="28"/>
+      <c r="I78" s="29"/>
+      <c r="J78" s="25"/>
+      <c r="K78" s="25"/>
+      <c r="L78" s="25"/>
+      <c r="M78" s="25"/>
+      <c r="O78" s="30"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="C79" s="26" t="s">
-        <v>177</v>
-      </c>
-      <c r="D79" s="24" t="n">
-        <v>32</v>
-      </c>
-      <c r="E79" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="F79" s="21"/>
-      <c r="G79" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="I79" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="J79" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="25" t="n">
-        <f aca="false">J79/8</f>
-        <v>0</v>
-      </c>
-      <c r="L79" s="25" t="n">
-        <f aca="false">J79/16</f>
-        <v>0</v>
-      </c>
-      <c r="M79" s="25" t="n">
-        <f aca="false">J79/32</f>
-        <v>0</v>
-      </c>
-      <c r="N79" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O79" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="A79" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B79" s="23"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="26" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C80" s="26" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D80" s="24" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E80" s="31" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="F80" s="21"/>
       <c r="G80" s="20" t="n">
         <v>0</v>
       </c>
+      <c r="H80" s="3" t="s">
+        <v>176</v>
+      </c>
       <c r="I80" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="J80" s="4" t="n">
-        <f aca="false">J79+D79</f>
-        <v>32</v>
-      </c>
-      <c r="K80" s="4" t="n">
+        <v>177</v>
+      </c>
+      <c r="J80" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="25" t="n">
         <f aca="false">J80/8</f>
-        <v>4</v>
-      </c>
-      <c r="L80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="25" t="n">
         <f aca="false">J80/16</f>
-        <v>2</v>
-      </c>
-      <c r="M80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="25" t="n">
         <f aca="false">J80/32</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N80" s="4" t="s">
         <v>28</v>
@@ -4591,42 +4482,39 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="26" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C81" s="26" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D81" s="24" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E81" s="31" t="s">
-        <v>178</v>
+        <v>25</v>
       </c>
       <c r="F81" s="21"/>
       <c r="G81" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H81" s="20" t="s">
-        <v>34</v>
-      </c>
       <c r="I81" s="25" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J81" s="4" t="n">
         <f aca="false">J80+D80</f>
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K81" s="4" t="n">
         <f aca="false">J81/8</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L81" s="4" t="n">
         <f aca="false">J81/16</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M81" s="4" t="n">
         <f aca="false">J81/32</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="N81" s="4" t="s">
         <v>28</v>
@@ -4643,15 +4531,17 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="26" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C82" s="26" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D82" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="E82" s="31"/>
+      <c r="E82" s="31" t="s">
+        <v>175</v>
+      </c>
       <c r="F82" s="21"/>
       <c r="G82" s="20" t="n">
         <v>0</v>
@@ -4660,23 +4550,23 @@
         <v>34</v>
       </c>
       <c r="I82" s="25" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="J82" s="4" t="n">
         <f aca="false">J81+D81</f>
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="K82" s="4" t="n">
         <f aca="false">J82/8</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L82" s="4" t="n">
         <f aca="false">J82/16</f>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="M82" s="4" t="n">
         <f aca="false">J82/32</f>
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="N82" s="4" t="s">
         <v>28</v>
@@ -4692,132 +4582,133 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B83" s="23"/>
-      <c r="C83" s="28"/>
-      <c r="D83" s="29"/>
-      <c r="E83" s="29"/>
-      <c r="F83" s="29"/>
-      <c r="G83" s="29"/>
-      <c r="H83" s="28"/>
-      <c r="I83" s="29" t="s">
-        <v>172</v>
+      <c r="B83" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="C83" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="D83" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E83" s="31"/>
+      <c r="F83" s="21"/>
+      <c r="G83" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I83" s="25" t="s">
+        <v>186</v>
       </c>
       <c r="J83" s="4" t="n">
         <f aca="false">J82+D82</f>
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="K83" s="4" t="n">
         <f aca="false">J83/8</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L83" s="4" t="n">
         <f aca="false">J83/16</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="M83" s="4" t="n">
         <f aca="false">J83/32</f>
+        <v>1.75</v>
+      </c>
+      <c r="N83" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O83" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B84" s="23"/>
+      <c r="C84" s="28"/>
+      <c r="D84" s="29"/>
+      <c r="E84" s="29"/>
+      <c r="F84" s="29"/>
+      <c r="G84" s="29"/>
+      <c r="H84" s="28"/>
+      <c r="I84" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="J84" s="4" t="n">
+        <f aca="false">J83+D83</f>
+        <v>64</v>
+      </c>
+      <c r="K84" s="4" t="n">
+        <f aca="false">J84/8</f>
+        <v>8</v>
+      </c>
+      <c r="L84" s="4" t="n">
+        <f aca="false">J84/16</f>
+        <v>4</v>
+      </c>
+      <c r="M84" s="4" t="n">
+        <f aca="false">J84/32</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="23"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="23"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="B86" s="23"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="C87" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="D87" s="24" t="n">
-        <v>32</v>
-      </c>
-      <c r="E87" s="31"/>
-      <c r="F87" s="21"/>
-      <c r="G87" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="I87" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="J87" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="25" t="n">
-        <f aca="false">J87/8</f>
-        <v>0</v>
-      </c>
-      <c r="L87" s="25" t="n">
-        <f aca="false">J87/16</f>
-        <v>0</v>
-      </c>
-      <c r="M87" s="25" t="n">
-        <f aca="false">J87/32</f>
-        <v>0</v>
-      </c>
-      <c r="N87" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O87" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="A87" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B87" s="23"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="26" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C88" s="26" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D88" s="24" t="n">
-        <v>16</v>
-      </c>
-      <c r="E88" s="31" t="s">
-        <v>25</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="E88" s="31"/>
       <c r="F88" s="21"/>
       <c r="G88" s="20" t="n">
         <v>0</v>
       </c>
+      <c r="H88" s="3" t="s">
+        <v>176</v>
+      </c>
       <c r="I88" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="J88" s="4" t="n">
-        <f aca="false">J87+D87</f>
-        <v>32</v>
-      </c>
-      <c r="K88" s="4" t="n">
+        <v>177</v>
+      </c>
+      <c r="J88" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="25" t="n">
         <f aca="false">J88/8</f>
-        <v>4</v>
-      </c>
-      <c r="L88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="25" t="n">
         <f aca="false">J88/16</f>
-        <v>2</v>
-      </c>
-      <c r="M88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="25" t="n">
         <f aca="false">J88/32</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N88" s="4" t="s">
         <v>28</v>
@@ -4834,37 +4725,39 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="26" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C89" s="26" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D89" s="24" t="n">
         <v>16</v>
       </c>
-      <c r="E89" s="31"/>
+      <c r="E89" s="31" t="s">
+        <v>25</v>
+      </c>
       <c r="F89" s="21"/>
       <c r="G89" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I89" s="25" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="J89" s="4" t="n">
         <f aca="false">J88+D88</f>
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K89" s="4" t="n">
         <f aca="false">J89/8</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L89" s="4" t="n">
         <f aca="false">J89/16</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M89" s="4" t="n">
         <f aca="false">J89/32</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="N89" s="4" t="s">
         <v>28</v>
@@ -4881,13 +4774,13 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="26" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C90" s="26" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D90" s="24" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E90" s="31"/>
       <c r="F90" s="21"/>
@@ -4895,23 +4788,23 @@
         <v>0</v>
       </c>
       <c r="I90" s="25" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="J90" s="4" t="n">
         <f aca="false">J89+D89</f>
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="K90" s="4" t="n">
         <f aca="false">J90/8</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L90" s="4" t="n">
         <f aca="false">J90/16</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M90" s="4" t="n">
         <f aca="false">J90/32</f>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="N90" s="4" t="s">
         <v>28</v>
@@ -4928,42 +4821,37 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="26" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C91" s="26" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D91" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="E91" s="31" t="s">
-        <v>178</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="E91" s="31"/>
       <c r="F91" s="21"/>
       <c r="G91" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H91" s="20" t="s">
-        <v>34</v>
-      </c>
       <c r="I91" s="25" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="J91" s="4" t="n">
         <f aca="false">J90+D90</f>
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="K91" s="4" t="n">
         <f aca="false">J91/8</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L91" s="4" t="n">
         <f aca="false">J91/16</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M91" s="4" t="n">
         <f aca="false">J91/32</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N91" s="4" t="s">
         <v>28</v>
@@ -4980,16 +4868,16 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="26" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="C92" s="26" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D92" s="24" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E92" s="31" t="s">
-        <v>64</v>
+        <v>175</v>
       </c>
       <c r="F92" s="21"/>
       <c r="G92" s="20" t="n">
@@ -4998,22 +4886,24 @@
       <c r="H92" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I92" s="25"/>
+      <c r="I92" s="25" t="s">
+        <v>200</v>
+      </c>
       <c r="J92" s="4" t="n">
         <f aca="false">J91+D91</f>
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="K92" s="4" t="n">
         <f aca="false">J92/8</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L92" s="4" t="n">
         <f aca="false">J92/16</f>
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="M92" s="4" t="n">
         <f aca="false">J92/32</f>
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N92" s="4" t="s">
         <v>28</v>
@@ -5029,114 +4919,113 @@
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B93" s="27"/>
-      <c r="C93" s="28"/>
-      <c r="D93" s="29"/>
-      <c r="E93" s="29"/>
-      <c r="F93" s="29"/>
-      <c r="G93" s="29"/>
-      <c r="H93" s="28"/>
-      <c r="I93" s="29" t="s">
-        <v>172</v>
-      </c>
+      <c r="B93" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="C93" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="D93" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="E93" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="F93" s="21"/>
+      <c r="G93" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I93" s="25"/>
       <c r="J93" s="4" t="n">
         <f aca="false">J92+D92</f>
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="K93" s="4" t="n">
         <f aca="false">J93/8</f>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L93" s="4" t="n">
         <f aca="false">J93/16</f>
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="M93" s="4" t="n">
         <f aca="false">J93/32</f>
+        <v>3.25</v>
+      </c>
+      <c r="N93" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B94" s="27"/>
+      <c r="C94" s="28"/>
+      <c r="D94" s="29"/>
+      <c r="E94" s="29"/>
+      <c r="F94" s="29"/>
+      <c r="G94" s="29"/>
+      <c r="H94" s="28"/>
+      <c r="I94" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="J94" s="4" t="n">
+        <f aca="false">J93+D93</f>
+        <v>128</v>
+      </c>
+      <c r="K94" s="4" t="n">
+        <f aca="false">J94/8</f>
+        <v>16</v>
+      </c>
+      <c r="L94" s="4" t="n">
+        <f aca="false">J94/16</f>
+        <v>8</v>
+      </c>
+      <c r="M94" s="4" t="n">
+        <f aca="false">J94/32</f>
         <v>4</v>
       </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="23"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="23"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="B96" s="23"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="B97" s="23"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B98" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="C98" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="D98" s="24" t="n">
-        <v>32</v>
-      </c>
-      <c r="E98" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F98" s="21"/>
-      <c r="G98" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="32" t="s">
-        <v>136</v>
-      </c>
-      <c r="I98" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="J98" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" s="25" t="n">
-        <f aca="false">J98/8</f>
-        <v>0</v>
-      </c>
-      <c r="L98" s="25" t="n">
-        <f aca="false">J98/16</f>
-        <v>0</v>
-      </c>
-      <c r="M98" s="25" t="n">
-        <f aca="false">J98/32</f>
-        <v>0</v>
-      </c>
-      <c r="N98" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O98" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q98" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="A98" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B98" s="23"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B99" s="26" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C99" s="26" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D99" s="24" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E99" s="31" t="s">
         <v>25</v>
@@ -5146,35 +5035,34 @@
         <v>0</v>
       </c>
       <c r="H99" s="32" t="s">
-        <v>34</v>
+        <v>176</v>
       </c>
       <c r="I99" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="J99" s="4" t="n">
-        <f aca="false">J98+D98</f>
-        <v>32</v>
-      </c>
-      <c r="K99" s="4" t="n">
+        <v>205</v>
+      </c>
+      <c r="J99" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="25" t="n">
         <f aca="false">J99/8</f>
-        <v>4</v>
-      </c>
-      <c r="L99" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="25" t="n">
         <f aca="false">J99/16</f>
-        <v>2</v>
-      </c>
-      <c r="M99" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="25" t="n">
         <f aca="false">J99/32</f>
+        <v>0</v>
+      </c>
+      <c r="N99" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="O99" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="N99" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O99" s="22" t="n">
-        <v>0</v>
-      </c>
       <c r="P99" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q99" s="1" t="n">
         <v>0</v>
@@ -5182,13 +5070,13 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="26" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C100" s="26" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D100" s="24" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E100" s="31" t="s">
         <v>25</v>
@@ -5197,196 +5085,197 @@
       <c r="G100" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H100" s="20" t="s">
+      <c r="H100" s="32" t="s">
         <v>34</v>
       </c>
       <c r="I100" s="25" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="J100" s="4" t="n">
         <f aca="false">J99+D99</f>
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K100" s="4" t="n">
         <f aca="false">J100/8</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L100" s="4" t="n">
         <f aca="false">J100/16</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M100" s="4" t="n">
         <f aca="false">J100/32</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="N100" s="4" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="O100" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P100" s="1" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q100" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B101" s="26"/>
-      <c r="I101" s="1" t="s">
-        <v>107</v>
+      <c r="B101" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="C101" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="D101" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E101" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F101" s="21"/>
+      <c r="G101" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I101" s="25" t="s">
+        <v>210</v>
       </c>
       <c r="J101" s="4" t="n">
         <f aca="false">J100+D100</f>
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="K101" s="4" t="n">
         <f aca="false">J101/8</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L101" s="4" t="n">
         <f aca="false">J101/16</f>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="M101" s="4" t="n">
         <f aca="false">J101/32</f>
+        <v>1.5</v>
+      </c>
+      <c r="N101" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="O101" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P101" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q101" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B102" s="26"/>
+      <c r="I102" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J102" s="4" t="n">
+        <f aca="false">J101+D101</f>
+        <v>56</v>
+      </c>
+      <c r="K102" s="4" t="n">
+        <f aca="false">J102/8</f>
+        <v>7</v>
+      </c>
+      <c r="L102" s="4" t="n">
+        <f aca="false">J102/16</f>
+        <v>3.5</v>
+      </c>
+      <c r="M102" s="4" t="n">
+        <f aca="false">J102/32</f>
         <v>1.75</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B102" s="26"/>
-      <c r="J102" s="25"/>
-      <c r="K102" s="25"/>
-      <c r="L102" s="25"/>
-      <c r="M102" s="25"/>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="33" t="s">
-        <v>213</v>
-      </c>
-      <c r="J104" s="34"/>
-      <c r="K104" s="25"/>
-      <c r="L104" s="25"/>
-      <c r="M104" s="25"/>
-      <c r="N104" s="18" t="s">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B103" s="26"/>
+      <c r="J103" s="25"/>
+      <c r="K103" s="25"/>
+      <c r="L103" s="25"/>
+      <c r="M103" s="25"/>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="J105" s="34"/>
+      <c r="K105" s="25"/>
+      <c r="L105" s="25"/>
+      <c r="M105" s="25"/>
+      <c r="N105" s="18" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="105" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B105" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C105" s="12" t="s">
+    <row r="106" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B106" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C106" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D105" s="12" t="s">
+      <c r="D106" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E105" s="12" t="s">
+      <c r="E106" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F105" s="12" t="s">
+      <c r="F106" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="G105" s="12" t="s">
+      <c r="G106" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="H105" s="12" t="s">
+      <c r="H106" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="I105" s="13" t="s">
+      <c r="I106" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="J105" s="14" t="s">
+      <c r="J106" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="K105" s="14" t="s">
+      <c r="K106" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="L105" s="14" t="s">
+      <c r="L106" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="M105" s="14" t="s">
+      <c r="M106" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="N105" s="4"/>
-      <c r="O105" s="19" t="s">
+      <c r="N106" s="4"/>
+      <c r="O106" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="P105" s="14" t="s">
+      <c r="P106" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="Q105" s="14" t="s">
+      <c r="Q106" s="14" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="106" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B106" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="C106" s="36" t="s">
-        <v>215</v>
-      </c>
-      <c r="D106" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="E106" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F106" s="37"/>
-      <c r="G106" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="H106" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I106" s="31" t="s">
-        <v>216</v>
-      </c>
-      <c r="J106" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" s="25" t="n">
-        <f aca="false">J106/8</f>
-        <v>0</v>
-      </c>
-      <c r="L106" s="25" t="n">
-        <f aca="false">J106/16</f>
-        <v>0</v>
-      </c>
-      <c r="M106" s="25" t="n">
-        <f aca="false">J106/32</f>
-        <v>0</v>
-      </c>
-      <c r="N106" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="O106" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P106" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q106" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="107" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B107" s="20" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C107" s="36" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D107" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E107" s="31" t="s">
         <v>25</v>
@@ -5399,32 +5288,31 @@
         <v>34</v>
       </c>
       <c r="I107" s="31" t="s">
-        <v>216</v>
-      </c>
-      <c r="J107" s="4" t="n">
-        <f aca="false">J106+D106</f>
-        <v>9</v>
-      </c>
-      <c r="K107" s="4" t="n">
+        <v>214</v>
+      </c>
+      <c r="J107" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="25" t="n">
         <f aca="false">J107/8</f>
-        <v>1.125</v>
-      </c>
-      <c r="L107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="25" t="n">
         <f aca="false">J107/16</f>
-        <v>0.5625</v>
-      </c>
-      <c r="M107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="25" t="n">
         <f aca="false">J107/32</f>
-        <v>0.28125</v>
+        <v>0</v>
       </c>
       <c r="N107" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O107" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P107" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="P107" s="1" t="n">
-        <v>2</v>
       </c>
       <c r="Q107" s="1" t="n">
         <v>0</v>
@@ -5432,13 +5320,13 @@
     </row>
     <row r="108" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B108" s="20" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C108" s="36" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D108" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E108" s="31" t="s">
         <v>25</v>
@@ -5451,32 +5339,32 @@
         <v>34</v>
       </c>
       <c r="I108" s="31" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="J108" s="4" t="n">
         <f aca="false">J107+D107</f>
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K108" s="4" t="n">
         <f aca="false">J108/8</f>
-        <v>1.75</v>
+        <v>1.125</v>
       </c>
       <c r="L108" s="4" t="n">
         <f aca="false">J108/16</f>
-        <v>0.875</v>
+        <v>0.5625</v>
       </c>
       <c r="M108" s="4" t="n">
         <f aca="false">J108/32</f>
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="N108" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O108" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P108" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q108" s="1" t="n">
         <v>0</v>
@@ -5484,10 +5372,10 @@
     </row>
     <row r="109" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B109" s="20" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C109" s="36" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D109" s="1" t="n">
         <v>4</v>
@@ -5503,32 +5391,32 @@
         <v>34</v>
       </c>
       <c r="I109" s="31" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="J109" s="4" t="n">
         <f aca="false">J108+D108</f>
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K109" s="4" t="n">
         <f aca="false">J109/8</f>
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="L109" s="4" t="n">
         <f aca="false">J109/16</f>
-        <v>1.125</v>
+        <v>0.875</v>
       </c>
       <c r="M109" s="4" t="n">
         <f aca="false">J109/32</f>
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="N109" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O109" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P109" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q109" s="1" t="n">
         <v>0</v>
@@ -5536,51 +5424,51 @@
     </row>
     <row r="110" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B110" s="20" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C110" s="36" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D110" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E110" s="31" t="s">
         <v>25</v>
       </c>
       <c r="F110" s="37"/>
-      <c r="G110" s="20" t="n">
+      <c r="G110" s="31" t="n">
         <v>2</v>
       </c>
       <c r="H110" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I110" s="20" t="s">
-        <v>227</v>
+      <c r="I110" s="31" t="s">
+        <v>222</v>
       </c>
       <c r="J110" s="4" t="n">
         <f aca="false">J109+D109</f>
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K110" s="4" t="n">
         <f aca="false">J110/8</f>
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="L110" s="4" t="n">
         <f aca="false">J110/16</f>
-        <v>1.375</v>
+        <v>1.125</v>
       </c>
       <c r="M110" s="4" t="n">
         <f aca="false">J110/32</f>
-        <v>0.6875</v>
+        <v>0.5625</v>
       </c>
       <c r="N110" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O110" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P110" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q110" s="1" t="n">
         <v>0</v>
@@ -5588,13 +5476,13 @@
     </row>
     <row r="111" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B111" s="20" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C111" s="36" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D111" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E111" s="31" t="s">
         <v>25</v>
@@ -5607,32 +5495,32 @@
         <v>34</v>
       </c>
       <c r="I111" s="20" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="J111" s="4" t="n">
         <f aca="false">J110+D110</f>
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K111" s="4" t="n">
         <f aca="false">J111/8</f>
-        <v>3.125</v>
+        <v>2.75</v>
       </c>
       <c r="L111" s="4" t="n">
         <f aca="false">J111/16</f>
-        <v>1.5625</v>
+        <v>1.375</v>
       </c>
       <c r="M111" s="4" t="n">
         <f aca="false">J111/32</f>
-        <v>0.78125</v>
+        <v>0.6875</v>
       </c>
       <c r="N111" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O111" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P111" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q111" s="1" t="n">
         <v>0</v>
@@ -5640,10 +5528,10 @@
     </row>
     <row r="112" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B112" s="20" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C112" s="36" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D112" s="1" t="n">
         <v>1</v>
@@ -5653,38 +5541,38 @@
       </c>
       <c r="F112" s="37"/>
       <c r="G112" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H112" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I112" s="31" t="s">
-        <v>216</v>
+      <c r="I112" s="20" t="s">
+        <v>228</v>
       </c>
       <c r="J112" s="4" t="n">
         <f aca="false">J111+D111</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K112" s="4" t="n">
         <f aca="false">J112/8</f>
-        <v>3.25</v>
+        <v>3.125</v>
       </c>
       <c r="L112" s="4" t="n">
         <f aca="false">J112/16</f>
-        <v>1.625</v>
+        <v>1.5625</v>
       </c>
       <c r="M112" s="4" t="n">
         <f aca="false">J112/32</f>
-        <v>0.8125</v>
+        <v>0.78125</v>
       </c>
       <c r="N112" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O112" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P112" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q112" s="1" t="n">
         <v>0</v>
@@ -5692,51 +5580,51 @@
     </row>
     <row r="113" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B113" s="20" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C113" s="36" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D113" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E113" s="31" t="s">
         <v>25</v>
       </c>
       <c r="F113" s="37"/>
       <c r="G113" s="20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H113" s="31" t="s">
         <v>34</v>
       </c>
       <c r="I113" s="31" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J113" s="4" t="n">
         <f aca="false">J112+D112</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K113" s="4" t="n">
         <f aca="false">J113/8</f>
-        <v>3.375</v>
+        <v>3.25</v>
       </c>
       <c r="L113" s="4" t="n">
         <f aca="false">J113/16</f>
-        <v>1.6875</v>
+        <v>1.625</v>
       </c>
       <c r="M113" s="4" t="n">
         <f aca="false">J113/32</f>
-        <v>0.84375</v>
+        <v>0.8125</v>
       </c>
       <c r="N113" s="4" t="s">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="O113" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P113" s="1" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q113" s="1" t="n">
         <v>0</v>
@@ -5744,103 +5632,103 @@
     </row>
     <row r="114" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B114" s="20" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C114" s="36" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D114" s="1" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="E114" s="31" t="s">
         <v>25</v>
       </c>
       <c r="F114" s="37"/>
       <c r="G114" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H114" s="31" t="s">
         <v>34</v>
       </c>
       <c r="I114" s="31" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J114" s="4" t="n">
         <f aca="false">J113+D113</f>
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K114" s="4" t="n">
         <f aca="false">J114/8</f>
-        <v>4</v>
+        <v>3.375</v>
       </c>
       <c r="L114" s="4" t="n">
         <f aca="false">J114/16</f>
-        <v>2</v>
+        <v>1.6875</v>
       </c>
       <c r="M114" s="4" t="n">
         <f aca="false">J114/32</f>
-        <v>1</v>
+        <v>0.84375</v>
       </c>
       <c r="N114" s="4" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="O114" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P114" s="1" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q114" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B115" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="C115" s="20" t="s">
-        <v>238</v>
+        <v>233</v>
+      </c>
+      <c r="C115" s="36" t="s">
+        <v>234</v>
       </c>
       <c r="D115" s="1" t="n">
         <v>32</v>
       </c>
       <c r="E115" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="F115" s="31"/>
+        <v>25</v>
+      </c>
+      <c r="F115" s="37"/>
       <c r="G115" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H115" s="31" t="s">
         <v>34</v>
       </c>
       <c r="I115" s="31" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J115" s="4" t="n">
         <f aca="false">J114+D114</f>
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="K115" s="4" t="n">
         <f aca="false">J115/8</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L115" s="4" t="n">
         <f aca="false">J115/16</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M115" s="4" t="n">
         <f aca="false">J115/32</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N115" s="4" t="s">
-        <v>239</v>
+        <v>98</v>
       </c>
       <c r="O115" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P115" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q115" s="1" t="n">
         <v>0</v>
@@ -5848,16 +5736,16 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B116" s="20" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C116" s="20" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D116" s="1" t="n">
         <v>32</v>
       </c>
       <c r="E116" s="31" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="F116" s="31"/>
       <c r="G116" s="20" t="n">
@@ -5867,32 +5755,32 @@
         <v>34</v>
       </c>
       <c r="I116" s="31" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J116" s="4" t="n">
         <f aca="false">J115+D115</f>
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="K116" s="4" t="n">
         <f aca="false">J116/8</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L116" s="4" t="n">
         <f aca="false">J116/16</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M116" s="4" t="n">
         <f aca="false">J116/32</f>
+        <v>2</v>
+      </c>
+      <c r="N116" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="O116" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="N116" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="O116" s="22" t="n">
-        <v>2</v>
-      </c>
       <c r="P116" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q116" s="1" t="n">
         <v>0</v>
@@ -5900,16 +5788,16 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B117" s="20" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C117" s="20" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D117" s="1" t="n">
         <v>32</v>
       </c>
       <c r="E117" s="31" t="s">
-        <v>178</v>
+        <v>25</v>
       </c>
       <c r="F117" s="31"/>
       <c r="G117" s="20" t="n">
@@ -5919,32 +5807,32 @@
         <v>34</v>
       </c>
       <c r="I117" s="31" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J117" s="4" t="n">
         <f aca="false">J116+D116</f>
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="K117" s="4" t="n">
         <f aca="false">J117/8</f>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L117" s="4" t="n">
         <f aca="false">J117/16</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M117" s="4" t="n">
         <f aca="false">J117/32</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N117" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="O117" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P117" s="1" t="n">
         <v>2</v>
-      </c>
-      <c r="P117" s="1" t="n">
-        <v>3</v>
       </c>
       <c r="Q117" s="1" t="n">
         <v>0</v>
@@ -5952,16 +5840,16 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B118" s="20" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C118" s="20" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D118" s="1" t="n">
         <v>32</v>
       </c>
       <c r="E118" s="31" t="s">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="F118" s="31"/>
       <c r="G118" s="20" t="n">
@@ -5971,32 +5859,32 @@
         <v>34</v>
       </c>
       <c r="I118" s="31" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J118" s="4" t="n">
         <f aca="false">J117+D117</f>
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="K118" s="4" t="n">
         <f aca="false">J118/8</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L118" s="4" t="n">
         <f aca="false">J118/16</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M118" s="4" t="n">
         <f aca="false">J118/32</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N118" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="O118" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P118" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q118" s="1" t="n">
         <v>0</v>
@@ -6004,13 +5892,13 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B119" s="20" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C119" s="20" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D119" s="1" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E119" s="31" t="s">
         <v>25</v>
@@ -6023,32 +5911,32 @@
         <v>34</v>
       </c>
       <c r="I119" s="31" t="s">
-        <v>248</v>
+        <v>214</v>
       </c>
       <c r="J119" s="4" t="n">
         <f aca="false">J118+D118</f>
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="K119" s="4" t="n">
         <f aca="false">J119/8</f>
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L119" s="4" t="n">
         <f aca="false">J119/16</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M119" s="4" t="n">
         <f aca="false">J119/32</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N119" s="4" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="O119" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P119" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="P119" s="1" t="n">
-        <v>1</v>
       </c>
       <c r="Q119" s="1" t="n">
         <v>0</v>
@@ -6056,10 +5944,10 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B120" s="20" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C120" s="20" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D120" s="1" t="n">
         <v>8</v>
@@ -6075,32 +5963,32 @@
         <v>34</v>
       </c>
       <c r="I120" s="31" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="J120" s="4" t="n">
         <f aca="false">J119+D119</f>
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="K120" s="4" t="n">
         <f aca="false">J120/8</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L120" s="4" t="n">
         <f aca="false">J120/16</f>
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="M120" s="4" t="n">
         <f aca="false">J120/32</f>
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="N120" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O120" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P120" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q120" s="1" t="n">
         <v>0</v>
@@ -6108,10 +5996,10 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B121" s="20" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C121" s="20" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D121" s="1" t="n">
         <v>8</v>
@@ -6127,32 +6015,32 @@
         <v>34</v>
       </c>
       <c r="I121" s="31" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="J121" s="4" t="n">
         <f aca="false">J120+D120</f>
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="K121" s="4" t="n">
         <f aca="false">J121/8</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L121" s="4" t="n">
         <f aca="false">J121/16</f>
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="M121" s="4" t="n">
         <f aca="false">J121/32</f>
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="N121" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O121" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P121" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q121" s="1" t="n">
         <v>0</v>
@@ -6160,10 +6048,10 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B122" s="20" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C122" s="20" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D122" s="1" t="n">
         <v>8</v>
@@ -6179,32 +6067,32 @@
         <v>34</v>
       </c>
       <c r="I122" s="31" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="J122" s="4" t="n">
         <f aca="false">J121+D121</f>
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="K122" s="4" t="n">
         <f aca="false">J122/8</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L122" s="4" t="n">
         <f aca="false">J122/16</f>
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="M122" s="4" t="n">
         <f aca="false">J122/32</f>
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="N122" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O122" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P122" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q122" s="1" t="n">
         <v>0</v>
@@ -6212,10 +6100,10 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B123" s="20" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C123" s="20" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D123" s="1" t="n">
         <v>8</v>
@@ -6231,32 +6119,32 @@
         <v>34</v>
       </c>
       <c r="I123" s="31" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="J123" s="4" t="n">
         <f aca="false">J122+D122</f>
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="K123" s="4" t="n">
         <f aca="false">J123/8</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L123" s="4" t="n">
         <f aca="false">J123/16</f>
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="M123" s="4" t="n">
         <f aca="false">J123/32</f>
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="N123" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O123" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="P123" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="P123" s="1" t="n">
-        <v>5</v>
       </c>
       <c r="Q123" s="1" t="n">
         <v>0</v>
@@ -6264,10 +6152,10 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B124" s="20" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C124" s="20" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D124" s="1" t="n">
         <v>8</v>
@@ -6282,33 +6170,33 @@
       <c r="H124" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I124" s="20" t="s">
-        <v>262</v>
+      <c r="I124" s="31" t="s">
+        <v>259</v>
       </c>
       <c r="J124" s="4" t="n">
         <f aca="false">J123+D123</f>
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="K124" s="4" t="n">
         <f aca="false">J124/8</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L124" s="4" t="n">
         <f aca="false">J124/16</f>
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="M124" s="4" t="n">
         <f aca="false">J124/32</f>
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="N124" s="4" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="O124" s="22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P124" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q124" s="1" t="n">
         <v>0</v>
@@ -6316,10 +6204,10 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B125" s="20" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C125" s="20" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="D125" s="1" t="n">
         <v>8</v>
@@ -6335,32 +6223,32 @@
         <v>34</v>
       </c>
       <c r="I125" s="20" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="J125" s="4" t="n">
         <f aca="false">J124+D124</f>
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="K125" s="4" t="n">
         <f aca="false">J125/8</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L125" s="4" t="n">
         <f aca="false">J125/16</f>
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="M125" s="4" t="n">
         <f aca="false">J125/32</f>
-        <v>7.5</v>
+        <v>7.25</v>
       </c>
       <c r="N125" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O125" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P125" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q125" s="1" t="n">
         <v>0</v>
@@ -6368,10 +6256,10 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B126" s="20" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C126" s="20" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D126" s="1" t="n">
         <v>8</v>
@@ -6387,32 +6275,32 @@
         <v>34</v>
       </c>
       <c r="I126" s="20" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J126" s="4" t="n">
         <f aca="false">J125+D125</f>
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="K126" s="4" t="n">
         <f aca="false">J126/8</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L126" s="4" t="n">
         <f aca="false">J126/16</f>
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="M126" s="4" t="n">
         <f aca="false">J126/32</f>
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="N126" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O126" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P126" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q126" s="1" t="n">
         <v>0</v>
@@ -6420,10 +6308,10 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B127" s="20" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C127" s="20" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D127" s="1" t="n">
         <v>8</v>
@@ -6439,32 +6327,32 @@
         <v>34</v>
       </c>
       <c r="I127" s="20" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="J127" s="4" t="n">
         <f aca="false">J126+D126</f>
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="K127" s="4" t="n">
         <f aca="false">J127/8</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L127" s="4" t="n">
         <f aca="false">J127/16</f>
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="M127" s="4" t="n">
         <f aca="false">J127/32</f>
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="N127" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O127" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="P127" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="P127" s="1" t="n">
-        <v>4</v>
       </c>
       <c r="Q127" s="1" t="n">
         <v>0</v>
@@ -6472,10 +6360,10 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B128" s="20" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C128" s="20" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D128" s="1" t="n">
         <v>8</v>
@@ -6491,32 +6379,32 @@
         <v>34</v>
       </c>
       <c r="I128" s="20" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J128" s="4" t="n">
         <f aca="false">J127+D127</f>
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="K128" s="4" t="n">
         <f aca="false">J128/8</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L128" s="4" t="n">
         <f aca="false">J128/16</f>
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="M128" s="4" t="n">
         <f aca="false">J128/32</f>
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="N128" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O128" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P128" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q128" s="1" t="n">
         <v>0</v>
@@ -6524,10 +6412,10 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B129" s="20" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C129" s="20" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D129" s="1" t="n">
         <v>8</v>
@@ -6543,32 +6431,32 @@
         <v>34</v>
       </c>
       <c r="I129" s="20" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="J129" s="4" t="n">
         <f aca="false">J128+D128</f>
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="K129" s="4" t="n">
         <f aca="false">J129/8</f>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L129" s="4" t="n">
         <f aca="false">J129/16</f>
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="M129" s="4" t="n">
         <f aca="false">J129/32</f>
-        <v>8.5</v>
+        <v>8.25</v>
       </c>
       <c r="N129" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O129" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P129" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q129" s="1" t="n">
         <v>0</v>
@@ -6576,10 +6464,10 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B130" s="20" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C130" s="20" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D130" s="1" t="n">
         <v>8</v>
@@ -6595,32 +6483,32 @@
         <v>34</v>
       </c>
       <c r="I130" s="20" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="J130" s="4" t="n">
         <f aca="false">J129+D129</f>
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="K130" s="4" t="n">
         <f aca="false">J130/8</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L130" s="4" t="n">
         <f aca="false">J130/16</f>
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="M130" s="4" t="n">
         <f aca="false">J130/32</f>
-        <v>8.75</v>
+        <v>8.5</v>
       </c>
       <c r="N130" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O130" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P130" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q130" s="1" t="n">
         <v>0</v>
@@ -6628,10 +6516,10 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B131" s="20" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C131" s="20" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D131" s="1" t="n">
         <v>8</v>
@@ -6647,32 +6535,32 @@
         <v>34</v>
       </c>
       <c r="I131" s="20" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="J131" s="4" t="n">
         <f aca="false">J130+D130</f>
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="K131" s="4" t="n">
         <f aca="false">J131/8</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L131" s="4" t="n">
         <f aca="false">J131/16</f>
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="M131" s="4" t="n">
         <f aca="false">J131/32</f>
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="N131" s="4" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="O131" s="22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P131" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q131" s="1" t="n">
         <v>0</v>
@@ -6680,10 +6568,10 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B132" s="20" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C132" s="20" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D132" s="1" t="n">
         <v>8</v>
@@ -6699,32 +6587,32 @@
         <v>34</v>
       </c>
       <c r="I132" s="20" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="J132" s="4" t="n">
         <f aca="false">J131+D131</f>
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="K132" s="4" t="n">
         <f aca="false">J132/8</f>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L132" s="4" t="n">
         <f aca="false">J132/16</f>
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="M132" s="4" t="n">
         <f aca="false">J132/32</f>
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="N132" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="O132" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P132" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q132" s="1" t="n">
         <v>0</v>
@@ -6732,10 +6620,10 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B133" s="20" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C133" s="20" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D133" s="1" t="n">
         <v>8</v>
@@ -6751,32 +6639,32 @@
         <v>34</v>
       </c>
       <c r="I133" s="20" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="J133" s="4" t="n">
         <f aca="false">J132+D132</f>
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="K133" s="4" t="n">
         <f aca="false">J133/8</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L133" s="4" t="n">
         <f aca="false">J133/16</f>
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="M133" s="4" t="n">
         <f aca="false">J133/32</f>
-        <v>9.5</v>
+        <v>9.25</v>
       </c>
       <c r="N133" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="O133" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P133" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q133" s="1" t="n">
         <v>0</v>
@@ -6784,10 +6672,10 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B134" s="20" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C134" s="20" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D134" s="1" t="n">
         <v>8</v>
@@ -6803,32 +6691,32 @@
         <v>34</v>
       </c>
       <c r="I134" s="20" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="J134" s="4" t="n">
         <f aca="false">J133+D133</f>
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="K134" s="4" t="n">
         <f aca="false">J134/8</f>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L134" s="4" t="n">
         <f aca="false">J134/16</f>
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="M134" s="4" t="n">
         <f aca="false">J134/32</f>
-        <v>9.75</v>
+        <v>9.5</v>
       </c>
       <c r="N134" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="O134" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P134" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q134" s="1" t="n">
         <v>0</v>
@@ -6836,10 +6724,10 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B135" s="20" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C135" s="20" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D135" s="1" t="n">
         <v>8</v>
@@ -6855,32 +6743,32 @@
         <v>34</v>
       </c>
       <c r="I135" s="20" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="J135" s="4" t="n">
         <f aca="false">J134+D134</f>
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="K135" s="4" t="n">
         <f aca="false">J135/8</f>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L135" s="4" t="n">
         <f aca="false">J135/16</f>
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="M135" s="4" t="n">
         <f aca="false">J135/32</f>
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="N135" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="O135" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P135" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q135" s="1" t="n">
         <v>0</v>
@@ -6888,10 +6776,10 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B136" s="20" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C136" s="20" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D136" s="1" t="n">
         <v>8</v>
@@ -6907,32 +6795,32 @@
         <v>34</v>
       </c>
       <c r="I136" s="20" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="J136" s="4" t="n">
         <f aca="false">J135+D135</f>
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="K136" s="4" t="n">
         <f aca="false">J136/8</f>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L136" s="4" t="n">
         <f aca="false">J136/16</f>
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="M136" s="4" t="n">
         <f aca="false">J136/32</f>
-        <v>10.25</v>
+        <v>10</v>
       </c>
       <c r="N136" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="O136" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P136" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q136" s="1" t="n">
         <v>0</v>
@@ -6940,10 +6828,10 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B137" s="20" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C137" s="20" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D137" s="1" t="n">
         <v>8</v>
@@ -6959,32 +6847,32 @@
         <v>34</v>
       </c>
       <c r="I137" s="20" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="J137" s="4" t="n">
         <f aca="false">J136+D136</f>
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="K137" s="4" t="n">
         <f aca="false">J137/8</f>
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L137" s="4" t="n">
         <f aca="false">J137/16</f>
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="M137" s="4" t="n">
         <f aca="false">J137/32</f>
-        <v>10.5</v>
+        <v>10.25</v>
       </c>
       <c r="N137" s="4" t="s">
-        <v>100</v>
+        <v>237</v>
       </c>
       <c r="O137" s="22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P137" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q137" s="1" t="n">
         <v>0</v>
@@ -6992,10 +6880,10 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B138" s="20" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C138" s="20" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D138" s="1" t="n">
         <v>8</v>
@@ -7011,32 +6899,32 @@
         <v>34</v>
       </c>
       <c r="I138" s="20" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="J138" s="4" t="n">
         <f aca="false">J137+D137</f>
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="K138" s="4" t="n">
         <f aca="false">J138/8</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L138" s="4" t="n">
         <f aca="false">J138/16</f>
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="M138" s="4" t="n">
         <f aca="false">J138/32</f>
-        <v>10.75</v>
+        <v>10.5</v>
       </c>
       <c r="N138" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O138" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P138" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q138" s="1" t="n">
         <v>0</v>
@@ -7044,10 +6932,10 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B139" s="20" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C139" s="20" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D139" s="1" t="n">
         <v>8</v>
@@ -7063,32 +6951,32 @@
         <v>34</v>
       </c>
       <c r="I139" s="20" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="J139" s="4" t="n">
         <f aca="false">J138+D138</f>
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="K139" s="4" t="n">
         <f aca="false">J139/8</f>
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L139" s="4" t="n">
         <f aca="false">J139/16</f>
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="M139" s="4" t="n">
         <f aca="false">J139/32</f>
-        <v>11</v>
+        <v>10.75</v>
       </c>
       <c r="N139" s="4" t="s">
-        <v>239</v>
+        <v>98</v>
       </c>
       <c r="O139" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P139" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q139" s="1" t="n">
         <v>0</v>
@@ -7096,10 +6984,10 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B140" s="20" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C140" s="20" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D140" s="1" t="n">
         <v>8</v>
@@ -7115,32 +7003,32 @@
         <v>34</v>
       </c>
       <c r="I140" s="20" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="J140" s="4" t="n">
         <f aca="false">J139+D139</f>
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="K140" s="4" t="n">
         <f aca="false">J140/8</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L140" s="4" t="n">
         <f aca="false">J140/16</f>
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="M140" s="4" t="n">
         <f aca="false">J140/32</f>
-        <v>11.25</v>
+        <v>11</v>
       </c>
       <c r="N140" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="O140" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P140" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q140" s="1" t="n">
         <v>0</v>
@@ -7148,10 +7036,10 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B141" s="20" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C141" s="20" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D141" s="1" t="n">
         <v>8</v>
@@ -7167,32 +7055,32 @@
         <v>34</v>
       </c>
       <c r="I141" s="20" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="J141" s="4" t="n">
         <f aca="false">J140+D140</f>
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="K141" s="4" t="n">
         <f aca="false">J141/8</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L141" s="4" t="n">
         <f aca="false">J141/16</f>
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="M141" s="4" t="n">
         <f aca="false">J141/32</f>
-        <v>11.5</v>
+        <v>11.25</v>
       </c>
       <c r="N141" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="O141" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P141" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q141" s="1" t="n">
         <v>0</v>
@@ -7200,10 +7088,10 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B142" s="20" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C142" s="20" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D142" s="1" t="n">
         <v>8</v>
@@ -7219,32 +7107,32 @@
         <v>34</v>
       </c>
       <c r="I142" s="20" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="J142" s="4" t="n">
         <f aca="false">J141+D141</f>
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="K142" s="4" t="n">
         <f aca="false">J142/8</f>
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L142" s="4" t="n">
         <f aca="false">J142/16</f>
-        <v>23.5</v>
+        <v>23</v>
       </c>
       <c r="M142" s="4" t="n">
         <f aca="false">J142/32</f>
-        <v>11.75</v>
+        <v>11.5</v>
       </c>
       <c r="N142" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="O142" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P142" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q142" s="1" t="n">
         <v>0</v>
@@ -7252,10 +7140,10 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B143" s="20" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C143" s="20" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D143" s="1" t="n">
         <v>8</v>
@@ -7271,32 +7159,32 @@
         <v>34</v>
       </c>
       <c r="I143" s="20" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="J143" s="4" t="n">
         <f aca="false">J142+D142</f>
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="K143" s="4" t="n">
         <f aca="false">J143/8</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L143" s="4" t="n">
         <f aca="false">J143/16</f>
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="M143" s="4" t="n">
         <f aca="false">J143/32</f>
-        <v>12</v>
+        <v>11.75</v>
       </c>
       <c r="N143" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="O143" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P143" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q143" s="1" t="n">
         <v>0</v>
@@ -7304,10 +7192,10 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B144" s="20" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C144" s="20" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D144" s="1" t="n">
         <v>8</v>
@@ -7323,32 +7211,32 @@
         <v>34</v>
       </c>
       <c r="I144" s="20" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="J144" s="4" t="n">
         <f aca="false">J143+D143</f>
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="K144" s="4" t="n">
         <f aca="false">J144/8</f>
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L144" s="4" t="n">
         <f aca="false">J144/16</f>
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="M144" s="4" t="n">
         <f aca="false">J144/32</f>
-        <v>12.25</v>
+        <v>12</v>
       </c>
       <c r="N144" s="4" t="s">
-        <v>100</v>
+        <v>237</v>
       </c>
       <c r="O144" s="22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P144" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q144" s="1" t="n">
         <v>0</v>
@@ -7356,10 +7244,10 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B145" s="20" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C145" s="20" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D145" s="1" t="n">
         <v>8</v>
@@ -7375,32 +7263,32 @@
         <v>34</v>
       </c>
       <c r="I145" s="20" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="J145" s="4" t="n">
         <f aca="false">J144+D144</f>
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="K145" s="4" t="n">
         <f aca="false">J145/8</f>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L145" s="4" t="n">
         <f aca="false">J145/16</f>
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="M145" s="4" t="n">
         <f aca="false">J145/32</f>
-        <v>12.5</v>
+        <v>12.25</v>
       </c>
       <c r="N145" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O145" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P145" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q145" s="1" t="n">
         <v>0</v>
@@ -7408,10 +7296,10 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B146" s="20" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C146" s="20" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D146" s="1" t="n">
         <v>8</v>
@@ -7427,226 +7315,277 @@
         <v>34</v>
       </c>
       <c r="I146" s="20" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="J146" s="4" t="n">
         <f aca="false">J145+D145</f>
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="K146" s="4" t="n">
         <f aca="false">J146/8</f>
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L146" s="4" t="n">
         <f aca="false">J146/16</f>
-        <v>25.5</v>
+        <v>25</v>
       </c>
       <c r="M146" s="4" t="n">
         <f aca="false">J146/32</f>
-        <v>12.75</v>
+        <v>12.5</v>
       </c>
       <c r="N146" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O146" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P146" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q146" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B147" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C147" s="3" t="s">
-        <v>310</v>
+      <c r="B147" s="20" t="s">
+        <v>305</v>
+      </c>
+      <c r="C147" s="20" t="s">
+        <v>306</v>
       </c>
       <c r="D147" s="1" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E147" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="F147" s="31" t="s">
-        <v>64</v>
-      </c>
+      <c r="F147" s="31"/>
       <c r="G147" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H147" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I147" s="3" t="s">
-        <v>309</v>
+      <c r="I147" s="20" t="s">
+        <v>305</v>
       </c>
       <c r="J147" s="4" t="n">
         <f aca="false">J146+D146</f>
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="K147" s="4" t="n">
         <f aca="false">J147/8</f>
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L147" s="4" t="n">
         <f aca="false">J147/16</f>
-        <v>26</v>
+        <v>25.5</v>
       </c>
       <c r="M147" s="4" t="n">
         <f aca="false">J147/32</f>
+        <v>12.75</v>
+      </c>
+      <c r="N147" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="O147" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P147" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="N147" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="O147" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P147" s="1" t="n">
-        <v>14</v>
-      </c>
       <c r="Q147" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B148" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="C148" s="20" t="s">
-        <v>312</v>
+      <c r="B148" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>308</v>
       </c>
       <c r="D148" s="1" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E148" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="F148" s="31"/>
+      <c r="F148" s="31" t="s">
+        <v>64</v>
+      </c>
       <c r="G148" s="20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H148" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I148" s="20" t="s">
-        <v>311</v>
+      <c r="I148" s="3" t="s">
+        <v>307</v>
       </c>
       <c r="J148" s="4" t="n">
         <f aca="false">J147+D147</f>
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="K148" s="4" t="n">
         <f aca="false">J148/8</f>
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L148" s="4" t="n">
         <f aca="false">J148/16</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M148" s="4" t="n">
         <f aca="false">J148/32</f>
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="N148" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O148" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P148" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q148" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B149" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C149" s="3" t="s">
-        <v>314</v>
+      <c r="B149" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="C149" s="20" t="s">
+        <v>310</v>
       </c>
       <c r="D149" s="1" t="n">
         <v>8</v>
       </c>
       <c r="E149" s="31" t="s">
-        <v>315</v>
+        <v>25</v>
       </c>
       <c r="F149" s="31"/>
       <c r="G149" s="20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H149" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="I149" s="31" t="s">
-        <v>216</v>
+      <c r="I149" s="20" t="s">
+        <v>309</v>
       </c>
       <c r="J149" s="4" t="n">
         <f aca="false">J148+D148</f>
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="K149" s="4" t="n">
         <f aca="false">J149/8</f>
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L149" s="4" t="n">
         <f aca="false">J149/16</f>
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="M149" s="4" t="n">
         <f aca="false">J149/32</f>
-        <v>13.75</v>
+        <v>13.5</v>
       </c>
       <c r="N149" s="4" t="s">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="O149" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P149" s="1" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q149" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="1" t="s">
-        <v>45</v>
+      <c r="B150" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D150" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E150" s="31" t="s">
+        <v>313</v>
       </c>
       <c r="F150" s="31"/>
-      <c r="G150" s="31"/>
-      <c r="H150" s="31"/>
-      <c r="I150" s="31"/>
+      <c r="G150" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I150" s="31" t="s">
+        <v>214</v>
+      </c>
       <c r="J150" s="4" t="n">
         <f aca="false">J149+D149</f>
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="K150" s="4" t="n">
         <f aca="false">J150/8</f>
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L150" s="4" t="n">
         <f aca="false">J150/16</f>
-        <v>28</v>
+        <v>27.5</v>
       </c>
       <c r="M150" s="4" t="n">
         <f aca="false">J150/32</f>
+        <v>13.75</v>
+      </c>
+      <c r="N150" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O150" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F151" s="31"/>
+      <c r="G151" s="31"/>
+      <c r="H151" s="31"/>
+      <c r="I151" s="31"/>
+      <c r="J151" s="4" t="n">
+        <f aca="false">J150+D150</f>
+        <v>448</v>
+      </c>
+      <c r="K151" s="4" t="n">
+        <f aca="false">J151/8</f>
+        <v>56</v>
+      </c>
+      <c r="L151" s="4" t="n">
+        <f aca="false">J151/16</f>
+        <v>28</v>
+      </c>
+      <c r="M151" s="4" t="n">
+        <f aca="false">J151/32</f>
         <v>14</v>
       </c>
     </row>
-    <row r="151" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C151" s="3"/>
-      <c r="H151" s="3"/>
-      <c r="O151" s="3"/>
-    </row>
-    <row r="1048303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="152" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C152" s="3"/>
+      <c r="H152" s="3"/>
+      <c r="O152" s="3"/>
+    </row>
     <row r="1048304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -7927,10 +7866,10 @@
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="B4:I4"/>
     <mergeCell ref="B5:I5"/>
-    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="B41:I41"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A104" r:id="rId1" display="Structure:rt1Errors_t,file:rt1ErrorsDownlink.h"/>
+    <hyperlink ref="A105" r:id="rId1" display="Structure:rt1Errors_t,file:rt1ErrorsDownlink.h"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -7943,12 +7882,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B6:I20"/>
-  <sheetFormatPr defaultColWidth="9.2890625" defaultRowHeight="13.2" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.30078125" defaultRowHeight="13.2" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="38" width="20.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="38" width="16.11"/>
@@ -7958,22 +7897,22 @@
     <row r="6" s="39" customFormat="true" ht="34.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="40"/>
       <c r="C6" s="40" t="s">
+        <v>314</v>
+      </c>
+      <c r="D6" s="40" t="s">
+        <v>315</v>
+      </c>
+      <c r="E6" s="40" t="s">
         <v>316</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="F6" s="40" t="s">
         <v>317</v>
       </c>
-      <c r="E6" s="40" t="s">
+      <c r="G6" s="40" t="s">
         <v>318</v>
       </c>
-      <c r="F6" s="40" t="s">
+      <c r="H6" s="40" t="s">
         <v>319</v>
-      </c>
-      <c r="G6" s="40" t="s">
-        <v>320</v>
-      </c>
-      <c r="H6" s="40" t="s">
-        <v>321</v>
       </c>
       <c r="I6" s="40"/>
     </row>

--- a/TelemDefinition/DownlinkSpecPacsat.xlsx
+++ b/TelemDefinition/DownlinkSpecPacsat.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="345">
   <si>
     <t xml:space="preserve">//</t>
   </si>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">TX Power Mode</t>
   </si>
   <si>
-    <t xml:space="preserve">Mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TxMode</t>
+    <t xml:space="preserve">Modulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TxModMode</t>
   </si>
   <si>
     <t xml:space="preserve">The modulation mode of the TX</t>
@@ -278,6 +278,30 @@
     <t xml:space="preserve">Receiver 4</t>
   </si>
   <si>
+    <t xml:space="preserve">RX0ModMode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX0 Modulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX1ModMode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX1 Modulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX2ModMode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX2 Modulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX3ModMode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX3 Modulation</t>
+  </si>
+  <si>
     <t xml:space="preserve">RX0RSSI</t>
   </si>
   <si>
@@ -305,7 +329,7 @@
     <t xml:space="preserve">RSSI for receiver 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Temperature</t>
+    <t xml:space="preserve">CPU Temp</t>
   </si>
   <si>
     <t xml:space="preserve">IHUTemp</t>
@@ -338,6 +362,15 @@
     <t xml:space="preserve">Power Supply Temperature</t>
   </si>
   <si>
+    <t xml:space="preserve">Filler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pad0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Make same length as WOD</t>
+  </si>
+  <si>
     <t xml:space="preserve">Totals:</t>
   </si>
   <si>
@@ -521,13 +554,40 @@
     <t xml:space="preserve">Command Ring showing last 4 commands</t>
   </si>
   <si>
-    <t xml:space="preserve">MRAM Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRAMstatus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status of the MRAM</t>
+    <t xml:space="preserve">MRAM0 Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRAMstatus0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status of MRAM0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRAM1 Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRAMstatus1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status of MRAM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRAM2 Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRAMstatus2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status of MRAM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRAM3 Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRAMstatus3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status of MRAM3</t>
   </si>
   <si>
     <t xml:space="preserve">Total Length</t>
@@ -536,7 +596,7 @@
     <t xml:space="preserve">Structure: realtimeSpecific_t, file:realtimeDownlink.h</t>
   </si>
   <si>
-    <t xml:space="preserve">Pad5</t>
+    <t xml:space="preserve">pad2</t>
   </si>
   <si>
     <t xml:space="preserve">Structure: maxSpecific_t, file: maxDownlink.h</t>
@@ -575,13 +635,7 @@
     <t xml:space="preserve">CRC Error for the Max Payload</t>
   </si>
   <si>
-    <t xml:space="preserve">Filler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pad0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Make same length as WOD</t>
+    <t xml:space="preserve">pad3</t>
   </si>
   <si>
     <t xml:space="preserve">Structure: minSpecific_t, file: minDownlink.h</t>
@@ -626,7 +680,7 @@
     <t xml:space="preserve">CRC Error for the min payload</t>
   </si>
   <si>
-    <t xml:space="preserve">Pad192</t>
+    <t xml:space="preserve">pad4</t>
   </si>
   <si>
     <t xml:space="preserve">Structure:wodSpecific_t,file:wodSpecificDownlink.h</t>
@@ -656,6 +710,9 @@
     <t xml:space="preserve">CRC Error for the WOD Payload</t>
   </si>
   <si>
+    <t xml:space="preserve">pad5</t>
+  </si>
+  <si>
     <t xml:space="preserve">Structure:rt1Errors_t,file:rt1ErrorsDownlink.h</t>
   </si>
   <si>
@@ -719,7 +776,7 @@
     <t xml:space="preserve">pad to 32 bits</t>
   </si>
   <si>
-    <t xml:space="preserve">pad316</t>
+    <t xml:space="preserve">pad6</t>
   </si>
   <si>
     <t xml:space="preserve">Error Data</t>
@@ -956,10 +1013,28 @@
     <t xml:space="preserve">TxDroppedPkts</t>
   </si>
   <si>
+    <t xml:space="preserve">RTOS Failures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTOSfailure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTOS Errs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REDFS Errors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REDFSIOerror</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RED File System Errors</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fill to 32-bits</t>
   </si>
   <si>
-    <t xml:space="preserve">pad362</t>
+    <t xml:space="preserve">pad7</t>
   </si>
   <si>
     <t xml:space="preserve">Unisgned</t>
@@ -1228,6 +1303,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1241,10 +1320,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2468,7 +2543,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="26" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C32" s="26" t="s">
         <v>85</v>
@@ -2481,13 +2556,13 @@
       </c>
       <c r="F32" s="21"/>
       <c r="G32" s="20" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H32" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I32" s="21" t="s">
         <v>86</v>
-      </c>
-      <c r="I32" s="21" t="s">
-        <v>87</v>
       </c>
       <c r="J32" s="4" t="n">
         <f aca="false">J31+D31</f>
@@ -2512,7 +2587,7 @@
         <v>5</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Q32" s="1" t="n">
         <v>0</v>
@@ -2520,10 +2595,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="26" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D33" s="26" t="n">
         <v>8</v>
@@ -2533,13 +2608,13 @@
       </c>
       <c r="F33" s="21"/>
       <c r="G33" s="20" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="I33" s="21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J33" s="4" t="n">
         <f aca="false">J32+D32</f>
@@ -2564,7 +2639,7 @@
         <v>6</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q33" s="1" t="n">
         <v>0</v>
@@ -2572,10 +2647,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="26" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D34" s="26" t="n">
         <v>8</v>
@@ -2585,13 +2660,13 @@
       </c>
       <c r="F34" s="21"/>
       <c r="G34" s="20" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="I34" s="21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J34" s="4" t="n">
         <f aca="false">J33+D33</f>
@@ -2616,7 +2691,7 @@
         <v>7</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Q34" s="1" t="n">
         <v>0</v>
@@ -2624,10 +2699,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="26" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D35" s="26" t="n">
         <v>8</v>
@@ -2637,13 +2712,13 @@
       </c>
       <c r="F35" s="21"/>
       <c r="G35" s="20" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="I35" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J35" s="4" t="n">
         <f aca="false">J34+D34</f>
@@ -2668,7 +2743,7 @@
         <v>8</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Q35" s="1" t="n">
         <v>0</v>
@@ -2676,10 +2751,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D36" s="26" t="n">
         <v>8</v>
@@ -2689,13 +2764,13 @@
       </c>
       <c r="F36" s="21"/>
       <c r="G36" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>96</v>
+        <v>6</v>
+      </c>
+      <c r="H36" s="20" t="s">
+        <v>94</v>
       </c>
       <c r="I36" s="21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J36" s="4" t="n">
         <f aca="false">J35+D35</f>
@@ -2714,13 +2789,13 @@
         <v>4.75</v>
       </c>
       <c r="N36" s="4" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="O36" s="22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q36" s="1" t="n">
         <v>0</v>
@@ -2728,10 +2803,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="26" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D37" s="26" t="n">
         <v>8</v>
@@ -2741,13 +2816,13 @@
       </c>
       <c r="F37" s="21"/>
       <c r="G37" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>96</v>
+        <v>6</v>
+      </c>
+      <c r="H37" s="20" t="s">
+        <v>94</v>
       </c>
       <c r="I37" s="21" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="J37" s="4" t="n">
         <f aca="false">J36+D36</f>
@@ -2766,13 +2841,13 @@
         <v>5</v>
       </c>
       <c r="N37" s="4" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="O37" s="22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q37" s="1" t="n">
         <v>0</v>
@@ -2780,10 +2855,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="26" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C38" s="26" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D38" s="26" t="n">
         <v>8</v>
@@ -2793,13 +2868,13 @@
       </c>
       <c r="F38" s="21"/>
       <c r="G38" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>96</v>
+        <v>6</v>
+      </c>
+      <c r="H38" s="20" t="s">
+        <v>94</v>
       </c>
       <c r="I38" s="21" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="J38" s="4" t="n">
         <f aca="false">J37+D37</f>
@@ -2818,31 +2893,40 @@
         <v>5.25</v>
       </c>
       <c r="N38" s="4" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O38" s="22" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q38" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="21"/>
+      <c r="B39" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="C39" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="D39" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>25</v>
+      </c>
       <c r="F39" s="21"/>
-      <c r="G39" s="21"/>
-      <c r="H39" s="21"/>
+      <c r="G39" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" s="20" t="s">
+        <v>94</v>
+      </c>
       <c r="I39" s="21" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J39" s="4" t="n">
         <f aca="false">J38+D38</f>
@@ -2860,458 +2944,515 @@
         <f aca="false">J39/32</f>
         <v>5.5</v>
       </c>
+      <c r="N39" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="O39" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="P39" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q39" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="26"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="21"/>
+      <c r="B40" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="C40" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="D40" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E40" s="21" t="s">
+        <v>25</v>
+      </c>
       <c r="F40" s="21"/>
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="25"/>
-      <c r="K40" s="25"/>
-      <c r="L40" s="25"/>
-      <c r="M40" s="25"/>
-    </row>
-    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B41" s="7" t="s">
+      <c r="G40" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I40" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <f aca="false">J39+D39</f>
+        <v>184</v>
+      </c>
+      <c r="K40" s="4" t="n">
+        <f aca="false">J40/8</f>
+        <v>23</v>
+      </c>
+      <c r="L40" s="4" t="n">
+        <f aca="false">J40/16</f>
+        <v>11.5</v>
+      </c>
+      <c r="M40" s="4" t="n">
+        <f aca="false">J40/32</f>
+        <v>5.75</v>
+      </c>
+      <c r="N40" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
-      <c r="I41" s="7"/>
+      <c r="O40" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P40" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="C41" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="D41" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E41" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" s="21"/>
+      <c r="G41" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I41" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="J41" s="4" t="n">
+        <f aca="false">J40+D40</f>
+        <v>192</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <f aca="false">J41/8</f>
+        <v>24</v>
+      </c>
+      <c r="L41" s="4" t="n">
+        <f aca="false">J41/16</f>
+        <v>12</v>
+      </c>
+      <c r="M41" s="4" t="n">
+        <f aca="false">J41/32</f>
+        <v>6</v>
+      </c>
+      <c r="N41" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="O41" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="P41" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q41" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="21"/>
+      <c r="B42" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="C42" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="D42" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E42" s="21" t="s">
+        <v>25</v>
+      </c>
       <c r="F42" s="21"/>
-      <c r="G42" s="21"/>
-      <c r="H42" s="21"/>
-      <c r="I42" s="21"/>
-      <c r="J42" s="25"/>
-      <c r="K42" s="25"/>
-      <c r="L42" s="25"/>
-      <c r="M42" s="25"/>
+      <c r="G42" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I42" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <f aca="false">J41+D41</f>
+        <v>200</v>
+      </c>
+      <c r="K42" s="4" t="n">
+        <f aca="false">J42/8</f>
+        <v>25</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <f aca="false">J42/16</f>
+        <v>12.5</v>
+      </c>
+      <c r="M42" s="4" t="n">
+        <f aca="false">J42/32</f>
+        <v>6.25</v>
+      </c>
+      <c r="N42" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="O42" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P42" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q42" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B43" s="26"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="21"/>
+      <c r="B43" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="C43" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="D43" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="E43" s="27"/>
       <c r="F43" s="21"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="21"/>
-      <c r="J43" s="25"/>
-      <c r="K43" s="25"/>
-      <c r="L43" s="25"/>
-      <c r="M43" s="25"/>
+      <c r="G43" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I43" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <f aca="false">J42+D42</f>
+        <v>208</v>
+      </c>
+      <c r="K43" s="4" t="n">
+        <f aca="false">J43/8</f>
+        <v>26</v>
+      </c>
+      <c r="L43" s="4" t="n">
+        <f aca="false">J43/16</f>
+        <v>13</v>
+      </c>
+      <c r="M43" s="4" t="n">
+        <f aca="false">J43/32</f>
+        <v>6.5</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O43" s="22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="C44" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="D44" s="26" t="n">
+      <c r="A44" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="26"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="21"/>
+      <c r="I44" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <f aca="false">J43+D43</f>
+        <v>224</v>
+      </c>
+      <c r="K44" s="4" t="n">
+        <f aca="false">J44/8</f>
+        <v>28</v>
+      </c>
+      <c r="L44" s="4" t="n">
+        <f aca="false">J44/16</f>
+        <v>14</v>
+      </c>
+      <c r="M44" s="4" t="n">
+        <f aca="false">J44/32</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="26"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="21"/>
+      <c r="J45" s="25"/>
+      <c r="K45" s="25"/>
+      <c r="L45" s="25"/>
+      <c r="M45" s="25"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B47" s="26"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="21"/>
+      <c r="G47" s="21"/>
+      <c r="H47" s="21"/>
+      <c r="I47" s="21"/>
+      <c r="J47" s="25"/>
+      <c r="K47" s="25"/>
+      <c r="L47" s="25"/>
+      <c r="M47" s="25"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B48" s="26"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="21"/>
+      <c r="F48" s="21"/>
+      <c r="G48" s="21"/>
+      <c r="H48" s="21"/>
+      <c r="I48" s="21"/>
+      <c r="J48" s="25"/>
+      <c r="K48" s="25"/>
+      <c r="L48" s="25"/>
+      <c r="M48" s="25"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="C49" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="D49" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="E44" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F44" s="21"/>
-      <c r="G44" s="20" t="n">
+      <c r="E49" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F49" s="21"/>
+      <c r="G49" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="I44" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="J44" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="25" t="n">
-        <f aca="false">J44/8</f>
-        <v>0</v>
-      </c>
-      <c r="L44" s="25" t="n">
-        <f aca="false">J44/16</f>
-        <v>0</v>
-      </c>
-      <c r="M44" s="25" t="n">
-        <f aca="false">J44/32</f>
-        <v>0</v>
-      </c>
-      <c r="N44" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="O44" s="22" t="n">
+      <c r="H49" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I49" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="J49" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="25" t="n">
+        <f aca="false">J49/8</f>
+        <v>0</v>
+      </c>
+      <c r="L49" s="25" t="n">
+        <f aca="false">J49/16</f>
+        <v>0</v>
+      </c>
+      <c r="M49" s="25" t="n">
+        <f aca="false">J49/32</f>
+        <v>0</v>
+      </c>
+      <c r="N49" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="O49" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="P44" s="1" t="n">
+      <c r="P49" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="Q44" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="C45" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="D45" s="26" t="n">
+      <c r="Q49" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="C50" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="D50" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="E45" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F45" s="21"/>
-      <c r="G45" s="20" t="n">
+      <c r="E50" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="21"/>
+      <c r="G50" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="I45" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="J45" s="4" t="n">
-        <f aca="false">J44+D44</f>
+      <c r="H50" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I50" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="J50" s="4" t="n">
+        <f aca="false">J49+D49</f>
         <v>1</v>
       </c>
-      <c r="K45" s="4" t="n">
-        <f aca="false">J45/8</f>
+      <c r="K50" s="4" t="n">
+        <f aca="false">J50/8</f>
         <v>0.125</v>
       </c>
-      <c r="L45" s="4" t="n">
-        <f aca="false">J45/16</f>
+      <c r="L50" s="4" t="n">
+        <f aca="false">J50/16</f>
         <v>0.0625</v>
       </c>
-      <c r="M45" s="4" t="n">
-        <f aca="false">J45/32</f>
+      <c r="M50" s="4" t="n">
+        <f aca="false">J50/32</f>
         <v>0.03125</v>
       </c>
-      <c r="N45" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="O45" s="22" t="n">
+      <c r="N50" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="O50" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="P45" s="1" t="n">
+      <c r="P50" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="Q45" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="C46" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="D46" s="26" t="n">
+      <c r="Q50" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="C51" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="D51" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="E46" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F46" s="21"/>
-      <c r="G46" s="20" t="n">
+      <c r="E51" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51" s="21"/>
+      <c r="G51" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="I46" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="J46" s="4" t="n">
-        <f aca="false">J45+D45</f>
+      <c r="H51" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I51" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="J51" s="4" t="n">
+        <f aca="false">J50+D50</f>
         <v>2</v>
       </c>
-      <c r="K46" s="4" t="n">
-        <f aca="false">J46/8</f>
+      <c r="K51" s="4" t="n">
+        <f aca="false">J51/8</f>
         <v>0.25</v>
       </c>
-      <c r="L46" s="4" t="n">
-        <f aca="false">J46/16</f>
+      <c r="L51" s="4" t="n">
+        <f aca="false">J51/16</f>
         <v>0.125</v>
       </c>
-      <c r="M46" s="4" t="n">
-        <f aca="false">J46/32</f>
+      <c r="M51" s="4" t="n">
+        <f aca="false">J51/32</f>
         <v>0.0625</v>
       </c>
-      <c r="N46" s="4" t="s">
+      <c r="N51" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="O46" s="22" t="n">
+      <c r="O51" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="P46" s="1" t="n">
+      <c r="P51" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="Q46" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="C47" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="D47" s="26" t="n">
+      <c r="Q51" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="C52" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="D52" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="E47" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F47" s="21"/>
-      <c r="G47" s="20" t="n">
+      <c r="E52" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F52" s="21"/>
+      <c r="G52" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="I47" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="J47" s="4" t="n">
-        <f aca="false">J46+D46</f>
-        <v>3</v>
-      </c>
-      <c r="K47" s="4" t="n">
-        <f aca="false">J47/8</f>
-        <v>0.375</v>
-      </c>
-      <c r="L47" s="4" t="n">
-        <f aca="false">J47/16</f>
-        <v>0.1875</v>
-      </c>
-      <c r="M47" s="4" t="n">
-        <f aca="false">J47/32</f>
-        <v>0.09375</v>
-      </c>
-      <c r="N47" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="O47" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="P47" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q47" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="C48" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="D48" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F48" s="21"/>
-      <c r="G48" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="I48" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="J48" s="4" t="n">
-        <f aca="false">J47+D47</f>
-        <v>4</v>
-      </c>
-      <c r="K48" s="4" t="n">
-        <f aca="false">J48/8</f>
-        <v>0.5</v>
-      </c>
-      <c r="L48" s="4" t="n">
-        <f aca="false">J48/16</f>
-        <v>0.25</v>
-      </c>
-      <c r="M48" s="4" t="n">
-        <f aca="false">J48/32</f>
-        <v>0.125</v>
-      </c>
-      <c r="N48" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="O48" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="P48" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q48" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="C49" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="D49" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="E49" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F49" s="20"/>
-      <c r="G49" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="I49" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="J49" s="4" t="n">
-        <f aca="false">J48+D48</f>
-        <v>5</v>
-      </c>
-      <c r="K49" s="4" t="n">
-        <f aca="false">J49/8</f>
-        <v>0.625</v>
-      </c>
-      <c r="L49" s="4" t="n">
-        <f aca="false">J49/16</f>
-        <v>0.3125</v>
-      </c>
-      <c r="M49" s="4" t="n">
-        <f aca="false">J49/32</f>
-        <v>0.15625</v>
-      </c>
-      <c r="N49" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O49" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B50" s="20"/>
-      <c r="C50" s="20"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
-      <c r="F50" s="20"/>
-      <c r="G50" s="20"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="21"/>
-      <c r="N50" s="4"/>
-      <c r="O50" s="22"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B51" s="20"/>
-      <c r="C51" s="20"/>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
-      <c r="F51" s="20"/>
-      <c r="G51" s="20"/>
-      <c r="H51" s="20"/>
-      <c r="I51" s="21"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="22"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="C52" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="D52" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="E52" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F52" s="20"/>
-      <c r="G52" s="20" t="n">
-        <v>0</v>
-      </c>
       <c r="H52" s="20" t="s">
         <v>34</v>
       </c>
       <c r="I52" s="21" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="J52" s="4" t="n">
         <f aca="false">J51+D51</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K52" s="4" t="n">
         <f aca="false">J52/8</f>
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="L52" s="4" t="n">
         <f aca="false">J52/16</f>
-        <v>0</v>
+        <v>0.1875</v>
       </c>
       <c r="M52" s="4" t="n">
         <f aca="false">J52/32</f>
-        <v>0</v>
+        <v>0.09375</v>
       </c>
       <c r="N52" s="4" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="O52" s="22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P52" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q52" s="1" t="n">
         <v>0</v>
@@ -3319,10 +3460,10 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="26" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="C53" s="26" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="D53" s="26" t="n">
         <v>1</v>
@@ -3338,23 +3479,23 @@
         <v>34</v>
       </c>
       <c r="I53" s="21" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="J53" s="4" t="n">
         <f aca="false">J52+D52</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K53" s="4" t="n">
         <f aca="false">J53/8</f>
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
       <c r="L53" s="4" t="n">
         <f aca="false">J53/16</f>
-        <v>0.1875</v>
+        <v>0.25</v>
       </c>
       <c r="M53" s="4" t="n">
         <f aca="false">J53/32</f>
-        <v>0.09375</v>
+        <v>0.125</v>
       </c>
       <c r="N53" s="4" t="s">
         <v>52</v>
@@ -3370,244 +3511,207 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="C54" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="D54" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F54" s="21"/>
+      <c r="B54" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="C54" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="D54" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" s="20"/>
       <c r="G54" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54" s="20" t="s">
         <v>34</v>
       </c>
       <c r="I54" s="21" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="J54" s="4" t="n">
         <f aca="false">J53+D53</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K54" s="4" t="n">
         <f aca="false">J54/8</f>
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="L54" s="4" t="n">
         <f aca="false">J54/16</f>
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="M54" s="4" t="n">
         <f aca="false">J54/32</f>
-        <v>0.125</v>
+        <v>0.15625</v>
       </c>
       <c r="N54" s="4" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="O54" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B55" s="20"/>
+      <c r="C55" s="20"/>
+      <c r="D55" s="20"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="20"/>
+      <c r="G55" s="20"/>
+      <c r="H55" s="20"/>
+      <c r="I55" s="21"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="22"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B56" s="20"/>
+      <c r="C56" s="20"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="20"/>
+      <c r="G56" s="20"/>
+      <c r="H56" s="20"/>
+      <c r="I56" s="21"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="22"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="C57" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="D57" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="P54" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q54" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="C55" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="D55" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F55" s="21"/>
-      <c r="G55" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="I55" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="J55" s="4" t="n">
-        <f aca="false">J54+D54</f>
-        <v>5</v>
-      </c>
-      <c r="K55" s="4" t="n">
-        <f aca="false">J55/8</f>
-        <v>0.625</v>
-      </c>
-      <c r="L55" s="4" t="n">
-        <f aca="false">J55/16</f>
-        <v>0.3125</v>
-      </c>
-      <c r="M55" s="4" t="n">
-        <f aca="false">J55/32</f>
-        <v>0.15625</v>
-      </c>
-      <c r="N55" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="O55" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="P55" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q55" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="C56" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="D56" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F56" s="21"/>
-      <c r="G56" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H56" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="I56" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="J56" s="4" t="n">
-        <f aca="false">J55+D55</f>
-        <v>6</v>
-      </c>
-      <c r="K56" s="4" t="n">
-        <f aca="false">J56/8</f>
-        <v>0.75</v>
-      </c>
-      <c r="L56" s="4" t="n">
-        <f aca="false">J56/16</f>
-        <v>0.375</v>
-      </c>
-      <c r="M56" s="4" t="n">
-        <f aca="false">J56/32</f>
-        <v>0.1875</v>
-      </c>
-      <c r="N56" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="O56" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="P56" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q56" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="C57" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="D57" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F57" s="21"/>
+      <c r="E57" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F57" s="20"/>
       <c r="G57" s="20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" s="20" t="s">
         <v>34</v>
       </c>
       <c r="I57" s="21" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="J57" s="4" t="n">
         <f aca="false">J56+D56</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K57" s="4" t="n">
         <f aca="false">J57/8</f>
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="L57" s="4" t="n">
         <f aca="false">J57/16</f>
-        <v>0.4375</v>
+        <v>0</v>
       </c>
       <c r="M57" s="4" t="n">
         <f aca="false">J57/32</f>
-        <v>0.21875</v>
+        <v>0</v>
       </c>
       <c r="N57" s="4" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="O57" s="22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q57" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B58" s="20"/>
-      <c r="C58" s="20"/>
-      <c r="D58" s="20"/>
-      <c r="E58" s="20"/>
-      <c r="F58" s="20"/>
-      <c r="G58" s="20"/>
-      <c r="H58" s="20"/>
-      <c r="I58" s="21"/>
-      <c r="N58" s="4"/>
-      <c r="O58" s="22"/>
+      <c r="B58" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="C58" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="D58" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" s="21"/>
+      <c r="G58" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I58" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="J58" s="4" t="n">
+        <f aca="false">J57+D57</f>
+        <v>3</v>
+      </c>
+      <c r="K58" s="4" t="n">
+        <f aca="false">J58/8</f>
+        <v>0.375</v>
+      </c>
+      <c r="L58" s="4" t="n">
+        <f aca="false">J58/16</f>
+        <v>0.1875</v>
+      </c>
+      <c r="M58" s="4" t="n">
+        <f aca="false">J58/32</f>
+        <v>0.09375</v>
+      </c>
+      <c r="N58" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O58" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P58" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q58" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="20" t="s">
+      <c r="B59" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="C59" s="20" t="s">
+      <c r="C59" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="D59" s="20" t="n">
-        <v>8</v>
+      <c r="D59" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="E59" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="F59" s="20"/>
+      <c r="F59" s="21"/>
       <c r="G59" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H59" s="20" t="s">
         <v>34</v>
@@ -3616,130 +3720,130 @@
         <v>131</v>
       </c>
       <c r="J59" s="4" t="n">
-        <f aca="false">J57+D57</f>
-        <v>8</v>
+        <f aca="false">J58+D58</f>
+        <v>4</v>
       </c>
       <c r="K59" s="4" t="n">
         <f aca="false">J59/8</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L59" s="4" t="n">
         <f aca="false">J59/16</f>
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="M59" s="4" t="n">
         <f aca="false">J59/32</f>
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="N59" s="4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="O59" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P59" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q59" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="C60" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="D60" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="P59" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q59" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="C60" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="D60" s="20" t="n">
-        <v>8</v>
-      </c>
       <c r="E60" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="F60" s="20"/>
+      <c r="F60" s="21"/>
       <c r="G60" s="20" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H60" s="20" t="s">
-        <v>134</v>
+        <v>34</v>
       </c>
       <c r="I60" s="21" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="J60" s="4" t="n">
         <f aca="false">J59+D59</f>
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="K60" s="4" t="n">
         <f aca="false">J60/8</f>
-        <v>2</v>
+        <v>0.625</v>
       </c>
       <c r="L60" s="4" t="n">
         <f aca="false">J60/16</f>
-        <v>1</v>
+        <v>0.3125</v>
       </c>
       <c r="M60" s="4" t="n">
         <f aca="false">J60/32</f>
-        <v>0.5</v>
+        <v>0.15625</v>
       </c>
       <c r="N60" s="4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="O60" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P60" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q60" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="C61" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="D61" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="P60" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q60" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="C61" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="D61" s="20" t="n">
-        <v>8</v>
-      </c>
       <c r="E61" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="F61" s="20"/>
+      <c r="F61" s="21"/>
       <c r="G61" s="20" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>134</v>
+        <v>34</v>
       </c>
       <c r="I61" s="21" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="J61" s="4" t="n">
         <f aca="false">J60+D60</f>
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="K61" s="4" t="n">
         <f aca="false">J61/8</f>
-        <v>3</v>
+        <v>0.75</v>
       </c>
       <c r="L61" s="4" t="n">
         <f aca="false">J61/16</f>
-        <v>1.5</v>
+        <v>0.375</v>
       </c>
       <c r="M61" s="4" t="n">
         <f aca="false">J61/32</f>
-        <v>0.75</v>
+        <v>0.1875</v>
       </c>
       <c r="N61" s="4" t="s">
-        <v>44</v>
+        <v>106</v>
       </c>
       <c r="O61" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P61" s="1" t="n">
         <v>3</v>
@@ -3749,115 +3853,78 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="C62" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="D62" s="20" t="n">
-        <v>8</v>
+      <c r="B62" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="C62" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="D62" s="26" t="n">
+        <v>1</v>
       </c>
       <c r="E62" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="F62" s="20"/>
+      <c r="F62" s="21"/>
       <c r="G62" s="20" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H62" s="20" t="s">
-        <v>134</v>
+        <v>34</v>
       </c>
       <c r="I62" s="21" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="J62" s="4" t="n">
         <f aca="false">J61+D61</f>
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="K62" s="4" t="n">
         <f aca="false">J62/8</f>
-        <v>4</v>
+        <v>0.875</v>
       </c>
       <c r="L62" s="4" t="n">
         <f aca="false">J62/16</f>
-        <v>2</v>
+        <v>0.4375</v>
       </c>
       <c r="M62" s="4" t="n">
         <f aca="false">J62/32</f>
-        <v>1</v>
+        <v>0.21875</v>
       </c>
       <c r="N62" s="4" t="s">
-        <v>44</v>
+        <v>106</v>
       </c>
       <c r="O62" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q62" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="C63" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="D63" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="E63" s="21" t="s">
-        <v>25</v>
-      </c>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B63" s="20"/>
+      <c r="C63" s="20"/>
+      <c r="D63" s="20"/>
+      <c r="E63" s="20"/>
       <c r="F63" s="20"/>
-      <c r="G63" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="H63" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="I63" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="J63" s="4" t="n">
-        <f aca="false">J62+D62</f>
-        <v>40</v>
-      </c>
-      <c r="K63" s="4" t="n">
-        <f aca="false">J63/8</f>
-        <v>5</v>
-      </c>
-      <c r="L63" s="4" t="n">
-        <f aca="false">J63/16</f>
-        <v>2.5</v>
-      </c>
-      <c r="M63" s="4" t="n">
-        <f aca="false">J63/32</f>
-        <v>1.25</v>
-      </c>
-      <c r="N63" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="O63" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P63" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q63" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G63" s="20"/>
+      <c r="H63" s="20"/>
+      <c r="I63" s="21"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="22"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="20" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D64" s="20" t="n">
         <v>8</v>
@@ -3867,29 +3934,29 @@
       </c>
       <c r="F64" s="20"/>
       <c r="G64" s="20" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H64" s="20" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="I64" s="21" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="J64" s="4" t="n">
-        <f aca="false">J63+D63</f>
-        <v>48</v>
+        <f aca="false">J62+D62</f>
+        <v>8</v>
       </c>
       <c r="K64" s="4" t="n">
         <f aca="false">J64/8</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L64" s="4" t="n">
         <f aca="false">J64/16</f>
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="M64" s="4" t="n">
         <f aca="false">J64/32</f>
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="N64" s="4" t="s">
         <v>44</v>
@@ -3898,18 +3965,18 @@
         <v>1</v>
       </c>
       <c r="P64" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q64" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="20" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D65" s="20" t="n">
         <v>8</v>
@@ -3922,35 +3989,35 @@
         <v>7</v>
       </c>
       <c r="H65" s="20" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="I65" s="21" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J65" s="4" t="n">
         <f aca="false">J64+D64</f>
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="K65" s="4" t="n">
         <f aca="false">J65/8</f>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L65" s="4" t="n">
         <f aca="false">J65/16</f>
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="M65" s="4" t="n">
         <f aca="false">J65/32</f>
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="N65" s="4" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="O65" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q65" s="1" t="n">
         <v>0</v>
@@ -3958,10 +4025,10 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="20" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D66" s="20" t="n">
         <v>8</v>
@@ -3974,35 +4041,35 @@
         <v>7</v>
       </c>
       <c r="H66" s="20" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="I66" s="21" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="J66" s="4" t="n">
         <f aca="false">J65+D65</f>
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="K66" s="4" t="n">
         <f aca="false">J66/8</f>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L66" s="4" t="n">
         <f aca="false">J66/16</f>
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="M66" s="4" t="n">
         <f aca="false">J66/32</f>
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="N66" s="4" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="O66" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="P66" s="1" t="n">
-        <v>9</v>
       </c>
       <c r="Q66" s="1" t="n">
         <v>0</v>
@@ -4010,10 +4077,10 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="20" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D67" s="20" t="n">
         <v>8</v>
@@ -4026,78 +4093,78 @@
         <v>7</v>
       </c>
       <c r="H67" s="20" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="I67" s="21" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="J67" s="4" t="n">
         <f aca="false">J66+D66</f>
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="K67" s="4" t="n">
         <f aca="false">J67/8</f>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L67" s="4" t="n">
         <f aca="false">J67/16</f>
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="M67" s="4" t="n">
         <f aca="false">J67/32</f>
-        <v>2.25</v>
+        <v>1</v>
       </c>
       <c r="N67" s="4" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="O67" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Q67" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="C68" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="D68" s="26" t="n">
+    <row r="68" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="C68" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="D68" s="20" t="n">
         <v>8</v>
       </c>
       <c r="E68" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="F68" s="21"/>
+        <v>25</v>
+      </c>
+      <c r="F68" s="20"/>
       <c r="G68" s="20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H68" s="20" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="I68" s="21" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="J68" s="4" t="n">
         <f aca="false">J67+D67</f>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="K68" s="4" t="n">
         <f aca="false">J68/8</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L68" s="4" t="n">
         <f aca="false">J68/16</f>
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M68" s="4" t="n">
         <f aca="false">J68/32</f>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="N68" s="4" t="s">
         <v>44</v>
@@ -4106,50 +4173,50 @@
         <v>1</v>
       </c>
       <c r="P68" s="1" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q68" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="C69" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="D69" s="26" t="n">
+      <c r="B69" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="C69" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="D69" s="20" t="n">
         <v>8</v>
       </c>
       <c r="E69" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="F69" s="21"/>
+      <c r="F69" s="20"/>
       <c r="G69" s="20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H69" s="20" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="I69" s="21" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="J69" s="4" t="n">
         <f aca="false">J68+D68</f>
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="K69" s="4" t="n">
         <f aca="false">J69/8</f>
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L69" s="4" t="n">
         <f aca="false">J69/16</f>
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="M69" s="4" t="n">
         <f aca="false">J69/32</f>
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="N69" s="4" t="s">
         <v>44</v>
@@ -4158,179 +4225,330 @@
         <v>1</v>
       </c>
       <c r="P69" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q69" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="26" t="s">
-        <v>163</v>
-      </c>
-      <c r="C70" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="D70" s="26" t="n">
-        <v>32</v>
+    <row r="70" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="C70" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="D70" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="E70" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="F70" s="21"/>
+      <c r="F70" s="20"/>
       <c r="G70" s="20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H70" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="I70" s="26" t="s">
-        <v>165</v>
+        <v>145</v>
+      </c>
+      <c r="I70" s="21" t="s">
+        <v>161</v>
       </c>
       <c r="J70" s="4" t="n">
         <f aca="false">J69+D69</f>
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="K70" s="4" t="n">
         <f aca="false">J70/8</f>
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L70" s="4" t="n">
         <f aca="false">J70/16</f>
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="M70" s="4" t="n">
         <f aca="false">J70/32</f>
+        <v>1.75</v>
+      </c>
+      <c r="N70" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O70" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="N70" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="O70" s="22" t="n">
-        <v>1</v>
-      </c>
       <c r="P70" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q70" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="C71" s="26" t="s">
-        <v>167</v>
-      </c>
-      <c r="D71" s="26" t="n">
+      <c r="B71" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="C71" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="D71" s="20" t="n">
         <v>8</v>
       </c>
       <c r="E71" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="F71" s="21"/>
+        <v>25</v>
+      </c>
+      <c r="F71" s="20"/>
       <c r="G71" s="20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H71" s="20" t="s">
-        <v>34</v>
+        <v>145</v>
       </c>
       <c r="I71" s="21" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J71" s="4" t="n">
         <f aca="false">J70+D70</f>
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="K71" s="4" t="n">
         <f aca="false">J71/8</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L71" s="4" t="n">
         <f aca="false">J71/16</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M71" s="4" t="n">
         <f aca="false">J71/32</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N71" s="4" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="O71" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q71" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="72" s="14" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B72" s="27"/>
-      <c r="C72" s="28"/>
-      <c r="D72" s="29"/>
-      <c r="E72" s="29"/>
-      <c r="F72" s="29"/>
-      <c r="G72" s="29"/>
-      <c r="H72" s="28"/>
-      <c r="I72" s="29" t="s">
-        <v>169</v>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B72" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="C72" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="D72" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="E72" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F72" s="20"/>
+      <c r="G72" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="H72" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="I72" s="21" t="s">
+        <v>167</v>
       </c>
       <c r="J72" s="4" t="n">
         <f aca="false">J71+D71</f>
-        <v>136</v>
+        <v>72</v>
       </c>
       <c r="K72" s="4" t="n">
         <f aca="false">J72/8</f>
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="L72" s="4" t="n">
         <f aca="false">J72/16</f>
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="M72" s="4" t="n">
         <f aca="false">J72/32</f>
-        <v>4.25</v>
-      </c>
-      <c r="O72" s="30"/>
+        <v>2.25</v>
+      </c>
+      <c r="N72" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O72" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P72" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q72" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="23"/>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
+      <c r="B73" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="C73" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="D73" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E73" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F73" s="21"/>
+      <c r="G73" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H73" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I73" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="J73" s="4" t="n">
+        <f aca="false">J72+D72</f>
+        <v>80</v>
+      </c>
+      <c r="K73" s="4" t="n">
+        <f aca="false">J73/8</f>
+        <v>10</v>
+      </c>
+      <c r="L73" s="4" t="n">
+        <f aca="false">J73/16</f>
+        <v>5</v>
+      </c>
+      <c r="M73" s="4" t="n">
+        <f aca="false">J73/32</f>
+        <v>2.5</v>
+      </c>
+      <c r="N73" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="O73" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P73" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q73" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B74" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="C74" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="D74" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E74" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F74" s="21"/>
+      <c r="G74" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H74" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I74" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="J74" s="4" t="n">
+        <f aca="false">J73+D73</f>
+        <v>88</v>
+      </c>
+      <c r="K74" s="4" t="n">
+        <f aca="false">J74/8</f>
+        <v>11</v>
+      </c>
+      <c r="L74" s="4" t="n">
+        <f aca="false">J74/16</f>
+        <v>5.5</v>
+      </c>
+      <c r="M74" s="4" t="n">
+        <f aca="false">J74/32</f>
+        <v>2.75</v>
+      </c>
+      <c r="N74" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="O74" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P74" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q74" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="B75" s="26"/>
-      <c r="C75" s="26"/>
-      <c r="D75" s="26"/>
-      <c r="E75" s="21"/>
+      <c r="B75" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="C75" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="D75" s="26" t="n">
+        <v>32</v>
+      </c>
+      <c r="E75" s="21" t="s">
+        <v>25</v>
+      </c>
       <c r="F75" s="21"/>
-      <c r="G75" s="21"/>
-      <c r="H75" s="21"/>
-      <c r="I75" s="21"/>
-      <c r="J75" s="25"/>
-      <c r="K75" s="25"/>
-      <c r="L75" s="25"/>
-      <c r="M75" s="25"/>
+      <c r="G75" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I75" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="J75" s="4" t="n">
+        <f aca="false">J74+D74</f>
+        <v>96</v>
+      </c>
+      <c r="K75" s="4" t="n">
+        <f aca="false">J75/8</f>
+        <v>12</v>
+      </c>
+      <c r="L75" s="4" t="n">
+        <f aca="false">J75/16</f>
+        <v>6</v>
+      </c>
+      <c r="M75" s="4" t="n">
+        <f aca="false">J75/32</f>
+        <v>3</v>
+      </c>
+      <c r="N75" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="O75" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q75" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="26" t="s">
-        <v>126</v>
+        <v>177</v>
       </c>
       <c r="C76" s="26" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D76" s="26" t="n">
         <v>8</v>
@@ -4339,361 +4557,383 @@
         <v>64</v>
       </c>
       <c r="F76" s="21"/>
-      <c r="G76" s="21" t="n">
+      <c r="G76" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="20" t="s">
         <v>34</v>
       </c>
       <c r="I76" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="J76" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" s="25" t="n">
+        <v>179</v>
+      </c>
+      <c r="J76" s="4" t="n">
+        <f aca="false">J75+D75</f>
+        <v>128</v>
+      </c>
+      <c r="K76" s="4" t="n">
         <f aca="false">J76/8</f>
-        <v>0</v>
-      </c>
-      <c r="L76" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="L76" s="4" t="n">
         <f aca="false">J76/16</f>
-        <v>0</v>
-      </c>
-      <c r="M76" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="M76" s="4" t="n">
         <f aca="false">J76/32</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N76" s="4" t="s">
-        <v>28</v>
+        <v>106</v>
       </c>
       <c r="O76" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P76" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q76" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="77" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B77" s="27"/>
-      <c r="C77" s="28"/>
-      <c r="D77" s="29"/>
-      <c r="E77" s="29"/>
-      <c r="F77" s="29"/>
-      <c r="G77" s="29"/>
-      <c r="H77" s="28"/>
-      <c r="I77" s="29" t="s">
-        <v>169</v>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="C77" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="D77" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E77" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F77" s="21"/>
+      <c r="G77" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I77" s="21" t="s">
+        <v>182</v>
       </c>
       <c r="J77" s="4" t="n">
         <f aca="false">J76+D76</f>
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="K77" s="4" t="n">
         <f aca="false">J77/8</f>
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L77" s="4" t="n">
         <f aca="false">J77/16</f>
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="M77" s="4" t="n">
         <f aca="false">J77/32</f>
-        <v>0.25</v>
-      </c>
-      <c r="O77" s="30"/>
-    </row>
-    <row r="78" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="27"/>
-      <c r="C78" s="28"/>
-      <c r="D78" s="29"/>
-      <c r="E78" s="29"/>
-      <c r="F78" s="29"/>
-      <c r="G78" s="29"/>
-      <c r="H78" s="28"/>
-      <c r="I78" s="29"/>
-      <c r="J78" s="25"/>
-      <c r="K78" s="25"/>
-      <c r="L78" s="25"/>
-      <c r="M78" s="25"/>
-      <c r="O78" s="30"/>
+        <v>4.25</v>
+      </c>
+      <c r="N77" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="O77" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P77" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q77" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="C78" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="D78" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E78" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F78" s="21"/>
+      <c r="G78" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I78" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="J78" s="4" t="n">
+        <f aca="false">J77+D77</f>
+        <v>144</v>
+      </c>
+      <c r="K78" s="4" t="n">
+        <f aca="false">J78/8</f>
+        <v>18</v>
+      </c>
+      <c r="L78" s="4" t="n">
+        <f aca="false">J78/16</f>
+        <v>9</v>
+      </c>
+      <c r="M78" s="4" t="n">
+        <f aca="false">J78/32</f>
+        <v>4.5</v>
+      </c>
+      <c r="N78" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="O78" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P78" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q78" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B79" s="23"/>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="C80" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="D80" s="24" t="n">
+      <c r="B79" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="C79" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="D79" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E79" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F79" s="21"/>
+      <c r="G79" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I79" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="J79" s="4" t="n">
+        <f aca="false">J78+D78</f>
+        <v>152</v>
+      </c>
+      <c r="K79" s="4" t="n">
+        <f aca="false">J79/8</f>
+        <v>19</v>
+      </c>
+      <c r="L79" s="4" t="n">
+        <f aca="false">J79/16</f>
+        <v>9.5</v>
+      </c>
+      <c r="M79" s="4" t="n">
+        <f aca="false">J79/32</f>
+        <v>4.75</v>
+      </c>
+      <c r="N79" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="O79" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P79" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q79" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" s="14" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B80" s="28"/>
+      <c r="C80" s="29"/>
+      <c r="D80" s="30"/>
+      <c r="E80" s="30"/>
+      <c r="F80" s="30"/>
+      <c r="G80" s="30"/>
+      <c r="H80" s="29"/>
+      <c r="I80" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="J80" s="4" t="n">
+        <f aca="false">J79+D79</f>
+        <v>160</v>
+      </c>
+      <c r="K80" s="4" t="n">
+        <f aca="false">J80/8</f>
+        <v>20</v>
+      </c>
+      <c r="L80" s="4" t="n">
+        <f aca="false">J80/16</f>
+        <v>10</v>
+      </c>
+      <c r="M80" s="4" t="n">
+        <f aca="false">J80/32</f>
+        <v>5</v>
+      </c>
+      <c r="O80" s="31"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="23"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B83" s="26"/>
+      <c r="C83" s="26"/>
+      <c r="D83" s="26"/>
+      <c r="E83" s="21"/>
+      <c r="F83" s="21"/>
+      <c r="G83" s="21"/>
+      <c r="H83" s="21"/>
+      <c r="I83" s="21"/>
+      <c r="J83" s="25"/>
+      <c r="K83" s="25"/>
+      <c r="L83" s="25"/>
+      <c r="M83" s="25"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="C84" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="D84" s="26" t="n">
         <v>32</v>
       </c>
-      <c r="E80" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="F80" s="21"/>
-      <c r="G80" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="I80" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="J80" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" s="25" t="n">
-        <f aca="false">J80/8</f>
-        <v>0</v>
-      </c>
-      <c r="L80" s="25" t="n">
-        <f aca="false">J80/16</f>
-        <v>0</v>
-      </c>
-      <c r="M80" s="25" t="n">
-        <f aca="false">J80/32</f>
-        <v>0</v>
-      </c>
-      <c r="N80" s="4" t="s">
+      <c r="E84" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F84" s="21"/>
+      <c r="G84" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I84" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="J84" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="25" t="n">
+        <f aca="false">J84/8</f>
+        <v>0</v>
+      </c>
+      <c r="L84" s="25" t="n">
+        <f aca="false">J84/16</f>
+        <v>0</v>
+      </c>
+      <c r="M84" s="25" t="n">
+        <f aca="false">J84/32</f>
+        <v>0</v>
+      </c>
+      <c r="N84" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O80" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="C81" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="D81" s="24" t="n">
-        <v>16</v>
-      </c>
-      <c r="E81" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F81" s="21"/>
-      <c r="G81" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="J81" s="4" t="n">
-        <f aca="false">J80+D80</f>
+      <c r="O84" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B85" s="28"/>
+      <c r="C85" s="29"/>
+      <c r="D85" s="30"/>
+      <c r="E85" s="30"/>
+      <c r="F85" s="30"/>
+      <c r="G85" s="30"/>
+      <c r="H85" s="29"/>
+      <c r="I85" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="J85" s="4" t="n">
+        <f aca="false">J84+D84</f>
         <v>32</v>
       </c>
-      <c r="K81" s="4" t="n">
-        <f aca="false">J81/8</f>
+      <c r="K85" s="4" t="n">
+        <f aca="false">J85/8</f>
         <v>4</v>
       </c>
-      <c r="L81" s="4" t="n">
-        <f aca="false">J81/16</f>
+      <c r="L85" s="4" t="n">
+        <f aca="false">J85/16</f>
         <v>2</v>
       </c>
-      <c r="M81" s="4" t="n">
-        <f aca="false">J81/32</f>
+      <c r="M85" s="4" t="n">
+        <f aca="false">J85/32</f>
         <v>1</v>
       </c>
-      <c r="N81" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O81" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="C82" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="D82" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="E82" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="F82" s="21"/>
-      <c r="G82" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="I82" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="J82" s="4" t="n">
-        <f aca="false">J81+D81</f>
-        <v>48</v>
-      </c>
-      <c r="K82" s="4" t="n">
-        <f aca="false">J82/8</f>
-        <v>6</v>
-      </c>
-      <c r="L82" s="4" t="n">
-        <f aca="false">J82/16</f>
-        <v>3</v>
-      </c>
-      <c r="M82" s="4" t="n">
-        <f aca="false">J82/32</f>
-        <v>1.5</v>
-      </c>
-      <c r="N82" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O82" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="C83" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="D83" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="E83" s="31"/>
-      <c r="F83" s="21"/>
-      <c r="G83" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="I83" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="J83" s="4" t="n">
-        <f aca="false">J82+D82</f>
-        <v>56</v>
-      </c>
-      <c r="K83" s="4" t="n">
-        <f aca="false">J83/8</f>
-        <v>7</v>
-      </c>
-      <c r="L83" s="4" t="n">
-        <f aca="false">J83/16</f>
-        <v>3.5</v>
-      </c>
-      <c r="M83" s="4" t="n">
-        <f aca="false">J83/32</f>
-        <v>1.75</v>
-      </c>
-      <c r="N83" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O83" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B84" s="23"/>
-      <c r="C84" s="28"/>
-      <c r="D84" s="29"/>
-      <c r="E84" s="29"/>
-      <c r="F84" s="29"/>
-      <c r="G84" s="29"/>
-      <c r="H84" s="28"/>
-      <c r="I84" s="29" t="s">
-        <v>169</v>
-      </c>
-      <c r="J84" s="4" t="n">
-        <f aca="false">J83+D83</f>
-        <v>64</v>
-      </c>
-      <c r="K84" s="4" t="n">
-        <f aca="false">J84/8</f>
-        <v>8</v>
-      </c>
-      <c r="L84" s="4" t="n">
-        <f aca="false">J84/16</f>
-        <v>4</v>
-      </c>
-      <c r="M84" s="4" t="n">
-        <f aca="false">J84/32</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="23"/>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="23"/>
+      <c r="O85" s="31"/>
+    </row>
+    <row r="86" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="28"/>
+      <c r="C86" s="29"/>
+      <c r="D86" s="30"/>
+      <c r="E86" s="30"/>
+      <c r="F86" s="30"/>
+      <c r="G86" s="30"/>
+      <c r="H86" s="29"/>
+      <c r="I86" s="30"/>
+      <c r="J86" s="25"/>
+      <c r="K86" s="25"/>
+      <c r="L86" s="25"/>
+      <c r="M86" s="25"/>
+      <c r="O86" s="31"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B87" s="23"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="26" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C88" s="26" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D88" s="24" t="n">
         <v>32</v>
       </c>
-      <c r="E88" s="31"/>
+      <c r="E88" s="27" t="s">
+        <v>195</v>
+      </c>
       <c r="F88" s="21"/>
       <c r="G88" s="20" t="n">
         <v>0</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="I88" s="25" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="J88" s="25" t="n">
         <v>0</v>
@@ -4725,15 +4965,15 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="26" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="C89" s="26" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="D89" s="24" t="n">
         <v>16</v>
       </c>
-      <c r="E89" s="31" t="s">
+      <c r="E89" s="27" t="s">
         <v>25</v>
       </c>
       <c r="F89" s="21"/>
@@ -4741,7 +4981,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="25" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="J89" s="4" t="n">
         <f aca="false">J88+D88</f>
@@ -4774,21 +5014,26 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="26" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="C90" s="26" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="D90" s="24" t="n">
-        <v>16</v>
-      </c>
-      <c r="E90" s="31"/>
+        <v>8</v>
+      </c>
+      <c r="E90" s="27" t="s">
+        <v>195</v>
+      </c>
       <c r="F90" s="21"/>
       <c r="G90" s="20" t="n">
         <v>0</v>
       </c>
+      <c r="H90" s="20" t="s">
+        <v>34</v>
+      </c>
       <c r="I90" s="25" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="J90" s="4" t="n">
         <f aca="false">J89+D89</f>
@@ -4821,37 +5066,40 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="26" t="s">
-        <v>195</v>
+        <v>113</v>
       </c>
       <c r="C91" s="26" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="D91" s="24" t="n">
-        <v>32</v>
-      </c>
-      <c r="E91" s="31"/>
+        <v>8</v>
+      </c>
+      <c r="E91" s="27"/>
       <c r="F91" s="21"/>
       <c r="G91" s="20" t="n">
         <v>0</v>
       </c>
+      <c r="H91" s="20" t="s">
+        <v>34</v>
+      </c>
       <c r="I91" s="25" t="s">
-        <v>197</v>
+        <v>115</v>
       </c>
       <c r="J91" s="4" t="n">
         <f aca="false">J90+D90</f>
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="K91" s="4" t="n">
         <f aca="false">J91/8</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L91" s="4" t="n">
         <f aca="false">J91/16</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="M91" s="4" t="n">
         <f aca="false">J91/32</f>
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="N91" s="4" t="s">
         <v>28</v>
@@ -4867,202 +5115,235 @@
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B92" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="C92" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="D92" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="E92" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="F92" s="21"/>
-      <c r="G92" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="I92" s="25" t="s">
-        <v>200</v>
+      <c r="A92" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B92" s="23"/>
+      <c r="C92" s="29"/>
+      <c r="D92" s="30"/>
+      <c r="E92" s="30"/>
+      <c r="F92" s="30"/>
+      <c r="G92" s="30"/>
+      <c r="H92" s="29"/>
+      <c r="I92" s="30" t="s">
+        <v>189</v>
       </c>
       <c r="J92" s="4" t="n">
         <f aca="false">J91+D91</f>
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="K92" s="4" t="n">
         <f aca="false">J92/8</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L92" s="4" t="n">
         <f aca="false">J92/16</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M92" s="4" t="n">
         <f aca="false">J92/32</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B93" s="23"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B94" s="23"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B95" s="23"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B96" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="C96" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="D96" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="E96" s="27"/>
+      <c r="F96" s="21"/>
+      <c r="G96" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="I96" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="J96" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="25" t="n">
+        <f aca="false">J96/8</f>
+        <v>0</v>
+      </c>
+      <c r="L96" s="25" t="n">
+        <f aca="false">J96/16</f>
+        <v>0</v>
+      </c>
+      <c r="M96" s="25" t="n">
+        <f aca="false">J96/32</f>
+        <v>0</v>
+      </c>
+      <c r="N96" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O96" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B97" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="C97" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="D97" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="E97" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F97" s="21"/>
+      <c r="G97" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="J97" s="4" t="n">
+        <f aca="false">J96+D96</f>
+        <v>32</v>
+      </c>
+      <c r="K97" s="4" t="n">
+        <f aca="false">J97/8</f>
+        <v>4</v>
+      </c>
+      <c r="L97" s="4" t="n">
+        <f aca="false">J97/16</f>
+        <v>2</v>
+      </c>
+      <c r="M97" s="4" t="n">
+        <f aca="false">J97/32</f>
+        <v>1</v>
+      </c>
+      <c r="N97" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B98" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="C98" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="D98" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="E98" s="27"/>
+      <c r="F98" s="21"/>
+      <c r="G98" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="J98" s="4" t="n">
+        <f aca="false">J97+D97</f>
+        <v>48</v>
+      </c>
+      <c r="K98" s="4" t="n">
+        <f aca="false">J98/8</f>
+        <v>6</v>
+      </c>
+      <c r="L98" s="4" t="n">
+        <f aca="false">J98/16</f>
         <v>3</v>
       </c>
-      <c r="N92" s="4" t="s">
+      <c r="M98" s="4" t="n">
+        <f aca="false">J98/32</f>
+        <v>1.5</v>
+      </c>
+      <c r="N98" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="O92" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B93" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="C93" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="D93" s="24" t="n">
-        <v>24</v>
-      </c>
-      <c r="E93" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="F93" s="21"/>
-      <c r="G93" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="I93" s="25"/>
-      <c r="J93" s="4" t="n">
-        <f aca="false">J92+D92</f>
-        <v>104</v>
-      </c>
-      <c r="K93" s="4" t="n">
-        <f aca="false">J93/8</f>
-        <v>13</v>
-      </c>
-      <c r="L93" s="4" t="n">
-        <f aca="false">J93/16</f>
-        <v>6.5</v>
-      </c>
-      <c r="M93" s="4" t="n">
-        <f aca="false">J93/32</f>
-        <v>3.25</v>
-      </c>
-      <c r="N93" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O93" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B94" s="27"/>
-      <c r="C94" s="28"/>
-      <c r="D94" s="29"/>
-      <c r="E94" s="29"/>
-      <c r="F94" s="29"/>
-      <c r="G94" s="29"/>
-      <c r="H94" s="28"/>
-      <c r="I94" s="29" t="s">
-        <v>169</v>
-      </c>
-      <c r="J94" s="4" t="n">
-        <f aca="false">J93+D93</f>
-        <v>128</v>
-      </c>
-      <c r="K94" s="4" t="n">
-        <f aca="false">J94/8</f>
-        <v>16</v>
-      </c>
-      <c r="L94" s="4" t="n">
-        <f aca="false">J94/16</f>
-        <v>8</v>
-      </c>
-      <c r="M94" s="4" t="n">
-        <f aca="false">J94/32</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B95" s="23"/>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B96" s="23"/>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B97" s="23"/>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B98" s="23"/>
+      <c r="O98" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B99" s="26" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C99" s="26" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="D99" s="24" t="n">
         <v>32</v>
       </c>
-      <c r="E99" s="31" t="s">
-        <v>25</v>
-      </c>
+      <c r="E99" s="27"/>
       <c r="F99" s="21"/>
       <c r="G99" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H99" s="32" t="s">
-        <v>176</v>
-      </c>
       <c r="I99" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="J99" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" s="25" t="n">
+        <v>215</v>
+      </c>
+      <c r="J99" s="4" t="n">
+        <f aca="false">J98+D98</f>
+        <v>64</v>
+      </c>
+      <c r="K99" s="4" t="n">
         <f aca="false">J99/8</f>
-        <v>0</v>
-      </c>
-      <c r="L99" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="L99" s="4" t="n">
         <f aca="false">J99/16</f>
-        <v>0</v>
-      </c>
-      <c r="M99" s="25" t="n">
+        <v>4</v>
+      </c>
+      <c r="M99" s="4" t="n">
         <f aca="false">J99/32</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N99" s="4" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="O99" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P99" s="1" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q99" s="1" t="n">
         <v>0</v>
@@ -5070,51 +5351,51 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="26" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="C100" s="26" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="D100" s="24" t="n">
-        <v>16</v>
-      </c>
-      <c r="E100" s="31" t="s">
-        <v>25</v>
+        <v>8</v>
+      </c>
+      <c r="E100" s="27" t="s">
+        <v>195</v>
       </c>
       <c r="F100" s="21"/>
       <c r="G100" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H100" s="32" t="s">
+      <c r="H100" s="20" t="s">
         <v>34</v>
       </c>
       <c r="I100" s="25" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="J100" s="4" t="n">
         <f aca="false">J99+D99</f>
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="K100" s="4" t="n">
         <f aca="false">J100/8</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L100" s="4" t="n">
         <f aca="false">J100/16</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M100" s="4" t="n">
         <f aca="false">J100/32</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N100" s="4" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="O100" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P100" s="1" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q100" s="1" t="n">
         <v>0</v>
@@ -5122,16 +5403,16 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B101" s="26" t="s">
-        <v>208</v>
+        <v>113</v>
       </c>
       <c r="C101" s="26" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="D101" s="24" t="n">
-        <v>8</v>
-      </c>
-      <c r="E101" s="31" t="s">
-        <v>25</v>
+        <v>24</v>
+      </c>
+      <c r="E101" s="27" t="s">
+        <v>64</v>
       </c>
       <c r="F101" s="21"/>
       <c r="G101" s="20" t="n">
@@ -5140,33 +5421,31 @@
       <c r="H101" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="I101" s="25" t="s">
-        <v>210</v>
-      </c>
+      <c r="I101" s="25"/>
       <c r="J101" s="4" t="n">
         <f aca="false">J100+D100</f>
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="K101" s="4" t="n">
         <f aca="false">J101/8</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="L101" s="4" t="n">
         <f aca="false">J101/16</f>
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="M101" s="4" t="n">
         <f aca="false">J101/32</f>
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="N101" s="4" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="O101" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P101" s="1" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q101" s="1" t="n">
         <v>0</v>
@@ -5176,119 +5455,73 @@
       <c r="A102" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B102" s="26"/>
-      <c r="I102" s="1" t="s">
-        <v>105</v>
+      <c r="B102" s="28"/>
+      <c r="C102" s="29"/>
+      <c r="D102" s="30"/>
+      <c r="E102" s="30"/>
+      <c r="F102" s="30"/>
+      <c r="G102" s="30"/>
+      <c r="H102" s="29"/>
+      <c r="I102" s="30" t="s">
+        <v>189</v>
       </c>
       <c r="J102" s="4" t="n">
         <f aca="false">J101+D101</f>
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="K102" s="4" t="n">
         <f aca="false">J102/8</f>
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="L102" s="4" t="n">
         <f aca="false">J102/16</f>
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="M102" s="4" t="n">
         <f aca="false">J102/32</f>
-        <v>1.75</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B103" s="26"/>
-      <c r="J103" s="25"/>
-      <c r="K103" s="25"/>
-      <c r="L103" s="25"/>
-      <c r="M103" s="25"/>
+      <c r="B103" s="23"/>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B104" s="23"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="J105" s="34"/>
-      <c r="K105" s="25"/>
-      <c r="L105" s="25"/>
-      <c r="M105" s="25"/>
-      <c r="N105" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="106" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B106" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C106" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D106" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E106" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F106" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G106" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="H106" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="I106" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J106" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="K106" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="L106" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="M106" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="N106" s="4"/>
-      <c r="O106" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="P106" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q106" s="14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="107" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B107" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="C107" s="36" t="s">
-        <v>213</v>
-      </c>
-      <c r="D107" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="E107" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F107" s="37"/>
-      <c r="G107" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="H107" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I107" s="31" t="s">
-        <v>214</v>
+      <c r="A105" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B105" s="23"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B106" s="23"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B107" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="C107" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="D107" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="E107" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F107" s="21"/>
+      <c r="G107" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="I107" s="25" t="s">
+        <v>223</v>
       </c>
       <c r="J107" s="25" t="n">
         <v>0</v>
@@ -5306,845 +5539,716 @@
         <v>0</v>
       </c>
       <c r="N107" s="4" t="s">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="O107" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P107" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q107" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="108" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B108" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="C108" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="D108" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E108" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F108" s="37"/>
-      <c r="G108" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="H108" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I108" s="31" t="s">
-        <v>214</v>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B108" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="C108" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="D108" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="E108" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F108" s="21"/>
+      <c r="G108" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="I108" s="25" t="s">
+        <v>223</v>
       </c>
       <c r="J108" s="4" t="n">
         <f aca="false">J107+D107</f>
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="K108" s="4" t="n">
         <f aca="false">J108/8</f>
-        <v>1.125</v>
+        <v>4</v>
       </c>
       <c r="L108" s="4" t="n">
         <f aca="false">J108/16</f>
-        <v>0.5625</v>
+        <v>2</v>
       </c>
       <c r="M108" s="4" t="n">
         <f aca="false">J108/32</f>
-        <v>0.28125</v>
+        <v>1</v>
       </c>
       <c r="N108" s="4" t="s">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="O108" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P108" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Q108" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="109" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B109" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="C109" s="36" t="s">
-        <v>218</v>
-      </c>
-      <c r="D109" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E109" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F109" s="37"/>
-      <c r="G109" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="H109" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I109" s="31" t="s">
-        <v>219</v>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B109" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="C109" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="D109" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E109" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F109" s="21"/>
+      <c r="G109" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I109" s="25" t="s">
+        <v>228</v>
       </c>
       <c r="J109" s="4" t="n">
         <f aca="false">J108+D108</f>
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="K109" s="4" t="n">
         <f aca="false">J109/8</f>
-        <v>1.75</v>
+        <v>6</v>
       </c>
       <c r="L109" s="4" t="n">
         <f aca="false">J109/16</f>
-        <v>0.875</v>
+        <v>3</v>
       </c>
       <c r="M109" s="4" t="n">
         <f aca="false">J109/32</f>
-        <v>0.4375</v>
+        <v>1.5</v>
       </c>
       <c r="N109" s="4" t="s">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="O109" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P109" s="1" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q109" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="110" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B110" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="C110" s="36" t="s">
-        <v>221</v>
-      </c>
-      <c r="D110" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E110" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F110" s="37"/>
-      <c r="G110" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="H110" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I110" s="31" t="s">
-        <v>222</v>
-      </c>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B110" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="C110" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="D110" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E110" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="F110" s="21"/>
+      <c r="G110" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="I110" s="25"/>
       <c r="J110" s="4" t="n">
         <f aca="false">J109+D109</f>
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="K110" s="4" t="n">
         <f aca="false">J110/8</f>
-        <v>2.25</v>
+        <v>7</v>
       </c>
       <c r="L110" s="4" t="n">
         <f aca="false">J110/16</f>
-        <v>1.125</v>
+        <v>3.5</v>
       </c>
       <c r="M110" s="4" t="n">
         <f aca="false">J110/32</f>
-        <v>0.5625</v>
+        <v>1.75</v>
       </c>
       <c r="N110" s="4" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="O110" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="P110" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q110" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B111" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="C111" s="36" t="s">
-        <v>224</v>
-      </c>
-      <c r="D111" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E111" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F111" s="37"/>
-      <c r="G111" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H111" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I111" s="20" t="s">
-        <v>225</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B111" s="26"/>
+      <c r="I111" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="J111" s="4" t="n">
         <f aca="false">J110+D110</f>
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="K111" s="4" t="n">
         <f aca="false">J111/8</f>
-        <v>2.75</v>
+        <v>8</v>
       </c>
       <c r="L111" s="4" t="n">
         <f aca="false">J111/16</f>
-        <v>1.375</v>
+        <v>4</v>
       </c>
       <c r="M111" s="4" t="n">
         <f aca="false">J111/32</f>
-        <v>0.6875</v>
-      </c>
-      <c r="N111" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="O111" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="P111" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q111" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B112" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="C112" s="36" t="s">
-        <v>227</v>
-      </c>
-      <c r="D112" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E112" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F112" s="37"/>
-      <c r="G112" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H112" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I112" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="J112" s="4" t="n">
-        <f aca="false">J111+D111</f>
-        <v>25</v>
-      </c>
-      <c r="K112" s="4" t="n">
-        <f aca="false">J112/8</f>
-        <v>3.125</v>
-      </c>
-      <c r="L112" s="4" t="n">
-        <f aca="false">J112/16</f>
-        <v>1.5625</v>
-      </c>
-      <c r="M112" s="4" t="n">
-        <f aca="false">J112/32</f>
-        <v>0.78125</v>
-      </c>
-      <c r="N112" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="O112" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="P112" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q112" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B113" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="C113" s="36" t="s">
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="33" t="s">
         <v>230</v>
       </c>
-      <c r="D113" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E113" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F113" s="37"/>
-      <c r="G113" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H113" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I113" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="J113" s="4" t="n">
-        <f aca="false">J112+D112</f>
-        <v>26</v>
-      </c>
-      <c r="K113" s="4" t="n">
-        <f aca="false">J113/8</f>
-        <v>3.25</v>
-      </c>
-      <c r="L113" s="4" t="n">
-        <f aca="false">J113/16</f>
-        <v>1.625</v>
-      </c>
-      <c r="M113" s="4" t="n">
-        <f aca="false">J113/32</f>
-        <v>0.8125</v>
-      </c>
-      <c r="N113" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="O113" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="P113" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q113" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B114" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="C114" s="36" t="s">
-        <v>232</v>
-      </c>
-      <c r="D114" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E114" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F114" s="37"/>
-      <c r="G114" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H114" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I114" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="J114" s="4" t="n">
-        <f aca="false">J113+D113</f>
-        <v>27</v>
-      </c>
-      <c r="K114" s="4" t="n">
-        <f aca="false">J114/8</f>
-        <v>3.375</v>
-      </c>
-      <c r="L114" s="4" t="n">
-        <f aca="false">J114/16</f>
-        <v>1.6875</v>
-      </c>
-      <c r="M114" s="4" t="n">
-        <f aca="false">J114/32</f>
-        <v>0.84375</v>
-      </c>
-      <c r="N114" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="O114" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P114" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q114" s="1" t="n">
-        <v>0</v>
+      <c r="J113" s="34"/>
+      <c r="K113" s="25"/>
+      <c r="L113" s="25"/>
+      <c r="M113" s="25"/>
+      <c r="N113" s="18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114" s="14" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B114" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C114" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D114" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E114" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F114" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G114" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H114" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I114" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J114" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="K114" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L114" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="M114" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="N114" s="4"/>
+      <c r="O114" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="P114" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q114" s="14" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="115" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B115" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="C115" s="36" t="s">
+        <v>232</v>
+      </c>
+      <c r="D115" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="E115" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F115" s="37"/>
+      <c r="G115" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H115" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I115" s="27" t="s">
         <v>233</v>
       </c>
-      <c r="C115" s="36" t="s">
-        <v>234</v>
-      </c>
-      <c r="D115" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="E115" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F115" s="37"/>
-      <c r="G115" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H115" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I115" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="J115" s="4" t="n">
-        <f aca="false">J114+D114</f>
-        <v>32</v>
-      </c>
-      <c r="K115" s="4" t="n">
+      <c r="J115" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="25" t="n">
         <f aca="false">J115/8</f>
-        <v>4</v>
-      </c>
-      <c r="L115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="25" t="n">
         <f aca="false">J115/16</f>
-        <v>2</v>
-      </c>
-      <c r="M115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="25" t="n">
         <f aca="false">J115/32</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N115" s="4" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="O115" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P115" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q115" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B116" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="C116" s="36" t="s">
         <v>235</v>
       </c>
-      <c r="C116" s="20" t="s">
-        <v>236</v>
-      </c>
       <c r="D116" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="E116" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="F116" s="31"/>
-      <c r="G116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I116" s="31" t="s">
-        <v>214</v>
+        <v>5</v>
+      </c>
+      <c r="E116" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F116" s="37"/>
+      <c r="G116" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H116" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I116" s="27" t="s">
+        <v>233</v>
       </c>
       <c r="J116" s="4" t="n">
         <f aca="false">J115+D115</f>
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="K116" s="4" t="n">
         <f aca="false">J116/8</f>
-        <v>8</v>
+        <v>1.125</v>
       </c>
       <c r="L116" s="4" t="n">
         <f aca="false">J116/16</f>
-        <v>4</v>
+        <v>0.5625</v>
       </c>
       <c r="M116" s="4" t="n">
         <f aca="false">J116/32</f>
+        <v>0.28125</v>
+      </c>
+      <c r="N116" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="O116" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="N116" s="4" t="s">
+      <c r="P116" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q116" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B117" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="C117" s="36" t="s">
         <v>237</v>
       </c>
-      <c r="O116" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="P116" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q116" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B117" s="20" t="s">
+      <c r="D117" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="E117" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F117" s="37"/>
+      <c r="G117" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H117" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I117" s="27" t="s">
         <v>238</v>
-      </c>
-      <c r="C117" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="D117" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="E117" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F117" s="31"/>
-      <c r="G117" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H117" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I117" s="31" t="s">
-        <v>214</v>
       </c>
       <c r="J117" s="4" t="n">
         <f aca="false">J116+D116</f>
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="K117" s="4" t="n">
         <f aca="false">J117/8</f>
-        <v>12</v>
+        <v>1.75</v>
       </c>
       <c r="L117" s="4" t="n">
         <f aca="false">J117/16</f>
-        <v>6</v>
+        <v>0.875</v>
       </c>
       <c r="M117" s="4" t="n">
         <f aca="false">J117/32</f>
+        <v>0.4375</v>
+      </c>
+      <c r="N117" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="O117" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P117" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="N117" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="O117" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="P117" s="1" t="n">
+      <c r="Q117" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B118" s="20" t="s">
+        <v>239</v>
+      </c>
+      <c r="C118" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="D118" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="E118" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F118" s="37"/>
+      <c r="G118" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="Q117" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B118" s="20" t="s">
-        <v>240</v>
-      </c>
-      <c r="C118" s="20" t="s">
+      <c r="H118" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I118" s="27" t="s">
         <v>241</v>
-      </c>
-      <c r="D118" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="E118" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="F118" s="31"/>
-      <c r="G118" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I118" s="31" t="s">
-        <v>214</v>
       </c>
       <c r="J118" s="4" t="n">
         <f aca="false">J117+D117</f>
-        <v>128</v>
+        <v>18</v>
       </c>
       <c r="K118" s="4" t="n">
         <f aca="false">J118/8</f>
-        <v>16</v>
+        <v>2.25</v>
       </c>
       <c r="L118" s="4" t="n">
         <f aca="false">J118/16</f>
-        <v>8</v>
+        <v>1.125</v>
       </c>
       <c r="M118" s="4" t="n">
         <f aca="false">J118/32</f>
+        <v>0.5625</v>
+      </c>
+      <c r="N118" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="O118" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P118" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="N118" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="O118" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="P118" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="Q118" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B119" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="C119" s="20" t="s">
+      <c r="C119" s="36" t="s">
         <v>243</v>
       </c>
       <c r="D119" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="E119" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F119" s="31"/>
+        <v>3</v>
+      </c>
+      <c r="E119" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F119" s="37"/>
       <c r="G119" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I119" s="31" t="s">
-        <v>214</v>
+        <v>2</v>
+      </c>
+      <c r="H119" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I119" s="20" t="s">
+        <v>244</v>
       </c>
       <c r="J119" s="4" t="n">
         <f aca="false">J118+D118</f>
-        <v>160</v>
+        <v>22</v>
       </c>
       <c r="K119" s="4" t="n">
         <f aca="false">J119/8</f>
-        <v>20</v>
+        <v>2.75</v>
       </c>
       <c r="L119" s="4" t="n">
         <f aca="false">J119/16</f>
-        <v>10</v>
+        <v>1.375</v>
       </c>
       <c r="M119" s="4" t="n">
         <f aca="false">J119/32</f>
+        <v>0.6875</v>
+      </c>
+      <c r="N119" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="O119" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P119" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="N119" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="O119" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="P119" s="1" t="n">
-        <v>4</v>
-      </c>
       <c r="Q119" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B120" s="20" t="s">
-        <v>244</v>
-      </c>
-      <c r="C120" s="20" t="s">
         <v>245</v>
       </c>
+      <c r="C120" s="36" t="s">
+        <v>246</v>
+      </c>
       <c r="D120" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E120" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F120" s="31"/>
+        <v>1</v>
+      </c>
+      <c r="E120" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F120" s="37"/>
       <c r="G120" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I120" s="31" t="s">
-        <v>246</v>
+        <v>2</v>
+      </c>
+      <c r="H120" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I120" s="20" t="s">
+        <v>247</v>
       </c>
       <c r="J120" s="4" t="n">
         <f aca="false">J119+D119</f>
-        <v>192</v>
+        <v>25</v>
       </c>
       <c r="K120" s="4" t="n">
         <f aca="false">J120/8</f>
-        <v>24</v>
+        <v>3.125</v>
       </c>
       <c r="L120" s="4" t="n">
         <f aca="false">J120/16</f>
-        <v>12</v>
+        <v>1.5625</v>
       </c>
       <c r="M120" s="4" t="n">
         <f aca="false">J120/32</f>
+        <v>0.78125</v>
+      </c>
+      <c r="N120" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="O120" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P120" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="N120" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="O120" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="P120" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="Q120" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B121" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="C121" s="20" t="s">
+      <c r="C121" s="36" t="s">
         <v>249</v>
       </c>
       <c r="D121" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E121" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F121" s="31"/>
+        <v>1</v>
+      </c>
+      <c r="E121" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F121" s="37"/>
       <c r="G121" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H121" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I121" s="31" t="s">
-        <v>250</v>
+        <v>1</v>
+      </c>
+      <c r="H121" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I121" s="27" t="s">
+        <v>233</v>
       </c>
       <c r="J121" s="4" t="n">
         <f aca="false">J120+D120</f>
-        <v>200</v>
+        <v>26</v>
       </c>
       <c r="K121" s="4" t="n">
         <f aca="false">J121/8</f>
-        <v>25</v>
+        <v>3.25</v>
       </c>
       <c r="L121" s="4" t="n">
         <f aca="false">J121/16</f>
-        <v>12.5</v>
+        <v>1.625</v>
       </c>
       <c r="M121" s="4" t="n">
         <f aca="false">J121/32</f>
-        <v>6.25</v>
+        <v>0.8125</v>
       </c>
       <c r="N121" s="4" t="s">
-        <v>247</v>
+        <v>106</v>
       </c>
       <c r="O121" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P121" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q121" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B122" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="C122" s="36" t="s">
+        <v>251</v>
+      </c>
+      <c r="D122" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="P121" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q121" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B122" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="C122" s="20" t="s">
-        <v>252</v>
-      </c>
-      <c r="D122" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E122" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F122" s="31"/>
+      <c r="E122" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F122" s="37"/>
       <c r="G122" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H122" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I122" s="31" t="s">
-        <v>253</v>
+      <c r="H122" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I122" s="27" t="s">
+        <v>233</v>
       </c>
       <c r="J122" s="4" t="n">
         <f aca="false">J121+D121</f>
-        <v>208</v>
+        <v>27</v>
       </c>
       <c r="K122" s="4" t="n">
         <f aca="false">J122/8</f>
-        <v>26</v>
+        <v>3.375</v>
       </c>
       <c r="L122" s="4" t="n">
         <f aca="false">J122/16</f>
-        <v>13</v>
+        <v>1.6875</v>
       </c>
       <c r="M122" s="4" t="n">
         <f aca="false">J122/32</f>
-        <v>6.5</v>
+        <v>0.84375</v>
       </c>
       <c r="N122" s="4" t="s">
-        <v>247</v>
+        <v>28</v>
       </c>
       <c r="O122" s="22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P122" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q122" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" s="35" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B123" s="20" t="s">
-        <v>254</v>
-      </c>
-      <c r="C123" s="20" t="s">
-        <v>255</v>
+        <v>252</v>
+      </c>
+      <c r="C123" s="36" t="s">
+        <v>253</v>
       </c>
       <c r="D123" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E123" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F123" s="31"/>
+        <v>32</v>
+      </c>
+      <c r="E123" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F123" s="37"/>
       <c r="G123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H123" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I123" s="31" t="s">
-        <v>256</v>
+        <v>2</v>
+      </c>
+      <c r="H123" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I123" s="27" t="s">
+        <v>233</v>
       </c>
       <c r="J123" s="4" t="n">
         <f aca="false">J122+D122</f>
-        <v>216</v>
+        <v>32</v>
       </c>
       <c r="K123" s="4" t="n">
         <f aca="false">J123/8</f>
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="L123" s="4" t="n">
         <f aca="false">J123/16</f>
-        <v>13.5</v>
+        <v>2</v>
       </c>
       <c r="M123" s="4" t="n">
         <f aca="false">J123/32</f>
-        <v>6.75</v>
+        <v>1</v>
       </c>
       <c r="N123" s="4" t="s">
-        <v>247</v>
+        <v>106</v>
       </c>
       <c r="O123" s="22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P123" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q123" s="1" t="n">
         <v>0</v>
@@ -6152,51 +6256,51 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B124" s="20" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C124" s="20" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D124" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E124" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F124" s="31"/>
+        <v>32</v>
+      </c>
+      <c r="E124" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="F124" s="27"/>
       <c r="G124" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H124" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I124" s="31" t="s">
-        <v>259</v>
+      <c r="H124" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I124" s="27" t="s">
+        <v>233</v>
       </c>
       <c r="J124" s="4" t="n">
         <f aca="false">J123+D123</f>
-        <v>224</v>
+        <v>64</v>
       </c>
       <c r="K124" s="4" t="n">
         <f aca="false">J124/8</f>
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="L124" s="4" t="n">
         <f aca="false">J124/16</f>
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M124" s="4" t="n">
         <f aca="false">J124/32</f>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N124" s="4" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="O124" s="22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P124" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q124" s="1" t="n">
         <v>0</v>
@@ -6204,51 +6308,51 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B125" s="20" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C125" s="20" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D125" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E125" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F125" s="31"/>
+        <v>32</v>
+      </c>
+      <c r="E125" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F125" s="27"/>
       <c r="G125" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H125" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I125" s="20" t="s">
-        <v>260</v>
+      <c r="H125" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I125" s="27" t="s">
+        <v>233</v>
       </c>
       <c r="J125" s="4" t="n">
         <f aca="false">J124+D124</f>
-        <v>232</v>
+        <v>96</v>
       </c>
       <c r="K125" s="4" t="n">
         <f aca="false">J125/8</f>
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="L125" s="4" t="n">
         <f aca="false">J125/16</f>
-        <v>14.5</v>
+        <v>6</v>
       </c>
       <c r="M125" s="4" t="n">
         <f aca="false">J125/32</f>
-        <v>7.25</v>
+        <v>3</v>
       </c>
       <c r="N125" s="4" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="O125" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P125" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q125" s="1" t="n">
         <v>0</v>
@@ -6256,51 +6360,51 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B126" s="20" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C126" s="20" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D126" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E126" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F126" s="31"/>
+        <v>32</v>
+      </c>
+      <c r="E126" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="F126" s="27"/>
       <c r="G126" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H126" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I126" s="20" t="s">
-        <v>263</v>
+      <c r="H126" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I126" s="27" t="s">
+        <v>233</v>
       </c>
       <c r="J126" s="4" t="n">
         <f aca="false">J125+D125</f>
-        <v>240</v>
+        <v>128</v>
       </c>
       <c r="K126" s="4" t="n">
         <f aca="false">J126/8</f>
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="L126" s="4" t="n">
         <f aca="false">J126/16</f>
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="M126" s="4" t="n">
         <f aca="false">J126/32</f>
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="N126" s="4" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="O126" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P126" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q126" s="1" t="n">
         <v>0</v>
@@ -6308,51 +6412,51 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B127" s="20" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C127" s="20" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D127" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E127" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F127" s="31"/>
+        <v>32</v>
+      </c>
+      <c r="E127" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F127" s="27"/>
       <c r="G127" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H127" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I127" s="20" t="s">
-        <v>265</v>
+      <c r="H127" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I127" s="27" t="s">
+        <v>233</v>
       </c>
       <c r="J127" s="4" t="n">
         <f aca="false">J126+D126</f>
-        <v>248</v>
+        <v>160</v>
       </c>
       <c r="K127" s="4" t="n">
         <f aca="false">J127/8</f>
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="L127" s="4" t="n">
         <f aca="false">J127/16</f>
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="M127" s="4" t="n">
         <f aca="false">J127/32</f>
-        <v>7.75</v>
+        <v>5</v>
       </c>
       <c r="N127" s="4" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="O127" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P127" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="P127" s="1" t="n">
-        <v>3</v>
       </c>
       <c r="Q127" s="1" t="n">
         <v>0</v>
@@ -6360,51 +6464,51 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B128" s="20" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C128" s="20" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D128" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E128" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F128" s="31"/>
+      <c r="E128" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F128" s="27"/>
       <c r="G128" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H128" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I128" s="20" t="s">
-        <v>267</v>
+      <c r="H128" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I128" s="27" t="s">
+        <v>265</v>
       </c>
       <c r="J128" s="4" t="n">
         <f aca="false">J127+D127</f>
-        <v>256</v>
+        <v>192</v>
       </c>
       <c r="K128" s="4" t="n">
         <f aca="false">J128/8</f>
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="L128" s="4" t="n">
         <f aca="false">J128/16</f>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M128" s="4" t="n">
         <f aca="false">J128/32</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N128" s="4" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="O128" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P128" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q128" s="1" t="n">
         <v>0</v>
@@ -6412,51 +6516,51 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B129" s="20" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C129" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D129" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E129" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F129" s="31"/>
+      <c r="E129" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F129" s="27"/>
       <c r="G129" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H129" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I129" s="20" t="s">
+      <c r="H129" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I129" s="27" t="s">
         <v>269</v>
       </c>
       <c r="J129" s="4" t="n">
         <f aca="false">J128+D128</f>
-        <v>264</v>
+        <v>200</v>
       </c>
       <c r="K129" s="4" t="n">
         <f aca="false">J129/8</f>
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="L129" s="4" t="n">
         <f aca="false">J129/16</f>
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="M129" s="4" t="n">
         <f aca="false">J129/32</f>
-        <v>8.25</v>
+        <v>6.25</v>
       </c>
       <c r="N129" s="4" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="O129" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P129" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q129" s="1" t="n">
         <v>0</v>
@@ -6464,51 +6568,51 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B130" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="C130" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="C130" s="20" t="s">
+      <c r="D130" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E130" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F130" s="27"/>
+      <c r="G130" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I130" s="27" t="s">
         <v>272</v>
-      </c>
-      <c r="D130" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E130" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F130" s="31"/>
-      <c r="G130" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I130" s="20" t="s">
-        <v>271</v>
       </c>
       <c r="J130" s="4" t="n">
         <f aca="false">J129+D129</f>
-        <v>272</v>
+        <v>208</v>
       </c>
       <c r="K130" s="4" t="n">
         <f aca="false">J130/8</f>
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="L130" s="4" t="n">
         <f aca="false">J130/16</f>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M130" s="4" t="n">
         <f aca="false">J130/32</f>
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="N130" s="4" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="O130" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P130" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q130" s="1" t="n">
         <v>0</v>
@@ -6524,43 +6628,43 @@
       <c r="D131" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E131" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F131" s="31"/>
+      <c r="E131" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F131" s="27"/>
       <c r="G131" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H131" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I131" s="20" t="s">
-        <v>273</v>
+      <c r="H131" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I131" s="27" t="s">
+        <v>275</v>
       </c>
       <c r="J131" s="4" t="n">
         <f aca="false">J130+D130</f>
-        <v>280</v>
+        <v>216</v>
       </c>
       <c r="K131" s="4" t="n">
         <f aca="false">J131/8</f>
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="L131" s="4" t="n">
         <f aca="false">J131/16</f>
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="M131" s="4" t="n">
         <f aca="false">J131/32</f>
-        <v>8.75</v>
+        <v>6.75</v>
       </c>
       <c r="N131" s="4" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="O131" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="P131" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="P131" s="1" t="n">
-        <v>7</v>
       </c>
       <c r="Q131" s="1" t="n">
         <v>0</v>
@@ -6568,48 +6672,48 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B132" s="20" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C132" s="20" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D132" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E132" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F132" s="31"/>
+      <c r="E132" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F132" s="27"/>
       <c r="G132" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H132" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I132" s="20" t="s">
-        <v>275</v>
+      <c r="H132" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I132" s="27" t="s">
+        <v>278</v>
       </c>
       <c r="J132" s="4" t="n">
         <f aca="false">J131+D131</f>
-        <v>288</v>
+        <v>224</v>
       </c>
       <c r="K132" s="4" t="n">
         <f aca="false">J132/8</f>
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="L132" s="4" t="n">
         <f aca="false">J132/16</f>
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="M132" s="4" t="n">
         <f aca="false">J132/32</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N132" s="4" t="s">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="O132" s="22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P132" s="1" t="n">
         <v>5</v>
@@ -6620,51 +6724,51 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B133" s="20" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C133" s="20" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D133" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E133" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F133" s="31"/>
+      <c r="E133" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F133" s="27"/>
       <c r="G133" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H133" s="31" t="s">
+      <c r="H133" s="27" t="s">
         <v>34</v>
       </c>
       <c r="I133" s="20" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="J133" s="4" t="n">
         <f aca="false">J132+D132</f>
-        <v>296</v>
+        <v>232</v>
       </c>
       <c r="K133" s="4" t="n">
         <f aca="false">J133/8</f>
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="L133" s="4" t="n">
         <f aca="false">J133/16</f>
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="M133" s="4" t="n">
         <f aca="false">J133/32</f>
-        <v>9.25</v>
+        <v>7.25</v>
       </c>
       <c r="N133" s="4" t="s">
-        <v>237</v>
+        <v>281</v>
       </c>
       <c r="O133" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P133" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q133" s="1" t="n">
         <v>0</v>
@@ -6672,51 +6776,51 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B134" s="20" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C134" s="20" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D134" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E134" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F134" s="31"/>
+      <c r="E134" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F134" s="27"/>
       <c r="G134" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H134" s="31" t="s">
+      <c r="H134" s="27" t="s">
         <v>34</v>
       </c>
       <c r="I134" s="20" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="J134" s="4" t="n">
         <f aca="false">J133+D133</f>
-        <v>304</v>
+        <v>240</v>
       </c>
       <c r="K134" s="4" t="n">
         <f aca="false">J134/8</f>
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="L134" s="4" t="n">
         <f aca="false">J134/16</f>
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M134" s="4" t="n">
         <f aca="false">J134/32</f>
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="N134" s="4" t="s">
-        <v>237</v>
+        <v>281</v>
       </c>
       <c r="O134" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P134" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Q134" s="1" t="n">
         <v>0</v>
@@ -6724,51 +6828,51 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B135" s="20" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C135" s="20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D135" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E135" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F135" s="31"/>
+      <c r="E135" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F135" s="27"/>
       <c r="G135" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H135" s="31" t="s">
+      <c r="H135" s="27" t="s">
         <v>34</v>
       </c>
       <c r="I135" s="20" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="J135" s="4" t="n">
         <f aca="false">J134+D134</f>
-        <v>312</v>
+        <v>248</v>
       </c>
       <c r="K135" s="4" t="n">
         <f aca="false">J135/8</f>
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="L135" s="4" t="n">
         <f aca="false">J135/16</f>
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="M135" s="4" t="n">
         <f aca="false">J135/32</f>
-        <v>9.75</v>
+        <v>7.75</v>
       </c>
       <c r="N135" s="4" t="s">
-        <v>237</v>
+        <v>281</v>
       </c>
       <c r="O135" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="P135" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="P135" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="Q135" s="1" t="n">
         <v>0</v>
@@ -6776,51 +6880,51 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B136" s="20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C136" s="20" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D136" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E136" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F136" s="31"/>
+      <c r="E136" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F136" s="27"/>
       <c r="G136" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H136" s="31" t="s">
+      <c r="H136" s="27" t="s">
         <v>34</v>
       </c>
       <c r="I136" s="20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="J136" s="4" t="n">
         <f aca="false">J135+D135</f>
-        <v>320</v>
+        <v>256</v>
       </c>
       <c r="K136" s="4" t="n">
         <f aca="false">J136/8</f>
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="L136" s="4" t="n">
         <f aca="false">J136/16</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="M136" s="4" t="n">
         <f aca="false">J136/32</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N136" s="4" t="s">
-        <v>237</v>
+        <v>281</v>
       </c>
       <c r="O136" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P136" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Q136" s="1" t="n">
         <v>0</v>
@@ -6828,51 +6932,51 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B137" s="20" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C137" s="20" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D137" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E137" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F137" s="31"/>
+      <c r="E137" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F137" s="27"/>
       <c r="G137" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H137" s="31" t="s">
+      <c r="H137" s="27" t="s">
         <v>34</v>
       </c>
       <c r="I137" s="20" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="J137" s="4" t="n">
         <f aca="false">J136+D136</f>
-        <v>328</v>
+        <v>264</v>
       </c>
       <c r="K137" s="4" t="n">
         <f aca="false">J137/8</f>
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="L137" s="4" t="n">
         <f aca="false">J137/16</f>
-        <v>20.5</v>
+        <v>16.5</v>
       </c>
       <c r="M137" s="4" t="n">
         <f aca="false">J137/32</f>
-        <v>10.25</v>
+        <v>8.25</v>
       </c>
       <c r="N137" s="4" t="s">
-        <v>237</v>
+        <v>281</v>
       </c>
       <c r="O137" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P137" s="1" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q137" s="1" t="n">
         <v>0</v>
@@ -6880,51 +6984,51 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B138" s="20" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C138" s="20" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D138" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E138" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F138" s="31"/>
+      <c r="E138" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F138" s="27"/>
       <c r="G138" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H138" s="31" t="s">
+      <c r="H138" s="27" t="s">
         <v>34</v>
       </c>
       <c r="I138" s="20" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="J138" s="4" t="n">
         <f aca="false">J137+D137</f>
-        <v>336</v>
+        <v>272</v>
       </c>
       <c r="K138" s="4" t="n">
         <f aca="false">J138/8</f>
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="L138" s="4" t="n">
         <f aca="false">J138/16</f>
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="M138" s="4" t="n">
         <f aca="false">J138/32</f>
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="N138" s="4" t="s">
-        <v>98</v>
+        <v>281</v>
       </c>
       <c r="O138" s="22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P138" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q138" s="1" t="n">
         <v>0</v>
@@ -6932,51 +7036,51 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B139" s="20" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C139" s="20" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D139" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E139" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F139" s="31"/>
+      <c r="E139" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F139" s="27"/>
       <c r="G139" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H139" s="31" t="s">
+      <c r="H139" s="27" t="s">
         <v>34</v>
       </c>
       <c r="I139" s="20" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="J139" s="4" t="n">
         <f aca="false">J138+D138</f>
-        <v>344</v>
+        <v>280</v>
       </c>
       <c r="K139" s="4" t="n">
         <f aca="false">J139/8</f>
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L139" s="4" t="n">
         <f aca="false">J139/16</f>
-        <v>21.5</v>
+        <v>17.5</v>
       </c>
       <c r="M139" s="4" t="n">
         <f aca="false">J139/32</f>
-        <v>10.75</v>
+        <v>8.75</v>
       </c>
       <c r="N139" s="4" t="s">
-        <v>98</v>
+        <v>281</v>
       </c>
       <c r="O139" s="22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P139" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q139" s="1" t="n">
         <v>0</v>
@@ -6984,51 +7088,51 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B140" s="20" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C140" s="20" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D140" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E140" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F140" s="31"/>
+      <c r="E140" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F140" s="27"/>
       <c r="G140" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H140" s="31" t="s">
+      <c r="H140" s="27" t="s">
         <v>34</v>
       </c>
       <c r="I140" s="20" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="J140" s="4" t="n">
         <f aca="false">J139+D139</f>
-        <v>352</v>
+        <v>288</v>
       </c>
       <c r="K140" s="4" t="n">
         <f aca="false">J140/8</f>
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="L140" s="4" t="n">
         <f aca="false">J140/16</f>
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="M140" s="4" t="n">
         <f aca="false">J140/32</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N140" s="4" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="O140" s="22" t="n">
         <v>3</v>
       </c>
       <c r="P140" s="1" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Q140" s="1" t="n">
         <v>0</v>
@@ -7036,51 +7140,51 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B141" s="20" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C141" s="20" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D141" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E141" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F141" s="31"/>
+      <c r="E141" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F141" s="27"/>
       <c r="G141" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H141" s="31" t="s">
+      <c r="H141" s="27" t="s">
         <v>34</v>
       </c>
       <c r="I141" s="20" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="J141" s="4" t="n">
         <f aca="false">J140+D140</f>
-        <v>360</v>
+        <v>296</v>
       </c>
       <c r="K141" s="4" t="n">
         <f aca="false">J141/8</f>
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="L141" s="4" t="n">
         <f aca="false">J141/16</f>
-        <v>22.5</v>
+        <v>18.5</v>
       </c>
       <c r="M141" s="4" t="n">
         <f aca="false">J141/32</f>
-        <v>11.25</v>
+        <v>9.25</v>
       </c>
       <c r="N141" s="4" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="O141" s="22" t="n">
         <v>3</v>
       </c>
       <c r="P141" s="1" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q141" s="1" t="n">
         <v>0</v>
@@ -7088,51 +7192,51 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B142" s="20" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C142" s="20" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D142" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E142" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F142" s="31"/>
+      <c r="E142" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F142" s="27"/>
       <c r="G142" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H142" s="31" t="s">
+      <c r="H142" s="27" t="s">
         <v>34</v>
       </c>
       <c r="I142" s="20" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="J142" s="4" t="n">
         <f aca="false">J141+D141</f>
-        <v>368</v>
+        <v>304</v>
       </c>
       <c r="K142" s="4" t="n">
         <f aca="false">J142/8</f>
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="L142" s="4" t="n">
         <f aca="false">J142/16</f>
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="M142" s="4" t="n">
         <f aca="false">J142/32</f>
-        <v>11.5</v>
+        <v>9.5</v>
       </c>
       <c r="N142" s="4" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="O142" s="22" t="n">
         <v>3</v>
       </c>
       <c r="P142" s="1" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Q142" s="1" t="n">
         <v>0</v>
@@ -7140,51 +7244,51 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B143" s="20" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C143" s="20" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D143" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E143" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F143" s="31"/>
+      <c r="E143" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F143" s="27"/>
       <c r="G143" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H143" s="31" t="s">
+      <c r="H143" s="27" t="s">
         <v>34</v>
       </c>
       <c r="I143" s="20" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="J143" s="4" t="n">
         <f aca="false">J142+D142</f>
-        <v>376</v>
+        <v>312</v>
       </c>
       <c r="K143" s="4" t="n">
         <f aca="false">J143/8</f>
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="L143" s="4" t="n">
         <f aca="false">J143/16</f>
-        <v>23.5</v>
+        <v>19.5</v>
       </c>
       <c r="M143" s="4" t="n">
         <f aca="false">J143/32</f>
-        <v>11.75</v>
+        <v>9.75</v>
       </c>
       <c r="N143" s="4" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="O143" s="22" t="n">
         <v>3</v>
       </c>
       <c r="P143" s="1" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Q143" s="1" t="n">
         <v>0</v>
@@ -7192,51 +7296,51 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B144" s="20" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C144" s="20" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D144" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E144" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F144" s="31"/>
+      <c r="E144" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F144" s="27"/>
       <c r="G144" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H144" s="31" t="s">
+      <c r="H144" s="27" t="s">
         <v>34</v>
       </c>
       <c r="I144" s="20" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="J144" s="4" t="n">
         <f aca="false">J143+D143</f>
-        <v>384</v>
+        <v>320</v>
       </c>
       <c r="K144" s="4" t="n">
         <f aca="false">J144/8</f>
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L144" s="4" t="n">
         <f aca="false">J144/16</f>
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M144" s="4" t="n">
         <f aca="false">J144/32</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N144" s="4" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="O144" s="22" t="n">
         <v>3</v>
       </c>
       <c r="P144" s="1" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q144" s="1" t="n">
         <v>0</v>
@@ -7244,51 +7348,51 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B145" s="20" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C145" s="20" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D145" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E145" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F145" s="31"/>
+      <c r="E145" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F145" s="27"/>
       <c r="G145" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H145" s="31" t="s">
+      <c r="H145" s="27" t="s">
         <v>34</v>
       </c>
       <c r="I145" s="20" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="J145" s="4" t="n">
         <f aca="false">J144+D144</f>
-        <v>392</v>
+        <v>328</v>
       </c>
       <c r="K145" s="4" t="n">
         <f aca="false">J145/8</f>
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="L145" s="4" t="n">
         <f aca="false">J145/16</f>
-        <v>24.5</v>
+        <v>20.5</v>
       </c>
       <c r="M145" s="4" t="n">
         <f aca="false">J145/32</f>
-        <v>12.25</v>
+        <v>10.25</v>
       </c>
       <c r="N145" s="4" t="s">
-        <v>98</v>
+        <v>256</v>
       </c>
       <c r="O145" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P145" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q145" s="1" t="n">
         <v>0</v>
@@ -7296,51 +7400,51 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B146" s="20" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C146" s="20" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D146" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E146" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F146" s="31"/>
+      <c r="E146" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F146" s="27"/>
       <c r="G146" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H146" s="31" t="s">
+      <c r="H146" s="27" t="s">
         <v>34</v>
       </c>
       <c r="I146" s="20" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="J146" s="4" t="n">
         <f aca="false">J145+D145</f>
-        <v>400</v>
+        <v>336</v>
       </c>
       <c r="K146" s="4" t="n">
         <f aca="false">J146/8</f>
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="L146" s="4" t="n">
         <f aca="false">J146/16</f>
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="M146" s="4" t="n">
         <f aca="false">J146/32</f>
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="N146" s="4" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="O146" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P146" s="1" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q146" s="1" t="n">
         <v>0</v>
@@ -7348,105 +7452,103 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B147" s="20" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C147" s="20" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D147" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E147" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F147" s="31"/>
+      <c r="E147" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F147" s="27"/>
       <c r="G147" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H147" s="31" t="s">
+      <c r="H147" s="27" t="s">
         <v>34</v>
       </c>
       <c r="I147" s="20" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="J147" s="4" t="n">
         <f aca="false">J146+D146</f>
-        <v>408</v>
+        <v>344</v>
       </c>
       <c r="K147" s="4" t="n">
         <f aca="false">J147/8</f>
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="L147" s="4" t="n">
         <f aca="false">J147/16</f>
-        <v>25.5</v>
+        <v>21.5</v>
       </c>
       <c r="M147" s="4" t="n">
         <f aca="false">J147/32</f>
-        <v>12.75</v>
+        <v>10.75</v>
       </c>
       <c r="N147" s="4" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="O147" s="22" t="n">
         <v>2</v>
       </c>
       <c r="P147" s="1" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q147" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B148" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="C148" s="3" t="s">
-        <v>308</v>
+      <c r="B148" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="C148" s="20" t="s">
+        <v>311</v>
       </c>
       <c r="D148" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="E148" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F148" s="31" t="s">
-        <v>64</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E148" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F148" s="27"/>
       <c r="G148" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H148" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I148" s="3" t="s">
-        <v>307</v>
+      <c r="H148" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I148" s="20" t="s">
+        <v>310</v>
       </c>
       <c r="J148" s="4" t="n">
         <f aca="false">J147+D147</f>
-        <v>416</v>
+        <v>352</v>
       </c>
       <c r="K148" s="4" t="n">
         <f aca="false">J148/8</f>
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="L148" s="4" t="n">
         <f aca="false">J148/16</f>
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M148" s="4" t="n">
         <f aca="false">J148/32</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N148" s="4" t="s">
-        <v>98</v>
+        <v>256</v>
       </c>
       <c r="O148" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P148" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q148" s="1" t="n">
         <v>0</v>
@@ -7454,148 +7556,660 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B149" s="20" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C149" s="20" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D149" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E149" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="F149" s="31"/>
+      <c r="E149" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F149" s="27"/>
       <c r="G149" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H149" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="H149" s="27" t="s">
         <v>34</v>
       </c>
       <c r="I149" s="20" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="J149" s="4" t="n">
         <f aca="false">J148+D148</f>
-        <v>432</v>
+        <v>360</v>
       </c>
       <c r="K149" s="4" t="n">
         <f aca="false">J149/8</f>
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="L149" s="4" t="n">
         <f aca="false">J149/16</f>
-        <v>27</v>
+        <v>22.5</v>
       </c>
       <c r="M149" s="4" t="n">
         <f aca="false">J149/32</f>
-        <v>13.5</v>
+        <v>11.25</v>
       </c>
       <c r="N149" s="4" t="s">
-        <v>98</v>
+        <v>256</v>
       </c>
       <c r="O149" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P149" s="1" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q149" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B150" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="C150" s="3" t="s">
-        <v>312</v>
+      <c r="B150" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="C150" s="20" t="s">
+        <v>315</v>
       </c>
       <c r="D150" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="E150" s="31" t="s">
-        <v>313</v>
-      </c>
-      <c r="F150" s="31"/>
+      <c r="E150" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F150" s="27"/>
       <c r="G150" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H150" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I150" s="31" t="s">
-        <v>214</v>
+      <c r="H150" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I150" s="20" t="s">
+        <v>314</v>
       </c>
       <c r="J150" s="4" t="n">
         <f aca="false">J149+D149</f>
-        <v>440</v>
+        <v>368</v>
       </c>
       <c r="K150" s="4" t="n">
         <f aca="false">J150/8</f>
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="L150" s="4" t="n">
         <f aca="false">J150/16</f>
-        <v>27.5</v>
+        <v>23</v>
       </c>
       <c r="M150" s="4" t="n">
         <f aca="false">J150/32</f>
-        <v>13.75</v>
+        <v>11.5</v>
       </c>
       <c r="N150" s="4" t="s">
-        <v>28</v>
+        <v>256</v>
       </c>
       <c r="O150" s="22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P150" s="1" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q150" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F151" s="31"/>
-      <c r="G151" s="31"/>
-      <c r="H151" s="31"/>
-      <c r="I151" s="31"/>
+      <c r="B151" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="C151" s="20" t="s">
+        <v>317</v>
+      </c>
+      <c r="D151" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E151" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F151" s="27"/>
+      <c r="G151" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I151" s="20" t="s">
+        <v>316</v>
+      </c>
       <c r="J151" s="4" t="n">
         <f aca="false">J150+D150</f>
-        <v>448</v>
+        <v>376</v>
       </c>
       <c r="K151" s="4" t="n">
         <f aca="false">J151/8</f>
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="L151" s="4" t="n">
         <f aca="false">J151/16</f>
-        <v>28</v>
+        <v>23.5</v>
       </c>
       <c r="M151" s="4" t="n">
         <f aca="false">J151/32</f>
+        <v>11.75</v>
+      </c>
+      <c r="N151" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="O151" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P151" s="1" t="n">
         <v>14</v>
       </c>
-    </row>
-    <row r="152" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C152" s="3"/>
-      <c r="H152" s="3"/>
-      <c r="O152" s="3"/>
-    </row>
-    <row r="1048304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="Q151" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B152" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="C152" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="D152" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E152" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F152" s="27"/>
+      <c r="G152" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I152" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="J152" s="4" t="n">
+        <f aca="false">J151+D151</f>
+        <v>384</v>
+      </c>
+      <c r="K152" s="4" t="n">
+        <f aca="false">J152/8</f>
+        <v>48</v>
+      </c>
+      <c r="L152" s="4" t="n">
+        <f aca="false">J152/16</f>
+        <v>24</v>
+      </c>
+      <c r="M152" s="4" t="n">
+        <f aca="false">J152/32</f>
+        <v>12</v>
+      </c>
+      <c r="N152" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="O152" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P152" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q152" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B153" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="C153" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="D153" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E153" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F153" s="27"/>
+      <c r="G153" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I153" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="J153" s="4" t="n">
+        <f aca="false">J152+D152</f>
+        <v>392</v>
+      </c>
+      <c r="K153" s="4" t="n">
+        <f aca="false">J153/8</f>
+        <v>49</v>
+      </c>
+      <c r="L153" s="4" t="n">
+        <f aca="false">J153/16</f>
+        <v>24.5</v>
+      </c>
+      <c r="M153" s="4" t="n">
+        <f aca="false">J153/32</f>
+        <v>12.25</v>
+      </c>
+      <c r="N153" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="O153" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P153" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q153" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B154" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="C154" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="D154" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E154" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F154" s="27"/>
+      <c r="G154" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I154" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="J154" s="4" t="n">
+        <f aca="false">J153+D153</f>
+        <v>400</v>
+      </c>
+      <c r="K154" s="4" t="n">
+        <f aca="false">J154/8</f>
+        <v>50</v>
+      </c>
+      <c r="L154" s="4" t="n">
+        <f aca="false">J154/16</f>
+        <v>25</v>
+      </c>
+      <c r="M154" s="4" t="n">
+        <f aca="false">J154/32</f>
+        <v>12.5</v>
+      </c>
+      <c r="N154" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="O154" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P154" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q154" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B155" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="C155" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="D155" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E155" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F155" s="27"/>
+      <c r="G155" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I155" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="J155" s="4" t="n">
+        <f aca="false">J154+D154</f>
+        <v>408</v>
+      </c>
+      <c r="K155" s="4" t="n">
+        <f aca="false">J155/8</f>
+        <v>51</v>
+      </c>
+      <c r="L155" s="4" t="n">
+        <f aca="false">J155/16</f>
+        <v>25.5</v>
+      </c>
+      <c r="M155" s="4" t="n">
+        <f aca="false">J155/32</f>
+        <v>12.75</v>
+      </c>
+      <c r="N155" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="O155" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P155" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q155" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B156" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D156" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="E156" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F156" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="G156" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I156" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="J156" s="4" t="n">
+        <f aca="false">J155+D155</f>
+        <v>416</v>
+      </c>
+      <c r="K156" s="4" t="n">
+        <f aca="false">J156/8</f>
+        <v>52</v>
+      </c>
+      <c r="L156" s="4" t="n">
+        <f aca="false">J156/16</f>
+        <v>26</v>
+      </c>
+      <c r="M156" s="4" t="n">
+        <f aca="false">J156/32</f>
+        <v>13</v>
+      </c>
+      <c r="N156" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="O156" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P156" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q156" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B157" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="C157" s="20" t="s">
+        <v>329</v>
+      </c>
+      <c r="D157" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E157" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F157" s="27"/>
+      <c r="G157" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H157" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I157" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="J157" s="4" t="n">
+        <f aca="false">J156+D156</f>
+        <v>432</v>
+      </c>
+      <c r="K157" s="4" t="n">
+        <f aca="false">J157/8</f>
+        <v>54</v>
+      </c>
+      <c r="L157" s="4" t="n">
+        <f aca="false">J157/16</f>
+        <v>27</v>
+      </c>
+      <c r="M157" s="4" t="n">
+        <f aca="false">J157/32</f>
+        <v>13.5</v>
+      </c>
+      <c r="N157" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="O157" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P157" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q157" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B158" s="20" t="s">
+        <v>330</v>
+      </c>
+      <c r="C158" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="D158" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E158" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F158" s="27"/>
+      <c r="G158" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H158" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I158" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="J158" s="4" t="n">
+        <f aca="false">J157+D157</f>
+        <v>440</v>
+      </c>
+      <c r="K158" s="4" t="n">
+        <f aca="false">J158/8</f>
+        <v>55</v>
+      </c>
+      <c r="L158" s="4" t="n">
+        <f aca="false">J158/16</f>
+        <v>27.5</v>
+      </c>
+      <c r="M158" s="4" t="n">
+        <f aca="false">J158/32</f>
+        <v>13.75</v>
+      </c>
+      <c r="N158" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="O158" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P158" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q158" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B159" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="C159" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="D159" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E159" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F159" s="27"/>
+      <c r="G159" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H159" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I159" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="J159" s="4" t="n">
+        <f aca="false">J158+D158</f>
+        <v>448</v>
+      </c>
+      <c r="K159" s="4" t="n">
+        <f aca="false">J159/8</f>
+        <v>56</v>
+      </c>
+      <c r="L159" s="4" t="n">
+        <f aca="false">J159/16</f>
+        <v>28</v>
+      </c>
+      <c r="M159" s="4" t="n">
+        <f aca="false">J159/32</f>
+        <v>14</v>
+      </c>
+      <c r="N159" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="O159" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P159" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q159" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B160" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="D160" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E160" s="27" t="s">
+        <v>338</v>
+      </c>
+      <c r="F160" s="27"/>
+      <c r="G160" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I160" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="J160" s="4" t="n">
+        <f aca="false">J159+D159</f>
+        <v>456</v>
+      </c>
+      <c r="K160" s="4" t="n">
+        <f aca="false">J160/8</f>
+        <v>57</v>
+      </c>
+      <c r="L160" s="4" t="n">
+        <f aca="false">J160/16</f>
+        <v>28.5</v>
+      </c>
+      <c r="M160" s="4" t="n">
+        <f aca="false">J160/32</f>
+        <v>14.25</v>
+      </c>
+      <c r="N160" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O160" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q160" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F161" s="27"/>
+      <c r="G161" s="27"/>
+      <c r="H161" s="27"/>
+      <c r="I161" s="27"/>
+      <c r="J161" s="4" t="n">
+        <f aca="false">J160+D160</f>
+        <v>480</v>
+      </c>
+      <c r="K161" s="4" t="n">
+        <f aca="false">J161/8</f>
+        <v>60</v>
+      </c>
+      <c r="L161" s="4" t="n">
+        <f aca="false">J161/16</f>
+        <v>30</v>
+      </c>
+      <c r="M161" s="4" t="n">
+        <f aca="false">J161/32</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="162" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C162" s="3"/>
+      <c r="H162" s="3"/>
+      <c r="O162" s="3"/>
+    </row>
     <row r="1048314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -7866,10 +8480,10 @@
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="B4:I4"/>
     <mergeCell ref="B5:I5"/>
-    <mergeCell ref="B41:I41"/>
+    <mergeCell ref="B46:I46"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A105" r:id="rId1" display="Structure:rt1Errors_t,file:rt1ErrorsDownlink.h"/>
+    <hyperlink ref="A113" r:id="rId1" display="Structure:rt1Errors_t,file:rt1ErrorsDownlink.h"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -7887,7 +8501,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B6:I20"/>
-  <sheetFormatPr defaultColWidth="9.30078125" defaultRowHeight="13.2" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.34375" defaultRowHeight="13.2" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="38" width="20.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="38" width="16.11"/>
@@ -7897,22 +8511,22 @@
     <row r="6" s="39" customFormat="true" ht="34.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="40"/>
       <c r="C6" s="40" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="D6" s="40" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="E6" s="40" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
       <c r="F6" s="40" t="s">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="G6" s="40" t="s">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="H6" s="40" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="I6" s="40"/>
     </row>

--- a/TelemDefinition/DownlinkSpecPacsat.xlsx
+++ b/TelemDefinition/DownlinkSpecPacsat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\workspace_ccs\PacSatDocs\TelemDefinition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39A7465-62B4-408A-B2D1-18FF48D9786C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FC1F0C0-A01E-4884-8DFC-76BB2AD56780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="24105" windowHeight="13920" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="26310" windowHeight="13920" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DownlinkSpecPacsat" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="347">
   <si>
     <t>//</t>
   </si>
@@ -1072,6 +1072,12 @@
   </si>
   <si>
     <t>Time to Downlink</t>
+  </si>
+  <si>
+    <t>Pwr Mode</t>
+  </si>
+  <si>
+    <t>RSSI</t>
   </si>
 </sst>
 </file>
@@ -2462,7 +2468,7 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
-        <v>68</v>
+        <v>345</v>
       </c>
       <c r="C26" s="20" t="s">
         <v>68</v>
@@ -2558,7 +2564,7 @@
         <v>4</v>
       </c>
       <c r="P27" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q27" s="1">
         <v>0</v>
@@ -2566,7 +2572,7 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
-        <v>73</v>
+        <v>345</v>
       </c>
       <c r="C28" s="20" t="s">
         <v>73</v>
@@ -2618,7 +2624,7 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B29" s="20" t="s">
-        <v>76</v>
+        <v>345</v>
       </c>
       <c r="C29" s="20" t="s">
         <v>76</v>
@@ -2670,7 +2676,7 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
-        <v>79</v>
+        <v>345</v>
       </c>
       <c r="C30" s="20" t="s">
         <v>79</v>
@@ -2722,7 +2728,7 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B31" s="20" t="s">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="C31" s="20" t="s">
         <v>82</v>
@@ -2982,7 +2988,7 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B36" s="20" t="s">
-        <v>93</v>
+        <v>346</v>
       </c>
       <c r="C36" s="20" t="s">
         <v>93</v>
@@ -3034,7 +3040,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B37" s="20" t="s">
-        <v>96</v>
+        <v>346</v>
       </c>
       <c r="C37" s="20" t="s">
         <v>96</v>
@@ -3086,7 +3092,7 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
-        <v>98</v>
+        <v>346</v>
       </c>
       <c r="C38" s="20" t="s">
         <v>98</v>
@@ -3138,7 +3144,7 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B39" s="20" t="s">
-        <v>100</v>
+        <v>346</v>
       </c>
       <c r="C39" s="20" t="s">
         <v>100</v>
@@ -3338,7 +3344,7 @@
         <v>2</v>
       </c>
       <c r="P42" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q42" s="1">
         <v>0</v>
@@ -5778,7 +5784,7 @@
         <v>1</v>
       </c>
       <c r="P107" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q107" s="1">
         <v>0</v>
@@ -5830,7 +5836,7 @@
         <v>1</v>
       </c>
       <c r="P108" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q108" s="1">
         <v>0</v>
@@ -5882,7 +5888,7 @@
         <v>1</v>
       </c>
       <c r="P109" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q109" s="1">
         <v>0</v>

--- a/TelemDefinition/DownlinkSpecPacsat.xlsx
+++ b/TelemDefinition/DownlinkSpecPacsat.xlsx
@@ -377,7 +377,7 @@
     <t xml:space="preserve">VoltageVal3v3</t>
   </si>
   <si>
-    <t xml:space="preserve">V</t>
+    <t xml:space="preserve">mV</t>
   </si>
   <si>
     <t xml:space="preserve">Voltage of the 3V3 rail</t>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="F43" s="19"/>
       <c r="G43" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43" s="18" t="s">
         <v>118</v>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="F44" s="19"/>
       <c r="G44" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" s="18" t="s">
         <v>118</v>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="F45" s="19"/>
       <c r="G45" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" s="18" t="s">
         <v>118</v>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="F46" s="19"/>
       <c r="G46" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46" s="18" t="s">
         <v>118</v>
@@ -9006,7 +9006,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B6:I20"/>
-  <sheetFormatPr defaultColWidth="9.31640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.328125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.14"/>

--- a/TelemDefinition/DownlinkSpecPacsat.xlsx
+++ b/TelemDefinition/DownlinkSpecPacsat.xlsx
@@ -431,6 +431,24 @@
     <t xml:space="preserve">ifdef LEGACY_IHU</t>
   </si>
   <si>
+    <t xml:space="preserve">Power Radios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PowerFlagAx5043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radio Power is enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pad155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pad202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pad</t>
+  </si>
+  <si>
     <t xml:space="preserve">Auto Safe Allowed</t>
   </si>
   <si>
@@ -501,24 +519,6 @@
   </si>
   <si>
     <t xml:space="preserve">SSPA Power is enabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power Radios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PowerFlagAx5043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radio Power is enabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pad155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pad202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pad</t>
   </si>
   <si>
     <t xml:space="preserve">endif</t>
@@ -1453,7 +1453,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q1048576"/>
+  <dimension ref="A1:AMJ1048576"/>
   <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.29"/>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="F43" s="19"/>
       <c r="G43" s="18" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H43" s="18" t="s">
         <v>118</v>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="F44" s="19"/>
       <c r="G44" s="18" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H44" s="18" t="s">
         <v>118</v>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="F45" s="19"/>
       <c r="G45" s="18" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H45" s="18" t="s">
         <v>118</v>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="F46" s="19"/>
       <c r="G46" s="18" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H46" s="18" t="s">
         <v>118</v>
@@ -3570,50 +3570,51 @@
       <c r="I53" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="J53" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="22" t="n">
+      <c r="J53" s="1" t="n">
+        <f aca="false">J52+D52</f>
+        <v>0</v>
+      </c>
+      <c r="K53" s="1" t="n">
         <f aca="false">J53/8</f>
         <v>0</v>
       </c>
-      <c r="L53" s="22" t="n">
+      <c r="L53" s="1" t="n">
         <f aca="false">J53/16</f>
         <v>0</v>
       </c>
-      <c r="M53" s="22" t="n">
+      <c r="M53" s="1" t="n">
         <f aca="false">J53/32</f>
         <v>0</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="O53" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P53" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q53" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="23" t="s">
+      <c r="B54" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="C54" s="23" t="s">
+      <c r="C54" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="D54" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F54" s="19"/>
+      <c r="D54" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E54" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" s="18"/>
       <c r="G54" s="18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54" s="18" t="s">
         <v>34</v>
@@ -3638,13 +3639,13 @@
         <v>0.03125</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P54" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="1" t="n">
         <v>0</v>
@@ -3675,28 +3676,28 @@
       </c>
       <c r="J55" s="1" t="n">
         <f aca="false">J54+D54</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K55" s="1" t="n">
         <f aca="false">J55/8</f>
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L55" s="1" t="n">
         <f aca="false">J55/16</f>
-        <v>0.125</v>
+        <v>0.5</v>
       </c>
       <c r="M55" s="1" t="n">
         <f aca="false">J55/32</f>
-        <v>0.0625</v>
+        <v>0.25</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="O55" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q55" s="1" t="n">
         <v>0</v>
@@ -3727,28 +3728,28 @@
       </c>
       <c r="J56" s="1" t="n">
         <f aca="false">J55+D55</f>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K56" s="1" t="n">
         <f aca="false">J56/8</f>
-        <v>0.375</v>
+        <v>1.125</v>
       </c>
       <c r="L56" s="1" t="n">
         <f aca="false">J56/16</f>
-        <v>0.1875</v>
+        <v>0.5625</v>
       </c>
       <c r="M56" s="1" t="n">
         <f aca="false">J56/32</f>
-        <v>0.09375</v>
+        <v>0.28125</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="O56" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P56" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="P56" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="Q56" s="1" t="n">
         <v>0</v>
@@ -3779,19 +3780,19 @@
       </c>
       <c r="J57" s="1" t="n">
         <f aca="false">J56+D56</f>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K57" s="1" t="n">
         <f aca="false">J57/8</f>
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="L57" s="1" t="n">
         <f aca="false">J57/16</f>
-        <v>0.25</v>
+        <v>0.625</v>
       </c>
       <c r="M57" s="1" t="n">
         <f aca="false">J57/32</f>
-        <v>0.125</v>
+        <v>0.3125</v>
       </c>
       <c r="N57" s="1" t="s">
         <v>53</v>
@@ -3800,7 +3801,7 @@
         <v>3</v>
       </c>
       <c r="P57" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q57" s="1" t="n">
         <v>0</v>
@@ -3831,28 +3832,28 @@
       </c>
       <c r="J58" s="1" t="n">
         <f aca="false">J57+D57</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K58" s="1" t="n">
         <f aca="false">J58/8</f>
-        <v>0.625</v>
+        <v>1.375</v>
       </c>
       <c r="L58" s="1" t="n">
         <f aca="false">J58/16</f>
-        <v>0.3125</v>
+        <v>0.6875</v>
       </c>
       <c r="M58" s="1" t="n">
         <f aca="false">J58/32</f>
-        <v>0.15625</v>
+        <v>0.34375</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="O58" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q58" s="1" t="n">
         <v>0</v>
@@ -3883,28 +3884,28 @@
       </c>
       <c r="J59" s="1" t="n">
         <f aca="false">J58+D58</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K59" s="1" t="n">
         <f aca="false">J59/8</f>
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="L59" s="1" t="n">
         <f aca="false">J59/16</f>
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
       <c r="M59" s="1" t="n">
         <f aca="false">J59/32</f>
-        <v>0.1875</v>
+        <v>0.375</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P59" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q59" s="1" t="n">
         <v>0</v>
@@ -3935,28 +3936,28 @@
       </c>
       <c r="J60" s="1" t="n">
         <f aca="false">J59+D59</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K60" s="1" t="n">
         <f aca="false">J60/8</f>
-        <v>0.875</v>
+        <v>1.625</v>
       </c>
       <c r="L60" s="1" t="n">
         <f aca="false">J60/16</f>
-        <v>0.4375</v>
+        <v>0.8125</v>
       </c>
       <c r="M60" s="1" t="n">
         <f aca="false">J60/32</f>
-        <v>0.21875</v>
+        <v>0.40625</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="O60" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Q60" s="1" t="n">
         <v>0</v>
@@ -3987,19 +3988,19 @@
       </c>
       <c r="J61" s="1" t="n">
         <f aca="false">J60+D60</f>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K61" s="1" t="n">
         <f aca="false">J61/8</f>
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="L61" s="1" t="n">
         <f aca="false">J61/16</f>
-        <v>0.5</v>
+        <v>0.875</v>
       </c>
       <c r="M61" s="1" t="n">
         <f aca="false">J61/32</f>
-        <v>0.25</v>
+        <v>0.4375</v>
       </c>
       <c r="N61" s="1" t="s">
         <v>68</v>
@@ -4008,28 +4009,28 @@
         <v>4</v>
       </c>
       <c r="P61" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q61" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="18" t="s">
+      <c r="B62" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="C62" s="18" t="s">
+      <c r="C62" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="D62" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="E62" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="F62" s="18"/>
+      <c r="D62" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62" s="19"/>
       <c r="G62" s="18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" s="18" t="s">
         <v>34</v>
@@ -4038,211 +4039,1133 @@
         <v>165</v>
       </c>
       <c r="J62" s="1" t="n">
-        <f aca="false">J57+D57</f>
-        <v>5</v>
+        <f aca="false">J61+D61</f>
+        <v>15</v>
       </c>
       <c r="K62" s="1" t="n">
         <f aca="false">J62/8</f>
-        <v>0.625</v>
+        <v>1.875</v>
       </c>
       <c r="L62" s="1" t="n">
         <f aca="false">J62/16</f>
-        <v>0.3125</v>
+        <v>0.9375</v>
       </c>
       <c r="M62" s="1" t="n">
         <f aca="false">J62/32</f>
-        <v>0.15625</v>
+        <v>0.46875</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="O62" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P62" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q62" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="0"/>
+      <c r="B63" s="0"/>
+      <c r="C63" s="0"/>
+      <c r="D63" s="0"/>
+      <c r="E63" s="0"/>
+      <c r="F63" s="0"/>
+      <c r="G63" s="0"/>
+      <c r="H63" s="0"/>
+      <c r="I63" s="0"/>
+      <c r="J63" s="0"/>
+      <c r="K63" s="0"/>
+      <c r="L63" s="0"/>
+      <c r="M63" s="0"/>
+      <c r="N63" s="0"/>
+      <c r="O63" s="0"/>
+      <c r="P63" s="0"/>
+      <c r="Q63" s="0"/>
+      <c r="R63" s="0"/>
+      <c r="S63" s="0"/>
+      <c r="T63" s="0"/>
+      <c r="U63" s="0"/>
+      <c r="V63" s="0"/>
+      <c r="W63" s="0"/>
+      <c r="X63" s="0"/>
+      <c r="Y63" s="0"/>
+      <c r="Z63" s="0"/>
+      <c r="AA63" s="0"/>
+      <c r="AB63" s="0"/>
+      <c r="AC63" s="0"/>
+      <c r="AD63" s="0"/>
+      <c r="AE63" s="0"/>
+      <c r="AF63" s="0"/>
+      <c r="AG63" s="0"/>
+      <c r="AH63" s="0"/>
+      <c r="AI63" s="0"/>
+      <c r="AJ63" s="0"/>
+      <c r="AK63" s="0"/>
+      <c r="AL63" s="0"/>
+      <c r="AM63" s="0"/>
+      <c r="AN63" s="0"/>
+      <c r="AO63" s="0"/>
+      <c r="AP63" s="0"/>
+      <c r="AQ63" s="0"/>
+      <c r="AR63" s="0"/>
+      <c r="AS63" s="0"/>
+      <c r="AT63" s="0"/>
+      <c r="AU63" s="0"/>
+      <c r="AV63" s="0"/>
+      <c r="AW63" s="0"/>
+      <c r="AX63" s="0"/>
+      <c r="AY63" s="0"/>
+      <c r="AZ63" s="0"/>
+      <c r="BA63" s="0"/>
+      <c r="BB63" s="0"/>
+      <c r="BC63" s="0"/>
+      <c r="BD63" s="0"/>
+      <c r="BE63" s="0"/>
+      <c r="BF63" s="0"/>
+      <c r="BG63" s="0"/>
+      <c r="BH63" s="0"/>
+      <c r="BI63" s="0"/>
+      <c r="BJ63" s="0"/>
+      <c r="BK63" s="0"/>
+      <c r="BL63" s="0"/>
+      <c r="BM63" s="0"/>
+      <c r="BN63" s="0"/>
+      <c r="BO63" s="0"/>
+      <c r="BP63" s="0"/>
+      <c r="BQ63" s="0"/>
+      <c r="BR63" s="0"/>
+      <c r="BS63" s="0"/>
+      <c r="BT63" s="0"/>
+      <c r="BU63" s="0"/>
+      <c r="BV63" s="0"/>
+      <c r="BW63" s="0"/>
+      <c r="BX63" s="0"/>
+      <c r="BY63" s="0"/>
+      <c r="BZ63" s="0"/>
+      <c r="CA63" s="0"/>
+      <c r="CB63" s="0"/>
+      <c r="CC63" s="0"/>
+      <c r="CD63" s="0"/>
+      <c r="CE63" s="0"/>
+      <c r="CF63" s="0"/>
+      <c r="CG63" s="0"/>
+      <c r="CH63" s="0"/>
+      <c r="CI63" s="0"/>
+      <c r="CJ63" s="0"/>
+      <c r="CK63" s="0"/>
+      <c r="CL63" s="0"/>
+      <c r="CM63" s="0"/>
+      <c r="CN63" s="0"/>
+      <c r="CO63" s="0"/>
+      <c r="CP63" s="0"/>
+      <c r="CQ63" s="0"/>
+      <c r="CR63" s="0"/>
+      <c r="CS63" s="0"/>
+      <c r="CT63" s="0"/>
+      <c r="CU63" s="0"/>
+      <c r="CV63" s="0"/>
+      <c r="CW63" s="0"/>
+      <c r="CX63" s="0"/>
+      <c r="CY63" s="0"/>
+      <c r="CZ63" s="0"/>
+      <c r="DA63" s="0"/>
+      <c r="DB63" s="0"/>
+      <c r="DC63" s="0"/>
+      <c r="DD63" s="0"/>
+      <c r="DE63" s="0"/>
+      <c r="DF63" s="0"/>
+      <c r="DG63" s="0"/>
+      <c r="DH63" s="0"/>
+      <c r="DI63" s="0"/>
+      <c r="DJ63" s="0"/>
+      <c r="DK63" s="0"/>
+      <c r="DL63" s="0"/>
+      <c r="DM63" s="0"/>
+      <c r="DN63" s="0"/>
+      <c r="DO63" s="0"/>
+      <c r="DP63" s="0"/>
+      <c r="DQ63" s="0"/>
+      <c r="DR63" s="0"/>
+      <c r="DS63" s="0"/>
+      <c r="DT63" s="0"/>
+      <c r="DU63" s="0"/>
+      <c r="DV63" s="0"/>
+      <c r="DW63" s="0"/>
+      <c r="DX63" s="0"/>
+      <c r="DY63" s="0"/>
+      <c r="DZ63" s="0"/>
+      <c r="EA63" s="0"/>
+      <c r="EB63" s="0"/>
+      <c r="EC63" s="0"/>
+      <c r="ED63" s="0"/>
+      <c r="EE63" s="0"/>
+      <c r="EF63" s="0"/>
+      <c r="EG63" s="0"/>
+      <c r="EH63" s="0"/>
+      <c r="EI63" s="0"/>
+      <c r="EJ63" s="0"/>
+      <c r="EK63" s="0"/>
+      <c r="EL63" s="0"/>
+      <c r="EM63" s="0"/>
+      <c r="EN63" s="0"/>
+      <c r="EO63" s="0"/>
+      <c r="EP63" s="0"/>
+      <c r="EQ63" s="0"/>
+      <c r="ER63" s="0"/>
+      <c r="ES63" s="0"/>
+      <c r="ET63" s="0"/>
+      <c r="EU63" s="0"/>
+      <c r="EV63" s="0"/>
+      <c r="EW63" s="0"/>
+      <c r="EX63" s="0"/>
+      <c r="EY63" s="0"/>
+      <c r="EZ63" s="0"/>
+      <c r="FA63" s="0"/>
+      <c r="FB63" s="0"/>
+      <c r="FC63" s="0"/>
+      <c r="FD63" s="0"/>
+      <c r="FE63" s="0"/>
+      <c r="FF63" s="0"/>
+      <c r="FG63" s="0"/>
+      <c r="FH63" s="0"/>
+      <c r="FI63" s="0"/>
+      <c r="FJ63" s="0"/>
+      <c r="FK63" s="0"/>
+      <c r="FL63" s="0"/>
+      <c r="FM63" s="0"/>
+      <c r="FN63" s="0"/>
+      <c r="FO63" s="0"/>
+      <c r="FP63" s="0"/>
+      <c r="FQ63" s="0"/>
+      <c r="FR63" s="0"/>
+      <c r="FS63" s="0"/>
+      <c r="FT63" s="0"/>
+      <c r="FU63" s="0"/>
+      <c r="FV63" s="0"/>
+      <c r="FW63" s="0"/>
+      <c r="FX63" s="0"/>
+      <c r="FY63" s="0"/>
+      <c r="FZ63" s="0"/>
+      <c r="GA63" s="0"/>
+      <c r="GB63" s="0"/>
+      <c r="GC63" s="0"/>
+      <c r="GD63" s="0"/>
+      <c r="GE63" s="0"/>
+      <c r="GF63" s="0"/>
+      <c r="GG63" s="0"/>
+      <c r="GH63" s="0"/>
+      <c r="GI63" s="0"/>
+      <c r="GJ63" s="0"/>
+      <c r="GK63" s="0"/>
+      <c r="GL63" s="0"/>
+      <c r="GM63" s="0"/>
+      <c r="GN63" s="0"/>
+      <c r="GO63" s="0"/>
+      <c r="GP63" s="0"/>
+      <c r="GQ63" s="0"/>
+      <c r="GR63" s="0"/>
+      <c r="GS63" s="0"/>
+      <c r="GT63" s="0"/>
+      <c r="GU63" s="0"/>
+      <c r="GV63" s="0"/>
+      <c r="GW63" s="0"/>
+      <c r="GX63" s="0"/>
+      <c r="GY63" s="0"/>
+      <c r="GZ63" s="0"/>
+      <c r="HA63" s="0"/>
+      <c r="HB63" s="0"/>
+      <c r="HC63" s="0"/>
+      <c r="HD63" s="0"/>
+      <c r="HE63" s="0"/>
+      <c r="HF63" s="0"/>
+      <c r="HG63" s="0"/>
+      <c r="HH63" s="0"/>
+      <c r="HI63" s="0"/>
+      <c r="HJ63" s="0"/>
+      <c r="HK63" s="0"/>
+      <c r="HL63" s="0"/>
+      <c r="HM63" s="0"/>
+      <c r="HN63" s="0"/>
+      <c r="HO63" s="0"/>
+      <c r="HP63" s="0"/>
+      <c r="HQ63" s="0"/>
+      <c r="HR63" s="0"/>
+      <c r="HS63" s="0"/>
+      <c r="HT63" s="0"/>
+      <c r="HU63" s="0"/>
+      <c r="HV63" s="0"/>
+      <c r="HW63" s="0"/>
+      <c r="HX63" s="0"/>
+      <c r="HY63" s="0"/>
+      <c r="HZ63" s="0"/>
+      <c r="IA63" s="0"/>
+      <c r="IB63" s="0"/>
+      <c r="IC63" s="0"/>
+      <c r="ID63" s="0"/>
+      <c r="IE63" s="0"/>
+      <c r="IF63" s="0"/>
+      <c r="IG63" s="0"/>
+      <c r="IH63" s="0"/>
+      <c r="II63" s="0"/>
+      <c r="IJ63" s="0"/>
+      <c r="IK63" s="0"/>
+      <c r="IL63" s="0"/>
+      <c r="IM63" s="0"/>
+      <c r="IN63" s="0"/>
+      <c r="IO63" s="0"/>
+      <c r="IP63" s="0"/>
+      <c r="IQ63" s="0"/>
+      <c r="IR63" s="0"/>
+      <c r="IS63" s="0"/>
+      <c r="IT63" s="0"/>
+      <c r="IU63" s="0"/>
+      <c r="IV63" s="0"/>
+      <c r="IW63" s="0"/>
+      <c r="IX63" s="0"/>
+      <c r="IY63" s="0"/>
+      <c r="IZ63" s="0"/>
+      <c r="JA63" s="0"/>
+      <c r="JB63" s="0"/>
+      <c r="JC63" s="0"/>
+      <c r="JD63" s="0"/>
+      <c r="JE63" s="0"/>
+      <c r="JF63" s="0"/>
+      <c r="JG63" s="0"/>
+      <c r="JH63" s="0"/>
+      <c r="JI63" s="0"/>
+      <c r="JJ63" s="0"/>
+      <c r="JK63" s="0"/>
+      <c r="JL63" s="0"/>
+      <c r="JM63" s="0"/>
+      <c r="JN63" s="0"/>
+      <c r="JO63" s="0"/>
+      <c r="JP63" s="0"/>
+      <c r="JQ63" s="0"/>
+      <c r="JR63" s="0"/>
+      <c r="JS63" s="0"/>
+      <c r="JT63" s="0"/>
+      <c r="JU63" s="0"/>
+      <c r="JV63" s="0"/>
+      <c r="JW63" s="0"/>
+      <c r="JX63" s="0"/>
+      <c r="JY63" s="0"/>
+      <c r="JZ63" s="0"/>
+      <c r="KA63" s="0"/>
+      <c r="KB63" s="0"/>
+      <c r="KC63" s="0"/>
+      <c r="KD63" s="0"/>
+      <c r="KE63" s="0"/>
+      <c r="KF63" s="0"/>
+      <c r="KG63" s="0"/>
+      <c r="KH63" s="0"/>
+      <c r="KI63" s="0"/>
+      <c r="KJ63" s="0"/>
+      <c r="KK63" s="0"/>
+      <c r="KL63" s="0"/>
+      <c r="KM63" s="0"/>
+      <c r="KN63" s="0"/>
+      <c r="KO63" s="0"/>
+      <c r="KP63" s="0"/>
+      <c r="KQ63" s="0"/>
+      <c r="KR63" s="0"/>
+      <c r="KS63" s="0"/>
+      <c r="KT63" s="0"/>
+      <c r="KU63" s="0"/>
+      <c r="KV63" s="0"/>
+      <c r="KW63" s="0"/>
+      <c r="KX63" s="0"/>
+      <c r="KY63" s="0"/>
+      <c r="KZ63" s="0"/>
+      <c r="LA63" s="0"/>
+      <c r="LB63" s="0"/>
+      <c r="LC63" s="0"/>
+      <c r="LD63" s="0"/>
+      <c r="LE63" s="0"/>
+      <c r="LF63" s="0"/>
+      <c r="LG63" s="0"/>
+      <c r="LH63" s="0"/>
+      <c r="LI63" s="0"/>
+      <c r="LJ63" s="0"/>
+      <c r="LK63" s="0"/>
+      <c r="LL63" s="0"/>
+      <c r="LM63" s="0"/>
+      <c r="LN63" s="0"/>
+      <c r="LO63" s="0"/>
+      <c r="LP63" s="0"/>
+      <c r="LQ63" s="0"/>
+      <c r="LR63" s="0"/>
+      <c r="LS63" s="0"/>
+      <c r="LT63" s="0"/>
+      <c r="LU63" s="0"/>
+      <c r="LV63" s="0"/>
+      <c r="LW63" s="0"/>
+      <c r="LX63" s="0"/>
+      <c r="LY63" s="0"/>
+      <c r="LZ63" s="0"/>
+      <c r="MA63" s="0"/>
+      <c r="MB63" s="0"/>
+      <c r="MC63" s="0"/>
+      <c r="MD63" s="0"/>
+      <c r="ME63" s="0"/>
+      <c r="MF63" s="0"/>
+      <c r="MG63" s="0"/>
+      <c r="MH63" s="0"/>
+      <c r="MI63" s="0"/>
+      <c r="MJ63" s="0"/>
+      <c r="MK63" s="0"/>
+      <c r="ML63" s="0"/>
+      <c r="MM63" s="0"/>
+      <c r="MN63" s="0"/>
+      <c r="MO63" s="0"/>
+      <c r="MP63" s="0"/>
+      <c r="MQ63" s="0"/>
+      <c r="MR63" s="0"/>
+      <c r="MS63" s="0"/>
+      <c r="MT63" s="0"/>
+      <c r="MU63" s="0"/>
+      <c r="MV63" s="0"/>
+      <c r="MW63" s="0"/>
+      <c r="MX63" s="0"/>
+      <c r="MY63" s="0"/>
+      <c r="MZ63" s="0"/>
+      <c r="NA63" s="0"/>
+      <c r="NB63" s="0"/>
+      <c r="NC63" s="0"/>
+      <c r="ND63" s="0"/>
+      <c r="NE63" s="0"/>
+      <c r="NF63" s="0"/>
+      <c r="NG63" s="0"/>
+      <c r="NH63" s="0"/>
+      <c r="NI63" s="0"/>
+      <c r="NJ63" s="0"/>
+      <c r="NK63" s="0"/>
+      <c r="NL63" s="0"/>
+      <c r="NM63" s="0"/>
+      <c r="NN63" s="0"/>
+      <c r="NO63" s="0"/>
+      <c r="NP63" s="0"/>
+      <c r="NQ63" s="0"/>
+      <c r="NR63" s="0"/>
+      <c r="NS63" s="0"/>
+      <c r="NT63" s="0"/>
+      <c r="NU63" s="0"/>
+      <c r="NV63" s="0"/>
+      <c r="NW63" s="0"/>
+      <c r="NX63" s="0"/>
+      <c r="NY63" s="0"/>
+      <c r="NZ63" s="0"/>
+      <c r="OA63" s="0"/>
+      <c r="OB63" s="0"/>
+      <c r="OC63" s="0"/>
+      <c r="OD63" s="0"/>
+      <c r="OE63" s="0"/>
+      <c r="OF63" s="0"/>
+      <c r="OG63" s="0"/>
+      <c r="OH63" s="0"/>
+      <c r="OI63" s="0"/>
+      <c r="OJ63" s="0"/>
+      <c r="OK63" s="0"/>
+      <c r="OL63" s="0"/>
+      <c r="OM63" s="0"/>
+      <c r="ON63" s="0"/>
+      <c r="OO63" s="0"/>
+      <c r="OP63" s="0"/>
+      <c r="OQ63" s="0"/>
+      <c r="OR63" s="0"/>
+      <c r="OS63" s="0"/>
+      <c r="OT63" s="0"/>
+      <c r="OU63" s="0"/>
+      <c r="OV63" s="0"/>
+      <c r="OW63" s="0"/>
+      <c r="OX63" s="0"/>
+      <c r="OY63" s="0"/>
+      <c r="OZ63" s="0"/>
+      <c r="PA63" s="0"/>
+      <c r="PB63" s="0"/>
+      <c r="PC63" s="0"/>
+      <c r="PD63" s="0"/>
+      <c r="PE63" s="0"/>
+      <c r="PF63" s="0"/>
+      <c r="PG63" s="0"/>
+      <c r="PH63" s="0"/>
+      <c r="PI63" s="0"/>
+      <c r="PJ63" s="0"/>
+      <c r="PK63" s="0"/>
+      <c r="PL63" s="0"/>
+      <c r="PM63" s="0"/>
+      <c r="PN63" s="0"/>
+      <c r="PO63" s="0"/>
+      <c r="PP63" s="0"/>
+      <c r="PQ63" s="0"/>
+      <c r="PR63" s="0"/>
+      <c r="PS63" s="0"/>
+      <c r="PT63" s="0"/>
+      <c r="PU63" s="0"/>
+      <c r="PV63" s="0"/>
+      <c r="PW63" s="0"/>
+      <c r="PX63" s="0"/>
+      <c r="PY63" s="0"/>
+      <c r="PZ63" s="0"/>
+      <c r="QA63" s="0"/>
+      <c r="QB63" s="0"/>
+      <c r="QC63" s="0"/>
+      <c r="QD63" s="0"/>
+      <c r="QE63" s="0"/>
+      <c r="QF63" s="0"/>
+      <c r="QG63" s="0"/>
+      <c r="QH63" s="0"/>
+      <c r="QI63" s="0"/>
+      <c r="QJ63" s="0"/>
+      <c r="QK63" s="0"/>
+      <c r="QL63" s="0"/>
+      <c r="QM63" s="0"/>
+      <c r="QN63" s="0"/>
+      <c r="QO63" s="0"/>
+      <c r="QP63" s="0"/>
+      <c r="QQ63" s="0"/>
+      <c r="QR63" s="0"/>
+      <c r="QS63" s="0"/>
+      <c r="QT63" s="0"/>
+      <c r="QU63" s="0"/>
+      <c r="QV63" s="0"/>
+      <c r="QW63" s="0"/>
+      <c r="QX63" s="0"/>
+      <c r="QY63" s="0"/>
+      <c r="QZ63" s="0"/>
+      <c r="RA63" s="0"/>
+      <c r="RB63" s="0"/>
+      <c r="RC63" s="0"/>
+      <c r="RD63" s="0"/>
+      <c r="RE63" s="0"/>
+      <c r="RF63" s="0"/>
+      <c r="RG63" s="0"/>
+      <c r="RH63" s="0"/>
+      <c r="RI63" s="0"/>
+      <c r="RJ63" s="0"/>
+      <c r="RK63" s="0"/>
+      <c r="RL63" s="0"/>
+      <c r="RM63" s="0"/>
+      <c r="RN63" s="0"/>
+      <c r="RO63" s="0"/>
+      <c r="RP63" s="0"/>
+      <c r="RQ63" s="0"/>
+      <c r="RR63" s="0"/>
+      <c r="RS63" s="0"/>
+      <c r="RT63" s="0"/>
+      <c r="RU63" s="0"/>
+      <c r="RV63" s="0"/>
+      <c r="RW63" s="0"/>
+      <c r="RX63" s="0"/>
+      <c r="RY63" s="0"/>
+      <c r="RZ63" s="0"/>
+      <c r="SA63" s="0"/>
+      <c r="SB63" s="0"/>
+      <c r="SC63" s="0"/>
+      <c r="SD63" s="0"/>
+      <c r="SE63" s="0"/>
+      <c r="SF63" s="0"/>
+      <c r="SG63" s="0"/>
+      <c r="SH63" s="0"/>
+      <c r="SI63" s="0"/>
+      <c r="SJ63" s="0"/>
+      <c r="SK63" s="0"/>
+      <c r="SL63" s="0"/>
+      <c r="SM63" s="0"/>
+      <c r="SN63" s="0"/>
+      <c r="SO63" s="0"/>
+      <c r="SP63" s="0"/>
+      <c r="SQ63" s="0"/>
+      <c r="SR63" s="0"/>
+      <c r="SS63" s="0"/>
+      <c r="ST63" s="0"/>
+      <c r="SU63" s="0"/>
+      <c r="SV63" s="0"/>
+      <c r="SW63" s="0"/>
+      <c r="SX63" s="0"/>
+      <c r="SY63" s="0"/>
+      <c r="SZ63" s="0"/>
+      <c r="TA63" s="0"/>
+      <c r="TB63" s="0"/>
+      <c r="TC63" s="0"/>
+      <c r="TD63" s="0"/>
+      <c r="TE63" s="0"/>
+      <c r="TF63" s="0"/>
+      <c r="TG63" s="0"/>
+      <c r="TH63" s="0"/>
+      <c r="TI63" s="0"/>
+      <c r="TJ63" s="0"/>
+      <c r="TK63" s="0"/>
+      <c r="TL63" s="0"/>
+      <c r="TM63" s="0"/>
+      <c r="TN63" s="0"/>
+      <c r="TO63" s="0"/>
+      <c r="TP63" s="0"/>
+      <c r="TQ63" s="0"/>
+      <c r="TR63" s="0"/>
+      <c r="TS63" s="0"/>
+      <c r="TT63" s="0"/>
+      <c r="TU63" s="0"/>
+      <c r="TV63" s="0"/>
+      <c r="TW63" s="0"/>
+      <c r="TX63" s="0"/>
+      <c r="TY63" s="0"/>
+      <c r="TZ63" s="0"/>
+      <c r="UA63" s="0"/>
+      <c r="UB63" s="0"/>
+      <c r="UC63" s="0"/>
+      <c r="UD63" s="0"/>
+      <c r="UE63" s="0"/>
+      <c r="UF63" s="0"/>
+      <c r="UG63" s="0"/>
+      <c r="UH63" s="0"/>
+      <c r="UI63" s="0"/>
+      <c r="UJ63" s="0"/>
+      <c r="UK63" s="0"/>
+      <c r="UL63" s="0"/>
+      <c r="UM63" s="0"/>
+      <c r="UN63" s="0"/>
+      <c r="UO63" s="0"/>
+      <c r="UP63" s="0"/>
+      <c r="UQ63" s="0"/>
+      <c r="UR63" s="0"/>
+      <c r="US63" s="0"/>
+      <c r="UT63" s="0"/>
+      <c r="UU63" s="0"/>
+      <c r="UV63" s="0"/>
+      <c r="UW63" s="0"/>
+      <c r="UX63" s="0"/>
+      <c r="UY63" s="0"/>
+      <c r="UZ63" s="0"/>
+      <c r="VA63" s="0"/>
+      <c r="VB63" s="0"/>
+      <c r="VC63" s="0"/>
+      <c r="VD63" s="0"/>
+      <c r="VE63" s="0"/>
+      <c r="VF63" s="0"/>
+      <c r="VG63" s="0"/>
+      <c r="VH63" s="0"/>
+      <c r="VI63" s="0"/>
+      <c r="VJ63" s="0"/>
+      <c r="VK63" s="0"/>
+      <c r="VL63" s="0"/>
+      <c r="VM63" s="0"/>
+      <c r="VN63" s="0"/>
+      <c r="VO63" s="0"/>
+      <c r="VP63" s="0"/>
+      <c r="VQ63" s="0"/>
+      <c r="VR63" s="0"/>
+      <c r="VS63" s="0"/>
+      <c r="VT63" s="0"/>
+      <c r="VU63" s="0"/>
+      <c r="VV63" s="0"/>
+      <c r="VW63" s="0"/>
+      <c r="VX63" s="0"/>
+      <c r="VY63" s="0"/>
+      <c r="VZ63" s="0"/>
+      <c r="WA63" s="0"/>
+      <c r="WB63" s="0"/>
+      <c r="WC63" s="0"/>
+      <c r="WD63" s="0"/>
+      <c r="WE63" s="0"/>
+      <c r="WF63" s="0"/>
+      <c r="WG63" s="0"/>
+      <c r="WH63" s="0"/>
+      <c r="WI63" s="0"/>
+      <c r="WJ63" s="0"/>
+      <c r="WK63" s="0"/>
+      <c r="WL63" s="0"/>
+      <c r="WM63" s="0"/>
+      <c r="WN63" s="0"/>
+      <c r="WO63" s="0"/>
+      <c r="WP63" s="0"/>
+      <c r="WQ63" s="0"/>
+      <c r="WR63" s="0"/>
+      <c r="WS63" s="0"/>
+      <c r="WT63" s="0"/>
+      <c r="WU63" s="0"/>
+      <c r="WV63" s="0"/>
+      <c r="WW63" s="0"/>
+      <c r="WX63" s="0"/>
+      <c r="WY63" s="0"/>
+      <c r="WZ63" s="0"/>
+      <c r="XA63" s="0"/>
+      <c r="XB63" s="0"/>
+      <c r="XC63" s="0"/>
+      <c r="XD63" s="0"/>
+      <c r="XE63" s="0"/>
+      <c r="XF63" s="0"/>
+      <c r="XG63" s="0"/>
+      <c r="XH63" s="0"/>
+      <c r="XI63" s="0"/>
+      <c r="XJ63" s="0"/>
+      <c r="XK63" s="0"/>
+      <c r="XL63" s="0"/>
+      <c r="XM63" s="0"/>
+      <c r="XN63" s="0"/>
+      <c r="XO63" s="0"/>
+      <c r="XP63" s="0"/>
+      <c r="XQ63" s="0"/>
+      <c r="XR63" s="0"/>
+      <c r="XS63" s="0"/>
+      <c r="XT63" s="0"/>
+      <c r="XU63" s="0"/>
+      <c r="XV63" s="0"/>
+      <c r="XW63" s="0"/>
+      <c r="XX63" s="0"/>
+      <c r="XY63" s="0"/>
+      <c r="XZ63" s="0"/>
+      <c r="YA63" s="0"/>
+      <c r="YB63" s="0"/>
+      <c r="YC63" s="0"/>
+      <c r="YD63" s="0"/>
+      <c r="YE63" s="0"/>
+      <c r="YF63" s="0"/>
+      <c r="YG63" s="0"/>
+      <c r="YH63" s="0"/>
+      <c r="YI63" s="0"/>
+      <c r="YJ63" s="0"/>
+      <c r="YK63" s="0"/>
+      <c r="YL63" s="0"/>
+      <c r="YM63" s="0"/>
+      <c r="YN63" s="0"/>
+      <c r="YO63" s="0"/>
+      <c r="YP63" s="0"/>
+      <c r="YQ63" s="0"/>
+      <c r="YR63" s="0"/>
+      <c r="YS63" s="0"/>
+      <c r="YT63" s="0"/>
+      <c r="YU63" s="0"/>
+      <c r="YV63" s="0"/>
+      <c r="YW63" s="0"/>
+      <c r="YX63" s="0"/>
+      <c r="YY63" s="0"/>
+      <c r="YZ63" s="0"/>
+      <c r="ZA63" s="0"/>
+      <c r="ZB63" s="0"/>
+      <c r="ZC63" s="0"/>
+      <c r="ZD63" s="0"/>
+      <c r="ZE63" s="0"/>
+      <c r="ZF63" s="0"/>
+      <c r="ZG63" s="0"/>
+      <c r="ZH63" s="0"/>
+      <c r="ZI63" s="0"/>
+      <c r="ZJ63" s="0"/>
+      <c r="ZK63" s="0"/>
+      <c r="ZL63" s="0"/>
+      <c r="ZM63" s="0"/>
+      <c r="ZN63" s="0"/>
+      <c r="ZO63" s="0"/>
+      <c r="ZP63" s="0"/>
+      <c r="ZQ63" s="0"/>
+      <c r="ZR63" s="0"/>
+      <c r="ZS63" s="0"/>
+      <c r="ZT63" s="0"/>
+      <c r="ZU63" s="0"/>
+      <c r="ZV63" s="0"/>
+      <c r="ZW63" s="0"/>
+      <c r="ZX63" s="0"/>
+      <c r="ZY63" s="0"/>
+      <c r="ZZ63" s="0"/>
+      <c r="AAA63" s="0"/>
+      <c r="AAB63" s="0"/>
+      <c r="AAC63" s="0"/>
+      <c r="AAD63" s="0"/>
+      <c r="AAE63" s="0"/>
+      <c r="AAF63" s="0"/>
+      <c r="AAG63" s="0"/>
+      <c r="AAH63" s="0"/>
+      <c r="AAI63" s="0"/>
+      <c r="AAJ63" s="0"/>
+      <c r="AAK63" s="0"/>
+      <c r="AAL63" s="0"/>
+      <c r="AAM63" s="0"/>
+      <c r="AAN63" s="0"/>
+      <c r="AAO63" s="0"/>
+      <c r="AAP63" s="0"/>
+      <c r="AAQ63" s="0"/>
+      <c r="AAR63" s="0"/>
+      <c r="AAS63" s="0"/>
+      <c r="AAT63" s="0"/>
+      <c r="AAU63" s="0"/>
+      <c r="AAV63" s="0"/>
+      <c r="AAW63" s="0"/>
+      <c r="AAX63" s="0"/>
+      <c r="AAY63" s="0"/>
+      <c r="AAZ63" s="0"/>
+      <c r="ABA63" s="0"/>
+      <c r="ABB63" s="0"/>
+      <c r="ABC63" s="0"/>
+      <c r="ABD63" s="0"/>
+      <c r="ABE63" s="0"/>
+      <c r="ABF63" s="0"/>
+      <c r="ABG63" s="0"/>
+      <c r="ABH63" s="0"/>
+      <c r="ABI63" s="0"/>
+      <c r="ABJ63" s="0"/>
+      <c r="ABK63" s="0"/>
+      <c r="ABL63" s="0"/>
+      <c r="ABM63" s="0"/>
+      <c r="ABN63" s="0"/>
+      <c r="ABO63" s="0"/>
+      <c r="ABP63" s="0"/>
+      <c r="ABQ63" s="0"/>
+      <c r="ABR63" s="0"/>
+      <c r="ABS63" s="0"/>
+      <c r="ABT63" s="0"/>
+      <c r="ABU63" s="0"/>
+      <c r="ABV63" s="0"/>
+      <c r="ABW63" s="0"/>
+      <c r="ABX63" s="0"/>
+      <c r="ABY63" s="0"/>
+      <c r="ABZ63" s="0"/>
+      <c r="ACA63" s="0"/>
+      <c r="ACB63" s="0"/>
+      <c r="ACC63" s="0"/>
+      <c r="ACD63" s="0"/>
+      <c r="ACE63" s="0"/>
+      <c r="ACF63" s="0"/>
+      <c r="ACG63" s="0"/>
+      <c r="ACH63" s="0"/>
+      <c r="ACI63" s="0"/>
+      <c r="ACJ63" s="0"/>
+      <c r="ACK63" s="0"/>
+      <c r="ACL63" s="0"/>
+      <c r="ACM63" s="0"/>
+      <c r="ACN63" s="0"/>
+      <c r="ACO63" s="0"/>
+      <c r="ACP63" s="0"/>
+      <c r="ACQ63" s="0"/>
+      <c r="ACR63" s="0"/>
+      <c r="ACS63" s="0"/>
+      <c r="ACT63" s="0"/>
+      <c r="ACU63" s="0"/>
+      <c r="ACV63" s="0"/>
+      <c r="ACW63" s="0"/>
+      <c r="ACX63" s="0"/>
+      <c r="ACY63" s="0"/>
+      <c r="ACZ63" s="0"/>
+      <c r="ADA63" s="0"/>
+      <c r="ADB63" s="0"/>
+      <c r="ADC63" s="0"/>
+      <c r="ADD63" s="0"/>
+      <c r="ADE63" s="0"/>
+      <c r="ADF63" s="0"/>
+      <c r="ADG63" s="0"/>
+      <c r="ADH63" s="0"/>
+      <c r="ADI63" s="0"/>
+      <c r="ADJ63" s="0"/>
+      <c r="ADK63" s="0"/>
+      <c r="ADL63" s="0"/>
+      <c r="ADM63" s="0"/>
+      <c r="ADN63" s="0"/>
+      <c r="ADO63" s="0"/>
+      <c r="ADP63" s="0"/>
+      <c r="ADQ63" s="0"/>
+      <c r="ADR63" s="0"/>
+      <c r="ADS63" s="0"/>
+      <c r="ADT63" s="0"/>
+      <c r="ADU63" s="0"/>
+      <c r="ADV63" s="0"/>
+      <c r="ADW63" s="0"/>
+      <c r="ADX63" s="0"/>
+      <c r="ADY63" s="0"/>
+      <c r="ADZ63" s="0"/>
+      <c r="AEA63" s="0"/>
+      <c r="AEB63" s="0"/>
+      <c r="AEC63" s="0"/>
+      <c r="AED63" s="0"/>
+      <c r="AEE63" s="0"/>
+      <c r="AEF63" s="0"/>
+      <c r="AEG63" s="0"/>
+      <c r="AEH63" s="0"/>
+      <c r="AEI63" s="0"/>
+      <c r="AEJ63" s="0"/>
+      <c r="AEK63" s="0"/>
+      <c r="AEL63" s="0"/>
+      <c r="AEM63" s="0"/>
+      <c r="AEN63" s="0"/>
+      <c r="AEO63" s="0"/>
+      <c r="AEP63" s="0"/>
+      <c r="AEQ63" s="0"/>
+      <c r="AER63" s="0"/>
+      <c r="AES63" s="0"/>
+      <c r="AET63" s="0"/>
+      <c r="AEU63" s="0"/>
+      <c r="AEV63" s="0"/>
+      <c r="AEW63" s="0"/>
+      <c r="AEX63" s="0"/>
+      <c r="AEY63" s="0"/>
+      <c r="AEZ63" s="0"/>
+      <c r="AFA63" s="0"/>
+      <c r="AFB63" s="0"/>
+      <c r="AFC63" s="0"/>
+      <c r="AFD63" s="0"/>
+      <c r="AFE63" s="0"/>
+      <c r="AFF63" s="0"/>
+      <c r="AFG63" s="0"/>
+      <c r="AFH63" s="0"/>
+      <c r="AFI63" s="0"/>
+      <c r="AFJ63" s="0"/>
+      <c r="AFK63" s="0"/>
+      <c r="AFL63" s="0"/>
+      <c r="AFM63" s="0"/>
+      <c r="AFN63" s="0"/>
+      <c r="AFO63" s="0"/>
+      <c r="AFP63" s="0"/>
+      <c r="AFQ63" s="0"/>
+      <c r="AFR63" s="0"/>
+      <c r="AFS63" s="0"/>
+      <c r="AFT63" s="0"/>
+      <c r="AFU63" s="0"/>
+      <c r="AFV63" s="0"/>
+      <c r="AFW63" s="0"/>
+      <c r="AFX63" s="0"/>
+      <c r="AFY63" s="0"/>
+      <c r="AFZ63" s="0"/>
+      <c r="AGA63" s="0"/>
+      <c r="AGB63" s="0"/>
+      <c r="AGC63" s="0"/>
+      <c r="AGD63" s="0"/>
+      <c r="AGE63" s="0"/>
+      <c r="AGF63" s="0"/>
+      <c r="AGG63" s="0"/>
+      <c r="AGH63" s="0"/>
+      <c r="AGI63" s="0"/>
+      <c r="AGJ63" s="0"/>
+      <c r="AGK63" s="0"/>
+      <c r="AGL63" s="0"/>
+      <c r="AGM63" s="0"/>
+      <c r="AGN63" s="0"/>
+      <c r="AGO63" s="0"/>
+      <c r="AGP63" s="0"/>
+      <c r="AGQ63" s="0"/>
+      <c r="AGR63" s="0"/>
+      <c r="AGS63" s="0"/>
+      <c r="AGT63" s="0"/>
+      <c r="AGU63" s="0"/>
+      <c r="AGV63" s="0"/>
+      <c r="AGW63" s="0"/>
+      <c r="AGX63" s="0"/>
+      <c r="AGY63" s="0"/>
+      <c r="AGZ63" s="0"/>
+      <c r="AHA63" s="0"/>
+      <c r="AHB63" s="0"/>
+      <c r="AHC63" s="0"/>
+      <c r="AHD63" s="0"/>
+      <c r="AHE63" s="0"/>
+      <c r="AHF63" s="0"/>
+      <c r="AHG63" s="0"/>
+      <c r="AHH63" s="0"/>
+      <c r="AHI63" s="0"/>
+      <c r="AHJ63" s="0"/>
+      <c r="AHK63" s="0"/>
+      <c r="AHL63" s="0"/>
+      <c r="AHM63" s="0"/>
+      <c r="AHN63" s="0"/>
+      <c r="AHO63" s="0"/>
+      <c r="AHP63" s="0"/>
+      <c r="AHQ63" s="0"/>
+      <c r="AHR63" s="0"/>
+      <c r="AHS63" s="0"/>
+      <c r="AHT63" s="0"/>
+      <c r="AHU63" s="0"/>
+      <c r="AHV63" s="0"/>
+      <c r="AHW63" s="0"/>
+      <c r="AHX63" s="0"/>
+      <c r="AHY63" s="0"/>
+      <c r="AHZ63" s="0"/>
+      <c r="AIA63" s="0"/>
+      <c r="AIB63" s="0"/>
+      <c r="AIC63" s="0"/>
+      <c r="AID63" s="0"/>
+      <c r="AIE63" s="0"/>
+      <c r="AIF63" s="0"/>
+      <c r="AIG63" s="0"/>
+      <c r="AIH63" s="0"/>
+      <c r="AII63" s="0"/>
+      <c r="AIJ63" s="0"/>
+      <c r="AIK63" s="0"/>
+      <c r="AIL63" s="0"/>
+      <c r="AIM63" s="0"/>
+      <c r="AIN63" s="0"/>
+      <c r="AIO63" s="0"/>
+      <c r="AIP63" s="0"/>
+      <c r="AIQ63" s="0"/>
+      <c r="AIR63" s="0"/>
+      <c r="AIS63" s="0"/>
+      <c r="AIT63" s="0"/>
+      <c r="AIU63" s="0"/>
+      <c r="AIV63" s="0"/>
+      <c r="AIW63" s="0"/>
+      <c r="AIX63" s="0"/>
+      <c r="AIY63" s="0"/>
+      <c r="AIZ63" s="0"/>
+      <c r="AJA63" s="0"/>
+      <c r="AJB63" s="0"/>
+      <c r="AJC63" s="0"/>
+      <c r="AJD63" s="0"/>
+      <c r="AJE63" s="0"/>
+      <c r="AJF63" s="0"/>
+      <c r="AJG63" s="0"/>
+      <c r="AJH63" s="0"/>
+      <c r="AJI63" s="0"/>
+      <c r="AJJ63" s="0"/>
+      <c r="AJK63" s="0"/>
+      <c r="AJL63" s="0"/>
+      <c r="AJM63" s="0"/>
+      <c r="AJN63" s="0"/>
+      <c r="AJO63" s="0"/>
+      <c r="AJP63" s="0"/>
+      <c r="AJQ63" s="0"/>
+      <c r="AJR63" s="0"/>
+      <c r="AJS63" s="0"/>
+      <c r="AJT63" s="0"/>
+      <c r="AJU63" s="0"/>
+      <c r="AJV63" s="0"/>
+      <c r="AJW63" s="0"/>
+      <c r="AJX63" s="0"/>
+      <c r="AJY63" s="0"/>
+      <c r="AJZ63" s="0"/>
+      <c r="AKA63" s="0"/>
+      <c r="AKB63" s="0"/>
+      <c r="AKC63" s="0"/>
+      <c r="AKD63" s="0"/>
+      <c r="AKE63" s="0"/>
+      <c r="AKF63" s="0"/>
+      <c r="AKG63" s="0"/>
+      <c r="AKH63" s="0"/>
+      <c r="AKI63" s="0"/>
+      <c r="AKJ63" s="0"/>
+      <c r="AKK63" s="0"/>
+      <c r="AKL63" s="0"/>
+      <c r="AKM63" s="0"/>
+      <c r="AKN63" s="0"/>
+      <c r="AKO63" s="0"/>
+      <c r="AKP63" s="0"/>
+      <c r="AKQ63" s="0"/>
+      <c r="AKR63" s="0"/>
+      <c r="AKS63" s="0"/>
+      <c r="AKT63" s="0"/>
+      <c r="AKU63" s="0"/>
+      <c r="AKV63" s="0"/>
+      <c r="AKW63" s="0"/>
+      <c r="AKX63" s="0"/>
+      <c r="AKY63" s="0"/>
+      <c r="AKZ63" s="0"/>
+      <c r="ALA63" s="0"/>
+      <c r="ALB63" s="0"/>
+      <c r="ALC63" s="0"/>
+      <c r="ALD63" s="0"/>
+      <c r="ALE63" s="0"/>
+      <c r="ALF63" s="0"/>
+      <c r="ALG63" s="0"/>
+      <c r="ALH63" s="0"/>
+      <c r="ALI63" s="0"/>
+      <c r="ALJ63" s="0"/>
+      <c r="ALK63" s="0"/>
+      <c r="ALL63" s="0"/>
+      <c r="ALM63" s="0"/>
+      <c r="ALN63" s="0"/>
+      <c r="ALO63" s="0"/>
+      <c r="ALP63" s="0"/>
+      <c r="ALQ63" s="0"/>
+      <c r="ALR63" s="0"/>
+      <c r="ALS63" s="0"/>
+      <c r="ALT63" s="0"/>
+      <c r="ALU63" s="0"/>
+      <c r="ALV63" s="0"/>
+      <c r="ALW63" s="0"/>
+      <c r="ALX63" s="0"/>
+      <c r="ALY63" s="0"/>
+      <c r="ALZ63" s="0"/>
+      <c r="AMA63" s="0"/>
+      <c r="AMB63" s="0"/>
+      <c r="AMC63" s="0"/>
+      <c r="AMD63" s="0"/>
+      <c r="AME63" s="0"/>
+      <c r="AMF63" s="0"/>
+      <c r="AMG63" s="0"/>
+      <c r="AMH63" s="0"/>
+      <c r="AMI63" s="0"/>
+      <c r="AMJ63" s="0"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B63" s="18"/>
-      <c r="C63" s="18"/>
-      <c r="D63" s="18"/>
-      <c r="E63" s="18"/>
-      <c r="F63" s="18"/>
-      <c r="G63" s="18"/>
-      <c r="H63" s="18"/>
-      <c r="I63" s="19"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="18"/>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="18"/>
+      <c r="H65" s="18"/>
+      <c r="I65" s="19"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B64" s="18"/>
-      <c r="C64" s="18"/>
-      <c r="D64" s="18"/>
-      <c r="E64" s="18"/>
-      <c r="F64" s="18"/>
-      <c r="G64" s="18"/>
-      <c r="H64" s="18"/>
-      <c r="I64" s="19"/>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="C65" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="D65" s="18" t="n">
+      <c r="B66" s="18"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="18"/>
+      <c r="E66" s="18"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="18"/>
+      <c r="H66" s="18"/>
+      <c r="I66" s="19"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C67" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D67" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="E65" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="F65" s="18"/>
-      <c r="G65" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I65" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="J65" s="1" t="n">
-        <f aca="false">J64+D64</f>
-        <v>0</v>
-      </c>
-      <c r="K65" s="1" t="n">
-        <f aca="false">J65/8</f>
-        <v>0</v>
-      </c>
-      <c r="L65" s="1" t="n">
-        <f aca="false">J65/16</f>
-        <v>0</v>
-      </c>
-      <c r="M65" s="1" t="n">
-        <f aca="false">J65/32</f>
-        <v>0</v>
-      </c>
-      <c r="N65" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="C66" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="D66" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F66" s="19"/>
-      <c r="G66" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H66" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I66" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="J66" s="1" t="n">
-        <f aca="false">J65+D65</f>
-        <v>7</v>
-      </c>
-      <c r="K66" s="1" t="n">
-        <f aca="false">J66/8</f>
-        <v>0.875</v>
-      </c>
-      <c r="L66" s="1" t="n">
-        <f aca="false">J66/16</f>
-        <v>0.4375</v>
-      </c>
-      <c r="M66" s="1" t="n">
-        <f aca="false">J66/32</f>
-        <v>0.21875</v>
-      </c>
-      <c r="N66" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="O66" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="P66" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q66" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="C67" s="23" t="s">
-        <v>158</v>
-      </c>
-      <c r="D67" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F67" s="19"/>
+      <c r="E67" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F67" s="18"/>
       <c r="G67" s="18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" s="18" t="s">
         <v>34</v>
       </c>
       <c r="I67" s="19" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="J67" s="1" t="n">
         <f aca="false">J66+D66</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K67" s="1" t="n">
         <f aca="false">J67/8</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" s="1" t="n">
         <f aca="false">J67/16</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M67" s="1" t="n">
         <f aca="false">J67/32</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q67" s="1" t="n">
         <v>0</v>
@@ -4250,10 +5173,10 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="23" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="D68" s="23" t="n">
         <v>1</v>
@@ -4269,23 +5192,23 @@
         <v>34</v>
       </c>
       <c r="I68" s="19" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="J68" s="1" t="n">
         <f aca="false">J67+D67</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K68" s="1" t="n">
         <f aca="false">J68/8</f>
-        <v>1.125</v>
+        <v>0.875</v>
       </c>
       <c r="L68" s="1" t="n">
         <f aca="false">J68/16</f>
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="M68" s="1" t="n">
         <f aca="false">J68/32</f>
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="N68" s="1" t="s">
         <v>68</v>
@@ -4294,7 +5217,7 @@
         <v>4</v>
       </c>
       <c r="P68" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q68" s="1" t="n">
         <v>0</v>
@@ -4302,10 +5225,10 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="23" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="C69" s="23" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="D69" s="23" t="n">
         <v>1</v>
@@ -4321,32 +5244,32 @@
         <v>34</v>
       </c>
       <c r="I69" s="19" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="J69" s="1" t="n">
         <f aca="false">J68+D68</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K69" s="1" t="n">
         <f aca="false">J69/8</f>
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="L69" s="1" t="n">
         <f aca="false">J69/16</f>
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="M69" s="1" t="n">
         <f aca="false">J69/32</f>
-        <v>0.3125</v>
+        <v>0.25</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P69" s="1" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q69" s="1" t="n">
         <v>0</v>
@@ -4354,10 +5277,10 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="23" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="C70" s="23" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="D70" s="23" t="n">
         <v>1</v>
@@ -4373,32 +5296,32 @@
         <v>34</v>
       </c>
       <c r="I70" s="19" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="J70" s="1" t="n">
         <f aca="false">J69+D69</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K70" s="1" t="n">
         <f aca="false">J70/8</f>
-        <v>1.375</v>
+        <v>1.125</v>
       </c>
       <c r="L70" s="1" t="n">
         <f aca="false">J70/16</f>
-        <v>0.6875</v>
+        <v>0.5625</v>
       </c>
       <c r="M70" s="1" t="n">
         <f aca="false">J70/32</f>
-        <v>0.34375</v>
+        <v>0.28125</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P70" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q70" s="1" t="n">
         <v>0</v>
@@ -4406,10 +5329,10 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="23" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="D71" s="23" t="n">
         <v>1</v>
@@ -4425,32 +5348,32 @@
         <v>34</v>
       </c>
       <c r="I71" s="19" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="J71" s="1" t="n">
         <f aca="false">J70+D70</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K71" s="1" t="n">
         <f aca="false">J71/8</f>
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="L71" s="1" t="n">
         <f aca="false">J71/16</f>
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="M71" s="1" t="n">
         <f aca="false">J71/32</f>
-        <v>0.375</v>
+        <v>0.3125</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Q71" s="1" t="n">
         <v>0</v>
@@ -4458,10 +5381,10 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="23" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="D72" s="23" t="n">
         <v>1</v>
@@ -4477,23 +5400,23 @@
         <v>34</v>
       </c>
       <c r="I72" s="19" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="J72" s="1" t="n">
         <f aca="false">J71+D71</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K72" s="1" t="n">
         <f aca="false">J72/8</f>
-        <v>1.625</v>
+        <v>1.375</v>
       </c>
       <c r="L72" s="1" t="n">
         <f aca="false">J72/16</f>
-        <v>0.8125</v>
+        <v>0.6875</v>
       </c>
       <c r="M72" s="1" t="n">
         <f aca="false">J72/32</f>
-        <v>0.40625</v>
+        <v>0.34375</v>
       </c>
       <c r="N72" s="1" t="s">
         <v>53</v>
@@ -4502,7 +5425,7 @@
         <v>3</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q72" s="1" t="n">
         <v>0</v>
@@ -4510,10 +5433,10 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="23" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="C73" s="23" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="D73" s="23" t="n">
         <v>1</v>
@@ -4529,32 +5452,32 @@
         <v>34</v>
       </c>
       <c r="I73" s="19" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="J73" s="1" t="n">
         <f aca="false">J72+D72</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K73" s="1" t="n">
         <f aca="false">J73/8</f>
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="L73" s="1" t="n">
         <f aca="false">J73/16</f>
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="M73" s="1" t="n">
         <f aca="false">J73/32</f>
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="O73" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P73" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q73" s="1" t="n">
         <v>0</v>
@@ -4562,10 +5485,10 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="23" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="C74" s="23" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D74" s="23" t="n">
         <v>1</v>
@@ -4581,160 +5504,160 @@
         <v>34</v>
       </c>
       <c r="I74" s="19" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="J74" s="1" t="n">
         <f aca="false">J73+D73</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K74" s="1" t="n">
         <f aca="false">J74/8</f>
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="L74" s="1" t="n">
         <f aca="false">J74/16</f>
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="M74" s="1" t="n">
         <f aca="false">J74/32</f>
-        <v>0.46875</v>
+        <v>0.40625</v>
       </c>
       <c r="N74" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O74" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P74" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q74" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="C75" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="D75" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F75" s="19"/>
+      <c r="G75" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I75" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="J75" s="1" t="n">
+        <f aca="false">J74+D74</f>
+        <v>14</v>
+      </c>
+      <c r="K75" s="1" t="n">
+        <f aca="false">J75/8</f>
+        <v>1.75</v>
+      </c>
+      <c r="L75" s="1" t="n">
+        <f aca="false">J75/16</f>
+        <v>0.875</v>
+      </c>
+      <c r="M75" s="1" t="n">
+        <f aca="false">J75/32</f>
+        <v>0.4375</v>
+      </c>
+      <c r="N75" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="O74" s="3" t="n">
+      <c r="O75" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="P74" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q74" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B75" s="18"/>
-      <c r="C75" s="18"/>
-      <c r="D75" s="18"/>
-      <c r="E75" s="18"/>
-      <c r="F75" s="18"/>
-      <c r="G75" s="18"/>
-      <c r="H75" s="18"/>
-      <c r="I75" s="19"/>
+      <c r="P75" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q75" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="C76" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="D76" s="18" t="n">
-        <v>8</v>
+      <c r="B76" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="C76" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="D76" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="E76" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F76" s="18"/>
+      <c r="F76" s="19"/>
       <c r="G76" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H76" s="18" t="s">
         <v>34</v>
       </c>
       <c r="I76" s="19" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="J76" s="1" t="n">
-        <f aca="false">J74+D74</f>
-        <v>16</v>
+        <f aca="false">J75+D75</f>
+        <v>15</v>
       </c>
       <c r="K76" s="1" t="n">
         <f aca="false">J76/8</f>
-        <v>2</v>
+        <v>1.875</v>
       </c>
       <c r="L76" s="1" t="n">
         <f aca="false">J76/16</f>
-        <v>1</v>
+        <v>0.9375</v>
       </c>
       <c r="M76" s="1" t="n">
         <f aca="false">J76/32</f>
-        <v>0.5</v>
+        <v>0.46875</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P76" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Q76" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="C77" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="D77" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="E77" s="19" t="s">
-        <v>25</v>
-      </c>
+      <c r="A77" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B77" s="18"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="18"/>
       <c r="F77" s="18"/>
-      <c r="G77" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="H77" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="I77" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="J77" s="1" t="n">
-        <f aca="false">J76+D76</f>
-        <v>24</v>
-      </c>
-      <c r="K77" s="1" t="n">
-        <f aca="false">J77/8</f>
-        <v>3</v>
-      </c>
-      <c r="L77" s="1" t="n">
-        <f aca="false">J77/16</f>
-        <v>1.5</v>
-      </c>
-      <c r="M77" s="1" t="n">
-        <f aca="false">J77/32</f>
-        <v>0.75</v>
-      </c>
-      <c r="N77" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="O77" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P77" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q77" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="G77" s="18"/>
+      <c r="H77" s="18"/>
+      <c r="I77" s="19"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="18" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D78" s="18" t="n">
         <v>8</v>
@@ -4744,29 +5667,29 @@
       </c>
       <c r="F78" s="18"/>
       <c r="G78" s="18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H78" s="18" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="I78" s="19" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="J78" s="1" t="n">
-        <f aca="false">J77+D77</f>
-        <v>32</v>
+        <f aca="false">J76+D76</f>
+        <v>16</v>
       </c>
       <c r="K78" s="1" t="n">
         <f aca="false">J78/8</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L78" s="1" t="n">
         <f aca="false">J78/16</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M78" s="1" t="n">
         <f aca="false">J78/32</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N78" s="1" t="s">
         <v>44</v>
@@ -4775,7 +5698,7 @@
         <v>1</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q78" s="1" t="n">
         <v>0</v>
@@ -4783,10 +5706,10 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="18" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D79" s="18" t="n">
         <v>8</v>
@@ -4802,23 +5725,23 @@
         <v>173</v>
       </c>
       <c r="I79" s="19" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="J79" s="1" t="n">
         <f aca="false">J78+D78</f>
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="K79" s="1" t="n">
         <f aca="false">J79/8</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L79" s="1" t="n">
         <f aca="false">J79/16</f>
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="M79" s="1" t="n">
         <f aca="false">J79/32</f>
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="N79" s="1" t="s">
         <v>44</v>
@@ -4827,18 +5750,18 @@
         <v>1</v>
       </c>
       <c r="P79" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q79" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="18" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C80" s="18" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D80" s="18" t="n">
         <v>8</v>
@@ -4848,29 +5771,29 @@
       </c>
       <c r="F80" s="18"/>
       <c r="G80" s="18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H80" s="18" t="s">
-        <v>51</v>
+        <v>173</v>
       </c>
       <c r="I80" s="19" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="J80" s="1" t="n">
         <f aca="false">J79+D79</f>
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K80" s="1" t="n">
         <f aca="false">J80/8</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L80" s="1" t="n">
         <f aca="false">J80/16</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M80" s="1" t="n">
         <f aca="false">J80/32</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="N80" s="1" t="s">
         <v>44</v>
@@ -4879,18 +5802,18 @@
         <v>1</v>
       </c>
       <c r="P80" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q80" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="18" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C81" s="18" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D81" s="18" t="n">
         <v>8</v>
@@ -4900,29 +5823,29 @@
       </c>
       <c r="F81" s="18"/>
       <c r="G81" s="18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H81" s="18" t="s">
-        <v>51</v>
+        <v>173</v>
       </c>
       <c r="I81" s="19" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="J81" s="1" t="n">
         <f aca="false">J80+D80</f>
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="K81" s="1" t="n">
         <f aca="false">J81/8</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L81" s="1" t="n">
         <f aca="false">J81/16</f>
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="M81" s="1" t="n">
         <f aca="false">J81/32</f>
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="N81" s="1" t="s">
         <v>44</v>
@@ -4931,7 +5854,7 @@
         <v>1</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q81" s="1" t="n">
         <v>0</v>
@@ -4939,10 +5862,10 @@
     </row>
     <row r="82" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="18" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C82" s="18" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D82" s="18" t="n">
         <v>8</v>
@@ -4952,49 +5875,49 @@
       </c>
       <c r="F82" s="18"/>
       <c r="G82" s="18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H82" s="18" t="s">
-        <v>173</v>
+        <v>51</v>
       </c>
       <c r="I82" s="19" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="J82" s="1" t="n">
         <f aca="false">J81+D81</f>
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="K82" s="1" t="n">
         <f aca="false">J82/8</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L82" s="1" t="n">
         <f aca="false">J82/16</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M82" s="1" t="n">
         <f aca="false">J82/32</f>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="O82" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q82" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="18" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C83" s="18" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D83" s="18" t="n">
         <v>8</v>
@@ -5004,49 +5927,49 @@
       </c>
       <c r="F83" s="18"/>
       <c r="G83" s="18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H83" s="18" t="s">
-        <v>173</v>
+        <v>51</v>
       </c>
       <c r="I83" s="19" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="J83" s="1" t="n">
         <f aca="false">J82+D82</f>
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="K83" s="1" t="n">
         <f aca="false">J83/8</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L83" s="1" t="n">
         <f aca="false">J83/16</f>
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="M83" s="1" t="n">
         <f aca="false">J83/32</f>
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="O83" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q83" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B84" s="18" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C84" s="18" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D84" s="18" t="n">
         <v>8</v>
@@ -5062,23 +5985,23 @@
         <v>173</v>
       </c>
       <c r="I84" s="19" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="J84" s="1" t="n">
         <f aca="false">J83+D83</f>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="K84" s="1" t="n">
         <f aca="false">J84/8</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L84" s="1" t="n">
         <f aca="false">J84/16</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M84" s="1" t="n">
         <f aca="false">J84/32</f>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="N84" s="1" t="s">
         <v>53</v>
@@ -5087,206 +6010,206 @@
         <v>3</v>
       </c>
       <c r="P84" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q84" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="23" t="s">
-        <v>196</v>
-      </c>
-      <c r="C85" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="D85" s="23" t="n">
+      <c r="B85" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="C85" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="D85" s="18" t="n">
         <v>8</v>
       </c>
       <c r="E85" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="F85" s="19"/>
+        <v>25</v>
+      </c>
+      <c r="F85" s="18"/>
       <c r="G85" s="18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H85" s="18" t="s">
-        <v>34</v>
+        <v>173</v>
       </c>
       <c r="I85" s="19" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="J85" s="1" t="n">
         <f aca="false">J84+D84</f>
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="K85" s="1" t="n">
         <f aca="false">J85/8</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L85" s="1" t="n">
         <f aca="false">J85/16</f>
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="M85" s="1" t="n">
         <f aca="false">J85/32</f>
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P85" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q85" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="C86" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="D86" s="23" t="n">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="C86" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="D86" s="18" t="n">
         <v>8</v>
       </c>
       <c r="E86" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F86" s="19"/>
+      <c r="F86" s="18"/>
       <c r="G86" s="18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H86" s="18" t="s">
-        <v>34</v>
+        <v>173</v>
       </c>
       <c r="I86" s="19" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="J86" s="1" t="n">
         <f aca="false">J85+D85</f>
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="K86" s="1" t="n">
         <f aca="false">J86/8</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L86" s="1" t="n">
         <f aca="false">J86/16</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M86" s="1" t="n">
         <f aca="false">J86/32</f>
+        <v>2.5</v>
+      </c>
+      <c r="N86" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O86" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="N86" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="O86" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="P86" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q86" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="C87" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="D87" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="Q86" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="C87" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="D87" s="21" t="n">
-        <v>24</v>
-      </c>
-      <c r="E87" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="F87" s="18"/>
+      <c r="E87" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F87" s="19"/>
       <c r="G87" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H87" s="18" t="s">
         <v>34</v>
       </c>
       <c r="I87" s="19" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="J87" s="1" t="n">
         <f aca="false">J86+D86</f>
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="K87" s="1" t="n">
         <f aca="false">J87/8</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L87" s="1" t="n">
         <f aca="false">J87/16</f>
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="M87" s="1" t="n">
         <f aca="false">J87/32</f>
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="O87" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q87" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="23" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C88" s="23" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D88" s="23" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E88" s="19" t="s">
         <v>25</v>
       </c>
       <c r="F88" s="19"/>
       <c r="G88" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H88" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="I88" s="23" t="s">
-        <v>206</v>
+      <c r="I88" s="19" t="s">
+        <v>201</v>
       </c>
       <c r="J88" s="1" t="n">
         <f aca="false">J87+D87</f>
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="K88" s="1" t="n">
         <f aca="false">J88/8</f>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L88" s="1" t="n">
         <f aca="false">J88/16</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M88" s="1" t="n">
         <f aca="false">J88/32</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N88" s="1" t="s">
         <v>44</v>
@@ -5295,26 +6218,26 @@
         <v>1</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q88" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="23" t="s">
-        <v>207</v>
+        <v>129</v>
       </c>
       <c r="C89" s="23" t="s">
-        <v>208</v>
-      </c>
-      <c r="D89" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E89" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="F89" s="19"/>
+        <v>202</v>
+      </c>
+      <c r="D89" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="E89" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F89" s="18"/>
       <c r="G89" s="18" t="n">
         <v>0</v>
       </c>
@@ -5322,32 +6245,32 @@
         <v>34</v>
       </c>
       <c r="I89" s="19" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="J89" s="1" t="n">
         <f aca="false">J88+D88</f>
-        <v>160</v>
+        <v>104</v>
       </c>
       <c r="K89" s="1" t="n">
         <f aca="false">J89/8</f>
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="L89" s="1" t="n">
         <f aca="false">J89/16</f>
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="M89" s="1" t="n">
         <f aca="false">J89/32</f>
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P89" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q89" s="1" t="n">
         <v>0</v>
@@ -5355,16 +6278,16 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="23" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C90" s="23" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D90" s="23" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E90" s="19" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="F90" s="19"/>
       <c r="G90" s="18" t="n">
@@ -5373,33 +6296,33 @@
       <c r="H90" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="I90" s="19" t="s">
-        <v>212</v>
+      <c r="I90" s="23" t="s">
+        <v>206</v>
       </c>
       <c r="J90" s="1" t="n">
         <f aca="false">J89+D89</f>
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="K90" s="1" t="n">
         <f aca="false">J90/8</f>
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="L90" s="1" t="n">
         <f aca="false">J90/16</f>
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="M90" s="1" t="n">
         <f aca="false">J90/32</f>
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>109</v>
+        <v>44</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P90" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q90" s="1" t="n">
         <v>0</v>
@@ -5407,10 +6330,10 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="23" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C91" s="23" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D91" s="23" t="n">
         <v>8</v>
@@ -5426,23 +6349,23 @@
         <v>34</v>
       </c>
       <c r="I91" s="19" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="J91" s="1" t="n">
         <f aca="false">J90+D90</f>
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="K91" s="1" t="n">
         <f aca="false">J91/8</f>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L91" s="1" t="n">
         <f aca="false">J91/16</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M91" s="1" t="n">
         <f aca="false">J91/32</f>
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="N91" s="1" t="s">
         <v>109</v>
@@ -5451,7 +6374,7 @@
         <v>2</v>
       </c>
       <c r="P91" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q91" s="1" t="n">
         <v>0</v>
@@ -5459,10 +6382,10 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="23" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C92" s="23" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D92" s="23" t="n">
         <v>8</v>
@@ -5478,23 +6401,23 @@
         <v>34</v>
       </c>
       <c r="I92" s="19" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="J92" s="1" t="n">
         <f aca="false">J91+D91</f>
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="K92" s="1" t="n">
         <f aca="false">J92/8</f>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L92" s="1" t="n">
         <f aca="false">J92/16</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="M92" s="1" t="n">
         <f aca="false">J92/32</f>
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="N92" s="1" t="s">
         <v>109</v>
@@ -5503,282 +6426,286 @@
         <v>2</v>
       </c>
       <c r="P92" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q92" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="93" s="13" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B93" s="24"/>
-      <c r="C93" s="25"/>
-      <c r="D93" s="26"/>
-      <c r="E93" s="26"/>
-      <c r="F93" s="26"/>
-      <c r="G93" s="26"/>
-      <c r="H93" s="25"/>
-      <c r="I93" s="26" t="s">
-        <v>219</v>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B93" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="C93" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="D93" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E93" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F93" s="19"/>
+      <c r="G93" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I93" s="19" t="s">
+        <v>215</v>
       </c>
       <c r="J93" s="1" t="n">
         <f aca="false">J92+D92</f>
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="K93" s="1" t="n">
         <f aca="false">J93/8</f>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L93" s="1" t="n">
         <f aca="false">J93/16</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M93" s="1" t="n">
         <f aca="false">J93/32</f>
+        <v>5.5</v>
+      </c>
+      <c r="N93" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="O93" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P93" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="O93" s="17"/>
+      <c r="Q93" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="20"/>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="B94" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="C94" s="23" t="s">
+        <v>217</v>
+      </c>
+      <c r="D94" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E94" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F94" s="19"/>
+      <c r="G94" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I94" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="J94" s="1" t="n">
+        <f aca="false">J93+D93</f>
+        <v>184</v>
+      </c>
+      <c r="K94" s="1" t="n">
+        <f aca="false">J94/8</f>
+        <v>23</v>
+      </c>
+      <c r="L94" s="1" t="n">
+        <f aca="false">J94/16</f>
+        <v>11.5</v>
+      </c>
+      <c r="M94" s="1" t="n">
+        <f aca="false">J94/32</f>
+        <v>5.75</v>
+      </c>
+      <c r="N94" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="O94" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P94" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q94" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" s="13" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B95" s="24"/>
+      <c r="C95" s="25"/>
+      <c r="D95" s="26"/>
+      <c r="E95" s="26"/>
+      <c r="F95" s="26"/>
+      <c r="G95" s="26"/>
+      <c r="H95" s="25"/>
+      <c r="I95" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="J95" s="1" t="n">
+        <f aca="false">J94+D94</f>
+        <v>192</v>
+      </c>
+      <c r="K95" s="1" t="n">
+        <f aca="false">J95/8</f>
+        <v>24</v>
+      </c>
+      <c r="L95" s="1" t="n">
+        <f aca="false">J95/16</f>
+        <v>12</v>
+      </c>
+      <c r="M95" s="1" t="n">
+        <f aca="false">J95/32</f>
+        <v>6</v>
+      </c>
+      <c r="O95" s="17"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1" t="s">
+      <c r="B96" s="20"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B96" s="23"/>
-      <c r="C96" s="23"/>
-      <c r="D96" s="23"/>
-      <c r="E96" s="19"/>
-      <c r="F96" s="19"/>
-      <c r="G96" s="19"/>
-      <c r="H96" s="19"/>
-      <c r="I96" s="19"/>
-      <c r="J96" s="22"/>
-      <c r="K96" s="22"/>
-      <c r="L96" s="22"/>
-      <c r="M96" s="22"/>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B97" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="C97" s="23" t="s">
+      <c r="B98" s="23"/>
+      <c r="C98" s="23"/>
+      <c r="D98" s="23"/>
+      <c r="E98" s="19"/>
+      <c r="F98" s="19"/>
+      <c r="G98" s="19"/>
+      <c r="H98" s="19"/>
+      <c r="I98" s="19"/>
+      <c r="J98" s="22"/>
+      <c r="K98" s="22"/>
+      <c r="L98" s="22"/>
+      <c r="M98" s="22"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B99" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="C99" s="23" t="s">
         <v>221</v>
       </c>
-      <c r="D97" s="23" t="n">
+      <c r="D99" s="23" t="n">
         <v>32</v>
       </c>
-      <c r="E97" s="19" t="s">
+      <c r="E99" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="F97" s="19"/>
-      <c r="G97" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="18" t="s">
+      <c r="F99" s="19"/>
+      <c r="G99" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="I97" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="J97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" s="22" t="n">
-        <f aca="false">J97/8</f>
-        <v>0</v>
-      </c>
-      <c r="L97" s="22" t="n">
-        <f aca="false">J97/16</f>
-        <v>0</v>
-      </c>
-      <c r="M97" s="22" t="n">
-        <f aca="false">J97/32</f>
-        <v>0</v>
-      </c>
-      <c r="N97" s="1" t="s">
+      <c r="I99" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="J99" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="22" t="n">
+        <f aca="false">J99/8</f>
+        <v>0</v>
+      </c>
+      <c r="L99" s="22" t="n">
+        <f aca="false">J99/16</f>
+        <v>0</v>
+      </c>
+      <c r="M99" s="22" t="n">
+        <f aca="false">J99/32</f>
+        <v>0</v>
+      </c>
+      <c r="N99" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="O97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q97" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" s="13" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="13" t="s">
+      <c r="O99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" s="13" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B98" s="24"/>
-      <c r="C98" s="25"/>
-      <c r="D98" s="26"/>
-      <c r="E98" s="26"/>
-      <c r="F98" s="26"/>
-      <c r="G98" s="26"/>
-      <c r="H98" s="25"/>
-      <c r="I98" s="26" t="s">
+      <c r="B100" s="24"/>
+      <c r="C100" s="25"/>
+      <c r="D100" s="26"/>
+      <c r="E100" s="26"/>
+      <c r="F100" s="26"/>
+      <c r="G100" s="26"/>
+      <c r="H100" s="25"/>
+      <c r="I100" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="J98" s="1" t="n">
-        <f aca="false">J97+D97</f>
+      <c r="J100" s="1" t="n">
+        <f aca="false">J99+D99</f>
         <v>32</v>
       </c>
-      <c r="K98" s="1" t="n">
-        <f aca="false">J98/8</f>
+      <c r="K100" s="1" t="n">
+        <f aca="false">J100/8</f>
         <v>4</v>
       </c>
-      <c r="L98" s="1" t="n">
-        <f aca="false">J98/16</f>
+      <c r="L100" s="1" t="n">
+        <f aca="false">J100/16</f>
         <v>2</v>
       </c>
-      <c r="M98" s="1" t="n">
-        <f aca="false">J98/32</f>
+      <c r="M100" s="1" t="n">
+        <f aca="false">J100/32</f>
         <v>1</v>
       </c>
-      <c r="O98" s="17"/>
-    </row>
-    <row r="99" s="13" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B99" s="24"/>
-      <c r="C99" s="25"/>
-      <c r="D99" s="26"/>
-      <c r="E99" s="26"/>
-      <c r="F99" s="26"/>
-      <c r="G99" s="26"/>
-      <c r="H99" s="25"/>
-      <c r="I99" s="26"/>
-      <c r="J99" s="22"/>
-      <c r="K99" s="22"/>
-      <c r="L99" s="22"/>
-      <c r="M99" s="22"/>
-      <c r="O99" s="17"/>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1" t="s">
+      <c r="O100" s="17"/>
+    </row>
+    <row r="101" s="13" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B101" s="24"/>
+      <c r="C101" s="25"/>
+      <c r="D101" s="26"/>
+      <c r="E101" s="26"/>
+      <c r="F101" s="26"/>
+      <c r="G101" s="26"/>
+      <c r="H101" s="25"/>
+      <c r="I101" s="26"/>
+      <c r="J101" s="22"/>
+      <c r="K101" s="22"/>
+      <c r="L101" s="22"/>
+      <c r="M101" s="22"/>
+      <c r="O101" s="17"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B100" s="20"/>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B101" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="C101" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="D101" s="21" t="n">
-        <v>32</v>
-      </c>
-      <c r="E101" s="27" t="s">
-        <v>225</v>
-      </c>
-      <c r="F101" s="19"/>
-      <c r="G101" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="I101" s="22" t="s">
-        <v>227</v>
-      </c>
-      <c r="J101" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" s="22" t="n">
-        <f aca="false">J101/8</f>
-        <v>0</v>
-      </c>
-      <c r="L101" s="22" t="n">
-        <f aca="false">J101/16</f>
-        <v>0</v>
-      </c>
-      <c r="M101" s="22" t="n">
-        <f aca="false">J101/32</f>
-        <v>0</v>
-      </c>
-      <c r="N101" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B102" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="C102" s="23" t="s">
-        <v>229</v>
-      </c>
-      <c r="D102" s="21" t="n">
-        <v>16</v>
-      </c>
-      <c r="E102" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="F102" s="19"/>
-      <c r="G102" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="J102" s="1" t="n">
-        <f aca="false">J101+D101</f>
-        <v>32</v>
-      </c>
-      <c r="K102" s="1" t="n">
-        <f aca="false">J102/8</f>
-        <v>4</v>
-      </c>
-      <c r="L102" s="1" t="n">
-        <f aca="false">J102/16</f>
-        <v>2</v>
-      </c>
-      <c r="M102" s="1" t="n">
-        <f aca="false">J102/32</f>
-        <v>1</v>
-      </c>
-      <c r="N102" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O102" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="B102" s="20"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="23" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="C103" s="23" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D103" s="21" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E103" s="27" t="s">
         <v>225</v>
@@ -5787,27 +6714,26 @@
       <c r="G103" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H103" s="18" t="s">
-        <v>34</v>
+      <c r="H103" s="3" t="s">
+        <v>226</v>
       </c>
       <c r="I103" s="22" t="s">
-        <v>233</v>
-      </c>
-      <c r="J103" s="1" t="n">
-        <f aca="false">J102+D102</f>
-        <v>48</v>
-      </c>
-      <c r="K103" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="J103" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="22" t="n">
         <f aca="false">J103/8</f>
-        <v>6</v>
-      </c>
-      <c r="L103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="22" t="n">
         <f aca="false">J103/16</f>
-        <v>3</v>
-      </c>
-      <c r="M103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="22" t="n">
         <f aca="false">J103/32</f>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N103" s="1" t="s">
         <v>28</v>
@@ -5824,40 +6750,39 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B104" s="23" t="s">
-        <v>129</v>
+        <v>228</v>
       </c>
       <c r="C104" s="23" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D104" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="E104" s="27"/>
+        <v>16</v>
+      </c>
+      <c r="E104" s="27" t="s">
+        <v>25</v>
+      </c>
       <c r="F104" s="19"/>
       <c r="G104" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H104" s="18" t="s">
-        <v>34</v>
-      </c>
       <c r="I104" s="22" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="J104" s="1" t="n">
         <f aca="false">J103+D103</f>
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="K104" s="1" t="n">
         <f aca="false">J104/8</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L104" s="1" t="n">
         <f aca="false">J104/16</f>
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="M104" s="1" t="n">
         <f aca="false">J104/32</f>
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="N104" s="1" t="s">
         <v>28</v>
@@ -5872,180 +6797,186 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B105" s="20"/>
-      <c r="C105" s="25"/>
-      <c r="D105" s="26"/>
-      <c r="E105" s="26"/>
-      <c r="F105" s="26"/>
-      <c r="G105" s="26"/>
-      <c r="H105" s="25"/>
-      <c r="I105" s="26" t="s">
-        <v>219</v>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B105" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="C105" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="D105" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E105" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="F105" s="19"/>
+      <c r="G105" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I105" s="22" t="s">
+        <v>233</v>
       </c>
       <c r="J105" s="1" t="n">
         <f aca="false">J104+D104</f>
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="K105" s="1" t="n">
         <f aca="false">J105/8</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L105" s="1" t="n">
         <f aca="false">J105/16</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M105" s="1" t="n">
         <f aca="false">J105/32</f>
+        <v>1.5</v>
+      </c>
+      <c r="N105" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B106" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C106" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="D106" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E106" s="27"/>
+      <c r="F106" s="19"/>
+      <c r="G106" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I106" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="J106" s="1" t="n">
+        <f aca="false">J105+D105</f>
+        <v>56</v>
+      </c>
+      <c r="K106" s="1" t="n">
+        <f aca="false">J106/8</f>
+        <v>7</v>
+      </c>
+      <c r="L106" s="1" t="n">
+        <f aca="false">J106/16</f>
+        <v>3.5</v>
+      </c>
+      <c r="M106" s="1" t="n">
+        <f aca="false">J106/32</f>
+        <v>1.75</v>
+      </c>
+      <c r="N106" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B107" s="20"/>
+      <c r="C107" s="25"/>
+      <c r="D107" s="26"/>
+      <c r="E107" s="26"/>
+      <c r="F107" s="26"/>
+      <c r="G107" s="26"/>
+      <c r="H107" s="25"/>
+      <c r="I107" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="J107" s="1" t="n">
+        <f aca="false">J106+D106</f>
+        <v>64</v>
+      </c>
+      <c r="K107" s="1" t="n">
+        <f aca="false">J107/8</f>
+        <v>8</v>
+      </c>
+      <c r="L107" s="1" t="n">
+        <f aca="false">J107/16</f>
+        <v>4</v>
+      </c>
+      <c r="M107" s="1" t="n">
+        <f aca="false">J107/32</f>
         <v>2</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B106" s="20"/>
-    </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B107" s="20"/>
-    </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="1" t="s">
+      <c r="B108" s="20"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B109" s="20"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B108" s="20"/>
-    </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B109" s="23" t="s">
-        <v>237</v>
-      </c>
-      <c r="C109" s="23" t="s">
-        <v>238</v>
-      </c>
-      <c r="D109" s="21" t="n">
-        <v>32</v>
-      </c>
-      <c r="E109" s="27"/>
-      <c r="F109" s="19"/>
-      <c r="G109" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="I109" s="22" t="s">
-        <v>227</v>
-      </c>
-      <c r="J109" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" s="22" t="n">
-        <f aca="false">J109/8</f>
-        <v>0</v>
-      </c>
-      <c r="L109" s="22" t="n">
-        <f aca="false">J109/16</f>
-        <v>0</v>
-      </c>
-      <c r="M109" s="22" t="n">
-        <f aca="false">J109/32</f>
-        <v>0</v>
-      </c>
-      <c r="N109" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O109" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P109" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q109" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B110" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="C110" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="D110" s="21" t="n">
-        <v>16</v>
-      </c>
-      <c r="E110" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="F110" s="19"/>
-      <c r="G110" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="J110" s="1" t="n">
-        <f aca="false">J109+D109</f>
-        <v>32</v>
-      </c>
-      <c r="K110" s="1" t="n">
-        <f aca="false">J110/8</f>
-        <v>4</v>
-      </c>
-      <c r="L110" s="1" t="n">
-        <f aca="false">J110/16</f>
-        <v>2</v>
-      </c>
-      <c r="M110" s="1" t="n">
-        <f aca="false">J110/32</f>
-        <v>1</v>
-      </c>
-      <c r="N110" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P110" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q110" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="B110" s="20"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B111" s="23" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C111" s="23" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D111" s="21" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E111" s="27"/>
       <c r="F111" s="19"/>
       <c r="G111" s="18" t="n">
         <v>0</v>
       </c>
+      <c r="H111" s="3" t="s">
+        <v>226</v>
+      </c>
       <c r="I111" s="22" t="s">
-        <v>243</v>
-      </c>
-      <c r="J111" s="1" t="n">
-        <f aca="false">J110+D110</f>
-        <v>48</v>
-      </c>
-      <c r="K111" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="J111" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" s="22" t="n">
         <f aca="false">J111/8</f>
-        <v>6</v>
-      </c>
-      <c r="L111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="22" t="n">
         <f aca="false">J111/16</f>
-        <v>3</v>
-      </c>
-      <c r="M111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="22" t="n">
         <f aca="false">J111/32</f>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N111" s="1" t="s">
         <v>28</v>
@@ -6062,37 +6993,39 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B112" s="23" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C112" s="23" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D112" s="21" t="n">
-        <v>32</v>
-      </c>
-      <c r="E112" s="27"/>
+        <v>16</v>
+      </c>
+      <c r="E112" s="27" t="s">
+        <v>25</v>
+      </c>
       <c r="F112" s="19"/>
       <c r="G112" s="18" t="n">
         <v>0</v>
       </c>
       <c r="I112" s="22" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="J112" s="1" t="n">
         <f aca="false">J111+D111</f>
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="K112" s="1" t="n">
         <f aca="false">J112/8</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L112" s="1" t="n">
         <f aca="false">J112/16</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M112" s="1" t="n">
         <f aca="false">J112/32</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N112" s="1" t="s">
         <v>28</v>
@@ -6109,42 +7042,37 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B113" s="23" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C113" s="23" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D113" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="E113" s="27" t="s">
-        <v>225</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="E113" s="27"/>
       <c r="F113" s="19"/>
       <c r="G113" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H113" s="18" t="s">
-        <v>34</v>
-      </c>
       <c r="I113" s="22" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="J113" s="1" t="n">
         <f aca="false">J112+D112</f>
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="K113" s="1" t="n">
         <f aca="false">J113/8</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L113" s="1" t="n">
         <f aca="false">J113/16</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M113" s="1" t="n">
         <f aca="false">J113/32</f>
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="N113" s="1" t="s">
         <v>28</v>
@@ -6161,40 +7089,37 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B114" s="23" t="s">
-        <v>129</v>
+        <v>244</v>
       </c>
       <c r="C114" s="23" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D114" s="21" t="n">
-        <v>24</v>
-      </c>
-      <c r="E114" s="27" t="s">
-        <v>65</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="E114" s="27"/>
       <c r="F114" s="19"/>
       <c r="G114" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H114" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I114" s="22"/>
+      <c r="I114" s="22" t="s">
+        <v>246</v>
+      </c>
       <c r="J114" s="1" t="n">
         <f aca="false">J113+D113</f>
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="K114" s="1" t="n">
         <f aca="false">J114/8</f>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L114" s="1" t="n">
         <f aca="false">J114/16</f>
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="M114" s="1" t="n">
         <f aca="false">J114/32</f>
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="N114" s="1" t="s">
         <v>28</v>
@@ -6209,167 +7134,166 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B115" s="24"/>
-      <c r="C115" s="25"/>
-      <c r="D115" s="26"/>
-      <c r="E115" s="26"/>
-      <c r="F115" s="26"/>
-      <c r="G115" s="26"/>
-      <c r="H115" s="25"/>
-      <c r="I115" s="26" t="s">
-        <v>219</v>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B115" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="C115" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="D115" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E115" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="F115" s="19"/>
+      <c r="G115" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I115" s="22" t="s">
+        <v>249</v>
       </c>
       <c r="J115" s="1" t="n">
         <f aca="false">J114+D114</f>
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="K115" s="1" t="n">
         <f aca="false">J115/8</f>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L115" s="1" t="n">
         <f aca="false">J115/16</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M115" s="1" t="n">
         <f aca="false">J115/32</f>
+        <v>3</v>
+      </c>
+      <c r="N115" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B116" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C116" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="D116" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="E116" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F116" s="19"/>
+      <c r="G116" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I116" s="22"/>
+      <c r="J116" s="1" t="n">
+        <f aca="false">J115+D115</f>
+        <v>104</v>
+      </c>
+      <c r="K116" s="1" t="n">
+        <f aca="false">J116/8</f>
+        <v>13</v>
+      </c>
+      <c r="L116" s="1" t="n">
+        <f aca="false">J116/16</f>
+        <v>6.5</v>
+      </c>
+      <c r="M116" s="1" t="n">
+        <f aca="false">J116/32</f>
+        <v>3.25</v>
+      </c>
+      <c r="N116" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B117" s="24"/>
+      <c r="C117" s="25"/>
+      <c r="D117" s="26"/>
+      <c r="E117" s="26"/>
+      <c r="F117" s="26"/>
+      <c r="G117" s="26"/>
+      <c r="H117" s="25"/>
+      <c r="I117" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="J117" s="1" t="n">
+        <f aca="false">J116+D116</f>
+        <v>128</v>
+      </c>
+      <c r="K117" s="1" t="n">
+        <f aca="false">J117/8</f>
+        <v>16</v>
+      </c>
+      <c r="L117" s="1" t="n">
+        <f aca="false">J117/16</f>
+        <v>8</v>
+      </c>
+      <c r="M117" s="1" t="n">
+        <f aca="false">J117/32</f>
         <v>4</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B116" s="20"/>
-    </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B117" s="20"/>
-    </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="B118" s="20"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="1" t="s">
+      <c r="B119" s="20"/>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B120" s="20"/>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B119" s="20"/>
-    </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B120" s="23" t="s">
-        <v>252</v>
-      </c>
-      <c r="C120" s="23" t="s">
-        <v>253</v>
-      </c>
-      <c r="D120" s="21" t="n">
-        <v>32</v>
-      </c>
-      <c r="E120" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="F120" s="19"/>
-      <c r="G120" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" s="28" t="s">
-        <v>226</v>
-      </c>
-      <c r="I120" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="J120" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" s="22" t="n">
-        <f aca="false">J120/8</f>
-        <v>0</v>
-      </c>
-      <c r="L120" s="22" t="n">
-        <f aca="false">J120/16</f>
-        <v>0</v>
-      </c>
-      <c r="M120" s="22" t="n">
-        <f aca="false">J120/32</f>
-        <v>0</v>
-      </c>
-      <c r="N120" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="O120" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P120" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q120" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B121" s="23" t="s">
-        <v>255</v>
-      </c>
-      <c r="C121" s="23" t="s">
-        <v>256</v>
-      </c>
-      <c r="D121" s="21" t="n">
-        <v>16</v>
-      </c>
-      <c r="E121" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="F121" s="19"/>
-      <c r="G121" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H121" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="I121" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="J121" s="1" t="n">
-        <f aca="false">J120+D120</f>
-        <v>32</v>
-      </c>
-      <c r="K121" s="1" t="n">
-        <f aca="false">J121/8</f>
-        <v>4</v>
-      </c>
-      <c r="L121" s="1" t="n">
-        <f aca="false">J121/16</f>
-        <v>2</v>
-      </c>
-      <c r="M121" s="1" t="n">
-        <f aca="false">J121/32</f>
-        <v>1</v>
-      </c>
-      <c r="N121" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="O121" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P121" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q121" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="B121" s="20"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B122" s="23" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C122" s="23" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D122" s="21" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E122" s="27" t="s">
         <v>25</v>
@@ -6378,27 +7302,26 @@
       <c r="G122" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H122" s="18" t="s">
-        <v>34</v>
+      <c r="H122" s="28" t="s">
+        <v>226</v>
       </c>
       <c r="I122" s="22" t="s">
-        <v>259</v>
-      </c>
-      <c r="J122" s="1" t="n">
-        <f aca="false">J121+D121</f>
-        <v>48</v>
-      </c>
-      <c r="K122" s="1" t="n">
+        <v>254</v>
+      </c>
+      <c r="J122" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="22" t="n">
         <f aca="false">J122/8</f>
-        <v>6</v>
-      </c>
-      <c r="L122" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="22" t="n">
         <f aca="false">J122/16</f>
-        <v>3</v>
-      </c>
-      <c r="M122" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="22" t="n">
         <f aca="false">J122/32</f>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N122" s="1" t="s">
         <v>44</v>
@@ -6407,7 +7330,7 @@
         <v>1</v>
       </c>
       <c r="P122" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q122" s="1" t="n">
         <v>0</v>
@@ -6415,256 +7338,257 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B123" s="23" t="s">
-        <v>129</v>
+        <v>255</v>
       </c>
       <c r="C123" s="23" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D123" s="21" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E123" s="27" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="F123" s="19"/>
       <c r="G123" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H123" s="18" t="s">
+      <c r="H123" s="28" t="s">
         <v>34</v>
       </c>
       <c r="I123" s="22" t="s">
-        <v>165</v>
+        <v>254</v>
       </c>
       <c r="J123" s="1" t="n">
         <f aca="false">J122+D122</f>
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="K123" s="1" t="n">
         <f aca="false">J123/8</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L123" s="1" t="n">
         <f aca="false">J123/16</f>
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="M123" s="1" t="n">
         <f aca="false">J123/32</f>
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="N123" s="1" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="O123" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P123" s="1" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q123" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B124" s="23"/>
-      <c r="I124" s="1" t="s">
-        <v>132</v>
+      <c r="B124" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="C124" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="D124" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E124" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F124" s="19"/>
+      <c r="G124" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I124" s="22" t="s">
+        <v>259</v>
       </c>
       <c r="J124" s="1" t="n">
         <f aca="false">J123+D123</f>
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="K124" s="1" t="n">
         <f aca="false">J124/8</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L124" s="1" t="n">
         <f aca="false">J124/16</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M124" s="1" t="n">
         <f aca="false">J124/32</f>
+        <v>1.5</v>
+      </c>
+      <c r="N124" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O124" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P124" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q124" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B125" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C125" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="D125" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E125" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F125" s="19"/>
+      <c r="G125" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I125" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="J125" s="1" t="n">
+        <f aca="false">J124+D124</f>
+        <v>56</v>
+      </c>
+      <c r="K125" s="1" t="n">
+        <f aca="false">J125/8</f>
+        <v>7</v>
+      </c>
+      <c r="L125" s="1" t="n">
+        <f aca="false">J125/16</f>
+        <v>3.5</v>
+      </c>
+      <c r="M125" s="1" t="n">
+        <f aca="false">J125/32</f>
+        <v>1.75</v>
+      </c>
+      <c r="N125" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B126" s="23"/>
+      <c r="I126" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J126" s="1" t="n">
+        <f aca="false">J125+D125</f>
+        <v>64</v>
+      </c>
+      <c r="K126" s="1" t="n">
+        <f aca="false">J126/8</f>
+        <v>8</v>
+      </c>
+      <c r="L126" s="1" t="n">
+        <f aca="false">J126/16</f>
+        <v>4</v>
+      </c>
+      <c r="M126" s="1" t="n">
+        <f aca="false">J126/32</f>
         <v>2</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="29" t="s">
+    <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="29" t="s">
         <v>261</v>
       </c>
-      <c r="J126" s="30"/>
-      <c r="K126" s="22"/>
-      <c r="L126" s="22"/>
-      <c r="M126" s="22"/>
-      <c r="N126" s="13" t="s">
+      <c r="J128" s="30"/>
+      <c r="K128" s="22"/>
+      <c r="L128" s="22"/>
+      <c r="M128" s="22"/>
+      <c r="N128" s="13" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="127" s="13" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B127" s="14" t="s">
+    <row r="129" s="13" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B129" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C127" s="11" t="s">
+      <c r="C129" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D127" s="11" t="s">
+      <c r="D129" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E127" s="11" t="s">
+      <c r="E129" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F127" s="11" t="s">
+      <c r="F129" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G127" s="11" t="s">
+      <c r="G129" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H127" s="11" t="s">
+      <c r="H129" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="I127" s="12" t="s">
+      <c r="I129" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="J127" s="13" t="s">
+      <c r="J129" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K127" s="13" t="s">
+      <c r="K129" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="L127" s="13" t="s">
+      <c r="L129" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="M127" s="13" t="s">
+      <c r="M129" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="N127" s="1"/>
-      <c r="O127" s="17" t="s">
+      <c r="N129" s="1"/>
+      <c r="O129" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="P127" s="13" t="s">
+      <c r="P129" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="Q127" s="13" t="s">
+      <c r="Q129" s="13" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="128" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B128" s="18" t="s">
-        <v>262</v>
-      </c>
-      <c r="C128" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D128" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="E128" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="F128" s="33"/>
-      <c r="G128" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="H128" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="I128" s="27" t="s">
-        <v>264</v>
-      </c>
-      <c r="J128" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" s="22" t="n">
-        <f aca="false">J128/8</f>
-        <v>0</v>
-      </c>
-      <c r="L128" s="22" t="n">
-        <f aca="false">J128/16</f>
-        <v>0</v>
-      </c>
-      <c r="M128" s="22" t="n">
-        <f aca="false">J128/32</f>
-        <v>0</v>
-      </c>
-      <c r="N128" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="O128" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P128" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q128" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B129" s="18" t="s">
-        <v>265</v>
-      </c>
-      <c r="C129" s="32" t="s">
-        <v>266</v>
-      </c>
-      <c r="D129" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E129" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="F129" s="33"/>
-      <c r="G129" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="H129" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="I129" s="27" t="s">
-        <v>264</v>
-      </c>
-      <c r="J129" s="1" t="n">
-        <f aca="false">J128+D128</f>
-        <v>9</v>
-      </c>
-      <c r="K129" s="1" t="n">
-        <f aca="false">J129/8</f>
-        <v>1.125</v>
-      </c>
-      <c r="L129" s="1" t="n">
-        <f aca="false">J129/16</f>
-        <v>0.5625</v>
-      </c>
-      <c r="M129" s="1" t="n">
-        <f aca="false">J129/32</f>
-        <v>0.28125</v>
-      </c>
-      <c r="N129" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="O129" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P129" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q129" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="130" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B130" s="18" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C130" s="32" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="D130" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E130" s="27" t="s">
         <v>25</v>
@@ -6677,23 +7601,22 @@
         <v>34</v>
       </c>
       <c r="I130" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="J130" s="1" t="n">
-        <f aca="false">J129+D129</f>
-        <v>14</v>
-      </c>
-      <c r="K130" s="1" t="n">
+        <v>264</v>
+      </c>
+      <c r="J130" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" s="22" t="n">
         <f aca="false">J130/8</f>
-        <v>1.75</v>
-      </c>
-      <c r="L130" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" s="22" t="n">
         <f aca="false">J130/16</f>
-        <v>0.875</v>
-      </c>
-      <c r="M130" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="22" t="n">
         <f aca="false">J130/32</f>
-        <v>0.4375</v>
+        <v>0</v>
       </c>
       <c r="N130" s="1" t="s">
         <v>109</v>
@@ -6702,7 +7625,7 @@
         <v>2</v>
       </c>
       <c r="P130" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q130" s="1" t="n">
         <v>0</v>
@@ -6710,13 +7633,13 @@
     </row>
     <row r="131" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B131" s="18" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C131" s="32" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D131" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E131" s="27" t="s">
         <v>25</v>
@@ -6729,23 +7652,23 @@
         <v>34</v>
       </c>
       <c r="I131" s="27" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="J131" s="1" t="n">
         <f aca="false">J130+D130</f>
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K131" s="1" t="n">
         <f aca="false">J131/8</f>
-        <v>2.25</v>
+        <v>1.125</v>
       </c>
       <c r="L131" s="1" t="n">
         <f aca="false">J131/16</f>
-        <v>1.125</v>
+        <v>0.5625</v>
       </c>
       <c r="M131" s="1" t="n">
         <f aca="false">J131/32</f>
-        <v>0.5625</v>
+        <v>0.28125</v>
       </c>
       <c r="N131" s="1" t="s">
         <v>109</v>
@@ -6754,7 +7677,7 @@
         <v>2</v>
       </c>
       <c r="P131" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q131" s="1" t="n">
         <v>0</v>
@@ -6762,42 +7685,42 @@
     </row>
     <row r="132" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B132" s="18" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="C132" s="32" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="D132" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E132" s="27" t="s">
         <v>25</v>
       </c>
       <c r="F132" s="33"/>
-      <c r="G132" s="18" t="n">
+      <c r="G132" s="27" t="n">
         <v>2</v>
       </c>
       <c r="H132" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I132" s="18" t="s">
-        <v>275</v>
+      <c r="I132" s="27" t="s">
+        <v>269</v>
       </c>
       <c r="J132" s="1" t="n">
         <f aca="false">J131+D131</f>
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K132" s="1" t="n">
         <f aca="false">J132/8</f>
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="L132" s="1" t="n">
         <f aca="false">J132/16</f>
-        <v>1.375</v>
+        <v>0.875</v>
       </c>
       <c r="M132" s="1" t="n">
         <f aca="false">J132/32</f>
-        <v>0.6875</v>
+        <v>0.4375</v>
       </c>
       <c r="N132" s="1" t="s">
         <v>109</v>
@@ -6806,7 +7729,7 @@
         <v>2</v>
       </c>
       <c r="P132" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q132" s="1" t="n">
         <v>0</v>
@@ -6814,42 +7737,42 @@
     </row>
     <row r="133" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B133" s="18" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C133" s="32" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="D133" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E133" s="27" t="s">
         <v>25</v>
       </c>
       <c r="F133" s="33"/>
-      <c r="G133" s="18" t="n">
+      <c r="G133" s="27" t="n">
         <v>2</v>
       </c>
       <c r="H133" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I133" s="18" t="s">
-        <v>278</v>
+      <c r="I133" s="27" t="s">
+        <v>272</v>
       </c>
       <c r="J133" s="1" t="n">
         <f aca="false">J132+D132</f>
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K133" s="1" t="n">
         <f aca="false">J133/8</f>
-        <v>3.125</v>
+        <v>2.25</v>
       </c>
       <c r="L133" s="1" t="n">
         <f aca="false">J133/16</f>
-        <v>1.5625</v>
+        <v>1.125</v>
       </c>
       <c r="M133" s="1" t="n">
         <f aca="false">J133/32</f>
-        <v>0.78125</v>
+        <v>0.5625</v>
       </c>
       <c r="N133" s="1" t="s">
         <v>109</v>
@@ -6858,7 +7781,7 @@
         <v>2</v>
       </c>
       <c r="P133" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q133" s="1" t="n">
         <v>0</v>
@@ -6866,42 +7789,42 @@
     </row>
     <row r="134" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B134" s="18" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C134" s="32" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="D134" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E134" s="27" t="s">
         <v>25</v>
       </c>
       <c r="F134" s="33"/>
       <c r="G134" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H134" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I134" s="27" t="s">
-        <v>264</v>
+      <c r="I134" s="18" t="s">
+        <v>275</v>
       </c>
       <c r="J134" s="1" t="n">
         <f aca="false">J133+D133</f>
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K134" s="1" t="n">
         <f aca="false">J134/8</f>
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="L134" s="1" t="n">
         <f aca="false">J134/16</f>
-        <v>1.625</v>
+        <v>1.375</v>
       </c>
       <c r="M134" s="1" t="n">
         <f aca="false">J134/32</f>
-        <v>0.8125</v>
+        <v>0.6875</v>
       </c>
       <c r="N134" s="1" t="s">
         <v>109</v>
@@ -6910,7 +7833,7 @@
         <v>2</v>
       </c>
       <c r="P134" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q134" s="1" t="n">
         <v>0</v>
@@ -6918,51 +7841,51 @@
     </row>
     <row r="135" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B135" s="18" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C135" s="32" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="D135" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E135" s="27" t="s">
         <v>25</v>
       </c>
       <c r="F135" s="33"/>
       <c r="G135" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H135" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I135" s="27" t="s">
-        <v>264</v>
+      <c r="I135" s="18" t="s">
+        <v>278</v>
       </c>
       <c r="J135" s="1" t="n">
         <f aca="false">J134+D134</f>
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K135" s="1" t="n">
         <f aca="false">J135/8</f>
-        <v>3.375</v>
+        <v>3.125</v>
       </c>
       <c r="L135" s="1" t="n">
         <f aca="false">J135/16</f>
-        <v>1.6875</v>
+        <v>1.5625</v>
       </c>
       <c r="M135" s="1" t="n">
         <f aca="false">J135/32</f>
-        <v>0.84375</v>
+        <v>0.78125</v>
       </c>
       <c r="N135" s="1" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P135" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q135" s="1" t="n">
         <v>0</v>
@@ -6970,20 +7893,20 @@
     </row>
     <row r="136" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B136" s="18" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C136" s="32" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D136" s="1" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="E136" s="27" t="s">
         <v>25</v>
       </c>
       <c r="F136" s="33"/>
       <c r="G136" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H136" s="27" t="s">
         <v>34</v>
@@ -6993,19 +7916,19 @@
       </c>
       <c r="J136" s="1" t="n">
         <f aca="false">J135+D135</f>
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="K136" s="1" t="n">
         <f aca="false">J136/8</f>
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="L136" s="1" t="n">
         <f aca="false">J136/16</f>
-        <v>2</v>
+        <v>1.625</v>
       </c>
       <c r="M136" s="1" t="n">
         <f aca="false">J136/32</f>
-        <v>1</v>
+        <v>0.8125</v>
       </c>
       <c r="N136" s="1" t="s">
         <v>109</v>
@@ -7014,26 +7937,26 @@
         <v>2</v>
       </c>
       <c r="P136" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q136" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B137" s="18" t="s">
-        <v>285</v>
-      </c>
-      <c r="C137" s="18" t="s">
-        <v>286</v>
+        <v>281</v>
+      </c>
+      <c r="C137" s="32" t="s">
+        <v>282</v>
       </c>
       <c r="D137" s="1" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="E137" s="27" t="s">
-        <v>225</v>
-      </c>
-      <c r="F137" s="27"/>
+        <v>25</v>
+      </c>
+      <c r="F137" s="33"/>
       <c r="G137" s="18" t="n">
         <v>0</v>
       </c>
@@ -7045,39 +7968,39 @@
       </c>
       <c r="J137" s="1" t="n">
         <f aca="false">J136+D136</f>
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="K137" s="1" t="n">
         <f aca="false">J137/8</f>
-        <v>8</v>
+        <v>3.375</v>
       </c>
       <c r="L137" s="1" t="n">
         <f aca="false">J137/16</f>
-        <v>4</v>
+        <v>1.6875</v>
       </c>
       <c r="M137" s="1" t="n">
         <f aca="false">J137/32</f>
-        <v>2</v>
+        <v>0.84375</v>
       </c>
       <c r="N137" s="1" t="s">
-        <v>287</v>
+        <v>28</v>
       </c>
       <c r="O137" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P137" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q137" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B138" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="C138" s="18" t="s">
-        <v>289</v>
+        <v>283</v>
+      </c>
+      <c r="C138" s="32" t="s">
+        <v>284</v>
       </c>
       <c r="D138" s="1" t="n">
         <v>32</v>
@@ -7085,9 +8008,9 @@
       <c r="E138" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="F138" s="27"/>
+      <c r="F138" s="33"/>
       <c r="G138" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H138" s="27" t="s">
         <v>34</v>
@@ -7097,28 +8020,28 @@
       </c>
       <c r="J138" s="1" t="n">
         <f aca="false">J137+D137</f>
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="K138" s="1" t="n">
         <f aca="false">J138/8</f>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L138" s="1" t="n">
         <f aca="false">J138/16</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M138" s="1" t="n">
         <f aca="false">J138/32</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N138" s="1" t="s">
-        <v>287</v>
+        <v>109</v>
       </c>
       <c r="O138" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P138" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q138" s="1" t="n">
         <v>0</v>
@@ -7126,10 +8049,10 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B139" s="18" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C139" s="18" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D139" s="1" t="n">
         <v>32</v>
@@ -7149,19 +8072,19 @@
       </c>
       <c r="J139" s="1" t="n">
         <f aca="false">J138+D138</f>
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="K139" s="1" t="n">
         <f aca="false">J139/8</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L139" s="1" t="n">
         <f aca="false">J139/16</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M139" s="1" t="n">
         <f aca="false">J139/32</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N139" s="1" t="s">
         <v>287</v>
@@ -7170,7 +8093,7 @@
         <v>3</v>
       </c>
       <c r="P139" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q139" s="1" t="n">
         <v>0</v>
@@ -7178,10 +8101,10 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B140" s="18" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C140" s="18" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D140" s="1" t="n">
         <v>32</v>
@@ -7201,19 +8124,19 @@
       </c>
       <c r="J140" s="1" t="n">
         <f aca="false">J139+D139</f>
-        <v>160</v>
+        <v>96</v>
       </c>
       <c r="K140" s="1" t="n">
         <f aca="false">J140/8</f>
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L140" s="1" t="n">
         <f aca="false">J140/16</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M140" s="1" t="n">
         <f aca="false">J140/32</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N140" s="1" t="s">
         <v>287</v>
@@ -7222,7 +8145,7 @@
         <v>3</v>
       </c>
       <c r="P140" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q140" s="1" t="n">
         <v>0</v>
@@ -7230,16 +8153,16 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B141" s="18" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C141" s="18" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D141" s="1" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E141" s="27" t="s">
-        <v>25</v>
+        <v>225</v>
       </c>
       <c r="F141" s="27"/>
       <c r="G141" s="18" t="n">
@@ -7249,32 +8172,32 @@
         <v>34</v>
       </c>
       <c r="I141" s="27" t="s">
-        <v>296</v>
+        <v>264</v>
       </c>
       <c r="J141" s="1" t="n">
         <f aca="false">J140+D140</f>
-        <v>192</v>
+        <v>128</v>
       </c>
       <c r="K141" s="1" t="n">
         <f aca="false">J141/8</f>
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="L141" s="1" t="n">
         <f aca="false">J141/16</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M141" s="1" t="n">
         <f aca="false">J141/32</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N141" s="1" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="O141" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P141" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q141" s="1" t="n">
         <v>0</v>
@@ -7282,13 +8205,13 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B142" s="18" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C142" s="18" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="D142" s="1" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E142" s="27" t="s">
         <v>25</v>
@@ -7301,32 +8224,32 @@
         <v>34</v>
       </c>
       <c r="I142" s="27" t="s">
-        <v>300</v>
+        <v>264</v>
       </c>
       <c r="J142" s="1" t="n">
         <f aca="false">J141+D141</f>
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="K142" s="1" t="n">
         <f aca="false">J142/8</f>
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L142" s="1" t="n">
         <f aca="false">J142/16</f>
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="M142" s="1" t="n">
         <f aca="false">J142/32</f>
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="N142" s="1" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="O142" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P142" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q142" s="1" t="n">
         <v>0</v>
@@ -7334,10 +8257,10 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B143" s="18" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="C143" s="18" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="D143" s="1" t="n">
         <v>8</v>
@@ -7353,23 +8276,23 @@
         <v>34</v>
       </c>
       <c r="I143" s="27" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="J143" s="1" t="n">
         <f aca="false">J142+D142</f>
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="K143" s="1" t="n">
         <f aca="false">J143/8</f>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L143" s="1" t="n">
         <f aca="false">J143/16</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M143" s="1" t="n">
         <f aca="false">J143/32</f>
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="N143" s="1" t="s">
         <v>297</v>
@@ -7378,7 +8301,7 @@
         <v>5</v>
       </c>
       <c r="P143" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q143" s="1" t="n">
         <v>0</v>
@@ -7386,10 +8309,10 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B144" s="18" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C144" s="18" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="D144" s="1" t="n">
         <v>8</v>
@@ -7405,23 +8328,23 @@
         <v>34</v>
       </c>
       <c r="I144" s="27" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="J144" s="1" t="n">
         <f aca="false">J143+D143</f>
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="K144" s="1" t="n">
         <f aca="false">J144/8</f>
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L144" s="1" t="n">
         <f aca="false">J144/16</f>
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="M144" s="1" t="n">
         <f aca="false">J144/32</f>
-        <v>6.75</v>
+        <v>6.25</v>
       </c>
       <c r="N144" s="1" t="s">
         <v>297</v>
@@ -7430,7 +8353,7 @@
         <v>5</v>
       </c>
       <c r="P144" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q144" s="1" t="n">
         <v>0</v>
@@ -7438,10 +8361,10 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B145" s="18" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C145" s="18" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="D145" s="1" t="n">
         <v>8</v>
@@ -7457,23 +8380,23 @@
         <v>34</v>
       </c>
       <c r="I145" s="27" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="J145" s="1" t="n">
         <f aca="false">J144+D144</f>
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="K145" s="1" t="n">
         <f aca="false">J145/8</f>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L145" s="1" t="n">
         <f aca="false">J145/16</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M145" s="1" t="n">
         <f aca="false">J145/32</f>
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="N145" s="1" t="s">
         <v>297</v>
@@ -7482,7 +8405,7 @@
         <v>5</v>
       </c>
       <c r="P145" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q145" s="1" t="n">
         <v>0</v>
@@ -7490,10 +8413,10 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B146" s="18" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C146" s="18" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="D146" s="1" t="n">
         <v>8</v>
@@ -7508,33 +8431,33 @@
       <c r="H146" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I146" s="18" t="s">
-        <v>310</v>
+      <c r="I146" s="27" t="s">
+        <v>306</v>
       </c>
       <c r="J146" s="1" t="n">
         <f aca="false">J145+D145</f>
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="K146" s="1" t="n">
         <f aca="false">J146/8</f>
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L146" s="1" t="n">
         <f aca="false">J146/16</f>
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="M146" s="1" t="n">
         <f aca="false">J146/32</f>
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
       <c r="N146" s="1" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="O146" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P146" s="1" t="n">
         <v>4</v>
-      </c>
-      <c r="P146" s="1" t="n">
-        <v>1</v>
       </c>
       <c r="Q146" s="1" t="n">
         <v>0</v>
@@ -7542,10 +8465,10 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B147" s="18" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C147" s="18" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="D147" s="1" t="n">
         <v>8</v>
@@ -7560,33 +8483,33 @@
       <c r="H147" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I147" s="18" t="s">
-        <v>313</v>
+      <c r="I147" s="27" t="s">
+        <v>309</v>
       </c>
       <c r="J147" s="1" t="n">
         <f aca="false">J146+D146</f>
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="K147" s="1" t="n">
         <f aca="false">J147/8</f>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L147" s="1" t="n">
         <f aca="false">J147/16</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M147" s="1" t="n">
         <f aca="false">J147/32</f>
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="N147" s="1" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="O147" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P147" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q147" s="1" t="n">
         <v>0</v>
@@ -7594,10 +8517,10 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B148" s="18" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C148" s="18" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D148" s="1" t="n">
         <v>8</v>
@@ -7613,23 +8536,23 @@
         <v>34</v>
       </c>
       <c r="I148" s="18" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="J148" s="1" t="n">
         <f aca="false">J147+D147</f>
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="K148" s="1" t="n">
         <f aca="false">J148/8</f>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L148" s="1" t="n">
         <f aca="false">J148/16</f>
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="M148" s="1" t="n">
         <f aca="false">J148/32</f>
-        <v>7.75</v>
+        <v>7.25</v>
       </c>
       <c r="N148" s="1" t="s">
         <v>312</v>
@@ -7638,7 +8561,7 @@
         <v>4</v>
       </c>
       <c r="P148" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q148" s="1" t="n">
         <v>0</v>
@@ -7646,10 +8569,10 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B149" s="18" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C149" s="18" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D149" s="1" t="n">
         <v>8</v>
@@ -7665,23 +8588,23 @@
         <v>34</v>
       </c>
       <c r="I149" s="18" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="J149" s="1" t="n">
         <f aca="false">J148+D148</f>
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="K149" s="1" t="n">
         <f aca="false">J149/8</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L149" s="1" t="n">
         <f aca="false">J149/16</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M149" s="1" t="n">
         <f aca="false">J149/32</f>
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="N149" s="1" t="s">
         <v>312</v>
@@ -7690,7 +8613,7 @@
         <v>4</v>
       </c>
       <c r="P149" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q149" s="1" t="n">
         <v>0</v>
@@ -7698,10 +8621,10 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B150" s="18" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C150" s="18" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D150" s="1" t="n">
         <v>8</v>
@@ -7717,23 +8640,23 @@
         <v>34</v>
       </c>
       <c r="I150" s="18" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="J150" s="1" t="n">
         <f aca="false">J149+D149</f>
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="K150" s="1" t="n">
         <f aca="false">J150/8</f>
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L150" s="1" t="n">
         <f aca="false">J150/16</f>
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="M150" s="1" t="n">
         <f aca="false">J150/32</f>
-        <v>8.25</v>
+        <v>7.75</v>
       </c>
       <c r="N150" s="1" t="s">
         <v>312</v>
@@ -7742,7 +8665,7 @@
         <v>4</v>
       </c>
       <c r="P150" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q150" s="1" t="n">
         <v>0</v>
@@ -7750,10 +8673,10 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B151" s="18" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C151" s="18" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D151" s="1" t="n">
         <v>8</v>
@@ -7769,23 +8692,23 @@
         <v>34</v>
       </c>
       <c r="I151" s="18" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="J151" s="1" t="n">
         <f aca="false">J150+D150</f>
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="K151" s="1" t="n">
         <f aca="false">J151/8</f>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L151" s="1" t="n">
         <f aca="false">J151/16</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M151" s="1" t="n">
         <f aca="false">J151/32</f>
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="N151" s="1" t="s">
         <v>312</v>
@@ -7794,7 +8717,7 @@
         <v>4</v>
       </c>
       <c r="P151" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q151" s="1" t="n">
         <v>0</v>
@@ -7802,10 +8725,10 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B152" s="18" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C152" s="18" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D152" s="1" t="n">
         <v>8</v>
@@ -7821,23 +8744,23 @@
         <v>34</v>
       </c>
       <c r="I152" s="18" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="J152" s="1" t="n">
         <f aca="false">J151+D151</f>
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="K152" s="1" t="n">
         <f aca="false">J152/8</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L152" s="1" t="n">
         <f aca="false">J152/16</f>
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="M152" s="1" t="n">
         <f aca="false">J152/32</f>
-        <v>8.75</v>
+        <v>8.25</v>
       </c>
       <c r="N152" s="1" t="s">
         <v>312</v>
@@ -7846,7 +8769,7 @@
         <v>4</v>
       </c>
       <c r="P152" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q152" s="1" t="n">
         <v>0</v>
@@ -7854,10 +8777,10 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B153" s="18" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C153" s="18" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D153" s="1" t="n">
         <v>8</v>
@@ -7873,32 +8796,32 @@
         <v>34</v>
       </c>
       <c r="I153" s="18" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="J153" s="1" t="n">
         <f aca="false">J152+D152</f>
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="K153" s="1" t="n">
         <f aca="false">J153/8</f>
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L153" s="1" t="n">
         <f aca="false">J153/16</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M153" s="1" t="n">
         <f aca="false">J153/32</f>
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="N153" s="1" t="s">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="O153" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P153" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q153" s="1" t="n">
         <v>0</v>
@@ -7906,10 +8829,10 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B154" s="18" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C154" s="18" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D154" s="1" t="n">
         <v>8</v>
@@ -7925,32 +8848,32 @@
         <v>34</v>
       </c>
       <c r="I154" s="18" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="J154" s="1" t="n">
         <f aca="false">J153+D153</f>
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="K154" s="1" t="n">
         <f aca="false">J154/8</f>
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L154" s="1" t="n">
         <f aca="false">J154/16</f>
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="M154" s="1" t="n">
         <f aca="false">J154/32</f>
-        <v>9.25</v>
+        <v>8.75</v>
       </c>
       <c r="N154" s="1" t="s">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="O154" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P154" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q154" s="1" t="n">
         <v>0</v>
@@ -7958,10 +8881,10 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B155" s="18" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C155" s="18" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D155" s="1" t="n">
         <v>8</v>
@@ -7977,23 +8900,23 @@
         <v>34</v>
       </c>
       <c r="I155" s="18" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J155" s="1" t="n">
         <f aca="false">J154+D154</f>
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="K155" s="1" t="n">
         <f aca="false">J155/8</f>
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L155" s="1" t="n">
         <f aca="false">J155/16</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M155" s="1" t="n">
         <f aca="false">J155/32</f>
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="N155" s="1" t="s">
         <v>287</v>
@@ -8002,7 +8925,7 @@
         <v>3</v>
       </c>
       <c r="P155" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q155" s="1" t="n">
         <v>0</v>
@@ -8010,10 +8933,10 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B156" s="18" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C156" s="18" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D156" s="1" t="n">
         <v>8</v>
@@ -8029,23 +8952,23 @@
         <v>34</v>
       </c>
       <c r="I156" s="18" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="J156" s="1" t="n">
         <f aca="false">J155+D155</f>
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="K156" s="1" t="n">
         <f aca="false">J156/8</f>
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L156" s="1" t="n">
         <f aca="false">J156/16</f>
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="M156" s="1" t="n">
         <f aca="false">J156/32</f>
-        <v>9.75</v>
+        <v>9.25</v>
       </c>
       <c r="N156" s="1" t="s">
         <v>287</v>
@@ -8054,7 +8977,7 @@
         <v>3</v>
       </c>
       <c r="P156" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q156" s="1" t="n">
         <v>0</v>
@@ -8062,10 +8985,10 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B157" s="18" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C157" s="18" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D157" s="1" t="n">
         <v>8</v>
@@ -8081,23 +9004,23 @@
         <v>34</v>
       </c>
       <c r="I157" s="18" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="J157" s="1" t="n">
         <f aca="false">J156+D156</f>
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="K157" s="1" t="n">
         <f aca="false">J157/8</f>
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L157" s="1" t="n">
         <f aca="false">J157/16</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M157" s="1" t="n">
         <f aca="false">J157/32</f>
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="N157" s="1" t="s">
         <v>287</v>
@@ -8106,7 +9029,7 @@
         <v>3</v>
       </c>
       <c r="P157" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q157" s="1" t="n">
         <v>0</v>
@@ -8114,10 +9037,10 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B158" s="18" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C158" s="18" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D158" s="1" t="n">
         <v>8</v>
@@ -8133,23 +9056,23 @@
         <v>34</v>
       </c>
       <c r="I158" s="18" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="J158" s="1" t="n">
         <f aca="false">J157+D157</f>
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="K158" s="1" t="n">
         <f aca="false">J158/8</f>
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L158" s="1" t="n">
         <f aca="false">J158/16</f>
-        <v>20.5</v>
+        <v>19.5</v>
       </c>
       <c r="M158" s="1" t="n">
         <f aca="false">J158/32</f>
-        <v>10.25</v>
+        <v>9.75</v>
       </c>
       <c r="N158" s="1" t="s">
         <v>287</v>
@@ -8158,7 +9081,7 @@
         <v>3</v>
       </c>
       <c r="P158" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q158" s="1" t="n">
         <v>0</v>
@@ -8166,10 +9089,10 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B159" s="18" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C159" s="18" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D159" s="1" t="n">
         <v>8</v>
@@ -8185,29 +9108,29 @@
         <v>34</v>
       </c>
       <c r="I159" s="18" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="J159" s="1" t="n">
         <f aca="false">J158+D158</f>
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="K159" s="1" t="n">
         <f aca="false">J159/8</f>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L159" s="1" t="n">
         <f aca="false">J159/16</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M159" s="1" t="n">
         <f aca="false">J159/32</f>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="N159" s="1" t="s">
-        <v>109</v>
+        <v>287</v>
       </c>
       <c r="O159" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P159" s="1" t="n">
         <v>9</v>
@@ -8218,10 +9141,10 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B160" s="18" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C160" s="18" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D160" s="1" t="n">
         <v>8</v>
@@ -8237,29 +9160,29 @@
         <v>34</v>
       </c>
       <c r="I160" s="18" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="J160" s="1" t="n">
         <f aca="false">J159+D159</f>
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="K160" s="1" t="n">
         <f aca="false">J160/8</f>
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L160" s="1" t="n">
         <f aca="false">J160/16</f>
-        <v>21.5</v>
+        <v>20.5</v>
       </c>
       <c r="M160" s="1" t="n">
         <f aca="false">J160/32</f>
-        <v>10.75</v>
+        <v>10.25</v>
       </c>
       <c r="N160" s="1" t="s">
-        <v>109</v>
+        <v>287</v>
       </c>
       <c r="O160" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P160" s="1" t="n">
         <v>10</v>
@@ -8270,10 +9193,10 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B161" s="18" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C161" s="18" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D161" s="1" t="n">
         <v>8</v>
@@ -8289,32 +9212,32 @@
         <v>34</v>
       </c>
       <c r="I161" s="18" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="J161" s="1" t="n">
         <f aca="false">J160+D160</f>
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K161" s="1" t="n">
         <f aca="false">J161/8</f>
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L161" s="1" t="n">
         <f aca="false">J161/16</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M161" s="1" t="n">
         <f aca="false">J161/32</f>
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="N161" s="1" t="s">
-        <v>287</v>
+        <v>109</v>
       </c>
       <c r="O161" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P161" s="1" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q161" s="1" t="n">
         <v>0</v>
@@ -8322,10 +9245,10 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B162" s="18" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C162" s="18" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D162" s="1" t="n">
         <v>8</v>
@@ -8341,32 +9264,32 @@
         <v>34</v>
       </c>
       <c r="I162" s="18" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="J162" s="1" t="n">
         <f aca="false">J161+D161</f>
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="K162" s="1" t="n">
         <f aca="false">J162/8</f>
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L162" s="1" t="n">
         <f aca="false">J162/16</f>
-        <v>22.5</v>
+        <v>21.5</v>
       </c>
       <c r="M162" s="1" t="n">
         <f aca="false">J162/32</f>
-        <v>11.25</v>
+        <v>10.75</v>
       </c>
       <c r="N162" s="1" t="s">
-        <v>287</v>
+        <v>109</v>
       </c>
       <c r="O162" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P162" s="1" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q162" s="1" t="n">
         <v>0</v>
@@ -8374,10 +9297,10 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B163" s="18" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C163" s="18" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D163" s="1" t="n">
         <v>8</v>
@@ -8393,23 +9316,23 @@
         <v>34</v>
       </c>
       <c r="I163" s="18" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="J163" s="1" t="n">
         <f aca="false">J162+D162</f>
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="K163" s="1" t="n">
         <f aca="false">J163/8</f>
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L163" s="1" t="n">
         <f aca="false">J163/16</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M163" s="1" t="n">
         <f aca="false">J163/32</f>
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="N163" s="1" t="s">
         <v>287</v>
@@ -8418,7 +9341,7 @@
         <v>3</v>
       </c>
       <c r="P163" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q163" s="1" t="n">
         <v>0</v>
@@ -8426,10 +9349,10 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B164" s="18" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C164" s="18" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D164" s="1" t="n">
         <v>8</v>
@@ -8445,23 +9368,23 @@
         <v>34</v>
       </c>
       <c r="I164" s="18" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="J164" s="1" t="n">
         <f aca="false">J163+D163</f>
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="K164" s="1" t="n">
         <f aca="false">J164/8</f>
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L164" s="1" t="n">
         <f aca="false">J164/16</f>
-        <v>23.5</v>
+        <v>22.5</v>
       </c>
       <c r="M164" s="1" t="n">
         <f aca="false">J164/32</f>
-        <v>11.75</v>
+        <v>11.25</v>
       </c>
       <c r="N164" s="1" t="s">
         <v>287</v>
@@ -8470,7 +9393,7 @@
         <v>3</v>
       </c>
       <c r="P164" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q164" s="1" t="n">
         <v>0</v>
@@ -8478,10 +9401,10 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B165" s="18" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C165" s="18" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D165" s="1" t="n">
         <v>8</v>
@@ -8497,23 +9420,23 @@
         <v>34</v>
       </c>
       <c r="I165" s="18" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="J165" s="1" t="n">
         <f aca="false">J164+D164</f>
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="K165" s="1" t="n">
         <f aca="false">J165/8</f>
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L165" s="1" t="n">
         <f aca="false">J165/16</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M165" s="1" t="n">
         <f aca="false">J165/32</f>
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="N165" s="1" t="s">
         <v>287</v>
@@ -8522,7 +9445,7 @@
         <v>3</v>
       </c>
       <c r="P165" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q165" s="1" t="n">
         <v>0</v>
@@ -8530,10 +9453,10 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B166" s="18" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C166" s="18" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="D166" s="1" t="n">
         <v>8</v>
@@ -8549,32 +9472,32 @@
         <v>34</v>
       </c>
       <c r="I166" s="18" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="J166" s="1" t="n">
         <f aca="false">J165+D165</f>
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="K166" s="1" t="n">
         <f aca="false">J166/8</f>
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L166" s="1" t="n">
         <f aca="false">J166/16</f>
-        <v>24.5</v>
+        <v>23.5</v>
       </c>
       <c r="M166" s="1" t="n">
         <f aca="false">J166/32</f>
-        <v>12.25</v>
+        <v>11.75</v>
       </c>
       <c r="N166" s="1" t="s">
-        <v>109</v>
+        <v>287</v>
       </c>
       <c r="O166" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P166" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q166" s="1" t="n">
         <v>0</v>
@@ -8582,10 +9505,10 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B167" s="18" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C167" s="18" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D167" s="1" t="n">
         <v>8</v>
@@ -8601,32 +9524,32 @@
         <v>34</v>
       </c>
       <c r="I167" s="18" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="J167" s="1" t="n">
         <f aca="false">J166+D166</f>
-        <v>400</v>
+        <v>384</v>
       </c>
       <c r="K167" s="1" t="n">
         <f aca="false">J167/8</f>
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L167" s="1" t="n">
         <f aca="false">J167/16</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M167" s="1" t="n">
         <f aca="false">J167/32</f>
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="N167" s="1" t="s">
-        <v>109</v>
+        <v>287</v>
       </c>
       <c r="O167" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P167" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q167" s="1" t="n">
         <v>0</v>
@@ -8634,10 +9557,10 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B168" s="18" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C168" s="18" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D168" s="1" t="n">
         <v>8</v>
@@ -8653,23 +9576,23 @@
         <v>34</v>
       </c>
       <c r="I168" s="18" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="J168" s="1" t="n">
         <f aca="false">J167+D167</f>
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="K168" s="1" t="n">
         <f aca="false">J168/8</f>
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L168" s="1" t="n">
         <f aca="false">J168/16</f>
-        <v>25.5</v>
+        <v>24.5</v>
       </c>
       <c r="M168" s="1" t="n">
         <f aca="false">J168/32</f>
-        <v>12.75</v>
+        <v>12.25</v>
       </c>
       <c r="N168" s="1" t="s">
         <v>109</v>
@@ -8678,52 +9601,50 @@
         <v>2</v>
       </c>
       <c r="P168" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q168" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B169" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="C169" s="3" t="s">
-        <v>358</v>
+      <c r="B169" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="C169" s="18" t="s">
+        <v>354</v>
       </c>
       <c r="D169" s="1" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E169" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="F169" s="27" t="s">
-        <v>65</v>
-      </c>
+      <c r="F169" s="27"/>
       <c r="G169" s="18" t="n">
         <v>0</v>
       </c>
       <c r="H169" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I169" s="3" t="s">
-        <v>357</v>
+      <c r="I169" s="18" t="s">
+        <v>353</v>
       </c>
       <c r="J169" s="1" t="n">
         <f aca="false">J168+D168</f>
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="K169" s="1" t="n">
         <f aca="false">J169/8</f>
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="L169" s="1" t="n">
         <f aca="false">J169/16</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M169" s="1" t="n">
         <f aca="false">J169/32</f>
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="N169" s="1" t="s">
         <v>109</v>
@@ -8732,7 +9653,7 @@
         <v>2</v>
       </c>
       <c r="P169" s="1" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q169" s="1" t="n">
         <v>0</v>
@@ -8740,10 +9661,10 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B170" s="18" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C170" s="18" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D170" s="1" t="n">
         <v>8</v>
@@ -8753,29 +9674,29 @@
       </c>
       <c r="F170" s="27"/>
       <c r="G170" s="18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H170" s="27" t="s">
         <v>34</v>
       </c>
       <c r="I170" s="18" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="J170" s="1" t="n">
         <f aca="false">J169+D169</f>
-        <v>432</v>
+        <v>408</v>
       </c>
       <c r="K170" s="1" t="n">
         <f aca="false">J170/8</f>
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="L170" s="1" t="n">
         <f aca="false">J170/16</f>
-        <v>27</v>
+        <v>25.5</v>
       </c>
       <c r="M170" s="1" t="n">
         <f aca="false">J170/32</f>
-        <v>13.5</v>
+        <v>12.75</v>
       </c>
       <c r="N170" s="1" t="s">
         <v>109</v>
@@ -8784,50 +9705,52 @@
         <v>2</v>
       </c>
       <c r="P170" s="1" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q170" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B171" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="C171" s="18" t="s">
-        <v>362</v>
+      <c r="B171" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>358</v>
       </c>
       <c r="D171" s="1" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E171" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="F171" s="27"/>
+      <c r="F171" s="27" t="s">
+        <v>65</v>
+      </c>
       <c r="G171" s="18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H171" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I171" s="18" t="s">
-        <v>363</v>
+      <c r="I171" s="3" t="s">
+        <v>357</v>
       </c>
       <c r="J171" s="1" t="n">
         <f aca="false">J170+D170</f>
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="K171" s="1" t="n">
         <f aca="false">J171/8</f>
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="L171" s="1" t="n">
         <f aca="false">J171/16</f>
-        <v>27.5</v>
+        <v>26</v>
       </c>
       <c r="M171" s="1" t="n">
         <f aca="false">J171/32</f>
-        <v>13.75</v>
+        <v>13</v>
       </c>
       <c r="N171" s="1" t="s">
         <v>109</v>
@@ -8836,7 +9759,7 @@
         <v>2</v>
       </c>
       <c r="P171" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q171" s="1" t="n">
         <v>0</v>
@@ -8844,10 +9767,10 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B172" s="18" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C172" s="18" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D172" s="1" t="n">
         <v>8</v>
@@ -8863,23 +9786,23 @@
         <v>34</v>
       </c>
       <c r="I172" s="18" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="J172" s="1" t="n">
         <f aca="false">J171+D171</f>
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="K172" s="1" t="n">
         <f aca="false">J172/8</f>
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L172" s="1" t="n">
         <f aca="false">J172/16</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M172" s="1" t="n">
         <f aca="false">J172/32</f>
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="N172" s="1" t="s">
         <v>109</v>
@@ -8888,94 +9811,196 @@
         <v>2</v>
       </c>
       <c r="P172" s="1" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q172" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B173" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="C173" s="3" t="s">
-        <v>368</v>
+      <c r="B173" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="C173" s="18" t="s">
+        <v>362</v>
       </c>
       <c r="D173" s="1" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E173" s="27" t="s">
-        <v>369</v>
+        <v>25</v>
       </c>
       <c r="F173" s="27"/>
       <c r="G173" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H173" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I173" s="27" t="s">
-        <v>264</v>
+      <c r="I173" s="18" t="s">
+        <v>363</v>
       </c>
       <c r="J173" s="1" t="n">
         <f aca="false">J172+D172</f>
-        <v>456</v>
+        <v>440</v>
       </c>
       <c r="K173" s="1" t="n">
         <f aca="false">J173/8</f>
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L173" s="1" t="n">
         <f aca="false">J173/16</f>
-        <v>28.5</v>
+        <v>27.5</v>
       </c>
       <c r="M173" s="1" t="n">
         <f aca="false">J173/32</f>
-        <v>14.25</v>
+        <v>13.75</v>
       </c>
       <c r="N173" s="1" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="O173" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P173" s="1" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q173" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="1" t="s">
-        <v>45</v>
+      <c r="B174" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="C174" s="18" t="s">
+        <v>365</v>
+      </c>
+      <c r="D174" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E174" s="27" t="s">
+        <v>25</v>
       </c>
       <c r="F174" s="27"/>
-      <c r="G174" s="27"/>
-      <c r="H174" s="27"/>
-      <c r="I174" s="27"/>
+      <c r="G174" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H174" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I174" s="18" t="s">
+        <v>366</v>
+      </c>
       <c r="J174" s="1" t="n">
         <f aca="false">J173+D173</f>
-        <v>480</v>
+        <v>448</v>
       </c>
       <c r="K174" s="1" t="n">
         <f aca="false">J174/8</f>
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="L174" s="1" t="n">
         <f aca="false">J174/16</f>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M174" s="1" t="n">
         <f aca="false">J174/32</f>
+        <v>14</v>
+      </c>
+      <c r="N174" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="O174" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P174" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q174" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B175" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D175" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E175" s="27" t="s">
+        <v>369</v>
+      </c>
+      <c r="F175" s="27"/>
+      <c r="G175" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I175" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="J175" s="1" t="n">
+        <f aca="false">J174+D174</f>
+        <v>456</v>
+      </c>
+      <c r="K175" s="1" t="n">
+        <f aca="false">J175/8</f>
+        <v>57</v>
+      </c>
+      <c r="L175" s="1" t="n">
+        <f aca="false">J175/16</f>
+        <v>28.5</v>
+      </c>
+      <c r="M175" s="1" t="n">
+        <f aca="false">J175/32</f>
+        <v>14.25</v>
+      </c>
+      <c r="N175" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O175" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q175" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F176" s="27"/>
+      <c r="G176" s="27"/>
+      <c r="H176" s="27"/>
+      <c r="I176" s="27"/>
+      <c r="J176" s="1" t="n">
+        <f aca="false">J175+D175</f>
+        <v>480</v>
+      </c>
+      <c r="K176" s="1" t="n">
+        <f aca="false">J176/8</f>
+        <v>60</v>
+      </c>
+      <c r="L176" s="1" t="n">
+        <f aca="false">J176/16</f>
+        <v>30</v>
+      </c>
+      <c r="M176" s="1" t="n">
+        <f aca="false">J176/32</f>
         <v>15</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B175" s="1"/>
-    </row>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B177" s="1"/>
+    </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="7">
@@ -8988,7 +10013,7 @@
     <mergeCell ref="B50:I50"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A126" r:id="rId1" display="Structure:rt1Errors_t,file:rt1ErrorsDownlink.h"/>
+    <hyperlink ref="A128" r:id="rId1" display="Structure:rt1Errors_t,file:rt1ErrorsDownlink.h"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -9006,7 +10031,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B6:I20"/>
-  <sheetFormatPr defaultColWidth="9.328125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.3359375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.14"/>

--- a/TelemDefinition/DownlinkSpecPacsat.xlsx
+++ b/TelemDefinition/DownlinkSpecPacsat.xlsx
@@ -1453,7 +1453,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AMJ1048576"/>
+  <dimension ref="A1:Q1048576"/>
   <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.29"/>
@@ -4067,1105 +4067,183 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0"/>
-      <c r="B63" s="0"/>
-      <c r="C63" s="0"/>
-      <c r="D63" s="0"/>
-      <c r="E63" s="0"/>
-      <c r="F63" s="0"/>
-      <c r="G63" s="0"/>
-      <c r="H63" s="0"/>
-      <c r="I63" s="0"/>
-      <c r="J63" s="0"/>
-      <c r="K63" s="0"/>
-      <c r="L63" s="0"/>
-      <c r="M63" s="0"/>
-      <c r="N63" s="0"/>
-      <c r="O63" s="0"/>
-      <c r="P63" s="0"/>
-      <c r="Q63" s="0"/>
-      <c r="R63" s="0"/>
-      <c r="S63" s="0"/>
-      <c r="T63" s="0"/>
-      <c r="U63" s="0"/>
-      <c r="V63" s="0"/>
-      <c r="W63" s="0"/>
-      <c r="X63" s="0"/>
-      <c r="Y63" s="0"/>
-      <c r="Z63" s="0"/>
-      <c r="AA63" s="0"/>
-      <c r="AB63" s="0"/>
-      <c r="AC63" s="0"/>
-      <c r="AD63" s="0"/>
-      <c r="AE63" s="0"/>
-      <c r="AF63" s="0"/>
-      <c r="AG63" s="0"/>
-      <c r="AH63" s="0"/>
-      <c r="AI63" s="0"/>
-      <c r="AJ63" s="0"/>
-      <c r="AK63" s="0"/>
-      <c r="AL63" s="0"/>
-      <c r="AM63" s="0"/>
-      <c r="AN63" s="0"/>
-      <c r="AO63" s="0"/>
-      <c r="AP63" s="0"/>
-      <c r="AQ63" s="0"/>
-      <c r="AR63" s="0"/>
-      <c r="AS63" s="0"/>
-      <c r="AT63" s="0"/>
-      <c r="AU63" s="0"/>
-      <c r="AV63" s="0"/>
-      <c r="AW63" s="0"/>
-      <c r="AX63" s="0"/>
-      <c r="AY63" s="0"/>
-      <c r="AZ63" s="0"/>
-      <c r="BA63" s="0"/>
-      <c r="BB63" s="0"/>
-      <c r="BC63" s="0"/>
-      <c r="BD63" s="0"/>
-      <c r="BE63" s="0"/>
-      <c r="BF63" s="0"/>
-      <c r="BG63" s="0"/>
-      <c r="BH63" s="0"/>
-      <c r="BI63" s="0"/>
-      <c r="BJ63" s="0"/>
-      <c r="BK63" s="0"/>
-      <c r="BL63" s="0"/>
-      <c r="BM63" s="0"/>
-      <c r="BN63" s="0"/>
-      <c r="BO63" s="0"/>
-      <c r="BP63" s="0"/>
-      <c r="BQ63" s="0"/>
-      <c r="BR63" s="0"/>
-      <c r="BS63" s="0"/>
-      <c r="BT63" s="0"/>
-      <c r="BU63" s="0"/>
-      <c r="BV63" s="0"/>
-      <c r="BW63" s="0"/>
-      <c r="BX63" s="0"/>
-      <c r="BY63" s="0"/>
-      <c r="BZ63" s="0"/>
-      <c r="CA63" s="0"/>
-      <c r="CB63" s="0"/>
-      <c r="CC63" s="0"/>
-      <c r="CD63" s="0"/>
-      <c r="CE63" s="0"/>
-      <c r="CF63" s="0"/>
-      <c r="CG63" s="0"/>
-      <c r="CH63" s="0"/>
-      <c r="CI63" s="0"/>
-      <c r="CJ63" s="0"/>
-      <c r="CK63" s="0"/>
-      <c r="CL63" s="0"/>
-      <c r="CM63" s="0"/>
-      <c r="CN63" s="0"/>
-      <c r="CO63" s="0"/>
-      <c r="CP63" s="0"/>
-      <c r="CQ63" s="0"/>
-      <c r="CR63" s="0"/>
-      <c r="CS63" s="0"/>
-      <c r="CT63" s="0"/>
-      <c r="CU63" s="0"/>
-      <c r="CV63" s="0"/>
-      <c r="CW63" s="0"/>
-      <c r="CX63" s="0"/>
-      <c r="CY63" s="0"/>
-      <c r="CZ63" s="0"/>
-      <c r="DA63" s="0"/>
-      <c r="DB63" s="0"/>
-      <c r="DC63" s="0"/>
-      <c r="DD63" s="0"/>
-      <c r="DE63" s="0"/>
-      <c r="DF63" s="0"/>
-      <c r="DG63" s="0"/>
-      <c r="DH63" s="0"/>
-      <c r="DI63" s="0"/>
-      <c r="DJ63" s="0"/>
-      <c r="DK63" s="0"/>
-      <c r="DL63" s="0"/>
-      <c r="DM63" s="0"/>
-      <c r="DN63" s="0"/>
-      <c r="DO63" s="0"/>
-      <c r="DP63" s="0"/>
-      <c r="DQ63" s="0"/>
-      <c r="DR63" s="0"/>
-      <c r="DS63" s="0"/>
-      <c r="DT63" s="0"/>
-      <c r="DU63" s="0"/>
-      <c r="DV63" s="0"/>
-      <c r="DW63" s="0"/>
-      <c r="DX63" s="0"/>
-      <c r="DY63" s="0"/>
-      <c r="DZ63" s="0"/>
-      <c r="EA63" s="0"/>
-      <c r="EB63" s="0"/>
-      <c r="EC63" s="0"/>
-      <c r="ED63" s="0"/>
-      <c r="EE63" s="0"/>
-      <c r="EF63" s="0"/>
-      <c r="EG63" s="0"/>
-      <c r="EH63" s="0"/>
-      <c r="EI63" s="0"/>
-      <c r="EJ63" s="0"/>
-      <c r="EK63" s="0"/>
-      <c r="EL63" s="0"/>
-      <c r="EM63" s="0"/>
-      <c r="EN63" s="0"/>
-      <c r="EO63" s="0"/>
-      <c r="EP63" s="0"/>
-      <c r="EQ63" s="0"/>
-      <c r="ER63" s="0"/>
-      <c r="ES63" s="0"/>
-      <c r="ET63" s="0"/>
-      <c r="EU63" s="0"/>
-      <c r="EV63" s="0"/>
-      <c r="EW63" s="0"/>
-      <c r="EX63" s="0"/>
-      <c r="EY63" s="0"/>
-      <c r="EZ63" s="0"/>
-      <c r="FA63" s="0"/>
-      <c r="FB63" s="0"/>
-      <c r="FC63" s="0"/>
-      <c r="FD63" s="0"/>
-      <c r="FE63" s="0"/>
-      <c r="FF63" s="0"/>
-      <c r="FG63" s="0"/>
-      <c r="FH63" s="0"/>
-      <c r="FI63" s="0"/>
-      <c r="FJ63" s="0"/>
-      <c r="FK63" s="0"/>
-      <c r="FL63" s="0"/>
-      <c r="FM63" s="0"/>
-      <c r="FN63" s="0"/>
-      <c r="FO63" s="0"/>
-      <c r="FP63" s="0"/>
-      <c r="FQ63" s="0"/>
-      <c r="FR63" s="0"/>
-      <c r="FS63" s="0"/>
-      <c r="FT63" s="0"/>
-      <c r="FU63" s="0"/>
-      <c r="FV63" s="0"/>
-      <c r="FW63" s="0"/>
-      <c r="FX63" s="0"/>
-      <c r="FY63" s="0"/>
-      <c r="FZ63" s="0"/>
-      <c r="GA63" s="0"/>
-      <c r="GB63" s="0"/>
-      <c r="GC63" s="0"/>
-      <c r="GD63" s="0"/>
-      <c r="GE63" s="0"/>
-      <c r="GF63" s="0"/>
-      <c r="GG63" s="0"/>
-      <c r="GH63" s="0"/>
-      <c r="GI63" s="0"/>
-      <c r="GJ63" s="0"/>
-      <c r="GK63" s="0"/>
-      <c r="GL63" s="0"/>
-      <c r="GM63" s="0"/>
-      <c r="GN63" s="0"/>
-      <c r="GO63" s="0"/>
-      <c r="GP63" s="0"/>
-      <c r="GQ63" s="0"/>
-      <c r="GR63" s="0"/>
-      <c r="GS63" s="0"/>
-      <c r="GT63" s="0"/>
-      <c r="GU63" s="0"/>
-      <c r="GV63" s="0"/>
-      <c r="GW63" s="0"/>
-      <c r="GX63" s="0"/>
-      <c r="GY63" s="0"/>
-      <c r="GZ63" s="0"/>
-      <c r="HA63" s="0"/>
-      <c r="HB63" s="0"/>
-      <c r="HC63" s="0"/>
-      <c r="HD63" s="0"/>
-      <c r="HE63" s="0"/>
-      <c r="HF63" s="0"/>
-      <c r="HG63" s="0"/>
-      <c r="HH63" s="0"/>
-      <c r="HI63" s="0"/>
-      <c r="HJ63" s="0"/>
-      <c r="HK63" s="0"/>
-      <c r="HL63" s="0"/>
-      <c r="HM63" s="0"/>
-      <c r="HN63" s="0"/>
-      <c r="HO63" s="0"/>
-      <c r="HP63" s="0"/>
-      <c r="HQ63" s="0"/>
-      <c r="HR63" s="0"/>
-      <c r="HS63" s="0"/>
-      <c r="HT63" s="0"/>
-      <c r="HU63" s="0"/>
-      <c r="HV63" s="0"/>
-      <c r="HW63" s="0"/>
-      <c r="HX63" s="0"/>
-      <c r="HY63" s="0"/>
-      <c r="HZ63" s="0"/>
-      <c r="IA63" s="0"/>
-      <c r="IB63" s="0"/>
-      <c r="IC63" s="0"/>
-      <c r="ID63" s="0"/>
-      <c r="IE63" s="0"/>
-      <c r="IF63" s="0"/>
-      <c r="IG63" s="0"/>
-      <c r="IH63" s="0"/>
-      <c r="II63" s="0"/>
-      <c r="IJ63" s="0"/>
-      <c r="IK63" s="0"/>
-      <c r="IL63" s="0"/>
-      <c r="IM63" s="0"/>
-      <c r="IN63" s="0"/>
-      <c r="IO63" s="0"/>
-      <c r="IP63" s="0"/>
-      <c r="IQ63" s="0"/>
-      <c r="IR63" s="0"/>
-      <c r="IS63" s="0"/>
-      <c r="IT63" s="0"/>
-      <c r="IU63" s="0"/>
-      <c r="IV63" s="0"/>
-      <c r="IW63" s="0"/>
-      <c r="IX63" s="0"/>
-      <c r="IY63" s="0"/>
-      <c r="IZ63" s="0"/>
-      <c r="JA63" s="0"/>
-      <c r="JB63" s="0"/>
-      <c r="JC63" s="0"/>
-      <c r="JD63" s="0"/>
-      <c r="JE63" s="0"/>
-      <c r="JF63" s="0"/>
-      <c r="JG63" s="0"/>
-      <c r="JH63" s="0"/>
-      <c r="JI63" s="0"/>
-      <c r="JJ63" s="0"/>
-      <c r="JK63" s="0"/>
-      <c r="JL63" s="0"/>
-      <c r="JM63" s="0"/>
-      <c r="JN63" s="0"/>
-      <c r="JO63" s="0"/>
-      <c r="JP63" s="0"/>
-      <c r="JQ63" s="0"/>
-      <c r="JR63" s="0"/>
-      <c r="JS63" s="0"/>
-      <c r="JT63" s="0"/>
-      <c r="JU63" s="0"/>
-      <c r="JV63" s="0"/>
-      <c r="JW63" s="0"/>
-      <c r="JX63" s="0"/>
-      <c r="JY63" s="0"/>
-      <c r="JZ63" s="0"/>
-      <c r="KA63" s="0"/>
-      <c r="KB63" s="0"/>
-      <c r="KC63" s="0"/>
-      <c r="KD63" s="0"/>
-      <c r="KE63" s="0"/>
-      <c r="KF63" s="0"/>
-      <c r="KG63" s="0"/>
-      <c r="KH63" s="0"/>
-      <c r="KI63" s="0"/>
-      <c r="KJ63" s="0"/>
-      <c r="KK63" s="0"/>
-      <c r="KL63" s="0"/>
-      <c r="KM63" s="0"/>
-      <c r="KN63" s="0"/>
-      <c r="KO63" s="0"/>
-      <c r="KP63" s="0"/>
-      <c r="KQ63" s="0"/>
-      <c r="KR63" s="0"/>
-      <c r="KS63" s="0"/>
-      <c r="KT63" s="0"/>
-      <c r="KU63" s="0"/>
-      <c r="KV63" s="0"/>
-      <c r="KW63" s="0"/>
-      <c r="KX63" s="0"/>
-      <c r="KY63" s="0"/>
-      <c r="KZ63" s="0"/>
-      <c r="LA63" s="0"/>
-      <c r="LB63" s="0"/>
-      <c r="LC63" s="0"/>
-      <c r="LD63" s="0"/>
-      <c r="LE63" s="0"/>
-      <c r="LF63" s="0"/>
-      <c r="LG63" s="0"/>
-      <c r="LH63" s="0"/>
-      <c r="LI63" s="0"/>
-      <c r="LJ63" s="0"/>
-      <c r="LK63" s="0"/>
-      <c r="LL63" s="0"/>
-      <c r="LM63" s="0"/>
-      <c r="LN63" s="0"/>
-      <c r="LO63" s="0"/>
-      <c r="LP63" s="0"/>
-      <c r="LQ63" s="0"/>
-      <c r="LR63" s="0"/>
-      <c r="LS63" s="0"/>
-      <c r="LT63" s="0"/>
-      <c r="LU63" s="0"/>
-      <c r="LV63" s="0"/>
-      <c r="LW63" s="0"/>
-      <c r="LX63" s="0"/>
-      <c r="LY63" s="0"/>
-      <c r="LZ63" s="0"/>
-      <c r="MA63" s="0"/>
-      <c r="MB63" s="0"/>
-      <c r="MC63" s="0"/>
-      <c r="MD63" s="0"/>
-      <c r="ME63" s="0"/>
-      <c r="MF63" s="0"/>
-      <c r="MG63" s="0"/>
-      <c r="MH63" s="0"/>
-      <c r="MI63" s="0"/>
-      <c r="MJ63" s="0"/>
-      <c r="MK63" s="0"/>
-      <c r="ML63" s="0"/>
-      <c r="MM63" s="0"/>
-      <c r="MN63" s="0"/>
-      <c r="MO63" s="0"/>
-      <c r="MP63" s="0"/>
-      <c r="MQ63" s="0"/>
-      <c r="MR63" s="0"/>
-      <c r="MS63" s="0"/>
-      <c r="MT63" s="0"/>
-      <c r="MU63" s="0"/>
-      <c r="MV63" s="0"/>
-      <c r="MW63" s="0"/>
-      <c r="MX63" s="0"/>
-      <c r="MY63" s="0"/>
-      <c r="MZ63" s="0"/>
-      <c r="NA63" s="0"/>
-      <c r="NB63" s="0"/>
-      <c r="NC63" s="0"/>
-      <c r="ND63" s="0"/>
-      <c r="NE63" s="0"/>
-      <c r="NF63" s="0"/>
-      <c r="NG63" s="0"/>
-      <c r="NH63" s="0"/>
-      <c r="NI63" s="0"/>
-      <c r="NJ63" s="0"/>
-      <c r="NK63" s="0"/>
-      <c r="NL63" s="0"/>
-      <c r="NM63" s="0"/>
-      <c r="NN63" s="0"/>
-      <c r="NO63" s="0"/>
-      <c r="NP63" s="0"/>
-      <c r="NQ63" s="0"/>
-      <c r="NR63" s="0"/>
-      <c r="NS63" s="0"/>
-      <c r="NT63" s="0"/>
-      <c r="NU63" s="0"/>
-      <c r="NV63" s="0"/>
-      <c r="NW63" s="0"/>
-      <c r="NX63" s="0"/>
-      <c r="NY63" s="0"/>
-      <c r="NZ63" s="0"/>
-      <c r="OA63" s="0"/>
-      <c r="OB63" s="0"/>
-      <c r="OC63" s="0"/>
-      <c r="OD63" s="0"/>
-      <c r="OE63" s="0"/>
-      <c r="OF63" s="0"/>
-      <c r="OG63" s="0"/>
-      <c r="OH63" s="0"/>
-      <c r="OI63" s="0"/>
-      <c r="OJ63" s="0"/>
-      <c r="OK63" s="0"/>
-      <c r="OL63" s="0"/>
-      <c r="OM63" s="0"/>
-      <c r="ON63" s="0"/>
-      <c r="OO63" s="0"/>
-      <c r="OP63" s="0"/>
-      <c r="OQ63" s="0"/>
-      <c r="OR63" s="0"/>
-      <c r="OS63" s="0"/>
-      <c r="OT63" s="0"/>
-      <c r="OU63" s="0"/>
-      <c r="OV63" s="0"/>
-      <c r="OW63" s="0"/>
-      <c r="OX63" s="0"/>
-      <c r="OY63" s="0"/>
-      <c r="OZ63" s="0"/>
-      <c r="PA63" s="0"/>
-      <c r="PB63" s="0"/>
-      <c r="PC63" s="0"/>
-      <c r="PD63" s="0"/>
-      <c r="PE63" s="0"/>
-      <c r="PF63" s="0"/>
-      <c r="PG63" s="0"/>
-      <c r="PH63" s="0"/>
-      <c r="PI63" s="0"/>
-      <c r="PJ63" s="0"/>
-      <c r="PK63" s="0"/>
-      <c r="PL63" s="0"/>
-      <c r="PM63" s="0"/>
-      <c r="PN63" s="0"/>
-      <c r="PO63" s="0"/>
-      <c r="PP63" s="0"/>
-      <c r="PQ63" s="0"/>
-      <c r="PR63" s="0"/>
-      <c r="PS63" s="0"/>
-      <c r="PT63" s="0"/>
-      <c r="PU63" s="0"/>
-      <c r="PV63" s="0"/>
-      <c r="PW63" s="0"/>
-      <c r="PX63" s="0"/>
-      <c r="PY63" s="0"/>
-      <c r="PZ63" s="0"/>
-      <c r="QA63" s="0"/>
-      <c r="QB63" s="0"/>
-      <c r="QC63" s="0"/>
-      <c r="QD63" s="0"/>
-      <c r="QE63" s="0"/>
-      <c r="QF63" s="0"/>
-      <c r="QG63" s="0"/>
-      <c r="QH63" s="0"/>
-      <c r="QI63" s="0"/>
-      <c r="QJ63" s="0"/>
-      <c r="QK63" s="0"/>
-      <c r="QL63" s="0"/>
-      <c r="QM63" s="0"/>
-      <c r="QN63" s="0"/>
-      <c r="QO63" s="0"/>
-      <c r="QP63" s="0"/>
-      <c r="QQ63" s="0"/>
-      <c r="QR63" s="0"/>
-      <c r="QS63" s="0"/>
-      <c r="QT63" s="0"/>
-      <c r="QU63" s="0"/>
-      <c r="QV63" s="0"/>
-      <c r="QW63" s="0"/>
-      <c r="QX63" s="0"/>
-      <c r="QY63" s="0"/>
-      <c r="QZ63" s="0"/>
-      <c r="RA63" s="0"/>
-      <c r="RB63" s="0"/>
-      <c r="RC63" s="0"/>
-      <c r="RD63" s="0"/>
-      <c r="RE63" s="0"/>
-      <c r="RF63" s="0"/>
-      <c r="RG63" s="0"/>
-      <c r="RH63" s="0"/>
-      <c r="RI63" s="0"/>
-      <c r="RJ63" s="0"/>
-      <c r="RK63" s="0"/>
-      <c r="RL63" s="0"/>
-      <c r="RM63" s="0"/>
-      <c r="RN63" s="0"/>
-      <c r="RO63" s="0"/>
-      <c r="RP63" s="0"/>
-      <c r="RQ63" s="0"/>
-      <c r="RR63" s="0"/>
-      <c r="RS63" s="0"/>
-      <c r="RT63" s="0"/>
-      <c r="RU63" s="0"/>
-      <c r="RV63" s="0"/>
-      <c r="RW63" s="0"/>
-      <c r="RX63" s="0"/>
-      <c r="RY63" s="0"/>
-      <c r="RZ63" s="0"/>
-      <c r="SA63" s="0"/>
-      <c r="SB63" s="0"/>
-      <c r="SC63" s="0"/>
-      <c r="SD63" s="0"/>
-      <c r="SE63" s="0"/>
-      <c r="SF63" s="0"/>
-      <c r="SG63" s="0"/>
-      <c r="SH63" s="0"/>
-      <c r="SI63" s="0"/>
-      <c r="SJ63" s="0"/>
-      <c r="SK63" s="0"/>
-      <c r="SL63" s="0"/>
-      <c r="SM63" s="0"/>
-      <c r="SN63" s="0"/>
-      <c r="SO63" s="0"/>
-      <c r="SP63" s="0"/>
-      <c r="SQ63" s="0"/>
-      <c r="SR63" s="0"/>
-      <c r="SS63" s="0"/>
-      <c r="ST63" s="0"/>
-      <c r="SU63" s="0"/>
-      <c r="SV63" s="0"/>
-      <c r="SW63" s="0"/>
-      <c r="SX63" s="0"/>
-      <c r="SY63" s="0"/>
-      <c r="SZ63" s="0"/>
-      <c r="TA63" s="0"/>
-      <c r="TB63" s="0"/>
-      <c r="TC63" s="0"/>
-      <c r="TD63" s="0"/>
-      <c r="TE63" s="0"/>
-      <c r="TF63" s="0"/>
-      <c r="TG63" s="0"/>
-      <c r="TH63" s="0"/>
-      <c r="TI63" s="0"/>
-      <c r="TJ63" s="0"/>
-      <c r="TK63" s="0"/>
-      <c r="TL63" s="0"/>
-      <c r="TM63" s="0"/>
-      <c r="TN63" s="0"/>
-      <c r="TO63" s="0"/>
-      <c r="TP63" s="0"/>
-      <c r="TQ63" s="0"/>
-      <c r="TR63" s="0"/>
-      <c r="TS63" s="0"/>
-      <c r="TT63" s="0"/>
-      <c r="TU63" s="0"/>
-      <c r="TV63" s="0"/>
-      <c r="TW63" s="0"/>
-      <c r="TX63" s="0"/>
-      <c r="TY63" s="0"/>
-      <c r="TZ63" s="0"/>
-      <c r="UA63" s="0"/>
-      <c r="UB63" s="0"/>
-      <c r="UC63" s="0"/>
-      <c r="UD63" s="0"/>
-      <c r="UE63" s="0"/>
-      <c r="UF63" s="0"/>
-      <c r="UG63" s="0"/>
-      <c r="UH63" s="0"/>
-      <c r="UI63" s="0"/>
-      <c r="UJ63" s="0"/>
-      <c r="UK63" s="0"/>
-      <c r="UL63" s="0"/>
-      <c r="UM63" s="0"/>
-      <c r="UN63" s="0"/>
-      <c r="UO63" s="0"/>
-      <c r="UP63" s="0"/>
-      <c r="UQ63" s="0"/>
-      <c r="UR63" s="0"/>
-      <c r="US63" s="0"/>
-      <c r="UT63" s="0"/>
-      <c r="UU63" s="0"/>
-      <c r="UV63" s="0"/>
-      <c r="UW63" s="0"/>
-      <c r="UX63" s="0"/>
-      <c r="UY63" s="0"/>
-      <c r="UZ63" s="0"/>
-      <c r="VA63" s="0"/>
-      <c r="VB63" s="0"/>
-      <c r="VC63" s="0"/>
-      <c r="VD63" s="0"/>
-      <c r="VE63" s="0"/>
-      <c r="VF63" s="0"/>
-      <c r="VG63" s="0"/>
-      <c r="VH63" s="0"/>
-      <c r="VI63" s="0"/>
-      <c r="VJ63" s="0"/>
-      <c r="VK63" s="0"/>
-      <c r="VL63" s="0"/>
-      <c r="VM63" s="0"/>
-      <c r="VN63" s="0"/>
-      <c r="VO63" s="0"/>
-      <c r="VP63" s="0"/>
-      <c r="VQ63" s="0"/>
-      <c r="VR63" s="0"/>
-      <c r="VS63" s="0"/>
-      <c r="VT63" s="0"/>
-      <c r="VU63" s="0"/>
-      <c r="VV63" s="0"/>
-      <c r="VW63" s="0"/>
-      <c r="VX63" s="0"/>
-      <c r="VY63" s="0"/>
-      <c r="VZ63" s="0"/>
-      <c r="WA63" s="0"/>
-      <c r="WB63" s="0"/>
-      <c r="WC63" s="0"/>
-      <c r="WD63" s="0"/>
-      <c r="WE63" s="0"/>
-      <c r="WF63" s="0"/>
-      <c r="WG63" s="0"/>
-      <c r="WH63" s="0"/>
-      <c r="WI63" s="0"/>
-      <c r="WJ63" s="0"/>
-      <c r="WK63" s="0"/>
-      <c r="WL63" s="0"/>
-      <c r="WM63" s="0"/>
-      <c r="WN63" s="0"/>
-      <c r="WO63" s="0"/>
-      <c r="WP63" s="0"/>
-      <c r="WQ63" s="0"/>
-      <c r="WR63" s="0"/>
-      <c r="WS63" s="0"/>
-      <c r="WT63" s="0"/>
-      <c r="WU63" s="0"/>
-      <c r="WV63" s="0"/>
-      <c r="WW63" s="0"/>
-      <c r="WX63" s="0"/>
-      <c r="WY63" s="0"/>
-      <c r="WZ63" s="0"/>
-      <c r="XA63" s="0"/>
-      <c r="XB63" s="0"/>
-      <c r="XC63" s="0"/>
-      <c r="XD63" s="0"/>
-      <c r="XE63" s="0"/>
-      <c r="XF63" s="0"/>
-      <c r="XG63" s="0"/>
-      <c r="XH63" s="0"/>
-      <c r="XI63" s="0"/>
-      <c r="XJ63" s="0"/>
-      <c r="XK63" s="0"/>
-      <c r="XL63" s="0"/>
-      <c r="XM63" s="0"/>
-      <c r="XN63" s="0"/>
-      <c r="XO63" s="0"/>
-      <c r="XP63" s="0"/>
-      <c r="XQ63" s="0"/>
-      <c r="XR63" s="0"/>
-      <c r="XS63" s="0"/>
-      <c r="XT63" s="0"/>
-      <c r="XU63" s="0"/>
-      <c r="XV63" s="0"/>
-      <c r="XW63" s="0"/>
-      <c r="XX63" s="0"/>
-      <c r="XY63" s="0"/>
-      <c r="XZ63" s="0"/>
-      <c r="YA63" s="0"/>
-      <c r="YB63" s="0"/>
-      <c r="YC63" s="0"/>
-      <c r="YD63" s="0"/>
-      <c r="YE63" s="0"/>
-      <c r="YF63" s="0"/>
-      <c r="YG63" s="0"/>
-      <c r="YH63" s="0"/>
-      <c r="YI63" s="0"/>
-      <c r="YJ63" s="0"/>
-      <c r="YK63" s="0"/>
-      <c r="YL63" s="0"/>
-      <c r="YM63" s="0"/>
-      <c r="YN63" s="0"/>
-      <c r="YO63" s="0"/>
-      <c r="YP63" s="0"/>
-      <c r="YQ63" s="0"/>
-      <c r="YR63" s="0"/>
-      <c r="YS63" s="0"/>
-      <c r="YT63" s="0"/>
-      <c r="YU63" s="0"/>
-      <c r="YV63" s="0"/>
-      <c r="YW63" s="0"/>
-      <c r="YX63" s="0"/>
-      <c r="YY63" s="0"/>
-      <c r="YZ63" s="0"/>
-      <c r="ZA63" s="0"/>
-      <c r="ZB63" s="0"/>
-      <c r="ZC63" s="0"/>
-      <c r="ZD63" s="0"/>
-      <c r="ZE63" s="0"/>
-      <c r="ZF63" s="0"/>
-      <c r="ZG63" s="0"/>
-      <c r="ZH63" s="0"/>
-      <c r="ZI63" s="0"/>
-      <c r="ZJ63" s="0"/>
-      <c r="ZK63" s="0"/>
-      <c r="ZL63" s="0"/>
-      <c r="ZM63" s="0"/>
-      <c r="ZN63" s="0"/>
-      <c r="ZO63" s="0"/>
-      <c r="ZP63" s="0"/>
-      <c r="ZQ63" s="0"/>
-      <c r="ZR63" s="0"/>
-      <c r="ZS63" s="0"/>
-      <c r="ZT63" s="0"/>
-      <c r="ZU63" s="0"/>
-      <c r="ZV63" s="0"/>
-      <c r="ZW63" s="0"/>
-      <c r="ZX63" s="0"/>
-      <c r="ZY63" s="0"/>
-      <c r="ZZ63" s="0"/>
-      <c r="AAA63" s="0"/>
-      <c r="AAB63" s="0"/>
-      <c r="AAC63" s="0"/>
-      <c r="AAD63" s="0"/>
-      <c r="AAE63" s="0"/>
-      <c r="AAF63" s="0"/>
-      <c r="AAG63" s="0"/>
-      <c r="AAH63" s="0"/>
-      <c r="AAI63" s="0"/>
-      <c r="AAJ63" s="0"/>
-      <c r="AAK63" s="0"/>
-      <c r="AAL63" s="0"/>
-      <c r="AAM63" s="0"/>
-      <c r="AAN63" s="0"/>
-      <c r="AAO63" s="0"/>
-      <c r="AAP63" s="0"/>
-      <c r="AAQ63" s="0"/>
-      <c r="AAR63" s="0"/>
-      <c r="AAS63" s="0"/>
-      <c r="AAT63" s="0"/>
-      <c r="AAU63" s="0"/>
-      <c r="AAV63" s="0"/>
-      <c r="AAW63" s="0"/>
-      <c r="AAX63" s="0"/>
-      <c r="AAY63" s="0"/>
-      <c r="AAZ63" s="0"/>
-      <c r="ABA63" s="0"/>
-      <c r="ABB63" s="0"/>
-      <c r="ABC63" s="0"/>
-      <c r="ABD63" s="0"/>
-      <c r="ABE63" s="0"/>
-      <c r="ABF63" s="0"/>
-      <c r="ABG63" s="0"/>
-      <c r="ABH63" s="0"/>
-      <c r="ABI63" s="0"/>
-      <c r="ABJ63" s="0"/>
-      <c r="ABK63" s="0"/>
-      <c r="ABL63" s="0"/>
-      <c r="ABM63" s="0"/>
-      <c r="ABN63" s="0"/>
-      <c r="ABO63" s="0"/>
-      <c r="ABP63" s="0"/>
-      <c r="ABQ63" s="0"/>
-      <c r="ABR63" s="0"/>
-      <c r="ABS63" s="0"/>
-      <c r="ABT63" s="0"/>
-      <c r="ABU63" s="0"/>
-      <c r="ABV63" s="0"/>
-      <c r="ABW63" s="0"/>
-      <c r="ABX63" s="0"/>
-      <c r="ABY63" s="0"/>
-      <c r="ABZ63" s="0"/>
-      <c r="ACA63" s="0"/>
-      <c r="ACB63" s="0"/>
-      <c r="ACC63" s="0"/>
-      <c r="ACD63" s="0"/>
-      <c r="ACE63" s="0"/>
-      <c r="ACF63" s="0"/>
-      <c r="ACG63" s="0"/>
-      <c r="ACH63" s="0"/>
-      <c r="ACI63" s="0"/>
-      <c r="ACJ63" s="0"/>
-      <c r="ACK63" s="0"/>
-      <c r="ACL63" s="0"/>
-      <c r="ACM63" s="0"/>
-      <c r="ACN63" s="0"/>
-      <c r="ACO63" s="0"/>
-      <c r="ACP63" s="0"/>
-      <c r="ACQ63" s="0"/>
-      <c r="ACR63" s="0"/>
-      <c r="ACS63" s="0"/>
-      <c r="ACT63" s="0"/>
-      <c r="ACU63" s="0"/>
-      <c r="ACV63" s="0"/>
-      <c r="ACW63" s="0"/>
-      <c r="ACX63" s="0"/>
-      <c r="ACY63" s="0"/>
-      <c r="ACZ63" s="0"/>
-      <c r="ADA63" s="0"/>
-      <c r="ADB63" s="0"/>
-      <c r="ADC63" s="0"/>
-      <c r="ADD63" s="0"/>
-      <c r="ADE63" s="0"/>
-      <c r="ADF63" s="0"/>
-      <c r="ADG63" s="0"/>
-      <c r="ADH63" s="0"/>
-      <c r="ADI63" s="0"/>
-      <c r="ADJ63" s="0"/>
-      <c r="ADK63" s="0"/>
-      <c r="ADL63" s="0"/>
-      <c r="ADM63" s="0"/>
-      <c r="ADN63" s="0"/>
-      <c r="ADO63" s="0"/>
-      <c r="ADP63" s="0"/>
-      <c r="ADQ63" s="0"/>
-      <c r="ADR63" s="0"/>
-      <c r="ADS63" s="0"/>
-      <c r="ADT63" s="0"/>
-      <c r="ADU63" s="0"/>
-      <c r="ADV63" s="0"/>
-      <c r="ADW63" s="0"/>
-      <c r="ADX63" s="0"/>
-      <c r="ADY63" s="0"/>
-      <c r="ADZ63" s="0"/>
-      <c r="AEA63" s="0"/>
-      <c r="AEB63" s="0"/>
-      <c r="AEC63" s="0"/>
-      <c r="AED63" s="0"/>
-      <c r="AEE63" s="0"/>
-      <c r="AEF63" s="0"/>
-      <c r="AEG63" s="0"/>
-      <c r="AEH63" s="0"/>
-      <c r="AEI63" s="0"/>
-      <c r="AEJ63" s="0"/>
-      <c r="AEK63" s="0"/>
-      <c r="AEL63" s="0"/>
-      <c r="AEM63" s="0"/>
-      <c r="AEN63" s="0"/>
-      <c r="AEO63" s="0"/>
-      <c r="AEP63" s="0"/>
-      <c r="AEQ63" s="0"/>
-      <c r="AER63" s="0"/>
-      <c r="AES63" s="0"/>
-      <c r="AET63" s="0"/>
-      <c r="AEU63" s="0"/>
-      <c r="AEV63" s="0"/>
-      <c r="AEW63" s="0"/>
-      <c r="AEX63" s="0"/>
-      <c r="AEY63" s="0"/>
-      <c r="AEZ63" s="0"/>
-      <c r="AFA63" s="0"/>
-      <c r="AFB63" s="0"/>
-      <c r="AFC63" s="0"/>
-      <c r="AFD63" s="0"/>
-      <c r="AFE63" s="0"/>
-      <c r="AFF63" s="0"/>
-      <c r="AFG63" s="0"/>
-      <c r="AFH63" s="0"/>
-      <c r="AFI63" s="0"/>
-      <c r="AFJ63" s="0"/>
-      <c r="AFK63" s="0"/>
-      <c r="AFL63" s="0"/>
-      <c r="AFM63" s="0"/>
-      <c r="AFN63" s="0"/>
-      <c r="AFO63" s="0"/>
-      <c r="AFP63" s="0"/>
-      <c r="AFQ63" s="0"/>
-      <c r="AFR63" s="0"/>
-      <c r="AFS63" s="0"/>
-      <c r="AFT63" s="0"/>
-      <c r="AFU63" s="0"/>
-      <c r="AFV63" s="0"/>
-      <c r="AFW63" s="0"/>
-      <c r="AFX63" s="0"/>
-      <c r="AFY63" s="0"/>
-      <c r="AFZ63" s="0"/>
-      <c r="AGA63" s="0"/>
-      <c r="AGB63" s="0"/>
-      <c r="AGC63" s="0"/>
-      <c r="AGD63" s="0"/>
-      <c r="AGE63" s="0"/>
-      <c r="AGF63" s="0"/>
-      <c r="AGG63" s="0"/>
-      <c r="AGH63" s="0"/>
-      <c r="AGI63" s="0"/>
-      <c r="AGJ63" s="0"/>
-      <c r="AGK63" s="0"/>
-      <c r="AGL63" s="0"/>
-      <c r="AGM63" s="0"/>
-      <c r="AGN63" s="0"/>
-      <c r="AGO63" s="0"/>
-      <c r="AGP63" s="0"/>
-      <c r="AGQ63" s="0"/>
-      <c r="AGR63" s="0"/>
-      <c r="AGS63" s="0"/>
-      <c r="AGT63" s="0"/>
-      <c r="AGU63" s="0"/>
-      <c r="AGV63" s="0"/>
-      <c r="AGW63" s="0"/>
-      <c r="AGX63" s="0"/>
-      <c r="AGY63" s="0"/>
-      <c r="AGZ63" s="0"/>
-      <c r="AHA63" s="0"/>
-      <c r="AHB63" s="0"/>
-      <c r="AHC63" s="0"/>
-      <c r="AHD63" s="0"/>
-      <c r="AHE63" s="0"/>
-      <c r="AHF63" s="0"/>
-      <c r="AHG63" s="0"/>
-      <c r="AHH63" s="0"/>
-      <c r="AHI63" s="0"/>
-      <c r="AHJ63" s="0"/>
-      <c r="AHK63" s="0"/>
-      <c r="AHL63" s="0"/>
-      <c r="AHM63" s="0"/>
-      <c r="AHN63" s="0"/>
-      <c r="AHO63" s="0"/>
-      <c r="AHP63" s="0"/>
-      <c r="AHQ63" s="0"/>
-      <c r="AHR63" s="0"/>
-      <c r="AHS63" s="0"/>
-      <c r="AHT63" s="0"/>
-      <c r="AHU63" s="0"/>
-      <c r="AHV63" s="0"/>
-      <c r="AHW63" s="0"/>
-      <c r="AHX63" s="0"/>
-      <c r="AHY63" s="0"/>
-      <c r="AHZ63" s="0"/>
-      <c r="AIA63" s="0"/>
-      <c r="AIB63" s="0"/>
-      <c r="AIC63" s="0"/>
-      <c r="AID63" s="0"/>
-      <c r="AIE63" s="0"/>
-      <c r="AIF63" s="0"/>
-      <c r="AIG63" s="0"/>
-      <c r="AIH63" s="0"/>
-      <c r="AII63" s="0"/>
-      <c r="AIJ63" s="0"/>
-      <c r="AIK63" s="0"/>
-      <c r="AIL63" s="0"/>
-      <c r="AIM63" s="0"/>
-      <c r="AIN63" s="0"/>
-      <c r="AIO63" s="0"/>
-      <c r="AIP63" s="0"/>
-      <c r="AIQ63" s="0"/>
-      <c r="AIR63" s="0"/>
-      <c r="AIS63" s="0"/>
-      <c r="AIT63" s="0"/>
-      <c r="AIU63" s="0"/>
-      <c r="AIV63" s="0"/>
-      <c r="AIW63" s="0"/>
-      <c r="AIX63" s="0"/>
-      <c r="AIY63" s="0"/>
-      <c r="AIZ63" s="0"/>
-      <c r="AJA63" s="0"/>
-      <c r="AJB63" s="0"/>
-      <c r="AJC63" s="0"/>
-      <c r="AJD63" s="0"/>
-      <c r="AJE63" s="0"/>
-      <c r="AJF63" s="0"/>
-      <c r="AJG63" s="0"/>
-      <c r="AJH63" s="0"/>
-      <c r="AJI63" s="0"/>
-      <c r="AJJ63" s="0"/>
-      <c r="AJK63" s="0"/>
-      <c r="AJL63" s="0"/>
-      <c r="AJM63" s="0"/>
-      <c r="AJN63" s="0"/>
-      <c r="AJO63" s="0"/>
-      <c r="AJP63" s="0"/>
-      <c r="AJQ63" s="0"/>
-      <c r="AJR63" s="0"/>
-      <c r="AJS63" s="0"/>
-      <c r="AJT63" s="0"/>
-      <c r="AJU63" s="0"/>
-      <c r="AJV63" s="0"/>
-      <c r="AJW63" s="0"/>
-      <c r="AJX63" s="0"/>
-      <c r="AJY63" s="0"/>
-      <c r="AJZ63" s="0"/>
-      <c r="AKA63" s="0"/>
-      <c r="AKB63" s="0"/>
-      <c r="AKC63" s="0"/>
-      <c r="AKD63" s="0"/>
-      <c r="AKE63" s="0"/>
-      <c r="AKF63" s="0"/>
-      <c r="AKG63" s="0"/>
-      <c r="AKH63" s="0"/>
-      <c r="AKI63" s="0"/>
-      <c r="AKJ63" s="0"/>
-      <c r="AKK63" s="0"/>
-      <c r="AKL63" s="0"/>
-      <c r="AKM63" s="0"/>
-      <c r="AKN63" s="0"/>
-      <c r="AKO63" s="0"/>
-      <c r="AKP63" s="0"/>
-      <c r="AKQ63" s="0"/>
-      <c r="AKR63" s="0"/>
-      <c r="AKS63" s="0"/>
-      <c r="AKT63" s="0"/>
-      <c r="AKU63" s="0"/>
-      <c r="AKV63" s="0"/>
-      <c r="AKW63" s="0"/>
-      <c r="AKX63" s="0"/>
-      <c r="AKY63" s="0"/>
-      <c r="AKZ63" s="0"/>
-      <c r="ALA63" s="0"/>
-      <c r="ALB63" s="0"/>
-      <c r="ALC63" s="0"/>
-      <c r="ALD63" s="0"/>
-      <c r="ALE63" s="0"/>
-      <c r="ALF63" s="0"/>
-      <c r="ALG63" s="0"/>
-      <c r="ALH63" s="0"/>
-      <c r="ALI63" s="0"/>
-      <c r="ALJ63" s="0"/>
-      <c r="ALK63" s="0"/>
-      <c r="ALL63" s="0"/>
-      <c r="ALM63" s="0"/>
-      <c r="ALN63" s="0"/>
-      <c r="ALO63" s="0"/>
-      <c r="ALP63" s="0"/>
-      <c r="ALQ63" s="0"/>
-      <c r="ALR63" s="0"/>
-      <c r="ALS63" s="0"/>
-      <c r="ALT63" s="0"/>
-      <c r="ALU63" s="0"/>
-      <c r="ALV63" s="0"/>
-      <c r="ALW63" s="0"/>
-      <c r="ALX63" s="0"/>
-      <c r="ALY63" s="0"/>
-      <c r="ALZ63" s="0"/>
-      <c r="AMA63" s="0"/>
-      <c r="AMB63" s="0"/>
-      <c r="AMC63" s="0"/>
-      <c r="AMD63" s="0"/>
-      <c r="AME63" s="0"/>
-      <c r="AMF63" s="0"/>
-      <c r="AMG63" s="0"/>
-      <c r="AMH63" s="0"/>
-      <c r="AMI63" s="0"/>
-      <c r="AMJ63" s="0"/>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B63" s="18"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="18"/>
+      <c r="E63" s="18"/>
+      <c r="F63" s="18"/>
+      <c r="G63" s="18"/>
+      <c r="H63" s="18"/>
+      <c r="I63" s="19"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B64" s="18"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="18"/>
+      <c r="E64" s="18"/>
+      <c r="F64" s="18"/>
+      <c r="G64" s="18"/>
+      <c r="H64" s="18"/>
+      <c r="I64" s="19"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B65" s="18"/>
-      <c r="C65" s="18"/>
-      <c r="D65" s="18"/>
-      <c r="E65" s="18"/>
+      <c r="B65" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C65" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D65" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E65" s="18" t="s">
+        <v>25</v>
+      </c>
       <c r="F65" s="18"/>
-      <c r="G65" s="18"/>
-      <c r="H65" s="18"/>
-      <c r="I65" s="19"/>
+      <c r="G65" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I65" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="J65" s="1" t="n">
+        <f aca="false">J64+D64</f>
+        <v>0</v>
+      </c>
+      <c r="K65" s="1" t="n">
+        <f aca="false">J65/8</f>
+        <v>0</v>
+      </c>
+      <c r="L65" s="1" t="n">
+        <f aca="false">J65/16</f>
+        <v>0</v>
+      </c>
+      <c r="M65" s="1" t="n">
+        <f aca="false">J65/32</f>
+        <v>0</v>
+      </c>
+      <c r="N65" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="B66" s="18"/>
-      <c r="C66" s="18"/>
-      <c r="D66" s="18"/>
-      <c r="E66" s="18"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="18"/>
-      <c r="H66" s="18"/>
-      <c r="I66" s="19"/>
+      <c r="B66" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="C66" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="D66" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F66" s="19"/>
+      <c r="G66" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I66" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="J66" s="1" t="n">
+        <f aca="false">J65+D65</f>
+        <v>7</v>
+      </c>
+      <c r="K66" s="1" t="n">
+        <f aca="false">J66/8</f>
+        <v>0.875</v>
+      </c>
+      <c r="L66" s="1" t="n">
+        <f aca="false">J66/16</f>
+        <v>0.4375</v>
+      </c>
+      <c r="M66" s="1" t="n">
+        <f aca="false">J66/32</f>
+        <v>0.21875</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="O66" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P66" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q66" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="C67" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="D67" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="E67" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="F67" s="18"/>
+      <c r="B67" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="C67" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="D67" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F67" s="19"/>
       <c r="G67" s="18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" s="18" t="s">
         <v>34</v>
       </c>
       <c r="I67" s="19" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="J67" s="1" t="n">
         <f aca="false">J66+D66</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K67" s="1" t="n">
         <f aca="false">J67/8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="1" t="n">
         <f aca="false">J67/16</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M67" s="1" t="n">
         <f aca="false">J67/32</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q67" s="1" t="n">
         <v>0</v>
@@ -5173,10 +4251,10 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="23" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="D68" s="23" t="n">
         <v>1</v>
@@ -5192,23 +4270,23 @@
         <v>34</v>
       </c>
       <c r="I68" s="19" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="J68" s="1" t="n">
         <f aca="false">J67+D67</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K68" s="1" t="n">
         <f aca="false">J68/8</f>
-        <v>0.875</v>
+        <v>1.125</v>
       </c>
       <c r="L68" s="1" t="n">
         <f aca="false">J68/16</f>
-        <v>0.4375</v>
+        <v>0.5625</v>
       </c>
       <c r="M68" s="1" t="n">
         <f aca="false">J68/32</f>
-        <v>0.21875</v>
+        <v>0.28125</v>
       </c>
       <c r="N68" s="1" t="s">
         <v>68</v>
@@ -5217,7 +4295,7 @@
         <v>4</v>
       </c>
       <c r="P68" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q68" s="1" t="n">
         <v>0</v>
@@ -5225,10 +4303,10 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="23" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C69" s="23" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D69" s="23" t="n">
         <v>1</v>
@@ -5244,32 +4322,32 @@
         <v>34</v>
       </c>
       <c r="I69" s="19" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="J69" s="1" t="n">
         <f aca="false">J68+D68</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K69" s="1" t="n">
         <f aca="false">J69/8</f>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L69" s="1" t="n">
         <f aca="false">J69/16</f>
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="M69" s="1" t="n">
         <f aca="false">J69/32</f>
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P69" s="1" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Q69" s="1" t="n">
         <v>0</v>
@@ -5277,10 +4355,10 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="23" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C70" s="23" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D70" s="23" t="n">
         <v>1</v>
@@ -5296,32 +4374,32 @@
         <v>34</v>
       </c>
       <c r="I70" s="19" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="J70" s="1" t="n">
         <f aca="false">J69+D69</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K70" s="1" t="n">
         <f aca="false">J70/8</f>
-        <v>1.125</v>
+        <v>1.375</v>
       </c>
       <c r="L70" s="1" t="n">
         <f aca="false">J70/16</f>
-        <v>0.5625</v>
+        <v>0.6875</v>
       </c>
       <c r="M70" s="1" t="n">
         <f aca="false">J70/32</f>
-        <v>0.28125</v>
+        <v>0.34375</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P70" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q70" s="1" t="n">
         <v>0</v>
@@ -5329,10 +4407,10 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="23" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D71" s="23" t="n">
         <v>1</v>
@@ -5348,32 +4426,32 @@
         <v>34</v>
       </c>
       <c r="I71" s="19" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J71" s="1" t="n">
         <f aca="false">J70+D70</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K71" s="1" t="n">
         <f aca="false">J71/8</f>
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="L71" s="1" t="n">
         <f aca="false">J71/16</f>
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="M71" s="1" t="n">
         <f aca="false">J71/32</f>
-        <v>0.3125</v>
+        <v>0.375</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q71" s="1" t="n">
         <v>0</v>
@@ -5381,10 +4459,10 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="23" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D72" s="23" t="n">
         <v>1</v>
@@ -5400,23 +4478,23 @@
         <v>34</v>
       </c>
       <c r="I72" s="19" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="J72" s="1" t="n">
         <f aca="false">J71+D71</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K72" s="1" t="n">
         <f aca="false">J72/8</f>
-        <v>1.375</v>
+        <v>1.625</v>
       </c>
       <c r="L72" s="1" t="n">
         <f aca="false">J72/16</f>
-        <v>0.6875</v>
+        <v>0.8125</v>
       </c>
       <c r="M72" s="1" t="n">
         <f aca="false">J72/32</f>
-        <v>0.34375</v>
+        <v>0.40625</v>
       </c>
       <c r="N72" s="1" t="s">
         <v>53</v>
@@ -5425,7 +4503,7 @@
         <v>3</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q72" s="1" t="n">
         <v>0</v>
@@ -5433,10 +4511,10 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="23" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C73" s="23" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D73" s="23" t="n">
         <v>1</v>
@@ -5452,32 +4530,32 @@
         <v>34</v>
       </c>
       <c r="I73" s="19" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="J73" s="1" t="n">
         <f aca="false">J72+D72</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K73" s="1" t="n">
         <f aca="false">J73/8</f>
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="L73" s="1" t="n">
         <f aca="false">J73/16</f>
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="M73" s="1" t="n">
         <f aca="false">J73/32</f>
-        <v>0.375</v>
+        <v>0.4375</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="O73" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P73" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="P73" s="1" t="n">
-        <v>6</v>
       </c>
       <c r="Q73" s="1" t="n">
         <v>0</v>
@@ -5485,10 +4563,10 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="23" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C74" s="23" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D74" s="23" t="n">
         <v>1</v>
@@ -5504,160 +4582,160 @@
         <v>34</v>
       </c>
       <c r="I74" s="19" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="J74" s="1" t="n">
         <f aca="false">J73+D73</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K74" s="1" t="n">
         <f aca="false">J74/8</f>
-        <v>1.625</v>
+        <v>1.875</v>
       </c>
       <c r="L74" s="1" t="n">
         <f aca="false">J74/16</f>
-        <v>0.8125</v>
+        <v>0.9375</v>
       </c>
       <c r="M74" s="1" t="n">
         <f aca="false">J74/32</f>
-        <v>0.40625</v>
+        <v>0.46875</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P74" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q74" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="C75" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="D75" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E75" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F75" s="19"/>
-      <c r="G75" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I75" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="J75" s="1" t="n">
+      <c r="A75" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B75" s="18"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="18"/>
+      <c r="E75" s="18"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="18"/>
+      <c r="H75" s="18"/>
+      <c r="I75" s="19"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="C76" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="D76" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E76" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F76" s="18"/>
+      <c r="G76" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I76" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="J76" s="1" t="n">
         <f aca="false">J74+D74</f>
-        <v>14</v>
-      </c>
-      <c r="K75" s="1" t="n">
-        <f aca="false">J75/8</f>
-        <v>1.75</v>
-      </c>
-      <c r="L75" s="1" t="n">
-        <f aca="false">J75/16</f>
-        <v>0.875</v>
-      </c>
-      <c r="M75" s="1" t="n">
-        <f aca="false">J75/32</f>
-        <v>0.4375</v>
-      </c>
-      <c r="N75" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="O75" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P75" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q75" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="C76" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="D76" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E76" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F76" s="19"/>
-      <c r="G76" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H76" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I76" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="J76" s="1" t="n">
-        <f aca="false">J75+D75</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K76" s="1" t="n">
         <f aca="false">J76/8</f>
-        <v>1.875</v>
+        <v>2</v>
       </c>
       <c r="L76" s="1" t="n">
         <f aca="false">J76/16</f>
-        <v>0.9375</v>
+        <v>1</v>
       </c>
       <c r="M76" s="1" t="n">
         <f aca="false">J76/32</f>
-        <v>0.46875</v>
+        <v>0.5</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>109</v>
+        <v>44</v>
       </c>
       <c r="O76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P76" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q76" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="C77" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="D77" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E77" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F77" s="18"/>
+      <c r="G77" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="H77" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="I77" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="J77" s="1" t="n">
+        <f aca="false">J76+D76</f>
+        <v>24</v>
+      </c>
+      <c r="K77" s="1" t="n">
+        <f aca="false">J77/8</f>
+        <v>3</v>
+      </c>
+      <c r="L77" s="1" t="n">
+        <f aca="false">J77/16</f>
+        <v>1.5</v>
+      </c>
+      <c r="M77" s="1" t="n">
+        <f aca="false">J77/32</f>
+        <v>0.75</v>
+      </c>
+      <c r="N77" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O77" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P77" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="P76" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q76" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B77" s="18"/>
-      <c r="C77" s="18"/>
-      <c r="D77" s="18"/>
-      <c r="E77" s="18"/>
-      <c r="F77" s="18"/>
-      <c r="G77" s="18"/>
-      <c r="H77" s="18"/>
-      <c r="I77" s="19"/>
+      <c r="Q77" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="18" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D78" s="18" t="n">
         <v>8</v>
@@ -5667,29 +4745,29 @@
       </c>
       <c r="F78" s="18"/>
       <c r="G78" s="18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H78" s="18" t="s">
-        <v>34</v>
+        <v>173</v>
       </c>
       <c r="I78" s="19" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="J78" s="1" t="n">
-        <f aca="false">J76+D76</f>
-        <v>16</v>
+        <f aca="false">J77+D77</f>
+        <v>32</v>
       </c>
       <c r="K78" s="1" t="n">
         <f aca="false">J78/8</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L78" s="1" t="n">
         <f aca="false">J78/16</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M78" s="1" t="n">
         <f aca="false">J78/32</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N78" s="1" t="s">
         <v>44</v>
@@ -5698,7 +4776,7 @@
         <v>1</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q78" s="1" t="n">
         <v>0</v>
@@ -5706,10 +4784,10 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="18" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D79" s="18" t="n">
         <v>8</v>
@@ -5725,23 +4803,23 @@
         <v>173</v>
       </c>
       <c r="I79" s="19" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="J79" s="1" t="n">
         <f aca="false">J78+D78</f>
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="K79" s="1" t="n">
         <f aca="false">J79/8</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L79" s="1" t="n">
         <f aca="false">J79/16</f>
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="M79" s="1" t="n">
         <f aca="false">J79/32</f>
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="N79" s="1" t="s">
         <v>44</v>
@@ -5750,18 +4828,18 @@
         <v>1</v>
       </c>
       <c r="P79" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q79" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="18" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C80" s="18" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D80" s="18" t="n">
         <v>8</v>
@@ -5771,29 +4849,29 @@
       </c>
       <c r="F80" s="18"/>
       <c r="G80" s="18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H80" s="18" t="s">
-        <v>173</v>
+        <v>51</v>
       </c>
       <c r="I80" s="19" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="J80" s="1" t="n">
         <f aca="false">J79+D79</f>
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="K80" s="1" t="n">
         <f aca="false">J80/8</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L80" s="1" t="n">
         <f aca="false">J80/16</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M80" s="1" t="n">
         <f aca="false">J80/32</f>
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="N80" s="1" t="s">
         <v>44</v>
@@ -5802,18 +4880,18 @@
         <v>1</v>
       </c>
       <c r="P80" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q80" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="18" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C81" s="18" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D81" s="18" t="n">
         <v>8</v>
@@ -5823,29 +4901,29 @@
       </c>
       <c r="F81" s="18"/>
       <c r="G81" s="18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H81" s="18" t="s">
-        <v>173</v>
+        <v>51</v>
       </c>
       <c r="I81" s="19" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="J81" s="1" t="n">
         <f aca="false">J80+D80</f>
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="K81" s="1" t="n">
         <f aca="false">J81/8</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L81" s="1" t="n">
         <f aca="false">J81/16</f>
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="M81" s="1" t="n">
         <f aca="false">J81/32</f>
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="N81" s="1" t="s">
         <v>44</v>
@@ -5854,7 +4932,7 @@
         <v>1</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q81" s="1" t="n">
         <v>0</v>
@@ -5862,10 +4940,10 @@
     </row>
     <row r="82" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="18" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C82" s="18" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D82" s="18" t="n">
         <v>8</v>
@@ -5875,49 +4953,49 @@
       </c>
       <c r="F82" s="18"/>
       <c r="G82" s="18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H82" s="18" t="s">
-        <v>51</v>
+        <v>173</v>
       </c>
       <c r="I82" s="19" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J82" s="1" t="n">
         <f aca="false">J81+D81</f>
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="K82" s="1" t="n">
         <f aca="false">J82/8</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L82" s="1" t="n">
         <f aca="false">J82/16</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M82" s="1" t="n">
         <f aca="false">J82/32</f>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="O82" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q82" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="18" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C83" s="18" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D83" s="18" t="n">
         <v>8</v>
@@ -5927,49 +5005,49 @@
       </c>
       <c r="F83" s="18"/>
       <c r="G83" s="18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H83" s="18" t="s">
-        <v>51</v>
+        <v>173</v>
       </c>
       <c r="I83" s="19" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="J83" s="1" t="n">
         <f aca="false">J82+D82</f>
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="K83" s="1" t="n">
         <f aca="false">J83/8</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L83" s="1" t="n">
         <f aca="false">J83/16</f>
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="M83" s="1" t="n">
         <f aca="false">J83/32</f>
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="O83" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q83" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B84" s="18" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C84" s="18" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="D84" s="18" t="n">
         <v>8</v>
@@ -5985,23 +5063,23 @@
         <v>173</v>
       </c>
       <c r="I84" s="19" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="J84" s="1" t="n">
         <f aca="false">J83+D83</f>
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="K84" s="1" t="n">
         <f aca="false">J84/8</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L84" s="1" t="n">
         <f aca="false">J84/16</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M84" s="1" t="n">
         <f aca="false">J84/32</f>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="N84" s="1" t="s">
         <v>53</v>
@@ -6010,206 +5088,206 @@
         <v>3</v>
       </c>
       <c r="P84" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q84" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="C85" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="D85" s="18" t="n">
+      <c r="B85" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="C85" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="D85" s="23" t="n">
         <v>8</v>
       </c>
       <c r="E85" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F85" s="18"/>
+        <v>65</v>
+      </c>
+      <c r="F85" s="19"/>
       <c r="G85" s="18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H85" s="18" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="I85" s="19" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="J85" s="1" t="n">
         <f aca="false">J84+D84</f>
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="K85" s="1" t="n">
         <f aca="false">J85/8</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L85" s="1" t="n">
         <f aca="false">J85/16</f>
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="M85" s="1" t="n">
         <f aca="false">J85/32</f>
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P85" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q85" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="C86" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="D86" s="18" t="n">
+    <row r="86" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="C86" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="D86" s="23" t="n">
         <v>8</v>
       </c>
       <c r="E86" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F86" s="18"/>
+      <c r="F86" s="19"/>
       <c r="G86" s="18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H86" s="18" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="I86" s="19" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="J86" s="1" t="n">
         <f aca="false">J85+D85</f>
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="K86" s="1" t="n">
         <f aca="false">J86/8</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L86" s="1" t="n">
         <f aca="false">J86/16</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M86" s="1" t="n">
         <f aca="false">J86/32</f>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P86" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q86" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="23" t="s">
-        <v>196</v>
+        <v>129</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="D87" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E87" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="F87" s="19"/>
+        <v>202</v>
+      </c>
+      <c r="D87" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="E87" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F87" s="18"/>
       <c r="G87" s="18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H87" s="18" t="s">
         <v>34</v>
       </c>
       <c r="I87" s="19" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="J87" s="1" t="n">
         <f aca="false">J86+D86</f>
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="K87" s="1" t="n">
         <f aca="false">J87/8</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L87" s="1" t="n">
         <f aca="false">J87/16</f>
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="M87" s="1" t="n">
         <f aca="false">J87/32</f>
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="O87" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q87" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="23" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C88" s="23" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D88" s="23" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E88" s="19" t="s">
         <v>25</v>
       </c>
       <c r="F88" s="19"/>
       <c r="G88" s="18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H88" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="I88" s="19" t="s">
-        <v>201</v>
+      <c r="I88" s="23" t="s">
+        <v>206</v>
       </c>
       <c r="J88" s="1" t="n">
         <f aca="false">J87+D87</f>
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="K88" s="1" t="n">
         <f aca="false">J88/8</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L88" s="1" t="n">
         <f aca="false">J88/16</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M88" s="1" t="n">
         <f aca="false">J88/32</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N88" s="1" t="s">
         <v>44</v>
@@ -6218,26 +5296,26 @@
         <v>1</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q88" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="23" t="s">
-        <v>129</v>
+        <v>207</v>
       </c>
       <c r="C89" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="D89" s="21" t="n">
-        <v>24</v>
-      </c>
-      <c r="E89" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="F89" s="18"/>
+        <v>208</v>
+      </c>
+      <c r="D89" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E89" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F89" s="19"/>
       <c r="G89" s="18" t="n">
         <v>0</v>
       </c>
@@ -6245,32 +5323,32 @@
         <v>34</v>
       </c>
       <c r="I89" s="19" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="J89" s="1" t="n">
         <f aca="false">J88+D88</f>
-        <v>104</v>
+        <v>160</v>
       </c>
       <c r="K89" s="1" t="n">
         <f aca="false">J89/8</f>
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="L89" s="1" t="n">
         <f aca="false">J89/16</f>
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="M89" s="1" t="n">
         <f aca="false">J89/32</f>
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P89" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q89" s="1" t="n">
         <v>0</v>
@@ -6278,16 +5356,16 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="23" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="C90" s="23" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D90" s="23" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E90" s="19" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="F90" s="19"/>
       <c r="G90" s="18" t="n">
@@ -6296,33 +5374,33 @@
       <c r="H90" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="I90" s="23" t="s">
-        <v>206</v>
+      <c r="I90" s="19" t="s">
+        <v>212</v>
       </c>
       <c r="J90" s="1" t="n">
         <f aca="false">J89+D89</f>
-        <v>128</v>
+        <v>168</v>
       </c>
       <c r="K90" s="1" t="n">
         <f aca="false">J90/8</f>
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L90" s="1" t="n">
         <f aca="false">J90/16</f>
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="M90" s="1" t="n">
         <f aca="false">J90/32</f>
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P90" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q90" s="1" t="n">
         <v>0</v>
@@ -6330,10 +5408,10 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="23" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C91" s="23" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D91" s="23" t="n">
         <v>8</v>
@@ -6349,23 +5427,23 @@
         <v>34</v>
       </c>
       <c r="I91" s="19" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="J91" s="1" t="n">
         <f aca="false">J90+D90</f>
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="K91" s="1" t="n">
         <f aca="false">J91/8</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L91" s="1" t="n">
         <f aca="false">J91/16</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M91" s="1" t="n">
         <f aca="false">J91/32</f>
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="N91" s="1" t="s">
         <v>109</v>
@@ -6374,7 +5452,7 @@
         <v>2</v>
       </c>
       <c r="P91" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q91" s="1" t="n">
         <v>0</v>
@@ -6382,10 +5460,10 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="23" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C92" s="23" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D92" s="23" t="n">
         <v>8</v>
@@ -6401,23 +5479,23 @@
         <v>34</v>
       </c>
       <c r="I92" s="19" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="J92" s="1" t="n">
         <f aca="false">J91+D91</f>
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="K92" s="1" t="n">
         <f aca="false">J92/8</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L92" s="1" t="n">
         <f aca="false">J92/16</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="M92" s="1" t="n">
         <f aca="false">J92/32</f>
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="N92" s="1" t="s">
         <v>109</v>
@@ -6426,286 +5504,282 @@
         <v>2</v>
       </c>
       <c r="P92" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q92" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B93" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="C93" s="23" t="s">
-        <v>214</v>
-      </c>
-      <c r="D93" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E93" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="F93" s="19"/>
-      <c r="G93" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I93" s="19" t="s">
-        <v>215</v>
+    <row r="93" s="13" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B93" s="24"/>
+      <c r="C93" s="25"/>
+      <c r="D93" s="26"/>
+      <c r="E93" s="26"/>
+      <c r="F93" s="26"/>
+      <c r="G93" s="26"/>
+      <c r="H93" s="25"/>
+      <c r="I93" s="26" t="s">
+        <v>219</v>
       </c>
       <c r="J93" s="1" t="n">
         <f aca="false">J92+D92</f>
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="K93" s="1" t="n">
         <f aca="false">J93/8</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L93" s="1" t="n">
         <f aca="false">J93/16</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M93" s="1" t="n">
         <f aca="false">J93/32</f>
-        <v>5.5</v>
-      </c>
-      <c r="N93" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="O93" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="O93" s="17"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B94" s="20"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B96" s="23"/>
+      <c r="C96" s="23"/>
+      <c r="D96" s="23"/>
+      <c r="E96" s="19"/>
+      <c r="F96" s="19"/>
+      <c r="G96" s="19"/>
+      <c r="H96" s="19"/>
+      <c r="I96" s="19"/>
+      <c r="J96" s="22"/>
+      <c r="K96" s="22"/>
+      <c r="L96" s="22"/>
+      <c r="M96" s="22"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B97" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="C97" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="D97" s="23" t="n">
+        <v>32</v>
+      </c>
+      <c r="E97" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F97" s="19"/>
+      <c r="G97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I97" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="J97" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="22" t="n">
+        <f aca="false">J97/8</f>
+        <v>0</v>
+      </c>
+      <c r="L97" s="22" t="n">
+        <f aca="false">J97/16</f>
+        <v>0</v>
+      </c>
+      <c r="M97" s="22" t="n">
+        <f aca="false">J97/32</f>
+        <v>0</v>
+      </c>
+      <c r="N97" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" s="13" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B98" s="24"/>
+      <c r="C98" s="25"/>
+      <c r="D98" s="26"/>
+      <c r="E98" s="26"/>
+      <c r="F98" s="26"/>
+      <c r="G98" s="26"/>
+      <c r="H98" s="25"/>
+      <c r="I98" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="J98" s="1" t="n">
+        <f aca="false">J97+D97</f>
+        <v>32</v>
+      </c>
+      <c r="K98" s="1" t="n">
+        <f aca="false">J98/8</f>
+        <v>4</v>
+      </c>
+      <c r="L98" s="1" t="n">
+        <f aca="false">J98/16</f>
         <v>2</v>
       </c>
-      <c r="P93" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q93" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="23" t="s">
-        <v>216</v>
-      </c>
-      <c r="C94" s="23" t="s">
-        <v>217</v>
-      </c>
-      <c r="D94" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E94" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="F94" s="19"/>
-      <c r="G94" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I94" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="J94" s="1" t="n">
-        <f aca="false">J93+D93</f>
-        <v>184</v>
-      </c>
-      <c r="K94" s="1" t="n">
-        <f aca="false">J94/8</f>
-        <v>23</v>
-      </c>
-      <c r="L94" s="1" t="n">
-        <f aca="false">J94/16</f>
-        <v>11.5</v>
-      </c>
-      <c r="M94" s="1" t="n">
-        <f aca="false">J94/32</f>
-        <v>5.75</v>
-      </c>
-      <c r="N94" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="O94" s="3" t="n">
+      <c r="M98" s="1" t="n">
+        <f aca="false">J98/32</f>
+        <v>1</v>
+      </c>
+      <c r="O98" s="17"/>
+    </row>
+    <row r="99" s="13" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B99" s="24"/>
+      <c r="C99" s="25"/>
+      <c r="D99" s="26"/>
+      <c r="E99" s="26"/>
+      <c r="F99" s="26"/>
+      <c r="G99" s="26"/>
+      <c r="H99" s="25"/>
+      <c r="I99" s="26"/>
+      <c r="J99" s="22"/>
+      <c r="K99" s="22"/>
+      <c r="L99" s="22"/>
+      <c r="M99" s="22"/>
+      <c r="O99" s="17"/>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B100" s="20"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B101" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="C101" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="D101" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="E101" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="F101" s="19"/>
+      <c r="G101" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="I101" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="J101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="22" t="n">
+        <f aca="false">J101/8</f>
+        <v>0</v>
+      </c>
+      <c r="L101" s="22" t="n">
+        <f aca="false">J101/16</f>
+        <v>0</v>
+      </c>
+      <c r="M101" s="22" t="n">
+        <f aca="false">J101/32</f>
+        <v>0</v>
+      </c>
+      <c r="N101" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B102" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="C102" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="D102" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="E102" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F102" s="19"/>
+      <c r="G102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="J102" s="1" t="n">
+        <f aca="false">J101+D101</f>
+        <v>32</v>
+      </c>
+      <c r="K102" s="1" t="n">
+        <f aca="false">J102/8</f>
+        <v>4</v>
+      </c>
+      <c r="L102" s="1" t="n">
+        <f aca="false">J102/16</f>
         <v>2</v>
       </c>
-      <c r="P94" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q94" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" s="13" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B95" s="24"/>
-      <c r="C95" s="25"/>
-      <c r="D95" s="26"/>
-      <c r="E95" s="26"/>
-      <c r="F95" s="26"/>
-      <c r="G95" s="26"/>
-      <c r="H95" s="25"/>
-      <c r="I95" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="J95" s="1" t="n">
-        <f aca="false">J94+D94</f>
-        <v>192</v>
-      </c>
-      <c r="K95" s="1" t="n">
-        <f aca="false">J95/8</f>
-        <v>24</v>
-      </c>
-      <c r="L95" s="1" t="n">
-        <f aca="false">J95/16</f>
-        <v>12</v>
-      </c>
-      <c r="M95" s="1" t="n">
-        <f aca="false">J95/32</f>
-        <v>6</v>
-      </c>
-      <c r="O95" s="17"/>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B96" s="20"/>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B98" s="23"/>
-      <c r="C98" s="23"/>
-      <c r="D98" s="23"/>
-      <c r="E98" s="19"/>
-      <c r="F98" s="19"/>
-      <c r="G98" s="19"/>
-      <c r="H98" s="19"/>
-      <c r="I98" s="19"/>
-      <c r="J98" s="22"/>
-      <c r="K98" s="22"/>
-      <c r="L98" s="22"/>
-      <c r="M98" s="22"/>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B99" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="C99" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="D99" s="23" t="n">
-        <v>32</v>
-      </c>
-      <c r="E99" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="F99" s="19"/>
-      <c r="G99" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I99" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="J99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" s="22" t="n">
-        <f aca="false">J99/8</f>
-        <v>0</v>
-      </c>
-      <c r="L99" s="22" t="n">
-        <f aca="false">J99/16</f>
-        <v>0</v>
-      </c>
-      <c r="M99" s="22" t="n">
-        <f aca="false">J99/32</f>
-        <v>0</v>
-      </c>
-      <c r="N99" s="1" t="s">
+      <c r="M102" s="1" t="n">
+        <f aca="false">J102/32</f>
+        <v>1</v>
+      </c>
+      <c r="N102" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="O99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" s="13" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B100" s="24"/>
-      <c r="C100" s="25"/>
-      <c r="D100" s="26"/>
-      <c r="E100" s="26"/>
-      <c r="F100" s="26"/>
-      <c r="G100" s="26"/>
-      <c r="H100" s="25"/>
-      <c r="I100" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="J100" s="1" t="n">
-        <f aca="false">J99+D99</f>
-        <v>32</v>
-      </c>
-      <c r="K100" s="1" t="n">
-        <f aca="false">J100/8</f>
-        <v>4</v>
-      </c>
-      <c r="L100" s="1" t="n">
-        <f aca="false">J100/16</f>
-        <v>2</v>
-      </c>
-      <c r="M100" s="1" t="n">
-        <f aca="false">J100/32</f>
-        <v>1</v>
-      </c>
-      <c r="O100" s="17"/>
-    </row>
-    <row r="101" s="13" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B101" s="24"/>
-      <c r="C101" s="25"/>
-      <c r="D101" s="26"/>
-      <c r="E101" s="26"/>
-      <c r="F101" s="26"/>
-      <c r="G101" s="26"/>
-      <c r="H101" s="25"/>
-      <c r="I101" s="26"/>
-      <c r="J101" s="22"/>
-      <c r="K101" s="22"/>
-      <c r="L101" s="22"/>
-      <c r="M101" s="22"/>
-      <c r="O101" s="17"/>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B102" s="20"/>
+      <c r="O102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="23" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C103" s="23" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="D103" s="21" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E103" s="27" t="s">
         <v>225</v>
@@ -6714,26 +5788,27 @@
       <c r="G103" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H103" s="3" t="s">
-        <v>226</v>
+      <c r="H103" s="18" t="s">
+        <v>34</v>
       </c>
       <c r="I103" s="22" t="s">
-        <v>227</v>
-      </c>
-      <c r="J103" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" s="22" t="n">
+        <v>233</v>
+      </c>
+      <c r="J103" s="1" t="n">
+        <f aca="false">J102+D102</f>
+        <v>48</v>
+      </c>
+      <c r="K103" s="1" t="n">
         <f aca="false">J103/8</f>
-        <v>0</v>
-      </c>
-      <c r="L103" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="L103" s="1" t="n">
         <f aca="false">J103/16</f>
-        <v>0</v>
-      </c>
-      <c r="M103" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M103" s="1" t="n">
         <f aca="false">J103/32</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N103" s="1" t="s">
         <v>28</v>
@@ -6750,39 +5825,40 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B104" s="23" t="s">
-        <v>228</v>
+        <v>129</v>
       </c>
       <c r="C104" s="23" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D104" s="21" t="n">
-        <v>16</v>
-      </c>
-      <c r="E104" s="27" t="s">
-        <v>25</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E104" s="27"/>
       <c r="F104" s="19"/>
       <c r="G104" s="18" t="n">
         <v>0</v>
       </c>
+      <c r="H104" s="18" t="s">
+        <v>34</v>
+      </c>
       <c r="I104" s="22" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="J104" s="1" t="n">
         <f aca="false">J103+D103</f>
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="K104" s="1" t="n">
         <f aca="false">J104/8</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L104" s="1" t="n">
         <f aca="false">J104/16</f>
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="M104" s="1" t="n">
         <f aca="false">J104/32</f>
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="N104" s="1" t="s">
         <v>28</v>
@@ -6797,186 +5873,180 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B105" s="23" t="s">
-        <v>231</v>
-      </c>
-      <c r="C105" s="23" t="s">
-        <v>232</v>
-      </c>
-      <c r="D105" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="E105" s="27" t="s">
-        <v>225</v>
-      </c>
-      <c r="F105" s="19"/>
-      <c r="G105" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I105" s="22" t="s">
-        <v>233</v>
+    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B105" s="20"/>
+      <c r="C105" s="25"/>
+      <c r="D105" s="26"/>
+      <c r="E105" s="26"/>
+      <c r="F105" s="26"/>
+      <c r="G105" s="26"/>
+      <c r="H105" s="25"/>
+      <c r="I105" s="26" t="s">
+        <v>219</v>
       </c>
       <c r="J105" s="1" t="n">
         <f aca="false">J104+D104</f>
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="K105" s="1" t="n">
         <f aca="false">J105/8</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L105" s="1" t="n">
         <f aca="false">J105/16</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M105" s="1" t="n">
         <f aca="false">J105/32</f>
-        <v>1.5</v>
-      </c>
-      <c r="N105" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B106" s="20"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B107" s="20"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B108" s="20"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B109" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="C109" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="D109" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="E109" s="27"/>
+      <c r="F109" s="19"/>
+      <c r="G109" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="I109" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="J109" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="22" t="n">
+        <f aca="false">J109/8</f>
+        <v>0</v>
+      </c>
+      <c r="L109" s="22" t="n">
+        <f aca="false">J109/16</f>
+        <v>0</v>
+      </c>
+      <c r="M109" s="22" t="n">
+        <f aca="false">J109/32</f>
+        <v>0</v>
+      </c>
+      <c r="N109" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="O105" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P105" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q105" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B106" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="C106" s="23" t="s">
-        <v>234</v>
-      </c>
-      <c r="D106" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="E106" s="27"/>
-      <c r="F106" s="19"/>
-      <c r="G106" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I106" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="J106" s="1" t="n">
-        <f aca="false">J105+D105</f>
-        <v>56</v>
-      </c>
-      <c r="K106" s="1" t="n">
-        <f aca="false">J106/8</f>
-        <v>7</v>
-      </c>
-      <c r="L106" s="1" t="n">
-        <f aca="false">J106/16</f>
-        <v>3.5</v>
-      </c>
-      <c r="M106" s="1" t="n">
-        <f aca="false">J106/32</f>
-        <v>1.75</v>
-      </c>
-      <c r="N106" s="1" t="s">
+      <c r="O109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B110" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="C110" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="D110" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="E110" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F110" s="19"/>
+      <c r="G110" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="J110" s="1" t="n">
+        <f aca="false">J109+D109</f>
+        <v>32</v>
+      </c>
+      <c r="K110" s="1" t="n">
+        <f aca="false">J110/8</f>
+        <v>4</v>
+      </c>
+      <c r="L110" s="1" t="n">
+        <f aca="false">J110/16</f>
+        <v>2</v>
+      </c>
+      <c r="M110" s="1" t="n">
+        <f aca="false">J110/32</f>
+        <v>1</v>
+      </c>
+      <c r="N110" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="O106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P106" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B107" s="20"/>
-      <c r="C107" s="25"/>
-      <c r="D107" s="26"/>
-      <c r="E107" s="26"/>
-      <c r="F107" s="26"/>
-      <c r="G107" s="26"/>
-      <c r="H107" s="25"/>
-      <c r="I107" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="J107" s="1" t="n">
-        <f aca="false">J106+D106</f>
-        <v>64</v>
-      </c>
-      <c r="K107" s="1" t="n">
-        <f aca="false">J107/8</f>
-        <v>8</v>
-      </c>
-      <c r="L107" s="1" t="n">
-        <f aca="false">J107/16</f>
-        <v>4</v>
-      </c>
-      <c r="M107" s="1" t="n">
-        <f aca="false">J107/32</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B108" s="20"/>
-    </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B109" s="20"/>
-    </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B110" s="20"/>
+      <c r="O110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B111" s="23" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C111" s="23" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D111" s="21" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E111" s="27"/>
       <c r="F111" s="19"/>
       <c r="G111" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H111" s="3" t="s">
-        <v>226</v>
-      </c>
       <c r="I111" s="22" t="s">
-        <v>227</v>
-      </c>
-      <c r="J111" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K111" s="22" t="n">
+        <v>243</v>
+      </c>
+      <c r="J111" s="1" t="n">
+        <f aca="false">J110+D110</f>
+        <v>48</v>
+      </c>
+      <c r="K111" s="1" t="n">
         <f aca="false">J111/8</f>
-        <v>0</v>
-      </c>
-      <c r="L111" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="L111" s="1" t="n">
         <f aca="false">J111/16</f>
-        <v>0</v>
-      </c>
-      <c r="M111" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M111" s="1" t="n">
         <f aca="false">J111/32</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N111" s="1" t="s">
         <v>28</v>
@@ -6993,39 +6063,37 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B112" s="23" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C112" s="23" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D112" s="21" t="n">
-        <v>16</v>
-      </c>
-      <c r="E112" s="27" t="s">
-        <v>25</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="E112" s="27"/>
       <c r="F112" s="19"/>
       <c r="G112" s="18" t="n">
         <v>0</v>
       </c>
       <c r="I112" s="22" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="J112" s="1" t="n">
         <f aca="false">J111+D111</f>
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="K112" s="1" t="n">
         <f aca="false">J112/8</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L112" s="1" t="n">
         <f aca="false">J112/16</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M112" s="1" t="n">
         <f aca="false">J112/32</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N112" s="1" t="s">
         <v>28</v>
@@ -7042,37 +6110,42 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B113" s="23" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C113" s="23" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D113" s="21" t="n">
-        <v>16</v>
-      </c>
-      <c r="E113" s="27"/>
+        <v>8</v>
+      </c>
+      <c r="E113" s="27" t="s">
+        <v>225</v>
+      </c>
       <c r="F113" s="19"/>
       <c r="G113" s="18" t="n">
         <v>0</v>
       </c>
+      <c r="H113" s="18" t="s">
+        <v>34</v>
+      </c>
       <c r="I113" s="22" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="J113" s="1" t="n">
         <f aca="false">J112+D112</f>
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="K113" s="1" t="n">
         <f aca="false">J113/8</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L113" s="1" t="n">
         <f aca="false">J113/16</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M113" s="1" t="n">
         <f aca="false">J113/32</f>
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="N113" s="1" t="s">
         <v>28</v>
@@ -7089,37 +6162,40 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B114" s="23" t="s">
-        <v>244</v>
+        <v>129</v>
       </c>
       <c r="C114" s="23" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D114" s="21" t="n">
-        <v>32</v>
-      </c>
-      <c r="E114" s="27"/>
+        <v>24</v>
+      </c>
+      <c r="E114" s="27" t="s">
+        <v>65</v>
+      </c>
       <c r="F114" s="19"/>
       <c r="G114" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="I114" s="22" t="s">
-        <v>246</v>
-      </c>
+      <c r="H114" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I114" s="22"/>
       <c r="J114" s="1" t="n">
         <f aca="false">J113+D113</f>
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="K114" s="1" t="n">
         <f aca="false">J114/8</f>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L114" s="1" t="n">
         <f aca="false">J114/16</f>
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="M114" s="1" t="n">
         <f aca="false">J114/32</f>
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="N114" s="1" t="s">
         <v>28</v>
@@ -7134,166 +6210,167 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B115" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="C115" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="D115" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="E115" s="27" t="s">
-        <v>225</v>
-      </c>
-      <c r="F115" s="19"/>
-      <c r="G115" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I115" s="22" t="s">
-        <v>249</v>
+    <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B115" s="24"/>
+      <c r="C115" s="25"/>
+      <c r="D115" s="26"/>
+      <c r="E115" s="26"/>
+      <c r="F115" s="26"/>
+      <c r="G115" s="26"/>
+      <c r="H115" s="25"/>
+      <c r="I115" s="26" t="s">
+        <v>219</v>
       </c>
       <c r="J115" s="1" t="n">
         <f aca="false">J114+D114</f>
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="K115" s="1" t="n">
         <f aca="false">J115/8</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L115" s="1" t="n">
         <f aca="false">J115/16</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M115" s="1" t="n">
         <f aca="false">J115/32</f>
-        <v>3</v>
-      </c>
-      <c r="N115" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O115" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q115" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B116" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="C116" s="23" t="s">
-        <v>250</v>
-      </c>
-      <c r="D116" s="21" t="n">
-        <v>24</v>
-      </c>
-      <c r="E116" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="F116" s="19"/>
-      <c r="G116" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I116" s="22"/>
-      <c r="J116" s="1" t="n">
-        <f aca="false">J115+D115</f>
-        <v>104</v>
-      </c>
-      <c r="K116" s="1" t="n">
-        <f aca="false">J116/8</f>
-        <v>13</v>
-      </c>
-      <c r="L116" s="1" t="n">
-        <f aca="false">J116/16</f>
-        <v>6.5</v>
-      </c>
-      <c r="M116" s="1" t="n">
-        <f aca="false">J116/32</f>
-        <v>3.25</v>
-      </c>
-      <c r="N116" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O116" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B117" s="24"/>
-      <c r="C117" s="25"/>
-      <c r="D117" s="26"/>
-      <c r="E117" s="26"/>
-      <c r="F117" s="26"/>
-      <c r="G117" s="26"/>
-      <c r="H117" s="25"/>
-      <c r="I117" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="J117" s="1" t="n">
-        <f aca="false">J116+D116</f>
-        <v>128</v>
-      </c>
-      <c r="K117" s="1" t="n">
-        <f aca="false">J117/8</f>
+      <c r="B116" s="20"/>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B117" s="20"/>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B118" s="20"/>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B119" s="20"/>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B120" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="C120" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="D120" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="E120" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F120" s="19"/>
+      <c r="G120" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="I120" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="J120" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="22" t="n">
+        <f aca="false">J120/8</f>
+        <v>0</v>
+      </c>
+      <c r="L120" s="22" t="n">
+        <f aca="false">J120/16</f>
+        <v>0</v>
+      </c>
+      <c r="M120" s="22" t="n">
+        <f aca="false">J120/32</f>
+        <v>0</v>
+      </c>
+      <c r="N120" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O120" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P120" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q120" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B121" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="C121" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="D121" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="L117" s="1" t="n">
-        <f aca="false">J117/16</f>
-        <v>8</v>
-      </c>
-      <c r="M117" s="1" t="n">
-        <f aca="false">J117/32</f>
+      <c r="E121" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F121" s="19"/>
+      <c r="G121" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="I121" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="J121" s="1" t="n">
+        <f aca="false">J120+D120</f>
+        <v>32</v>
+      </c>
+      <c r="K121" s="1" t="n">
+        <f aca="false">J121/8</f>
         <v>4</v>
       </c>
-    </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B118" s="20"/>
-    </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B119" s="20"/>
-    </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B120" s="20"/>
-    </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B121" s="20"/>
+      <c r="L121" s="1" t="n">
+        <f aca="false">J121/16</f>
+        <v>2</v>
+      </c>
+      <c r="M121" s="1" t="n">
+        <f aca="false">J121/32</f>
+        <v>1</v>
+      </c>
+      <c r="N121" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O121" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P121" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q121" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B122" s="23" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C122" s="23" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="D122" s="21" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E122" s="27" t="s">
         <v>25</v>
@@ -7302,26 +6379,27 @@
       <c r="G122" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H122" s="28" t="s">
-        <v>226</v>
+      <c r="H122" s="18" t="s">
+        <v>34</v>
       </c>
       <c r="I122" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="J122" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" s="22" t="n">
+        <v>259</v>
+      </c>
+      <c r="J122" s="1" t="n">
+        <f aca="false">J121+D121</f>
+        <v>48</v>
+      </c>
+      <c r="K122" s="1" t="n">
         <f aca="false">J122/8</f>
-        <v>0</v>
-      </c>
-      <c r="L122" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="L122" s="1" t="n">
         <f aca="false">J122/16</f>
-        <v>0</v>
-      </c>
-      <c r="M122" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M122" s="1" t="n">
         <f aca="false">J122/32</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N122" s="1" t="s">
         <v>44</v>
@@ -7330,7 +6408,7 @@
         <v>1</v>
       </c>
       <c r="P122" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q122" s="1" t="n">
         <v>0</v>
@@ -7338,257 +6416,256 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B123" s="23" t="s">
-        <v>255</v>
+        <v>129</v>
       </c>
       <c r="C123" s="23" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D123" s="21" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E123" s="27" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="F123" s="19"/>
       <c r="G123" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H123" s="28" t="s">
+      <c r="H123" s="18" t="s">
         <v>34</v>
       </c>
       <c r="I123" s="22" t="s">
-        <v>254</v>
+        <v>141</v>
       </c>
       <c r="J123" s="1" t="n">
         <f aca="false">J122+D122</f>
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="K123" s="1" t="n">
         <f aca="false">J123/8</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L123" s="1" t="n">
         <f aca="false">J123/16</f>
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="M123" s="1" t="n">
         <f aca="false">J123/32</f>
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="N123" s="1" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="O123" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P123" s="1" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q123" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B124" s="23" t="s">
-        <v>257</v>
-      </c>
-      <c r="C124" s="23" t="s">
-        <v>258</v>
-      </c>
-      <c r="D124" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="E124" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="F124" s="19"/>
-      <c r="G124" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H124" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I124" s="22" t="s">
-        <v>259</v>
+      <c r="A124" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B124" s="23"/>
+      <c r="I124" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="J124" s="1" t="n">
         <f aca="false">J123+D123</f>
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="K124" s="1" t="n">
         <f aca="false">J124/8</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L124" s="1" t="n">
         <f aca="false">J124/16</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M124" s="1" t="n">
         <f aca="false">J124/32</f>
-        <v>1.5</v>
-      </c>
-      <c r="N124" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="O124" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="J126" s="30"/>
+      <c r="K126" s="22"/>
+      <c r="L126" s="22"/>
+      <c r="M126" s="22"/>
+      <c r="N126" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="127" s="13" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B127" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C127" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D127" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E127" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F127" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G127" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H127" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I127" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="J127" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="K127" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="L127" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="M127" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="N127" s="1"/>
+      <c r="O127" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="P127" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q127" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="128" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B128" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="C128" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="D128" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="E128" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F128" s="33"/>
+      <c r="G128" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H128" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I128" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="J128" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" s="22" t="n">
+        <f aca="false">J128/8</f>
+        <v>0</v>
+      </c>
+      <c r="L128" s="22" t="n">
+        <f aca="false">J128/16</f>
+        <v>0</v>
+      </c>
+      <c r="M128" s="22" t="n">
+        <f aca="false">J128/32</f>
+        <v>0</v>
+      </c>
+      <c r="N128" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="O128" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P128" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="P124" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q124" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B125" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="C125" s="23" t="s">
-        <v>260</v>
-      </c>
-      <c r="D125" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="E125" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="F125" s="19"/>
-      <c r="G125" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H125" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I125" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="J125" s="1" t="n">
-        <f aca="false">J124+D124</f>
-        <v>56</v>
-      </c>
-      <c r="K125" s="1" t="n">
-        <f aca="false">J125/8</f>
-        <v>7</v>
-      </c>
-      <c r="L125" s="1" t="n">
-        <f aca="false">J125/16</f>
-        <v>3.5</v>
-      </c>
-      <c r="M125" s="1" t="n">
-        <f aca="false">J125/32</f>
-        <v>1.75</v>
-      </c>
-      <c r="N125" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O125" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P125" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q125" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B126" s="23"/>
-      <c r="I126" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J126" s="1" t="n">
-        <f aca="false">J125+D125</f>
-        <v>64</v>
-      </c>
-      <c r="K126" s="1" t="n">
-        <f aca="false">J126/8</f>
-        <v>8</v>
-      </c>
-      <c r="L126" s="1" t="n">
-        <f aca="false">J126/16</f>
-        <v>4</v>
-      </c>
-      <c r="M126" s="1" t="n">
-        <f aca="false">J126/32</f>
+      <c r="Q128" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B129" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="C129" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="D129" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E129" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F129" s="33"/>
+      <c r="G129" s="27" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="29" t="s">
-        <v>261</v>
-      </c>
-      <c r="J128" s="30"/>
-      <c r="K128" s="22"/>
-      <c r="L128" s="22"/>
-      <c r="M128" s="22"/>
-      <c r="N128" s="13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="129" s="13" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B129" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C129" s="11" t="s">
+      <c r="H129" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I129" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="J129" s="1" t="n">
+        <f aca="false">J128+D128</f>
         <v>9</v>
       </c>
-      <c r="D129" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E129" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F129" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G129" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H129" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I129" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="J129" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="K129" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="L129" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="M129" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="N129" s="1"/>
-      <c r="O129" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="P129" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q129" s="13" t="s">
-        <v>23</v>
+      <c r="K129" s="1" t="n">
+        <f aca="false">J129/8</f>
+        <v>1.125</v>
+      </c>
+      <c r="L129" s="1" t="n">
+        <f aca="false">J129/16</f>
+        <v>0.5625</v>
+      </c>
+      <c r="M129" s="1" t="n">
+        <f aca="false">J129/32</f>
+        <v>0.28125</v>
+      </c>
+      <c r="N129" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="O129" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P129" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q129" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="130" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B130" s="18" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C130" s="32" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D130" s="1" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E130" s="27" t="s">
         <v>25</v>
@@ -7601,22 +6678,23 @@
         <v>34</v>
       </c>
       <c r="I130" s="27" t="s">
-        <v>264</v>
-      </c>
-      <c r="J130" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" s="22" t="n">
+        <v>269</v>
+      </c>
+      <c r="J130" s="1" t="n">
+        <f aca="false">J129+D129</f>
+        <v>14</v>
+      </c>
+      <c r="K130" s="1" t="n">
         <f aca="false">J130/8</f>
-        <v>0</v>
-      </c>
-      <c r="L130" s="22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L130" s="1" t="n">
         <f aca="false">J130/16</f>
-        <v>0</v>
-      </c>
-      <c r="M130" s="22" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="M130" s="1" t="n">
         <f aca="false">J130/32</f>
-        <v>0</v>
+        <v>0.4375</v>
       </c>
       <c r="N130" s="1" t="s">
         <v>109</v>
@@ -7625,7 +6703,7 @@
         <v>2</v>
       </c>
       <c r="P130" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q130" s="1" t="n">
         <v>0</v>
@@ -7633,13 +6711,13 @@
     </row>
     <row r="131" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B131" s="18" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C131" s="32" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D131" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E131" s="27" t="s">
         <v>25</v>
@@ -7652,23 +6730,23 @@
         <v>34</v>
       </c>
       <c r="I131" s="27" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="J131" s="1" t="n">
         <f aca="false">J130+D130</f>
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K131" s="1" t="n">
         <f aca="false">J131/8</f>
-        <v>1.125</v>
+        <v>2.25</v>
       </c>
       <c r="L131" s="1" t="n">
         <f aca="false">J131/16</f>
-        <v>0.5625</v>
+        <v>1.125</v>
       </c>
       <c r="M131" s="1" t="n">
         <f aca="false">J131/32</f>
-        <v>0.28125</v>
+        <v>0.5625</v>
       </c>
       <c r="N131" s="1" t="s">
         <v>109</v>
@@ -7677,7 +6755,7 @@
         <v>2</v>
       </c>
       <c r="P131" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q131" s="1" t="n">
         <v>0</v>
@@ -7685,42 +6763,42 @@
     </row>
     <row r="132" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B132" s="18" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C132" s="32" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D132" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E132" s="27" t="s">
         <v>25</v>
       </c>
       <c r="F132" s="33"/>
-      <c r="G132" s="27" t="n">
+      <c r="G132" s="18" t="n">
         <v>2</v>
       </c>
       <c r="H132" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I132" s="27" t="s">
-        <v>269</v>
+      <c r="I132" s="18" t="s">
+        <v>275</v>
       </c>
       <c r="J132" s="1" t="n">
         <f aca="false">J131+D131</f>
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K132" s="1" t="n">
         <f aca="false">J132/8</f>
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="L132" s="1" t="n">
         <f aca="false">J132/16</f>
-        <v>0.875</v>
+        <v>1.375</v>
       </c>
       <c r="M132" s="1" t="n">
         <f aca="false">J132/32</f>
-        <v>0.4375</v>
+        <v>0.6875</v>
       </c>
       <c r="N132" s="1" t="s">
         <v>109</v>
@@ -7729,7 +6807,7 @@
         <v>2</v>
       </c>
       <c r="P132" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q132" s="1" t="n">
         <v>0</v>
@@ -7737,42 +6815,42 @@
     </row>
     <row r="133" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B133" s="18" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C133" s="32" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="D133" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E133" s="27" t="s">
         <v>25</v>
       </c>
       <c r="F133" s="33"/>
-      <c r="G133" s="27" t="n">
+      <c r="G133" s="18" t="n">
         <v>2</v>
       </c>
       <c r="H133" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I133" s="27" t="s">
-        <v>272</v>
+      <c r="I133" s="18" t="s">
+        <v>278</v>
       </c>
       <c r="J133" s="1" t="n">
         <f aca="false">J132+D132</f>
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K133" s="1" t="n">
         <f aca="false">J133/8</f>
-        <v>2.25</v>
+        <v>3.125</v>
       </c>
       <c r="L133" s="1" t="n">
         <f aca="false">J133/16</f>
-        <v>1.125</v>
+        <v>1.5625</v>
       </c>
       <c r="M133" s="1" t="n">
         <f aca="false">J133/32</f>
-        <v>0.5625</v>
+        <v>0.78125</v>
       </c>
       <c r="N133" s="1" t="s">
         <v>109</v>
@@ -7781,7 +6859,7 @@
         <v>2</v>
       </c>
       <c r="P133" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q133" s="1" t="n">
         <v>0</v>
@@ -7789,42 +6867,42 @@
     </row>
     <row r="134" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B134" s="18" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C134" s="32" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="D134" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E134" s="27" t="s">
         <v>25</v>
       </c>
       <c r="F134" s="33"/>
       <c r="G134" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H134" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I134" s="18" t="s">
-        <v>275</v>
+      <c r="I134" s="27" t="s">
+        <v>264</v>
       </c>
       <c r="J134" s="1" t="n">
         <f aca="false">J133+D133</f>
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K134" s="1" t="n">
         <f aca="false">J134/8</f>
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="L134" s="1" t="n">
         <f aca="false">J134/16</f>
-        <v>1.375</v>
+        <v>1.625</v>
       </c>
       <c r="M134" s="1" t="n">
         <f aca="false">J134/32</f>
-        <v>0.6875</v>
+        <v>0.8125</v>
       </c>
       <c r="N134" s="1" t="s">
         <v>109</v>
@@ -7833,7 +6911,7 @@
         <v>2</v>
       </c>
       <c r="P134" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q134" s="1" t="n">
         <v>0</v>
@@ -7841,51 +6919,51 @@
     </row>
     <row r="135" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B135" s="18" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C135" s="32" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="D135" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E135" s="27" t="s">
         <v>25</v>
       </c>
       <c r="F135" s="33"/>
       <c r="G135" s="18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H135" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I135" s="18" t="s">
-        <v>278</v>
+      <c r="I135" s="27" t="s">
+        <v>264</v>
       </c>
       <c r="J135" s="1" t="n">
         <f aca="false">J134+D134</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K135" s="1" t="n">
         <f aca="false">J135/8</f>
-        <v>3.125</v>
+        <v>3.375</v>
       </c>
       <c r="L135" s="1" t="n">
         <f aca="false">J135/16</f>
-        <v>1.5625</v>
+        <v>1.6875</v>
       </c>
       <c r="M135" s="1" t="n">
         <f aca="false">J135/32</f>
-        <v>0.78125</v>
+        <v>0.84375</v>
       </c>
       <c r="N135" s="1" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P135" s="1" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q135" s="1" t="n">
         <v>0</v>
@@ -7893,20 +6971,20 @@
     </row>
     <row r="136" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B136" s="18" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C136" s="32" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D136" s="1" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="E136" s="27" t="s">
         <v>25</v>
       </c>
       <c r="F136" s="33"/>
       <c r="G136" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H136" s="27" t="s">
         <v>34</v>
@@ -7916,19 +6994,19 @@
       </c>
       <c r="J136" s="1" t="n">
         <f aca="false">J135+D135</f>
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K136" s="1" t="n">
         <f aca="false">J136/8</f>
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="L136" s="1" t="n">
         <f aca="false">J136/16</f>
-        <v>1.625</v>
+        <v>2</v>
       </c>
       <c r="M136" s="1" t="n">
         <f aca="false">J136/32</f>
-        <v>0.8125</v>
+        <v>1</v>
       </c>
       <c r="N136" s="1" t="s">
         <v>109</v>
@@ -7937,26 +7015,26 @@
         <v>2</v>
       </c>
       <c r="P136" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q136" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="137" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B137" s="18" t="s">
-        <v>281</v>
-      </c>
-      <c r="C137" s="32" t="s">
-        <v>282</v>
+        <v>285</v>
+      </c>
+      <c r="C137" s="18" t="s">
+        <v>286</v>
       </c>
       <c r="D137" s="1" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E137" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="F137" s="33"/>
+        <v>225</v>
+      </c>
+      <c r="F137" s="27"/>
       <c r="G137" s="18" t="n">
         <v>0</v>
       </c>
@@ -7968,39 +7046,39 @@
       </c>
       <c r="J137" s="1" t="n">
         <f aca="false">J136+D136</f>
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="K137" s="1" t="n">
         <f aca="false">J137/8</f>
-        <v>3.375</v>
+        <v>8</v>
       </c>
       <c r="L137" s="1" t="n">
         <f aca="false">J137/16</f>
-        <v>1.6875</v>
+        <v>4</v>
       </c>
       <c r="M137" s="1" t="n">
         <f aca="false">J137/32</f>
-        <v>0.84375</v>
+        <v>2</v>
       </c>
       <c r="N137" s="1" t="s">
-        <v>28</v>
+        <v>287</v>
       </c>
       <c r="O137" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P137" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q137" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="138" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B138" s="18" t="s">
-        <v>283</v>
-      </c>
-      <c r="C138" s="32" t="s">
-        <v>284</v>
+        <v>288</v>
+      </c>
+      <c r="C138" s="18" t="s">
+        <v>289</v>
       </c>
       <c r="D138" s="1" t="n">
         <v>32</v>
@@ -8008,9 +7086,9 @@
       <c r="E138" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="F138" s="33"/>
+      <c r="F138" s="27"/>
       <c r="G138" s="18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H138" s="27" t="s">
         <v>34</v>
@@ -8020,28 +7098,28 @@
       </c>
       <c r="J138" s="1" t="n">
         <f aca="false">J137+D137</f>
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="K138" s="1" t="n">
         <f aca="false">J138/8</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L138" s="1" t="n">
         <f aca="false">J138/16</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M138" s="1" t="n">
         <f aca="false">J138/32</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N138" s="1" t="s">
-        <v>109</v>
+        <v>287</v>
       </c>
       <c r="O138" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P138" s="1" t="n">
         <v>2</v>
-      </c>
-      <c r="P138" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="Q138" s="1" t="n">
         <v>0</v>
@@ -8049,10 +7127,10 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B139" s="18" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C139" s="18" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="D139" s="1" t="n">
         <v>32</v>
@@ -8072,19 +7150,19 @@
       </c>
       <c r="J139" s="1" t="n">
         <f aca="false">J138+D138</f>
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="K139" s="1" t="n">
         <f aca="false">J139/8</f>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L139" s="1" t="n">
         <f aca="false">J139/16</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M139" s="1" t="n">
         <f aca="false">J139/32</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N139" s="1" t="s">
         <v>287</v>
@@ -8093,7 +7171,7 @@
         <v>3</v>
       </c>
       <c r="P139" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q139" s="1" t="n">
         <v>0</v>
@@ -8101,10 +7179,10 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B140" s="18" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C140" s="18" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D140" s="1" t="n">
         <v>32</v>
@@ -8124,19 +7202,19 @@
       </c>
       <c r="J140" s="1" t="n">
         <f aca="false">J139+D139</f>
-        <v>96</v>
+        <v>160</v>
       </c>
       <c r="K140" s="1" t="n">
         <f aca="false">J140/8</f>
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="L140" s="1" t="n">
         <f aca="false">J140/16</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M140" s="1" t="n">
         <f aca="false">J140/32</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N140" s="1" t="s">
         <v>287</v>
@@ -8145,7 +7223,7 @@
         <v>3</v>
       </c>
       <c r="P140" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q140" s="1" t="n">
         <v>0</v>
@@ -8153,16 +7231,16 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B141" s="18" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C141" s="18" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D141" s="1" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E141" s="27" t="s">
-        <v>225</v>
+        <v>25</v>
       </c>
       <c r="F141" s="27"/>
       <c r="G141" s="18" t="n">
@@ -8172,32 +7250,32 @@
         <v>34</v>
       </c>
       <c r="I141" s="27" t="s">
-        <v>264</v>
+        <v>296</v>
       </c>
       <c r="J141" s="1" t="n">
         <f aca="false">J140+D140</f>
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="K141" s="1" t="n">
         <f aca="false">J141/8</f>
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="L141" s="1" t="n">
         <f aca="false">J141/16</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M141" s="1" t="n">
         <f aca="false">J141/32</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N141" s="1" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="O141" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P141" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q141" s="1" t="n">
         <v>0</v>
@@ -8205,13 +7283,13 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B142" s="18" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C142" s="18" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="D142" s="1" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E142" s="27" t="s">
         <v>25</v>
@@ -8224,32 +7302,32 @@
         <v>34</v>
       </c>
       <c r="I142" s="27" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="J142" s="1" t="n">
         <f aca="false">J141+D141</f>
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="K142" s="1" t="n">
         <f aca="false">J142/8</f>
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L142" s="1" t="n">
         <f aca="false">J142/16</f>
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="M142" s="1" t="n">
         <f aca="false">J142/32</f>
+        <v>6.25</v>
+      </c>
+      <c r="N142" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="O142" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="N142" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="O142" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="P142" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q142" s="1" t="n">
         <v>0</v>
@@ -8257,10 +7335,10 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B143" s="18" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="C143" s="18" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="D143" s="1" t="n">
         <v>8</v>
@@ -8276,23 +7354,23 @@
         <v>34</v>
       </c>
       <c r="I143" s="27" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="J143" s="1" t="n">
         <f aca="false">J142+D142</f>
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="K143" s="1" t="n">
         <f aca="false">J143/8</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L143" s="1" t="n">
         <f aca="false">J143/16</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M143" s="1" t="n">
         <f aca="false">J143/32</f>
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="N143" s="1" t="s">
         <v>297</v>
@@ -8301,7 +7379,7 @@
         <v>5</v>
       </c>
       <c r="P143" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q143" s="1" t="n">
         <v>0</v>
@@ -8309,10 +7387,10 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B144" s="18" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C144" s="18" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="D144" s="1" t="n">
         <v>8</v>
@@ -8328,23 +7406,23 @@
         <v>34</v>
       </c>
       <c r="I144" s="27" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="J144" s="1" t="n">
         <f aca="false">J143+D143</f>
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="K144" s="1" t="n">
         <f aca="false">J144/8</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L144" s="1" t="n">
         <f aca="false">J144/16</f>
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="M144" s="1" t="n">
         <f aca="false">J144/32</f>
-        <v>6.25</v>
+        <v>6.75</v>
       </c>
       <c r="N144" s="1" t="s">
         <v>297</v>
@@ -8353,7 +7431,7 @@
         <v>5</v>
       </c>
       <c r="P144" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q144" s="1" t="n">
         <v>0</v>
@@ -8361,10 +7439,10 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B145" s="18" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="C145" s="18" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="D145" s="1" t="n">
         <v>8</v>
@@ -8380,23 +7458,23 @@
         <v>34</v>
       </c>
       <c r="I145" s="27" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="J145" s="1" t="n">
         <f aca="false">J144+D144</f>
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="K145" s="1" t="n">
         <f aca="false">J145/8</f>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L145" s="1" t="n">
         <f aca="false">J145/16</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M145" s="1" t="n">
         <f aca="false">J145/32</f>
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="N145" s="1" t="s">
         <v>297</v>
@@ -8405,7 +7483,7 @@
         <v>5</v>
       </c>
       <c r="P145" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q145" s="1" t="n">
         <v>0</v>
@@ -8413,10 +7491,10 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B146" s="18" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C146" s="18" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="D146" s="1" t="n">
         <v>8</v>
@@ -8431,33 +7509,33 @@
       <c r="H146" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I146" s="27" t="s">
-        <v>306</v>
+      <c r="I146" s="18" t="s">
+        <v>310</v>
       </c>
       <c r="J146" s="1" t="n">
         <f aca="false">J145+D145</f>
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="K146" s="1" t="n">
         <f aca="false">J146/8</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L146" s="1" t="n">
         <f aca="false">J146/16</f>
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="M146" s="1" t="n">
         <f aca="false">J146/32</f>
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="N146" s="1" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="O146" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P146" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q146" s="1" t="n">
         <v>0</v>
@@ -8465,10 +7543,10 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B147" s="18" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C147" s="18" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="D147" s="1" t="n">
         <v>8</v>
@@ -8483,33 +7561,33 @@
       <c r="H147" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I147" s="27" t="s">
-        <v>309</v>
+      <c r="I147" s="18" t="s">
+        <v>313</v>
       </c>
       <c r="J147" s="1" t="n">
         <f aca="false">J146+D146</f>
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="K147" s="1" t="n">
         <f aca="false">J147/8</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L147" s="1" t="n">
         <f aca="false">J147/16</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M147" s="1" t="n">
         <f aca="false">J147/32</f>
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="N147" s="1" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="O147" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P147" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q147" s="1" t="n">
         <v>0</v>
@@ -8517,10 +7595,10 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B148" s="18" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C148" s="18" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D148" s="1" t="n">
         <v>8</v>
@@ -8536,23 +7614,23 @@
         <v>34</v>
       </c>
       <c r="I148" s="18" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="J148" s="1" t="n">
         <f aca="false">J147+D147</f>
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="K148" s="1" t="n">
         <f aca="false">J148/8</f>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L148" s="1" t="n">
         <f aca="false">J148/16</f>
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="M148" s="1" t="n">
         <f aca="false">J148/32</f>
-        <v>7.25</v>
+        <v>7.75</v>
       </c>
       <c r="N148" s="1" t="s">
         <v>312</v>
@@ -8561,7 +7639,7 @@
         <v>4</v>
       </c>
       <c r="P148" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q148" s="1" t="n">
         <v>0</v>
@@ -8569,10 +7647,10 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B149" s="18" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C149" s="18" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D149" s="1" t="n">
         <v>8</v>
@@ -8588,23 +7666,23 @@
         <v>34</v>
       </c>
       <c r="I149" s="18" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="J149" s="1" t="n">
         <f aca="false">J148+D148</f>
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="K149" s="1" t="n">
         <f aca="false">J149/8</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L149" s="1" t="n">
         <f aca="false">J149/16</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M149" s="1" t="n">
         <f aca="false">J149/32</f>
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="N149" s="1" t="s">
         <v>312</v>
@@ -8613,7 +7691,7 @@
         <v>4</v>
       </c>
       <c r="P149" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q149" s="1" t="n">
         <v>0</v>
@@ -8621,10 +7699,10 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B150" s="18" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C150" s="18" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D150" s="1" t="n">
         <v>8</v>
@@ -8640,23 +7718,23 @@
         <v>34</v>
       </c>
       <c r="I150" s="18" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="J150" s="1" t="n">
         <f aca="false">J149+D149</f>
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="K150" s="1" t="n">
         <f aca="false">J150/8</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L150" s="1" t="n">
         <f aca="false">J150/16</f>
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="M150" s="1" t="n">
         <f aca="false">J150/32</f>
-        <v>7.75</v>
+        <v>8.25</v>
       </c>
       <c r="N150" s="1" t="s">
         <v>312</v>
@@ -8665,7 +7743,7 @@
         <v>4</v>
       </c>
       <c r="P150" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q150" s="1" t="n">
         <v>0</v>
@@ -8673,10 +7751,10 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B151" s="18" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C151" s="18" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D151" s="1" t="n">
         <v>8</v>
@@ -8692,23 +7770,23 @@
         <v>34</v>
       </c>
       <c r="I151" s="18" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J151" s="1" t="n">
         <f aca="false">J150+D150</f>
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="K151" s="1" t="n">
         <f aca="false">J151/8</f>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L151" s="1" t="n">
         <f aca="false">J151/16</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M151" s="1" t="n">
         <f aca="false">J151/32</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="N151" s="1" t="s">
         <v>312</v>
@@ -8717,7 +7795,7 @@
         <v>4</v>
       </c>
       <c r="P151" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q151" s="1" t="n">
         <v>0</v>
@@ -8725,10 +7803,10 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B152" s="18" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C152" s="18" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="D152" s="1" t="n">
         <v>8</v>
@@ -8744,23 +7822,23 @@
         <v>34</v>
       </c>
       <c r="I152" s="18" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="J152" s="1" t="n">
         <f aca="false">J151+D151</f>
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="K152" s="1" t="n">
         <f aca="false">J152/8</f>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L152" s="1" t="n">
         <f aca="false">J152/16</f>
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="M152" s="1" t="n">
         <f aca="false">J152/32</f>
-        <v>8.25</v>
+        <v>8.75</v>
       </c>
       <c r="N152" s="1" t="s">
         <v>312</v>
@@ -8769,7 +7847,7 @@
         <v>4</v>
       </c>
       <c r="P152" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q152" s="1" t="n">
         <v>0</v>
@@ -8777,10 +7855,10 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B153" s="18" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C153" s="18" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D153" s="1" t="n">
         <v>8</v>
@@ -8796,32 +7874,32 @@
         <v>34</v>
       </c>
       <c r="I153" s="18" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="J153" s="1" t="n">
         <f aca="false">J152+D152</f>
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="K153" s="1" t="n">
         <f aca="false">J153/8</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L153" s="1" t="n">
         <f aca="false">J153/16</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M153" s="1" t="n">
         <f aca="false">J153/32</f>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="N153" s="1" t="s">
-        <v>312</v>
+        <v>287</v>
       </c>
       <c r="O153" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P153" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q153" s="1" t="n">
         <v>0</v>
@@ -8829,10 +7907,10 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B154" s="18" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C154" s="18" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D154" s="1" t="n">
         <v>8</v>
@@ -8848,32 +7926,32 @@
         <v>34</v>
       </c>
       <c r="I154" s="18" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="J154" s="1" t="n">
         <f aca="false">J153+D153</f>
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="K154" s="1" t="n">
         <f aca="false">J154/8</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L154" s="1" t="n">
         <f aca="false">J154/16</f>
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="M154" s="1" t="n">
         <f aca="false">J154/32</f>
-        <v>8.75</v>
+        <v>9.25</v>
       </c>
       <c r="N154" s="1" t="s">
-        <v>312</v>
+        <v>287</v>
       </c>
       <c r="O154" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P154" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q154" s="1" t="n">
         <v>0</v>
@@ -8881,10 +7959,10 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B155" s="18" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C155" s="18" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D155" s="1" t="n">
         <v>8</v>
@@ -8900,23 +7978,23 @@
         <v>34</v>
       </c>
       <c r="I155" s="18" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="J155" s="1" t="n">
         <f aca="false">J154+D154</f>
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="K155" s="1" t="n">
         <f aca="false">J155/8</f>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L155" s="1" t="n">
         <f aca="false">J155/16</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M155" s="1" t="n">
         <f aca="false">J155/32</f>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="N155" s="1" t="s">
         <v>287</v>
@@ -8925,7 +8003,7 @@
         <v>3</v>
       </c>
       <c r="P155" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q155" s="1" t="n">
         <v>0</v>
@@ -8933,10 +8011,10 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B156" s="18" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C156" s="18" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D156" s="1" t="n">
         <v>8</v>
@@ -8952,23 +8030,23 @@
         <v>34</v>
       </c>
       <c r="I156" s="18" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="J156" s="1" t="n">
         <f aca="false">J155+D155</f>
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="K156" s="1" t="n">
         <f aca="false">J156/8</f>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L156" s="1" t="n">
         <f aca="false">J156/16</f>
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="M156" s="1" t="n">
         <f aca="false">J156/32</f>
-        <v>9.25</v>
+        <v>9.75</v>
       </c>
       <c r="N156" s="1" t="s">
         <v>287</v>
@@ -8977,7 +8055,7 @@
         <v>3</v>
       </c>
       <c r="P156" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q156" s="1" t="n">
         <v>0</v>
@@ -8985,10 +8063,10 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B157" s="18" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C157" s="18" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D157" s="1" t="n">
         <v>8</v>
@@ -9004,23 +8082,23 @@
         <v>34</v>
       </c>
       <c r="I157" s="18" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="J157" s="1" t="n">
         <f aca="false">J156+D156</f>
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="K157" s="1" t="n">
         <f aca="false">J157/8</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L157" s="1" t="n">
         <f aca="false">J157/16</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M157" s="1" t="n">
         <f aca="false">J157/32</f>
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="N157" s="1" t="s">
         <v>287</v>
@@ -9029,7 +8107,7 @@
         <v>3</v>
       </c>
       <c r="P157" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q157" s="1" t="n">
         <v>0</v>
@@ -9037,10 +8115,10 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B158" s="18" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C158" s="18" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D158" s="1" t="n">
         <v>8</v>
@@ -9056,23 +8134,23 @@
         <v>34</v>
       </c>
       <c r="I158" s="18" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="J158" s="1" t="n">
         <f aca="false">J157+D157</f>
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="K158" s="1" t="n">
         <f aca="false">J158/8</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L158" s="1" t="n">
         <f aca="false">J158/16</f>
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
       <c r="M158" s="1" t="n">
         <f aca="false">J158/32</f>
-        <v>9.75</v>
+        <v>10.25</v>
       </c>
       <c r="N158" s="1" t="s">
         <v>287</v>
@@ -9081,7 +8159,7 @@
         <v>3</v>
       </c>
       <c r="P158" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q158" s="1" t="n">
         <v>0</v>
@@ -9089,10 +8167,10 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B159" s="18" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C159" s="18" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D159" s="1" t="n">
         <v>8</v>
@@ -9108,29 +8186,29 @@
         <v>34</v>
       </c>
       <c r="I159" s="18" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="J159" s="1" t="n">
         <f aca="false">J158+D158</f>
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="K159" s="1" t="n">
         <f aca="false">J159/8</f>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L159" s="1" t="n">
         <f aca="false">J159/16</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M159" s="1" t="n">
         <f aca="false">J159/32</f>
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="N159" s="1" t="s">
-        <v>287</v>
+        <v>109</v>
       </c>
       <c r="O159" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P159" s="1" t="n">
         <v>9</v>
@@ -9141,10 +8219,10 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B160" s="18" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C160" s="18" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D160" s="1" t="n">
         <v>8</v>
@@ -9160,29 +8238,29 @@
         <v>34</v>
       </c>
       <c r="I160" s="18" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="J160" s="1" t="n">
         <f aca="false">J159+D159</f>
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="K160" s="1" t="n">
         <f aca="false">J160/8</f>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L160" s="1" t="n">
         <f aca="false">J160/16</f>
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="M160" s="1" t="n">
         <f aca="false">J160/32</f>
-        <v>10.25</v>
+        <v>10.75</v>
       </c>
       <c r="N160" s="1" t="s">
-        <v>287</v>
+        <v>109</v>
       </c>
       <c r="O160" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P160" s="1" t="n">
         <v>10</v>
@@ -9193,10 +8271,10 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B161" s="18" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C161" s="18" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D161" s="1" t="n">
         <v>8</v>
@@ -9212,32 +8290,32 @@
         <v>34</v>
       </c>
       <c r="I161" s="18" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="J161" s="1" t="n">
         <f aca="false">J160+D160</f>
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="K161" s="1" t="n">
         <f aca="false">J161/8</f>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L161" s="1" t="n">
         <f aca="false">J161/16</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M161" s="1" t="n">
         <f aca="false">J161/32</f>
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="N161" s="1" t="s">
-        <v>109</v>
+        <v>287</v>
       </c>
       <c r="O161" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P161" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q161" s="1" t="n">
         <v>0</v>
@@ -9245,10 +8323,10 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B162" s="18" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C162" s="18" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D162" s="1" t="n">
         <v>8</v>
@@ -9264,32 +8342,32 @@
         <v>34</v>
       </c>
       <c r="I162" s="18" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J162" s="1" t="n">
         <f aca="false">J161+D161</f>
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="K162" s="1" t="n">
         <f aca="false">J162/8</f>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L162" s="1" t="n">
         <f aca="false">J162/16</f>
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="M162" s="1" t="n">
         <f aca="false">J162/32</f>
-        <v>10.75</v>
+        <v>11.25</v>
       </c>
       <c r="N162" s="1" t="s">
-        <v>109</v>
+        <v>287</v>
       </c>
       <c r="O162" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P162" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q162" s="1" t="n">
         <v>0</v>
@@ -9297,10 +8375,10 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B163" s="18" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C163" s="18" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D163" s="1" t="n">
         <v>8</v>
@@ -9316,23 +8394,23 @@
         <v>34</v>
       </c>
       <c r="I163" s="18" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="J163" s="1" t="n">
         <f aca="false">J162+D162</f>
-        <v>352</v>
+        <v>368</v>
       </c>
       <c r="K163" s="1" t="n">
         <f aca="false">J163/8</f>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L163" s="1" t="n">
         <f aca="false">J163/16</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M163" s="1" t="n">
         <f aca="false">J163/32</f>
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="N163" s="1" t="s">
         <v>287</v>
@@ -9341,7 +8419,7 @@
         <v>3</v>
       </c>
       <c r="P163" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q163" s="1" t="n">
         <v>0</v>
@@ -9349,10 +8427,10 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B164" s="18" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C164" s="18" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D164" s="1" t="n">
         <v>8</v>
@@ -9368,23 +8446,23 @@
         <v>34</v>
       </c>
       <c r="I164" s="18" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="J164" s="1" t="n">
         <f aca="false">J163+D163</f>
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="K164" s="1" t="n">
         <f aca="false">J164/8</f>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L164" s="1" t="n">
         <f aca="false">J164/16</f>
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
       <c r="M164" s="1" t="n">
         <f aca="false">J164/32</f>
-        <v>11.25</v>
+        <v>11.75</v>
       </c>
       <c r="N164" s="1" t="s">
         <v>287</v>
@@ -9393,7 +8471,7 @@
         <v>3</v>
       </c>
       <c r="P164" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q164" s="1" t="n">
         <v>0</v>
@@ -9401,10 +8479,10 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B165" s="18" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C165" s="18" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D165" s="1" t="n">
         <v>8</v>
@@ -9420,23 +8498,23 @@
         <v>34</v>
       </c>
       <c r="I165" s="18" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="J165" s="1" t="n">
         <f aca="false">J164+D164</f>
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="K165" s="1" t="n">
         <f aca="false">J165/8</f>
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L165" s="1" t="n">
         <f aca="false">J165/16</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M165" s="1" t="n">
         <f aca="false">J165/32</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="N165" s="1" t="s">
         <v>287</v>
@@ -9445,7 +8523,7 @@
         <v>3</v>
       </c>
       <c r="P165" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q165" s="1" t="n">
         <v>0</v>
@@ -9453,10 +8531,10 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B166" s="18" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C166" s="18" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D166" s="1" t="n">
         <v>8</v>
@@ -9472,32 +8550,32 @@
         <v>34</v>
       </c>
       <c r="I166" s="18" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="J166" s="1" t="n">
         <f aca="false">J165+D165</f>
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="K166" s="1" t="n">
         <f aca="false">J166/8</f>
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L166" s="1" t="n">
         <f aca="false">J166/16</f>
-        <v>23.5</v>
+        <v>24.5</v>
       </c>
       <c r="M166" s="1" t="n">
         <f aca="false">J166/32</f>
-        <v>11.75</v>
+        <v>12.25</v>
       </c>
       <c r="N166" s="1" t="s">
-        <v>287</v>
+        <v>109</v>
       </c>
       <c r="O166" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P166" s="1" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q166" s="1" t="n">
         <v>0</v>
@@ -9505,10 +8583,10 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B167" s="18" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C167" s="18" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D167" s="1" t="n">
         <v>8</v>
@@ -9524,32 +8602,32 @@
         <v>34</v>
       </c>
       <c r="I167" s="18" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="J167" s="1" t="n">
         <f aca="false">J166+D166</f>
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="K167" s="1" t="n">
         <f aca="false">J167/8</f>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L167" s="1" t="n">
         <f aca="false">J167/16</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M167" s="1" t="n">
         <f aca="false">J167/32</f>
+        <v>12.5</v>
+      </c>
+      <c r="N167" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="O167" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P167" s="1" t="n">
         <v>12</v>
-      </c>
-      <c r="N167" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="O167" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="P167" s="1" t="n">
-        <v>15</v>
       </c>
       <c r="Q167" s="1" t="n">
         <v>0</v>
@@ -9557,10 +8635,10 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B168" s="18" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C168" s="18" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D168" s="1" t="n">
         <v>8</v>
@@ -9576,23 +8654,23 @@
         <v>34</v>
       </c>
       <c r="I168" s="18" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="J168" s="1" t="n">
         <f aca="false">J167+D167</f>
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="K168" s="1" t="n">
         <f aca="false">J168/8</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L168" s="1" t="n">
         <f aca="false">J168/16</f>
-        <v>24.5</v>
+        <v>25.5</v>
       </c>
       <c r="M168" s="1" t="n">
         <f aca="false">J168/32</f>
-        <v>12.25</v>
+        <v>12.75</v>
       </c>
       <c r="N168" s="1" t="s">
         <v>109</v>
@@ -9601,50 +8679,52 @@
         <v>2</v>
       </c>
       <c r="P168" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q168" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B169" s="18" t="s">
-        <v>353</v>
-      </c>
-      <c r="C169" s="18" t="s">
-        <v>354</v>
+      <c r="B169" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>358</v>
       </c>
       <c r="D169" s="1" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E169" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="F169" s="27"/>
+      <c r="F169" s="27" t="s">
+        <v>65</v>
+      </c>
       <c r="G169" s="18" t="n">
         <v>0</v>
       </c>
       <c r="H169" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I169" s="18" t="s">
-        <v>353</v>
+      <c r="I169" s="3" t="s">
+        <v>357</v>
       </c>
       <c r="J169" s="1" t="n">
         <f aca="false">J168+D168</f>
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="K169" s="1" t="n">
         <f aca="false">J169/8</f>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L169" s="1" t="n">
         <f aca="false">J169/16</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M169" s="1" t="n">
         <f aca="false">J169/32</f>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="N169" s="1" t="s">
         <v>109</v>
@@ -9653,7 +8733,7 @@
         <v>2</v>
       </c>
       <c r="P169" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q169" s="1" t="n">
         <v>0</v>
@@ -9661,10 +8741,10 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B170" s="18" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C170" s="18" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="D170" s="1" t="n">
         <v>8</v>
@@ -9674,29 +8754,29 @@
       </c>
       <c r="F170" s="27"/>
       <c r="G170" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H170" s="27" t="s">
         <v>34</v>
       </c>
       <c r="I170" s="18" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J170" s="1" t="n">
         <f aca="false">J169+D169</f>
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="K170" s="1" t="n">
         <f aca="false">J170/8</f>
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L170" s="1" t="n">
         <f aca="false">J170/16</f>
-        <v>25.5</v>
+        <v>27</v>
       </c>
       <c r="M170" s="1" t="n">
         <f aca="false">J170/32</f>
-        <v>12.75</v>
+        <v>13.5</v>
       </c>
       <c r="N170" s="1" t="s">
         <v>109</v>
@@ -9705,52 +8785,50 @@
         <v>2</v>
       </c>
       <c r="P170" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q170" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B171" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="C171" s="3" t="s">
-        <v>358</v>
+      <c r="B171" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="C171" s="18" t="s">
+        <v>362</v>
       </c>
       <c r="D171" s="1" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E171" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="F171" s="27" t="s">
-        <v>65</v>
-      </c>
+      <c r="F171" s="27"/>
       <c r="G171" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H171" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I171" s="3" t="s">
-        <v>357</v>
+      <c r="I171" s="18" t="s">
+        <v>363</v>
       </c>
       <c r="J171" s="1" t="n">
         <f aca="false">J170+D170</f>
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="K171" s="1" t="n">
         <f aca="false">J171/8</f>
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L171" s="1" t="n">
         <f aca="false">J171/16</f>
-        <v>26</v>
+        <v>27.5</v>
       </c>
       <c r="M171" s="1" t="n">
         <f aca="false">J171/32</f>
-        <v>13</v>
+        <v>13.75</v>
       </c>
       <c r="N171" s="1" t="s">
         <v>109</v>
@@ -9759,7 +8837,7 @@
         <v>2</v>
       </c>
       <c r="P171" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q171" s="1" t="n">
         <v>0</v>
@@ -9767,10 +8845,10 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B172" s="18" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C172" s="18" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="D172" s="1" t="n">
         <v>8</v>
@@ -9786,23 +8864,23 @@
         <v>34</v>
       </c>
       <c r="I172" s="18" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="J172" s="1" t="n">
         <f aca="false">J171+D171</f>
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="K172" s="1" t="n">
         <f aca="false">J172/8</f>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L172" s="1" t="n">
         <f aca="false">J172/16</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M172" s="1" t="n">
         <f aca="false">J172/32</f>
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="N172" s="1" t="s">
         <v>109</v>
@@ -9811,196 +8889,94 @@
         <v>2</v>
       </c>
       <c r="P172" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q172" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B173" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="C173" s="18" t="s">
-        <v>362</v>
+      <c r="B173" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>368</v>
       </c>
       <c r="D173" s="1" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E173" s="27" t="s">
-        <v>25</v>
+        <v>369</v>
       </c>
       <c r="F173" s="27"/>
       <c r="G173" s="18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H173" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I173" s="18" t="s">
-        <v>363</v>
+      <c r="I173" s="27" t="s">
+        <v>264</v>
       </c>
       <c r="J173" s="1" t="n">
         <f aca="false">J172+D172</f>
-        <v>440</v>
+        <v>456</v>
       </c>
       <c r="K173" s="1" t="n">
         <f aca="false">J173/8</f>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L173" s="1" t="n">
         <f aca="false">J173/16</f>
-        <v>27.5</v>
+        <v>28.5</v>
       </c>
       <c r="M173" s="1" t="n">
         <f aca="false">J173/32</f>
-        <v>13.75</v>
+        <v>14.25</v>
       </c>
       <c r="N173" s="1" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="O173" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P173" s="1" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q173" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B174" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="C174" s="18" t="s">
-        <v>365</v>
-      </c>
-      <c r="D174" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E174" s="27" t="s">
-        <v>25</v>
+      <c r="A174" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="F174" s="27"/>
-      <c r="G174" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H174" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="I174" s="18" t="s">
-        <v>366</v>
-      </c>
+      <c r="G174" s="27"/>
+      <c r="H174" s="27"/>
+      <c r="I174" s="27"/>
       <c r="J174" s="1" t="n">
         <f aca="false">J173+D173</f>
-        <v>448</v>
+        <v>480</v>
       </c>
       <c r="K174" s="1" t="n">
         <f aca="false">J174/8</f>
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L174" s="1" t="n">
         <f aca="false">J174/16</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M174" s="1" t="n">
         <f aca="false">J174/32</f>
-        <v>14</v>
-      </c>
-      <c r="N174" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="O174" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P174" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q174" s="1" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B175" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="C175" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="D175" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E175" s="27" t="s">
-        <v>369</v>
-      </c>
-      <c r="F175" s="27"/>
-      <c r="G175" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H175" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="I175" s="27" t="s">
-        <v>264</v>
-      </c>
-      <c r="J175" s="1" t="n">
-        <f aca="false">J174+D174</f>
-        <v>456</v>
-      </c>
-      <c r="K175" s="1" t="n">
-        <f aca="false">J175/8</f>
-        <v>57</v>
-      </c>
-      <c r="L175" s="1" t="n">
-        <f aca="false">J175/16</f>
-        <v>28.5</v>
-      </c>
-      <c r="M175" s="1" t="n">
-        <f aca="false">J175/32</f>
-        <v>14.25</v>
-      </c>
-      <c r="N175" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O175" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P175" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q175" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F176" s="27"/>
-      <c r="G176" s="27"/>
-      <c r="H176" s="27"/>
-      <c r="I176" s="27"/>
-      <c r="J176" s="1" t="n">
-        <f aca="false">J175+D175</f>
-        <v>480</v>
-      </c>
-      <c r="K176" s="1" t="n">
-        <f aca="false">J176/8</f>
-        <v>60</v>
-      </c>
-      <c r="L176" s="1" t="n">
-        <f aca="false">J176/16</f>
-        <v>30</v>
-      </c>
-      <c r="M176" s="1" t="n">
-        <f aca="false">J176/32</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B177" s="1"/>
-    </row>
+      <c r="B175" s="1"/>
+    </row>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="7">
@@ -10013,7 +8989,7 @@
     <mergeCell ref="B50:I50"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A128" r:id="rId1" display="Structure:rt1Errors_t,file:rt1ErrorsDownlink.h"/>
+    <hyperlink ref="A126" r:id="rId1" display="Structure:rt1Errors_t,file:rt1ErrorsDownlink.h"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -10031,7 +9007,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B6:I20"/>
-  <sheetFormatPr defaultColWidth="9.3359375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.34375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.14"/>

--- a/TelemDefinition/DownlinkSpecPacsat.xlsx
+++ b/TelemDefinition/DownlinkSpecPacsat.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="380">
   <si>
     <t xml:space="preserve">//</t>
   </si>
@@ -230,6 +230,384 @@
     <t xml:space="preserve">Radio</t>
   </si>
   <si>
+    <t xml:space="preserve">RSSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX0RSSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dBm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSSI for Receiver 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receiver 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX1RSSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSSI for Receiver 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receiver 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX2RSSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSSI for receiver 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receiver 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX3RSSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSSI for receiver 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receiver 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPU Temp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IHUTemp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA Temp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATemp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power Amplifier Temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power Temp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PowerTemp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power Supply Temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3V3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VoltageVal3v3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voltage of the 3V3 rail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VoltageVal5v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voltage of the 5V rail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1V2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VoltageVal1v2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voltage of the 1V2 rail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VoltageValBattery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voltage of the battery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Totals:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commonPayload2 is common to realtime,  hi/low, and WOD,  but it is not compared for hi/low.  It is fetched fresh.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structure: commonRtWodPayload_t,file:common2Downlink.h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ifdef LEGACY_IHU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power Radios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PowerFlagAx5043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radio Power is enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pad155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pad202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto Safe Allowed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AutoSafeAllowed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autosafe Allowed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto Safe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AutoSafeModeActive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autosafe Mode Active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PB Enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pbEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pacsat Broadcast is available for use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uplink Enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uplinkEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pacsat file upload is available for use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digi Enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DigiEnabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Packet Digipeater is enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power 5V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PowerFlag5V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5V Power is enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power LNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PowerFlagLNA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LNA is power is enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power SSPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PowerFlagSSPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSPA Power is enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">endif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ifdef RTIHU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LogLevel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The current logging level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time Period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TimePeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The period between time packets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telem Period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TelemPeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The period between telemetry packets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WOD Period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WodPeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The time between WOD saves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max WOD Size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxWodFileSize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The maximum size of a WOD file before it is added to the directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max EXP Size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxExpFileSize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The maximum size of a experiment file before it is added to the directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PB Status Period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PbStatusPeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The period between Pacsat Broadcast Status packets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PB Timeout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PbTimeout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The maximum time a client can be on the PB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uplink Status Period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UplinkStatusPeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The period between uplink status packets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SW Cmd Cnt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">swCmdCnt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of software commands since last reset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min/Max Resets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLMresets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of times command stations reset stored telemetry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pad203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fill to align to 32 bits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cmd Ring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">swCmds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Command Ring showing last 4 commands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRAM0 Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRAMstatus0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status of MRAM0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRAM1 Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRAMstatus1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status of MRAM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRAM2 Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRAMstatus2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status of MRAM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRAM3 Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRAMstatus3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status of MRAM3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pwr Mode</t>
   </si>
   <si>
@@ -254,36 +632,24 @@
     <t xml:space="preserve">RX0 Power Mode</t>
   </si>
   <si>
-    <t xml:space="preserve">Receiver 1</t>
-  </si>
-  <si>
     <t xml:space="preserve">RX1PwrMode</t>
   </si>
   <si>
     <t xml:space="preserve">RX1Power Mode</t>
   </si>
   <si>
-    <t xml:space="preserve">Receiver 2</t>
-  </si>
-  <si>
     <t xml:space="preserve">RX2PwrMode</t>
   </si>
   <si>
     <t xml:space="preserve">RX2 Power Mode</t>
   </si>
   <si>
-    <t xml:space="preserve">Receiver 3</t>
-  </si>
-  <si>
     <t xml:space="preserve">RX3PwrMode</t>
   </si>
   <si>
     <t xml:space="preserve">RX3 Power Mode</t>
   </si>
   <si>
-    <t xml:space="preserve">Receiver 4</t>
-  </si>
-  <si>
     <t xml:space="preserve">RX0ModMode</t>
   </si>
   <si>
@@ -308,376 +674,22 @@
     <t xml:space="preserve">RX3 Modulation</t>
   </si>
   <si>
-    <t xml:space="preserve">RSSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RX0RSSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dBm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RSSI for Receiver 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RX1RSSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RSSI for Receiver 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RX2RSSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RSSI for receiver 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RX3RSSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RSSI for receiver 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPU Temp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHUTemp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer temperature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA Temp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PATemp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power Amplifier Temperature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power Temp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PowerTemp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power Supply Temperature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3V3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VoltageVal3v3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voltage of the 3V3 rail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VoltageVal5v</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voltage of the 5V rail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1V2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VoltageVal1v2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voltage of the 1V2 rail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Battery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VoltageValBattery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voltage of the battery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pad0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fill to 32 bits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Totals:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commonPayload2 is common to realtime,  hi/low, and WOD,  but it is not compared for hi/low.  It is fetched fresh.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Structure: commonRtWodPayload_t,file:common2Downlink.h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ifdef LEGACY_IHU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power Radios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PowerFlagAx5043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radio Power is enabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pad155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pad202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto Safe Allowed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AutoSafeAllowed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autosafe Allowed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto Safe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AutoSafeModeActive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autosafe Mode Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PB Enabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pbEnabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pacsat Broadcast is available for use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uplink Enabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uplinkEnabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pacsat file upload is available for use</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digi Enabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DigiEnabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Packet Digipeater is enabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power 5V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PowerFlag5V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5V Power is enabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power LNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PowerFlagLNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LNA is power is enabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Power SSPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PowerFlagSSPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSPA Power is enabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">endif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ifdef RTIHU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LogLevel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The current logging level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time Period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TimePeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The period between time packets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Telem Period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TelemPeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The period between telemetry packets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WOD Period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WodPeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The time between WOD saves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max WOD Size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxWodFileSize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The maximum size of a WOD file before it is added to the directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max EXP Size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxExpFileSize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The maximum size of a experiment file before it is added to the directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PB Status Period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PbStatusPeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The period between Pacsat Broadcast Status packets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PB Timeout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PbTimeout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The maximum time a client can be on the PB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uplink Status Period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UplinkStatusPeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The period between uplink status packets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SW Cmd Cnt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">swCmdCnt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of software commands since last reset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Min/Max Resets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLMresets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of times command stations reset stored telemetry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pad203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fill to align to 32 bits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cmd Ring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">swCmds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Command Ring showing last 4 commands</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRAM0 Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRAMstatus0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status of MRAM0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRAM1 Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRAMstatus1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status of MRAM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRAM2 Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRAMstatus2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status of MRAM2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRAM3 Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRAMstatus3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status of MRAM3</t>
+    <t xml:space="preserve">Into AutoSafe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IntoAutoSafe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The voltage threshold to decide if the spacecraft automatically enters safe mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outof AutoSafe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OutofAutoSafe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The voltage threshold to decide if the spacecraft automatically exits safe mode</t>
   </si>
   <si>
     <t xml:space="preserve">Total Length</t>
@@ -2320,17 +2332,17 @@
         <v>8</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="F26" s="19"/>
       <c r="G26" s="18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="I26" s="19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J26" s="1" t="n">
         <f aca="false">J25+D25</f>
@@ -2349,13 +2361,13 @@
         <v>2.25</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q26" s="1" t="n">
         <v>0</v>
@@ -2363,26 +2375,26 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="23" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D27" s="23" t="n">
         <v>8</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="F27" s="19"/>
       <c r="G27" s="18" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="I27" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J27" s="1" t="n">
         <f aca="false">J26+D26</f>
@@ -2401,13 +2413,13 @@
         <v>2.5</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q27" s="1" t="n">
         <v>0</v>
@@ -2418,7 +2430,7 @@
         <v>69</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D28" s="23" t="n">
         <v>8</v>
@@ -2428,13 +2440,13 @@
       </c>
       <c r="F28" s="19"/>
       <c r="G28" s="18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="I28" s="19" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J28" s="1" t="n">
         <f aca="false">J27+D27</f>
@@ -2453,13 +2465,13 @@
         <v>2.75</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q28" s="1" t="n">
         <v>0</v>
@@ -2470,7 +2482,7 @@
         <v>69</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D29" s="23" t="n">
         <v>8</v>
@@ -2480,13 +2492,13 @@
       </c>
       <c r="F29" s="19"/>
       <c r="G29" s="18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="I29" s="19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J29" s="1" t="n">
         <f aca="false">J28+D28</f>
@@ -2505,13 +2517,13 @@
         <v>3</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q29" s="1" t="n">
         <v>0</v>
@@ -2519,10 +2531,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="23" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D30" s="23" t="n">
         <v>8</v>
@@ -2532,13 +2544,13 @@
       </c>
       <c r="F30" s="19"/>
       <c r="G30" s="18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="I30" s="19" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="J30" s="1" t="n">
         <f aca="false">J29+D29</f>
@@ -2557,10 +2569,10 @@
         <v>3.25</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P30" s="1" t="n">
         <v>1</v>
@@ -2571,10 +2583,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="23" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D31" s="23" t="n">
         <v>8</v>
@@ -2584,13 +2596,13 @@
       </c>
       <c r="F31" s="19"/>
       <c r="G31" s="18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="I31" s="19" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J31" s="1" t="n">
         <f aca="false">J30+D30</f>
@@ -2609,13 +2621,13 @@
         <v>3.5</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q31" s="1" t="n">
         <v>0</v>
@@ -2623,10 +2635,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="23" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D32" s="23" t="n">
         <v>8</v>
@@ -2636,13 +2648,13 @@
       </c>
       <c r="F32" s="19"/>
       <c r="G32" s="18" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J32" s="1" t="n">
         <f aca="false">J31+D31</f>
@@ -2661,13 +2673,13 @@
         <v>3.75</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q32" s="1" t="n">
         <v>0</v>
@@ -2675,26 +2687,26 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="23" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D33" s="23" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E33" s="19" t="s">
         <v>25</v>
       </c>
       <c r="F33" s="19"/>
       <c r="G33" s="18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="I33" s="19" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="J33" s="1" t="n">
         <f aca="false">J32+D32</f>
@@ -2713,13 +2725,13 @@
         <v>4</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Q33" s="1" t="n">
         <v>0</v>
@@ -2727,51 +2739,51 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="23" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D34" s="23" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E34" s="19" t="s">
         <v>25</v>
       </c>
       <c r="F34" s="19"/>
       <c r="G34" s="18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H34" s="18" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="I34" s="19" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="J34" s="1" t="n">
         <f aca="false">J33+D33</f>
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="K34" s="1" t="n">
         <f aca="false">J34/8</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L34" s="1" t="n">
         <f aca="false">J34/16</f>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="M34" s="1" t="n">
         <f aca="false">J34/32</f>
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q34" s="1" t="n">
         <v>0</v>
@@ -2779,51 +2791,51 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="23" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="D35" s="23" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E35" s="19" t="s">
         <v>25</v>
       </c>
       <c r="F35" s="19"/>
       <c r="G35" s="18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="I35" s="19" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="J35" s="1" t="n">
         <f aca="false">J34+D34</f>
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="K35" s="1" t="n">
         <f aca="false">J35/8</f>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L35" s="1" t="n">
         <f aca="false">J35/16</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M35" s="1" t="n">
         <f aca="false">J35/32</f>
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Q35" s="1" t="n">
         <v>0</v>
@@ -2831,415 +2843,249 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="23" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D36" s="23" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E36" s="19" t="s">
         <v>25</v>
       </c>
       <c r="F36" s="19"/>
       <c r="G36" s="18" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I36" s="19" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="J36" s="1" t="n">
         <f aca="false">J35+D35</f>
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="K36" s="1" t="n">
         <f aca="false">J36/8</f>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L36" s="1" t="n">
         <f aca="false">J36/16</f>
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="M36" s="1" t="n">
         <f aca="false">J36/32</f>
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q36" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="C37" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="D37" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E37" s="19" t="s">
-        <v>25</v>
-      </c>
+      <c r="A37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="19"/>
       <c r="F37" s="19"/>
-      <c r="G37" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="H37" s="18" t="s">
-        <v>97</v>
-      </c>
+      <c r="G37" s="19"/>
+      <c r="H37" s="18"/>
       <c r="I37" s="19" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="J37" s="1" t="n">
         <f aca="false">J36+D36</f>
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="K37" s="1" t="n">
         <f aca="false">J37/8</f>
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L37" s="1" t="n">
         <f aca="false">J37/16</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M37" s="1" t="n">
         <f aca="false">J37/32</f>
-        <v>5</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="O37" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q37" s="1" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="C38" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="D38" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E38" s="19" t="s">
-        <v>25</v>
-      </c>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="19"/>
       <c r="F38" s="19"/>
-      <c r="G38" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="H38" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="I38" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="J38" s="1" t="n">
-        <f aca="false">J37+D37</f>
-        <v>168</v>
-      </c>
-      <c r="K38" s="1" t="n">
-        <f aca="false">J38/8</f>
-        <v>21</v>
-      </c>
-      <c r="L38" s="1" t="n">
-        <f aca="false">J38/16</f>
-        <v>10.5</v>
-      </c>
-      <c r="M38" s="1" t="n">
-        <f aca="false">J38/32</f>
-        <v>5.25</v>
-      </c>
-      <c r="N38" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="O38" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="P38" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="C39" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="D39" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E39" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F39" s="19"/>
-      <c r="G39" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="H39" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="I39" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="J39" s="1" t="n">
-        <f aca="false">J38+D38</f>
-        <v>176</v>
-      </c>
-      <c r="K39" s="1" t="n">
-        <f aca="false">J39/8</f>
-        <v>22</v>
-      </c>
-      <c r="L39" s="1" t="n">
-        <f aca="false">J39/16</f>
-        <v>11</v>
-      </c>
-      <c r="M39" s="1" t="n">
-        <f aca="false">J39/32</f>
-        <v>5.5</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="P39" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q39" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="22"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="C40" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="D40" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E40" s="19" t="s">
-        <v>25</v>
-      </c>
+      <c r="A40" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="19"/>
       <c r="F40" s="19"/>
-      <c r="G40" s="18" t="n">
-        <v>9</v>
-      </c>
-      <c r="H40" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="I40" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="J40" s="1" t="n">
-        <f aca="false">J39+D39</f>
-        <v>184</v>
-      </c>
-      <c r="K40" s="1" t="n">
-        <f aca="false">J40/8</f>
-        <v>23</v>
-      </c>
-      <c r="L40" s="1" t="n">
-        <f aca="false">J40/16</f>
-        <v>11.5</v>
-      </c>
-      <c r="M40" s="1" t="n">
-        <f aca="false">J40/32</f>
-        <v>5.75</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="O40" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P40" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q40" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="22"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
+      <c r="M40" s="22"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="23" t="s">
+      <c r="A41" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C41" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="D41" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E41" s="19" t="s">
-        <v>25</v>
-      </c>
+      <c r="B41" s="23"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="19"/>
       <c r="F41" s="19"/>
-      <c r="G41" s="18" t="n">
-        <v>9</v>
-      </c>
-      <c r="H41" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="I41" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="J41" s="1" t="n">
-        <f aca="false">J40+D40</f>
-        <v>192</v>
-      </c>
-      <c r="K41" s="1" t="n">
-        <f aca="false">J41/8</f>
-        <v>24</v>
-      </c>
-      <c r="L41" s="1" t="n">
-        <f aca="false">J41/16</f>
-        <v>12</v>
-      </c>
-      <c r="M41" s="1" t="n">
-        <f aca="false">J41/32</f>
-        <v>6</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="O41" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="P41" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q41" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D42" s="23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E42" s="19" t="s">
         <v>25</v>
       </c>
       <c r="F42" s="19"/>
       <c r="G42" s="18" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H42" s="18" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J42" s="1" t="n">
         <f aca="false">J41+D41</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1" t="n">
         <f aca="false">J42/8</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L42" s="1" t="n">
         <f aca="false">J42/16</f>
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="M42" s="1" t="n">
         <f aca="false">J42/32</f>
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q42" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="23" t="s">
+      <c r="B43" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="D43" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E43" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I43" s="19" t="s">
         <v>116</v>
-      </c>
-      <c r="C43" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="D43" s="23" t="n">
-        <v>16</v>
-      </c>
-      <c r="E43" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" s="19"/>
-      <c r="G43" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="H43" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="I43" s="19" t="s">
-        <v>119</v>
       </c>
       <c r="J43" s="1" t="n">
         <f aca="false">J42+D42</f>
-        <v>208</v>
+        <v>1</v>
       </c>
       <c r="K43" s="1" t="n">
         <f aca="false">J43/8</f>
-        <v>26</v>
+        <v>0.125</v>
       </c>
       <c r="L43" s="1" t="n">
         <f aca="false">J43/16</f>
-        <v>13</v>
+        <v>0.0625</v>
       </c>
       <c r="M43" s="1" t="n">
         <f aca="false">J43/32</f>
-        <v>6.5</v>
+        <v>0.03125</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="1" t="n">
         <v>0</v>
@@ -3247,51 +3093,51 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="23" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D44" s="23" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E44" s="19" t="s">
         <v>25</v>
       </c>
       <c r="F44" s="19"/>
       <c r="G44" s="18" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H44" s="18" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
       <c r="I44" s="19" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J44" s="1" t="n">
         <f aca="false">J43+D43</f>
-        <v>224</v>
+        <v>8</v>
       </c>
       <c r="K44" s="1" t="n">
         <f aca="false">J44/8</f>
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="L44" s="1" t="n">
         <f aca="false">J44/16</f>
-        <v>14</v>
+        <v>0.5</v>
       </c>
       <c r="M44" s="1" t="n">
         <f aca="false">J44/32</f>
-        <v>7</v>
+        <v>0.25</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="O44" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Q44" s="1" t="n">
         <v>0</v>
@@ -3299,51 +3145,51 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="23" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D45" s="23" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E45" s="19" t="s">
         <v>25</v>
       </c>
       <c r="F45" s="19"/>
       <c r="G45" s="18" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H45" s="18" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
       <c r="I45" s="19" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="J45" s="1" t="n">
         <f aca="false">J44+D44</f>
-        <v>240</v>
+        <v>9</v>
       </c>
       <c r="K45" s="1" t="n">
         <f aca="false">J45/8</f>
-        <v>30</v>
+        <v>1.125</v>
       </c>
       <c r="L45" s="1" t="n">
         <f aca="false">J45/16</f>
-        <v>15</v>
+        <v>0.5625</v>
       </c>
       <c r="M45" s="1" t="n">
         <f aca="false">J45/32</f>
-        <v>7.5</v>
+        <v>0.28125</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Q45" s="1" t="n">
         <v>0</v>
@@ -3351,51 +3197,51 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="23" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D46" s="23" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E46" s="19" t="s">
         <v>25</v>
       </c>
       <c r="F46" s="19"/>
       <c r="G46" s="18" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H46" s="18" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
       <c r="I46" s="19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="J46" s="1" t="n">
         <f aca="false">J45+D45</f>
-        <v>256</v>
+        <v>10</v>
       </c>
       <c r="K46" s="1" t="n">
         <f aca="false">J46/8</f>
-        <v>32</v>
+        <v>1.25</v>
       </c>
       <c r="L46" s="1" t="n">
         <f aca="false">J46/16</f>
-        <v>16</v>
+        <v>0.625</v>
       </c>
       <c r="M46" s="1" t="n">
         <f aca="false">J46/32</f>
-        <v>8</v>
+        <v>0.3125</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Q46" s="1" t="n">
         <v>0</v>
@@ -3403,208 +3249,296 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="23" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="D47" s="21" t="n">
-        <v>16</v>
-      </c>
-      <c r="E47" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="F47" s="18"/>
+        <v>127</v>
+      </c>
+      <c r="D47" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" s="19"/>
       <c r="G47" s="18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" s="18" t="s">
         <v>34</v>
       </c>
       <c r="I47" s="19" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="J47" s="1" t="n">
-        <f aca="false">J42+D42</f>
-        <v>208</v>
+        <f aca="false">J46+D46</f>
+        <v>11</v>
       </c>
       <c r="K47" s="1" t="n">
         <f aca="false">J47/8</f>
-        <v>26</v>
+        <v>1.375</v>
       </c>
       <c r="L47" s="1" t="n">
         <f aca="false">J47/16</f>
-        <v>13</v>
+        <v>0.6875</v>
       </c>
       <c r="M47" s="1" t="n">
         <f aca="false">J47/32</f>
-        <v>6.5</v>
+        <v>0.34375</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="O47" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q47" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B48" s="23"/>
-      <c r="C48" s="23"/>
-      <c r="D48" s="23"/>
-      <c r="E48" s="19"/>
+      <c r="B48" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="C48" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="D48" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>25</v>
+      </c>
       <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="18"/>
+      <c r="G48" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="18" t="s">
+        <v>34</v>
+      </c>
       <c r="I48" s="19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J48" s="1" t="n">
         <f aca="false">J47+D47</f>
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="K48" s="1" t="n">
         <f aca="false">J48/8</f>
-        <v>28</v>
+        <v>1.5</v>
       </c>
       <c r="L48" s="1" t="n">
         <f aca="false">J48/16</f>
-        <v>14</v>
+        <v>0.75</v>
       </c>
       <c r="M48" s="1" t="n">
         <f aca="false">J48/32</f>
+        <v>0.375</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O48" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P48" s="1" t="n">
         <v>7</v>
       </c>
+      <c r="Q48" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="23"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="23"/>
-      <c r="E49" s="19"/>
+      <c r="B49" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="C49" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="D49" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>25</v>
+      </c>
       <c r="F49" s="19"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="19"/>
-      <c r="I49" s="19"/>
-      <c r="J49" s="22"/>
-      <c r="K49" s="22"/>
-      <c r="L49" s="22"/>
-      <c r="M49" s="22"/>
-    </row>
-    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
+      <c r="G49" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I49" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="J49" s="1" t="n">
+        <f aca="false">J48+D48</f>
+        <v>13</v>
+      </c>
+      <c r="K49" s="1" t="n">
+        <f aca="false">J49/8</f>
+        <v>1.625</v>
+      </c>
+      <c r="L49" s="1" t="n">
+        <f aca="false">J49/16</f>
+        <v>0.8125</v>
+      </c>
+      <c r="M49" s="1" t="n">
+        <f aca="false">J49/32</f>
+        <v>0.40625</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P49" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q49" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="D50" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="19"/>
+      <c r="G50" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I50" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="J50" s="1" t="n">
+        <f aca="false">J49+D49</f>
+        <v>14</v>
+      </c>
+      <c r="K50" s="1" t="n">
+        <f aca="false">J50/8</f>
+        <v>1.75</v>
+      </c>
+      <c r="L50" s="1" t="n">
+        <f aca="false">J50/16</f>
+        <v>0.875</v>
+      </c>
+      <c r="M50" s="1" t="n">
+        <f aca="false">J50/32</f>
+        <v>0.4375</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="O50" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P50" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q50" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B51" s="23"/>
-      <c r="C51" s="23"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="19"/>
+      <c r="B51" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="C51" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="D51" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="19" t="s">
+        <v>25</v>
+      </c>
       <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="19"/>
-      <c r="I51" s="19"/>
-      <c r="J51" s="22"/>
-      <c r="K51" s="22"/>
-      <c r="L51" s="22"/>
-      <c r="M51" s="22"/>
+      <c r="G51" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I51" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="J51" s="1" t="n">
+        <f aca="false">J50+D50</f>
+        <v>15</v>
+      </c>
+      <c r="K51" s="1" t="n">
+        <f aca="false">J51/8</f>
+        <v>1.875</v>
+      </c>
+      <c r="L51" s="1" t="n">
+        <f aca="false">J51/16</f>
+        <v>0.9375</v>
+      </c>
+      <c r="M51" s="1" t="n">
+        <f aca="false">J51/32</f>
+        <v>0.46875</v>
+      </c>
+      <c r="N51" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="O51" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P51" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q51" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B52" s="23"/>
-      <c r="C52" s="23"/>
-      <c r="D52" s="23"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="19"/>
+        <v>141</v>
+      </c>
+      <c r="B52" s="18"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="18"/>
       <c r="I52" s="19"/>
-      <c r="J52" s="22"/>
-      <c r="K52" s="22"/>
-      <c r="L52" s="22"/>
-      <c r="M52" s="22"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="C53" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="D53" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F53" s="19"/>
-      <c r="G53" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I53" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="J53" s="1" t="n">
-        <f aca="false">J52+D52</f>
-        <v>0</v>
-      </c>
-      <c r="K53" s="1" t="n">
-        <f aca="false">J53/8</f>
-        <v>0</v>
-      </c>
-      <c r="L53" s="1" t="n">
-        <f aca="false">J53/16</f>
-        <v>0</v>
-      </c>
-      <c r="M53" s="1" t="n">
-        <f aca="false">J53/32</f>
-        <v>0</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="O53" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="P53" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q53" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="A53" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B53" s="18"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="19"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="18" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="D54" s="18" t="n">
         <v>7</v>
@@ -3620,23 +3554,23 @@
         <v>34</v>
       </c>
       <c r="I54" s="19" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="J54" s="1" t="n">
         <f aca="false">J53+D53</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" s="1" t="n">
         <f aca="false">J54/8</f>
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="L54" s="1" t="n">
         <f aca="false">J54/16</f>
-        <v>0.0625</v>
+        <v>0</v>
       </c>
       <c r="M54" s="1" t="n">
         <f aca="false">J54/32</f>
-        <v>0.03125</v>
+        <v>0</v>
       </c>
       <c r="N54" s="1" t="s">
         <v>28</v>
@@ -3653,10 +3587,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="23" t="s">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="D55" s="23" t="n">
         <v>1</v>
@@ -3672,32 +3606,32 @@
         <v>34</v>
       </c>
       <c r="I55" s="19" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="J55" s="1" t="n">
         <f aca="false">J54+D54</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K55" s="1" t="n">
         <f aca="false">J55/8</f>
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="L55" s="1" t="n">
         <f aca="false">J55/16</f>
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="M55" s="1" t="n">
         <f aca="false">J55/32</f>
-        <v>0.25</v>
+        <v>0.21875</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="O55" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P55" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q55" s="1" t="n">
         <v>0</v>
@@ -3705,10 +3639,10 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="23" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D56" s="23" t="n">
         <v>1</v>
@@ -3724,32 +3658,32 @@
         <v>34</v>
       </c>
       <c r="I56" s="19" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="J56" s="1" t="n">
         <f aca="false">J55+D55</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K56" s="1" t="n">
         <f aca="false">J56/8</f>
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="L56" s="1" t="n">
         <f aca="false">J56/16</f>
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
       <c r="M56" s="1" t="n">
         <f aca="false">J56/32</f>
-        <v>0.28125</v>
+        <v>0.25</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P56" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q56" s="1" t="n">
         <v>0</v>
@@ -3757,10 +3691,10 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="23" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="C57" s="23" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="D57" s="23" t="n">
         <v>1</v>
@@ -3776,29 +3710,29 @@
         <v>34</v>
       </c>
       <c r="I57" s="19" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="J57" s="1" t="n">
         <f aca="false">J56+D56</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K57" s="1" t="n">
         <f aca="false">J57/8</f>
-        <v>1.25</v>
+        <v>1.125</v>
       </c>
       <c r="L57" s="1" t="n">
         <f aca="false">J57/16</f>
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
       <c r="M57" s="1" t="n">
         <f aca="false">J57/32</f>
-        <v>0.3125</v>
+        <v>0.28125</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="O57" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P57" s="1" t="n">
         <v>5</v>
@@ -3809,10 +3743,10 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="23" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="C58" s="23" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="D58" s="23" t="n">
         <v>1</v>
@@ -3828,32 +3762,32 @@
         <v>34</v>
       </c>
       <c r="I58" s="19" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="J58" s="1" t="n">
         <f aca="false">J57+D57</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K58" s="1" t="n">
         <f aca="false">J58/8</f>
-        <v>1.375</v>
+        <v>1.25</v>
       </c>
       <c r="L58" s="1" t="n">
         <f aca="false">J58/16</f>
-        <v>0.6875</v>
+        <v>0.625</v>
       </c>
       <c r="M58" s="1" t="n">
         <f aca="false">J58/32</f>
-        <v>0.34375</v>
+        <v>0.3125</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="O58" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P58" s="1" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Q58" s="1" t="n">
         <v>0</v>
@@ -3861,10 +3795,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="23" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="C59" s="23" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="D59" s="23" t="n">
         <v>1</v>
@@ -3880,23 +3814,23 @@
         <v>34</v>
       </c>
       <c r="I59" s="19" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="J59" s="1" t="n">
         <f aca="false">J58+D58</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K59" s="1" t="n">
         <f aca="false">J59/8</f>
-        <v>1.5</v>
+        <v>1.375</v>
       </c>
       <c r="L59" s="1" t="n">
         <f aca="false">J59/16</f>
-        <v>0.75</v>
+        <v>0.6875</v>
       </c>
       <c r="M59" s="1" t="n">
         <f aca="false">J59/32</f>
-        <v>0.375</v>
+        <v>0.34375</v>
       </c>
       <c r="N59" s="1" t="s">
         <v>53</v>
@@ -3913,10 +3847,10 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="23" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="D60" s="23" t="n">
         <v>1</v>
@@ -3932,32 +3866,32 @@
         <v>34</v>
       </c>
       <c r="I60" s="19" t="s">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="J60" s="1" t="n">
         <f aca="false">J59+D59</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K60" s="1" t="n">
         <f aca="false">J60/8</f>
-        <v>1.625</v>
+        <v>1.5</v>
       </c>
       <c r="L60" s="1" t="n">
         <f aca="false">J60/16</f>
-        <v>0.8125</v>
+        <v>0.75</v>
       </c>
       <c r="M60" s="1" t="n">
         <f aca="false">J60/32</f>
-        <v>0.40625</v>
+        <v>0.375</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="O60" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P60" s="1" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q60" s="1" t="n">
         <v>0</v>
@@ -3965,10 +3899,10 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="23" t="s">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="C61" s="23" t="s">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="D61" s="23" t="n">
         <v>1</v>
@@ -3984,29 +3918,29 @@
         <v>34</v>
       </c>
       <c r="I61" s="19" t="s">
-        <v>162</v>
+        <v>125</v>
       </c>
       <c r="J61" s="1" t="n">
         <f aca="false">J60+D60</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K61" s="1" t="n">
         <f aca="false">J61/8</f>
-        <v>1.75</v>
+        <v>1.625</v>
       </c>
       <c r="L61" s="1" t="n">
         <f aca="false">J61/16</f>
-        <v>0.875</v>
+        <v>0.8125</v>
       </c>
       <c r="M61" s="1" t="n">
         <f aca="false">J61/32</f>
-        <v>0.4375</v>
+        <v>0.40625</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P61" s="1" t="n">
         <v>5</v>
@@ -4017,10 +3951,10 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="23" t="s">
-        <v>163</v>
+        <v>120</v>
       </c>
       <c r="C62" s="23" t="s">
-        <v>164</v>
+        <v>121</v>
       </c>
       <c r="D62" s="23" t="n">
         <v>1</v>
@@ -4036,53 +3970,92 @@
         <v>34</v>
       </c>
       <c r="I62" s="19" t="s">
-        <v>165</v>
+        <v>122</v>
       </c>
       <c r="J62" s="1" t="n">
         <f aca="false">J61+D61</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K62" s="1" t="n">
         <f aca="false">J62/8</f>
-        <v>1.875</v>
+        <v>1.75</v>
       </c>
       <c r="L62" s="1" t="n">
         <f aca="false">J62/16</f>
-        <v>0.9375</v>
+        <v>0.875</v>
       </c>
       <c r="M62" s="1" t="n">
         <f aca="false">J62/32</f>
+        <v>0.4375</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O62" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P62" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="C63" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D63" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F63" s="19"/>
+      <c r="G63" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I63" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="J63" s="1" t="n">
+        <f aca="false">J62+D62</f>
+        <v>15</v>
+      </c>
+      <c r="K63" s="1" t="n">
+        <f aca="false">J63/8</f>
+        <v>1.875</v>
+      </c>
+      <c r="L63" s="1" t="n">
+        <f aca="false">J63/16</f>
+        <v>0.9375</v>
+      </c>
+      <c r="M63" s="1" t="n">
+        <f aca="false">J63/32</f>
         <v>0.46875</v>
       </c>
-      <c r="N62" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="O62" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="P62" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q62" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B63" s="18"/>
-      <c r="C63" s="18"/>
-      <c r="D63" s="18"/>
-      <c r="E63" s="18"/>
-      <c r="F63" s="18"/>
-      <c r="G63" s="18"/>
-      <c r="H63" s="18"/>
-      <c r="I63" s="19"/>
+      <c r="N63" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O63" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P63" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q63" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>167</v>
+        <v>141</v>
       </c>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
@@ -4095,354 +4068,354 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="18" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="E65" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E65" s="19" t="s">
         <v>25</v>
       </c>
       <c r="F65" s="18"/>
       <c r="G65" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H65" s="18" t="s">
         <v>34</v>
       </c>
       <c r="I65" s="19" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="J65" s="1" t="n">
-        <f aca="false">J64+D64</f>
-        <v>0</v>
+        <f aca="false">J63+D63</f>
+        <v>16</v>
       </c>
       <c r="K65" s="1" t="n">
         <f aca="false">J65/8</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="1" t="n">
         <f aca="false">J65/16</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="1" t="n">
         <f aca="false">J65/32</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="O65" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P65" s="1" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q65" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="C66" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="D66" s="23" t="n">
-        <v>1</v>
+      <c r="B66" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="C66" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D66" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="E66" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F66" s="19"/>
+      <c r="F66" s="18"/>
       <c r="G66" s="18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H66" s="18" t="s">
-        <v>34</v>
+        <v>148</v>
       </c>
       <c r="I66" s="19" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="J66" s="1" t="n">
         <f aca="false">J65+D65</f>
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="K66" s="1" t="n">
         <f aca="false">J66/8</f>
-        <v>0.875</v>
+        <v>3</v>
       </c>
       <c r="L66" s="1" t="n">
         <f aca="false">J66/16</f>
-        <v>0.4375</v>
+        <v>1.5</v>
       </c>
       <c r="M66" s="1" t="n">
         <f aca="false">J66/32</f>
-        <v>0.21875</v>
+        <v>0.75</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P66" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q66" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C67" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="D67" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E67" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F67" s="18"/>
+      <c r="G67" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="Q66" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="C67" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="D67" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F67" s="19"/>
-      <c r="G67" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="H67" s="18" t="s">
-        <v>34</v>
+        <v>148</v>
       </c>
       <c r="I67" s="19" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="J67" s="1" t="n">
         <f aca="false">J66+D66</f>
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="K67" s="1" t="n">
         <f aca="false">J67/8</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L67" s="1" t="n">
         <f aca="false">J67/16</f>
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="M67" s="1" t="n">
         <f aca="false">J67/32</f>
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P67" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q67" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="C68" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="D68" s="23" t="n">
-        <v>1</v>
+      <c r="B68" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="C68" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="D68" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="E68" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F68" s="19"/>
+      <c r="F68" s="18"/>
       <c r="G68" s="18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H68" s="18" t="s">
-        <v>34</v>
+        <v>148</v>
       </c>
       <c r="I68" s="19" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="J68" s="1" t="n">
         <f aca="false">J67+D67</f>
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="K68" s="1" t="n">
         <f aca="false">J68/8</f>
-        <v>1.125</v>
+        <v>5</v>
       </c>
       <c r="L68" s="1" t="n">
         <f aca="false">J68/16</f>
-        <v>0.5625</v>
+        <v>2.5</v>
       </c>
       <c r="M68" s="1" t="n">
         <f aca="false">J68/32</f>
-        <v>0.28125</v>
+        <v>1.25</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="O68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P68" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="P68" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Q68" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="23" t="s">
+    <row r="69" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="C69" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="C69" s="23" t="s">
+      <c r="D69" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E69" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F69" s="18"/>
+      <c r="G69" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="H69" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="I69" s="19" t="s">
         <v>158</v>
-      </c>
-      <c r="D69" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F69" s="19"/>
-      <c r="G69" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H69" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I69" s="19" t="s">
-        <v>159</v>
       </c>
       <c r="J69" s="1" t="n">
         <f aca="false">J68+D68</f>
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="K69" s="1" t="n">
         <f aca="false">J69/8</f>
-        <v>1.25</v>
+        <v>6</v>
       </c>
       <c r="L69" s="1" t="n">
         <f aca="false">J69/16</f>
-        <v>0.625</v>
+        <v>3</v>
       </c>
       <c r="M69" s="1" t="n">
         <f aca="false">J69/32</f>
-        <v>0.3125</v>
+        <v>1.5</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>109</v>
+        <v>44</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P69" s="1" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Q69" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="C70" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="D70" s="23" t="n">
-        <v>1</v>
+    <row r="70" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C70" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="D70" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="E70" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F70" s="19"/>
+      <c r="F70" s="18"/>
       <c r="G70" s="18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H70" s="18" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="I70" s="19" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J70" s="1" t="n">
         <f aca="false">J69+D69</f>
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="K70" s="1" t="n">
         <f aca="false">J70/8</f>
-        <v>1.375</v>
+        <v>7</v>
       </c>
       <c r="L70" s="1" t="n">
         <f aca="false">J70/16</f>
-        <v>0.6875</v>
+        <v>3.5</v>
       </c>
       <c r="M70" s="1" t="n">
         <f aca="false">J70/32</f>
-        <v>0.34375</v>
+        <v>1.75</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P70" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q70" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="C71" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="D71" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E71" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F71" s="18"/>
+      <c r="G71" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="Q70" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="C71" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="D71" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F71" s="19"/>
-      <c r="G71" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="H71" s="18" t="s">
-        <v>34</v>
+        <v>148</v>
       </c>
       <c r="I71" s="19" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="J71" s="1" t="n">
         <f aca="false">J70+D70</f>
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="K71" s="1" t="n">
         <f aca="false">J71/8</f>
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="L71" s="1" t="n">
         <f aca="false">J71/16</f>
-        <v>0.75</v>
+        <v>4</v>
       </c>
       <c r="M71" s="1" t="n">
         <f aca="false">J71/32</f>
-        <v>0.375</v>
+        <v>2</v>
       </c>
       <c r="N71" s="1" t="s">
         <v>53</v>
@@ -4451,50 +4424,50 @@
         <v>3</v>
       </c>
       <c r="P71" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q71" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="23" t="s">
+      <c r="B72" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C72" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="D72" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E72" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F72" s="18"/>
+      <c r="G72" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="H72" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="C72" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="D72" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F72" s="19"/>
-      <c r="G72" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H72" s="18" t="s">
-        <v>34</v>
-      </c>
       <c r="I72" s="19" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="J72" s="1" t="n">
         <f aca="false">J71+D71</f>
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="K72" s="1" t="n">
         <f aca="false">J72/8</f>
-        <v>1.625</v>
+        <v>9</v>
       </c>
       <c r="L72" s="1" t="n">
         <f aca="false">J72/16</f>
-        <v>0.8125</v>
+        <v>4.5</v>
       </c>
       <c r="M72" s="1" t="n">
         <f aca="false">J72/32</f>
-        <v>0.40625</v>
+        <v>2.25</v>
       </c>
       <c r="N72" s="1" t="s">
         <v>53</v>
@@ -4503,59 +4476,59 @@
         <v>3</v>
       </c>
       <c r="P72" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q72" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="C73" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="D73" s="23" t="n">
-        <v>1</v>
+      <c r="B73" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="C73" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="D73" s="18" t="n">
+        <v>8</v>
       </c>
       <c r="E73" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F73" s="19"/>
+      <c r="F73" s="18"/>
       <c r="G73" s="18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H73" s="18" t="s">
-        <v>34</v>
+        <v>148</v>
       </c>
       <c r="I73" s="19" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="J73" s="1" t="n">
         <f aca="false">J72+D72</f>
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="K73" s="1" t="n">
         <f aca="false">J73/8</f>
-        <v>1.75</v>
+        <v>10</v>
       </c>
       <c r="L73" s="1" t="n">
         <f aca="false">J73/16</f>
-        <v>0.875</v>
+        <v>5</v>
       </c>
       <c r="M73" s="1" t="n">
         <f aca="false">J73/32</f>
-        <v>0.4375</v>
+        <v>2.5</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="O73" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P73" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q73" s="1" t="n">
         <v>0</v>
@@ -4563,159 +4536,198 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="23" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="C74" s="23" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="D74" s="23" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E74" s="19" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="F74" s="19"/>
       <c r="G74" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H74" s="18" t="s">
         <v>34</v>
       </c>
       <c r="I74" s="19" t="s">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="J74" s="1" t="n">
         <f aca="false">J73+D73</f>
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="K74" s="1" t="n">
         <f aca="false">J74/8</f>
-        <v>1.875</v>
+        <v>11</v>
       </c>
       <c r="L74" s="1" t="n">
         <f aca="false">J74/16</f>
-        <v>0.9375</v>
+        <v>5.5</v>
       </c>
       <c r="M74" s="1" t="n">
         <f aca="false">J74/32</f>
-        <v>0.46875</v>
+        <v>2.75</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>109</v>
+        <v>44</v>
       </c>
       <c r="O74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P74" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q74" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="C75" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="D75" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E75" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F75" s="19"/>
+      <c r="G75" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="P74" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q74" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B75" s="18"/>
-      <c r="C75" s="18"/>
-      <c r="D75" s="18"/>
-      <c r="E75" s="18"/>
-      <c r="F75" s="18"/>
-      <c r="G75" s="18"/>
-      <c r="H75" s="18"/>
-      <c r="I75" s="19"/>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="C76" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="D76" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="E76" s="19" t="s">
+      <c r="H75" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I75" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="J75" s="1" t="n">
+        <f aca="false">J74+D74</f>
+        <v>96</v>
+      </c>
+      <c r="K75" s="1" t="n">
+        <f aca="false">J75/8</f>
+        <v>12</v>
+      </c>
+      <c r="L75" s="1" t="n">
+        <f aca="false">J75/16</f>
+        <v>6</v>
+      </c>
+      <c r="M75" s="1" t="n">
+        <f aca="false">J75/32</f>
+        <v>3</v>
+      </c>
+      <c r="N75" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O75" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q75" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="C76" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="D76" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="E76" s="18" t="s">
         <v>25</v>
       </c>
       <c r="F76" s="18"/>
       <c r="G76" s="18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H76" s="18" t="s">
         <v>34</v>
       </c>
       <c r="I76" s="19" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="J76" s="1" t="n">
-        <f aca="false">J74+D74</f>
-        <v>16</v>
+        <f aca="false">J75+D75</f>
+        <v>104</v>
       </c>
       <c r="K76" s="1" t="n">
         <f aca="false">J76/8</f>
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L76" s="1" t="n">
         <f aca="false">J76/16</f>
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="M76" s="1" t="n">
         <f aca="false">J76/32</f>
-        <v>0.5</v>
+        <v>3.25</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P76" s="1" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q76" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="C77" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="D77" s="18" t="n">
-        <v>8</v>
+      <c r="B77" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="C77" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="D77" s="23" t="n">
+        <v>32</v>
       </c>
       <c r="E77" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F77" s="18"/>
+      <c r="F77" s="19"/>
       <c r="G77" s="18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H77" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="I77" s="19" t="s">
-        <v>174</v>
+        <v>34</v>
+      </c>
+      <c r="I77" s="23" t="s">
+        <v>182</v>
       </c>
       <c r="J77" s="1" t="n">
         <f aca="false">J76+D76</f>
-        <v>24</v>
+        <v>128</v>
       </c>
       <c r="K77" s="1" t="n">
         <f aca="false">J77/8</f>
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="L77" s="1" t="n">
         <f aca="false">J77/16</f>
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="M77" s="1" t="n">
         <f aca="false">J77/32</f>
-        <v>0.75</v>
+        <v>4</v>
       </c>
       <c r="N77" s="1" t="s">
         <v>44</v>
@@ -4724,434 +4736,434 @@
         <v>1</v>
       </c>
       <c r="P77" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Q77" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="C78" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="D78" s="18" t="n">
+      <c r="B78" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="C78" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="D78" s="23" t="n">
         <v>8</v>
       </c>
       <c r="E78" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F78" s="18"/>
+        <v>65</v>
+      </c>
+      <c r="F78" s="19"/>
       <c r="G78" s="18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H78" s="18" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="I78" s="19" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="J78" s="1" t="n">
         <f aca="false">J77+D77</f>
-        <v>32</v>
+        <v>160</v>
       </c>
       <c r="K78" s="1" t="n">
         <f aca="false">J78/8</f>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L78" s="1" t="n">
         <f aca="false">J78/16</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M78" s="1" t="n">
         <f aca="false">J78/32</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="O78" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P78" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q78" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="C79" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="D79" s="18" t="n">
+      <c r="B79" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="C79" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="D79" s="23" t="n">
         <v>8</v>
       </c>
       <c r="E79" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F79" s="18"/>
+        <v>65</v>
+      </c>
+      <c r="F79" s="19"/>
       <c r="G79" s="18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H79" s="18" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="I79" s="19" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="J79" s="1" t="n">
         <f aca="false">J78+D78</f>
-        <v>40</v>
+        <v>168</v>
       </c>
       <c r="K79" s="1" t="n">
         <f aca="false">J79/8</f>
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="L79" s="1" t="n">
         <f aca="false">J79/16</f>
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
       <c r="M79" s="1" t="n">
         <f aca="false">J79/32</f>
-        <v>1.25</v>
+        <v>5.25</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P79" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q79" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="C80" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="D80" s="18" t="n">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="C80" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D80" s="23" t="n">
         <v>8</v>
       </c>
       <c r="E80" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F80" s="18"/>
+        <v>65</v>
+      </c>
+      <c r="F80" s="19"/>
       <c r="G80" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H80" s="18" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="I80" s="19" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="J80" s="1" t="n">
         <f aca="false">J79+D79</f>
-        <v>48</v>
+        <v>176</v>
       </c>
       <c r="K80" s="1" t="n">
         <f aca="false">J80/8</f>
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="L80" s="1" t="n">
         <f aca="false">J80/16</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M80" s="1" t="n">
         <f aca="false">J80/32</f>
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P80" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q80" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="C81" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="D81" s="18" t="n">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="C81" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="D81" s="23" t="n">
         <v>8</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F81" s="18"/>
+        <v>65</v>
+      </c>
+      <c r="F81" s="19"/>
       <c r="G81" s="18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H81" s="18" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="I81" s="19" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="J81" s="1" t="n">
         <f aca="false">J80+D80</f>
-        <v>56</v>
+        <v>184</v>
       </c>
       <c r="K81" s="1" t="n">
         <f aca="false">J81/8</f>
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="L81" s="1" t="n">
         <f aca="false">J81/16</f>
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="M81" s="1" t="n">
         <f aca="false">J81/32</f>
-        <v>1.75</v>
+        <v>5.75</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="O81" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P81" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q81" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="C82" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="D82" s="18" t="n">
+    <row r="82" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B82" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="C82" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="D82" s="23" t="n">
         <v>8</v>
       </c>
       <c r="E82" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F82" s="18"/>
+        <v>65</v>
+      </c>
+      <c r="F82" s="19"/>
       <c r="G82" s="18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H82" s="18" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="I82" s="19" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="J82" s="1" t="n">
         <f aca="false">J81+D81</f>
-        <v>64</v>
+        <v>192</v>
       </c>
       <c r="K82" s="1" t="n">
         <f aca="false">J82/8</f>
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="L82" s="1" t="n">
         <f aca="false">J82/16</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M82" s="1" t="n">
         <f aca="false">J82/32</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="O82" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P82" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q82" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="C83" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="D83" s="18" t="n">
+    <row r="83" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B83" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="C83" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="D83" s="23" t="n">
         <v>8</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="F83" s="18"/>
+        <v>65</v>
+      </c>
+      <c r="F83" s="19"/>
       <c r="G83" s="18" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H83" s="18" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="I83" s="19" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="J83" s="1" t="n">
         <f aca="false">J82+D82</f>
-        <v>72</v>
+        <v>200</v>
       </c>
       <c r="K83" s="1" t="n">
         <f aca="false">J83/8</f>
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="L83" s="1" t="n">
         <f aca="false">J83/16</f>
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="M83" s="1" t="n">
         <f aca="false">J83/32</f>
-        <v>2.25</v>
+        <v>6.25</v>
       </c>
       <c r="N83" s="1" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="O83" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P83" s="1" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Q83" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="C84" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="D84" s="18" t="n">
+    <row r="84" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="C84" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="D84" s="23" t="n">
         <v>8</v>
       </c>
       <c r="E84" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F84" s="18"/>
+      <c r="F84" s="19"/>
       <c r="G84" s="18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H84" s="18" t="s">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="I84" s="19" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="J84" s="1" t="n">
         <f aca="false">J83+D83</f>
-        <v>80</v>
+        <v>208</v>
       </c>
       <c r="K84" s="1" t="n">
         <f aca="false">J84/8</f>
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="L84" s="1" t="n">
         <f aca="false">J84/16</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M84" s="1" t="n">
         <f aca="false">J84/32</f>
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="N84" s="1" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P84" s="1" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q84" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D85" s="23" t="n">
         <v>8</v>
       </c>
       <c r="E85" s="19" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="F85" s="19"/>
       <c r="G85" s="18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H85" s="18" t="s">
         <v>34</v>
       </c>
       <c r="I85" s="19" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="J85" s="1" t="n">
         <f aca="false">J84+D84</f>
-        <v>88</v>
+        <v>216</v>
       </c>
       <c r="K85" s="1" t="n">
         <f aca="false">J85/8</f>
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="L85" s="1" t="n">
         <f aca="false">J85/16</f>
-        <v>5.5</v>
+        <v>13.5</v>
       </c>
       <c r="M85" s="1" t="n">
         <f aca="false">J85/32</f>
-        <v>2.75</v>
+        <v>6.75</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="O85" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P85" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="P85" s="1" t="n">
-        <v>10</v>
-      </c>
       <c r="Q85" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="30" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="23" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C86" s="23" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D86" s="23" t="n">
         <v>8</v>
@@ -5161,38 +5173,38 @@
       </c>
       <c r="F86" s="19"/>
       <c r="G86" s="18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H86" s="18" t="s">
         <v>34</v>
       </c>
       <c r="I86" s="19" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="J86" s="1" t="n">
         <f aca="false">J85+D85</f>
-        <v>96</v>
+        <v>224</v>
       </c>
       <c r="K86" s="1" t="n">
         <f aca="false">J86/8</f>
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="L86" s="1" t="n">
         <f aca="false">J86/16</f>
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M86" s="1" t="n">
         <f aca="false">J86/32</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="O86" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="P86" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="P86" s="1" t="n">
-        <v>8</v>
       </c>
       <c r="Q86" s="1" t="n">
         <v>0</v>
@@ -5200,457 +5212,480 @@
     </row>
     <row r="87" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="23" t="s">
-        <v>129</v>
+        <v>195</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="D87" s="21" t="n">
-        <v>24</v>
-      </c>
-      <c r="E87" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="F87" s="18"/>
+        <v>207</v>
+      </c>
+      <c r="D87" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E87" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F87" s="19"/>
       <c r="G87" s="18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H87" s="18" t="s">
         <v>34</v>
       </c>
       <c r="I87" s="19" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="J87" s="1" t="n">
         <f aca="false">J86+D86</f>
-        <v>104</v>
+        <v>232</v>
       </c>
       <c r="K87" s="1" t="n">
         <f aca="false">J87/8</f>
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="L87" s="1" t="n">
         <f aca="false">J87/16</f>
-        <v>6.5</v>
+        <v>14.5</v>
       </c>
       <c r="M87" s="1" t="n">
         <f aca="false">J87/32</f>
-        <v>3.25</v>
+        <v>7.25</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="O87" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P87" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q87" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="23" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C88" s="23" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D88" s="23" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E88" s="19" t="s">
         <v>25</v>
       </c>
       <c r="F88" s="19"/>
       <c r="G88" s="18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H88" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="I88" s="23" t="s">
-        <v>206</v>
+      <c r="I88" s="19" t="s">
+        <v>210</v>
       </c>
       <c r="J88" s="1" t="n">
         <f aca="false">J87+D87</f>
-        <v>128</v>
+        <v>240</v>
       </c>
       <c r="K88" s="1" t="n">
         <f aca="false">J88/8</f>
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="L88" s="1" t="n">
         <f aca="false">J88/16</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M88" s="1" t="n">
         <f aca="false">J88/32</f>
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="O88" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P88" s="1" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Q88" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="23" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C89" s="23" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D89" s="23" t="n">
         <v>8</v>
       </c>
       <c r="E89" s="19" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="F89" s="19"/>
       <c r="G89" s="18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H89" s="18" t="s">
         <v>34</v>
       </c>
       <c r="I89" s="19" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="J89" s="1" t="n">
         <f aca="false">J88+D88</f>
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="K89" s="1" t="n">
         <f aca="false">J89/8</f>
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="L89" s="1" t="n">
         <f aca="false">J89/16</f>
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="M89" s="1" t="n">
         <f aca="false">J89/32</f>
-        <v>5</v>
+        <v>7.75</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="O89" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P89" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="P89" s="1" t="n">
-        <v>4</v>
-      </c>
       <c r="Q89" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="23" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="C90" s="23" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D90" s="23" t="n">
         <v>8</v>
       </c>
       <c r="E90" s="19" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="F90" s="19"/>
       <c r="G90" s="18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H90" s="18" t="s">
         <v>34</v>
       </c>
       <c r="I90" s="19" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J90" s="1" t="n">
         <f aca="false">J89+D89</f>
-        <v>168</v>
+        <v>256</v>
       </c>
       <c r="K90" s="1" t="n">
         <f aca="false">J90/8</f>
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="L90" s="1" t="n">
         <f aca="false">J90/16</f>
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="M90" s="1" t="n">
         <f aca="false">J90/32</f>
-        <v>5.25</v>
+        <v>8</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="O90" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="P90" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="P90" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="Q90" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="23" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="C91" s="23" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D91" s="23" t="n">
         <v>8</v>
       </c>
       <c r="E91" s="19" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="F91" s="19"/>
       <c r="G91" s="18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H91" s="18" t="s">
         <v>34</v>
       </c>
       <c r="I91" s="19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J91" s="1" t="n">
         <f aca="false">J90+D90</f>
-        <v>176</v>
+        <v>264</v>
       </c>
       <c r="K91" s="1" t="n">
         <f aca="false">J91/8</f>
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L91" s="1" t="n">
         <f aca="false">J91/16</f>
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="M91" s="1" t="n">
         <f aca="false">J91/32</f>
-        <v>5.5</v>
+        <v>8.25</v>
       </c>
       <c r="N91" s="1" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="O91" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="P91" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="P91" s="1" t="n">
-        <v>6</v>
-      </c>
       <c r="Q91" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="23" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C92" s="23" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D92" s="23" t="n">
         <v>8</v>
       </c>
       <c r="E92" s="19" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="F92" s="19"/>
       <c r="G92" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H92" s="18" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="I92" s="19" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J92" s="1" t="n">
         <f aca="false">J91+D91</f>
-        <v>184</v>
+        <v>272</v>
       </c>
       <c r="K92" s="1" t="n">
         <f aca="false">J92/8</f>
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="L92" s="1" t="n">
         <f aca="false">J92/16</f>
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="M92" s="1" t="n">
         <f aca="false">J92/32</f>
-        <v>5.75</v>
+        <v>8.5</v>
       </c>
       <c r="N92" s="1" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="O92" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P92" s="1" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Q92" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="93" s="13" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B93" s="24"/>
-      <c r="C93" s="25"/>
-      <c r="D93" s="26"/>
-      <c r="E93" s="26"/>
-      <c r="F93" s="26"/>
-      <c r="G93" s="26"/>
-      <c r="H93" s="25"/>
-      <c r="I93" s="26" t="s">
-        <v>219</v>
+    <row r="93" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B93" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="C93" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="D93" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E93" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F93" s="19"/>
+      <c r="G93" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H93" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="I93" s="19" t="s">
+        <v>222</v>
       </c>
       <c r="J93" s="1" t="n">
         <f aca="false">J92+D92</f>
-        <v>192</v>
+        <v>280</v>
       </c>
       <c r="K93" s="1" t="n">
         <f aca="false">J93/8</f>
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L93" s="1" t="n">
         <f aca="false">J93/16</f>
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="M93" s="1" t="n">
         <f aca="false">J93/32</f>
+        <v>8.75</v>
+      </c>
+      <c r="N93" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O93" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P93" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q93" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" s="13" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B94" s="24"/>
+      <c r="C94" s="25"/>
+      <c r="D94" s="26"/>
+      <c r="E94" s="26"/>
+      <c r="F94" s="26"/>
+      <c r="G94" s="26"/>
+      <c r="H94" s="25"/>
+      <c r="I94" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="J94" s="1" t="n">
+        <f aca="false">J81+D81</f>
+        <v>192</v>
+      </c>
+      <c r="K94" s="1" t="n">
+        <f aca="false">J94/8</f>
+        <v>24</v>
+      </c>
+      <c r="L94" s="1" t="n">
+        <f aca="false">J94/16</f>
+        <v>12</v>
+      </c>
+      <c r="M94" s="1" t="n">
+        <f aca="false">J94/32</f>
         <v>6</v>
       </c>
-      <c r="O93" s="17"/>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="20"/>
+      <c r="O94" s="17"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="B95" s="20"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B96" s="23"/>
-      <c r="C96" s="23"/>
-      <c r="D96" s="23"/>
-      <c r="E96" s="19"/>
-      <c r="F96" s="19"/>
-      <c r="G96" s="19"/>
-      <c r="H96" s="19"/>
-      <c r="I96" s="19"/>
-      <c r="J96" s="22"/>
-      <c r="K96" s="22"/>
-      <c r="L96" s="22"/>
-      <c r="M96" s="22"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B97" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="C97" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="D97" s="23" t="n">
+      <c r="A97" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B97" s="23"/>
+      <c r="C97" s="23"/>
+      <c r="D97" s="23"/>
+      <c r="E97" s="19"/>
+      <c r="F97" s="19"/>
+      <c r="G97" s="19"/>
+      <c r="H97" s="19"/>
+      <c r="I97" s="19"/>
+      <c r="J97" s="22"/>
+      <c r="K97" s="22"/>
+      <c r="L97" s="22"/>
+      <c r="M97" s="22"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B98" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C98" s="23" t="s">
+        <v>225</v>
+      </c>
+      <c r="D98" s="23" t="n">
         <v>32</v>
       </c>
-      <c r="E97" s="19" t="s">
+      <c r="E98" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="F97" s="19"/>
-      <c r="G97" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="I97" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="J97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" s="22" t="n">
-        <f aca="false">J97/8</f>
-        <v>0</v>
-      </c>
-      <c r="L97" s="22" t="n">
-        <f aca="false">J97/16</f>
-        <v>0</v>
-      </c>
-      <c r="M97" s="22" t="n">
-        <f aca="false">J97/32</f>
-        <v>0</v>
-      </c>
-      <c r="N97" s="1" t="s">
+      <c r="F98" s="19"/>
+      <c r="G98" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I98" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="J98" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="22" t="n">
+        <f aca="false">J98/8</f>
+        <v>0</v>
+      </c>
+      <c r="L98" s="22" t="n">
+        <f aca="false">J98/16</f>
+        <v>0</v>
+      </c>
+      <c r="M98" s="22" t="n">
+        <f aca="false">J98/32</f>
+        <v>0</v>
+      </c>
+      <c r="N98" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="O97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q97" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" s="13" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="13" t="s">
+      <c r="O98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" s="13" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B98" s="24"/>
-      <c r="C98" s="25"/>
-      <c r="D98" s="26"/>
-      <c r="E98" s="26"/>
-      <c r="F98" s="26"/>
-      <c r="G98" s="26"/>
-      <c r="H98" s="25"/>
-      <c r="I98" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="J98" s="1" t="n">
-        <f aca="false">J97+D97</f>
-        <v>32</v>
-      </c>
-      <c r="K98" s="1" t="n">
-        <f aca="false">J98/8</f>
-        <v>4</v>
-      </c>
-      <c r="L98" s="1" t="n">
-        <f aca="false">J98/16</f>
-        <v>2</v>
-      </c>
-      <c r="M98" s="1" t="n">
-        <f aca="false">J98/32</f>
-        <v>1</v>
-      </c>
-      <c r="O98" s="17"/>
-    </row>
-    <row r="99" s="13" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B99" s="24"/>
       <c r="C99" s="25"/>
       <c r="D99" s="26"/>
@@ -5658,105 +5693,85 @@
       <c r="F99" s="26"/>
       <c r="G99" s="26"/>
       <c r="H99" s="25"/>
-      <c r="I99" s="26"/>
-      <c r="J99" s="22"/>
-      <c r="K99" s="22"/>
-      <c r="L99" s="22"/>
-      <c r="M99" s="22"/>
+      <c r="I99" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="J99" s="1" t="n">
+        <f aca="false">J98+D98</f>
+        <v>32</v>
+      </c>
+      <c r="K99" s="1" t="n">
+        <f aca="false">J99/8</f>
+        <v>4</v>
+      </c>
+      <c r="L99" s="1" t="n">
+        <f aca="false">J99/16</f>
+        <v>2</v>
+      </c>
+      <c r="M99" s="1" t="n">
+        <f aca="false">J99/32</f>
+        <v>1</v>
+      </c>
       <c r="O99" s="17"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B100" s="20"/>
+    <row r="100" s="13" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B100" s="24"/>
+      <c r="C100" s="25"/>
+      <c r="D100" s="26"/>
+      <c r="E100" s="26"/>
+      <c r="F100" s="26"/>
+      <c r="G100" s="26"/>
+      <c r="H100" s="25"/>
+      <c r="I100" s="26"/>
+      <c r="J100" s="22"/>
+      <c r="K100" s="22"/>
+      <c r="L100" s="22"/>
+      <c r="M100" s="22"/>
+      <c r="O100" s="17"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B101" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="C101" s="23" t="s">
-        <v>224</v>
-      </c>
-      <c r="D101" s="21" t="n">
-        <v>32</v>
-      </c>
-      <c r="E101" s="27" t="s">
-        <v>225</v>
-      </c>
-      <c r="F101" s="19"/>
-      <c r="G101" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3" t="s">
+      <c r="A101" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="I101" s="22" t="s">
-        <v>227</v>
-      </c>
-      <c r="J101" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" s="22" t="n">
-        <f aca="false">J101/8</f>
-        <v>0</v>
-      </c>
-      <c r="L101" s="22" t="n">
-        <f aca="false">J101/16</f>
-        <v>0</v>
-      </c>
-      <c r="M101" s="22" t="n">
-        <f aca="false">J101/32</f>
-        <v>0</v>
-      </c>
-      <c r="N101" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="B101" s="20"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B102" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="C102" s="23" t="s">
         <v>228</v>
       </c>
-      <c r="C102" s="23" t="s">
+      <c r="D102" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="E102" s="27" t="s">
         <v>229</v>
-      </c>
-      <c r="D102" s="21" t="n">
-        <v>16</v>
-      </c>
-      <c r="E102" s="27" t="s">
-        <v>25</v>
       </c>
       <c r="F102" s="19"/>
       <c r="G102" s="18" t="n">
         <v>0</v>
       </c>
+      <c r="H102" s="3" t="s">
+        <v>230</v>
+      </c>
       <c r="I102" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="J102" s="1" t="n">
-        <f aca="false">J101+D101</f>
-        <v>32</v>
-      </c>
-      <c r="K102" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="J102" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="22" t="n">
         <f aca="false">J102/8</f>
-        <v>4</v>
-      </c>
-      <c r="L102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="22" t="n">
         <f aca="false">J102/16</f>
-        <v>2</v>
-      </c>
-      <c r="M102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="22" t="n">
         <f aca="false">J102/32</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N102" s="1" t="s">
         <v>28</v>
@@ -5773,42 +5788,39 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="23" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C103" s="23" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D103" s="21" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E103" s="27" t="s">
-        <v>225</v>
+        <v>25</v>
       </c>
       <c r="F103" s="19"/>
       <c r="G103" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H103" s="18" t="s">
-        <v>34</v>
-      </c>
       <c r="I103" s="22" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J103" s="1" t="n">
         <f aca="false">J102+D102</f>
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K103" s="1" t="n">
         <f aca="false">J103/8</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L103" s="1" t="n">
         <f aca="false">J103/16</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M103" s="1" t="n">
         <f aca="false">J103/32</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="N103" s="1" t="s">
         <v>28</v>
@@ -5825,15 +5837,17 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B104" s="23" t="s">
-        <v>129</v>
+        <v>235</v>
       </c>
       <c r="C104" s="23" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D104" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E104" s="27"/>
+      <c r="E104" s="27" t="s">
+        <v>229</v>
+      </c>
       <c r="F104" s="19"/>
       <c r="G104" s="18" t="n">
         <v>0</v>
@@ -5842,23 +5856,23 @@
         <v>34</v>
       </c>
       <c r="I104" s="22" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J104" s="1" t="n">
         <f aca="false">J103+D103</f>
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="K104" s="1" t="n">
         <f aca="false">J104/8</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L104" s="1" t="n">
         <f aca="false">J104/16</f>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="M104" s="1" t="n">
         <f aca="false">J104/32</f>
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="N104" s="1" t="s">
         <v>28</v>
@@ -5873,133 +5887,134 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B105" s="20"/>
-      <c r="C105" s="25"/>
-      <c r="D105" s="26"/>
-      <c r="E105" s="26"/>
-      <c r="F105" s="26"/>
-      <c r="G105" s="26"/>
-      <c r="H105" s="25"/>
-      <c r="I105" s="26" t="s">
-        <v>219</v>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B105" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="C105" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="D105" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E105" s="27"/>
+      <c r="F105" s="19"/>
+      <c r="G105" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I105" s="22" t="s">
+        <v>239</v>
       </c>
       <c r="J105" s="1" t="n">
         <f aca="false">J104+D104</f>
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="K105" s="1" t="n">
         <f aca="false">J105/8</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L105" s="1" t="n">
         <f aca="false">J105/16</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="M105" s="1" t="n">
         <f aca="false">J105/32</f>
+        <v>1.75</v>
+      </c>
+      <c r="N105" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B106" s="20"/>
+      <c r="C106" s="25"/>
+      <c r="D106" s="26"/>
+      <c r="E106" s="26"/>
+      <c r="F106" s="26"/>
+      <c r="G106" s="26"/>
+      <c r="H106" s="25"/>
+      <c r="I106" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="J106" s="1" t="n">
+        <f aca="false">J105+D105</f>
+        <v>64</v>
+      </c>
+      <c r="K106" s="1" t="n">
+        <f aca="false">J106/8</f>
+        <v>8</v>
+      </c>
+      <c r="L106" s="1" t="n">
+        <f aca="false">J106/16</f>
+        <v>4</v>
+      </c>
+      <c r="M106" s="1" t="n">
+        <f aca="false">J106/32</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B106" s="20"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B107" s="20"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="B108" s="20"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B109" s="23" t="s">
-        <v>237</v>
-      </c>
-      <c r="C109" s="23" t="s">
-        <v>238</v>
-      </c>
-      <c r="D109" s="21" t="n">
-        <v>32</v>
-      </c>
-      <c r="E109" s="27"/>
-      <c r="F109" s="19"/>
-      <c r="G109" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="I109" s="22" t="s">
-        <v>227</v>
-      </c>
-      <c r="J109" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" s="22" t="n">
-        <f aca="false">J109/8</f>
-        <v>0</v>
-      </c>
-      <c r="L109" s="22" t="n">
-        <f aca="false">J109/16</f>
-        <v>0</v>
-      </c>
-      <c r="M109" s="22" t="n">
-        <f aca="false">J109/32</f>
-        <v>0</v>
-      </c>
-      <c r="N109" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O109" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P109" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q109" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="A109" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B109" s="20"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B110" s="23" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C110" s="23" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D110" s="21" t="n">
-        <v>16</v>
-      </c>
-      <c r="E110" s="27" t="s">
-        <v>25</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="E110" s="27"/>
       <c r="F110" s="19"/>
       <c r="G110" s="18" t="n">
         <v>0</v>
       </c>
+      <c r="H110" s="3" t="s">
+        <v>230</v>
+      </c>
       <c r="I110" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="J110" s="1" t="n">
-        <f aca="false">J109+D109</f>
-        <v>32</v>
-      </c>
-      <c r="K110" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="J110" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="22" t="n">
         <f aca="false">J110/8</f>
-        <v>4</v>
-      </c>
-      <c r="L110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="22" t="n">
         <f aca="false">J110/16</f>
-        <v>2</v>
-      </c>
-      <c r="M110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="22" t="n">
         <f aca="false">J110/32</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N110" s="1" t="s">
         <v>28</v>
@@ -6016,37 +6031,39 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B111" s="23" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C111" s="23" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D111" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="E111" s="27"/>
+      <c r="E111" s="27" t="s">
+        <v>25</v>
+      </c>
       <c r="F111" s="19"/>
       <c r="G111" s="18" t="n">
         <v>0</v>
       </c>
       <c r="I111" s="22" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="J111" s="1" t="n">
         <f aca="false">J110+D110</f>
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K111" s="1" t="n">
         <f aca="false">J111/8</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L111" s="1" t="n">
         <f aca="false">J111/16</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M111" s="1" t="n">
         <f aca="false">J111/32</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="N111" s="1" t="s">
         <v>28</v>
@@ -6063,13 +6080,13 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B112" s="23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C112" s="23" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D112" s="21" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E112" s="27"/>
       <c r="F112" s="19"/>
@@ -6077,23 +6094,23 @@
         <v>0</v>
       </c>
       <c r="I112" s="22" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J112" s="1" t="n">
         <f aca="false">J111+D111</f>
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="K112" s="1" t="n">
         <f aca="false">J112/8</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L112" s="1" t="n">
         <f aca="false">J112/16</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M112" s="1" t="n">
         <f aca="false">J112/32</f>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="N112" s="1" t="s">
         <v>28</v>
@@ -6110,42 +6127,37 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B113" s="23" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C113" s="23" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D113" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="E113" s="27" t="s">
-        <v>225</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="E113" s="27"/>
       <c r="F113" s="19"/>
       <c r="G113" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H113" s="18" t="s">
-        <v>34</v>
-      </c>
       <c r="I113" s="22" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J113" s="1" t="n">
         <f aca="false">J112+D112</f>
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="K113" s="1" t="n">
         <f aca="false">J113/8</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L113" s="1" t="n">
         <f aca="false">J113/16</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M113" s="1" t="n">
         <f aca="false">J113/32</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N113" s="1" t="s">
         <v>28</v>
@@ -6162,16 +6174,16 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B114" s="23" t="s">
-        <v>129</v>
+        <v>251</v>
       </c>
       <c r="C114" s="23" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D114" s="21" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E114" s="27" t="s">
-        <v>65</v>
+        <v>229</v>
       </c>
       <c r="F114" s="19"/>
       <c r="G114" s="18" t="n">
@@ -6180,22 +6192,24 @@
       <c r="H114" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="I114" s="22"/>
+      <c r="I114" s="22" t="s">
+        <v>253</v>
+      </c>
       <c r="J114" s="1" t="n">
         <f aca="false">J113+D113</f>
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="K114" s="1" t="n">
         <f aca="false">J114/8</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L114" s="1" t="n">
         <f aca="false">J114/16</f>
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="M114" s="1" t="n">
         <f aca="false">J114/32</f>
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N114" s="1" t="s">
         <v>28</v>
@@ -6210,115 +6224,114 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B115" s="24"/>
-      <c r="C115" s="25"/>
-      <c r="D115" s="26"/>
-      <c r="E115" s="26"/>
-      <c r="F115" s="26"/>
-      <c r="G115" s="26"/>
-      <c r="H115" s="25"/>
-      <c r="I115" s="26" t="s">
-        <v>219</v>
-      </c>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B115" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="C115" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="D115" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="E115" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F115" s="19"/>
+      <c r="G115" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I115" s="22"/>
       <c r="J115" s="1" t="n">
         <f aca="false">J114+D114</f>
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="K115" s="1" t="n">
         <f aca="false">J115/8</f>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L115" s="1" t="n">
         <f aca="false">J115/16</f>
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="M115" s="1" t="n">
         <f aca="false">J115/32</f>
+        <v>3.25</v>
+      </c>
+      <c r="N115" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B116" s="24"/>
+      <c r="C116" s="25"/>
+      <c r="D116" s="26"/>
+      <c r="E116" s="26"/>
+      <c r="F116" s="26"/>
+      <c r="G116" s="26"/>
+      <c r="H116" s="25"/>
+      <c r="I116" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="J116" s="1" t="n">
+        <f aca="false">J115+D115</f>
+        <v>128</v>
+      </c>
+      <c r="K116" s="1" t="n">
+        <f aca="false">J116/8</f>
+        <v>16</v>
+      </c>
+      <c r="L116" s="1" t="n">
+        <f aca="false">J116/16</f>
+        <v>8</v>
+      </c>
+      <c r="M116" s="1" t="n">
+        <f aca="false">J116/32</f>
         <v>4</v>
       </c>
-    </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B116" s="20"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B117" s="20"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="B118" s="20"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="B119" s="20"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B120" s="23" t="s">
-        <v>252</v>
-      </c>
-      <c r="C120" s="23" t="s">
-        <v>253</v>
-      </c>
-      <c r="D120" s="21" t="n">
-        <v>32</v>
-      </c>
-      <c r="E120" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="F120" s="19"/>
-      <c r="G120" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" s="28" t="s">
-        <v>226</v>
-      </c>
-      <c r="I120" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="J120" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" s="22" t="n">
-        <f aca="false">J120/8</f>
-        <v>0</v>
-      </c>
-      <c r="L120" s="22" t="n">
-        <f aca="false">J120/16</f>
-        <v>0</v>
-      </c>
-      <c r="M120" s="22" t="n">
-        <f aca="false">J120/32</f>
-        <v>0</v>
-      </c>
-      <c r="N120" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="O120" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P120" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q120" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="A120" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B120" s="20"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B121" s="23" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C121" s="23" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D121" s="21" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E121" s="27" t="s">
         <v>25</v>
@@ -6328,26 +6341,25 @@
         <v>0</v>
       </c>
       <c r="H121" s="28" t="s">
-        <v>34</v>
+        <v>230</v>
       </c>
       <c r="I121" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="J121" s="1" t="n">
-        <f aca="false">J120+D120</f>
-        <v>32</v>
-      </c>
-      <c r="K121" s="1" t="n">
+        <v>258</v>
+      </c>
+      <c r="J121" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" s="22" t="n">
         <f aca="false">J121/8</f>
-        <v>4</v>
-      </c>
-      <c r="L121" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="22" t="n">
         <f aca="false">J121/16</f>
-        <v>2</v>
-      </c>
-      <c r="M121" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="22" t="n">
         <f aca="false">J121/32</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N121" s="1" t="s">
         <v>44</v>
@@ -6356,7 +6368,7 @@
         <v>1</v>
       </c>
       <c r="P121" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q121" s="1" t="n">
         <v>0</v>
@@ -6364,13 +6376,13 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B122" s="23" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C122" s="23" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D122" s="21" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E122" s="27" t="s">
         <v>25</v>
@@ -6379,27 +6391,27 @@
       <c r="G122" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H122" s="18" t="s">
+      <c r="H122" s="28" t="s">
         <v>34</v>
       </c>
       <c r="I122" s="22" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J122" s="1" t="n">
         <f aca="false">J121+D121</f>
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="K122" s="1" t="n">
         <f aca="false">J122/8</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L122" s="1" t="n">
         <f aca="false">J122/16</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M122" s="1" t="n">
         <f aca="false">J122/32</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="N122" s="1" t="s">
         <v>44</v>
@@ -6408,7 +6420,7 @@
         <v>1</v>
       </c>
       <c r="P122" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q122" s="1" t="n">
         <v>0</v>
@@ -6416,16 +6428,16 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B123" s="23" t="s">
-        <v>129</v>
+        <v>261</v>
       </c>
       <c r="C123" s="23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D123" s="21" t="n">
         <v>8</v>
       </c>
       <c r="E123" s="27" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="F123" s="19"/>
       <c r="G123" s="18" t="n">
@@ -6435,185 +6447,186 @@
         <v>34</v>
       </c>
       <c r="I123" s="22" t="s">
-        <v>141</v>
+        <v>263</v>
       </c>
       <c r="J123" s="1" t="n">
         <f aca="false">J122+D122</f>
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="K123" s="1" t="n">
         <f aca="false">J123/8</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L123" s="1" t="n">
         <f aca="false">J123/16</f>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="M123" s="1" t="n">
         <f aca="false">J123/32</f>
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="N123" s="1" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="O123" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P123" s="1" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q123" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B124" s="23"/>
-      <c r="I124" s="1" t="s">
-        <v>132</v>
+      <c r="B124" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="C124" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="D124" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E124" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="F124" s="19"/>
+      <c r="G124" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I124" s="22" t="s">
+        <v>116</v>
       </c>
       <c r="J124" s="1" t="n">
         <f aca="false">J123+D123</f>
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="K124" s="1" t="n">
         <f aca="false">J124/8</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L124" s="1" t="n">
         <f aca="false">J124/16</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="M124" s="1" t="n">
         <f aca="false">J124/32</f>
+        <v>1.75</v>
+      </c>
+      <c r="N124" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B125" s="23"/>
+      <c r="I125" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J125" s="1" t="n">
+        <f aca="false">J124+D124</f>
+        <v>64</v>
+      </c>
+      <c r="K125" s="1" t="n">
+        <f aca="false">J125/8</f>
+        <v>8</v>
+      </c>
+      <c r="L125" s="1" t="n">
+        <f aca="false">J125/16</f>
+        <v>4</v>
+      </c>
+      <c r="M125" s="1" t="n">
+        <f aca="false">J125/32</f>
         <v>2</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="29" t="s">
-        <v>261</v>
-      </c>
-      <c r="J126" s="30"/>
-      <c r="K126" s="22"/>
-      <c r="L126" s="22"/>
-      <c r="M126" s="22"/>
-      <c r="N126" s="13" t="s">
+    <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="29" t="s">
+        <v>265</v>
+      </c>
+      <c r="J127" s="30"/>
+      <c r="K127" s="22"/>
+      <c r="L127" s="22"/>
+      <c r="M127" s="22"/>
+      <c r="N127" s="13" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="127" s="13" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B127" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C127" s="11" t="s">
+    <row r="128" s="13" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B128" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C128" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D127" s="11" t="s">
+      <c r="D128" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E127" s="11" t="s">
+      <c r="E128" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F127" s="11" t="s">
+      <c r="F128" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="G127" s="11" t="s">
+      <c r="G128" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H127" s="11" t="s">
+      <c r="H128" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="I127" s="12" t="s">
+      <c r="I128" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="J127" s="13" t="s">
+      <c r="J128" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="K127" s="13" t="s">
+      <c r="K128" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="L127" s="13" t="s">
+      <c r="L128" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="M127" s="13" t="s">
+      <c r="M128" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="N127" s="1"/>
-      <c r="O127" s="17" t="s">
+      <c r="N128" s="1"/>
+      <c r="O128" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="P127" s="13" t="s">
+      <c r="P128" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="Q127" s="13" t="s">
+      <c r="Q128" s="13" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="128" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B128" s="18" t="s">
-        <v>262</v>
-      </c>
-      <c r="C128" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="D128" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="E128" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="F128" s="33"/>
-      <c r="G128" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="H128" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="I128" s="27" t="s">
-        <v>264</v>
-      </c>
-      <c r="J128" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" s="22" t="n">
-        <f aca="false">J128/8</f>
-        <v>0</v>
-      </c>
-      <c r="L128" s="22" t="n">
-        <f aca="false">J128/16</f>
-        <v>0</v>
-      </c>
-      <c r="M128" s="22" t="n">
-        <f aca="false">J128/32</f>
-        <v>0</v>
-      </c>
-      <c r="N128" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="O128" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P128" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q128" s="1" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="129" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B129" s="18" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C129" s="32" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D129" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E129" s="27" t="s">
         <v>25</v>
@@ -6626,32 +6639,31 @@
         <v>34</v>
       </c>
       <c r="I129" s="27" t="s">
-        <v>264</v>
-      </c>
-      <c r="J129" s="1" t="n">
-        <f aca="false">J128+D128</f>
-        <v>9</v>
-      </c>
-      <c r="K129" s="1" t="n">
+        <v>268</v>
+      </c>
+      <c r="J129" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" s="22" t="n">
         <f aca="false">J129/8</f>
-        <v>1.125</v>
-      </c>
-      <c r="L129" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="22" t="n">
         <f aca="false">J129/16</f>
-        <v>0.5625</v>
-      </c>
-      <c r="M129" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="22" t="n">
         <f aca="false">J129/32</f>
-        <v>0.28125</v>
+        <v>0</v>
       </c>
       <c r="N129" s="1" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="O129" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P129" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q129" s="1" t="n">
         <v>0</v>
@@ -6659,13 +6671,13 @@
     </row>
     <row r="130" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B130" s="18" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C130" s="32" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D130" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E130" s="27" t="s">
         <v>25</v>
@@ -6678,32 +6690,32 @@
         <v>34</v>
       </c>
       <c r="I130" s="27" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J130" s="1" t="n">
         <f aca="false">J129+D129</f>
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K130" s="1" t="n">
         <f aca="false">J130/8</f>
-        <v>1.75</v>
+        <v>1.125</v>
       </c>
       <c r="L130" s="1" t="n">
         <f aca="false">J130/16</f>
-        <v>0.875</v>
+        <v>0.5625</v>
       </c>
       <c r="M130" s="1" t="n">
         <f aca="false">J130/32</f>
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="N130" s="1" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="O130" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P130" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q130" s="1" t="n">
         <v>0</v>
@@ -6711,10 +6723,10 @@
     </row>
     <row r="131" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B131" s="18" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C131" s="32" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D131" s="1" t="n">
         <v>4</v>
@@ -6730,32 +6742,32 @@
         <v>34</v>
       </c>
       <c r="I131" s="27" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J131" s="1" t="n">
         <f aca="false">J130+D130</f>
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K131" s="1" t="n">
         <f aca="false">J131/8</f>
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="L131" s="1" t="n">
         <f aca="false">J131/16</f>
-        <v>1.125</v>
+        <v>0.875</v>
       </c>
       <c r="M131" s="1" t="n">
         <f aca="false">J131/32</f>
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="N131" s="1" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="O131" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P131" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q131" s="1" t="n">
         <v>0</v>
@@ -6763,51 +6775,51 @@
     </row>
     <row r="132" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B132" s="18" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C132" s="32" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D132" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E132" s="27" t="s">
         <v>25</v>
       </c>
       <c r="F132" s="33"/>
-      <c r="G132" s="18" t="n">
+      <c r="G132" s="27" t="n">
         <v>2</v>
       </c>
       <c r="H132" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I132" s="18" t="s">
-        <v>275</v>
+      <c r="I132" s="27" t="s">
+        <v>276</v>
       </c>
       <c r="J132" s="1" t="n">
         <f aca="false">J131+D131</f>
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K132" s="1" t="n">
         <f aca="false">J132/8</f>
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="L132" s="1" t="n">
         <f aca="false">J132/16</f>
-        <v>1.375</v>
+        <v>1.125</v>
       </c>
       <c r="M132" s="1" t="n">
         <f aca="false">J132/32</f>
-        <v>0.6875</v>
+        <v>0.5625</v>
       </c>
       <c r="N132" s="1" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="O132" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P132" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q132" s="1" t="n">
         <v>0</v>
@@ -6815,13 +6827,13 @@
     </row>
     <row r="133" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B133" s="18" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C133" s="32" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D133" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E133" s="27" t="s">
         <v>25</v>
@@ -6834,32 +6846,32 @@
         <v>34</v>
       </c>
       <c r="I133" s="18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J133" s="1" t="n">
         <f aca="false">J132+D132</f>
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K133" s="1" t="n">
         <f aca="false">J133/8</f>
-        <v>3.125</v>
+        <v>2.75</v>
       </c>
       <c r="L133" s="1" t="n">
         <f aca="false">J133/16</f>
-        <v>1.5625</v>
+        <v>1.375</v>
       </c>
       <c r="M133" s="1" t="n">
         <f aca="false">J133/32</f>
-        <v>0.78125</v>
+        <v>0.6875</v>
       </c>
       <c r="N133" s="1" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="O133" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P133" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q133" s="1" t="n">
         <v>0</v>
@@ -6867,10 +6879,10 @@
     </row>
     <row r="134" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B134" s="18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C134" s="32" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D134" s="1" t="n">
         <v>1</v>
@@ -6880,38 +6892,38 @@
       </c>
       <c r="F134" s="33"/>
       <c r="G134" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H134" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I134" s="27" t="s">
-        <v>264</v>
+      <c r="I134" s="18" t="s">
+        <v>282</v>
       </c>
       <c r="J134" s="1" t="n">
         <f aca="false">J133+D133</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K134" s="1" t="n">
         <f aca="false">J134/8</f>
-        <v>3.25</v>
+        <v>3.125</v>
       </c>
       <c r="L134" s="1" t="n">
         <f aca="false">J134/16</f>
-        <v>1.625</v>
+        <v>1.5625</v>
       </c>
       <c r="M134" s="1" t="n">
         <f aca="false">J134/32</f>
-        <v>0.8125</v>
+        <v>0.78125</v>
       </c>
       <c r="N134" s="1" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="O134" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P134" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q134" s="1" t="n">
         <v>0</v>
@@ -6919,51 +6931,51 @@
     </row>
     <row r="135" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B135" s="18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C135" s="32" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D135" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E135" s="27" t="s">
         <v>25</v>
       </c>
       <c r="F135" s="33"/>
       <c r="G135" s="18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H135" s="27" t="s">
         <v>34</v>
       </c>
       <c r="I135" s="27" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="J135" s="1" t="n">
         <f aca="false">J134+D134</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K135" s="1" t="n">
         <f aca="false">J135/8</f>
-        <v>3.375</v>
+        <v>3.25</v>
       </c>
       <c r="L135" s="1" t="n">
         <f aca="false">J135/16</f>
-        <v>1.6875</v>
+        <v>1.625</v>
       </c>
       <c r="M135" s="1" t="n">
         <f aca="false">J135/32</f>
-        <v>0.84375</v>
+        <v>0.8125</v>
       </c>
       <c r="N135" s="1" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P135" s="1" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q135" s="1" t="n">
         <v>0</v>
@@ -6971,103 +6983,103 @@
     </row>
     <row r="136" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B136" s="18" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C136" s="32" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D136" s="1" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="E136" s="27" t="s">
         <v>25</v>
       </c>
       <c r="F136" s="33"/>
       <c r="G136" s="18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H136" s="27" t="s">
         <v>34</v>
       </c>
       <c r="I136" s="27" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="J136" s="1" t="n">
         <f aca="false">J135+D135</f>
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K136" s="1" t="n">
         <f aca="false">J136/8</f>
-        <v>4</v>
+        <v>3.375</v>
       </c>
       <c r="L136" s="1" t="n">
         <f aca="false">J136/16</f>
-        <v>2</v>
+        <v>1.6875</v>
       </c>
       <c r="M136" s="1" t="n">
         <f aca="false">J136/32</f>
-        <v>1</v>
+        <v>0.84375</v>
       </c>
       <c r="N136" s="1" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="O136" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P136" s="1" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q136" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" s="31" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B137" s="18" t="s">
-        <v>285</v>
-      </c>
-      <c r="C137" s="18" t="s">
-        <v>286</v>
+        <v>287</v>
+      </c>
+      <c r="C137" s="32" t="s">
+        <v>288</v>
       </c>
       <c r="D137" s="1" t="n">
         <v>32</v>
       </c>
       <c r="E137" s="27" t="s">
-        <v>225</v>
-      </c>
-      <c r="F137" s="27"/>
+        <v>25</v>
+      </c>
+      <c r="F137" s="33"/>
       <c r="G137" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H137" s="27" t="s">
         <v>34</v>
       </c>
       <c r="I137" s="27" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="J137" s="1" t="n">
         <f aca="false">J136+D136</f>
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="K137" s="1" t="n">
         <f aca="false">J137/8</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L137" s="1" t="n">
         <f aca="false">J137/16</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M137" s="1" t="n">
         <f aca="false">J137/32</f>
+        <v>1</v>
+      </c>
+      <c r="N137" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O137" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="N137" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="O137" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="P137" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q137" s="1" t="n">
         <v>0</v>
@@ -7075,16 +7087,16 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B138" s="18" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C138" s="18" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D138" s="1" t="n">
         <v>32</v>
       </c>
       <c r="E138" s="27" t="s">
-        <v>25</v>
+        <v>229</v>
       </c>
       <c r="F138" s="27"/>
       <c r="G138" s="18" t="n">
@@ -7094,32 +7106,32 @@
         <v>34</v>
       </c>
       <c r="I138" s="27" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="J138" s="1" t="n">
         <f aca="false">J137+D137</f>
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="K138" s="1" t="n">
         <f aca="false">J138/8</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L138" s="1" t="n">
         <f aca="false">J138/16</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M138" s="1" t="n">
         <f aca="false">J138/32</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N138" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="O138" s="3" t="n">
         <v>3</v>
       </c>
       <c r="P138" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q138" s="1" t="n">
         <v>0</v>
@@ -7127,16 +7139,16 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B139" s="18" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C139" s="18" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D139" s="1" t="n">
         <v>32</v>
       </c>
       <c r="E139" s="27" t="s">
-        <v>225</v>
+        <v>25</v>
       </c>
       <c r="F139" s="27"/>
       <c r="G139" s="18" t="n">
@@ -7146,32 +7158,32 @@
         <v>34</v>
       </c>
       <c r="I139" s="27" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="J139" s="1" t="n">
         <f aca="false">J138+D138</f>
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="K139" s="1" t="n">
         <f aca="false">J139/8</f>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L139" s="1" t="n">
         <f aca="false">J139/16</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M139" s="1" t="n">
         <f aca="false">J139/32</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N139" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="O139" s="3" t="n">
         <v>3</v>
       </c>
       <c r="P139" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q139" s="1" t="n">
         <v>0</v>
@@ -7179,16 +7191,16 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B140" s="18" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C140" s="18" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D140" s="1" t="n">
         <v>32</v>
       </c>
       <c r="E140" s="27" t="s">
-        <v>25</v>
+        <v>229</v>
       </c>
       <c r="F140" s="27"/>
       <c r="G140" s="18" t="n">
@@ -7198,32 +7210,32 @@
         <v>34</v>
       </c>
       <c r="I140" s="27" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="J140" s="1" t="n">
         <f aca="false">J139+D139</f>
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="K140" s="1" t="n">
         <f aca="false">J140/8</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L140" s="1" t="n">
         <f aca="false">J140/16</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M140" s="1" t="n">
         <f aca="false">J140/32</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N140" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="O140" s="3" t="n">
         <v>3</v>
       </c>
       <c r="P140" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q140" s="1" t="n">
         <v>0</v>
@@ -7231,13 +7243,13 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B141" s="18" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C141" s="18" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D141" s="1" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E141" s="27" t="s">
         <v>25</v>
@@ -7250,32 +7262,32 @@
         <v>34</v>
       </c>
       <c r="I141" s="27" t="s">
-        <v>296</v>
+        <v>268</v>
       </c>
       <c r="J141" s="1" t="n">
         <f aca="false">J140+D140</f>
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="K141" s="1" t="n">
         <f aca="false">J141/8</f>
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L141" s="1" t="n">
         <f aca="false">J141/16</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M141" s="1" t="n">
         <f aca="false">J141/32</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N141" s="1" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="O141" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P141" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q141" s="1" t="n">
         <v>0</v>
@@ -7306,28 +7318,28 @@
       </c>
       <c r="J142" s="1" t="n">
         <f aca="false">J141+D141</f>
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="K142" s="1" t="n">
         <f aca="false">J142/8</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L142" s="1" t="n">
         <f aca="false">J142/16</f>
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="M142" s="1" t="n">
         <f aca="false">J142/32</f>
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="N142" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="O142" s="3" t="n">
         <v>5</v>
       </c>
       <c r="P142" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q142" s="1" t="n">
         <v>0</v>
@@ -7335,10 +7347,10 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B143" s="18" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C143" s="18" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D143" s="1" t="n">
         <v>8</v>
@@ -7354,32 +7366,32 @@
         <v>34</v>
       </c>
       <c r="I143" s="27" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J143" s="1" t="n">
         <f aca="false">J142+D142</f>
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="K143" s="1" t="n">
         <f aca="false">J143/8</f>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L143" s="1" t="n">
         <f aca="false">J143/16</f>
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="M143" s="1" t="n">
         <f aca="false">J143/32</f>
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="N143" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="O143" s="3" t="n">
         <v>5</v>
       </c>
       <c r="P143" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q143" s="1" t="n">
         <v>0</v>
@@ -7387,10 +7399,10 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B144" s="18" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C144" s="18" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D144" s="1" t="n">
         <v>8</v>
@@ -7406,32 +7418,32 @@
         <v>34</v>
       </c>
       <c r="I144" s="27" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J144" s="1" t="n">
         <f aca="false">J143+D143</f>
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="K144" s="1" t="n">
         <f aca="false">J144/8</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L144" s="1" t="n">
         <f aca="false">J144/16</f>
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="M144" s="1" t="n">
         <f aca="false">J144/32</f>
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="O144" s="3" t="n">
         <v>5</v>
       </c>
       <c r="P144" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q144" s="1" t="n">
         <v>0</v>
@@ -7439,10 +7451,10 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B145" s="18" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C145" s="18" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D145" s="1" t="n">
         <v>8</v>
@@ -7458,32 +7470,32 @@
         <v>34</v>
       </c>
       <c r="I145" s="27" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J145" s="1" t="n">
         <f aca="false">J144+D144</f>
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="K145" s="1" t="n">
         <f aca="false">J145/8</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L145" s="1" t="n">
         <f aca="false">J145/16</f>
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="M145" s="1" t="n">
         <f aca="false">J145/32</f>
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="N145" s="1" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="O145" s="3" t="n">
         <v>5</v>
       </c>
       <c r="P145" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q145" s="1" t="n">
         <v>0</v>
@@ -7491,10 +7503,10 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B146" s="18" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C146" s="18" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D146" s="1" t="n">
         <v>8</v>
@@ -7509,33 +7521,33 @@
       <c r="H146" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I146" s="18" t="s">
-        <v>310</v>
+      <c r="I146" s="27" t="s">
+        <v>313</v>
       </c>
       <c r="J146" s="1" t="n">
         <f aca="false">J145+D145</f>
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="K146" s="1" t="n">
         <f aca="false">J146/8</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L146" s="1" t="n">
         <f aca="false">J146/16</f>
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="M146" s="1" t="n">
         <f aca="false">J146/32</f>
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="N146" s="1" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="O146" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P146" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q146" s="1" t="n">
         <v>0</v>
@@ -7543,10 +7555,10 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B147" s="18" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C147" s="18" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D147" s="1" t="n">
         <v>8</v>
@@ -7562,32 +7574,32 @@
         <v>34</v>
       </c>
       <c r="I147" s="18" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J147" s="1" t="n">
         <f aca="false">J146+D146</f>
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="K147" s="1" t="n">
         <f aca="false">J147/8</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L147" s="1" t="n">
         <f aca="false">J147/16</f>
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="M147" s="1" t="n">
         <f aca="false">J147/32</f>
-        <v>7.5</v>
+        <v>7.25</v>
       </c>
       <c r="N147" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="O147" s="3" t="n">
         <v>4</v>
       </c>
       <c r="P147" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q147" s="1" t="n">
         <v>0</v>
@@ -7595,10 +7607,10 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B148" s="18" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C148" s="18" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D148" s="1" t="n">
         <v>8</v>
@@ -7614,32 +7626,32 @@
         <v>34</v>
       </c>
       <c r="I148" s="18" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J148" s="1" t="n">
         <f aca="false">J147+D147</f>
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="K148" s="1" t="n">
         <f aca="false">J148/8</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L148" s="1" t="n">
         <f aca="false">J148/16</f>
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="M148" s="1" t="n">
         <f aca="false">J148/32</f>
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="N148" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="O148" s="3" t="n">
         <v>4</v>
       </c>
       <c r="P148" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q148" s="1" t="n">
         <v>0</v>
@@ -7647,10 +7659,10 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B149" s="18" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C149" s="18" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D149" s="1" t="n">
         <v>8</v>
@@ -7666,32 +7678,32 @@
         <v>34</v>
       </c>
       <c r="I149" s="18" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="J149" s="1" t="n">
         <f aca="false">J148+D148</f>
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="K149" s="1" t="n">
         <f aca="false">J149/8</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L149" s="1" t="n">
         <f aca="false">J149/16</f>
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="M149" s="1" t="n">
         <f aca="false">J149/32</f>
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="N149" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="O149" s="3" t="n">
         <v>4</v>
       </c>
       <c r="P149" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q149" s="1" t="n">
         <v>0</v>
@@ -7699,10 +7711,10 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B150" s="18" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C150" s="18" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D150" s="1" t="n">
         <v>8</v>
@@ -7718,32 +7730,32 @@
         <v>34</v>
       </c>
       <c r="I150" s="18" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J150" s="1" t="n">
         <f aca="false">J149+D149</f>
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="K150" s="1" t="n">
         <f aca="false">J150/8</f>
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L150" s="1" t="n">
         <f aca="false">J150/16</f>
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="M150" s="1" t="n">
         <f aca="false">J150/32</f>
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="N150" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="O150" s="3" t="n">
         <v>4</v>
       </c>
       <c r="P150" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q150" s="1" t="n">
         <v>0</v>
@@ -7751,10 +7763,10 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B151" s="18" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C151" s="18" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D151" s="1" t="n">
         <v>8</v>
@@ -7770,32 +7782,32 @@
         <v>34</v>
       </c>
       <c r="I151" s="18" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J151" s="1" t="n">
         <f aca="false">J150+D150</f>
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="K151" s="1" t="n">
         <f aca="false">J151/8</f>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L151" s="1" t="n">
         <f aca="false">J151/16</f>
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="M151" s="1" t="n">
         <f aca="false">J151/32</f>
-        <v>8.5</v>
+        <v>8.25</v>
       </c>
       <c r="N151" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="O151" s="3" t="n">
         <v>4</v>
       </c>
       <c r="P151" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q151" s="1" t="n">
         <v>0</v>
@@ -7803,10 +7815,10 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B152" s="18" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C152" s="18" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D152" s="1" t="n">
         <v>8</v>
@@ -7822,32 +7834,32 @@
         <v>34</v>
       </c>
       <c r="I152" s="18" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="J152" s="1" t="n">
         <f aca="false">J151+D151</f>
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="K152" s="1" t="n">
         <f aca="false">J152/8</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L152" s="1" t="n">
         <f aca="false">J152/16</f>
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="M152" s="1" t="n">
         <f aca="false">J152/32</f>
-        <v>8.75</v>
+        <v>8.5</v>
       </c>
       <c r="N152" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="O152" s="3" t="n">
         <v>4</v>
       </c>
       <c r="P152" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q152" s="1" t="n">
         <v>0</v>
@@ -7855,10 +7867,10 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B153" s="18" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C153" s="18" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D153" s="1" t="n">
         <v>8</v>
@@ -7874,32 +7886,32 @@
         <v>34</v>
       </c>
       <c r="I153" s="18" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="J153" s="1" t="n">
         <f aca="false">J152+D152</f>
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="K153" s="1" t="n">
         <f aca="false">J153/8</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L153" s="1" t="n">
         <f aca="false">J153/16</f>
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="M153" s="1" t="n">
         <f aca="false">J153/32</f>
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="N153" s="1" t="s">
-        <v>287</v>
+        <v>316</v>
       </c>
       <c r="O153" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P153" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q153" s="1" t="n">
         <v>0</v>
@@ -7907,10 +7919,10 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B154" s="18" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C154" s="18" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D154" s="1" t="n">
         <v>8</v>
@@ -7926,32 +7938,32 @@
         <v>34</v>
       </c>
       <c r="I154" s="18" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J154" s="1" t="n">
         <f aca="false">J153+D153</f>
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="K154" s="1" t="n">
         <f aca="false">J154/8</f>
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L154" s="1" t="n">
         <f aca="false">J154/16</f>
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="M154" s="1" t="n">
         <f aca="false">J154/32</f>
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="N154" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="O154" s="3" t="n">
         <v>3</v>
       </c>
       <c r="P154" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q154" s="1" t="n">
         <v>0</v>
@@ -7959,10 +7971,10 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B155" s="18" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C155" s="18" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D155" s="1" t="n">
         <v>8</v>
@@ -7978,32 +7990,32 @@
         <v>34</v>
       </c>
       <c r="I155" s="18" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="J155" s="1" t="n">
         <f aca="false">J154+D154</f>
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="K155" s="1" t="n">
         <f aca="false">J155/8</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L155" s="1" t="n">
         <f aca="false">J155/16</f>
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="M155" s="1" t="n">
         <f aca="false">J155/32</f>
-        <v>9.5</v>
+        <v>9.25</v>
       </c>
       <c r="N155" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="O155" s="3" t="n">
         <v>3</v>
       </c>
       <c r="P155" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q155" s="1" t="n">
         <v>0</v>
@@ -8011,10 +8023,10 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B156" s="18" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C156" s="18" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D156" s="1" t="n">
         <v>8</v>
@@ -8030,32 +8042,32 @@
         <v>34</v>
       </c>
       <c r="I156" s="18" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J156" s="1" t="n">
         <f aca="false">J155+D155</f>
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="K156" s="1" t="n">
         <f aca="false">J156/8</f>
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L156" s="1" t="n">
         <f aca="false">J156/16</f>
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="M156" s="1" t="n">
         <f aca="false">J156/32</f>
-        <v>9.75</v>
+        <v>9.5</v>
       </c>
       <c r="N156" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="O156" s="3" t="n">
         <v>3</v>
       </c>
       <c r="P156" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q156" s="1" t="n">
         <v>0</v>
@@ -8063,10 +8075,10 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B157" s="18" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C157" s="18" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D157" s="1" t="n">
         <v>8</v>
@@ -8082,32 +8094,32 @@
         <v>34</v>
       </c>
       <c r="I157" s="18" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J157" s="1" t="n">
         <f aca="false">J156+D156</f>
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="K157" s="1" t="n">
         <f aca="false">J157/8</f>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L157" s="1" t="n">
         <f aca="false">J157/16</f>
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="M157" s="1" t="n">
         <f aca="false">J157/32</f>
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="N157" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="O157" s="3" t="n">
         <v>3</v>
       </c>
       <c r="P157" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q157" s="1" t="n">
         <v>0</v>
@@ -8115,10 +8127,10 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B158" s="18" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C158" s="18" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D158" s="1" t="n">
         <v>8</v>
@@ -8134,32 +8146,32 @@
         <v>34</v>
       </c>
       <c r="I158" s="18" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J158" s="1" t="n">
         <f aca="false">J157+D157</f>
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="K158" s="1" t="n">
         <f aca="false">J158/8</f>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L158" s="1" t="n">
         <f aca="false">J158/16</f>
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="M158" s="1" t="n">
         <f aca="false">J158/32</f>
-        <v>10.25</v>
+        <v>10</v>
       </c>
       <c r="N158" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="O158" s="3" t="n">
         <v>3</v>
       </c>
       <c r="P158" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q158" s="1" t="n">
         <v>0</v>
@@ -8167,10 +8179,10 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B159" s="18" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C159" s="18" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D159" s="1" t="n">
         <v>8</v>
@@ -8186,32 +8198,32 @@
         <v>34</v>
       </c>
       <c r="I159" s="18" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J159" s="1" t="n">
         <f aca="false">J158+D158</f>
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="K159" s="1" t="n">
         <f aca="false">J159/8</f>
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L159" s="1" t="n">
         <f aca="false">J159/16</f>
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="M159" s="1" t="n">
         <f aca="false">J159/32</f>
-        <v>10.5</v>
+        <v>10.25</v>
       </c>
       <c r="N159" s="1" t="s">
-        <v>109</v>
+        <v>291</v>
       </c>
       <c r="O159" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P159" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q159" s="1" t="n">
         <v>0</v>
@@ -8219,10 +8231,10 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B160" s="18" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C160" s="18" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D160" s="1" t="n">
         <v>8</v>
@@ -8238,32 +8250,32 @@
         <v>34</v>
       </c>
       <c r="I160" s="18" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J160" s="1" t="n">
         <f aca="false">J159+D159</f>
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="K160" s="1" t="n">
         <f aca="false">J160/8</f>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L160" s="1" t="n">
         <f aca="false">J160/16</f>
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="M160" s="1" t="n">
         <f aca="false">J160/32</f>
-        <v>10.75</v>
+        <v>10.5</v>
       </c>
       <c r="N160" s="1" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="O160" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P160" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q160" s="1" t="n">
         <v>0</v>
@@ -8271,10 +8283,10 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B161" s="18" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C161" s="18" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D161" s="1" t="n">
         <v>8</v>
@@ -8290,32 +8302,32 @@
         <v>34</v>
       </c>
       <c r="I161" s="18" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J161" s="1" t="n">
         <f aca="false">J160+D160</f>
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="K161" s="1" t="n">
         <f aca="false">J161/8</f>
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L161" s="1" t="n">
         <f aca="false">J161/16</f>
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="M161" s="1" t="n">
         <f aca="false">J161/32</f>
-        <v>11</v>
+        <v>10.75</v>
       </c>
       <c r="N161" s="1" t="s">
-        <v>287</v>
+        <v>87</v>
       </c>
       <c r="O161" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P161" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q161" s="1" t="n">
         <v>0</v>
@@ -8323,10 +8335,10 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B162" s="18" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C162" s="18" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D162" s="1" t="n">
         <v>8</v>
@@ -8342,32 +8354,32 @@
         <v>34</v>
       </c>
       <c r="I162" s="18" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="J162" s="1" t="n">
         <f aca="false">J161+D161</f>
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="K162" s="1" t="n">
         <f aca="false">J162/8</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L162" s="1" t="n">
         <f aca="false">J162/16</f>
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="M162" s="1" t="n">
         <f aca="false">J162/32</f>
-        <v>11.25</v>
+        <v>11</v>
       </c>
       <c r="N162" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="O162" s="3" t="n">
         <v>3</v>
       </c>
       <c r="P162" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q162" s="1" t="n">
         <v>0</v>
@@ -8375,10 +8387,10 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B163" s="18" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C163" s="18" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D163" s="1" t="n">
         <v>8</v>
@@ -8394,32 +8406,32 @@
         <v>34</v>
       </c>
       <c r="I163" s="18" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J163" s="1" t="n">
         <f aca="false">J162+D162</f>
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="K163" s="1" t="n">
         <f aca="false">J163/8</f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L163" s="1" t="n">
         <f aca="false">J163/16</f>
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="M163" s="1" t="n">
         <f aca="false">J163/32</f>
-        <v>11.5</v>
+        <v>11.25</v>
       </c>
       <c r="N163" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="O163" s="3" t="n">
         <v>3</v>
       </c>
       <c r="P163" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q163" s="1" t="n">
         <v>0</v>
@@ -8427,10 +8439,10 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B164" s="18" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C164" s="18" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D164" s="1" t="n">
         <v>8</v>
@@ -8446,32 +8458,32 @@
         <v>34</v>
       </c>
       <c r="I164" s="18" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="J164" s="1" t="n">
         <f aca="false">J163+D163</f>
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="K164" s="1" t="n">
         <f aca="false">J164/8</f>
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L164" s="1" t="n">
         <f aca="false">J164/16</f>
-        <v>23.5</v>
+        <v>23</v>
       </c>
       <c r="M164" s="1" t="n">
         <f aca="false">J164/32</f>
-        <v>11.75</v>
+        <v>11.5</v>
       </c>
       <c r="N164" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="O164" s="3" t="n">
         <v>3</v>
       </c>
       <c r="P164" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q164" s="1" t="n">
         <v>0</v>
@@ -8479,10 +8491,10 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B165" s="18" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C165" s="18" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D165" s="1" t="n">
         <v>8</v>
@@ -8498,32 +8510,32 @@
         <v>34</v>
       </c>
       <c r="I165" s="18" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J165" s="1" t="n">
         <f aca="false">J164+D164</f>
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="K165" s="1" t="n">
         <f aca="false">J165/8</f>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L165" s="1" t="n">
         <f aca="false">J165/16</f>
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="M165" s="1" t="n">
         <f aca="false">J165/32</f>
-        <v>12</v>
+        <v>11.75</v>
       </c>
       <c r="N165" s="1" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="O165" s="3" t="n">
         <v>3</v>
       </c>
       <c r="P165" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q165" s="1" t="n">
         <v>0</v>
@@ -8531,10 +8543,10 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B166" s="18" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C166" s="18" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D166" s="1" t="n">
         <v>8</v>
@@ -8550,32 +8562,32 @@
         <v>34</v>
       </c>
       <c r="I166" s="18" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J166" s="1" t="n">
         <f aca="false">J165+D165</f>
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="K166" s="1" t="n">
         <f aca="false">J166/8</f>
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L166" s="1" t="n">
         <f aca="false">J166/16</f>
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="M166" s="1" t="n">
         <f aca="false">J166/32</f>
-        <v>12.25</v>
+        <v>12</v>
       </c>
       <c r="N166" s="1" t="s">
-        <v>109</v>
+        <v>291</v>
       </c>
       <c r="O166" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P166" s="1" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q166" s="1" t="n">
         <v>0</v>
@@ -8583,10 +8595,10 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B167" s="18" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C167" s="18" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D167" s="1" t="n">
         <v>8</v>
@@ -8602,32 +8614,32 @@
         <v>34</v>
       </c>
       <c r="I167" s="18" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J167" s="1" t="n">
         <f aca="false">J166+D166</f>
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="K167" s="1" t="n">
         <f aca="false">J167/8</f>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L167" s="1" t="n">
         <f aca="false">J167/16</f>
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="M167" s="1" t="n">
         <f aca="false">J167/32</f>
-        <v>12.5</v>
+        <v>12.25</v>
       </c>
       <c r="N167" s="1" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="O167" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P167" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q167" s="1" t="n">
         <v>0</v>
@@ -8635,10 +8647,10 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B168" s="18" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C168" s="18" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D168" s="1" t="n">
         <v>8</v>
@@ -8654,138 +8666,138 @@
         <v>34</v>
       </c>
       <c r="I168" s="18" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="J168" s="1" t="n">
         <f aca="false">J167+D167</f>
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="K168" s="1" t="n">
         <f aca="false">J168/8</f>
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L168" s="1" t="n">
         <f aca="false">J168/16</f>
-        <v>25.5</v>
+        <v>25</v>
       </c>
       <c r="M168" s="1" t="n">
         <f aca="false">J168/32</f>
-        <v>12.75</v>
+        <v>12.5</v>
       </c>
       <c r="N168" s="1" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="O168" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P168" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q168" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B169" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="C169" s="3" t="s">
-        <v>358</v>
+      <c r="B169" s="18" t="s">
+        <v>359</v>
+      </c>
+      <c r="C169" s="18" t="s">
+        <v>360</v>
       </c>
       <c r="D169" s="1" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E169" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="F169" s="27" t="s">
-        <v>65</v>
-      </c>
+      <c r="F169" s="27"/>
       <c r="G169" s="18" t="n">
         <v>0</v>
       </c>
       <c r="H169" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I169" s="3" t="s">
-        <v>357</v>
+      <c r="I169" s="18" t="s">
+        <v>359</v>
       </c>
       <c r="J169" s="1" t="n">
         <f aca="false">J168+D168</f>
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="K169" s="1" t="n">
         <f aca="false">J169/8</f>
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L169" s="1" t="n">
         <f aca="false">J169/16</f>
-        <v>26</v>
+        <v>25.5</v>
       </c>
       <c r="M169" s="1" t="n">
         <f aca="false">J169/32</f>
-        <v>13</v>
+        <v>12.75</v>
       </c>
       <c r="N169" s="1" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="O169" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P169" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q169" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B170" s="18" t="s">
-        <v>359</v>
-      </c>
-      <c r="C170" s="18" t="s">
-        <v>360</v>
+      <c r="B170" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>362</v>
       </c>
       <c r="D170" s="1" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E170" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="F170" s="27"/>
+      <c r="F170" s="27" t="s">
+        <v>65</v>
+      </c>
       <c r="G170" s="18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H170" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I170" s="18" t="s">
-        <v>359</v>
+      <c r="I170" s="3" t="s">
+        <v>361</v>
       </c>
       <c r="J170" s="1" t="n">
         <f aca="false">J169+D169</f>
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="K170" s="1" t="n">
         <f aca="false">J170/8</f>
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L170" s="1" t="n">
         <f aca="false">J170/16</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M170" s="1" t="n">
         <f aca="false">J170/32</f>
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="N170" s="1" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="O170" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P170" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q170" s="1" t="n">
         <v>0</v>
@@ -8793,10 +8805,10 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B171" s="18" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C171" s="18" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D171" s="1" t="n">
         <v>8</v>
@@ -8816,28 +8828,28 @@
       </c>
       <c r="J171" s="1" t="n">
         <f aca="false">J170+D170</f>
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="K171" s="1" t="n">
         <f aca="false">J171/8</f>
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L171" s="1" t="n">
         <f aca="false">J171/16</f>
-        <v>27.5</v>
+        <v>27</v>
       </c>
       <c r="M171" s="1" t="n">
         <f aca="false">J171/32</f>
-        <v>13.75</v>
+        <v>13.5</v>
       </c>
       <c r="N171" s="1" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="O171" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P171" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q171" s="1" t="n">
         <v>0</v>
@@ -8845,10 +8857,10 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B172" s="18" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C172" s="18" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D172" s="1" t="n">
         <v>8</v>
@@ -8864,117 +8876,175 @@
         <v>34</v>
       </c>
       <c r="I172" s="18" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J172" s="1" t="n">
         <f aca="false">J171+D171</f>
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="K172" s="1" t="n">
         <f aca="false">J172/8</f>
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L172" s="1" t="n">
         <f aca="false">J172/16</f>
-        <v>28</v>
+        <v>27.5</v>
       </c>
       <c r="M172" s="1" t="n">
         <f aca="false">J172/32</f>
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="N172" s="1" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="O172" s="3" t="n">
         <v>2</v>
       </c>
       <c r="P172" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q172" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B173" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="C173" s="3" t="s">
+      <c r="B173" s="18" t="s">
         <v>368</v>
       </c>
+      <c r="C173" s="18" t="s">
+        <v>369</v>
+      </c>
       <c r="D173" s="1" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E173" s="27" t="s">
-        <v>369</v>
+        <v>25</v>
       </c>
       <c r="F173" s="27"/>
       <c r="G173" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H173" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="I173" s="27" t="s">
-        <v>264</v>
+      <c r="I173" s="18" t="s">
+        <v>370</v>
       </c>
       <c r="J173" s="1" t="n">
         <f aca="false">J172+D172</f>
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="K173" s="1" t="n">
         <f aca="false">J173/8</f>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L173" s="1" t="n">
         <f aca="false">J173/16</f>
-        <v>28.5</v>
+        <v>28</v>
       </c>
       <c r="M173" s="1" t="n">
         <f aca="false">J173/32</f>
-        <v>14.25</v>
+        <v>14</v>
       </c>
       <c r="N173" s="1" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="O173" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P173" s="1" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q173" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="1" t="s">
-        <v>45</v>
+      <c r="B174" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D174" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="E174" s="27" t="s">
+        <v>373</v>
       </c>
       <c r="F174" s="27"/>
-      <c r="G174" s="27"/>
-      <c r="H174" s="27"/>
-      <c r="I174" s="27"/>
+      <c r="G174" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="I174" s="27" t="s">
+        <v>268</v>
+      </c>
       <c r="J174" s="1" t="n">
         <f aca="false">J173+D173</f>
-        <v>480</v>
+        <v>456</v>
       </c>
       <c r="K174" s="1" t="n">
         <f aca="false">J174/8</f>
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="L174" s="1" t="n">
         <f aca="false">J174/16</f>
-        <v>30</v>
+        <v>28.5</v>
       </c>
       <c r="M174" s="1" t="n">
         <f aca="false">J174/32</f>
+        <v>14.25</v>
+      </c>
+      <c r="N174" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O174" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q174" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F175" s="27"/>
+      <c r="G175" s="27"/>
+      <c r="H175" s="27"/>
+      <c r="I175" s="27"/>
+      <c r="J175" s="1" t="n">
+        <f aca="false">J174+D174</f>
+        <v>480</v>
+      </c>
+      <c r="K175" s="1" t="n">
+        <f aca="false">J175/8</f>
+        <v>60</v>
+      </c>
+      <c r="L175" s="1" t="n">
+        <f aca="false">J175/16</f>
+        <v>30</v>
+      </c>
+      <c r="M175" s="1" t="n">
+        <f aca="false">J175/32</f>
         <v>15</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B175" s="1"/>
-    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B176" s="1"/>
+    </row>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -8986,10 +9056,10 @@
     <mergeCell ref="B4:I4"/>
     <mergeCell ref="B5:I5"/>
     <mergeCell ref="B18:I18"/>
-    <mergeCell ref="B50:I50"/>
+    <mergeCell ref="B39:I39"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A126" r:id="rId1" display="Structure:rt1Errors_t,file:rt1ErrorsDownlink.h"/>
+    <hyperlink ref="A127" r:id="rId1" display="Structure:rt1Errors_t,file:rt1ErrorsDownlink.h"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -9007,7 +9077,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B6:I20"/>
-  <sheetFormatPr defaultColWidth="9.34375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.35546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.14"/>
@@ -9017,22 +9087,22 @@
     <row r="6" s="34" customFormat="true" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="35"/>
       <c r="C6" s="35" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H6" s="35" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="I6" s="35"/>
     </row>
